--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -3894,64 +3894,66 @@
       </c>
     </row>
     <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>Ⅱ-52</t>
         </is>
       </c>
-      <c r="B56" s="12" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>Ⅱ 計画策定</t>
         </is>
       </c>
-      <c r="C56" s="12" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>Ⅱ-1 基礎調査</t>
         </is>
       </c>
-      <c r="D56" s="13" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>前提条件と基本的課題の明確化</t>
         </is>
       </c>
-      <c r="E56" s="11" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>仕様書4Ⅱ(1)</t>
         </is>
       </c>
-      <c r="F56" s="11" t="inlineStr">
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G56" s="13" t="inlineStr">
+      <c r="G56" s="7" t="inlineStr">
         <is>
           <t>課題整理メモ</t>
         </is>
       </c>
-      <c r="H56" s="13" t="inlineStr"/>
-      <c r="I56" s="11" t="inlineStr">
+      <c r="H56" s="7" t="inlineStr"/>
+      <c r="I56" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J56" s="14" t="n"/>
-      <c r="K56" s="14" t="n"/>
-      <c r="L56" s="14" t="n">
+      <c r="J56" s="8" t="n"/>
+      <c r="K56" s="8" t="n"/>
+      <c r="L56" s="8" t="n">
         <v>46265</v>
       </c>
-      <c r="M56" s="14" t="n"/>
-      <c r="N56" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O56" s="16" t="inlineStr">
-        <is>
-          <t>着手</t>
-        </is>
-      </c>
-      <c r="P56" s="13" t="inlineStr">
-        <is>
-          <t>認定率上位31%／費用額下位25%というギャップを中心論点として特定（doc09）。</t>
+      <c r="M56" s="8" t="n">
+        <v>46265</v>
+      </c>
+      <c r="N56" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O56" s="10" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="P56" s="7" t="inlineStr">
+        <is>
+          <t>doc11として整理完了。前提条件4区分＋基本的課題5本。国の基本指針は未告示のため告示後に追記。</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4072,7 @@
       </c>
       <c r="M58" s="14" t="n"/>
       <c r="N58" s="15" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="O58" s="16" t="inlineStr">
         <is>
@@ -4079,7 +4081,7 @@
       </c>
       <c r="P58" s="13" t="inlineStr">
         <is>
-          <t>交付金評価の0点項目21件を施策候補として一覧化（doc07§5）。</t>
+          <t>doc14で第9期施策19本を評価。村単独事業の実績資料が未受領のため一部保留。</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4200,7 @@
       </c>
       <c r="M60" s="14" t="n"/>
       <c r="N60" s="15" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O60" s="16" t="inlineStr">
         <is>
@@ -4207,135 +4209,139 @@
       </c>
       <c r="P60" s="13" t="inlineStr">
         <is>
-          <t>第9期概要版①〜⑦と実績を全項目突合済（doc08）。令和6年度決算入手で確定。</t>
+          <t>doc12として計画書掲載様式（表2-16〜2-19）に整理完了。令和6年度決算と地域支援事業費の集計範囲の確認で確定。</t>
         </is>
       </c>
     </row>
     <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="11" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>Ⅱ-57</t>
         </is>
       </c>
-      <c r="B61" s="12" t="inlineStr">
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>Ⅱ 計画策定</t>
         </is>
       </c>
-      <c r="C61" s="12" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
         <is>
           <t>Ⅱ-2 現行計画の評価</t>
         </is>
       </c>
-      <c r="D61" s="13" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>課題の整理</t>
         </is>
       </c>
-      <c r="E61" s="11" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>仕様書4Ⅱ(2)</t>
         </is>
       </c>
-      <c r="F61" s="11" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G61" s="13" t="inlineStr">
+      <c r="G61" s="7" t="inlineStr">
         <is>
           <t>課題一覧</t>
         </is>
       </c>
-      <c r="H61" s="13" t="inlineStr"/>
-      <c r="I61" s="11" t="inlineStr">
+      <c r="H61" s="7" t="inlineStr"/>
+      <c r="I61" s="4" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J61" s="14" t="n"/>
-      <c r="K61" s="14" t="n"/>
-      <c r="L61" s="14" t="n">
+      <c r="J61" s="8" t="n"/>
+      <c r="K61" s="8" t="n"/>
+      <c r="L61" s="8" t="n">
         <v>46265</v>
       </c>
-      <c r="M61" s="14" t="n"/>
-      <c r="N61" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O61" s="16" t="inlineStr">
-        <is>
-          <t>着手</t>
-        </is>
-      </c>
-      <c r="P61" s="13" t="inlineStr">
-        <is>
-          <t>軽度者の重度化・総合事業の受け皿不在・保険料と費用額の逆転を抽出済。</t>
+      <c r="M61" s="8" t="n">
+        <v>46265</v>
+      </c>
+      <c r="N61" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" s="10" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="P61" s="7" t="inlineStr">
+        <is>
+          <t>doc11で基本的課題5本に集約完了。各課題を交付金評価指標と対応づけ。</t>
         </is>
       </c>
     </row>
     <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="11" t="inlineStr">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t>Ⅱ-58</t>
         </is>
       </c>
-      <c r="B62" s="12" t="inlineStr">
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>Ⅱ 計画策定</t>
         </is>
       </c>
-      <c r="C62" s="12" t="inlineStr">
+      <c r="C62" s="6" t="inlineStr">
         <is>
           <t>Ⅱ-3 見込量・保険料</t>
         </is>
       </c>
-      <c r="D62" s="13" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>将来人口の整理（2040年度含む中長期）</t>
         </is>
       </c>
-      <c r="E62" s="11" t="inlineStr">
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>仕様書4Ⅱ(3)</t>
         </is>
       </c>
-      <c r="F62" s="11" t="inlineStr">
+      <c r="F62" s="4" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G62" s="13" t="inlineStr">
+      <c r="G62" s="7" t="inlineStr">
         <is>
           <t>人口推計表</t>
         </is>
       </c>
-      <c r="H62" s="13" t="inlineStr">
+      <c r="H62" s="7" t="inlineStr">
         <is>
           <t>社人研の新推計（2050年まで）に差し替え</t>
         </is>
       </c>
-      <c r="I62" s="11" t="inlineStr">
+      <c r="I62" s="4" t="inlineStr">
         <is>
           <t>R8.11〜12</t>
         </is>
       </c>
-      <c r="J62" s="14" t="n"/>
-      <c r="K62" s="14" t="n"/>
-      <c r="L62" s="14" t="n">
+      <c r="J62" s="8" t="n"/>
+      <c r="K62" s="8" t="n"/>
+      <c r="L62" s="8" t="n">
         <v>46265</v>
       </c>
-      <c r="M62" s="14" t="n"/>
-      <c r="N62" s="15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O62" s="16" t="inlineStr">
-        <is>
-          <t>着手</t>
-        </is>
-      </c>
-      <c r="P62" s="13" t="inlineStr">
-        <is>
-          <t>P1により2050年まで整理済（doc09§3）。高齢者数は2020年ピーク、75歳以上は2030年ピーク。</t>
+      <c r="M62" s="8" t="n">
+        <v>46265</v>
+      </c>
+      <c r="N62" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" s="10" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="P62" s="7" t="inlineStr">
+        <is>
+          <t>doc13として2050年まで整理完了。高齢者数は2020年ピーク、75歳以上は2030年ピーク。</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4398,7 @@
       </c>
       <c r="M63" s="14" t="n"/>
       <c r="N63" s="15" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="O63" s="16" t="inlineStr">
         <is>
@@ -4401,7 +4407,7 @@
       </c>
       <c r="P63" s="13" t="inlineStr">
         <is>
-          <t>社人研推計が住基ベース実績より6〜8%少ない点を特定し補正方針を提示（doc09§4）。村合意待ち。</t>
+          <t>doc13で前期・後期別の乖離率補正により令和9〜11年度末を算定（1,002／997／990人）。scripts/estimate_population.pyで再現可能。補正手法の村合意と国ワークシートで確定。</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4464,7 @@
       </c>
       <c r="M64" s="14" t="n"/>
       <c r="N64" s="15" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="O64" s="16" t="inlineStr">
         <is>
@@ -4467,7 +4473,7 @@
       </c>
       <c r="P64" s="13" t="inlineStr">
         <is>
-          <t>要支援1が6年で3倍という実績を把握済。要介護度別推計は基本指針・ワークシート待ち。</t>
+          <t>doc13で年齢階級別認定率（前期6.49%／後期34.87%）による参考試算を実施（214→230人）。要介護度別推計は国ワークシート待ち。</t>
         </is>
       </c>
     </row>
@@ -4784,64 +4790,66 @@
       </c>
     </row>
     <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="11" t="inlineStr">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>Ⅱ-66</t>
         </is>
       </c>
-      <c r="B70" s="12" t="inlineStr">
+      <c r="B70" s="6" t="inlineStr">
         <is>
           <t>Ⅱ 計画策定</t>
         </is>
       </c>
-      <c r="C70" s="12" t="inlineStr">
+      <c r="C70" s="6" t="inlineStr">
         <is>
           <t>Ⅱ-4 高齢者福祉施策</t>
         </is>
       </c>
-      <c r="D70" s="13" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>現行計画の成果と課題の整理</t>
         </is>
       </c>
-      <c r="E70" s="11" t="inlineStr">
+      <c r="E70" s="4" t="inlineStr">
         <is>
           <t>仕様書4Ⅱ(4)</t>
         </is>
       </c>
-      <c r="F70" s="11" t="inlineStr">
+      <c r="F70" s="4" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G70" s="13" t="inlineStr">
+      <c r="G70" s="7" t="inlineStr">
         <is>
           <t>整理メモ</t>
         </is>
       </c>
-      <c r="H70" s="13" t="inlineStr"/>
-      <c r="I70" s="11" t="inlineStr">
+      <c r="H70" s="7" t="inlineStr"/>
+      <c r="I70" s="4" t="inlineStr">
         <is>
           <t>R8.11〜12</t>
         </is>
       </c>
-      <c r="J70" s="14" t="n"/>
-      <c r="K70" s="14" t="n"/>
-      <c r="L70" s="14" t="n">
+      <c r="J70" s="8" t="n"/>
+      <c r="K70" s="8" t="n"/>
+      <c r="L70" s="8" t="n">
         <v>46265</v>
       </c>
-      <c r="M70" s="14" t="n"/>
-      <c r="N70" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O70" s="16" t="inlineStr">
-        <is>
-          <t>着手</t>
-        </is>
-      </c>
-      <c r="P70" s="13" t="inlineStr">
-        <is>
-          <t>第9期施策体系と実績の突合を実施済（doc08§6）。</t>
+      <c r="M70" s="8" t="n">
+        <v>46265</v>
+      </c>
+      <c r="N70" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O70" s="10" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="P70" s="7" t="inlineStr">
+        <is>
+          <t>doc14として第9期の施策19本を4段階（◎○△✗）で評価完了。</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4906,7 @@
       </c>
       <c r="M71" s="14" t="n"/>
       <c r="N71" s="15" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="O71" s="16" t="inlineStr">
         <is>
@@ -4907,7 +4915,7 @@
       </c>
       <c r="P71" s="13" t="inlineStr">
         <is>
-          <t>0点項目21件を新規・強化、在宅医療介護連携／認知症を継続として整理。</t>
+          <t>doc14として施策案28本（継続11／強化7／新規9／改称1）を整理。基本目標5「計画の推進と進捗管理」の新設を提案。国の基本指針で追加・修正の可能性。</t>
         </is>
       </c>
     </row>
@@ -5088,60 +5096,66 @@
       <c r="P74" s="20" t="inlineStr"/>
     </row>
     <row r="75" ht="30" customHeight="1">
-      <c r="A75" s="23" t="inlineStr">
+      <c r="A75" s="11" t="inlineStr">
         <is>
           <t>Ⅱ-71</t>
         </is>
       </c>
-      <c r="B75" s="24" t="inlineStr">
+      <c r="B75" s="12" t="inlineStr">
         <is>
           <t>Ⅱ 計画策定</t>
         </is>
       </c>
-      <c r="C75" s="24" t="inlineStr">
+      <c r="C75" s="12" t="inlineStr">
         <is>
           <t>Ⅱ-6 計画案の検討</t>
         </is>
       </c>
-      <c r="D75" s="25" t="inlineStr">
+      <c r="D75" s="13" t="inlineStr">
         <is>
           <t>施策体系の整理</t>
         </is>
       </c>
-      <c r="E75" s="23" t="inlineStr">
+      <c r="E75" s="11" t="inlineStr">
         <is>
           <t>仕様書4Ⅱ(6)</t>
         </is>
       </c>
-      <c r="F75" s="23" t="inlineStr">
+      <c r="F75" s="11" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G75" s="25" t="inlineStr">
+      <c r="G75" s="13" t="inlineStr">
         <is>
           <t>施策体系図</t>
         </is>
       </c>
-      <c r="H75" s="25" t="inlineStr"/>
-      <c r="I75" s="23" t="inlineStr">
+      <c r="H75" s="13" t="inlineStr"/>
+      <c r="I75" s="11" t="inlineStr">
         <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="J75" s="26" t="n"/>
-      <c r="K75" s="26" t="n"/>
-      <c r="L75" s="26" t="n"/>
-      <c r="M75" s="26" t="n"/>
-      <c r="N75" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P75" s="25" t="inlineStr"/>
+      <c r="J75" s="14" t="n"/>
+      <c r="K75" s="14" t="n"/>
+      <c r="L75" s="14" t="n">
+        <v>46265</v>
+      </c>
+      <c r="M75" s="14" t="n"/>
+      <c r="N75" s="15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O75" s="16" t="inlineStr">
+        <is>
+          <t>着手</t>
+        </is>
+      </c>
+      <c r="P75" s="13" t="inlineStr">
+        <is>
+          <t>doc14で施策体系案を作成。基本目標5の独立可否は村と要協議。</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="18" t="inlineStr">
@@ -5270,60 +5284,66 @@
       </c>
     </row>
     <row r="78" ht="30" customHeight="1">
-      <c r="A78" s="18" t="inlineStr">
+      <c r="A78" s="11" t="inlineStr">
         <is>
           <t>Ⅱ-74</t>
         </is>
       </c>
-      <c r="B78" s="19" t="inlineStr">
+      <c r="B78" s="12" t="inlineStr">
         <is>
           <t>Ⅱ 計画策定</t>
         </is>
       </c>
-      <c r="C78" s="19" t="inlineStr">
+      <c r="C78" s="12" t="inlineStr">
         <is>
           <t>Ⅱ-7 計画書の作成</t>
         </is>
       </c>
-      <c r="D78" s="20" t="inlineStr">
+      <c r="D78" s="13" t="inlineStr">
         <is>
           <t>骨子案の作成</t>
         </is>
       </c>
-      <c r="E78" s="18" t="inlineStr">
+      <c r="E78" s="11" t="inlineStr">
         <is>
           <t>仕様書4Ⅱ(7)</t>
         </is>
       </c>
-      <c r="F78" s="18" t="inlineStr">
+      <c r="F78" s="11" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G78" s="20" t="inlineStr">
+      <c r="G78" s="13" t="inlineStr">
         <is>
           <t>骨子案</t>
         </is>
       </c>
-      <c r="H78" s="20" t="inlineStr"/>
-      <c r="I78" s="18" t="inlineStr">
+      <c r="H78" s="13" t="inlineStr"/>
+      <c r="I78" s="11" t="inlineStr">
         <is>
           <t>R8.11〜12</t>
         </is>
       </c>
-      <c r="J78" s="21" t="n"/>
-      <c r="K78" s="21" t="n"/>
-      <c r="L78" s="21" t="n"/>
-      <c r="M78" s="21" t="n"/>
-      <c r="N78" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="18" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P78" s="20" t="inlineStr"/>
+      <c r="J78" s="14" t="n"/>
+      <c r="K78" s="14" t="n"/>
+      <c r="L78" s="14" t="n">
+        <v>46265</v>
+      </c>
+      <c r="M78" s="14" t="n"/>
+      <c r="N78" s="15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O78" s="16" t="inlineStr">
+        <is>
+          <t>着手</t>
+        </is>
+      </c>
+      <c r="P78" s="13" t="inlineStr">
+        <is>
+          <t>doc15として全6章の章構成・節構成・想定頁数を整理。第2章に「保険者機能の評価」「第9期計画の進捗と評価」を新設。第2・3・6章は執筆可能、第5章は国ワークシート待ち。</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="23" t="inlineStr">
@@ -6498,7 +6518,7 @@
       </c>
       <c r="M98" s="14" t="n"/>
       <c r="N98" s="15" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="O98" s="16" t="inlineStr">
         <is>
@@ -6507,7 +6527,7 @@
       </c>
       <c r="P98" s="13" t="inlineStr">
         <is>
-          <t>通期。調査票発送前までに保管ルールを文書化。</t>
+          <t>doc16として管理ルールを文書化完了（10項目のチェックリスト付）。村との合意・従事者名簿・誓約書は未実施。</t>
         </is>
       </c>
     </row>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -5040,60 +5040,68 @@
       <c r="P73" s="25" t="inlineStr"/>
     </row>
     <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="18" t="inlineStr">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>Ⅱ-70</t>
         </is>
       </c>
-      <c r="B74" s="19" t="inlineStr">
+      <c r="B74" s="6" t="inlineStr">
         <is>
           <t>Ⅱ 計画策定</t>
         </is>
       </c>
-      <c r="C74" s="19" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>Ⅱ-6 計画案の検討</t>
         </is>
       </c>
-      <c r="D74" s="20" t="inlineStr">
+      <c r="D74" s="7" t="inlineStr">
         <is>
           <t>第10期の課題の整理</t>
         </is>
       </c>
-      <c r="E74" s="18" t="inlineStr">
+      <c r="E74" s="4" t="inlineStr">
         <is>
           <t>仕様書4Ⅱ(6)</t>
         </is>
       </c>
-      <c r="F74" s="18" t="inlineStr">
+      <c r="F74" s="4" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G74" s="20" t="inlineStr">
+      <c r="G74" s="7" t="inlineStr">
         <is>
           <t>課題整理</t>
         </is>
       </c>
-      <c r="H74" s="20" t="inlineStr"/>
-      <c r="I74" s="18" t="inlineStr">
+      <c r="H74" s="7" t="inlineStr"/>
+      <c r="I74" s="4" t="inlineStr">
         <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="J74" s="21" t="n"/>
-      <c r="K74" s="21" t="n"/>
-      <c r="L74" s="21" t="n"/>
-      <c r="M74" s="21" t="n"/>
-      <c r="N74" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="18" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P74" s="20" t="inlineStr"/>
+      <c r="J74" s="8" t="n"/>
+      <c r="K74" s="8" t="n"/>
+      <c r="L74" s="8" t="n">
+        <v>46265</v>
+      </c>
+      <c r="M74" s="8" t="n">
+        <v>46265</v>
+      </c>
+      <c r="N74" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O74" s="10" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="P74" s="7" t="inlineStr">
+        <is>
+          <t>doc11で基本的課題5本、doc17で第9期計画の課題20件（重大度A 13件）を洗い出し完了。</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="11" t="inlineStr">
@@ -5144,7 +5152,7 @@
       </c>
       <c r="M75" s="14" t="n"/>
       <c r="N75" s="15" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="O75" s="16" t="inlineStr">
         <is>
@@ -5153,7 +5161,7 @@
       </c>
       <c r="P75" s="13" t="inlineStr">
         <is>
-          <t>doc14で施策体系案を作成。基本目標5の独立可否は村と要協議。</t>
+          <t>doc14・doc18で施策体系（基本目標5本・施策28本）を確定。基本目標5の独立可否は村と要協議。</t>
         </is>
       </c>
     </row>
@@ -5284,122 +5292,130 @@
       </c>
     </row>
     <row r="78" ht="30" customHeight="1">
-      <c r="A78" s="11" t="inlineStr">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>Ⅱ-74</t>
         </is>
       </c>
-      <c r="B78" s="12" t="inlineStr">
+      <c r="B78" s="6" t="inlineStr">
         <is>
           <t>Ⅱ 計画策定</t>
         </is>
       </c>
-      <c r="C78" s="12" t="inlineStr">
+      <c r="C78" s="6" t="inlineStr">
         <is>
           <t>Ⅱ-7 計画書の作成</t>
         </is>
       </c>
-      <c r="D78" s="13" t="inlineStr">
+      <c r="D78" s="7" t="inlineStr">
         <is>
           <t>骨子案の作成</t>
         </is>
       </c>
-      <c r="E78" s="11" t="inlineStr">
+      <c r="E78" s="4" t="inlineStr">
         <is>
           <t>仕様書4Ⅱ(7)</t>
         </is>
       </c>
-      <c r="F78" s="11" t="inlineStr">
+      <c r="F78" s="4" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G78" s="13" t="inlineStr">
+      <c r="G78" s="7" t="inlineStr">
         <is>
           <t>骨子案</t>
         </is>
       </c>
-      <c r="H78" s="13" t="inlineStr"/>
-      <c r="I78" s="11" t="inlineStr">
+      <c r="H78" s="7" t="inlineStr"/>
+      <c r="I78" s="4" t="inlineStr">
         <is>
           <t>R8.11〜12</t>
         </is>
       </c>
-      <c r="J78" s="14" t="n"/>
-      <c r="K78" s="14" t="n"/>
-      <c r="L78" s="14" t="n">
+      <c r="J78" s="8" t="n"/>
+      <c r="K78" s="8" t="n"/>
+      <c r="L78" s="8" t="n">
         <v>46265</v>
       </c>
-      <c r="M78" s="14" t="n"/>
-      <c r="N78" s="15" t="n">
+      <c r="M78" s="8" t="n">
+        <v>46265</v>
+      </c>
+      <c r="N78" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O78" s="10" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="P78" s="7" t="inlineStr">
+        <is>
+          <t>doc15として全6章の章構成・節構成・想定頁数を確定。素案の作成に移行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>Ⅱ 計画策定</t>
+        </is>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>Ⅱ-7 計画書の作成</t>
+        </is>
+      </c>
+      <c r="D79" s="13" t="inlineStr">
+        <is>
+          <t>素案の作成</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>仕様書4Ⅱ(7)</t>
+        </is>
+      </c>
+      <c r="F79" s="11" t="inlineStr">
+        <is>
+          <t>受託者</t>
+        </is>
+      </c>
+      <c r="G79" s="13" t="inlineStr">
+        <is>
+          <t>素案</t>
+        </is>
+      </c>
+      <c r="H79" s="13" t="inlineStr"/>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>R8.12〜R9.1</t>
+        </is>
+      </c>
+      <c r="J79" s="14" t="n"/>
+      <c r="K79" s="14" t="n"/>
+      <c r="L79" s="14" t="n">
+        <v>46265</v>
+      </c>
+      <c r="M79" s="14" t="n"/>
+      <c r="N79" s="15" t="n">
         <v>0.6</v>
       </c>
-      <c r="O78" s="16" t="inlineStr">
+      <c r="O79" s="16" t="inlineStr">
         <is>
           <t>着手</t>
         </is>
       </c>
-      <c r="P78" s="13" t="inlineStr">
-        <is>
-          <t>doc15として全6章の章構成・節構成・想定頁数を整理。第2章に「保険者機能の評価」「第9期計画の進捗と評価」を新設。第2・3・6章は執筆可能、第5章は国ワークシート待ち。</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="30" customHeight="1">
-      <c r="A79" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-75</t>
-        </is>
-      </c>
-      <c r="B79" s="24" t="inlineStr">
-        <is>
-          <t>Ⅱ 計画策定</t>
-        </is>
-      </c>
-      <c r="C79" s="24" t="inlineStr">
-        <is>
-          <t>Ⅱ-7 計画書の作成</t>
-        </is>
-      </c>
-      <c r="D79" s="25" t="inlineStr">
-        <is>
-          <t>素案の作成</t>
-        </is>
-      </c>
-      <c r="E79" s="23" t="inlineStr">
-        <is>
-          <t>仕様書4Ⅱ(7)</t>
-        </is>
-      </c>
-      <c r="F79" s="23" t="inlineStr">
-        <is>
-          <t>受託者</t>
-        </is>
-      </c>
-      <c r="G79" s="25" t="inlineStr">
-        <is>
-          <t>素案</t>
-        </is>
-      </c>
-      <c r="H79" s="25" t="inlineStr"/>
-      <c r="I79" s="23" t="inlineStr">
-        <is>
-          <t>R8.12〜R9.1</t>
-        </is>
-      </c>
-      <c r="J79" s="26" t="n"/>
-      <c r="K79" s="26" t="n"/>
-      <c r="L79" s="26" t="n"/>
-      <c r="M79" s="26" t="n"/>
-      <c r="N79" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P79" s="25" t="inlineStr"/>
+      <c r="P79" s="13" t="inlineStr">
+        <is>
+          <t>doc18／output/06_計画素案.docx として全6章・63節・56表を作成。第1〜4章・第6章は本文執筆済。第5章は国ワークシート待ちのため枠組みのみ。【要確認】【要設定】を明示。</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="11" t="inlineStr">

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$101</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6753,7 +6753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7600,17 +7600,17 @@
       </c>
       <c r="D25" s="25" t="inlineStr">
         <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。</t>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t>doc02§17,doc07</t>
+          <t>doc02§17,doc07,doc18 4-1</t>
         </is>
       </c>
       <c r="G25" s="23" t="inlineStr">
@@ -7628,27 +7628,27 @@
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C26" s="25" t="inlineStr">
         <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
         </is>
       </c>
       <c r="D26" s="25" t="inlineStr">
         <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
         </is>
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-56,Ⅱ-75</t>
         </is>
       </c>
       <c r="F26" s="23" t="inlineStr">
         <is>
-          <t>doc07§4</t>
+          <t>doc17 C-1,doc02§20-2</t>
         </is>
       </c>
       <c r="G26" s="23" t="inlineStr">
@@ -7666,27 +7666,27 @@
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C27" s="25" t="inlineStr">
         <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
         </is>
       </c>
       <c r="D27" s="25" t="inlineStr">
         <is>
-          <t>評価指標の読み方に影響。</t>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
         </is>
       </c>
       <c r="E27" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-60,Ⅱ-65</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t>doc07§8-4</t>
+          <t>doc13§6</t>
         </is>
       </c>
       <c r="G27" s="23" t="inlineStr">
@@ -7709,22 +7709,22 @@
       </c>
       <c r="C28" s="25" t="inlineStr">
         <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
         </is>
       </c>
       <c r="D28" s="25" t="inlineStr">
         <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
         </is>
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F28" s="23" t="inlineStr">
         <is>
-          <t>doc08§4,§8-2</t>
+          <t>doc07§4</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="C29" s="25" t="inlineStr">
         <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
         </is>
       </c>
       <c r="D29" s="25" t="inlineStr">
         <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+          <t>評価指標の読み方に影響。</t>
         </is>
       </c>
       <c r="E29" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t>doc02§20-1</t>
+          <t>doc07§8-4</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr">
@@ -7780,27 +7780,27 @@
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C30" s="25" t="inlineStr">
         <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
         </is>
       </c>
       <c r="D30" s="25" t="inlineStr">
         <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
         </is>
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F30" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-4</t>
+          <t>doc08§4,§8-2</t>
         </is>
       </c>
       <c r="G30" s="23" t="inlineStr">
@@ -7818,27 +7818,27 @@
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C31" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
         </is>
       </c>
       <c r="D31" s="25" t="inlineStr">
         <is>
-          <t>第9期は基本目標4に内包する構成。</t>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-73</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t>doc01-5</t>
+          <t>doc02§20-1</t>
         </is>
       </c>
       <c r="G31" s="23" t="inlineStr">
@@ -7856,318 +7856,622 @@
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
+          <t>素案</t>
+        </is>
+      </c>
+      <c r="C32" s="25" t="inlineStr">
+        <is>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+        </is>
+      </c>
+      <c r="D32" s="25" t="inlineStr">
+        <is>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>doc15,doc18</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H32" s="25" t="inlineStr"/>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>素案</t>
+        </is>
+      </c>
+      <c r="C33" s="25" t="inlineStr">
+        <is>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+        </is>
+      </c>
+      <c r="D33" s="25" t="inlineStr">
+        <is>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-71,Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>doc14§5,doc18 3-1</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H33" s="25" t="inlineStr"/>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>素案</t>
+        </is>
+      </c>
+      <c r="C34" s="25" t="inlineStr">
+        <is>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+        </is>
+      </c>
+      <c r="D34" s="25" t="inlineStr">
+        <is>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-71,Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>doc14§5,doc15,doc18 4-5</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H34" s="25" t="inlineStr"/>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>素案</t>
+        </is>
+      </c>
+      <c r="C35" s="25" t="inlineStr">
+        <is>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+        </is>
+      </c>
+      <c r="D35" s="25" t="inlineStr">
+        <is>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>doc17 B-3,doc18 4-3</t>
+        </is>
+      </c>
+      <c r="G35" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H35" s="25" t="inlineStr"/>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>素案</t>
+        </is>
+      </c>
+      <c r="C36" s="25" t="inlineStr">
+        <is>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+        </is>
+      </c>
+      <c r="D36" s="25" t="inlineStr">
+        <is>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+        </is>
+      </c>
+      <c r="E36" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="inlineStr">
+        <is>
+          <t>doc17 A-1,doc18 2-9</t>
+        </is>
+      </c>
+      <c r="G36" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H36" s="25" t="inlineStr"/>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>素案</t>
+        </is>
+      </c>
+      <c r="C37" s="25" t="inlineStr">
+        <is>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+        </is>
+      </c>
+      <c r="D37" s="25" t="inlineStr">
+        <is>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+        </is>
+      </c>
+      <c r="E37" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-64,Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F37" s="23" t="inlineStr">
+        <is>
+          <t>doc17 A-1,doc18 5-7</t>
+        </is>
+      </c>
+      <c r="G37" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H37" s="25" t="inlineStr"/>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="inlineStr">
+        <is>
           <t>計画構成</t>
         </is>
       </c>
-      <c r="C32" s="25" t="inlineStr">
+      <c r="C38" s="25" t="inlineStr">
+        <is>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
+        </is>
+      </c>
+      <c r="D38" s="25" t="inlineStr">
+        <is>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+        </is>
+      </c>
+      <c r="E38" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F38" s="23" t="inlineStr">
+        <is>
+          <t>doc08§8-4</t>
+        </is>
+      </c>
+      <c r="G38" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H38" s="25" t="inlineStr"/>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C39" s="25" t="inlineStr">
+        <is>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+        </is>
+      </c>
+      <c r="D39" s="25" t="inlineStr">
+        <is>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+        </is>
+      </c>
+      <c r="E39" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-73,Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F39" s="23" t="inlineStr">
+        <is>
+          <t>doc01-5,doc18 1-2</t>
+        </is>
+      </c>
+      <c r="G39" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H39" s="25" t="inlineStr"/>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B40" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C40" s="25" t="inlineStr">
         <is>
           <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
         </is>
       </c>
-      <c r="D32" s="25" t="inlineStr">
+      <c r="D40" s="25" t="inlineStr">
         <is>
           <t>施策の書きぶりに影響。</t>
         </is>
       </c>
-      <c r="E32" s="23" t="inlineStr">
+      <c r="E40" s="23" t="inlineStr">
         <is>
           <t>Ⅱ-71,Ⅱ-72</t>
         </is>
       </c>
-      <c r="F32" s="23" t="inlineStr">
+      <c r="F40" s="23" t="inlineStr">
         <is>
           <t>doc01-12</t>
         </is>
       </c>
-      <c r="G32" s="23" t="inlineStr">
+      <c r="G40" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H32" s="25" t="inlineStr"/>
-    </row>
-    <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="34" t="inlineStr">
+      <c r="H40" s="25" t="inlineStr"/>
+    </row>
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="34" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B33" s="24" t="inlineStr">
+      <c r="B41" s="24" t="inlineStr">
         <is>
           <t>委員会</t>
         </is>
       </c>
-      <c r="C33" s="25" t="inlineStr">
+      <c r="C41" s="25" t="inlineStr">
         <is>
           <t>策定委員会の委員改選時期・第1回開催希望時期・開催形式（対面／オンライン）</t>
         </is>
       </c>
-      <c r="D33" s="25" t="inlineStr">
+      <c r="D41" s="25" t="inlineStr">
         <is>
           <t>会議資料の作成時期が決まる。</t>
         </is>
       </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="E41" s="23" t="inlineStr">
         <is>
           <t>Ⅱ-80,Ⅱ-81</t>
         </is>
       </c>
-      <c r="F33" s="23" t="inlineStr">
+      <c r="F41" s="23" t="inlineStr">
         <is>
           <t>doc01-6</t>
         </is>
       </c>
-      <c r="G33" s="23" t="inlineStr">
+      <c r="G41" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H33" s="25" t="inlineStr"/>
-    </row>
-    <row r="34" ht="34" customHeight="1">
-      <c r="A34" s="34" t="inlineStr">
+      <c r="H41" s="25" t="inlineStr"/>
+    </row>
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="34" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B34" s="24" t="inlineStr">
+      <c r="B42" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C34" s="25" t="inlineStr">
+      <c r="C42" s="25" t="inlineStr">
         <is>
           <t>パブリックコメントの実施時期・実施主体と意見反映の締切</t>
         </is>
       </c>
-      <c r="D34" s="25" t="inlineStr">
+      <c r="D42" s="25" t="inlineStr">
         <is>
           <t>R9.1〜2の工程に直結。</t>
         </is>
       </c>
-      <c r="E34" s="23" t="inlineStr">
+      <c r="E42" s="23" t="inlineStr">
         <is>
           <t>Ⅱ-76,Ⅱ-77</t>
         </is>
       </c>
-      <c r="F34" s="23" t="inlineStr">
+      <c r="F42" s="23" t="inlineStr">
         <is>
           <t>doc01-7</t>
         </is>
       </c>
-      <c r="G34" s="23" t="inlineStr">
+      <c r="G42" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H34" s="25" t="inlineStr"/>
-    </row>
-    <row r="35" ht="34" customHeight="1">
-      <c r="A35" s="34" t="inlineStr">
+      <c r="H42" s="25" t="inlineStr"/>
+    </row>
+    <row r="43" ht="34" customHeight="1">
+      <c r="A43" s="34" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B35" s="24" t="inlineStr">
+      <c r="B43" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C35" s="25" t="inlineStr">
+      <c r="C43" s="25" t="inlineStr">
         <is>
           <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
         </is>
       </c>
-      <c r="D35" s="25" t="inlineStr">
+      <c r="D43" s="25" t="inlineStr">
         <is>
           <t>第9期はA4・本文104頁・全6章＋資料編。</t>
         </is>
       </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="E43" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-89</t>
         </is>
       </c>
-      <c r="F35" s="23" t="inlineStr">
+      <c r="F43" s="23" t="inlineStr">
         <is>
           <t>doc01-10</t>
         </is>
       </c>
-      <c r="G35" s="23" t="inlineStr">
+      <c r="G43" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H35" s="25" t="inlineStr"/>
-    </row>
-    <row r="36" ht="34" customHeight="1">
-      <c r="A36" s="34" t="inlineStr">
+      <c r="H43" s="25" t="inlineStr"/>
+    </row>
+    <row r="44" ht="34" customHeight="1">
+      <c r="A44" s="34" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B36" s="24" t="inlineStr">
+      <c r="B44" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C36" s="25" t="inlineStr">
+      <c r="C44" s="25" t="inlineStr">
         <is>
           <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
         </is>
       </c>
-      <c r="D36" s="25" t="inlineStr">
+      <c r="D44" s="25" t="inlineStr">
         <is>
           <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
         </is>
       </c>
-      <c r="E36" s="23" t="inlineStr">
+      <c r="E44" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-92</t>
         </is>
       </c>
-      <c r="F36" s="23" t="inlineStr">
+      <c r="F44" s="23" t="inlineStr">
         <is>
           <t>doc01-10,doc08</t>
         </is>
       </c>
-      <c r="G36" s="23" t="inlineStr">
+      <c r="G44" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H36" s="25" t="inlineStr"/>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="35" t="inlineStr">
+      <c r="H44" s="25" t="inlineStr"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="35" t="inlineStr">
         <is>
           <t>■ 解決済み（記録）</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="34" customHeight="1">
-      <c r="A39" s="36" t="inlineStr">
+    <row r="47" ht="34" customHeight="1">
+      <c r="A47" s="36" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="B39" s="37" t="inlineStr">
+      <c r="B47" s="37" t="inlineStr">
         <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="C39" s="38" t="inlineStr">
+      <c r="C47" s="38" t="inlineStr">
         <is>
           <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
         </is>
       </c>
-      <c r="D39" s="38" t="inlineStr">
+      <c r="D47" s="38" t="inlineStr">
         <is>
           <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
         </is>
       </c>
-      <c r="E39" s="36" t="inlineStr">
+      <c r="E47" s="36" t="inlineStr">
         <is>
           <t>Ⅱ-56,Ⅱ-58</t>
         </is>
       </c>
-      <c r="F39" s="36" t="inlineStr">
+      <c r="F47" s="36" t="inlineStr">
         <is>
           <t>doc09</t>
         </is>
       </c>
-      <c r="G39" s="36" t="inlineStr">
+      <c r="G47" s="36" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H39" s="38" t="inlineStr"/>
-    </row>
-    <row r="40" ht="34" customHeight="1">
-      <c r="A40" s="36" t="inlineStr">
+      <c r="H47" s="38" t="inlineStr"/>
+    </row>
+    <row r="48" ht="34" customHeight="1">
+      <c r="A48" s="36" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="B40" s="37" t="inlineStr">
+      <c r="B48" s="37" t="inlineStr">
         <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="C40" s="38" t="inlineStr">
+      <c r="C48" s="38" t="inlineStr">
         <is>
           <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
         </is>
       </c>
-      <c r="D40" s="38" t="inlineStr">
+      <c r="D48" s="38" t="inlineStr">
         <is>
           <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
         </is>
       </c>
-      <c r="E40" s="36" t="inlineStr">
+      <c r="E48" s="36" t="inlineStr">
         <is>
           <t>Ⅱ-59</t>
         </is>
       </c>
-      <c r="F40" s="36" t="inlineStr">
+      <c r="F48" s="36" t="inlineStr">
         <is>
           <t>doc02§20-2</t>
         </is>
       </c>
-      <c r="G40" s="36" t="inlineStr">
+      <c r="G48" s="36" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H40" s="38" t="inlineStr"/>
-    </row>
-    <row r="41" ht="34" customHeight="1">
-      <c r="A41" s="36" t="inlineStr">
+      <c r="H48" s="38" t="inlineStr"/>
+    </row>
+    <row r="49" ht="34" customHeight="1">
+      <c r="A49" s="36" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="B41" s="37" t="inlineStr">
+      <c r="B49" s="37" t="inlineStr">
         <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="C41" s="38" t="inlineStr">
+      <c r="C49" s="38" t="inlineStr">
         <is>
           <t>国の指針・様式の更新有無</t>
         </is>
       </c>
-      <c r="D41" s="38" t="inlineStr">
+      <c r="D49" s="38" t="inlineStr">
         <is>
           <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
-      <c r="E41" s="36" t="inlineStr">
+      <c r="E49" s="36" t="inlineStr">
         <is>
           <t>Ⅰ-11</t>
         </is>
       </c>
-      <c r="F41" s="36" t="inlineStr">
+      <c r="F49" s="36" t="inlineStr">
         <is>
           <t>doc04,doc05</t>
         </is>
       </c>
-      <c r="G41" s="36" t="inlineStr">
+      <c r="G49" s="36" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H41" s="38" t="inlineStr"/>
+      <c r="H49" s="38" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H36"/>
+  <autoFilter ref="A4:H44"/>
   <mergeCells count="3">
-    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A46:H46"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$101</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -91,7 +91,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -130,7 +130,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF7C80"/>
+        <fgColor rgb="00FF5050"/>
       </patternFill>
     </fill>
     <fill>
@@ -140,7 +140,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD966"/>
+        <fgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -185,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -289,16 +294,19 @@
     <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -324,10 +332,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="9" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="9" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="9" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6753,7 +6761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6776,7 +6784,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>優先度A＝令和8年9月上旬までに回答が必要（調査工程のクリティカルパス上）／B＝令和8年11〜12月までに必要（計画策定工程）／C＝随時　｜　出所の doc番号は docs/北塩原村_第10期/ 配下の分析資料に対応します</t>
+          <t>優先度S＝キックオフ会議（令和8年9月1日）で決着が必要（9月9日の入稿・9月中旬の発送を守るため）／A＝令和8年9月中に確定が必要／B＝第1回策定委員会（11月）まで／C＝第2回以降　｜　出所の doc番号は docs/北塩原村_第10期/ 配下の分析資料に対応します</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6833,7 @@
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B5" s="30" t="inlineStr">
@@ -6863,32 +6871,32 @@
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>スケジュール</t>
         </is>
       </c>
       <c r="C6" s="31" t="inlineStr">
         <is>
-          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
+          <t>宛名ラベル・配布用封筒の提供期限の前倒し可否（9/14→9/11）</t>
         </is>
       </c>
       <c r="D6" s="31" t="inlineStr">
         <is>
-          <t>連絡体制表の確定。第9期概要版の発行は住民課。</t>
+          <t>★提供が1日遅れると発送が5連休に食い込む。村作業の遅延に対する余裕がない。</t>
         </is>
       </c>
       <c r="E6" s="32" t="inlineStr">
         <is>
-          <t>０-04</t>
+          <t>Ⅰ-25,Ⅰ-26</t>
         </is>
       </c>
       <c r="F6" s="32" t="inlineStr">
         <is>
-          <t>doc01-1</t>
+          <t>doc19 指-2</t>
         </is>
       </c>
       <c r="G6" s="32" t="inlineStr">
@@ -6901,32 +6909,32 @@
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C7" s="31" t="inlineStr">
         <is>
-          <t>契約締結日・契約書の取り交わし状況</t>
+          <t>在宅介護実態調査の手法（手法Ⅲか、手法Ⅳ〈新版 在宅生活改善調査〉を加えるか）</t>
         </is>
       </c>
       <c r="D7" s="31" t="inlineStr">
         <is>
-          <t>業務開始日の確定。</t>
+          <t>調査票の設計・印刷頁数・集計方法がすべて決まる。第10期の新設手法。</t>
         </is>
       </c>
       <c r="E7" s="32" t="inlineStr">
         <is>
-          <t>０-02</t>
+          <t>Ⅰ-07,Ⅰ-10</t>
         </is>
       </c>
       <c r="F7" s="32" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>doc03/doc05</t>
         </is>
       </c>
       <c r="G7" s="32" t="inlineStr">
@@ -6939,7 +6947,7 @@
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B8" s="30" t="inlineStr">
@@ -6949,22 +6957,22 @@
       </c>
       <c r="C8" s="31" t="inlineStr">
         <is>
-          <t>在宅介護実態調査の手法（手法Ⅲか、手法Ⅳ〈新版 在宅生活改善調査〉を加えるか）</t>
+          <t>ニーズ調査 約850人の抽出基準（要支援認定者を含むか／第9期との対比）</t>
         </is>
       </c>
       <c r="D8" s="31" t="inlineStr">
         <is>
-          <t>調査票の設計・印刷頁数・集計方法がすべて決まる。第10期の新設手法。</t>
+          <t>対象者数が確定しないと印刷部数・郵送費が固まらない。</t>
         </is>
       </c>
       <c r="E8" s="32" t="inlineStr">
         <is>
-          <t>Ⅰ-07,Ⅰ-10</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F8" s="32" t="inlineStr">
         <is>
-          <t>doc03/doc05</t>
+          <t>doc01-2,3</t>
         </is>
       </c>
       <c r="G8" s="32" t="inlineStr">
@@ -6977,7 +6985,7 @@
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B9" s="30" t="inlineStr">
@@ -6987,12 +6995,12 @@
       </c>
       <c r="C9" s="31" t="inlineStr">
         <is>
-          <t>ニーズ調査 約850人の抽出基準（要支援認定者を含むか／第9期との対比）</t>
+          <t>在宅介護実態調査 約150人の抽出基準（要支援を含むか／施設入所者の除外方法）</t>
         </is>
       </c>
       <c r="D9" s="31" t="inlineStr">
         <is>
-          <t>対象者数が確定しないと印刷部数・郵送費が固まらない。</t>
+          <t>同上。手法Ⅲの対象定義に直結。</t>
         </is>
       </c>
       <c r="E9" s="32" t="inlineStr">
@@ -7002,7 +7010,7 @@
       </c>
       <c r="F9" s="32" t="inlineStr">
         <is>
-          <t>doc01-2,3</t>
+          <t>doc01-2</t>
         </is>
       </c>
       <c r="G9" s="32" t="inlineStr">
@@ -7015,7 +7023,7 @@
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B10" s="30" t="inlineStr">
@@ -7025,22 +7033,22 @@
       </c>
       <c r="C10" s="31" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 約150人の抽出基準（要支援を含むか／施設入所者の除外方法）</t>
+          <t>オプション項目の採否（「問6 就労について」ほか）</t>
         </is>
       </c>
       <c r="D10" s="31" t="inlineStr">
         <is>
-          <t>同上。手法Ⅲの対象定義に直結。</t>
+          <t>令和7年8月版で就労はオプションと確定。採否で頁数が変わる。</t>
         </is>
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅰ-12</t>
         </is>
       </c>
       <c r="F10" s="32" t="inlineStr">
         <is>
-          <t>doc01-2</t>
+          <t>doc05</t>
         </is>
       </c>
       <c r="G10" s="32" t="inlineStr">
@@ -7053,7 +7061,7 @@
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B11" s="30" t="inlineStr">
@@ -7063,22 +7071,22 @@
       </c>
       <c r="C11" s="31" t="inlineStr">
         <is>
-          <t>オプション項目の採否（「問6 就労について」ほか）</t>
+          <t>村独自設問の採否（除雪・在宅医療・成年後見・歯科受診・服薬ほか）</t>
         </is>
       </c>
       <c r="D11" s="31" t="inlineStr">
         <is>
-          <t>令和7年8月版で就労はオプションと確定。採否で頁数が変わる。</t>
+          <t>第9期との時系列比較を優先するか、新規論点を入れるかの判断。</t>
         </is>
       </c>
       <c r="E11" s="32" t="inlineStr">
         <is>
-          <t>Ⅰ-12</t>
+          <t>Ⅰ-13</t>
         </is>
       </c>
       <c r="F11" s="32" t="inlineStr">
         <is>
-          <t>doc05</t>
+          <t>doc03</t>
         </is>
       </c>
       <c r="G11" s="32" t="inlineStr">
@@ -7091,7 +7099,7 @@
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B12" s="30" t="inlineStr">
@@ -7101,22 +7109,22 @@
       </c>
       <c r="C12" s="31" t="inlineStr">
         <is>
-          <t>村独自設問の採否（除雪・在宅医療・成年後見・歯科受診・服薬ほか）</t>
+          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
         </is>
       </c>
       <c r="D12" s="31" t="inlineStr">
         <is>
-          <t>第9期との時系列比較を優先するか、新規論点を入れるかの判断。</t>
+          <t>第10期の新規要件。ラベル発注前に確定が必要。</t>
         </is>
       </c>
       <c r="E12" s="32" t="inlineStr">
         <is>
-          <t>Ⅰ-13</t>
+          <t>Ⅰ-19,Ⅰ-25</t>
         </is>
       </c>
       <c r="F12" s="32" t="inlineStr">
         <is>
-          <t>doc03</t>
+          <t>doc01</t>
         </is>
       </c>
       <c r="G12" s="32" t="inlineStr">
@@ -7129,7 +7137,7 @@
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B13" s="30" t="inlineStr">
@@ -7139,22 +7147,22 @@
       </c>
       <c r="C13" s="31" t="inlineStr">
         <is>
-          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
+          <t>ウェブ回答フォームの仕様（回答期限・村HP掲載の有無・二次元コード印字位置）</t>
         </is>
       </c>
       <c r="D13" s="31" t="inlineStr">
         <is>
-          <t>第10期の新規要件。ラベル発注前に確定が必要。</t>
+          <t>入稿データ作成の前提。</t>
         </is>
       </c>
       <c r="E13" s="32" t="inlineStr">
         <is>
-          <t>Ⅰ-19,Ⅰ-25</t>
+          <t>Ⅰ-16,Ⅰ-17</t>
         </is>
       </c>
       <c r="F13" s="32" t="inlineStr">
         <is>
-          <t>doc01</t>
+          <t>doc01-8</t>
         </is>
       </c>
       <c r="G13" s="32" t="inlineStr">
@@ -7167,7 +7175,7 @@
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B14" s="30" t="inlineStr">
@@ -7177,22 +7185,22 @@
       </c>
       <c r="C14" s="31" t="inlineStr">
         <is>
-          <t>ウェブ回答フォームの仕様（回答期限・村HP掲載の有無・二次元コード印字位置）</t>
+          <t>★調査の基準日（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="D14" s="31" t="inlineStr">
         <is>
-          <t>入稿データ作成の前提。</t>
+          <t>資料が空欄。基準日が決まらないと村が対象者を抽出できない。第9期は令和5年8月1日基準。</t>
         </is>
       </c>
       <c r="E14" s="32" t="inlineStr">
         <is>
-          <t>Ⅰ-16,Ⅰ-17</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F14" s="32" t="inlineStr">
         <is>
-          <t>doc01-8</t>
+          <t>doc19 追-1</t>
         </is>
       </c>
       <c r="G14" s="32" t="inlineStr">
@@ -7203,984 +7211,984 @@
       <c r="H14" s="31" t="inlineStr"/>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="33" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C15" s="25" t="inlineStr">
-        <is>
-          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
-        </is>
-      </c>
-      <c r="D15" s="25" t="inlineStr">
-        <is>
-          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
-        </is>
-      </c>
-      <c r="E15" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="inlineStr">
-        <is>
-          <t>doc02§22,doc08§8</t>
-        </is>
-      </c>
-      <c r="G15" s="23" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C15" s="31" t="inlineStr">
+        <is>
+          <t>★発送日の確定（9/17前倒し／9/18のまま／9/24後ろ倒し）と回収期限</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="inlineStr">
+        <is>
+          <t>★9/18は金曜で翌日から9/19〜23の5連休。配達が連休明けにずれる可能性。以降の全工程を左右する。</t>
+        </is>
+      </c>
+      <c r="E15" s="32" t="inlineStr">
+        <is>
+          <t>Ⅰ-29,Ⅰ-32</t>
+        </is>
+      </c>
+      <c r="F15" s="32" t="inlineStr">
+        <is>
+          <t>doc19 指-1</t>
+        </is>
+      </c>
+      <c r="G15" s="32" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H15" s="25" t="inlineStr"/>
+      <c r="H15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="33" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C16" s="25" t="inlineStr">
-        <is>
-          <t>令和6年度決算および令和7年度の給付費見込</t>
-        </is>
-      </c>
-      <c r="D16" s="25" t="inlineStr">
-        <is>
-          <t>第9期の計画値と実績の乖離を確定させるために必要。</t>
-        </is>
-      </c>
-      <c r="E16" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
-        </is>
-      </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>doc08§8-1</t>
-        </is>
-      </c>
-      <c r="G16" s="23" t="inlineStr">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C16" s="31" t="inlineStr">
+        <is>
+          <t>★ウェブ回答フォームにGoogleフォームを用いることの可否</t>
+        </is>
+      </c>
+      <c r="D16" s="31" t="inlineStr">
+        <is>
+          <t>★通信の暗号化とデータの保存先は別の論点。回答データが村外サーバに保存される。個人情報保護条例上の取扱いと、重複排除の実装・エクスポート後の元データ削除・公開期間管理の確認が必要。</t>
+        </is>
+      </c>
+      <c r="E16" s="32" t="inlineStr">
+        <is>
+          <t>Ⅰ-16,Ⅰ-18</t>
+        </is>
+      </c>
+      <c r="F16" s="32" t="inlineStr">
+        <is>
+          <t>doc19 追-3</t>
+        </is>
+      </c>
+      <c r="G16" s="32" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H16" s="25" t="inlineStr"/>
+      <c r="H16" s="31" t="inlineStr"/>
     </row>
     <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="33" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B17" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C17" s="25" t="inlineStr">
-        <is>
-          <t>通いの場の実数（令和3〜7年度）</t>
-        </is>
-      </c>
-      <c r="D17" s="25" t="inlineStr">
-        <is>
-          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。</t>
-        </is>
-      </c>
-      <c r="E17" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F17" s="23" t="inlineStr">
-        <is>
-          <t>doc02§16,§22</t>
-        </is>
-      </c>
-      <c r="G17" s="23" t="inlineStr">
+      <c r="A17" s="29" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B17" s="30" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="inlineStr">
+        <is>
+          <t>調査票の印刷頁数の調整方針（仕様書はニーズ約12頁／在宅約8頁）</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>現在の調査票案は設問数が多く、レイアウト調整か設問の絞り込みが必要になる可能性。オプション項目の採否と一体。</t>
+        </is>
+      </c>
+      <c r="E17" s="32" t="inlineStr">
+        <is>
+          <t>Ⅰ-20,Ⅰ-21</t>
+        </is>
+      </c>
+      <c r="F17" s="32" t="inlineStr">
+        <is>
+          <t>doc19 S-5</t>
+        </is>
+      </c>
+      <c r="G17" s="32" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H17" s="25" t="inlineStr"/>
+      <c r="H17" s="31" t="inlineStr"/>
     </row>
     <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="33" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C18" s="25" t="inlineStr">
-        <is>
-          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
-        </is>
-      </c>
-      <c r="D18" s="25" t="inlineStr">
-        <is>
-          <t>成果目標・活動指標の目標値設定に必要。P1〜P4で主要4指標は解決済だがW系は未入手。</t>
-        </is>
-      </c>
-      <c r="E18" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F18" s="23" t="inlineStr">
-        <is>
-          <t>doc07§8-2,doc09§10</t>
-        </is>
-      </c>
-      <c r="G18" s="23" t="inlineStr">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="inlineStr">
+        <is>
+          <t>依頼状の差出人名義（村名義／村長名）</t>
+        </is>
+      </c>
+      <c r="D18" s="31" t="inlineStr">
+        <is>
+          <t>障がい福祉計画は村名義。回収率に影響し得るため村長名を推奨するが村の慣行による。</t>
+        </is>
+      </c>
+      <c r="E18" s="32" t="inlineStr">
+        <is>
+          <t>Ⅰ-14</t>
+        </is>
+      </c>
+      <c r="F18" s="32" t="inlineStr">
+        <is>
+          <t>doc19 追-4</t>
+        </is>
+      </c>
+      <c r="G18" s="32" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H18" s="25" t="inlineStr"/>
+      <c r="H18" s="31" t="inlineStr"/>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="33" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B19" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C19" s="25" t="inlineStr">
-        <is>
-          <t>交付要綱の配点表（満点）</t>
-        </is>
-      </c>
-      <c r="D19" s="25" t="inlineStr">
-        <is>
-          <t>得点しか出力されず達成率が算出できない。</t>
-        </is>
-      </c>
-      <c r="E19" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F19" s="23" t="inlineStr">
-        <is>
-          <t>doc07§8-1</t>
-        </is>
-      </c>
-      <c r="G19" s="23" t="inlineStr">
+      <c r="A19" s="29" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="inlineStr">
+        <is>
+          <t>調査票の印刷部数（予備を何部見込むか）</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>約1,000部＋予備。発送後の追加印刷は工程上困難。</t>
+        </is>
+      </c>
+      <c r="E19" s="32" t="inlineStr">
+        <is>
+          <t>Ⅰ-21,Ⅰ-22</t>
+        </is>
+      </c>
+      <c r="F19" s="32" t="inlineStr">
+        <is>
+          <t>doc19 追-5</t>
+        </is>
+      </c>
+      <c r="G19" s="32" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H19" s="25" t="inlineStr"/>
+      <c r="H19" s="31" t="inlineStr"/>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="33" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B20" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C20" s="25" t="inlineStr">
-        <is>
-          <t>令和6年度・令和7年度の交付金評価結果</t>
-        </is>
-      </c>
-      <c r="D20" s="25" t="inlineStr">
-        <is>
-          <t>受領データは令和5年度まで。第10期の基準値は最新年度に置くべき。</t>
-        </is>
-      </c>
-      <c r="E20" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F20" s="23" t="inlineStr">
-        <is>
-          <t>doc07§8-5</t>
-        </is>
-      </c>
-      <c r="G20" s="23" t="inlineStr">
+      <c r="A20" s="29" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="inlineStr">
+        <is>
+          <t>在宅介護実態調査 問8・問9の基準月</t>
+        </is>
+      </c>
+      <c r="D20" s="31" t="inlineStr">
+        <is>
+          <t>発送月の前月が通常。発送日の確定とセット。</t>
+        </is>
+      </c>
+      <c r="E20" s="32" t="inlineStr">
+        <is>
+          <t>Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F20" s="32" t="inlineStr">
+        <is>
+          <t>doc19 追-2</t>
+        </is>
+      </c>
+      <c r="G20" s="32" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H20" s="25" t="inlineStr"/>
+      <c r="H20" s="31" t="inlineStr"/>
     </row>
     <row r="21" ht="34" customHeight="1">
       <c r="A21" s="33" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B21" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C21" s="25" t="inlineStr">
-        <is>
-          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
-        </is>
-      </c>
-      <c r="D21" s="25" t="inlineStr">
-        <is>
-          <t>見える化に該当データがない。第9期は基本目標4-4に位置づけ。</t>
-        </is>
-      </c>
-      <c r="E21" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-68,Ⅱ-69</t>
-        </is>
-      </c>
-      <c r="F21" s="23" t="inlineStr">
-        <is>
-          <t>doc08§8-5</t>
-        </is>
-      </c>
-      <c r="G21" s="23" t="inlineStr">
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>体制</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="inlineStr">
+        <is>
+          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>連絡体制表の確定。第9期概要版の発行は住民課。</t>
+        </is>
+      </c>
+      <c r="E21" s="32" t="inlineStr">
+        <is>
+          <t>０-04</t>
+        </is>
+      </c>
+      <c r="F21" s="32" t="inlineStr">
+        <is>
+          <t>doc01-1</t>
+        </is>
+      </c>
+      <c r="G21" s="32" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H21" s="25" t="inlineStr"/>
+      <c r="H21" s="31" t="inlineStr"/>
     </row>
     <row r="22" ht="34" customHeight="1">
       <c r="A22" s="33" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B22" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C22" s="25" t="inlineStr">
-        <is>
-          <t>高齢者福祉事業（村単独事業）の実績資料</t>
-        </is>
-      </c>
-      <c r="D22" s="25" t="inlineStr">
-        <is>
-          <t>現行計画の評価に必要。</t>
-        </is>
-      </c>
-      <c r="E22" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
-        </is>
-      </c>
-      <c r="F22" s="23" t="inlineStr">
-        <is>
-          <t>doc01-11</t>
-        </is>
-      </c>
-      <c r="G22" s="23" t="inlineStr">
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>体制</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="inlineStr">
+        <is>
+          <t>契約締結日・契約書の取り交わし状況</t>
+        </is>
+      </c>
+      <c r="D22" s="31" t="inlineStr">
+        <is>
+          <t>業務開始日の確定。</t>
+        </is>
+      </c>
+      <c r="E22" s="32" t="inlineStr">
+        <is>
+          <t>０-02</t>
+        </is>
+      </c>
+      <c r="F22" s="32" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G22" s="32" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H22" s="25" t="inlineStr"/>
+      <c r="H22" s="31" t="inlineStr"/>
     </row>
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="33" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B23" s="24" t="inlineStr">
-        <is>
-          <t>方針</t>
-        </is>
-      </c>
-      <c r="C23" s="25" t="inlineStr">
-        <is>
-          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
-        </is>
-      </c>
-      <c r="D23" s="25" t="inlineStr">
-        <is>
-          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
-        </is>
-      </c>
-      <c r="E23" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-59</t>
-        </is>
-      </c>
-      <c r="F23" s="23" t="inlineStr">
-        <is>
-          <t>doc09§4,§10</t>
-        </is>
-      </c>
-      <c r="G23" s="23" t="inlineStr">
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>体制</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="inlineStr">
+        <is>
+          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
+        </is>
+      </c>
+      <c r="D23" s="31" t="inlineStr">
+        <is>
+          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
+        </is>
+      </c>
+      <c r="E23" s="32" t="inlineStr">
+        <is>
+          <t>０-06</t>
+        </is>
+      </c>
+      <c r="F23" s="32" t="inlineStr">
+        <is>
+          <t>doc19 追-12</t>
+        </is>
+      </c>
+      <c r="G23" s="32" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H23" s="25" t="inlineStr"/>
+      <c r="H23" s="31" t="inlineStr"/>
     </row>
     <row r="24" ht="34" customHeight="1">
       <c r="A24" s="33" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B24" s="24" t="inlineStr">
-        <is>
-          <t>方針</t>
-        </is>
-      </c>
-      <c r="C24" s="25" t="inlineStr">
-        <is>
-          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
-        </is>
-      </c>
-      <c r="D24" s="25" t="inlineStr">
-        <is>
-          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
-        </is>
-      </c>
-      <c r="E24" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F24" s="23" t="inlineStr">
-        <is>
-          <t>doc09§8,§10</t>
-        </is>
-      </c>
-      <c r="G24" s="23" t="inlineStr">
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>委員会</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="inlineStr">
+        <is>
+          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
+        </is>
+      </c>
+      <c r="D24" s="31" t="inlineStr">
+        <is>
+          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
+        </is>
+      </c>
+      <c r="E24" s="32" t="inlineStr">
+        <is>
+          <t>Ⅱ-80,Ⅱ-81</t>
+        </is>
+      </c>
+      <c r="F24" s="32" t="inlineStr">
+        <is>
+          <t>doc01-6,doc19 追-15</t>
+        </is>
+      </c>
+      <c r="G24" s="32" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H24" s="25" t="inlineStr"/>
+      <c r="H24" s="31" t="inlineStr"/>
     </row>
     <row r="25" ht="34" customHeight="1">
       <c r="A25" s="33" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>成果品</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="inlineStr">
+        <is>
+          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
+        </is>
+      </c>
+      <c r="D25" s="31" t="inlineStr">
+        <is>
+          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
+        </is>
+      </c>
+      <c r="E25" s="32" t="inlineStr">
+        <is>
+          <t>Ⅱ-76,Ⅱ-77</t>
+        </is>
+      </c>
+      <c r="F25" s="32" t="inlineStr">
+        <is>
+          <t>doc01-7,doc19 指-3</t>
+        </is>
+      </c>
+      <c r="G25" s="32" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H25" s="31" t="inlineStr"/>
+    </row>
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="34" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B25" s="24" t="inlineStr">
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C26" s="25" t="inlineStr">
+        <is>
+          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
+        </is>
+      </c>
+      <c r="D26" s="25" t="inlineStr">
+        <is>
+          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-63,Ⅱ-64</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>doc02§22,doc08§8</t>
+        </is>
+      </c>
+      <c r="G26" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H26" s="25" t="inlineStr"/>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C27" s="25" t="inlineStr">
+        <is>
+          <t>令和6年度決算および令和7年度の給付費見込</t>
+        </is>
+      </c>
+      <c r="D27" s="25" t="inlineStr">
+        <is>
+          <t>第9期の計画値と実績の乖離を確定させるために必要。</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-55,Ⅱ-56</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>doc08§8-1</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H27" s="25" t="inlineStr"/>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C28" s="25" t="inlineStr">
+        <is>
+          <t>通いの場の実数（令和3〜7年度）</t>
+        </is>
+      </c>
+      <c r="D28" s="25" t="inlineStr">
+        <is>
+          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>doc02§16,§22</t>
+        </is>
+      </c>
+      <c r="G28" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H28" s="25" t="inlineStr"/>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C29" s="25" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+        </is>
+      </c>
+      <c r="D29" s="25" t="inlineStr">
+        <is>
+          <t>成果目標・活動指標の目標値設定に必要。P1〜P4で主要4指標は解決済だがW系は未入手。</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>doc07§8-2,doc09§10</t>
+        </is>
+      </c>
+      <c r="G29" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H29" s="25" t="inlineStr"/>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C30" s="25" t="inlineStr">
+        <is>
+          <t>交付要綱の配点表（満点）</t>
+        </is>
+      </c>
+      <c r="D30" s="25" t="inlineStr">
+        <is>
+          <t>得点しか出力されず達成率が算出できない。</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>doc07§8-1</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H30" s="25" t="inlineStr"/>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C31" s="25" t="inlineStr">
+        <is>
+          <t>令和6年度・令和7年度の交付金評価結果</t>
+        </is>
+      </c>
+      <c r="D31" s="25" t="inlineStr">
+        <is>
+          <t>受領データは令和5年度まで。第10期の基準値は最新年度に置くべき。</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>doc07§8-5</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H31" s="25" t="inlineStr"/>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C32" s="25" t="inlineStr">
+        <is>
+          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
+        </is>
+      </c>
+      <c r="D32" s="25" t="inlineStr">
+        <is>
+          <t>見える化に該当データがない。第9期は基本目標4-4に位置づけ。</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-68,Ⅱ-69</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>doc08§8-5</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H32" s="25" t="inlineStr"/>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C33" s="25" t="inlineStr">
+        <is>
+          <t>高齢者福祉事業（村単独事業）の実績資料</t>
+        </is>
+      </c>
+      <c r="D33" s="25" t="inlineStr">
+        <is>
+          <t>現行計画の評価に必要。</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-53,Ⅱ-54</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>doc01-11</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H33" s="25" t="inlineStr"/>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C34" s="25" t="inlineStr">
+        <is>
+          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
+        </is>
+      </c>
+      <c r="D34" s="25" t="inlineStr">
+        <is>
+          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-58,Ⅱ-59</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-9</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H34" s="25" t="inlineStr"/>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C35" s="25" t="inlineStr">
+        <is>
+          <t>介護保険事業状況報告（月報・年報）の原データの提供可否</t>
+        </is>
+      </c>
+      <c r="D35" s="25" t="inlineStr">
+        <is>
+          <t>見える化に収録されていない項目（サービス種類別利用者数の月次推移等）が扱えるようになる。</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-55</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-10</t>
+        </is>
+      </c>
+      <c r="G35" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H35" s="25" t="inlineStr"/>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C36" s="25" t="inlineStr">
+        <is>
+          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
+        </is>
+      </c>
+      <c r="D36" s="25" t="inlineStr">
+        <is>
+          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
+        </is>
+      </c>
+      <c r="E36" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-54</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-11</t>
+        </is>
+      </c>
+      <c r="G36" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H36" s="25" t="inlineStr"/>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C37" s="25" t="inlineStr">
+        <is>
+          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
+        </is>
+      </c>
+      <c r="D37" s="25" t="inlineStr">
+        <is>
+          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
+        </is>
+      </c>
+      <c r="E37" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-53,Ⅱ-54</t>
+        </is>
+      </c>
+      <c r="F37" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-11</t>
+        </is>
+      </c>
+      <c r="G37" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H37" s="25" t="inlineStr"/>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C38" s="25" t="inlineStr">
+        <is>
+          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
+        </is>
+      </c>
+      <c r="D38" s="25" t="inlineStr">
+        <is>
+          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
+        </is>
+      </c>
+      <c r="E38" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-54</t>
+        </is>
+      </c>
+      <c r="F38" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-11</t>
+        </is>
+      </c>
+      <c r="G38" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H38" s="25" t="inlineStr"/>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>成果品</t>
+        </is>
+      </c>
+      <c r="C39" s="25" t="inlineStr">
+        <is>
+          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
+        </is>
+      </c>
+      <c r="D39" s="25" t="inlineStr">
+        <is>
+          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
+        </is>
+      </c>
+      <c r="E39" s="23" t="inlineStr">
+        <is>
+          <t>Ⅳ-92</t>
+        </is>
+      </c>
+      <c r="F39" s="23" t="inlineStr">
+        <is>
+          <t>doc19 指-5</t>
+        </is>
+      </c>
+      <c r="G39" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H39" s="25" t="inlineStr"/>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B40" s="24" t="inlineStr">
         <is>
           <t>方針</t>
         </is>
       </c>
-      <c r="C25" s="25" t="inlineStr">
-        <is>
-          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
-        </is>
-      </c>
-      <c r="D25" s="25" t="inlineStr">
-        <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
-        </is>
-      </c>
-      <c r="E25" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
-        </is>
-      </c>
-      <c r="F25" s="23" t="inlineStr">
-        <is>
-          <t>doc02§17,doc07,doc18 4-1</t>
-        </is>
-      </c>
-      <c r="G25" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H25" s="25" t="inlineStr"/>
-    </row>
-    <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="33" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B26" s="24" t="inlineStr">
-        <is>
-          <t>方針</t>
-        </is>
-      </c>
-      <c r="C26" s="25" t="inlineStr">
-        <is>
-          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
-        </is>
-      </c>
-      <c r="D26" s="25" t="inlineStr">
-        <is>
-          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
-        </is>
-      </c>
-      <c r="E26" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-56,Ⅱ-75</t>
-        </is>
-      </c>
-      <c r="F26" s="23" t="inlineStr">
-        <is>
-          <t>doc17 C-1,doc02§20-2</t>
-        </is>
-      </c>
-      <c r="G26" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H26" s="25" t="inlineStr"/>
-    </row>
-    <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="33" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B27" s="24" t="inlineStr">
-        <is>
-          <t>方針</t>
-        </is>
-      </c>
-      <c r="C27" s="25" t="inlineStr">
-        <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
-        </is>
-      </c>
-      <c r="D27" s="25" t="inlineStr">
-        <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
-        </is>
-      </c>
-      <c r="E27" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F27" s="23" t="inlineStr">
-        <is>
-          <t>doc13§6</t>
-        </is>
-      </c>
-      <c r="G27" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H27" s="25" t="inlineStr"/>
-    </row>
-    <row r="28" ht="34" customHeight="1">
-      <c r="A28" s="33" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B28" s="24" t="inlineStr">
-        <is>
-          <t>疑義</t>
-        </is>
-      </c>
-      <c r="C28" s="25" t="inlineStr">
-        <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
-        </is>
-      </c>
-      <c r="D28" s="25" t="inlineStr">
-        <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
-        </is>
-      </c>
-      <c r="E28" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-54</t>
-        </is>
-      </c>
-      <c r="F28" s="23" t="inlineStr">
-        <is>
-          <t>doc07§4</t>
-        </is>
-      </c>
-      <c r="G28" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H28" s="25" t="inlineStr"/>
-    </row>
-    <row r="29" ht="34" customHeight="1">
-      <c r="A29" s="33" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B29" s="24" t="inlineStr">
-        <is>
-          <t>疑義</t>
-        </is>
-      </c>
-      <c r="C29" s="25" t="inlineStr">
-        <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
-        </is>
-      </c>
-      <c r="D29" s="25" t="inlineStr">
-        <is>
-          <t>評価指標の読み方に影響。</t>
-        </is>
-      </c>
-      <c r="E29" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-54</t>
-        </is>
-      </c>
-      <c r="F29" s="23" t="inlineStr">
-        <is>
-          <t>doc07§8-4</t>
-        </is>
-      </c>
-      <c r="G29" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H29" s="25" t="inlineStr"/>
-    </row>
-    <row r="30" ht="34" customHeight="1">
-      <c r="A30" s="33" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B30" s="24" t="inlineStr">
-        <is>
-          <t>疑義</t>
-        </is>
-      </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
-        </is>
-      </c>
-      <c r="D30" s="25" t="inlineStr">
-        <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
-        </is>
-      </c>
-      <c r="E30" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
-        </is>
-      </c>
-      <c r="F30" s="23" t="inlineStr">
-        <is>
-          <t>doc08§4,§8-2</t>
-        </is>
-      </c>
-      <c r="G30" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H30" s="25" t="inlineStr"/>
-    </row>
-    <row r="31" ht="34" customHeight="1">
-      <c r="A31" s="33" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B31" s="24" t="inlineStr">
-        <is>
-          <t>疑義</t>
-        </is>
-      </c>
-      <c r="C31" s="25" t="inlineStr">
-        <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
-        </is>
-      </c>
-      <c r="D31" s="25" t="inlineStr">
-        <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
-        </is>
-      </c>
-      <c r="E31" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-55</t>
-        </is>
-      </c>
-      <c r="F31" s="23" t="inlineStr">
-        <is>
-          <t>doc02§20-1</t>
-        </is>
-      </c>
-      <c r="G31" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H31" s="25" t="inlineStr"/>
-    </row>
-    <row r="32" ht="34" customHeight="1">
-      <c r="A32" s="33" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B32" s="24" t="inlineStr">
-        <is>
-          <t>素案</t>
-        </is>
-      </c>
-      <c r="C32" s="25" t="inlineStr">
-        <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
-        </is>
-      </c>
-      <c r="D32" s="25" t="inlineStr">
-        <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
-        </is>
-      </c>
-      <c r="E32" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-75</t>
-        </is>
-      </c>
-      <c r="F32" s="23" t="inlineStr">
-        <is>
-          <t>doc15,doc18</t>
-        </is>
-      </c>
-      <c r="G32" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H32" s="25" t="inlineStr"/>
-    </row>
-    <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="33" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B33" s="24" t="inlineStr">
-        <is>
-          <t>素案</t>
-        </is>
-      </c>
-      <c r="C33" s="25" t="inlineStr">
-        <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
-        </is>
-      </c>
-      <c r="D33" s="25" t="inlineStr">
-        <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
-        </is>
-      </c>
-      <c r="E33" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
-        </is>
-      </c>
-      <c r="F33" s="23" t="inlineStr">
-        <is>
-          <t>doc14§5,doc18 3-1</t>
-        </is>
-      </c>
-      <c r="G33" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H33" s="25" t="inlineStr"/>
-    </row>
-    <row r="34" ht="34" customHeight="1">
-      <c r="A34" s="33" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B34" s="24" t="inlineStr">
-        <is>
-          <t>素案</t>
-        </is>
-      </c>
-      <c r="C34" s="25" t="inlineStr">
-        <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
-        </is>
-      </c>
-      <c r="D34" s="25" t="inlineStr">
-        <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
-        </is>
-      </c>
-      <c r="E34" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
-        </is>
-      </c>
-      <c r="F34" s="23" t="inlineStr">
-        <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
-        </is>
-      </c>
-      <c r="G34" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H34" s="25" t="inlineStr"/>
-    </row>
-    <row r="35" ht="34" customHeight="1">
-      <c r="A35" s="33" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B35" s="24" t="inlineStr">
-        <is>
-          <t>素案</t>
-        </is>
-      </c>
-      <c r="C35" s="25" t="inlineStr">
-        <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
-        </is>
-      </c>
-      <c r="D35" s="25" t="inlineStr">
-        <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
-        </is>
-      </c>
-      <c r="E35" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-75</t>
-        </is>
-      </c>
-      <c r="F35" s="23" t="inlineStr">
-        <is>
-          <t>doc17 B-3,doc18 4-3</t>
-        </is>
-      </c>
-      <c r="G35" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H35" s="25" t="inlineStr"/>
-    </row>
-    <row r="36" ht="34" customHeight="1">
-      <c r="A36" s="33" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B36" s="24" t="inlineStr">
-        <is>
-          <t>素案</t>
-        </is>
-      </c>
-      <c r="C36" s="25" t="inlineStr">
-        <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
-        </is>
-      </c>
-      <c r="D36" s="25" t="inlineStr">
-        <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
-        </is>
-      </c>
-      <c r="E36" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-75</t>
-        </is>
-      </c>
-      <c r="F36" s="23" t="inlineStr">
-        <is>
-          <t>doc17 A-1,doc18 2-9</t>
-        </is>
-      </c>
-      <c r="G36" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H36" s="25" t="inlineStr"/>
-    </row>
-    <row r="37" ht="34" customHeight="1">
-      <c r="A37" s="33" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B37" s="24" t="inlineStr">
-        <is>
-          <t>素案</t>
-        </is>
-      </c>
-      <c r="C37" s="25" t="inlineStr">
-        <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
-        </is>
-      </c>
-      <c r="D37" s="25" t="inlineStr">
-        <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
-        </is>
-      </c>
-      <c r="E37" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
-        </is>
-      </c>
-      <c r="F37" s="23" t="inlineStr">
-        <is>
-          <t>doc17 A-1,doc18 5-7</t>
-        </is>
-      </c>
-      <c r="G37" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H37" s="25" t="inlineStr"/>
-    </row>
-    <row r="38" ht="34" customHeight="1">
-      <c r="A38" s="33" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B38" s="24" t="inlineStr">
-        <is>
-          <t>計画構成</t>
-        </is>
-      </c>
-      <c r="C38" s="25" t="inlineStr">
-        <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
-        </is>
-      </c>
-      <c r="D38" s="25" t="inlineStr">
-        <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
-        </is>
-      </c>
-      <c r="E38" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-72</t>
-        </is>
-      </c>
-      <c r="F38" s="23" t="inlineStr">
-        <is>
-          <t>doc08§8-4</t>
-        </is>
-      </c>
-      <c r="G38" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H38" s="25" t="inlineStr"/>
-    </row>
-    <row r="39" ht="34" customHeight="1">
-      <c r="A39" s="33" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B39" s="24" t="inlineStr">
-        <is>
-          <t>計画構成</t>
-        </is>
-      </c>
-      <c r="C39" s="25" t="inlineStr">
-        <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
-        </is>
-      </c>
-      <c r="D39" s="25" t="inlineStr">
-        <is>
-          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
-        </is>
-      </c>
-      <c r="E39" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-73,Ⅱ-75</t>
-        </is>
-      </c>
-      <c r="F39" s="23" t="inlineStr">
-        <is>
-          <t>doc01-5,doc18 1-2</t>
-        </is>
-      </c>
-      <c r="G39" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H39" s="25" t="inlineStr"/>
-    </row>
-    <row r="40" ht="34" customHeight="1">
-      <c r="A40" s="33" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B40" s="24" t="inlineStr">
-        <is>
-          <t>計画構成</t>
-        </is>
-      </c>
       <c r="C40" s="25" t="inlineStr">
         <is>
-          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
         </is>
       </c>
       <c r="D40" s="25" t="inlineStr">
         <is>
-          <t>施策の書きぶりに影響。</t>
+          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
         </is>
       </c>
       <c r="E40" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-72</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F40" s="23" t="inlineStr">
         <is>
-          <t>doc01-12</t>
+          <t>doc09§4,§10</t>
         </is>
       </c>
       <c r="G40" s="23" t="inlineStr">
@@ -8193,32 +8201,32 @@
     <row r="41" ht="34" customHeight="1">
       <c r="A41" s="34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B41" s="24" t="inlineStr">
         <is>
-          <t>委員会</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C41" s="25" t="inlineStr">
         <is>
-          <t>策定委員会の委員改選時期・第1回開催希望時期・開催形式（対面／オンライン）</t>
+          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
         </is>
       </c>
       <c r="D41" s="25" t="inlineStr">
         <is>
-          <t>会議資料の作成時期が決まる。</t>
+          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
         </is>
       </c>
       <c r="E41" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-80,Ⅱ-81</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t>doc01-6</t>
+          <t>doc09§8,§10</t>
         </is>
       </c>
       <c r="G41" s="23" t="inlineStr">
@@ -8231,32 +8239,32 @@
     <row r="42" ht="34" customHeight="1">
       <c r="A42" s="34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B42" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C42" s="25" t="inlineStr">
         <is>
-          <t>パブリックコメントの実施時期・実施主体と意見反映の締切</t>
+          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
         </is>
       </c>
       <c r="D42" s="25" t="inlineStr">
         <is>
-          <t>R9.1〜2の工程に直結。</t>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
         </is>
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-76,Ⅱ-77</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F42" s="23" t="inlineStr">
         <is>
-          <t>doc01-7</t>
+          <t>doc02§17,doc07,doc18 4-1</t>
         </is>
       </c>
       <c r="G42" s="23" t="inlineStr">
@@ -8269,32 +8277,32 @@
     <row r="43" ht="34" customHeight="1">
       <c r="A43" s="34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B43" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C43" s="25" t="inlineStr">
         <is>
-          <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
         </is>
       </c>
       <c r="D43" s="25" t="inlineStr">
         <is>
-          <t>第9期はA4・本文104頁・全6章＋資料編。</t>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
         </is>
       </c>
       <c r="E43" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-89</t>
+          <t>Ⅱ-56,Ⅱ-75</t>
         </is>
       </c>
       <c r="F43" s="23" t="inlineStr">
         <is>
-          <t>doc01-10</t>
+          <t>doc17 C-1,doc02§20-2</t>
         </is>
       </c>
       <c r="G43" s="23" t="inlineStr">
@@ -8307,171 +8315,934 @@
     <row r="44" ht="34" customHeight="1">
       <c r="A44" s="34" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>方針</t>
+        </is>
+      </c>
+      <c r="C44" s="25" t="inlineStr">
+        <is>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+        </is>
+      </c>
+      <c r="D44" s="25" t="inlineStr">
+        <is>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+        </is>
+      </c>
+      <c r="E44" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-60,Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F44" s="23" t="inlineStr">
+        <is>
+          <t>doc13§6</t>
+        </is>
+      </c>
+      <c r="G44" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H44" s="25" t="inlineStr"/>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>方針</t>
+        </is>
+      </c>
+      <c r="C45" s="25" t="inlineStr">
+        <is>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+        </is>
+      </c>
+      <c r="D45" s="25" t="inlineStr">
+        <is>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
+        </is>
+      </c>
+      <c r="E45" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-63,Ⅱ-64</t>
+        </is>
+      </c>
+      <c r="F45" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-14</t>
+        </is>
+      </c>
+      <c r="G45" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H45" s="25" t="inlineStr"/>
+    </row>
+    <row r="46" ht="34" customHeight="1">
+      <c r="A46" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B46" s="24" t="inlineStr">
+        <is>
+          <t>方針</t>
+        </is>
+      </c>
+      <c r="C46" s="25" t="inlineStr">
+        <is>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+        </is>
+      </c>
+      <c r="D46" s="25" t="inlineStr">
+        <is>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+        </is>
+      </c>
+      <c r="E46" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-67,Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F46" s="23" t="inlineStr">
+        <is>
+          <t>doc19 §3</t>
+        </is>
+      </c>
+      <c r="G46" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H46" s="25" t="inlineStr"/>
+    </row>
+    <row r="47" ht="34" customHeight="1">
+      <c r="A47" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>疑義</t>
+        </is>
+      </c>
+      <c r="C47" s="25" t="inlineStr">
+        <is>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+        </is>
+      </c>
+      <c r="D47" s="25" t="inlineStr">
+        <is>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+        </is>
+      </c>
+      <c r="E47" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-54</t>
+        </is>
+      </c>
+      <c r="F47" s="23" t="inlineStr">
+        <is>
+          <t>doc07§4</t>
+        </is>
+      </c>
+      <c r="G47" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H47" s="25" t="inlineStr"/>
+    </row>
+    <row r="48" ht="34" customHeight="1">
+      <c r="A48" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B48" s="24" t="inlineStr">
+        <is>
+          <t>疑義</t>
+        </is>
+      </c>
+      <c r="C48" s="25" t="inlineStr">
+        <is>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+        </is>
+      </c>
+      <c r="D48" s="25" t="inlineStr">
+        <is>
+          <t>評価指標の読み方に影響。</t>
+        </is>
+      </c>
+      <c r="E48" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-54</t>
+        </is>
+      </c>
+      <c r="F48" s="23" t="inlineStr">
+        <is>
+          <t>doc07§8-4</t>
+        </is>
+      </c>
+      <c r="G48" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H48" s="25" t="inlineStr"/>
+    </row>
+    <row r="49" ht="34" customHeight="1">
+      <c r="A49" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B49" s="24" t="inlineStr">
+        <is>
+          <t>疑義</t>
+        </is>
+      </c>
+      <c r="C49" s="25" t="inlineStr">
+        <is>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+        </is>
+      </c>
+      <c r="D49" s="25" t="inlineStr">
+        <is>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+        </is>
+      </c>
+      <c r="E49" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-55,Ⅱ-56</t>
+        </is>
+      </c>
+      <c r="F49" s="23" t="inlineStr">
+        <is>
+          <t>doc08§4,§8-2</t>
+        </is>
+      </c>
+      <c r="G49" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H49" s="25" t="inlineStr"/>
+    </row>
+    <row r="50" ht="34" customHeight="1">
+      <c r="A50" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B50" s="24" t="inlineStr">
+        <is>
+          <t>疑義</t>
+        </is>
+      </c>
+      <c r="C50" s="25" t="inlineStr">
+        <is>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+        </is>
+      </c>
+      <c r="D50" s="25" t="inlineStr">
+        <is>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+        </is>
+      </c>
+      <c r="E50" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-55</t>
+        </is>
+      </c>
+      <c r="F50" s="23" t="inlineStr">
+        <is>
+          <t>doc02§20-1</t>
+        </is>
+      </c>
+      <c r="G50" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H50" s="25" t="inlineStr"/>
+    </row>
+    <row r="51" ht="34" customHeight="1">
+      <c r="A51" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B51" s="24" t="inlineStr">
+        <is>
+          <t>素案</t>
+        </is>
+      </c>
+      <c r="C51" s="25" t="inlineStr">
+        <is>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+        </is>
+      </c>
+      <c r="D51" s="25" t="inlineStr">
+        <is>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+        </is>
+      </c>
+      <c r="E51" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F51" s="23" t="inlineStr">
+        <is>
+          <t>doc15,doc18</t>
+        </is>
+      </c>
+      <c r="G51" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H51" s="25" t="inlineStr"/>
+    </row>
+    <row r="52" ht="34" customHeight="1">
+      <c r="A52" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B52" s="24" t="inlineStr">
+        <is>
+          <t>素案</t>
+        </is>
+      </c>
+      <c r="C52" s="25" t="inlineStr">
+        <is>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+        </is>
+      </c>
+      <c r="D52" s="25" t="inlineStr">
+        <is>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+        </is>
+      </c>
+      <c r="E52" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-71,Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F52" s="23" t="inlineStr">
+        <is>
+          <t>doc14§5,doc18 3-1</t>
+        </is>
+      </c>
+      <c r="G52" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H52" s="25" t="inlineStr"/>
+    </row>
+    <row r="53" ht="34" customHeight="1">
+      <c r="A53" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B53" s="24" t="inlineStr">
+        <is>
+          <t>素案</t>
+        </is>
+      </c>
+      <c r="C53" s="25" t="inlineStr">
+        <is>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+        </is>
+      </c>
+      <c r="D53" s="25" t="inlineStr">
+        <is>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+        </is>
+      </c>
+      <c r="E53" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-71,Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F53" s="23" t="inlineStr">
+        <is>
+          <t>doc14§5,doc15,doc18 4-5</t>
+        </is>
+      </c>
+      <c r="G53" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H53" s="25" t="inlineStr"/>
+    </row>
+    <row r="54" ht="34" customHeight="1">
+      <c r="A54" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B54" s="24" t="inlineStr">
+        <is>
+          <t>素案</t>
+        </is>
+      </c>
+      <c r="C54" s="25" t="inlineStr">
+        <is>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+        </is>
+      </c>
+      <c r="D54" s="25" t="inlineStr">
+        <is>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+        </is>
+      </c>
+      <c r="E54" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F54" s="23" t="inlineStr">
+        <is>
+          <t>doc17 B-3,doc18 4-3</t>
+        </is>
+      </c>
+      <c r="G54" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H54" s="25" t="inlineStr"/>
+    </row>
+    <row r="55" ht="34" customHeight="1">
+      <c r="A55" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B55" s="24" t="inlineStr">
+        <is>
+          <t>素案</t>
+        </is>
+      </c>
+      <c r="C55" s="25" t="inlineStr">
+        <is>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+        </is>
+      </c>
+      <c r="D55" s="25" t="inlineStr">
+        <is>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+        </is>
+      </c>
+      <c r="E55" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F55" s="23" t="inlineStr">
+        <is>
+          <t>doc17 A-1,doc18 2-9</t>
+        </is>
+      </c>
+      <c r="G55" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H55" s="25" t="inlineStr"/>
+    </row>
+    <row r="56" ht="34" customHeight="1">
+      <c r="A56" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B56" s="24" t="inlineStr">
+        <is>
+          <t>素案</t>
+        </is>
+      </c>
+      <c r="C56" s="25" t="inlineStr">
+        <is>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+        </is>
+      </c>
+      <c r="D56" s="25" t="inlineStr">
+        <is>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+        </is>
+      </c>
+      <c r="E56" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-64,Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F56" s="23" t="inlineStr">
+        <is>
+          <t>doc17 A-1,doc18 5-7</t>
+        </is>
+      </c>
+      <c r="G56" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H56" s="25" t="inlineStr"/>
+    </row>
+    <row r="57" ht="34" customHeight="1">
+      <c r="A57" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B57" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C57" s="25" t="inlineStr">
+        <is>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
+        </is>
+      </c>
+      <c r="D57" s="25" t="inlineStr">
+        <is>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+        </is>
+      </c>
+      <c r="E57" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F57" s="23" t="inlineStr">
+        <is>
+          <t>doc08§8-4</t>
+        </is>
+      </c>
+      <c r="G57" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H57" s="25" t="inlineStr"/>
+    </row>
+    <row r="58" ht="34" customHeight="1">
+      <c r="A58" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B58" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C58" s="25" t="inlineStr">
+        <is>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+        </is>
+      </c>
+      <c r="D58" s="25" t="inlineStr">
+        <is>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+        </is>
+      </c>
+      <c r="E58" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-73,Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F58" s="23" t="inlineStr">
+        <is>
+          <t>doc01-5,doc18 1-2</t>
+        </is>
+      </c>
+      <c r="G58" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H58" s="25" t="inlineStr"/>
+    </row>
+    <row r="59" ht="34" customHeight="1">
+      <c r="A59" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B59" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C59" s="25" t="inlineStr">
+        <is>
+          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+        </is>
+      </c>
+      <c r="D59" s="25" t="inlineStr">
+        <is>
+          <t>施策の書きぶりに影響。</t>
+        </is>
+      </c>
+      <c r="E59" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-71,Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F59" s="23" t="inlineStr">
+        <is>
+          <t>doc01-12</t>
+        </is>
+      </c>
+      <c r="G59" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H59" s="25" t="inlineStr"/>
+    </row>
+    <row r="60" ht="34" customHeight="1">
+      <c r="A60" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B60" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C60" s="25" t="inlineStr">
+        <is>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+        </is>
+      </c>
+      <c r="D60" s="25" t="inlineStr">
+        <is>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+        </is>
+      </c>
+      <c r="E60" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F60" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-13</t>
+        </is>
+      </c>
+      <c r="G60" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H60" s="25" t="inlineStr"/>
+    </row>
+    <row r="61" ht="34" customHeight="1">
+      <c r="A61" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B61" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C61" s="25" t="inlineStr">
+        <is>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+        </is>
+      </c>
+      <c r="D61" s="25" t="inlineStr">
+        <is>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+        </is>
+      </c>
+      <c r="E61" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-31</t>
+        </is>
+      </c>
+      <c r="F61" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-6</t>
+        </is>
+      </c>
+      <c r="G61" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H61" s="25" t="inlineStr"/>
+    </row>
+    <row r="62" ht="34" customHeight="1">
+      <c r="A62" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B62" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C62" s="25" t="inlineStr">
+        <is>
+          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+        </is>
+      </c>
+      <c r="D62" s="25" t="inlineStr">
+        <is>
+          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+        </is>
+      </c>
+      <c r="E62" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-40,Ⅰ-42</t>
+        </is>
+      </c>
+      <c r="F62" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-7</t>
+        </is>
+      </c>
+      <c r="G62" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H62" s="25" t="inlineStr"/>
+    </row>
+    <row r="63" ht="34" customHeight="1">
+      <c r="A63" s="35" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B44" s="24" t="inlineStr">
+      <c r="B63" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C44" s="25" t="inlineStr">
+      <c r="C63" s="25" t="inlineStr">
+        <is>
+          <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
+        </is>
+      </c>
+      <c r="D63" s="25" t="inlineStr">
+        <is>
+          <t>第9期はA4・本文104頁・全6章＋資料編。</t>
+        </is>
+      </c>
+      <c r="E63" s="23" t="inlineStr">
+        <is>
+          <t>Ⅳ-89</t>
+        </is>
+      </c>
+      <c r="F63" s="23" t="inlineStr">
+        <is>
+          <t>doc01-10</t>
+        </is>
+      </c>
+      <c r="G63" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H63" s="25" t="inlineStr"/>
+    </row>
+    <row r="64" ht="34" customHeight="1">
+      <c r="A64" s="35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B64" s="24" t="inlineStr">
+        <is>
+          <t>成果品</t>
+        </is>
+      </c>
+      <c r="C64" s="25" t="inlineStr">
         <is>
           <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
         </is>
       </c>
-      <c r="D44" s="25" t="inlineStr">
+      <c r="D64" s="25" t="inlineStr">
         <is>
           <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
         </is>
       </c>
-      <c r="E44" s="23" t="inlineStr">
+      <c r="E64" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-92</t>
         </is>
       </c>
-      <c r="F44" s="23" t="inlineStr">
+      <c r="F64" s="23" t="inlineStr">
         <is>
           <t>doc01-10,doc08</t>
         </is>
       </c>
-      <c r="G44" s="23" t="inlineStr">
+      <c r="G64" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H44" s="25" t="inlineStr"/>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="35" t="inlineStr">
+      <c r="H64" s="25" t="inlineStr"/>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="36" t="inlineStr">
         <is>
           <t>■ 解決済み（記録）</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="34" customHeight="1">
-      <c r="A47" s="36" t="inlineStr">
+    <row r="67" ht="34" customHeight="1">
+      <c r="A67" s="37" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="B47" s="37" t="inlineStr">
+      <c r="B67" s="38" t="inlineStr">
         <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="C47" s="38" t="inlineStr">
+      <c r="C67" s="39" t="inlineStr">
         <is>
           <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
         </is>
       </c>
-      <c r="D47" s="38" t="inlineStr">
+      <c r="D67" s="39" t="inlineStr">
         <is>
           <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
         </is>
       </c>
-      <c r="E47" s="36" t="inlineStr">
+      <c r="E67" s="37" t="inlineStr">
         <is>
           <t>Ⅱ-56,Ⅱ-58</t>
         </is>
       </c>
-      <c r="F47" s="36" t="inlineStr">
+      <c r="F67" s="37" t="inlineStr">
         <is>
           <t>doc09</t>
         </is>
       </c>
-      <c r="G47" s="36" t="inlineStr">
+      <c r="G67" s="37" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H47" s="38" t="inlineStr"/>
-    </row>
-    <row r="48" ht="34" customHeight="1">
-      <c r="A48" s="36" t="inlineStr">
+      <c r="H67" s="39" t="inlineStr"/>
+    </row>
+    <row r="68" ht="34" customHeight="1">
+      <c r="A68" s="37" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="B48" s="37" t="inlineStr">
+      <c r="B68" s="38" t="inlineStr">
         <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="C48" s="38" t="inlineStr">
+      <c r="C68" s="39" t="inlineStr">
         <is>
           <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
         </is>
       </c>
-      <c r="D48" s="38" t="inlineStr">
+      <c r="D68" s="39" t="inlineStr">
         <is>
           <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
         </is>
       </c>
-      <c r="E48" s="36" t="inlineStr">
+      <c r="E68" s="37" t="inlineStr">
         <is>
           <t>Ⅱ-59</t>
         </is>
       </c>
-      <c r="F48" s="36" t="inlineStr">
+      <c r="F68" s="37" t="inlineStr">
         <is>
           <t>doc02§20-2</t>
         </is>
       </c>
-      <c r="G48" s="36" t="inlineStr">
+      <c r="G68" s="37" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H48" s="38" t="inlineStr"/>
-    </row>
-    <row r="49" ht="34" customHeight="1">
-      <c r="A49" s="36" t="inlineStr">
+      <c r="H68" s="39" t="inlineStr"/>
+    </row>
+    <row r="69" ht="34" customHeight="1">
+      <c r="A69" s="37" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="B49" s="37" t="inlineStr">
+      <c r="B69" s="38" t="inlineStr">
         <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="C49" s="38" t="inlineStr">
+      <c r="C69" s="39" t="inlineStr">
         <is>
           <t>国の指針・様式の更新有無</t>
         </is>
       </c>
-      <c r="D49" s="38" t="inlineStr">
+      <c r="D69" s="39" t="inlineStr">
         <is>
           <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
-      <c r="E49" s="36" t="inlineStr">
+      <c r="E69" s="37" t="inlineStr">
         <is>
           <t>Ⅰ-11</t>
         </is>
       </c>
-      <c r="F49" s="36" t="inlineStr">
+      <c r="F69" s="37" t="inlineStr">
         <is>
           <t>doc04,doc05</t>
         </is>
       </c>
-      <c r="G49" s="36" t="inlineStr">
+      <c r="G69" s="37" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H49" s="38" t="inlineStr"/>
+      <c r="H69" s="39" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H44"/>
+  <autoFilter ref="A4:H64"/>
   <mergeCells count="3">
-    <mergeCell ref="A46:H46"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A66:H66"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="G5:G44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="2">
+    <dataValidation sqref="A5:A64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"S,A,B,C"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G5:G64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8558,7 +9329,7 @@
           <t>業務内容・成果品・その他条件</t>
         </is>
       </c>
-      <c r="D5" s="39" t="n">
+      <c r="D5" s="40" t="n">
         <v>46259</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -8588,7 +9359,7 @@
           <t>本文104頁・全6章＋資料編</t>
         </is>
       </c>
-      <c r="D6" s="39" t="n">
+      <c r="D6" s="40" t="n">
         <v>46259</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -8618,7 +9389,7 @@
           <t>基本理念・基本目標・数値①〜⑦・施策体系図</t>
         </is>
       </c>
-      <c r="D7" s="39" t="n">
+      <c r="D7" s="40" t="n">
         <v>46265</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -8712,7 +9483,7 @@
           <t>2版をレビュー済</t>
         </is>
       </c>
-      <c r="D10" s="39" t="n">
+      <c r="D10" s="40" t="n">
         <v>46259</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -8742,7 +9513,7 @@
           <t>修正案まで受領</t>
         </is>
       </c>
-      <c r="D11" s="39" t="n">
+      <c r="D11" s="40" t="n">
         <v>46259</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -8772,7 +9543,7 @@
           <t>逐条突合の基礎。要確認0件で完了</t>
         </is>
       </c>
-      <c r="D12" s="39" t="n">
+      <c r="D12" s="40" t="n">
         <v>46261</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -8802,7 +9573,7 @@
           <t>第1号被保険者数・認定者数・認定率ほか</t>
         </is>
       </c>
-      <c r="D13" s="39" t="n">
+      <c r="D13" s="40" t="n">
         <v>46259</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -8832,7 +9603,7 @@
           <t>第1号被保険者1人あたり給付月額ほか</t>
         </is>
       </c>
-      <c r="D14" s="39" t="n">
+      <c r="D14" s="40" t="n">
         <v>46265</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -8862,7 +9633,7 @@
           <t>村内施設ゼロを確認</t>
         </is>
       </c>
-      <c r="D15" s="39" t="n">
+      <c r="D15" s="40" t="n">
         <v>46265</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -8892,7 +9663,7 @@
           <t>定員は平成30年度以降据置</t>
         </is>
       </c>
-      <c r="D16" s="39" t="n">
+      <c r="D16" s="40" t="n">
         <v>46265</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -8922,7 +9693,7 @@
           <t>17系列が実データなし（＝未実施）</t>
         </is>
       </c>
-      <c r="D17" s="39" t="n">
+      <c r="D17" s="40" t="n">
         <v>46265</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -8952,7 +9723,7 @@
           <t>平成26〜令和5年度決算</t>
         </is>
       </c>
-      <c r="D18" s="39" t="n">
+      <c r="D18" s="40" t="n">
         <v>46265</v>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -8982,7 +9753,7 @@
           <t>令和3〜5年度。0点項目21件を抽出</t>
         </is>
       </c>
-      <c r="D19" s="39" t="n">
+      <c r="D19" s="40" t="n">
         <v>46265</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -9012,7 +9783,7 @@
           <t>令和5年度</t>
         </is>
       </c>
-      <c r="D20" s="39" t="n">
+      <c r="D20" s="40" t="n">
         <v>46265</v>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -9042,7 +9813,7 @@
           <t>県平均・全国平均・県内順位・全国順位</t>
         </is>
       </c>
-      <c r="D21" s="39" t="n">
+      <c r="D21" s="40" t="n">
         <v>46265</v>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -9328,7 +10099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I39"/>
+  <dimension ref="B2:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -9342,594 +10113,605 @@
   </cols>
   <sheetData>
     <row r="2" ht="26" customHeight="1">
-      <c r="B2" s="40" t="inlineStr">
+      <c r="B2" s="41" t="inlineStr">
         <is>
           <t>凡例・入力ルール／進捗集計</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="35" t="inlineStr">
+      <c r="B4" s="36" t="inlineStr">
         <is>
           <t>■ 入力する列（ここだけ編集してください）</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="41" t="inlineStr">
+      <c r="B5" s="42" t="inlineStr">
         <is>
           <t>予定開始・予定完了</t>
         </is>
       </c>
-      <c r="C5" s="42" t="inlineStr">
+      <c r="C5" s="43" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="D5" s="42" t="inlineStr">
+      <c r="D5" s="43" t="inlineStr">
         <is>
           <t>yyyy/mm/dd 形式で入力します。村との協議で工程が固まり次第、入力してください。</t>
         </is>
       </c>
-      <c r="E5" s="43" t="n"/>
-      <c r="F5" s="43" t="n"/>
-      <c r="G5" s="43" t="n"/>
-      <c r="H5" s="43" t="n"/>
+      <c r="E5" s="44" t="n"/>
+      <c r="F5" s="44" t="n"/>
+      <c r="G5" s="44" t="n"/>
+      <c r="H5" s="44" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="41" t="inlineStr">
+      <c r="B6" s="42" t="inlineStr">
         <is>
           <t>実績開始・実績完了</t>
         </is>
       </c>
-      <c r="C6" s="42" t="inlineStr">
+      <c r="C6" s="43" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="D6" s="42" t="inlineStr">
+      <c r="D6" s="43" t="inlineStr">
         <is>
           <t>着手日・完了日を実績として入力します。</t>
         </is>
       </c>
-      <c r="E6" s="43" t="n"/>
-      <c r="F6" s="43" t="n"/>
-      <c r="G6" s="43" t="n"/>
-      <c r="H6" s="43" t="n"/>
+      <c r="E6" s="44" t="n"/>
+      <c r="F6" s="44" t="n"/>
+      <c r="G6" s="44" t="n"/>
+      <c r="H6" s="44" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="41" t="inlineStr">
+      <c r="B7" s="42" t="inlineStr">
         <is>
           <t>進捗率</t>
         </is>
       </c>
-      <c r="C7" s="42" t="inlineStr">
+      <c r="C7" s="43" t="inlineStr">
         <is>
           <t>％</t>
         </is>
       </c>
-      <c r="D7" s="42" t="inlineStr">
+      <c r="D7" s="43" t="inlineStr">
         <is>
           <t>0〜100% を入力します。完了時は 100%。</t>
         </is>
       </c>
-      <c r="E7" s="43" t="n"/>
-      <c r="F7" s="43" t="n"/>
-      <c r="G7" s="43" t="n"/>
-      <c r="H7" s="43" t="n"/>
+      <c r="E7" s="44" t="n"/>
+      <c r="F7" s="44" t="n"/>
+      <c r="G7" s="44" t="n"/>
+      <c r="H7" s="44" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="41" t="inlineStr">
+      <c r="B8" s="42" t="inlineStr">
         <is>
           <t>ステータス</t>
         </is>
       </c>
-      <c r="C8" s="42" t="inlineStr">
+      <c r="C8" s="43" t="inlineStr">
         <is>
           <t>選択</t>
         </is>
       </c>
-      <c r="D8" s="42" t="inlineStr">
+      <c r="D8" s="43" t="inlineStr">
         <is>
           <t>未着手／着手／確認中／完了／保留／対象外 から選択します。</t>
         </is>
       </c>
-      <c r="E8" s="43" t="n"/>
-      <c r="F8" s="43" t="n"/>
-      <c r="G8" s="43" t="n"/>
-      <c r="H8" s="43" t="n"/>
+      <c r="E8" s="44" t="n"/>
+      <c r="F8" s="44" t="n"/>
+      <c r="G8" s="44" t="n"/>
+      <c r="H8" s="44" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="41" t="inlineStr">
+      <c r="B9" s="42" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="C9" s="42" t="inlineStr">
+      <c r="C9" s="43" t="inlineStr">
         <is>
           <t>自由</t>
         </is>
       </c>
-      <c r="D9" s="42" t="inlineStr">
+      <c r="D9" s="43" t="inlineStr">
         <is>
           <t>課題・懸案・村への確認事項などを記入します。</t>
         </is>
       </c>
-      <c r="E9" s="43" t="n"/>
-      <c r="F9" s="43" t="n"/>
-      <c r="G9" s="43" t="n"/>
-      <c r="H9" s="43" t="n"/>
+      <c r="E9" s="44" t="n"/>
+      <c r="F9" s="44" t="n"/>
+      <c r="G9" s="44" t="n"/>
+      <c r="H9" s="44" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>■ 行の塗り分け</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="44" t="inlineStr">
+      <c r="B12" s="45" t="inlineStr">
         <is>
           <t>薄い緑</t>
         </is>
       </c>
-      <c r="C12" s="42" t="inlineStr">
+      <c r="C12" s="43" t="inlineStr">
         <is>
           <t>完了した作業です。</t>
         </is>
       </c>
-      <c r="D12" s="43" t="n"/>
-      <c r="E12" s="43" t="n"/>
-      <c r="F12" s="43" t="n"/>
-      <c r="G12" s="43" t="n"/>
-      <c r="H12" s="43" t="n"/>
+      <c r="D12" s="44" t="n"/>
+      <c r="E12" s="44" t="n"/>
+      <c r="F12" s="44" t="n"/>
+      <c r="G12" s="44" t="n"/>
+      <c r="H12" s="44" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="45" t="inlineStr">
+      <c r="B13" s="46" t="inlineStr">
         <is>
           <t>薄い黄</t>
         </is>
       </c>
-      <c r="C13" s="42" t="inlineStr">
+      <c r="C13" s="43" t="inlineStr">
         <is>
           <t>着手中・確認中の作業、または北塩原村が担当する作業です。</t>
         </is>
       </c>
-      <c r="D13" s="43" t="n"/>
-      <c r="E13" s="43" t="n"/>
-      <c r="F13" s="43" t="n"/>
-      <c r="G13" s="43" t="n"/>
-      <c r="H13" s="43" t="n"/>
+      <c r="D13" s="44" t="n"/>
+      <c r="E13" s="44" t="n"/>
+      <c r="F13" s="44" t="n"/>
+      <c r="G13" s="44" t="n"/>
+      <c r="H13" s="44" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="46" t="inlineStr">
+      <c r="B14" s="47" t="inlineStr">
         <is>
           <t>薄い赤</t>
         </is>
       </c>
-      <c r="C14" s="42" t="inlineStr">
-        <is>
-          <t>「村への確認事項」シートの優先度A、および未受領の資料です。</t>
-        </is>
-      </c>
-      <c r="D14" s="43" t="n"/>
-      <c r="E14" s="43" t="n"/>
-      <c r="F14" s="43" t="n"/>
-      <c r="G14" s="43" t="n"/>
-      <c r="H14" s="43" t="n"/>
+      <c r="C14" s="43" t="inlineStr">
+        <is>
+          <t>「村への確認事項」シートの優先度S・A、および未受領の資料です。</t>
+        </is>
+      </c>
+      <c r="D14" s="44" t="n"/>
+      <c r="E14" s="44" t="n"/>
+      <c r="F14" s="44" t="n"/>
+      <c r="G14" s="44" t="n"/>
+      <c r="H14" s="44" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="35" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>■ 進捗集計（WBSシートから自動集計されます）</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="47" t="inlineStr">
+      <c r="B17" s="48" t="inlineStr">
         <is>
           <t>大分類</t>
         </is>
       </c>
-      <c r="C17" s="47" t="inlineStr">
+      <c r="C17" s="48" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="D17" s="47" t="inlineStr">
+      <c r="D17" s="48" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="E17" s="47" t="inlineStr">
+      <c r="E17" s="48" t="inlineStr">
         <is>
           <t>着手</t>
         </is>
       </c>
-      <c r="F17" s="47" t="inlineStr">
+      <c r="F17" s="48" t="inlineStr">
         <is>
           <t>確認中</t>
         </is>
       </c>
-      <c r="G17" s="47" t="inlineStr">
+      <c r="G17" s="48" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="H17" s="47" t="inlineStr">
+      <c r="H17" s="48" t="inlineStr">
         <is>
           <t>保留</t>
         </is>
       </c>
-      <c r="I17" s="47" t="inlineStr">
+      <c r="I17" s="48" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="42" t="inlineStr">
+      <c r="B18" s="43" t="inlineStr">
         <is>
           <t>０ 契約・立上げ</t>
         </is>
       </c>
-      <c r="C18" s="48">
+      <c r="C18" s="49">
         <f>COUNTIF('WBS・進捗管理'!$B$5:$B$101,$B18)</f>
         <v/>
       </c>
-      <c r="D18" s="48">
+      <c r="D18" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B18,'WBS・進捗管理'!$O$5:$O$101,D$17)</f>
         <v/>
       </c>
-      <c r="E18" s="48">
+      <c r="E18" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B18,'WBS・進捗管理'!$O$5:$O$101,E$17)</f>
         <v/>
       </c>
-      <c r="F18" s="48">
+      <c r="F18" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B18,'WBS・進捗管理'!$O$5:$O$101,F$17)</f>
         <v/>
       </c>
-      <c r="G18" s="48">
+      <c r="G18" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B18,'WBS・進捗管理'!$O$5:$O$101,G$17)</f>
         <v/>
       </c>
-      <c r="H18" s="48">
+      <c r="H18" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B18,'WBS・進捗管理'!$O$5:$O$101,H$17)</f>
         <v/>
       </c>
-      <c r="I18" s="48">
+      <c r="I18" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B18,'WBS・進捗管理'!$O$5:$O$101,I$17)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="42" t="inlineStr">
+      <c r="B19" s="43" t="inlineStr">
         <is>
           <t>Ⅰ ニーズ調査</t>
         </is>
       </c>
-      <c r="C19" s="48">
+      <c r="C19" s="49">
         <f>COUNTIF('WBS・進捗管理'!$B$5:$B$101,$B19)</f>
         <v/>
       </c>
-      <c r="D19" s="48">
+      <c r="D19" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B19,'WBS・進捗管理'!$O$5:$O$101,D$17)</f>
         <v/>
       </c>
-      <c r="E19" s="48">
+      <c r="E19" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B19,'WBS・進捗管理'!$O$5:$O$101,E$17)</f>
         <v/>
       </c>
-      <c r="F19" s="48">
+      <c r="F19" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B19,'WBS・進捗管理'!$O$5:$O$101,F$17)</f>
         <v/>
       </c>
-      <c r="G19" s="48">
+      <c r="G19" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B19,'WBS・進捗管理'!$O$5:$O$101,G$17)</f>
         <v/>
       </c>
-      <c r="H19" s="48">
+      <c r="H19" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B19,'WBS・進捗管理'!$O$5:$O$101,H$17)</f>
         <v/>
       </c>
-      <c r="I19" s="48">
+      <c r="I19" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B19,'WBS・進捗管理'!$O$5:$O$101,I$17)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="42" t="inlineStr">
+      <c r="B20" s="43" t="inlineStr">
         <is>
           <t>Ⅱ 計画策定</t>
         </is>
       </c>
-      <c r="C20" s="48">
+      <c r="C20" s="49">
         <f>COUNTIF('WBS・進捗管理'!$B$5:$B$101,$B20)</f>
         <v/>
       </c>
-      <c r="D20" s="48">
+      <c r="D20" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B20,'WBS・進捗管理'!$O$5:$O$101,D$17)</f>
         <v/>
       </c>
-      <c r="E20" s="48">
+      <c r="E20" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B20,'WBS・進捗管理'!$O$5:$O$101,E$17)</f>
         <v/>
       </c>
-      <c r="F20" s="48">
+      <c r="F20" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B20,'WBS・進捗管理'!$O$5:$O$101,F$17)</f>
         <v/>
       </c>
-      <c r="G20" s="48">
+      <c r="G20" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B20,'WBS・進捗管理'!$O$5:$O$101,G$17)</f>
         <v/>
       </c>
-      <c r="H20" s="48">
+      <c r="H20" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B20,'WBS・進捗管理'!$O$5:$O$101,H$17)</f>
         <v/>
       </c>
-      <c r="I20" s="48">
+      <c r="I20" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B20,'WBS・進捗管理'!$O$5:$O$101,I$17)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="42" t="inlineStr">
+      <c r="B21" s="43" t="inlineStr">
         <is>
           <t>Ⅲ 打合せ等</t>
         </is>
       </c>
-      <c r="C21" s="48">
+      <c r="C21" s="49">
         <f>COUNTIF('WBS・進捗管理'!$B$5:$B$101,$B21)</f>
         <v/>
       </c>
-      <c r="D21" s="48">
+      <c r="D21" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B21,'WBS・進捗管理'!$O$5:$O$101,D$17)</f>
         <v/>
       </c>
-      <c r="E21" s="48">
+      <c r="E21" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B21,'WBS・進捗管理'!$O$5:$O$101,E$17)</f>
         <v/>
       </c>
-      <c r="F21" s="48">
+      <c r="F21" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B21,'WBS・進捗管理'!$O$5:$O$101,F$17)</f>
         <v/>
       </c>
-      <c r="G21" s="48">
+      <c r="G21" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B21,'WBS・進捗管理'!$O$5:$O$101,G$17)</f>
         <v/>
       </c>
-      <c r="H21" s="48">
+      <c r="H21" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B21,'WBS・進捗管理'!$O$5:$O$101,H$17)</f>
         <v/>
       </c>
-      <c r="I21" s="48">
+      <c r="I21" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B21,'WBS・進捗管理'!$O$5:$O$101,I$17)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="42" t="inlineStr">
+      <c r="B22" s="43" t="inlineStr">
         <is>
           <t>Ⅳ 成果品・納品</t>
         </is>
       </c>
-      <c r="C22" s="48">
+      <c r="C22" s="49">
         <f>COUNTIF('WBS・進捗管理'!$B$5:$B$101,$B22)</f>
         <v/>
       </c>
-      <c r="D22" s="48">
+      <c r="D22" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B22,'WBS・進捗管理'!$O$5:$O$101,D$17)</f>
         <v/>
       </c>
-      <c r="E22" s="48">
+      <c r="E22" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B22,'WBS・進捗管理'!$O$5:$O$101,E$17)</f>
         <v/>
       </c>
-      <c r="F22" s="48">
+      <c r="F22" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B22,'WBS・進捗管理'!$O$5:$O$101,F$17)</f>
         <v/>
       </c>
-      <c r="G22" s="48">
+      <c r="G22" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B22,'WBS・進捗管理'!$O$5:$O$101,G$17)</f>
         <v/>
       </c>
-      <c r="H22" s="48">
+      <c r="H22" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B22,'WBS・進捗管理'!$O$5:$O$101,H$17)</f>
         <v/>
       </c>
-      <c r="I22" s="48">
+      <c r="I22" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B22,'WBS・進捗管理'!$O$5:$O$101,I$17)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="42" t="inlineStr">
+      <c r="B23" s="43" t="inlineStr">
         <is>
           <t>Ⅴ 管理</t>
         </is>
       </c>
-      <c r="C23" s="48">
+      <c r="C23" s="49">
         <f>COUNTIF('WBS・進捗管理'!$B$5:$B$101,$B23)</f>
         <v/>
       </c>
-      <c r="D23" s="48">
+      <c r="D23" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B23,'WBS・進捗管理'!$O$5:$O$101,D$17)</f>
         <v/>
       </c>
-      <c r="E23" s="48">
+      <c r="E23" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B23,'WBS・進捗管理'!$O$5:$O$101,E$17)</f>
         <v/>
       </c>
-      <c r="F23" s="48">
+      <c r="F23" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B23,'WBS・進捗管理'!$O$5:$O$101,F$17)</f>
         <v/>
       </c>
-      <c r="G23" s="48">
+      <c r="G23" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B23,'WBS・進捗管理'!$O$5:$O$101,G$17)</f>
         <v/>
       </c>
-      <c r="H23" s="48">
+      <c r="H23" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B23,'WBS・進捗管理'!$O$5:$O$101,H$17)</f>
         <v/>
       </c>
-      <c r="I23" s="48">
+      <c r="I23" s="49">
         <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B23,'WBS・進捗管理'!$O$5:$O$101,I$17)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="49" t="inlineStr">
+      <c r="B24" s="50" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="C24" s="50">
+      <c r="C24" s="51">
         <f>SUM(C18:C23)</f>
         <v/>
       </c>
-      <c r="D24" s="50">
+      <c r="D24" s="51">
         <f>SUM(D18:D23)</f>
         <v/>
       </c>
-      <c r="E24" s="50">
+      <c r="E24" s="51">
         <f>SUM(E18:E23)</f>
         <v/>
       </c>
-      <c r="F24" s="50">
+      <c r="F24" s="51">
         <f>SUM(F18:F23)</f>
         <v/>
       </c>
-      <c r="G24" s="50">
+      <c r="G24" s="51">
         <f>SUM(G18:G23)</f>
         <v/>
       </c>
-      <c r="H24" s="50">
+      <c r="H24" s="51">
         <f>SUM(H18:H23)</f>
         <v/>
       </c>
-      <c r="I24" s="50">
+      <c r="I24" s="51">
         <f>SUM(I18:I23)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="35" t="inlineStr">
+      <c r="B26" s="36" t="inlineStr">
         <is>
           <t>■ 主要指標</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="51" t="inlineStr">
+      <c r="B27" s="52" t="inlineStr">
         <is>
           <t>全体進捗率（平均）</t>
         </is>
       </c>
-      <c r="C27" s="52">
+      <c r="C27" s="53">
         <f>AVERAGE('WBS・進捗管理'!$N$5:$N$101)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="51" t="inlineStr">
+      <c r="B28" s="52" t="inlineStr">
         <is>
           <t>作業総数</t>
         </is>
       </c>
-      <c r="C28" s="53">
+      <c r="C28" s="54">
         <f>COUNTA('WBS・進捗管理'!$A$5:$A$101)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="51" t="inlineStr">
+      <c r="B29" s="52" t="inlineStr">
         <is>
           <t>完了した作業</t>
         </is>
       </c>
-      <c r="C29" s="53">
+      <c r="C29" s="54">
         <f>COUNTIF('WBS・進捗管理'!$O$5:$O$101,"完了")</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="51" t="inlineStr">
+      <c r="B30" s="52" t="inlineStr">
         <is>
           <t>着手・確認中の作業</t>
         </is>
       </c>
-      <c r="C30" s="53">
+      <c r="C30" s="54">
         <f>COUNTIF('WBS・進捗管理'!$O$5:$O$101,"着手")+COUNTIF('WBS・進捗管理'!$O$5:$O$101,"確認中")</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="51" t="inlineStr">
+      <c r="B31" s="52" t="inlineStr">
         <is>
           <t>未着手の作業</t>
         </is>
       </c>
-      <c r="C31" s="53">
+      <c r="C31" s="54">
         <f>COUNTIF('WBS・進捗管理'!$O$5:$O$101,"未着手")</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="51" t="inlineStr">
+      <c r="B32" s="52" t="inlineStr">
+        <is>
+          <t>村への確認事項（優先度S）</t>
+        </is>
+      </c>
+      <c r="C32" s="54">
+        <f>COUNTIF('村への確認事項'!$A:$A,"S")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="52" t="inlineStr">
         <is>
           <t>村への確認事項（優先度A）</t>
         </is>
       </c>
-      <c r="C32" s="53">
+      <c r="C33" s="54">
         <f>COUNTIF('村への確認事項'!$A:$A,"A")</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="51" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="52" t="inlineStr">
         <is>
           <t>村への確認事項（未依頼）</t>
         </is>
       </c>
-      <c r="C33" s="53">
+      <c r="C34" s="54">
         <f>COUNTIF('村への確認事項'!$G:$G,"未依頼")</f>
         <v/>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="51" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="52" t="inlineStr">
         <is>
           <t>未受領の資料・データ</t>
         </is>
       </c>
-      <c r="C34" s="53">
+      <c r="C35" s="54">
         <f>COUNTIF('受領資料・データ管理'!$F:$F,"未受領")</f>
         <v/>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="54" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="55" t="inlineStr">
         <is>
           <t>※「仕様書該当」欄の凡例：仕様書＝8北保福第483号 別紙／手引き＝厚生労働省の実施の手引き（令和7年8月版）／確認＝本業務での確認事項</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="54" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="55" t="inlineStr">
         <is>
           <t>※ 想定時期は仕様書の履行期限（令和9年3月31日）から逆算した目安です。村との協議結果により確定します。</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="54" t="inlineStr">
+    <row r="39">
+      <c r="B39" s="55" t="inlineStr">
         <is>
           <t>※ 令和8年9月19日（土）〜23日（水）は5連休（敬老の日9/21・国民の休日9/22・秋分の日9/23）です。発送・回収工程に影響します。</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="54" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="55" t="inlineStr">
         <is>
           <t>※ 進捗基準日は令和8年8月31日です。備考欄の doc番号は docs/北塩原村_第10期/ 配下の分析資料に対応します。</t>
         </is>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -4080,7 +4080,7 @@
       </c>
       <c r="M58" s="14" t="n"/>
       <c r="N58" s="15" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="O58" s="16" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="P58" s="13" t="inlineStr">
         <is>
-          <t>doc14で第9期施策19本を評価。村単独事業の実績資料が未受領のため一部保留。</t>
+          <t>doc14で第9期施策19本を評価。キックオフ資料により村単独事業名（除雪サービス・緊急通報・生活支援ハウス・はつらつ貯筋教室等）を把握。実績数値は未受領のため一部保留。</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M71" s="14" t="n"/>
       <c r="N71" s="15" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="O71" s="16" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="P71" s="13" t="inlineStr">
         <is>
-          <t>doc14として施策案28本（継続11／強化7／新規9／改称1）を整理。基本目標5「計画の推進と進捗管理」の新設を提案。国の基本指針で追加・修正の可能性。</t>
+          <t>doc14・doc18として施策案を整理。第4章は26施策。住民ニーズ第1位の除雪を独立施策（2-6）として新設。基本目標5「計画の推進と進捗管理」の新設を提案。国の基本指針で追加・修正の可能性。</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="M79" s="14" t="n"/>
       <c r="N79" s="15" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="O79" s="16" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="P79" s="13" t="inlineStr">
         <is>
-          <t>doc18／output/06_計画素案.docx として全6章・63節・56表を作成。第1〜4章・第6章は本文執筆済。第5章は国ワークシート待ちのため枠組みのみ。【要確認】【要設定】を明示。</t>
+          <t>doc18／output/06_計画素案.docx として全6章・64節・59表を作成。キックオフ資料から判明した第9期調査結果（除雪27.5%ほか）・事業名・診療所・定住自立圏を反映。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。第5章は国ワークシート待ち。</t>
         </is>
       </c>
     </row>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -5412,7 +5412,7 @@
       </c>
       <c r="M79" s="14" t="n"/>
       <c r="N79" s="15" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="O79" s="16" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="P79" s="13" t="inlineStr">
         <is>
-          <t>doc18／output/06_計画素案.docx として全6章・64節・59表を作成。キックオフ資料から判明した第9期調査結果（除雪27.5%ほか）・事業名・診療所・定住自立圏を反映。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。第5章は国ワークシート待ち。</t>
+          <t>doc18／output/06_計画素案.docx として全6章・64節・59表・図16点を作成。第2章の図はモノクロ印刷を前提に明度差＋線種＋マーカー＋ハッチングで識別。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。第5章は国ワークシート待ち。</t>
         </is>
       </c>
     </row>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -5421,7 +5421,7 @@
       </c>
       <c r="P79" s="13" t="inlineStr">
         <is>
-          <t>doc18／output/06_計画素案.docx として全6章・64節・59表・図16点を作成。第2章の図はモノクロ印刷を前提に明度差＋線種＋マーカー＋ハッチングで識別。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。第5章は国ワークシート待ち。</t>
+          <t>doc18／output/06_計画素案.docx として全6章・64節・61表・図18点を作成。第2章の図はモノクロ印刷を前提に明度差＋線種＋マーカー＋ハッチングで識別。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。サービス区分別分析（訪問系−50.8%）を追加。第5章は国ワークシート待ち。</t>
         </is>
       </c>
     </row>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -4486,124 +4486,136 @@
       </c>
     </row>
     <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="23" t="inlineStr">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t>Ⅱ-61</t>
         </is>
       </c>
-      <c r="B65" s="24" t="inlineStr">
+      <c r="B65" s="12" t="inlineStr">
         <is>
           <t>Ⅱ 計画策定</t>
         </is>
       </c>
-      <c r="C65" s="24" t="inlineStr">
+      <c r="C65" s="12" t="inlineStr">
         <is>
           <t>Ⅱ-3 見込量・保険料</t>
         </is>
       </c>
-      <c r="D65" s="25" t="inlineStr">
+      <c r="D65" s="13" t="inlineStr">
         <is>
           <t>各介護保険サービス見込量の推計</t>
         </is>
       </c>
-      <c r="E65" s="23" t="inlineStr">
+      <c r="E65" s="11" t="inlineStr">
         <is>
           <t>仕様書4Ⅱ(3)②</t>
         </is>
       </c>
-      <c r="F65" s="23" t="inlineStr">
+      <c r="F65" s="11" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G65" s="25" t="inlineStr">
+      <c r="G65" s="13" t="inlineStr">
         <is>
           <t>見込量表</t>
         </is>
       </c>
-      <c r="H65" s="25" t="inlineStr">
+      <c r="H65" s="13" t="inlineStr">
         <is>
           <t>居宅・施設・地域密着型・総合事業。村外利用を考慮</t>
         </is>
       </c>
-      <c r="I65" s="23" t="inlineStr">
+      <c r="I65" s="11" t="inlineStr">
         <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="J65" s="26" t="n"/>
-      <c r="K65" s="26" t="n"/>
-      <c r="L65" s="26" t="n"/>
-      <c r="M65" s="26" t="n"/>
-      <c r="N65" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P65" s="25" t="inlineStr"/>
+      <c r="J65" s="14" t="n"/>
+      <c r="K65" s="14" t="n"/>
+      <c r="L65" s="14" t="n">
+        <v>46265</v>
+      </c>
+      <c r="M65" s="14" t="n"/>
+      <c r="N65" s="15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O65" s="16" t="inlineStr">
+        <is>
+          <t>着手</t>
+        </is>
+      </c>
+      <c r="P65" s="13" t="inlineStr">
+        <is>
+          <t>doc18 第5章5-4に見込量の様式を作成。27サービスの利用状況（実績あり18／過去のみ5／実績なし4）を確定し、受給者1人あたり利用日数・回数の実績を整理。受給者数の実績と見込量の数値は国ワークシートと村の月報・年報待ち。</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="18" t="inlineStr">
+      <c r="A66" s="11" t="inlineStr">
         <is>
           <t>Ⅱ-62</t>
         </is>
       </c>
-      <c r="B66" s="19" t="inlineStr">
+      <c r="B66" s="12" t="inlineStr">
         <is>
           <t>Ⅱ 計画策定</t>
         </is>
       </c>
-      <c r="C66" s="19" t="inlineStr">
+      <c r="C66" s="12" t="inlineStr">
         <is>
           <t>Ⅱ-3 見込量・保険料</t>
         </is>
       </c>
-      <c r="D66" s="20" t="inlineStr">
+      <c r="D66" s="13" t="inlineStr">
         <is>
           <t>給付費の試算</t>
         </is>
       </c>
-      <c r="E66" s="18" t="inlineStr">
+      <c r="E66" s="11" t="inlineStr">
         <is>
           <t>仕様書4Ⅱ(3)③</t>
         </is>
       </c>
-      <c r="F66" s="18" t="inlineStr">
+      <c r="F66" s="11" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G66" s="20" t="inlineStr">
+      <c r="G66" s="13" t="inlineStr">
         <is>
           <t>給付費試算表</t>
         </is>
       </c>
-      <c r="H66" s="20" t="inlineStr">
+      <c r="H66" s="13" t="inlineStr">
         <is>
           <t>R9年度報酬改定は現行単価で仮試算→確定後に精緻化</t>
         </is>
       </c>
-      <c r="I66" s="18" t="inlineStr">
+      <c r="I66" s="11" t="inlineStr">
         <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="J66" s="21" t="n"/>
-      <c r="K66" s="21" t="n"/>
-      <c r="L66" s="21" t="n"/>
-      <c r="M66" s="21" t="n"/>
-      <c r="N66" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="18" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P66" s="20" t="inlineStr"/>
+      <c r="J66" s="14" t="n"/>
+      <c r="K66" s="14" t="n"/>
+      <c r="L66" s="14" t="n">
+        <v>46265</v>
+      </c>
+      <c r="M66" s="14" t="n"/>
+      <c r="N66" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O66" s="16" t="inlineStr">
+        <is>
+          <t>着手</t>
+        </is>
+      </c>
+      <c r="P66" s="13" t="inlineStr">
+        <is>
+          <t>doc18 第5章5-6に標準給付費の様式を作成。第9期の計画値と実績の対比を参考として掲載。数値は国ワークシート待ち。</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="11" t="inlineStr">
@@ -4672,64 +4684,70 @@
       </c>
     </row>
     <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="18" t="inlineStr">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t>Ⅱ-64</t>
         </is>
       </c>
-      <c r="B68" s="19" t="inlineStr">
+      <c r="B68" s="12" t="inlineStr">
         <is>
           <t>Ⅱ 計画策定</t>
         </is>
       </c>
-      <c r="C68" s="19" t="inlineStr">
+      <c r="C68" s="12" t="inlineStr">
         <is>
           <t>Ⅱ-3 見込量・保険料</t>
         </is>
       </c>
-      <c r="D68" s="20" t="inlineStr">
+      <c r="D68" s="13" t="inlineStr">
         <is>
           <t>介護保険料の試算（複数案の比較）</t>
         </is>
       </c>
-      <c r="E68" s="18" t="inlineStr">
+      <c r="E68" s="11" t="inlineStr">
         <is>
           <t>仕様書4Ⅱ(3)③</t>
         </is>
       </c>
-      <c r="F68" s="18" t="inlineStr">
+      <c r="F68" s="11" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G68" s="20" t="inlineStr">
+      <c r="G68" s="13" t="inlineStr">
         <is>
           <t>保険料試算表</t>
         </is>
       </c>
-      <c r="H68" s="20" t="inlineStr">
+      <c r="H68" s="13" t="inlineStr">
         <is>
           <t>所得段階・基金活用・上限の設定を反映</t>
         </is>
       </c>
-      <c r="I68" s="18" t="inlineStr">
+      <c r="I68" s="11" t="inlineStr">
         <is>
           <t>R8.12〜R9.1</t>
         </is>
       </c>
-      <c r="J68" s="21" t="n"/>
-      <c r="K68" s="21" t="n"/>
-      <c r="L68" s="21" t="n"/>
-      <c r="M68" s="21" t="n"/>
-      <c r="N68" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="18" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P68" s="20" t="inlineStr"/>
+      <c r="J68" s="14" t="n"/>
+      <c r="K68" s="14" t="n"/>
+      <c r="L68" s="14" t="n">
+        <v>46265</v>
+      </c>
+      <c r="M68" s="14" t="n"/>
+      <c r="N68" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O68" s="16" t="inlineStr">
+        <is>
+          <t>着手</t>
+        </is>
+      </c>
+      <c r="P68" s="13" t="inlineStr">
+        <is>
+          <t>doc18 第5章5-7に保険料算定の様式と所得段階13段階の枠を作成。第9期の算定結果を参考掲載。基金残高と国ワークシート待ち。</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="11" t="inlineStr">
@@ -5421,7 +5439,7 @@
       </c>
       <c r="P79" s="13" t="inlineStr">
         <is>
-          <t>doc18／output/06_計画素案.docx として全6章・64節・61表・図18点を作成。第2章の図はモノクロ印刷を前提に明度差＋線種＋マーカー＋ハッチングで識別。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。サービス区分別分析（訪問系−50.8%）を追加。第5章は国ワークシート待ち。</t>
+          <t>doc18／output/06_計画素案.docx として全6章・65節・73表・図18点を作成。第2章の図はモノクロ印刷を前提に明度差＋線種＋マーカー＋ハッチングで識別。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。サービス区分別分析（訪問系−50.8%）を追加。第5章に見込量27サービスの様式・保険料算定様式・所得段階13段階・2040年見通しの枠を作成。数値は国ワークシート待ち。</t>
         </is>
       </c>
     </row>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="WBS・進捗管理" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="村への確認事項" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="受領資料・データ管理" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="凡例・集計" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS・進捗管理" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="村への確認事項" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受領資料・データ管理" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="凡例・集計" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$101</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -6779,7 +6779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7464,27 +7464,27 @@
       </c>
       <c r="B21" s="30" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C21" s="31" t="inlineStr">
         <is>
-          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
+          <t>給付費適正化事業（ケアプラン点検・住宅改修点検・医療情報突合・縦覧点検・給付費通知）の実施状況</t>
         </is>
       </c>
       <c r="D21" s="31" t="inlineStr">
         <is>
-          <t>連絡体制表の確定。第9期概要版の発行は住民課。</t>
+          <t>★令和8年度交付金評価で推進目標Ⅱ「給付費適正化事業の取組状況」ア・ウ・エ・オが全て0点（アの全国該当率96.9%）。配点計30点の取りこぼしで最優先。</t>
         </is>
       </c>
       <c r="E21" s="32" t="inlineStr">
         <is>
-          <t>０-04</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F21" s="32" t="inlineStr">
         <is>
-          <t>doc01-1</t>
+          <t>doc20§6-2 K-61</t>
         </is>
       </c>
       <c r="G21" s="32" t="inlineStr">
@@ -7502,27 +7502,27 @@
       </c>
       <c r="B22" s="30" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C22" s="31" t="inlineStr">
         <is>
-          <t>契約締結日・契約書の取り交わし状況</t>
+          <t>認知症サポーター養成数・認知症地域支援推進員の配置と活動内容・チームオレンジの整備予定</t>
         </is>
       </c>
       <c r="D22" s="31" t="inlineStr">
         <is>
-          <t>業務開始日の確定。</t>
+          <t>★支援交付金目標Ⅱ（認知症総合支援）は32/100点で全国平均51.1点を19点下回る唯一の目標。3か年で唯一低下局面があった。</t>
         </is>
       </c>
       <c r="E22" s="32" t="inlineStr">
         <is>
-          <t>０-02</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F22" s="32" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>doc20§6-2 K-62</t>
         </is>
       </c>
       <c r="G22" s="32" t="inlineStr">
@@ -7540,27 +7540,27 @@
       </c>
       <c r="B23" s="30" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C23" s="31" t="inlineStr">
         <is>
-          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
+          <t>難聴高齢者の早期発見・早期介入の取組（健診での聴力チェック等）の有無</t>
         </is>
       </c>
       <c r="D23" s="31" t="inlineStr">
         <is>
-          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
+          <t>令和8年度評価で配点10点が0点（全国該当率48.8〜68.9%）。保健事業との連携で取得可能。</t>
         </is>
       </c>
       <c r="E23" s="32" t="inlineStr">
         <is>
-          <t>０-06</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F23" s="32" t="inlineStr">
         <is>
-          <t>doc19 追-12</t>
+          <t>doc20§6-2 K-63</t>
         </is>
       </c>
       <c r="G23" s="32" t="inlineStr">
@@ -7578,27 +7578,27 @@
       </c>
       <c r="B24" s="30" t="inlineStr">
         <is>
-          <t>委員会</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C24" s="31" t="inlineStr">
         <is>
-          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
+          <t>在宅医療・介護連携推進事業の実施体制（村単独か会津圏域か）と課題・対応策の検討の場</t>
         </is>
       </c>
       <c r="D24" s="31" t="inlineStr">
         <is>
-          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
+          <t>支援交付金目標Ⅲの「課題・対応策の検討」ア・エが0点（配点計10点、全国該当率57〜72%）。</t>
         </is>
       </c>
       <c r="E24" s="32" t="inlineStr">
         <is>
-          <t>Ⅱ-80,Ⅱ-81</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F24" s="32" t="inlineStr">
         <is>
-          <t>doc01-6,doc19 追-15</t>
+          <t>doc20§6-2 K-64</t>
         </is>
       </c>
       <c r="G24" s="32" t="inlineStr">
@@ -7616,301 +7616,301 @@
       </c>
       <c r="B25" s="30" t="inlineStr">
         <is>
+          <t>体制</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="inlineStr">
+        <is>
+          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
+        </is>
+      </c>
+      <c r="D25" s="31" t="inlineStr">
+        <is>
+          <t>連絡体制表の確定。第9期概要版の発行は住民課。</t>
+        </is>
+      </c>
+      <c r="E25" s="32" t="inlineStr">
+        <is>
+          <t>０-04</t>
+        </is>
+      </c>
+      <c r="F25" s="32" t="inlineStr">
+        <is>
+          <t>doc01-1</t>
+        </is>
+      </c>
+      <c r="G25" s="32" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H25" s="31" t="inlineStr"/>
+    </row>
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>体制</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="inlineStr">
+        <is>
+          <t>契約締結日・契約書の取り交わし状況</t>
+        </is>
+      </c>
+      <c r="D26" s="31" t="inlineStr">
+        <is>
+          <t>業務開始日の確定。</t>
+        </is>
+      </c>
+      <c r="E26" s="32" t="inlineStr">
+        <is>
+          <t>０-02</t>
+        </is>
+      </c>
+      <c r="F26" s="32" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G26" s="32" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H26" s="31" t="inlineStr"/>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>体制</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="inlineStr">
+        <is>
+          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
+        </is>
+      </c>
+      <c r="D27" s="31" t="inlineStr">
+        <is>
+          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
+        </is>
+      </c>
+      <c r="E27" s="32" t="inlineStr">
+        <is>
+          <t>０-06</t>
+        </is>
+      </c>
+      <c r="F27" s="32" t="inlineStr">
+        <is>
+          <t>doc19 追-12</t>
+        </is>
+      </c>
+      <c r="G27" s="32" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H27" s="31" t="inlineStr"/>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>委員会</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="inlineStr">
+        <is>
+          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
+        </is>
+      </c>
+      <c r="D28" s="31" t="inlineStr">
+        <is>
+          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
+        </is>
+      </c>
+      <c r="E28" s="32" t="inlineStr">
+        <is>
+          <t>Ⅱ-80,Ⅱ-81</t>
+        </is>
+      </c>
+      <c r="F28" s="32" t="inlineStr">
+        <is>
+          <t>doc01-6,doc19 追-15</t>
+        </is>
+      </c>
+      <c r="G28" s="32" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H28" s="31" t="inlineStr"/>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C25" s="31" t="inlineStr">
+      <c r="C29" s="31" t="inlineStr">
         <is>
           <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
         </is>
       </c>
-      <c r="D25" s="31" t="inlineStr">
+      <c r="D29" s="31" t="inlineStr">
         <is>
           <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
         </is>
       </c>
-      <c r="E25" s="32" t="inlineStr">
+      <c r="E29" s="32" t="inlineStr">
         <is>
           <t>Ⅱ-76,Ⅱ-77</t>
         </is>
       </c>
-      <c r="F25" s="32" t="inlineStr">
+      <c r="F29" s="32" t="inlineStr">
         <is>
           <t>doc01-7,doc19 指-3</t>
         </is>
       </c>
-      <c r="G25" s="32" t="inlineStr">
+      <c r="G29" s="32" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H25" s="31" t="inlineStr"/>
-    </row>
-    <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B26" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C26" s="25" t="inlineStr">
-        <is>
-          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
-        </is>
-      </c>
-      <c r="D26" s="25" t="inlineStr">
-        <is>
-          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
-        </is>
-      </c>
-      <c r="E26" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F26" s="23" t="inlineStr">
-        <is>
-          <t>doc02§22,doc08§8</t>
-        </is>
-      </c>
-      <c r="G26" s="23" t="inlineStr">
+      <c r="H29" s="31" t="inlineStr"/>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>方針</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="inlineStr">
+        <is>
+          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
+        </is>
+      </c>
+      <c r="D30" s="31" t="inlineStr">
+        <is>
+          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
+        </is>
+      </c>
+      <c r="E30" s="32" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F30" s="32" t="inlineStr">
+        <is>
+          <t>doc20§6-2 K-66</t>
+        </is>
+      </c>
+      <c r="G30" s="32" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H26" s="25" t="inlineStr"/>
-    </row>
-    <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B27" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C27" s="25" t="inlineStr">
-        <is>
-          <t>令和6年度決算および令和7年度の給付費見込</t>
-        </is>
-      </c>
-      <c r="D27" s="25" t="inlineStr">
-        <is>
-          <t>第9期の計画値と実績の乖離を確定させるために必要。</t>
-        </is>
-      </c>
-      <c r="E27" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
-        </is>
-      </c>
-      <c r="F27" s="23" t="inlineStr">
-        <is>
-          <t>doc08§8-1</t>
-        </is>
-      </c>
-      <c r="G27" s="23" t="inlineStr">
+      <c r="H30" s="31" t="inlineStr"/>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="inlineStr">
+        <is>
+          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
+        </is>
+      </c>
+      <c r="D31" s="31" t="inlineStr">
+        <is>
+          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
+        </is>
+      </c>
+      <c r="E31" s="32" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F31" s="32" t="inlineStr">
+        <is>
+          <t>doc21§5 K-69</t>
+        </is>
+      </c>
+      <c r="G31" s="32" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H27" s="25" t="inlineStr"/>
-    </row>
-    <row r="28" ht="34" customHeight="1">
-      <c r="A28" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B28" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C28" s="25" t="inlineStr">
-        <is>
-          <t>通いの場の実数（令和3〜7年度）</t>
-        </is>
-      </c>
-      <c r="D28" s="25" t="inlineStr">
-        <is>
-          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。</t>
-        </is>
-      </c>
-      <c r="E28" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F28" s="23" t="inlineStr">
-        <is>
-          <t>doc02§16,§22</t>
-        </is>
-      </c>
-      <c r="G28" s="23" t="inlineStr">
+      <c r="H31" s="31" t="inlineStr"/>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C32" s="31" t="inlineStr">
+        <is>
+          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
+        </is>
+      </c>
+      <c r="D32" s="31" t="inlineStr">
+        <is>
+          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
+        </is>
+      </c>
+      <c r="E32" s="32" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F32" s="32" t="inlineStr">
+        <is>
+          <t>doc21§5 K-70</t>
+        </is>
+      </c>
+      <c r="G32" s="32" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H28" s="25" t="inlineStr"/>
-    </row>
-    <row r="29" ht="34" customHeight="1">
-      <c r="A29" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B29" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C29" s="25" t="inlineStr">
-        <is>
-          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
-        </is>
-      </c>
-      <c r="D29" s="25" t="inlineStr">
-        <is>
-          <t>成果目標・活動指標の目標値設定に必要。P1〜P4で主要4指標は解決済だがW系は未入手。</t>
-        </is>
-      </c>
-      <c r="E29" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F29" s="23" t="inlineStr">
-        <is>
-          <t>doc07§8-2,doc09§10</t>
-        </is>
-      </c>
-      <c r="G29" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H29" s="25" t="inlineStr"/>
-    </row>
-    <row r="30" ht="34" customHeight="1">
-      <c r="A30" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B30" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>交付要綱の配点表（満点）</t>
-        </is>
-      </c>
-      <c r="D30" s="25" t="inlineStr">
-        <is>
-          <t>得点しか出力されず達成率が算出できない。</t>
-        </is>
-      </c>
-      <c r="E30" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F30" s="23" t="inlineStr">
-        <is>
-          <t>doc07§8-1</t>
-        </is>
-      </c>
-      <c r="G30" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H30" s="25" t="inlineStr"/>
-    </row>
-    <row r="31" ht="34" customHeight="1">
-      <c r="A31" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B31" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C31" s="25" t="inlineStr">
-        <is>
-          <t>令和6年度・令和7年度の交付金評価結果</t>
-        </is>
-      </c>
-      <c r="D31" s="25" t="inlineStr">
-        <is>
-          <t>受領データは令和5年度まで。第10期の基準値は最新年度に置くべき。</t>
-        </is>
-      </c>
-      <c r="E31" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F31" s="23" t="inlineStr">
-        <is>
-          <t>doc07§8-5</t>
-        </is>
-      </c>
-      <c r="G31" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H31" s="25" t="inlineStr"/>
-    </row>
-    <row r="32" ht="34" customHeight="1">
-      <c r="A32" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B32" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C32" s="25" t="inlineStr">
-        <is>
-          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
-        </is>
-      </c>
-      <c r="D32" s="25" t="inlineStr">
-        <is>
-          <t>見える化に該当データがない。第9期は基本目標4-4に位置づけ。</t>
-        </is>
-      </c>
-      <c r="E32" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-68,Ⅱ-69</t>
-        </is>
-      </c>
-      <c r="F32" s="23" t="inlineStr">
-        <is>
-          <t>doc08§8-5</t>
-        </is>
-      </c>
-      <c r="G32" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H32" s="25" t="inlineStr"/>
+      <c r="H32" s="31" t="inlineStr"/>
     </row>
     <row r="33" ht="34" customHeight="1">
       <c r="A33" s="34" t="inlineStr">
@@ -7925,22 +7925,22 @@
       </c>
       <c r="C33" s="25" t="inlineStr">
         <is>
-          <t>高齢者福祉事業（村単独事業）の実績資料</t>
+          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
         </is>
       </c>
       <c r="D33" s="25" t="inlineStr">
         <is>
-          <t>現行計画の評価に必要。</t>
+          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
         </is>
       </c>
       <c r="E33" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t>doc01-11</t>
+          <t>doc02§22,doc08§8</t>
         </is>
       </c>
       <c r="G33" s="23" t="inlineStr">
@@ -7963,22 +7963,22 @@
       </c>
       <c r="C34" s="25" t="inlineStr">
         <is>
-          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
+          <t>令和6年度決算および令和7年度の給付費見込</t>
         </is>
       </c>
       <c r="D34" s="25" t="inlineStr">
         <is>
-          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
+          <t>第9期の計画値と実績の乖離を確定させるために必要。</t>
         </is>
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-58,Ⅱ-59</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F34" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-9</t>
+          <t>doc08§8-1</t>
         </is>
       </c>
       <c r="G34" s="23" t="inlineStr">
@@ -8001,22 +8001,22 @@
       </c>
       <c r="C35" s="25" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告（月報・年報）の原データの提供可否</t>
+          <t>通いの場の実数（令和3〜7年度）</t>
         </is>
       </c>
       <c r="D35" s="25" t="inlineStr">
         <is>
-          <t>見える化に収録されていない項目（サービス種類別利用者数の月次推移等）が扱えるようになる。</t>
+          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。</t>
         </is>
       </c>
       <c r="E35" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-10</t>
+          <t>doc02§16,§22</t>
         </is>
       </c>
       <c r="G35" s="23" t="inlineStr">
@@ -8039,22 +8039,22 @@
       </c>
       <c r="C36" s="25" t="inlineStr">
         <is>
-          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
+          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
         </is>
       </c>
       <c r="D36" s="25" t="inlineStr">
         <is>
-          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
+          <t>見える化に該当データがない。第9期は基本目標4-4に位置づけ。</t>
         </is>
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-68,Ⅱ-69</t>
         </is>
       </c>
       <c r="F36" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc08§8-5</t>
         </is>
       </c>
       <c r="G36" s="23" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="C37" s="25" t="inlineStr">
         <is>
-          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
+          <t>高齢者福祉事業（村単独事業）の実績資料</t>
         </is>
       </c>
       <c r="D37" s="25" t="inlineStr">
         <is>
-          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
+          <t>現行計画の評価に必要。</t>
         </is>
       </c>
       <c r="E37" s="23" t="inlineStr">
@@ -8092,7 +8092,7 @@
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc01-11</t>
         </is>
       </c>
       <c r="G37" s="23" t="inlineStr">
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C38" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
+          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
         </is>
       </c>
       <c r="D38" s="25" t="inlineStr">
         <is>
-          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
+          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
         </is>
       </c>
       <c r="E38" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-58,Ⅱ-59</t>
         </is>
       </c>
       <c r="F38" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc19 追-9</t>
         </is>
       </c>
       <c r="G38" s="23" t="inlineStr">
@@ -8148,27 +8148,27 @@
       </c>
       <c r="B39" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C39" s="25" t="inlineStr">
         <is>
-          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
+          <t>介護保険事業状況報告（月報・年報）の原データの提供可否</t>
         </is>
       </c>
       <c r="D39" s="25" t="inlineStr">
         <is>
-          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
+          <t>見える化に収録されていない項目（サービス種類別利用者数の月次推移等）が扱えるようになる。</t>
         </is>
       </c>
       <c r="E39" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
-          <t>doc19 指-5</t>
+          <t>doc19 追-10</t>
         </is>
       </c>
       <c r="G39" s="23" t="inlineStr">
@@ -8186,27 +8186,27 @@
       </c>
       <c r="B40" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C40" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
+          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
         </is>
       </c>
       <c r="D40" s="25" t="inlineStr">
         <is>
-          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
+          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
         </is>
       </c>
       <c r="E40" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F40" s="23" t="inlineStr">
         <is>
-          <t>doc09§4,§10</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G40" s="23" t="inlineStr">
@@ -8224,27 +8224,27 @@
       </c>
       <c r="B41" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C41" s="25" t="inlineStr">
         <is>
-          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
+          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
         </is>
       </c>
       <c r="D41" s="25" t="inlineStr">
         <is>
-          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
+          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
         </is>
       </c>
       <c r="E41" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t>doc09§8,§10</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G41" s="23" t="inlineStr">
@@ -8262,27 +8262,27 @@
       </c>
       <c r="B42" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C42" s="25" t="inlineStr">
         <is>
-          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
+          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
         </is>
       </c>
       <c r="D42" s="25" t="inlineStr">
         <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
+          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
         </is>
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F42" s="23" t="inlineStr">
         <is>
-          <t>doc02§17,doc07,doc18 4-1</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G42" s="23" t="inlineStr">
@@ -8300,27 +8300,27 @@
       </c>
       <c r="B43" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C43" s="25" t="inlineStr">
         <is>
-          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
+          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
         </is>
       </c>
       <c r="D43" s="25" t="inlineStr">
         <is>
-          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
+          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
         </is>
       </c>
       <c r="E43" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-75</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F43" s="23" t="inlineStr">
         <is>
-          <t>doc17 C-1,doc02§20-2</t>
+          <t>doc20§6-2 K-65</t>
         </is>
       </c>
       <c r="G43" s="23" t="inlineStr">
@@ -8338,27 +8338,27 @@
       </c>
       <c r="B44" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C44" s="25" t="inlineStr">
         <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
         </is>
       </c>
       <c r="D44" s="25" t="inlineStr">
         <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
         </is>
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F44" s="23" t="inlineStr">
         <is>
-          <t>doc13§6</t>
+          <t>doc21§5 K-68</t>
         </is>
       </c>
       <c r="G44" s="23" t="inlineStr">
@@ -8376,27 +8376,27 @@
       </c>
       <c r="B45" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C45" s="25" t="inlineStr">
         <is>
-          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
         </is>
       </c>
       <c r="D45" s="25" t="inlineStr">
         <is>
-          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
+          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
         </is>
       </c>
       <c r="E45" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-14</t>
+          <t>doc21§5 K-71</t>
         </is>
       </c>
       <c r="G45" s="23" t="inlineStr">
@@ -8414,27 +8414,27 @@
       </c>
       <c r="B46" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C46" s="25" t="inlineStr">
         <is>
-          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+          <t>シルバー人材センターの会員数・受注実績</t>
         </is>
       </c>
       <c r="D46" s="25" t="inlineStr">
         <is>
-          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
         </is>
       </c>
       <c r="E46" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F46" s="23" t="inlineStr">
         <is>
-          <t>doc19 §3</t>
+          <t>doc21§5 K-72</t>
         </is>
       </c>
       <c r="G46" s="23" t="inlineStr">
@@ -8452,27 +8452,27 @@
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C47" s="25" t="inlineStr">
         <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
         </is>
       </c>
       <c r="D47" s="25" t="inlineStr">
         <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
         </is>
       </c>
       <c r="E47" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅴ-95</t>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t>doc07§4</t>
+          <t>doc20§6-2 K-67</t>
         </is>
       </c>
       <c r="G47" s="23" t="inlineStr">
@@ -8490,27 +8490,27 @@
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C48" s="25" t="inlineStr">
         <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
         </is>
       </c>
       <c r="D48" s="25" t="inlineStr">
         <is>
-          <t>評価指標の読み方に影響。</t>
+          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
         </is>
       </c>
       <c r="E48" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F48" s="23" t="inlineStr">
         <is>
-          <t>doc07§8-4</t>
+          <t>doc19 指-5</t>
         </is>
       </c>
       <c r="G48" s="23" t="inlineStr">
@@ -8528,27 +8528,27 @@
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C49" s="25" t="inlineStr">
         <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
         </is>
       </c>
       <c r="D49" s="25" t="inlineStr">
         <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
         </is>
       </c>
       <c r="E49" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
-          <t>doc08§4,§8-2</t>
+          <t>doc09§4,§10</t>
         </is>
       </c>
       <c r="G49" s="23" t="inlineStr">
@@ -8566,27 +8566,27 @@
       </c>
       <c r="B50" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C50" s="25" t="inlineStr">
         <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
         </is>
       </c>
       <c r="D50" s="25" t="inlineStr">
         <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
         </is>
       </c>
       <c r="E50" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F50" s="23" t="inlineStr">
         <is>
-          <t>doc02§20-1</t>
+          <t>doc09§8,§10</t>
         </is>
       </c>
       <c r="G50" s="23" t="inlineStr">
@@ -8604,27 +8604,27 @@
       </c>
       <c r="B51" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C51" s="25" t="inlineStr">
         <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
         </is>
       </c>
       <c r="D51" s="25" t="inlineStr">
         <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
         </is>
       </c>
       <c r="E51" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t>doc15,doc18</t>
+          <t>doc02§17,doc07,doc18 4-1</t>
         </is>
       </c>
       <c r="G51" s="23" t="inlineStr">
@@ -8642,27 +8642,27 @@
       </c>
       <c r="B52" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C52" s="25" t="inlineStr">
         <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
         </is>
       </c>
       <c r="D52" s="25" t="inlineStr">
         <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
         </is>
       </c>
       <c r="E52" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-56,Ⅱ-75</t>
         </is>
       </c>
       <c r="F52" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc18 3-1</t>
+          <t>doc17 C-1,doc02§20-2</t>
         </is>
       </c>
       <c r="G52" s="23" t="inlineStr">
@@ -8680,27 +8680,27 @@
       </c>
       <c r="B53" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C53" s="25" t="inlineStr">
         <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
         </is>
       </c>
       <c r="D53" s="25" t="inlineStr">
         <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
         </is>
       </c>
       <c r="E53" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-60,Ⅱ-65</t>
         </is>
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
+          <t>doc13§6</t>
         </is>
       </c>
       <c r="G53" s="23" t="inlineStr">
@@ -8718,27 +8718,27 @@
       </c>
       <c r="B54" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C54" s="25" t="inlineStr">
         <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
         </is>
       </c>
       <c r="D54" s="25" t="inlineStr">
         <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
         </is>
       </c>
       <c r="E54" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F54" s="23" t="inlineStr">
         <is>
-          <t>doc17 B-3,doc18 4-3</t>
+          <t>doc19 追-14</t>
         </is>
       </c>
       <c r="G54" s="23" t="inlineStr">
@@ -8756,27 +8756,27 @@
       </c>
       <c r="B55" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C55" s="25" t="inlineStr">
         <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
         </is>
       </c>
       <c r="D55" s="25" t="inlineStr">
         <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
         </is>
       </c>
       <c r="E55" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 2-9</t>
+          <t>doc19 §3</t>
         </is>
       </c>
       <c r="G55" s="23" t="inlineStr">
@@ -8794,27 +8794,27 @@
       </c>
       <c r="B56" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C56" s="25" t="inlineStr">
         <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
         </is>
       </c>
       <c r="D56" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
         </is>
       </c>
       <c r="E56" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F56" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 5-7</t>
+          <t>doc21§5 K-73</t>
         </is>
       </c>
       <c r="G56" s="23" t="inlineStr">
@@ -8832,27 +8832,27 @@
       </c>
       <c r="B57" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C57" s="25" t="inlineStr">
         <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
         </is>
       </c>
       <c r="D57" s="25" t="inlineStr">
         <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
         </is>
       </c>
       <c r="E57" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-4</t>
+          <t>doc07§4</t>
         </is>
       </c>
       <c r="G57" s="23" t="inlineStr">
@@ -8870,27 +8870,27 @@
       </c>
       <c r="B58" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C58" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
         </is>
       </c>
       <c r="D58" s="25" t="inlineStr">
         <is>
-          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+          <t>評価指標の読み方に影響。</t>
         </is>
       </c>
       <c r="E58" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-73,Ⅱ-75</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F58" s="23" t="inlineStr">
         <is>
-          <t>doc01-5,doc18 1-2</t>
+          <t>doc07§8-4</t>
         </is>
       </c>
       <c r="G58" s="23" t="inlineStr">
@@ -8908,27 +8908,27 @@
       </c>
       <c r="B59" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C59" s="25" t="inlineStr">
         <is>
-          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
         </is>
       </c>
       <c r="D59" s="25" t="inlineStr">
         <is>
-          <t>施策の書きぶりに影響。</t>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
         </is>
       </c>
       <c r="E59" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-72</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
-          <t>doc01-12</t>
+          <t>doc08§4,§8-2</t>
         </is>
       </c>
       <c r="G59" s="23" t="inlineStr">
@@ -8946,27 +8946,27 @@
       </c>
       <c r="B60" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C60" s="25" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
         </is>
       </c>
       <c r="D60" s="25" t="inlineStr">
         <is>
-          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
         </is>
       </c>
       <c r="E60" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F60" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-13</t>
+          <t>doc02§20-1</t>
         </is>
       </c>
       <c r="G60" s="23" t="inlineStr">
@@ -8984,27 +8984,27 @@
       </c>
       <c r="B61" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C61" s="25" t="inlineStr">
         <is>
-          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
         </is>
       </c>
       <c r="D61" s="25" t="inlineStr">
         <is>
-          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
         </is>
       </c>
       <c r="E61" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-31</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-6</t>
+          <t>doc15,doc18</t>
         </is>
       </c>
       <c r="G61" s="23" t="inlineStr">
@@ -9022,245 +9022,739 @@
       </c>
       <c r="B62" s="24" t="inlineStr">
         <is>
+          <t>素案</t>
+        </is>
+      </c>
+      <c r="C62" s="25" t="inlineStr">
+        <is>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+        </is>
+      </c>
+      <c r="D62" s="25" t="inlineStr">
+        <is>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+        </is>
+      </c>
+      <c r="E62" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-71,Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F62" s="23" t="inlineStr">
+        <is>
+          <t>doc14§5,doc18 3-1</t>
+        </is>
+      </c>
+      <c r="G62" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H62" s="25" t="inlineStr"/>
+    </row>
+    <row r="63" ht="34" customHeight="1">
+      <c r="A63" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B63" s="24" t="inlineStr">
+        <is>
+          <t>素案</t>
+        </is>
+      </c>
+      <c r="C63" s="25" t="inlineStr">
+        <is>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+        </is>
+      </c>
+      <c r="D63" s="25" t="inlineStr">
+        <is>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+        </is>
+      </c>
+      <c r="E63" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-71,Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F63" s="23" t="inlineStr">
+        <is>
+          <t>doc14§5,doc15,doc18 4-5</t>
+        </is>
+      </c>
+      <c r="G63" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H63" s="25" t="inlineStr"/>
+    </row>
+    <row r="64" ht="34" customHeight="1">
+      <c r="A64" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B64" s="24" t="inlineStr">
+        <is>
+          <t>素案</t>
+        </is>
+      </c>
+      <c r="C64" s="25" t="inlineStr">
+        <is>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+        </is>
+      </c>
+      <c r="D64" s="25" t="inlineStr">
+        <is>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+        </is>
+      </c>
+      <c r="E64" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F64" s="23" t="inlineStr">
+        <is>
+          <t>doc17 B-3,doc18 4-3</t>
+        </is>
+      </c>
+      <c r="G64" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H64" s="25" t="inlineStr"/>
+    </row>
+    <row r="65" ht="34" customHeight="1">
+      <c r="A65" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B65" s="24" t="inlineStr">
+        <is>
+          <t>素案</t>
+        </is>
+      </c>
+      <c r="C65" s="25" t="inlineStr">
+        <is>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+        </is>
+      </c>
+      <c r="D65" s="25" t="inlineStr">
+        <is>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+        </is>
+      </c>
+      <c r="E65" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F65" s="23" t="inlineStr">
+        <is>
+          <t>doc17 A-1,doc18 2-9</t>
+        </is>
+      </c>
+      <c r="G65" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H65" s="25" t="inlineStr"/>
+    </row>
+    <row r="66" ht="34" customHeight="1">
+      <c r="A66" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B66" s="24" t="inlineStr">
+        <is>
+          <t>素案</t>
+        </is>
+      </c>
+      <c r="C66" s="25" t="inlineStr">
+        <is>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+        </is>
+      </c>
+      <c r="D66" s="25" t="inlineStr">
+        <is>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+        </is>
+      </c>
+      <c r="E66" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-64,Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F66" s="23" t="inlineStr">
+        <is>
+          <t>doc17 A-1,doc18 5-7</t>
+        </is>
+      </c>
+      <c r="G66" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H66" s="25" t="inlineStr"/>
+    </row>
+    <row r="67" ht="34" customHeight="1">
+      <c r="A67" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B67" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C67" s="25" t="inlineStr">
+        <is>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
+        </is>
+      </c>
+      <c r="D67" s="25" t="inlineStr">
+        <is>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+        </is>
+      </c>
+      <c r="E67" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F67" s="23" t="inlineStr">
+        <is>
+          <t>doc08§8-4</t>
+        </is>
+      </c>
+      <c r="G67" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H67" s="25" t="inlineStr"/>
+    </row>
+    <row r="68" ht="34" customHeight="1">
+      <c r="A68" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B68" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C68" s="25" t="inlineStr">
+        <is>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+        </is>
+      </c>
+      <c r="D68" s="25" t="inlineStr">
+        <is>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+        </is>
+      </c>
+      <c r="E68" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-73,Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F68" s="23" t="inlineStr">
+        <is>
+          <t>doc01-5,doc18 1-2</t>
+        </is>
+      </c>
+      <c r="G68" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H68" s="25" t="inlineStr"/>
+    </row>
+    <row r="69" ht="34" customHeight="1">
+      <c r="A69" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B69" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C69" s="25" t="inlineStr">
+        <is>
+          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+        </is>
+      </c>
+      <c r="D69" s="25" t="inlineStr">
+        <is>
+          <t>施策の書きぶりに影響。</t>
+        </is>
+      </c>
+      <c r="E69" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-71,Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F69" s="23" t="inlineStr">
+        <is>
+          <t>doc01-12</t>
+        </is>
+      </c>
+      <c r="G69" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H69" s="25" t="inlineStr"/>
+    </row>
+    <row r="70" ht="34" customHeight="1">
+      <c r="A70" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B70" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C70" s="25" t="inlineStr">
+        <is>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+        </is>
+      </c>
+      <c r="D70" s="25" t="inlineStr">
+        <is>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+        </is>
+      </c>
+      <c r="E70" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F70" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-13</t>
+        </is>
+      </c>
+      <c r="G70" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H70" s="25" t="inlineStr"/>
+    </row>
+    <row r="71" ht="34" customHeight="1">
+      <c r="A71" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B71" s="24" t="inlineStr">
+        <is>
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C62" s="25" t="inlineStr">
+      <c r="C71" s="25" t="inlineStr">
+        <is>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+        </is>
+      </c>
+      <c r="D71" s="25" t="inlineStr">
+        <is>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+        </is>
+      </c>
+      <c r="E71" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-31</t>
+        </is>
+      </c>
+      <c r="F71" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-6</t>
+        </is>
+      </c>
+      <c r="G71" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H71" s="25" t="inlineStr"/>
+    </row>
+    <row r="72" ht="34" customHeight="1">
+      <c r="A72" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B72" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C72" s="25" t="inlineStr">
         <is>
           <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
         </is>
       </c>
-      <c r="D62" s="25" t="inlineStr">
+      <c r="D72" s="25" t="inlineStr">
         <is>
           <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
         </is>
       </c>
-      <c r="E62" s="23" t="inlineStr">
+      <c r="E72" s="23" t="inlineStr">
         <is>
           <t>Ⅰ-40,Ⅰ-42</t>
         </is>
       </c>
-      <c r="F62" s="23" t="inlineStr">
+      <c r="F72" s="23" t="inlineStr">
         <is>
           <t>doc19 追-7</t>
         </is>
       </c>
-      <c r="G62" s="23" t="inlineStr">
+      <c r="G72" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H62" s="25" t="inlineStr"/>
-    </row>
-    <row r="63" ht="34" customHeight="1">
-      <c r="A63" s="35" t="inlineStr">
+      <c r="H72" s="25" t="inlineStr"/>
+    </row>
+    <row r="73" ht="34" customHeight="1">
+      <c r="A73" s="35" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B63" s="24" t="inlineStr">
+      <c r="B73" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C63" s="25" t="inlineStr">
+      <c r="C73" s="25" t="inlineStr">
         <is>
           <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
         </is>
       </c>
-      <c r="D63" s="25" t="inlineStr">
+      <c r="D73" s="25" t="inlineStr">
         <is>
           <t>第9期はA4・本文104頁・全6章＋資料編。</t>
         </is>
       </c>
-      <c r="E63" s="23" t="inlineStr">
+      <c r="E73" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-89</t>
         </is>
       </c>
-      <c r="F63" s="23" t="inlineStr">
+      <c r="F73" s="23" t="inlineStr">
         <is>
           <t>doc01-10</t>
         </is>
       </c>
-      <c r="G63" s="23" t="inlineStr">
+      <c r="G73" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H63" s="25" t="inlineStr"/>
-    </row>
-    <row r="64" ht="34" customHeight="1">
-      <c r="A64" s="35" t="inlineStr">
+      <c r="H73" s="25" t="inlineStr"/>
+    </row>
+    <row r="74" ht="34" customHeight="1">
+      <c r="A74" s="35" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B64" s="24" t="inlineStr">
+      <c r="B74" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C64" s="25" t="inlineStr">
+      <c r="C74" s="25" t="inlineStr">
         <is>
           <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
         </is>
       </c>
-      <c r="D64" s="25" t="inlineStr">
+      <c r="D74" s="25" t="inlineStr">
         <is>
           <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
         </is>
       </c>
-      <c r="E64" s="23" t="inlineStr">
+      <c r="E74" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-92</t>
         </is>
       </c>
-      <c r="F64" s="23" t="inlineStr">
+      <c r="F74" s="23" t="inlineStr">
         <is>
           <t>doc01-10,doc08</t>
         </is>
       </c>
-      <c r="G64" s="23" t="inlineStr">
+      <c r="G74" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H64" s="25" t="inlineStr"/>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="36" t="inlineStr">
+      <c r="H74" s="25" t="inlineStr"/>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="36" t="inlineStr">
         <is>
           <t>■ 解決済み（記録）</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="34" customHeight="1">
-      <c r="A67" s="37" t="inlineStr">
+    <row r="77" ht="34" customHeight="1">
+      <c r="A77" s="37" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="B67" s="38" t="inlineStr">
+      <c r="B77" s="38" t="inlineStr">
         <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="C67" s="39" t="inlineStr">
+      <c r="C77" s="39" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+        </is>
+      </c>
+      <c r="D77" s="39" t="inlineStr">
+        <is>
+          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+        </is>
+      </c>
+      <c r="E77" s="37" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F77" s="37" t="inlineStr">
+        <is>
+          <t>doc20§3,§4</t>
+        </is>
+      </c>
+      <c r="G77" s="37" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H77" s="39" t="inlineStr"/>
+    </row>
+    <row r="78" ht="34" customHeight="1">
+      <c r="A78" s="37" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B78" s="38" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C78" s="39" t="inlineStr">
+        <is>
+          <t>交付要綱の配点表（満点）</t>
+        </is>
+      </c>
+      <c r="D78" s="39" t="inlineStr">
+        <is>
+          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+        </is>
+      </c>
+      <c r="E78" s="37" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F78" s="37" t="inlineStr">
+        <is>
+          <t>doc20§2</t>
+        </is>
+      </c>
+      <c r="G78" s="37" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H78" s="39" t="inlineStr"/>
+    </row>
+    <row r="79" ht="34" customHeight="1">
+      <c r="A79" s="37" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B79" s="38" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C79" s="39" t="inlineStr">
+        <is>
+          <t>令和6年度・令和7年度の交付金評価結果</t>
+        </is>
+      </c>
+      <c r="D79" s="39" t="inlineStr">
+        <is>
+          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+        </is>
+      </c>
+      <c r="E79" s="37" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F79" s="37" t="inlineStr">
+        <is>
+          <t>doc20§3-1</t>
+        </is>
+      </c>
+      <c r="G79" s="37" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H79" s="39" t="inlineStr"/>
+    </row>
+    <row r="80" ht="34" customHeight="1">
+      <c r="A80" s="37" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B80" s="38" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C80" s="39" t="inlineStr">
         <is>
           <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
         </is>
       </c>
-      <c r="D67" s="39" t="inlineStr">
+      <c r="D80" s="39" t="inlineStr">
         <is>
           <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
         </is>
       </c>
-      <c r="E67" s="37" t="inlineStr">
+      <c r="E80" s="37" t="inlineStr">
         <is>
           <t>Ⅱ-56,Ⅱ-58</t>
         </is>
       </c>
-      <c r="F67" s="37" t="inlineStr">
+      <c r="F80" s="37" t="inlineStr">
         <is>
           <t>doc09</t>
         </is>
       </c>
-      <c r="G67" s="37" t="inlineStr">
+      <c r="G80" s="37" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H67" s="39" t="inlineStr"/>
-    </row>
-    <row r="68" ht="34" customHeight="1">
-      <c r="A68" s="37" t="inlineStr">
+      <c r="H80" s="39" t="inlineStr"/>
+    </row>
+    <row r="81" ht="34" customHeight="1">
+      <c r="A81" s="37" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="B68" s="38" t="inlineStr">
+      <c r="B81" s="38" t="inlineStr">
         <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="C68" s="39" t="inlineStr">
+      <c r="C81" s="39" t="inlineStr">
         <is>
           <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
         </is>
       </c>
-      <c r="D68" s="39" t="inlineStr">
+      <c r="D81" s="39" t="inlineStr">
         <is>
           <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
         </is>
       </c>
-      <c r="E68" s="37" t="inlineStr">
+      <c r="E81" s="37" t="inlineStr">
         <is>
           <t>Ⅱ-59</t>
         </is>
       </c>
-      <c r="F68" s="37" t="inlineStr">
+      <c r="F81" s="37" t="inlineStr">
         <is>
           <t>doc02§20-2</t>
         </is>
       </c>
-      <c r="G68" s="37" t="inlineStr">
+      <c r="G81" s="37" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H68" s="39" t="inlineStr"/>
-    </row>
-    <row r="69" ht="34" customHeight="1">
-      <c r="A69" s="37" t="inlineStr">
+      <c r="H81" s="39" t="inlineStr"/>
+    </row>
+    <row r="82" ht="34" customHeight="1">
+      <c r="A82" s="37" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="B69" s="38" t="inlineStr">
+      <c r="B82" s="38" t="inlineStr">
         <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="C69" s="39" t="inlineStr">
+      <c r="C82" s="39" t="inlineStr">
         <is>
           <t>国の指針・様式の更新有無</t>
         </is>
       </c>
-      <c r="D69" s="39" t="inlineStr">
+      <c r="D82" s="39" t="inlineStr">
         <is>
           <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
-      <c r="E69" s="37" t="inlineStr">
+      <c r="E82" s="37" t="inlineStr">
         <is>
           <t>Ⅰ-11</t>
         </is>
       </c>
-      <c r="F69" s="37" t="inlineStr">
+      <c r="F82" s="37" t="inlineStr">
         <is>
           <t>doc04,doc05</t>
         </is>
       </c>
-      <c r="G69" s="37" t="inlineStr">
+      <c r="G82" s="37" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H69" s="39" t="inlineStr"/>
+      <c r="H82" s="39" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H64"/>
+  <autoFilter ref="A4:H74"/>
   <mergeCells count="3">
+    <mergeCell ref="A76:H76"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A66:H66"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9274,7 +9768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10006,103 +10500,189 @@
       </c>
     </row>
     <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="32" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>国資料</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>令和8年度 交付金評価指標（市町村分）配点表</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>全17頁。推進400点・支援400点、目標Ⅰ〜Ⅳ各100点</t>
+        </is>
+      </c>
+      <c r="D27" s="40" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>docs/…/20_交付金評価結果分析.md</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>国資料</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>令和6年度 該当状況調査票集計表（全国一覧表）</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>全国1,741市町村。村は第398行。合計295点</t>
+        </is>
+      </c>
+      <c r="D28" s="40" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>docs/…/20_交付金評価結果分析.md</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>国資料</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>令和7年度 該当状況調査票集計表（全国集計・市町村）</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>合計339点。全国平均435.0点</t>
+        </is>
+      </c>
+      <c r="D29" s="40" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>docs/…/20_交付金評価結果分析.md</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>国資料</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>令和8年度 該当状況調査票集計表（全国集計・市町村）</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>合計447点。全国平均455.1点／全国1,005位／県内34位</t>
+        </is>
+      </c>
+      <c r="D30" s="40" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>docs/…/20_交付金評価結果分析.md</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>関連計画</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>第四次北塩原村生涯学習推進計画</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>全112頁。2018〜2027年度。7z分割書庫4分割で受領</t>
+        </is>
+      </c>
+      <c r="D31" s="40" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>docs/…/21_関連計画_第四次生涯学習推進計画.md</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="32" t="inlineStr">
         <is>
           <t>村データ</t>
         </is>
       </c>
-      <c r="B27" s="31" t="inlineStr">
-        <is>
-          <t>★W系の福島県平均・全国平均／交付要綱の配点表</t>
-        </is>
-      </c>
-      <c r="C27" s="31" t="inlineStr">
-        <is>
-          <t>目標値設定に必要</t>
-        </is>
-      </c>
-      <c r="D27" s="32" t="inlineStr">
+      <c r="B32" s="31" t="inlineStr">
+        <is>
+          <t>★要介護認定データ（調査票との関連付け用）</t>
+        </is>
+      </c>
+      <c r="C32" s="31" t="inlineStr">
+        <is>
+          <t>仕様書4Ⅰ(5)。調査回収後に必要</t>
+        </is>
+      </c>
+      <c r="D32" s="32" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E27" s="31" t="inlineStr">
+      <c r="E32" s="31" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F27" s="32" t="inlineStr">
+      <c r="F32" s="32" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="32" t="inlineStr">
-        <is>
-          <t>村データ</t>
-        </is>
-      </c>
-      <c r="B28" s="31" t="inlineStr">
-        <is>
-          <t>★令和6・7年度の交付金評価結果</t>
-        </is>
-      </c>
-      <c r="C28" s="31" t="inlineStr">
-        <is>
-          <t>第10期の基準値を最新年度に置くため</t>
-        </is>
-      </c>
-      <c r="D28" s="32" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E28" s="31" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="F28" s="32" t="inlineStr">
-        <is>
-          <t>未受領</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="32" t="inlineStr">
-        <is>
-          <t>村データ</t>
-        </is>
-      </c>
-      <c r="B29" s="31" t="inlineStr">
-        <is>
-          <t>★要介護認定データ（調査票との関連付け用）</t>
-        </is>
-      </c>
-      <c r="C29" s="31" t="inlineStr">
-        <is>
-          <t>仕様書4Ⅰ(5)。調査回収後に必要</t>
-        </is>
-      </c>
-      <c r="D29" s="32" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E29" s="31" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="F29" s="32" t="inlineStr">
-        <is>
-          <t>未受領</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:F29"/>
+  <autoFilter ref="A4:F32"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$101</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6779,7 +6779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7469,12 +7469,12 @@
       </c>
       <c r="C21" s="31" t="inlineStr">
         <is>
-          <t>給付費適正化事業（ケアプラン点検・住宅改修点検・医療情報突合・縦覧点検・給付費通知）の実施状況</t>
+          <t>★給付費適正化「主要3事業の全て実施」が令和7年度6点→令和8年度0点に低下した理由</t>
         </is>
       </c>
       <c r="D21" s="31" t="inlineStr">
         <is>
-          <t>★令和8年度交付金評価で推進目標Ⅱ「給付費適正化事業の取組状況」ア・ウ・エ・オが全て0点（アの全国該当率96.9%）。配点計30点の取りこぼしで最優先。</t>
+          <t>★全国該当率96.9%の指標。縦覧点検は4帳票満点のため、①要介護認定の適正化 か ②ケアプラン等の点検 のいずれかが実施されなくなった可能性。取組の後退か調査票の記載漏れかで対応が変わる。</t>
         </is>
       </c>
       <c r="E21" s="32" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="F21" s="32" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-61</t>
+          <t>doc20§8-2 K-61</t>
         </is>
       </c>
       <c r="G21" s="32" t="inlineStr">
@@ -7507,22 +7507,22 @@
       </c>
       <c r="C22" s="31" t="inlineStr">
         <is>
-          <t>認知症サポーター養成数・認知症地域支援推進員の配置と活動内容・チームオレンジの整備予定</t>
+          <t>★福祉用具購入費・住宅改修費へのリハビリ専門職の関与（配点8点）が令和7年度8点→令和8年度0点に低下した理由</t>
         </is>
       </c>
       <c r="D22" s="31" t="inlineStr">
         <is>
-          <t>★支援交付金目標Ⅱ（認知症総合支援）は32/100点で全国平均51.1点を19点下回る唯一の目標。3か年で唯一低下局面があった。</t>
+          <t>★アと合わせ14点が1年で失われている。仕組みが失われたのか調査票の記載によるものかを確認。</t>
         </is>
       </c>
       <c r="E22" s="32" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F22" s="32" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-62</t>
+          <t>doc20§8-2 K-61b</t>
         </is>
       </c>
       <c r="G22" s="32" t="inlineStr">
@@ -7545,12 +7545,12 @@
       </c>
       <c r="C23" s="31" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入の取組（健診での聴力チェック等）の有無</t>
+          <t>認知症サポーター養成数・認知症地域支援推進員の配置と活動内容・チームオレンジの整備予定</t>
         </is>
       </c>
       <c r="D23" s="31" t="inlineStr">
         <is>
-          <t>令和8年度評価で配点10点が0点（全国該当率48.8〜68.9%）。保健事業との連携で取得可能。</t>
+          <t>★支援交付金目標Ⅱ（認知症総合支援）は32/100点で全国平均51.1点を19点下回る唯一の目標。3か年で唯一低下局面があった。</t>
         </is>
       </c>
       <c r="E23" s="32" t="inlineStr">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="F23" s="32" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-63</t>
+          <t>doc20§6-2 K-62</t>
         </is>
       </c>
       <c r="G23" s="32" t="inlineStr">
@@ -7583,22 +7583,22 @@
       </c>
       <c r="C24" s="31" t="inlineStr">
         <is>
-          <t>在宅医療・介護連携推進事業の実施体制（村単独か会津圏域か）と課題・対応策の検討の場</t>
+          <t>難聴高齢者の早期発見・早期介入の取組（健診での聴力チェック等）の有無</t>
         </is>
       </c>
       <c r="D24" s="31" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲの「課題・対応策の検討」ア・エが0点（配点計10点、全国該当率57〜72%）。</t>
+          <t>令和8年度評価で配点10点が0点（全国該当率48.8〜68.9%）。保健事業との連携で取得可能。</t>
         </is>
       </c>
       <c r="E24" s="32" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F24" s="32" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-64</t>
+          <t>doc20§6-2 K-63</t>
         </is>
       </c>
       <c r="G24" s="32" t="inlineStr">
@@ -7616,27 +7616,27 @@
       </c>
       <c r="B25" s="30" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C25" s="31" t="inlineStr">
         <is>
-          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
+          <t>在宅医療・介護連携推進事業の実施体制（村単独か会津圏域か）と課題・対応策の検討の場</t>
         </is>
       </c>
       <c r="D25" s="31" t="inlineStr">
         <is>
-          <t>連絡体制表の確定。第9期概要版の発行は住民課。</t>
+          <t>支援交付金目標Ⅲの「課題・対応策の検討」ア・エが0点（配点計10点、全国該当率57〜72%）。</t>
         </is>
       </c>
       <c r="E25" s="32" t="inlineStr">
         <is>
-          <t>０-04</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F25" s="32" t="inlineStr">
         <is>
-          <t>doc01-1</t>
+          <t>doc20§6-2 K-64</t>
         </is>
       </c>
       <c r="G25" s="32" t="inlineStr">
@@ -7659,22 +7659,22 @@
       </c>
       <c r="C26" s="31" t="inlineStr">
         <is>
-          <t>契約締結日・契約書の取り交わし状況</t>
+          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
         </is>
       </c>
       <c r="D26" s="31" t="inlineStr">
         <is>
-          <t>業務開始日の確定。</t>
+          <t>連絡体制表の確定。第9期概要版の発行は住民課。</t>
         </is>
       </c>
       <c r="E26" s="32" t="inlineStr">
         <is>
-          <t>０-02</t>
+          <t>０-04</t>
         </is>
       </c>
       <c r="F26" s="32" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>doc01-1</t>
         </is>
       </c>
       <c r="G26" s="32" t="inlineStr">
@@ -7697,22 +7697,22 @@
       </c>
       <c r="C27" s="31" t="inlineStr">
         <is>
-          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
+          <t>契約締結日・契約書の取り交わし状況</t>
         </is>
       </c>
       <c r="D27" s="31" t="inlineStr">
         <is>
-          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
+          <t>業務開始日の確定。</t>
         </is>
       </c>
       <c r="E27" s="32" t="inlineStr">
         <is>
-          <t>０-06</t>
+          <t>０-02</t>
         </is>
       </c>
       <c r="F27" s="32" t="inlineStr">
         <is>
-          <t>doc19 追-12</t>
+          <t>―</t>
         </is>
       </c>
       <c r="G27" s="32" t="inlineStr">
@@ -7730,27 +7730,27 @@
       </c>
       <c r="B28" s="30" t="inlineStr">
         <is>
-          <t>委員会</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C28" s="31" t="inlineStr">
         <is>
-          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
+          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
         </is>
       </c>
       <c r="D28" s="31" t="inlineStr">
         <is>
-          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
+          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
         </is>
       </c>
       <c r="E28" s="32" t="inlineStr">
         <is>
-          <t>Ⅱ-80,Ⅱ-81</t>
+          <t>０-06</t>
         </is>
       </c>
       <c r="F28" s="32" t="inlineStr">
         <is>
-          <t>doc01-6,doc19 追-15</t>
+          <t>doc19 追-12</t>
         </is>
       </c>
       <c r="G28" s="32" t="inlineStr">
@@ -7768,27 +7768,27 @@
       </c>
       <c r="B29" s="30" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>委員会</t>
         </is>
       </c>
       <c r="C29" s="31" t="inlineStr">
         <is>
-          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
+          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
         </is>
       </c>
       <c r="D29" s="31" t="inlineStr">
         <is>
-          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
+          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
         </is>
       </c>
       <c r="E29" s="32" t="inlineStr">
         <is>
-          <t>Ⅱ-76,Ⅱ-77</t>
+          <t>Ⅱ-80,Ⅱ-81</t>
         </is>
       </c>
       <c r="F29" s="32" t="inlineStr">
         <is>
-          <t>doc01-7,doc19 指-3</t>
+          <t>doc01-6,doc19 追-15</t>
         </is>
       </c>
       <c r="G29" s="32" t="inlineStr">
@@ -7806,27 +7806,27 @@
       </c>
       <c r="B30" s="30" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C30" s="31" t="inlineStr">
         <is>
-          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
+          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
         </is>
       </c>
       <c r="D30" s="31" t="inlineStr">
         <is>
-          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
+          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
         </is>
       </c>
       <c r="E30" s="32" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-76,Ⅱ-77</t>
         </is>
       </c>
       <c r="F30" s="32" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-66</t>
+          <t>doc01-7,doc19 指-3</t>
         </is>
       </c>
       <c r="G30" s="32" t="inlineStr">
@@ -7844,27 +7844,27 @@
       </c>
       <c r="B31" s="30" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C31" s="31" t="inlineStr">
         <is>
-          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
+          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
         </is>
       </c>
       <c r="D31" s="31" t="inlineStr">
         <is>
-          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
+          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
         </is>
       </c>
       <c r="E31" s="32" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F31" s="32" t="inlineStr">
         <is>
-          <t>doc21§5 K-69</t>
+          <t>doc20§6-2 K-66</t>
         </is>
       </c>
       <c r="G31" s="32" t="inlineStr">
@@ -7887,68 +7887,68 @@
       </c>
       <c r="C32" s="31" t="inlineStr">
         <is>
+          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
+        </is>
+      </c>
+      <c r="D32" s="31" t="inlineStr">
+        <is>
+          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
+        </is>
+      </c>
+      <c r="E32" s="32" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F32" s="32" t="inlineStr">
+        <is>
+          <t>doc21§5 K-69</t>
+        </is>
+      </c>
+      <c r="G32" s="32" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H32" s="31" t="inlineStr"/>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C33" s="31" t="inlineStr">
+        <is>
           <t>第六次総合振興計画（2027年度〜）の策定状況</t>
         </is>
       </c>
-      <c r="D32" s="31" t="inlineStr">
+      <c r="D33" s="31" t="inlineStr">
         <is>
           <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
         </is>
       </c>
-      <c r="E32" s="32" t="inlineStr">
+      <c r="E33" s="32" t="inlineStr">
         <is>
           <t>Ⅱ-72</t>
         </is>
       </c>
-      <c r="F32" s="32" t="inlineStr">
+      <c r="F33" s="32" t="inlineStr">
         <is>
           <t>doc21§5 K-70</t>
         </is>
       </c>
-      <c r="G32" s="32" t="inlineStr">
+      <c r="G33" s="32" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H32" s="31" t="inlineStr"/>
-    </row>
-    <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B33" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C33" s="25" t="inlineStr">
-        <is>
-          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
-        </is>
-      </c>
-      <c r="D33" s="25" t="inlineStr">
-        <is>
-          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
-        </is>
-      </c>
-      <c r="E33" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F33" s="23" t="inlineStr">
-        <is>
-          <t>doc02§22,doc08§8</t>
-        </is>
-      </c>
-      <c r="G33" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H33" s="25" t="inlineStr"/>
+      <c r="H33" s="31" t="inlineStr"/>
     </row>
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="34" t="inlineStr">
@@ -7963,22 +7963,22 @@
       </c>
       <c r="C34" s="25" t="inlineStr">
         <is>
-          <t>令和6年度決算および令和7年度の給付費見込</t>
+          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
         </is>
       </c>
       <c r="D34" s="25" t="inlineStr">
         <is>
-          <t>第9期の計画値と実績の乖離を確定させるために必要。</t>
+          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
         </is>
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F34" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-1</t>
+          <t>doc02§22,doc08§8</t>
         </is>
       </c>
       <c r="G34" s="23" t="inlineStr">
@@ -8001,22 +8001,22 @@
       </c>
       <c r="C35" s="25" t="inlineStr">
         <is>
-          <t>通いの場の実数（令和3〜7年度）</t>
+          <t>令和6年度決算および令和7年度の給付費見込</t>
         </is>
       </c>
       <c r="D35" s="25" t="inlineStr">
         <is>
-          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。</t>
+          <t>第9期の計画値と実績の乖離を確定させるために必要。</t>
         </is>
       </c>
       <c r="E35" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t>doc02§16,§22</t>
+          <t>doc08§8-1</t>
         </is>
       </c>
       <c r="G35" s="23" t="inlineStr">
@@ -8039,22 +8039,22 @@
       </c>
       <c r="C36" s="25" t="inlineStr">
         <is>
-          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
+          <t>通いの場の実数（令和3〜7年度）</t>
         </is>
       </c>
       <c r="D36" s="25" t="inlineStr">
         <is>
-          <t>見える化に該当データがない。第9期は基本目標4-4に位置づけ。</t>
+          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。</t>
         </is>
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-69</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F36" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-5</t>
+          <t>doc02§16,§22</t>
         </is>
       </c>
       <c r="G36" s="23" t="inlineStr">
@@ -8077,22 +8077,22 @@
       </c>
       <c r="C37" s="25" t="inlineStr">
         <is>
-          <t>高齢者福祉事業（村単独事業）の実績資料</t>
+          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
         </is>
       </c>
       <c r="D37" s="25" t="inlineStr">
         <is>
-          <t>現行計画の評価に必要。</t>
+          <t>見える化に該当データがない。第9期は基本目標4-4に位置づけ。</t>
         </is>
       </c>
       <c r="E37" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-68,Ⅱ-69</t>
         </is>
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t>doc01-11</t>
+          <t>doc08§8-5</t>
         </is>
       </c>
       <c r="G37" s="23" t="inlineStr">
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C38" s="25" t="inlineStr">
         <is>
-          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
+          <t>高齢者福祉事業（村単独事業）の実績資料</t>
         </is>
       </c>
       <c r="D38" s="25" t="inlineStr">
         <is>
-          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
+          <t>現行計画の評価に必要。</t>
         </is>
       </c>
       <c r="E38" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-58,Ⅱ-59</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F38" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-9</t>
+          <t>doc01-11</t>
         </is>
       </c>
       <c r="G38" s="23" t="inlineStr">
@@ -8153,22 +8153,22 @@
       </c>
       <c r="C39" s="25" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告（月報・年報）の原データの提供可否</t>
+          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
         </is>
       </c>
       <c r="D39" s="25" t="inlineStr">
         <is>
-          <t>見える化に収録されていない項目（サービス種類別利用者数の月次推移等）が扱えるようになる。</t>
+          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
         </is>
       </c>
       <c r="E39" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-58,Ⅱ-59</t>
         </is>
       </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-10</t>
+          <t>doc19 追-9</t>
         </is>
       </c>
       <c r="G39" s="23" t="inlineStr">
@@ -8191,22 +8191,22 @@
       </c>
       <c r="C40" s="25" t="inlineStr">
         <is>
-          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
+          <t>介護保険事業状況報告（月報・年報）の原データの提供可否</t>
         </is>
       </c>
       <c r="D40" s="25" t="inlineStr">
         <is>
-          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
+          <t>見える化に収録されていない項目（サービス種類別利用者数の月次推移等）が扱えるようになる。</t>
         </is>
       </c>
       <c r="E40" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F40" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc19 追-10</t>
         </is>
       </c>
       <c r="G40" s="23" t="inlineStr">
@@ -8229,17 +8229,17 @@
       </c>
       <c r="C41" s="25" t="inlineStr">
         <is>
-          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
+          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
         </is>
       </c>
       <c r="D41" s="25" t="inlineStr">
         <is>
-          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
+          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
         </is>
       </c>
       <c r="E41" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F41" s="23" t="inlineStr">
@@ -8267,17 +8267,17 @@
       </c>
       <c r="C42" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
+          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
         </is>
       </c>
       <c r="D42" s="25" t="inlineStr">
         <is>
-          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
+          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
         </is>
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F42" s="23" t="inlineStr">
@@ -8305,12 +8305,12 @@
       </c>
       <c r="C43" s="25" t="inlineStr">
         <is>
-          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
+          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
         </is>
       </c>
       <c r="D43" s="25" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
+          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
         </is>
       </c>
       <c r="E43" s="23" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="F43" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-65</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G43" s="23" t="inlineStr">
@@ -8343,22 +8343,22 @@
       </c>
       <c r="C44" s="25" t="inlineStr">
         <is>
-          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
+          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
         </is>
       </c>
       <c r="D44" s="25" t="inlineStr">
         <is>
-          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
+          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
         </is>
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F44" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-68</t>
+          <t>doc20§6-2 K-65</t>
         </is>
       </c>
       <c r="G44" s="23" t="inlineStr">
@@ -8381,22 +8381,22 @@
       </c>
       <c r="C45" s="25" t="inlineStr">
         <is>
-          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
+          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
         </is>
       </c>
       <c r="D45" s="25" t="inlineStr">
         <is>
-          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
+          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
         </is>
       </c>
       <c r="E45" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-71</t>
+          <t>doc21§5 K-68</t>
         </is>
       </c>
       <c r="G45" s="23" t="inlineStr">
@@ -8419,12 +8419,12 @@
       </c>
       <c r="C46" s="25" t="inlineStr">
         <is>
-          <t>シルバー人材センターの会員数・受注実績</t>
+          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
         </is>
       </c>
       <c r="D46" s="25" t="inlineStr">
         <is>
-          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
+          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
         </is>
       </c>
       <c r="E46" s="23" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="F46" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-72</t>
+          <t>doc21§5 K-71</t>
         </is>
       </c>
       <c r="G46" s="23" t="inlineStr">
@@ -8452,27 +8452,27 @@
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C47" s="25" t="inlineStr">
         <is>
-          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
+          <t>シルバー人材センターの会員数・受注実績</t>
         </is>
       </c>
       <c r="D47" s="25" t="inlineStr">
         <is>
-          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
+          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
         </is>
       </c>
       <c r="E47" s="23" t="inlineStr">
         <is>
-          <t>Ⅴ-95</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-67</t>
+          <t>doc21§5 K-72</t>
         </is>
       </c>
       <c r="G47" s="23" t="inlineStr">
@@ -8490,27 +8490,27 @@
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C48" s="25" t="inlineStr">
         <is>
-          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
+          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
         </is>
       </c>
       <c r="D48" s="25" t="inlineStr">
         <is>
-          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
+          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
         </is>
       </c>
       <c r="E48" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅴ-95</t>
         </is>
       </c>
       <c r="F48" s="23" t="inlineStr">
         <is>
-          <t>doc19 指-5</t>
+          <t>doc20§6-2 K-67</t>
         </is>
       </c>
       <c r="G48" s="23" t="inlineStr">
@@ -8528,27 +8528,27 @@
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C49" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
+          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
         </is>
       </c>
       <c r="D49" s="25" t="inlineStr">
         <is>
-          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
+          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
         </is>
       </c>
       <c r="E49" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
-          <t>doc09§4,§10</t>
+          <t>doc19 指-5</t>
         </is>
       </c>
       <c r="G49" s="23" t="inlineStr">
@@ -8571,22 +8571,22 @@
       </c>
       <c r="C50" s="25" t="inlineStr">
         <is>
-          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
+          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
         </is>
       </c>
       <c r="D50" s="25" t="inlineStr">
         <is>
-          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
+          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
         </is>
       </c>
       <c r="E50" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F50" s="23" t="inlineStr">
         <is>
-          <t>doc09§8,§10</t>
+          <t>doc09§4,§10</t>
         </is>
       </c>
       <c r="G50" s="23" t="inlineStr">
@@ -8609,22 +8609,22 @@
       </c>
       <c r="C51" s="25" t="inlineStr">
         <is>
-          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
+          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
         </is>
       </c>
       <c r="D51" s="25" t="inlineStr">
         <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
+          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
         </is>
       </c>
       <c r="E51" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t>doc02§17,doc07,doc18 4-1</t>
+          <t>doc09§8,§10</t>
         </is>
       </c>
       <c r="G51" s="23" t="inlineStr">
@@ -8647,22 +8647,22 @@
       </c>
       <c r="C52" s="25" t="inlineStr">
         <is>
-          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
+          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
         </is>
       </c>
       <c r="D52" s="25" t="inlineStr">
         <is>
-          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
         </is>
       </c>
       <c r="E52" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-75</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F52" s="23" t="inlineStr">
         <is>
-          <t>doc17 C-1,doc02§20-2</t>
+          <t>doc02§17,doc07,doc18 4-1</t>
         </is>
       </c>
       <c r="G52" s="23" t="inlineStr">
@@ -8685,22 +8685,22 @@
       </c>
       <c r="C53" s="25" t="inlineStr">
         <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
         </is>
       </c>
       <c r="D53" s="25" t="inlineStr">
         <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
         </is>
       </c>
       <c r="E53" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
+          <t>Ⅱ-56,Ⅱ-75</t>
         </is>
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t>doc13§6</t>
+          <t>doc17 C-1,doc02§20-2</t>
         </is>
       </c>
       <c r="G53" s="23" t="inlineStr">
@@ -8723,22 +8723,22 @@
       </c>
       <c r="C54" s="25" t="inlineStr">
         <is>
-          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
         </is>
       </c>
       <c r="D54" s="25" t="inlineStr">
         <is>
-          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
         </is>
       </c>
       <c r="E54" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅱ-60,Ⅱ-65</t>
         </is>
       </c>
       <c r="F54" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-14</t>
+          <t>doc13§6</t>
         </is>
       </c>
       <c r="G54" s="23" t="inlineStr">
@@ -8761,22 +8761,22 @@
       </c>
       <c r="C55" s="25" t="inlineStr">
         <is>
-          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
         </is>
       </c>
       <c r="D55" s="25" t="inlineStr">
         <is>
-          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
         </is>
       </c>
       <c r="E55" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t>doc19 §3</t>
+          <t>doc19 追-14</t>
         </is>
       </c>
       <c r="G55" s="23" t="inlineStr">
@@ -8799,22 +8799,22 @@
       </c>
       <c r="C56" s="25" t="inlineStr">
         <is>
-          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
         </is>
       </c>
       <c r="D56" s="25" t="inlineStr">
         <is>
-          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
         </is>
       </c>
       <c r="E56" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F56" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-73</t>
+          <t>doc19 §3</t>
         </is>
       </c>
       <c r="G56" s="23" t="inlineStr">
@@ -8832,27 +8832,27 @@
       </c>
       <c r="B57" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C57" s="25" t="inlineStr">
         <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
         </is>
       </c>
       <c r="D57" s="25" t="inlineStr">
         <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
         </is>
       </c>
       <c r="E57" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t>doc07§4</t>
+          <t>doc21§5 K-73</t>
         </is>
       </c>
       <c r="G57" s="23" t="inlineStr">
@@ -8875,12 +8875,12 @@
       </c>
       <c r="C58" s="25" t="inlineStr">
         <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
         </is>
       </c>
       <c r="D58" s="25" t="inlineStr">
         <is>
-          <t>評価指標の読み方に影響。</t>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
         </is>
       </c>
       <c r="E58" s="23" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="F58" s="23" t="inlineStr">
         <is>
-          <t>doc07§8-4</t>
+          <t>doc07§4</t>
         </is>
       </c>
       <c r="G58" s="23" t="inlineStr">
@@ -8913,22 +8913,22 @@
       </c>
       <c r="C59" s="25" t="inlineStr">
         <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
         </is>
       </c>
       <c r="D59" s="25" t="inlineStr">
         <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+          <t>評価指標の読み方に影響。</t>
         </is>
       </c>
       <c r="E59" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
-          <t>doc08§4,§8-2</t>
+          <t>doc07§8-4</t>
         </is>
       </c>
       <c r="G59" s="23" t="inlineStr">
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C60" s="25" t="inlineStr">
         <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
         </is>
       </c>
       <c r="D60" s="25" t="inlineStr">
         <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
         </is>
       </c>
       <c r="E60" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F60" s="23" t="inlineStr">
         <is>
-          <t>doc02§20-1</t>
+          <t>doc08§4,§8-2</t>
         </is>
       </c>
       <c r="G60" s="23" t="inlineStr">
@@ -8984,27 +8984,27 @@
       </c>
       <c r="B61" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C61" s="25" t="inlineStr">
         <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
         </is>
       </c>
       <c r="D61" s="25" t="inlineStr">
         <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
         </is>
       </c>
       <c r="E61" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t>doc15,doc18</t>
+          <t>doc02§20-1</t>
         </is>
       </c>
       <c r="G61" s="23" t="inlineStr">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C62" s="25" t="inlineStr">
         <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
         </is>
       </c>
       <c r="D62" s="25" t="inlineStr">
         <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
         </is>
       </c>
       <c r="E62" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F62" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc18 3-1</t>
+          <t>doc15,doc18</t>
         </is>
       </c>
       <c r="G62" s="23" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="C63" s="25" t="inlineStr">
         <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
         </is>
       </c>
       <c r="D63" s="25" t="inlineStr">
         <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
         </is>
       </c>
       <c r="E63" s="23" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
+          <t>doc14§5,doc18 3-1</t>
         </is>
       </c>
       <c r="G63" s="23" t="inlineStr">
@@ -9103,22 +9103,22 @@
       </c>
       <c r="C64" s="25" t="inlineStr">
         <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
         </is>
       </c>
       <c r="D64" s="25" t="inlineStr">
         <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
         </is>
       </c>
       <c r="E64" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F64" s="23" t="inlineStr">
         <is>
-          <t>doc17 B-3,doc18 4-3</t>
+          <t>doc14§5,doc15,doc18 4-5</t>
         </is>
       </c>
       <c r="G64" s="23" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="C65" s="25" t="inlineStr">
         <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
         </is>
       </c>
       <c r="D65" s="25" t="inlineStr">
         <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
         </is>
       </c>
       <c r="E65" s="23" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 2-9</t>
+          <t>doc17 B-3,doc18 4-3</t>
         </is>
       </c>
       <c r="G65" s="23" t="inlineStr">
@@ -9179,22 +9179,22 @@
       </c>
       <c r="C66" s="25" t="inlineStr">
         <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
         </is>
       </c>
       <c r="D66" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
         </is>
       </c>
       <c r="E66" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F66" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 5-7</t>
+          <t>doc17 A-1,doc18 2-9</t>
         </is>
       </c>
       <c r="G66" s="23" t="inlineStr">
@@ -9212,27 +9212,27 @@
       </c>
       <c r="B67" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C67" s="25" t="inlineStr">
         <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
         </is>
       </c>
       <c r="D67" s="25" t="inlineStr">
         <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
         </is>
       </c>
       <c r="E67" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-64,Ⅱ-75</t>
         </is>
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-4</t>
+          <t>doc17 A-1,doc18 5-7</t>
         </is>
       </c>
       <c r="G67" s="23" t="inlineStr">
@@ -9255,22 +9255,22 @@
       </c>
       <c r="C68" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
         </is>
       </c>
       <c r="D68" s="25" t="inlineStr">
         <is>
-          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
         </is>
       </c>
       <c r="E68" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-73,Ⅱ-75</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F68" s="23" t="inlineStr">
         <is>
-          <t>doc01-5,doc18 1-2</t>
+          <t>doc08§8-4</t>
         </is>
       </c>
       <c r="G68" s="23" t="inlineStr">
@@ -9293,22 +9293,22 @@
       </c>
       <c r="C69" s="25" t="inlineStr">
         <is>
-          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
         </is>
       </c>
       <c r="D69" s="25" t="inlineStr">
         <is>
-          <t>施策の書きぶりに影響。</t>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
         </is>
       </c>
       <c r="E69" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-72</t>
+          <t>Ⅱ-73,Ⅱ-75</t>
         </is>
       </c>
       <c r="F69" s="23" t="inlineStr">
         <is>
-          <t>doc01-12</t>
+          <t>doc01-5,doc18 1-2</t>
         </is>
       </c>
       <c r="G69" s="23" t="inlineStr">
@@ -9331,22 +9331,22 @@
       </c>
       <c r="C70" s="25" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
         </is>
       </c>
       <c r="D70" s="25" t="inlineStr">
         <is>
-          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+          <t>施策の書きぶりに影響。</t>
         </is>
       </c>
       <c r="E70" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-71,Ⅱ-72</t>
         </is>
       </c>
       <c r="F70" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-13</t>
+          <t>doc01-12</t>
         </is>
       </c>
       <c r="G70" s="23" t="inlineStr">
@@ -9364,27 +9364,27 @@
       </c>
       <c r="B71" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C71" s="25" t="inlineStr">
         <is>
-          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
         </is>
       </c>
       <c r="D71" s="25" t="inlineStr">
         <is>
-          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
         </is>
       </c>
       <c r="E71" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-31</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-6</t>
+          <t>doc19 追-13</t>
         </is>
       </c>
       <c r="G71" s="23" t="inlineStr">
@@ -9407,60 +9407,60 @@
       </c>
       <c r="C72" s="25" t="inlineStr">
         <is>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+        </is>
+      </c>
+      <c r="D72" s="25" t="inlineStr">
+        <is>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+        </is>
+      </c>
+      <c r="E72" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-31</t>
+        </is>
+      </c>
+      <c r="F72" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-6</t>
+        </is>
+      </c>
+      <c r="G72" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H72" s="25" t="inlineStr"/>
+    </row>
+    <row r="73" ht="34" customHeight="1">
+      <c r="A73" s="34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B73" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C73" s="25" t="inlineStr">
+        <is>
           <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
         </is>
       </c>
-      <c r="D72" s="25" t="inlineStr">
+      <c r="D73" s="25" t="inlineStr">
         <is>
           <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
         </is>
       </c>
-      <c r="E72" s="23" t="inlineStr">
+      <c r="E73" s="23" t="inlineStr">
         <is>
           <t>Ⅰ-40,Ⅰ-42</t>
         </is>
       </c>
-      <c r="F72" s="23" t="inlineStr">
+      <c r="F73" s="23" t="inlineStr">
         <is>
           <t>doc19 追-7</t>
-        </is>
-      </c>
-      <c r="G72" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H72" s="25" t="inlineStr"/>
-    </row>
-    <row r="73" ht="34" customHeight="1">
-      <c r="A73" s="35" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B73" s="24" t="inlineStr">
-        <is>
-          <t>成果品</t>
-        </is>
-      </c>
-      <c r="C73" s="25" t="inlineStr">
-        <is>
-          <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
-        </is>
-      </c>
-      <c r="D73" s="25" t="inlineStr">
-        <is>
-          <t>第9期はA4・本文104頁・全6章＋資料編。</t>
-        </is>
-      </c>
-      <c r="E73" s="23" t="inlineStr">
-        <is>
-          <t>Ⅳ-89</t>
-        </is>
-      </c>
-      <c r="F73" s="23" t="inlineStr">
-        <is>
-          <t>doc01-10</t>
         </is>
       </c>
       <c r="G73" s="23" t="inlineStr">
@@ -9483,75 +9483,75 @@
       </c>
       <c r="C74" s="25" t="inlineStr">
         <is>
+          <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
+        </is>
+      </c>
+      <c r="D74" s="25" t="inlineStr">
+        <is>
+          <t>第9期はA4・本文104頁・全6章＋資料編。</t>
+        </is>
+      </c>
+      <c r="E74" s="23" t="inlineStr">
+        <is>
+          <t>Ⅳ-89</t>
+        </is>
+      </c>
+      <c r="F74" s="23" t="inlineStr">
+        <is>
+          <t>doc01-10</t>
+        </is>
+      </c>
+      <c r="G74" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H74" s="25" t="inlineStr"/>
+    </row>
+    <row r="75" ht="34" customHeight="1">
+      <c r="A75" s="35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B75" s="24" t="inlineStr">
+        <is>
+          <t>成果品</t>
+        </is>
+      </c>
+      <c r="C75" s="25" t="inlineStr">
+        <is>
           <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
         </is>
       </c>
-      <c r="D74" s="25" t="inlineStr">
+      <c r="D75" s="25" t="inlineStr">
         <is>
           <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
         </is>
       </c>
-      <c r="E74" s="23" t="inlineStr">
+      <c r="E75" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-92</t>
         </is>
       </c>
-      <c r="F74" s="23" t="inlineStr">
+      <c r="F75" s="23" t="inlineStr">
         <is>
           <t>doc01-10,doc08</t>
         </is>
       </c>
-      <c r="G74" s="23" t="inlineStr">
+      <c r="G75" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H74" s="25" t="inlineStr"/>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="36" t="inlineStr">
+      <c r="H75" s="25" t="inlineStr"/>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="36" t="inlineStr">
         <is>
           <t>■ 解決済み（記録）</t>
         </is>
       </c>
-    </row>
-    <row r="77" ht="34" customHeight="1">
-      <c r="A77" s="37" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B77" s="38" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C77" s="39" t="inlineStr">
-        <is>
-          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
-        </is>
-      </c>
-      <c r="D77" s="39" t="inlineStr">
-        <is>
-          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
-        </is>
-      </c>
-      <c r="E77" s="37" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F77" s="37" t="inlineStr">
-        <is>
-          <t>doc20§3,§4</t>
-        </is>
-      </c>
-      <c r="G77" s="37" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H77" s="39" t="inlineStr"/>
     </row>
     <row r="78" ht="34" customHeight="1">
       <c r="A78" s="37" t="inlineStr">
@@ -9566,12 +9566,12 @@
       </c>
       <c r="C78" s="39" t="inlineStr">
         <is>
-          <t>交付要綱の配点表（満点）</t>
+          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
         </is>
       </c>
       <c r="D78" s="39" t="inlineStr">
         <is>
-          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
         </is>
       </c>
       <c r="E78" s="37" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="F78" s="37" t="inlineStr">
         <is>
-          <t>doc20§2</t>
+          <t>doc20§3,§4</t>
         </is>
       </c>
       <c r="G78" s="37" t="inlineStr">
@@ -9604,12 +9604,12 @@
       </c>
       <c r="C79" s="39" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の交付金評価結果</t>
+          <t>交付要綱の配点表（満点）</t>
         </is>
       </c>
       <c r="D79" s="39" t="inlineStr">
         <is>
-          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
         </is>
       </c>
       <c r="E79" s="37" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="F79" s="37" t="inlineStr">
         <is>
-          <t>doc20§3-1</t>
+          <t>doc20§2</t>
         </is>
       </c>
       <c r="G79" s="37" t="inlineStr">
@@ -9642,22 +9642,22 @@
       </c>
       <c r="C80" s="39" t="inlineStr">
         <is>
-          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+          <t>令和6年度・令和7年度の交付金評価結果</t>
         </is>
       </c>
       <c r="D80" s="39" t="inlineStr">
         <is>
-          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
         </is>
       </c>
       <c r="E80" s="37" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-58</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F80" s="37" t="inlineStr">
         <is>
-          <t>doc09</t>
+          <t>doc20§3-1</t>
         </is>
       </c>
       <c r="G80" s="37" t="inlineStr">
@@ -9680,22 +9680,22 @@
       </c>
       <c r="C81" s="39" t="inlineStr">
         <is>
-          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
         </is>
       </c>
       <c r="D81" s="39" t="inlineStr">
         <is>
-          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
         </is>
       </c>
       <c r="E81" s="37" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-56,Ⅱ-58</t>
         </is>
       </c>
       <c r="F81" s="37" t="inlineStr">
         <is>
-          <t>doc02§20-2</t>
+          <t>doc09</t>
         </is>
       </c>
       <c r="G81" s="37" t="inlineStr">
@@ -9718,43 +9718,81 @@
       </c>
       <c r="C82" s="39" t="inlineStr">
         <is>
+          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+        </is>
+      </c>
+      <c r="D82" s="39" t="inlineStr">
+        <is>
+          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+        </is>
+      </c>
+      <c r="E82" s="37" t="inlineStr">
+        <is>
+          <t>Ⅱ-59</t>
+        </is>
+      </c>
+      <c r="F82" s="37" t="inlineStr">
+        <is>
+          <t>doc02§20-2</t>
+        </is>
+      </c>
+      <c r="G82" s="37" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H82" s="39" t="inlineStr"/>
+    </row>
+    <row r="83" ht="34" customHeight="1">
+      <c r="A83" s="37" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B83" s="38" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C83" s="39" t="inlineStr">
+        <is>
           <t>国の指針・様式の更新有無</t>
         </is>
       </c>
-      <c r="D82" s="39" t="inlineStr">
+      <c r="D83" s="39" t="inlineStr">
         <is>
           <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
-      <c r="E82" s="37" t="inlineStr">
+      <c r="E83" s="37" t="inlineStr">
         <is>
           <t>Ⅰ-11</t>
         </is>
       </c>
-      <c r="F82" s="37" t="inlineStr">
+      <c r="F83" s="37" t="inlineStr">
         <is>
           <t>doc04,doc05</t>
         </is>
       </c>
-      <c r="G82" s="37" t="inlineStr">
+      <c r="G83" s="37" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H82" s="39" t="inlineStr"/>
+      <c r="H83" s="39" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H74"/>
+  <autoFilter ref="A4:H75"/>
   <mergeCells count="3">
-    <mergeCell ref="A76:H76"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A77:H77"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -190,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -337,6 +337,18 @@
     </xf>
     <xf numFmtId="1" fontId="9" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -998,16 +1010,16 @@
       </c>
       <c r="M7" s="14" t="n"/>
       <c r="N7" s="15" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>着手</t>
+          <t>確認中</t>
         </is>
       </c>
       <c r="P7" s="13" t="inlineStr">
         <is>
-          <t>キックオフ資料を2版レビュー済（0828版・082802版／doc03・doc06）。開催日程が未確定。</t>
+          <t>★資料上の開催予定日 令和8年9月1日（火）を経過。開催の有無・決着事項・宿題が未確認。優先度Sの16件が決着したかどうかで以降の工程が変わるため、最優先で結果を確認する必要がある（doc19）。</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1138,7 @@
       </c>
       <c r="M9" s="14" t="n"/>
       <c r="N9" s="15" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
@@ -1135,7 +1147,7 @@
       </c>
       <c r="P9" s="13" t="inlineStr">
         <is>
-          <t>第9期計画書・第9期概要版（表裏）を受領。第五次総合振興計画・第3次健康21が未受領。</t>
+          <t>第9期計画書・第9期概要版（表裏）に加え、第四次生涯学習推進計画（全112頁）を受領（doc21）。第五次総合振興計画・第3次健康21・障がい福祉計画が未受領。</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3836,7 @@
       </c>
       <c r="M54" s="14" t="n"/>
       <c r="N54" s="15" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="O54" s="16" t="inlineStr">
         <is>
@@ -4076,11 +4088,11 @@
       <c r="J58" s="14" t="n"/>
       <c r="K58" s="14" t="n"/>
       <c r="L58" s="14" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="M58" s="14" t="n"/>
       <c r="N58" s="15" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="O58" s="16" t="inlineStr">
         <is>
@@ -4089,7 +4101,7 @@
       </c>
       <c r="P58" s="13" t="inlineStr">
         <is>
-          <t>doc14で第9期施策19本を評価。キックオフ資料により村単独事業名（除雪サービス・緊急通報・生活支援ハウス・はつらつ貯筋教室等）を把握。実績数値は未受領のため一部保留。</t>
+          <t>doc14で第9期施策19本を評価。キックオフ資料により村単独事業名（除雪サービス・緊急通報・生活支援ハウス・はつらつ貯筋教室等）を把握。交付金の指標単位データにより給付適正化の実施状況が判明（doc20§8-2）。実績数値は未受領のため一部保留。進捗管理評価シート27頁の全文読み込みが未了。</t>
         </is>
       </c>
     </row>
@@ -4798,11 +4810,11 @@
       <c r="J69" s="14" t="n"/>
       <c r="K69" s="14" t="n"/>
       <c r="L69" s="14" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="M69" s="14" t="n"/>
       <c r="N69" s="15" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="O69" s="16" t="inlineStr">
         <is>
@@ -4811,7 +4823,7 @@
       </c>
       <c r="P69" s="13" t="inlineStr">
         <is>
-          <t>指標案8件を現状値付きで提示済（doc07§7）。目標値はW系の県・全国平均入手後。</t>
+          <t>★交付金の配点表・全国集計3か年の受領により、満点・全国平均・県平均・全国順位が判明（doc20）。目標値設定の前提が整った。取りこぼし32項目・配点122点を特定。国ワークシートに依存しない指標から先に確定できる。指標案8件は doc07§7。</t>
         </is>
       </c>
     </row>
@@ -5174,11 +5186,11 @@
       <c r="J75" s="14" t="n"/>
       <c r="K75" s="14" t="n"/>
       <c r="L75" s="14" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="M75" s="14" t="n"/>
       <c r="N75" s="15" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="O75" s="16" t="inlineStr">
         <is>
@@ -5187,69 +5199,75 @@
       </c>
       <c r="P75" s="13" t="inlineStr">
         <is>
-          <t>doc14・doc18で施策体系（基本目標5本・施策28本）を確定。基本目標5の独立可否は村と要協議。</t>
+          <t>doc14・doc18で施策体系（基本目標5本・施策28本）を確定。施策3-5「介護給付の適正化」を交付金配点表に基づき全面改訂（主要3事業への再編・縦覧点検4帳票満点の事実を反映）。基本目標5の独立可否は村と要協議。</t>
         </is>
       </c>
     </row>
     <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="18" t="inlineStr">
+      <c r="A76" s="11" t="inlineStr">
         <is>
           <t>Ⅱ-72</t>
         </is>
       </c>
-      <c r="B76" s="19" t="inlineStr">
+      <c r="B76" s="12" t="inlineStr">
         <is>
           <t>Ⅱ 計画策定</t>
         </is>
       </c>
-      <c r="C76" s="19" t="inlineStr">
+      <c r="C76" s="12" t="inlineStr">
         <is>
           <t>Ⅱ-6 計画案の検討</t>
         </is>
       </c>
-      <c r="D76" s="20" t="inlineStr">
+      <c r="D76" s="13" t="inlineStr">
         <is>
           <t>関連計画との整合確認</t>
         </is>
       </c>
-      <c r="E76" s="18" t="inlineStr">
+      <c r="E76" s="11" t="inlineStr">
         <is>
           <t>仕様書4Ⅱ(6)</t>
         </is>
       </c>
-      <c r="F76" s="18" t="inlineStr">
+      <c r="F76" s="11" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G76" s="20" t="inlineStr">
+      <c r="G76" s="13" t="inlineStr">
         <is>
           <t>整合確認表</t>
         </is>
       </c>
-      <c r="H76" s="20" t="inlineStr">
+      <c r="H76" s="13" t="inlineStr">
         <is>
           <t>第5次総合振興計画／第3次健康21・グッドヘルスプラン</t>
         </is>
       </c>
-      <c r="I76" s="18" t="inlineStr">
+      <c r="I76" s="11" t="inlineStr">
         <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="J76" s="21" t="n"/>
-      <c r="K76" s="21" t="n"/>
-      <c r="L76" s="21" t="n"/>
-      <c r="M76" s="21" t="n"/>
-      <c r="N76" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" s="18" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P76" s="20" t="inlineStr"/>
+      <c r="J76" s="14" t="n"/>
+      <c r="K76" s="14" t="n"/>
+      <c r="L76" s="14" t="n">
+        <v>46267</v>
+      </c>
+      <c r="M76" s="14" t="n"/>
+      <c r="N76" s="15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O76" s="16" t="inlineStr">
+        <is>
+          <t>着手</t>
+        </is>
+      </c>
+      <c r="P76" s="13" t="inlineStr">
+        <is>
+          <t>★第四次生涯学習推進計画（2018〜2027年度）を受領・確認（doc21）。第10期計画期間中に上位計画（第五次総合振興計画・R8年度満了）と生涯学習推進計画（R9年度満了）がともに切り替わることを特定。高齢者関連6施策を抽出し「地域で見守り・育む高齢者の支援」が生活支援体制整備事業と重複することを確認。第3次健康21・障がい福祉計画・地域福祉計画が未受領。</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="11" t="inlineStr">
@@ -5426,11 +5444,11 @@
       <c r="J79" s="14" t="n"/>
       <c r="K79" s="14" t="n"/>
       <c r="L79" s="14" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="M79" s="14" t="n"/>
       <c r="N79" s="15" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="O79" s="16" t="inlineStr">
         <is>
@@ -5729,7 +5747,11 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="P84" s="13" t="inlineStr"/>
+      <c r="P84" s="13" t="inlineStr">
+        <is>
+          <t>★現委員の任期が令和8年9月30日で満了（doc19 追-C）。第1回策定委員会を11月に開催するには10月中の改選・委嘱が必要。手続きの所要期間を村に確認し逆算する必要がある。</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="23" t="inlineStr">
@@ -6194,7 +6216,7 @@
       </c>
       <c r="M92" s="14" t="n"/>
       <c r="N92" s="15" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="O92" s="16" t="inlineStr">
         <is>
@@ -6203,7 +6225,7 @@
       </c>
       <c r="P92" s="13" t="inlineStr">
         <is>
-          <t>受領資料は「受領資料・データ管理」シートで管理。</t>
+          <t>受領資料は「受領資料・データ管理」シートで管理（28件）。7z分割書庫の全4分割が揃い展開完了。</t>
         </is>
       </c>
     </row>
@@ -6742,7 +6764,7 @@
       </c>
       <c r="M101" s="14" t="n"/>
       <c r="N101" s="15" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="O101" s="16" t="inlineStr">
         <is>
@@ -6751,7 +6773,7 @@
       </c>
       <c r="P101" s="13" t="inlineStr">
         <is>
-          <t>本表で管理。基準日 令和8年8月31日。</t>
+          <t>本表で管理。基準日 令和8年9月2日。村への確認事項71件（解決済6件）。</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I40"/>
+  <dimension ref="B2:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -11326,35 +11348,277 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="55" t="inlineStr">
+      <c r="B37" s="36" t="inlineStr">
+        <is>
+          <t>■ 直近のマイルストーン（基準日 令和8年9月2日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="55" t="inlineStr"/>
+      <c r="C38" s="55" t="inlineStr">
+        <is>
+          <t>期日</t>
+        </is>
+      </c>
+      <c r="D38" s="55" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="E38" s="55" t="inlineStr">
+        <is>
+          <t>留意点</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="56" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="C39" s="57" t="inlineStr">
+        <is>
+          <t>令和8年9月1日（火）</t>
+        </is>
+      </c>
+      <c r="D39" s="57" t="inlineStr">
+        <is>
+          <t>キックオフ会議（資料上の予定日）</t>
+        </is>
+      </c>
+      <c r="E39" s="58" t="inlineStr">
+        <is>
+          <t>経過・結果未確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="56" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="C40" s="57" t="inlineStr">
+        <is>
+          <t>令和8年9月9日（水）</t>
+        </is>
+      </c>
+      <c r="D40" s="57" t="inlineStr">
+        <is>
+          <t>調査票の入稿</t>
+        </is>
+      </c>
+      <c r="E40" s="58" t="inlineStr">
+        <is>
+          <t>残り7日。優先度Sの決着が前提</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="23" t="inlineStr"/>
+      <c r="C41" s="24" t="inlineStr">
+        <is>
+          <t>令和8年9月11日（金）</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="inlineStr">
+        <is>
+          <t>宛名ラベル・配布用封筒の提供（前倒し案）</t>
+        </is>
+      </c>
+      <c r="E41" s="25" t="inlineStr">
+        <is>
+          <t>村。原案は9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="23" t="inlineStr"/>
+      <c r="C42" s="24" t="inlineStr">
+        <is>
+          <t>令和8年9月16〜17日</t>
+        </is>
+      </c>
+      <c r="D42" s="24" t="inlineStr">
+        <is>
+          <t>宛名貼付・封入・封緘</t>
+        </is>
+      </c>
+      <c r="E42" s="25" t="inlineStr">
+        <is>
+          <t>受託者</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="56" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="C43" s="57" t="inlineStr">
+        <is>
+          <t>令和8年9月18日（金）</t>
+        </is>
+      </c>
+      <c r="D43" s="57" t="inlineStr">
+        <is>
+          <t>発送（案）</t>
+        </is>
+      </c>
+      <c r="E43" s="58" t="inlineStr">
+        <is>
+          <t>★5連休（9/19〜9/23）の直前。9/17前倒しを協議</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="56" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="C44" s="57" t="inlineStr">
+        <is>
+          <t>令和8年9月30日（水）</t>
+        </is>
+      </c>
+      <c r="D44" s="57" t="inlineStr">
+        <is>
+          <t>策定委員会 現委員の任期満了</t>
+        </is>
+      </c>
+      <c r="E44" s="58" t="inlineStr">
+        <is>
+          <t>★10月中の改選・委嘱が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="23" t="inlineStr"/>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>令和8年10月上旬</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="inlineStr">
+        <is>
+          <t>督促（リマインド）の要否判断</t>
+        </is>
+      </c>
+      <c r="E45" s="25" t="inlineStr">
+        <is>
+          <t>第9期の在宅調査回収率45.8%を踏まえ</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="23" t="inlineStr"/>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>令和8年11月</t>
+        </is>
+      </c>
+      <c r="D46" s="24" t="inlineStr">
+        <is>
+          <t>第1回策定委員会</t>
+        </is>
+      </c>
+      <c r="E46" s="25" t="inlineStr">
+        <is>
+          <t>委員改選の完了が前提</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="56" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="C47" s="57" t="inlineStr">
+        <is>
+          <t>令和8年12月中旬</t>
+        </is>
+      </c>
+      <c r="D47" s="57" t="inlineStr">
+        <is>
+          <t>第2回策定委員会</t>
+        </is>
+      </c>
+      <c r="E47" s="58" t="inlineStr">
+        <is>
+          <t>★12月を外すと第3回が3月となり履行期限に間に合わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="23" t="inlineStr"/>
+      <c r="C48" s="24" t="inlineStr">
+        <is>
+          <t>令和9年2月</t>
+        </is>
+      </c>
+      <c r="D48" s="24" t="inlineStr">
+        <is>
+          <t>第3回策定委員会</t>
+        </is>
+      </c>
+      <c r="E48" s="25" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="23" t="inlineStr"/>
+      <c r="C49" s="24" t="inlineStr">
+        <is>
+          <t>令和9年3月31日</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="inlineStr">
+        <is>
+          <t>履行期限（納品・検収）</t>
+        </is>
+      </c>
+      <c r="E49" s="25" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="B51" s="59" t="inlineStr">
         <is>
           <t>※「仕様書該当」欄の凡例：仕様書＝8北保福第483号 別紙／手引き＝厚生労働省の実施の手引き（令和7年8月版）／確認＝本業務での確認事項</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="55" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="59" t="inlineStr">
         <is>
           <t>※ 想定時期は仕様書の履行期限（令和9年3月31日）から逆算した目安です。村との協議結果により確定します。</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="55" t="inlineStr">
+    <row r="53">
+      <c r="B53" s="59" t="inlineStr">
         <is>
           <t>※ 令和8年9月19日（土）〜23日（水）は5連休（敬老の日9/21・国民の休日9/22・秋分の日9/23）です。発送・回収工程に影響します。</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="55" t="inlineStr">
-        <is>
-          <t>※ 進捗基準日は令和8年8月31日です。備考欄の doc番号は docs/北塩原村_第10期/ 配下の分析資料に対応します。</t>
+    <row r="54">
+      <c r="B54" s="59" t="inlineStr">
+        <is>
+          <t>※ 進捗基準日は令和8年9月2日です。備考欄の doc番号は docs/北塩原村_第10期/ 配下の分析資料に対応します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="59" t="inlineStr">
+        <is>
+          <t>※ マイルストーンの★印は、遅れると後続工程が連鎖的に破綻する項目です。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="D7:H7"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="D6:H6"/>
@@ -11367,6 +11631,7 @@
     <mergeCell ref="B16:H16"/>
     <mergeCell ref="B11:H11"/>
     <mergeCell ref="C12:H12"/>
+    <mergeCell ref="B37:H37"/>
     <mergeCell ref="D9:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="凡例・集計" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$101</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -190,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -273,7 +273,16 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -716,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P101"/>
+  <dimension ref="A1:P104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -962,64 +971,66 @@
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>０-03</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>０ 契約・立上げ</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>立上げ</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>キックオフ会議の開催</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>仕様書4Ⅲ</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>双方</t>
         </is>
       </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>キックオフ会議資料・議事録</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr"/>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>R8.9上</t>
         </is>
       </c>
-      <c r="J7" s="14" t="n"/>
-      <c r="K7" s="14" t="n"/>
-      <c r="L7" s="14" t="n">
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="8" t="n">
         <v>46259</v>
       </c>
-      <c r="M7" s="14" t="n"/>
-      <c r="N7" s="15" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="O7" s="16" t="inlineStr">
-        <is>
-          <t>確認中</t>
-        </is>
-      </c>
-      <c r="P7" s="13" t="inlineStr">
-        <is>
-          <t>★資料上の開催予定日 令和8年9月1日（火）を経過。開催の有無・決着事項・宿題が未確認。優先度Sの16件が決着したかどうかで以降の工程が変わるため、最優先で結果を確認する必要がある（doc19）。</t>
+      <c r="M7" s="8" t="n">
+        <v>46266</v>
+      </c>
+      <c r="N7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="10" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>令和8年9月1日（火）北塩原村役場にて開催。議事録を受領し確認・論点整理を完了（doc22）。優先度S 16件のうち9件が決着。基準日R8.9.1・在宅調査の抽出基準・管理番号の紐付け・発送9/18・ラベル封筒は村が用意・回収は100件ごとの小分け送付。</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1286,7 @@
       </c>
       <c r="P11" s="13" t="inlineStr">
         <is>
-          <t>手法Ⅲを想定。第10期新設の手法Ⅳ（新版 在宅生活改善調査）の採否が未決。</t>
+          <t>★議事録に記載なし。手法Ⅲか手法Ⅳ（新版 在宅生活改善調査）を加えるかが未決着。9/3の第1稿提出時に併せて提起する（doc22 A-1）。</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1343,7 @@
       </c>
       <c r="M12" s="14" t="n"/>
       <c r="N12" s="15" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="O12" s="16" t="inlineStr">
         <is>
@@ -1341,7 +1352,7 @@
       </c>
       <c r="P12" s="13" t="inlineStr">
         <is>
-          <t>3論点（要支援を含むか／更新・区分変更に限るか／サ高住等を含むか）を提示済。村回答待ち。</t>
+          <t>★在宅介護実態調査は「要支援1・2および要介護1〜5の在宅生活者等」150件で決着（議事録）。基準日は令和8年9月1日。ニーズ調査約850件の抽出基準（要支援を含むか）は未決着。</t>
         </is>
       </c>
     </row>
@@ -1738,124 +1749,136 @@
       <c r="P18" s="20" t="inlineStr"/>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Ⅰ-15</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>Ⅰ ニーズ調査</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>Ⅰ-1 調査設計</t>
         </is>
       </c>
-      <c r="D19" s="25" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>調査票の村協議・確定</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>仕様書4Ⅰ(2)</t>
         </is>
       </c>
-      <c r="F19" s="23" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>双方</t>
         </is>
       </c>
-      <c r="G19" s="25" t="inlineStr">
+      <c r="G19" s="13" t="inlineStr">
         <is>
           <t>確定版調査票</t>
         </is>
       </c>
-      <c r="H19" s="25" t="inlineStr">
+      <c r="H19" s="13" t="inlineStr">
         <is>
           <t>以降の全工程の起点</t>
         </is>
       </c>
-      <c r="I19" s="23" t="inlineStr">
+      <c r="I19" s="11" t="inlineStr">
         <is>
           <t>R8.9上</t>
         </is>
       </c>
-      <c r="J19" s="26" t="n"/>
-      <c r="K19" s="26" t="n"/>
-      <c r="L19" s="26" t="n"/>
-      <c r="M19" s="26" t="n"/>
-      <c r="N19" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P19" s="25" t="inlineStr"/>
+      <c r="J19" s="14" t="n"/>
+      <c r="K19" s="14" t="n"/>
+      <c r="L19" s="14" t="n">
+        <v>46267</v>
+      </c>
+      <c r="M19" s="14" t="n"/>
+      <c r="N19" s="15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O19" s="16" t="inlineStr">
+        <is>
+          <t>着手</t>
+        </is>
+      </c>
+      <c r="P19" s="13" t="inlineStr">
+        <is>
+          <t>★議事録により9/3に第1稿提出、9/9頃に最終校了と確定。未決事項（手法・オプション項目・独自設問・依頼状名義・部数）は選択肢併記で提出する。</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Ⅰ-16</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Ⅰ ニーズ調査</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>Ⅰ-1 調査設計</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>ウェブ回答フォームの作成</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>仕様書4Ⅰ(2)</t>
         </is>
       </c>
-      <c r="F20" s="18" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G20" s="20" t="inlineStr">
+      <c r="G20" s="13" t="inlineStr">
         <is>
           <t>ウェブフォーム</t>
         </is>
       </c>
-      <c r="H20" s="20" t="inlineStr">
+      <c r="H20" s="13" t="inlineStr">
         <is>
           <t>通信の暗号化・公開期間の設定</t>
         </is>
       </c>
-      <c r="I20" s="18" t="inlineStr">
+      <c r="I20" s="11" t="inlineStr">
         <is>
           <t>R8.9上</t>
         </is>
       </c>
-      <c r="J20" s="21" t="n"/>
-      <c r="K20" s="21" t="n"/>
-      <c r="L20" s="21" t="n"/>
-      <c r="M20" s="21" t="n"/>
-      <c r="N20" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="18" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P20" s="20" t="inlineStr"/>
+      <c r="J20" s="14" t="n"/>
+      <c r="K20" s="14" t="n"/>
+      <c r="L20" s="14" t="n">
+        <v>46267</v>
+      </c>
+      <c r="M20" s="14" t="n"/>
+      <c r="N20" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O20" s="16" t="inlineStr">
+        <is>
+          <t>確認中</t>
+        </is>
+      </c>
+      <c r="P20" s="13" t="inlineStr">
+        <is>
+          <t>★QRコード併用は議事録で決着。実装方法（Googleフォームの可否）が未決着で、不可の場合は代替の構築期間が必要となり9/9校了に影響する（doc22 A-2）。</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="23" t="inlineStr">
@@ -1918,64 +1941,70 @@
       <c r="P21" s="25" t="inlineStr"/>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Ⅰ-18</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>Ⅰ ニーズ調査</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>Ⅰ-1 調査設計</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>重複回答の管理方法の設計（管理番号）</t>
         </is>
       </c>
-      <c r="E22" s="18" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>仕様書4Ⅰ(2)</t>
         </is>
       </c>
-      <c r="F22" s="18" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G22" s="20" t="inlineStr">
+      <c r="G22" s="13" t="inlineStr">
         <is>
           <t>管理番号設計書</t>
         </is>
       </c>
-      <c r="H22" s="20" t="inlineStr">
+      <c r="H22" s="13" t="inlineStr">
         <is>
           <t>紙・ウェブの重複を排除</t>
         </is>
       </c>
-      <c r="I22" s="18" t="inlineStr">
+      <c r="I22" s="11" t="inlineStr">
         <is>
           <t>R8.9上</t>
         </is>
       </c>
-      <c r="J22" s="21" t="n"/>
-      <c r="K22" s="21" t="n"/>
-      <c r="L22" s="21" t="n"/>
-      <c r="M22" s="21" t="n"/>
-      <c r="N22" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="18" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P22" s="20" t="inlineStr"/>
+      <c r="J22" s="14" t="n"/>
+      <c r="K22" s="14" t="n"/>
+      <c r="L22" s="14" t="n">
+        <v>46261</v>
+      </c>
+      <c r="M22" s="14" t="n"/>
+      <c r="N22" s="15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O22" s="16" t="inlineStr">
+        <is>
+          <t>着手</t>
+        </is>
+      </c>
+      <c r="P22" s="13" t="inlineStr">
+        <is>
+          <t>★議事録で方針決着。氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
@@ -2030,7 +2059,7 @@
       </c>
       <c r="M23" s="14" t="n"/>
       <c r="N23" s="15" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="O23" s="16" t="inlineStr">
         <is>
@@ -2039,7 +2068,7 @@
       </c>
       <c r="P23" s="13" t="inlineStr">
         <is>
-          <t>第10期の新規要件として論点提示済。村のラベル作成仕様と一体で確定が必要。</t>
+          <t>★議事録で方針決着（同上）。見える化システムへの登録を見据えた設計とする。</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2130,11 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="P24" s="20" t="inlineStr"/>
+      <c r="P24" s="20" t="inlineStr">
+        <is>
+          <t>★9/9頃の校了・印刷依頼が目標（議事録）。9/3の第1稿提出→修正・確認を経て確定する。</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="23" t="inlineStr">
@@ -2655,7 +2688,7 @@
       </c>
       <c r="F34" s="18" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>双方</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr">
@@ -2663,7 +2696,11 @@
           <t>回収状況表</t>
         </is>
       </c>
-      <c r="H34" s="20" t="inlineStr"/>
+      <c r="H34" s="20" t="inlineStr">
+        <is>
+          <t>★議事録により、村で100件程度集まるごとに随時受託者へ小分け送付する運用と確定</t>
+        </is>
+      </c>
       <c r="I34" s="18" t="inlineStr">
         <is>
           <t>R8.9下〜10</t>
@@ -2681,7 +2718,11 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="P34" s="20" t="inlineStr"/>
+      <c r="P34" s="20" t="inlineStr">
+        <is>
+          <t>★小分け送付の運用に合わせ、村側の送付単位と受託者側の入力進捗を突き合わせる管理表が必要。</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="23" t="inlineStr">
@@ -3832,11 +3873,11 @@
       <c r="J54" s="14" t="n"/>
       <c r="K54" s="14" t="n"/>
       <c r="L54" s="14" t="n">
-        <v>46261</v>
+        <v>46259</v>
       </c>
       <c r="M54" s="14" t="n"/>
       <c r="N54" s="15" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="O54" s="16" t="inlineStr">
         <is>
@@ -3845,7 +3886,7 @@
       </c>
       <c r="P54" s="13" t="inlineStr">
         <is>
-          <t>国の指針・様式の更新確認を実施済（doc04）。令和7年8月版の反映まで完了。</t>
+          <t>交付金の令和8年度配点表を入手し評価指標の改定を確認（doc20）。★議事録により令和9年度の介護報酬改定への対応方針（現行単価で試算→単価確定後に補正）が決着。第10期の国の基本指針は告示待ち。</t>
         </is>
       </c>
     </row>
@@ -4678,11 +4719,11 @@
       <c r="J67" s="14" t="n"/>
       <c r="K67" s="14" t="n"/>
       <c r="L67" s="14" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="M67" s="14" t="n"/>
       <c r="N67" s="15" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="O67" s="16" t="inlineStr">
         <is>
@@ -4691,7 +4732,7 @@
       </c>
       <c r="P67" s="13" t="inlineStr">
         <is>
-          <t>★村へ依頼中。令和6年度末実績・令和7年度末見込。保険料算定の前提。</t>
+          <t>★議事録に「基金の取り崩し（第9期は800万円程度）」とあり、第9期計画から読み取った24,000,000円との齟齬がある。年額か期間合計かの確認が必要（doc22 K-74）。複数パターンのシミュレーションを受託者で行うことは決着。</t>
         </is>
       </c>
     </row>
@@ -4744,11 +4785,11 @@
       <c r="J68" s="14" t="n"/>
       <c r="K68" s="14" t="n"/>
       <c r="L68" s="14" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="M68" s="14" t="n"/>
       <c r="N68" s="15" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="O68" s="16" t="inlineStr">
         <is>
@@ -4757,7 +4798,7 @@
       </c>
       <c r="P68" s="13" t="inlineStr">
         <is>
-          <t>doc18 第5章5-7に保険料算定の様式と所得段階13段階の枠を作成。第9期の算定結果を参考掲載。基金残高と国ワークシート待ち。</t>
+          <t>★議事録で方針決着：第9期で県内平均を上回ったため急激な負担増を抑えたい意向。基金取崩も視野。令和9年度の介護報酬改定を見据え現行単価で一旦試算し単価確定後に補正。doc18 第5章5-7に様式と所得段階13段階の枠を作成済。</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5297,7 @@
       </c>
       <c r="M76" s="14" t="n"/>
       <c r="N76" s="15" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="O76" s="16" t="inlineStr">
         <is>
@@ -5265,7 +5306,7 @@
       </c>
       <c r="P76" s="13" t="inlineStr">
         <is>
-          <t>★第四次生涯学習推進計画（2018〜2027年度）を受領・確認（doc21）。第10期計画期間中に上位計画（第五次総合振興計画・R8年度満了）と生涯学習推進計画（R9年度満了）がともに切り替わることを特定。高齢者関連6施策を抽出し「地域で見守り・育む高齢者の支援」が生活支援体制整備事業と重複することを確認。第3次健康21・障がい福祉計画・地域福祉計画が未受領。</t>
+          <t>★議事録で整合対象が確定（障がい福祉計画・地域福祉計画・グッドヘルスプラン・生涯学習計画）。第四次生涯学習推進計画は受領・確認済（doc21）。他は未受領。</t>
         </is>
       </c>
     </row>
@@ -5318,20 +5359,20 @@
       <c r="J77" s="14" t="n"/>
       <c r="K77" s="14" t="n"/>
       <c r="L77" s="14" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="M77" s="14" t="n"/>
       <c r="N77" s="15" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="O77" s="16" t="inlineStr">
         <is>
-          <t>確認中</t>
+          <t>着手</t>
         </is>
       </c>
       <c r="P77" s="13" t="inlineStr">
         <is>
-          <t>第9期は認知症・成年後見を基本目標4に内包する構成（概要版裏面で確認）。第10期の踏襲可否を要確認。</t>
+          <t>★議事録により整合対象が確定：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。生涯学習計画は受領済（doc21）。</t>
         </is>
       </c>
     </row>
@@ -5499,12 +5540,12 @@
       </c>
       <c r="H80" s="13" t="inlineStr">
         <is>
-          <t>通常30日間</t>
+          <t>★議事録により第2回委員会（11月）の後に実施と確定。方向性や説明文を追記した上で実施</t>
         </is>
       </c>
       <c r="I80" s="11" t="inlineStr">
         <is>
-          <t>R8.12〜R9.1</t>
+          <t>R8.11〜12</t>
         </is>
       </c>
       <c r="J80" s="14" t="n"/>
@@ -5557,10 +5598,14 @@
           <t>対応表</t>
         </is>
       </c>
-      <c r="H81" s="25" t="inlineStr"/>
+      <c r="H81" s="25" t="inlineStr">
+        <is>
+          <t>第3回委員会（1月下旬〜2月上旬）で報告</t>
+        </is>
+      </c>
       <c r="I81" s="23" t="inlineStr">
         <is>
-          <t>R9.1〜2</t>
+          <t>R8.12〜R9.1</t>
         </is>
       </c>
       <c r="J81" s="26" t="n"/>
@@ -5727,7 +5772,7 @@
       </c>
       <c r="H84" s="13" t="inlineStr">
         <is>
-          <t>現委員の任期は令和8年9月30日満了</t>
+          <t>★現委員の任期は令和8年9月30日満了。議事録では触れられておらず改選の要否が未確認。第2回（11月）の前提</t>
         </is>
       </c>
       <c r="I84" s="11" t="inlineStr">
@@ -5791,12 +5836,12 @@
       </c>
       <c r="H85" s="25" t="inlineStr">
         <is>
-          <t>調査結果報告・第9期評価・策定方針</t>
+          <t>★議事録により第1回は受託前に開催済みと確定。本業務の対象外</t>
         </is>
       </c>
       <c r="I85" s="23" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>開催済</t>
         </is>
       </c>
       <c r="J85" s="26" t="n"/>
@@ -5804,14 +5849,18 @@
       <c r="L85" s="26" t="n"/>
       <c r="M85" s="26" t="n"/>
       <c r="N85" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O85" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P85" s="25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O85" s="28" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="P85" s="25" t="inlineStr">
+        <is>
+          <t>★議事録により第1回策定委員会は受託前に開催済みと確定。本業務の対象外。</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="18" t="inlineStr">
@@ -5849,10 +5898,14 @@
           <t>会議記録</t>
         </is>
       </c>
-      <c r="H86" s="20" t="inlineStr"/>
+      <c r="H86" s="20" t="inlineStr">
+        <is>
+          <t>★同上。開催済のため対象外</t>
+        </is>
+      </c>
       <c r="I86" s="18" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>開催済</t>
         </is>
       </c>
       <c r="J86" s="21" t="n"/>
@@ -5860,14 +5913,18 @@
       <c r="L86" s="21" t="n"/>
       <c r="M86" s="21" t="n"/>
       <c r="N86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" s="18" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P86" s="20" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O86" s="29" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="P86" s="20" t="inlineStr">
+        <is>
+          <t>★同上。対象外。</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="23" t="inlineStr">
@@ -5907,12 +5964,12 @@
       </c>
       <c r="H87" s="25" t="inlineStr">
         <is>
-          <t>計画素案・見込量・保険料の考え方</t>
+          <t>★アンケート分析結果・第9期の効果検証（R7実績まで）・骨子・施策体系・見込量・保険料概算・素案（完成度7割）</t>
         </is>
       </c>
       <c r="I87" s="23" t="inlineStr">
         <is>
-          <t>R8.12〜R9.1</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="J87" s="26" t="n"/>
@@ -5968,7 +6025,7 @@
       <c r="H88" s="20" t="inlineStr"/>
       <c r="I88" s="18" t="inlineStr">
         <is>
-          <t>R8.12〜R9.1</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="J88" s="21" t="n"/>
@@ -6023,12 +6080,12 @@
       </c>
       <c r="H89" s="25" t="inlineStr">
         <is>
-          <t>パブコメ結果の反映・計画原案・保険料の確定</t>
+          <t>パブコメ結果と反映内容の報告。ほぼ完成版の素案として最終合意</t>
         </is>
       </c>
       <c r="I89" s="23" t="inlineStr">
         <is>
-          <t>R9.2</t>
+          <t>R9.1下〜2上</t>
         </is>
       </c>
       <c r="J89" s="26" t="n"/>
@@ -6084,7 +6141,7 @@
       <c r="H90" s="20" t="inlineStr"/>
       <c r="I90" s="18" t="inlineStr">
         <is>
-          <t>R9.2</t>
+          <t>R9.1下〜2上</t>
         </is>
       </c>
       <c r="J90" s="21" t="n"/>
@@ -6235,7 +6292,7 @@
           <t>Ⅳ-89</t>
         </is>
       </c>
-      <c r="B93" s="28" t="inlineStr">
+      <c r="B93" s="30" t="inlineStr">
         <is>
           <t>Ⅳ 成果品・納品</t>
         </is>
@@ -6442,17 +6499,17 @@
       </c>
       <c r="G96" s="20" t="inlineStr">
         <is>
-          <t>概要版</t>
+          <t>概要版 A3両面程度</t>
         </is>
       </c>
       <c r="H96" s="20" t="inlineStr">
         <is>
-          <t>仕様書に記載なし。要否・費用・部数・体裁を要協議</t>
+          <t>★議事録で作成が合意（理念・体系図・推移データを記載）。2月末の議会全員協議会で使用。仕様の範囲内か追加対応かは要確認</t>
         </is>
       </c>
       <c r="I96" s="18" t="inlineStr">
         <is>
-          <t>R9.2〜3</t>
+          <t>R9.1〜2</t>
         </is>
       </c>
       <c r="J96" s="21" t="n"/>
@@ -6467,52 +6524,56 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="P96" s="20" t="inlineStr"/>
+      <c r="P96" s="20" t="inlineStr">
+        <is>
+          <t>★議事録でA3両面程度（理念・体系図・推移データ）と決着。第9期はA4 2ページ。仕様の範囲内か追加対応かは要確認（doc22 K-79）。</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-93</t>
-        </is>
-      </c>
-      <c r="B97" s="24" t="inlineStr">
-        <is>
-          <t>Ⅳ 成果品・納品</t>
+          <t>Ⅱ-93</t>
+        </is>
+      </c>
+      <c r="B97" s="30" t="inlineStr">
+        <is>
+          <t>Ⅱ 計画策定</t>
         </is>
       </c>
       <c r="C97" s="24" t="inlineStr">
         <is>
-          <t>Ⅳ-2 納品</t>
+          <t>Ⅱ-8 策定委員会支援</t>
         </is>
       </c>
       <c r="D97" s="25" t="inlineStr">
         <is>
-          <t>納品・検収</t>
+          <t>議会全員協議会 説明資料の作成</t>
         </is>
       </c>
       <c r="E97" s="23" t="inlineStr">
         <is>
-          <t>仕様書3</t>
+          <t>確認</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t>双方</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="G97" s="25" t="inlineStr">
         <is>
-          <t>検収書</t>
+          <t>説明資料</t>
         </is>
       </c>
       <c r="H97" s="25" t="inlineStr">
         <is>
-          <t>履行期限 令和9年3月31日</t>
+          <t>★議事録で新設。概要版を用いて次期計画を説明。受託者の関与範囲（資料のみか出席を含むか）は要確認</t>
         </is>
       </c>
       <c r="I97" s="23" t="inlineStr">
         <is>
-          <t>R9.3</t>
+          <t>R9.2末</t>
         </is>
       </c>
       <c r="J97" s="26" t="n"/>
@@ -6527,98 +6588,100 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="P97" s="25" t="inlineStr"/>
+      <c r="P97" s="25" t="inlineStr">
+        <is>
+          <t>★議事録で新設。令和9年2月末頃に概要版を用いて次期計画を説明。受託者の関与範囲（資料作成のみか出席・説明を含むか）が未確認（doc22 K-80）。</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="30" customHeight="1">
-      <c r="A98" s="11" t="inlineStr">
-        <is>
-          <t>Ⅴ-94</t>
-        </is>
-      </c>
-      <c r="B98" s="17" t="inlineStr">
-        <is>
-          <t>Ⅴ 管理</t>
-        </is>
-      </c>
-      <c r="C98" s="12" t="inlineStr">
-        <is>
-          <t>Ⅴ-1 情報管理</t>
-        </is>
-      </c>
-      <c r="D98" s="13" t="inlineStr">
-        <is>
-          <t>個人情報の適正管理（アクセス制限・保管ルール）</t>
-        </is>
-      </c>
-      <c r="E98" s="11" t="inlineStr">
-        <is>
-          <t>仕様書6(1)</t>
-        </is>
-      </c>
-      <c r="F98" s="11" t="inlineStr">
-        <is>
-          <t>受託者</t>
-        </is>
-      </c>
-      <c r="G98" s="13" t="inlineStr">
-        <is>
-          <t>管理記録</t>
-        </is>
-      </c>
-      <c r="H98" s="13" t="inlineStr">
-        <is>
-          <t>契約終了後・解除後も同様</t>
-        </is>
-      </c>
-      <c r="I98" s="11" t="inlineStr">
-        <is>
-          <t>通期</t>
-        </is>
-      </c>
-      <c r="J98" s="14" t="n"/>
-      <c r="K98" s="14" t="n"/>
-      <c r="L98" s="14" t="n">
-        <v>46259</v>
-      </c>
-      <c r="M98" s="14" t="n"/>
-      <c r="N98" s="15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O98" s="16" t="inlineStr">
-        <is>
-          <t>着手</t>
-        </is>
-      </c>
-      <c r="P98" s="13" t="inlineStr">
-        <is>
-          <t>doc16として管理ルールを文書化完了（10項目のチェックリスト付）。村との合意・従事者名簿・誓約書は未実施。</t>
+      <c r="A98" s="18" t="inlineStr">
+        <is>
+          <t>Ⅰ-94</t>
+        </is>
+      </c>
+      <c r="B98" s="31" t="inlineStr">
+        <is>
+          <t>Ⅰ ニーズ調査</t>
+        </is>
+      </c>
+      <c r="C98" s="19" t="inlineStr">
+        <is>
+          <t>Ⅰ-3 発送・回収</t>
+        </is>
+      </c>
+      <c r="D98" s="20" t="inlineStr">
+        <is>
+          <t>調査票の受渡し記録の作成・運用</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="F98" s="18" t="inlineStr">
+        <is>
+          <t>双方</t>
+        </is>
+      </c>
+      <c r="G98" s="20" t="inlineStr">
+        <is>
+          <t>受渡し記録</t>
+        </is>
+      </c>
+      <c r="H98" s="20" t="inlineStr">
+        <is>
+          <t>★小分け送付の運用に対応。日付・数量・受渡者・受領者を記録。doc16に追記</t>
+        </is>
+      </c>
+      <c r="I98" s="18" t="inlineStr">
+        <is>
+          <t>R8.9下〜11</t>
+        </is>
+      </c>
+      <c r="J98" s="21" t="n"/>
+      <c r="K98" s="21" t="n"/>
+      <c r="L98" s="21" t="n"/>
+      <c r="M98" s="21" t="n"/>
+      <c r="N98" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="18" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="P98" s="20" t="inlineStr">
+        <is>
+          <t>★議事録により村が100件程度ごとに随時送付する運用と確定。個人情報の授受が複数回に分かれるため受渡し記録の様式を用意し doc16 に追記する。</t>
         </is>
       </c>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="23" t="inlineStr">
         <is>
-          <t>Ⅴ-95</t>
+          <t>Ⅰ-95</t>
         </is>
       </c>
       <c r="B99" s="24" t="inlineStr">
         <is>
-          <t>Ⅴ 管理</t>
+          <t>Ⅰ ニーズ調査</t>
         </is>
       </c>
       <c r="C99" s="24" t="inlineStr">
         <is>
-          <t>Ⅴ-1 情報管理</t>
+          <t>Ⅰ-5 集計・分析</t>
         </is>
       </c>
       <c r="D99" s="25" t="inlineStr">
         <is>
-          <t>業務完了後の情報の返還・消去</t>
+          <t>ICFの構成要素に基づくクロス分析の設計</t>
         </is>
       </c>
       <c r="E99" s="23" t="inlineStr">
         <is>
-          <t>仕様書6(1)</t>
+          <t>確認</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
@@ -6628,17 +6691,17 @@
       </c>
       <c r="G99" s="25" t="inlineStr">
         <is>
-          <t>消去証明</t>
+          <t>分析設計書</t>
         </is>
       </c>
       <c r="H99" s="25" t="inlineStr">
         <is>
-          <t>村の指示に従う</t>
+          <t>★議事録で新規要件。単純なリスク分析ではなくICFの健康度指標で「元気な高齢者」×「地域のニーズ」を分析。調査票設計段階で軸の確保が必要</t>
         </is>
       </c>
       <c r="I99" s="23" t="inlineStr">
         <is>
-          <t>R9.3</t>
+          <t>R8.9上</t>
         </is>
       </c>
       <c r="J99" s="26" t="n"/>
@@ -6653,32 +6716,36 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="P99" s="25" t="inlineStr"/>
+      <c r="P99" s="25" t="inlineStr">
+        <is>
+          <t>★議事録で新規要件。単純なリスク分析ではなくICF（国際生活機能分類）等の健康度指標でクロス分析し、「元気な高齢者」×「地域のニーズ」から共助・互助の必要性を示す。調査票の第1稿段階でクロス軸を確保する必要があるため、9/3までに設問との対応表が要る。</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="18" t="inlineStr">
         <is>
-          <t>Ⅴ-96</t>
-        </is>
-      </c>
-      <c r="B100" s="19" t="inlineStr">
-        <is>
-          <t>Ⅴ 管理</t>
+          <t>Ⅳ-96</t>
+        </is>
+      </c>
+      <c r="B100" s="31" t="inlineStr">
+        <is>
+          <t>Ⅳ 成果品・納品</t>
         </is>
       </c>
       <c r="C100" s="19" t="inlineStr">
         <is>
-          <t>Ⅴ-2 再委託</t>
+          <t>Ⅳ-2 納品</t>
         </is>
       </c>
       <c r="D100" s="20" t="inlineStr">
         <is>
-          <t>再委託の書面承諾の取得</t>
+          <t>納品・検収</t>
         </is>
       </c>
       <c r="E100" s="18" t="inlineStr">
         <is>
-          <t>仕様書6(2)</t>
+          <t>仕様書3</t>
         </is>
       </c>
       <c r="F100" s="18" t="inlineStr">
@@ -6688,17 +6755,17 @@
       </c>
       <c r="G100" s="20" t="inlineStr">
         <is>
-          <t>承諾書</t>
+          <t>検収書</t>
         </is>
       </c>
       <c r="H100" s="20" t="inlineStr">
         <is>
-          <t>印刷・データ入力・ウェブフォーム構築等を外注する場合</t>
+          <t>履行期限 令和9年3月31日</t>
         </is>
       </c>
       <c r="I100" s="18" t="inlineStr">
         <is>
-          <t>随時</t>
+          <t>R9.3</t>
         </is>
       </c>
       <c r="J100" s="21" t="n"/>
@@ -6721,24 +6788,24 @@
           <t>Ⅴ-97</t>
         </is>
       </c>
-      <c r="B101" s="12" t="inlineStr">
+      <c r="B101" s="17" t="inlineStr">
         <is>
           <t>Ⅴ 管理</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Ⅴ-3 進捗管理</t>
+          <t>Ⅴ-1 情報管理</t>
         </is>
       </c>
       <c r="D101" s="13" t="inlineStr">
         <is>
-          <t>進捗管理・課題管理</t>
+          <t>個人情報の適正管理（アクセス制限・保管ルール）</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>仕様書6(1)</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
@@ -6748,10 +6815,14 @@
       </c>
       <c r="G101" s="13" t="inlineStr">
         <is>
-          <t>本進捗管理表</t>
-        </is>
-      </c>
-      <c r="H101" s="13" t="inlineStr"/>
+          <t>管理記録</t>
+        </is>
+      </c>
+      <c r="H101" s="13" t="inlineStr">
+        <is>
+          <t>契約終了後・解除後も同様</t>
+        </is>
+      </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
           <t>通期</t>
@@ -6760,34 +6831,216 @@
       <c r="J101" s="14" t="n"/>
       <c r="K101" s="14" t="n"/>
       <c r="L101" s="14" t="n">
-        <v>46265</v>
+        <v>46259</v>
       </c>
       <c r="M101" s="14" t="n"/>
       <c r="N101" s="15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O101" s="16" t="inlineStr">
+        <is>
+          <t>着手</t>
+        </is>
+      </c>
+      <c r="P101" s="13" t="inlineStr">
+        <is>
+          <t>doc16として管理ルールを文書化完了（10項目のチェックリスト付）。村との合意・従事者名簿・誓約書は未実施。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="30" customHeight="1">
+      <c r="A102" s="18" t="inlineStr">
+        <is>
+          <t>Ⅴ-98</t>
+        </is>
+      </c>
+      <c r="B102" s="19" t="inlineStr">
+        <is>
+          <t>Ⅴ 管理</t>
+        </is>
+      </c>
+      <c r="C102" s="19" t="inlineStr">
+        <is>
+          <t>Ⅴ-1 情報管理</t>
+        </is>
+      </c>
+      <c r="D102" s="20" t="inlineStr">
+        <is>
+          <t>業務完了後の情報の返還・消去</t>
+        </is>
+      </c>
+      <c r="E102" s="18" t="inlineStr">
+        <is>
+          <t>仕様書6(1)</t>
+        </is>
+      </c>
+      <c r="F102" s="18" t="inlineStr">
+        <is>
+          <t>受託者</t>
+        </is>
+      </c>
+      <c r="G102" s="20" t="inlineStr">
+        <is>
+          <t>消去証明</t>
+        </is>
+      </c>
+      <c r="H102" s="20" t="inlineStr">
+        <is>
+          <t>村の指示に従う</t>
+        </is>
+      </c>
+      <c r="I102" s="18" t="inlineStr">
+        <is>
+          <t>R9.3</t>
+        </is>
+      </c>
+      <c r="J102" s="21" t="n"/>
+      <c r="K102" s="21" t="n"/>
+      <c r="L102" s="21" t="n"/>
+      <c r="M102" s="21" t="n"/>
+      <c r="N102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="18" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="P102" s="20" t="inlineStr"/>
+    </row>
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="23" t="inlineStr">
+        <is>
+          <t>Ⅴ-99</t>
+        </is>
+      </c>
+      <c r="B103" s="24" t="inlineStr">
+        <is>
+          <t>Ⅴ 管理</t>
+        </is>
+      </c>
+      <c r="C103" s="24" t="inlineStr">
+        <is>
+          <t>Ⅴ-2 再委託</t>
+        </is>
+      </c>
+      <c r="D103" s="25" t="inlineStr">
+        <is>
+          <t>再委託の書面承諾の取得</t>
+        </is>
+      </c>
+      <c r="E103" s="23" t="inlineStr">
+        <is>
+          <t>仕様書6(2)</t>
+        </is>
+      </c>
+      <c r="F103" s="23" t="inlineStr">
+        <is>
+          <t>双方</t>
+        </is>
+      </c>
+      <c r="G103" s="25" t="inlineStr">
+        <is>
+          <t>承諾書</t>
+        </is>
+      </c>
+      <c r="H103" s="25" t="inlineStr">
+        <is>
+          <t>印刷・データ入力・ウェブフォーム構築等を外注する場合</t>
+        </is>
+      </c>
+      <c r="I103" s="23" t="inlineStr">
+        <is>
+          <t>随時</t>
+        </is>
+      </c>
+      <c r="J103" s="26" t="n"/>
+      <c r="K103" s="26" t="n"/>
+      <c r="L103" s="26" t="n"/>
+      <c r="M103" s="26" t="n"/>
+      <c r="N103" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" s="23" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="P103" s="25" t="inlineStr"/>
+    </row>
+    <row r="104" ht="30" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>Ⅴ-100</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="inlineStr">
+        <is>
+          <t>Ⅴ 管理</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>Ⅴ-3 進捗管理</t>
+        </is>
+      </c>
+      <c r="D104" s="13" t="inlineStr">
+        <is>
+          <t>進捗管理・課題管理</t>
+        </is>
+      </c>
+      <c r="E104" s="11" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F104" s="11" t="inlineStr">
+        <is>
+          <t>受託者</t>
+        </is>
+      </c>
+      <c r="G104" s="13" t="inlineStr">
+        <is>
+          <t>本進捗管理表</t>
+        </is>
+      </c>
+      <c r="H104" s="13" t="inlineStr"/>
+      <c r="I104" s="11" t="inlineStr">
+        <is>
+          <t>通期</t>
+        </is>
+      </c>
+      <c r="J104" s="14" t="n"/>
+      <c r="K104" s="14" t="n"/>
+      <c r="L104" s="14" t="n">
+        <v>46265</v>
+      </c>
+      <c r="M104" s="14" t="n"/>
+      <c r="N104" s="15" t="n">
         <v>0.35</v>
       </c>
-      <c r="O101" s="16" t="inlineStr">
+      <c r="O104" s="16" t="inlineStr">
         <is>
           <t>着手</t>
         </is>
       </c>
-      <c r="P101" s="13" t="inlineStr">
+      <c r="P104" s="13" t="inlineStr">
         <is>
           <t>本表で管理。基準日 令和8年9月2日。村への確認事項71件（解決済6件）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P101"/>
+  <autoFilter ref="A4:P104"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="O5:O101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O5:O104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未着手,着手,確認中,完了,保留,対象外"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"受託者,北塩原村,双方"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6801,7 +7054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6824,7 +7077,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>優先度S＝キックオフ会議（令和8年9月1日）で決着が必要（9月9日の入稿・9月中旬の発送を守るため）／A＝令和8年9月中に確定が必要／B＝第1回策定委員会（11月）まで／C＝第2回以降　｜　出所の doc番号は docs/北塩原村_第10期/ 配下の分析資料に対応します</t>
+          <t>優先度S＝9月3日の調査票第1稿提出・9月9日の校了・9月18日の発送を守るために決着が必要（キックオフ議事録で未決着のもの）／A＝令和8年9月中に確定が必要／B＝第1回策定委員会（11月）まで／C＝第2回以降　｜　出所の doc番号は docs/北塩原村_第10期/ 配下の分析資料に対応します</t>
         </is>
       </c>
     </row>
@@ -6871,2950 +7124,3330 @@
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>スケジュール</t>
         </is>
       </c>
-      <c r="C5" s="31" t="inlineStr">
+      <c r="C5" s="34" t="inlineStr">
         <is>
           <t>対象者抽出・宛名ラベル・配布用封筒の提供時期</t>
         </is>
       </c>
-      <c r="D5" s="31" t="inlineStr">
+      <c r="D5" s="34" t="inlineStr">
         <is>
           <t>村作業が遅れると発送が連鎖的に遅れる。9/19〜23が5連休。</t>
         </is>
       </c>
-      <c r="E5" s="32" t="inlineStr">
+      <c r="E5" s="35" t="inlineStr">
         <is>
           <t>Ⅰ-24,Ⅰ-25,Ⅰ-26</t>
         </is>
       </c>
-      <c r="F5" s="32" t="inlineStr">
+      <c r="F5" s="35" t="inlineStr">
         <is>
           <t>doc01-4</t>
         </is>
       </c>
-      <c r="G5" s="32" t="inlineStr">
+      <c r="G5" s="35" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H5" s="31" t="inlineStr"/>
+      <c r="H5" s="34" t="inlineStr"/>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="32" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>スケジュール</t>
         </is>
       </c>
-      <c r="C6" s="31" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>宛名ラベル・配布用封筒の提供期限の前倒し可否（9/14→9/11）</t>
         </is>
       </c>
-      <c r="D6" s="31" t="inlineStr">
+      <c r="D6" s="34" t="inlineStr">
         <is>
           <t>★提供が1日遅れると発送が5連休に食い込む。村作業の遅延に対する余裕がない。</t>
         </is>
       </c>
-      <c r="E6" s="32" t="inlineStr">
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>Ⅰ-25,Ⅰ-26</t>
         </is>
       </c>
-      <c r="F6" s="32" t="inlineStr">
+      <c r="F6" s="35" t="inlineStr">
         <is>
           <t>doc19 指-2</t>
         </is>
       </c>
-      <c r="G6" s="32" t="inlineStr">
+      <c r="G6" s="35" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H6" s="31" t="inlineStr"/>
+      <c r="H6" s="34" t="inlineStr"/>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>スケジュール</t>
+        </is>
+      </c>
+      <c r="C7" s="34" t="inlineStr">
+        <is>
+          <t>★策定委員会 現委員の任期満了（令和8年9月30日）と改選手続きの所要期間</t>
+        </is>
+      </c>
+      <c r="D7" s="34" t="inlineStr">
+        <is>
+          <t>★議事録で触れられていない。第2回を11月に開催するには10月中の改選・委嘱が必要。</t>
+        </is>
+      </c>
+      <c r="E7" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-102</t>
+        </is>
+      </c>
+      <c r="F7" s="35" t="inlineStr">
+        <is>
+          <t>doc22 K-76</t>
+        </is>
+      </c>
+      <c r="G7" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H7" s="34" t="inlineStr"/>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>分析</t>
+        </is>
+      </c>
+      <c r="C8" s="34" t="inlineStr">
+        <is>
+          <t>★ICFを用いたクロス分析の具体的な期待像（軸・アウトプットのイメージ）</t>
+        </is>
+      </c>
+      <c r="D8" s="34" t="inlineStr">
+        <is>
+          <t>★議事録の新規要件。「元気な高齢者」×「地域のニーズ」で共助・互助の必要性を示す分析。調査票の設計段階でクロス軸を確保しないと後から分析できない。9/3の第1稿に影響。</t>
+        </is>
+      </c>
+      <c r="E8" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-50</t>
+        </is>
+      </c>
+      <c r="F8" s="35" t="inlineStr">
+        <is>
+          <t>doc22 K-77</t>
+        </is>
+      </c>
+      <c r="G8" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H8" s="34" t="inlineStr"/>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>方針</t>
+        </is>
+      </c>
+      <c r="C9" s="34" t="inlineStr">
+        <is>
+          <t>★基金取崩額の確認（第9期計画の24,000,000円と議事録の「800万円程度」の関係。年額か期間合計か）</t>
+        </is>
+      </c>
+      <c r="D9" s="34" t="inlineStr">
+        <is>
+          <t>★保険料試算の前提が3倍変わる。議事録で基金取崩を視野に入れる方針が示されたため、正確な残高と取崩実績の確認が必須。</t>
+        </is>
+      </c>
+      <c r="E9" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-63,Ⅱ-64</t>
+        </is>
+      </c>
+      <c r="F9" s="35" t="inlineStr">
+        <is>
+          <t>doc22 K-74</t>
+        </is>
+      </c>
+      <c r="G9" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H9" s="34" t="inlineStr"/>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C7" s="31" t="inlineStr">
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t>在宅介護実態調査の手法（手法Ⅲか、手法Ⅳ〈新版 在宅生活改善調査〉を加えるか）</t>
         </is>
       </c>
-      <c r="D7" s="31" t="inlineStr">
+      <c r="D10" s="34" t="inlineStr">
         <is>
           <t>調査票の設計・印刷頁数・集計方法がすべて決まる。第10期の新設手法。</t>
         </is>
       </c>
-      <c r="E7" s="32" t="inlineStr">
+      <c r="E10" s="35" t="inlineStr">
         <is>
           <t>Ⅰ-07,Ⅰ-10</t>
         </is>
       </c>
-      <c r="F7" s="32" t="inlineStr">
+      <c r="F10" s="35" t="inlineStr">
         <is>
           <t>doc03/doc05</t>
         </is>
       </c>
-      <c r="G7" s="32" t="inlineStr">
+      <c r="G10" s="35" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H7" s="31" t="inlineStr"/>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="H10" s="34" t="inlineStr"/>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
+      <c r="C11" s="34" t="inlineStr">
         <is>
           <t>ニーズ調査 約850人の抽出基準（要支援認定者を含むか／第9期との対比）</t>
         </is>
       </c>
-      <c r="D8" s="31" t="inlineStr">
-        <is>
-          <t>対象者数が確定しないと印刷部数・郵送費が固まらない。</t>
-        </is>
-      </c>
-      <c r="E8" s="32" t="inlineStr">
+      <c r="D11" s="34" t="inlineStr">
+        <is>
+          <t>議事録で在宅150件は「要支援1・2および要介護1〜5の在宅生活者等」と決着。ニーズ約850件の抽出基準（要支援を含むか）は未決着のため残置。</t>
+        </is>
+      </c>
+      <c r="E11" s="35" t="inlineStr">
         <is>
           <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
-      <c r="F8" s="32" t="inlineStr">
-        <is>
-          <t>doc01-2,3</t>
-        </is>
-      </c>
-      <c r="G8" s="32" t="inlineStr">
+      <c r="F11" s="35" t="inlineStr">
+        <is>
+          <t>doc01-2,3／doc22</t>
+        </is>
+      </c>
+      <c r="G11" s="35" t="inlineStr">
+        <is>
+          <t>一部回答</t>
+        </is>
+      </c>
+      <c r="H11" s="34" t="inlineStr"/>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C12" s="34" t="inlineStr">
+        <is>
+          <t>オプション項目の採否（「問6 就労について」ほか）</t>
+        </is>
+      </c>
+      <c r="D12" s="34" t="inlineStr">
+        <is>
+          <t>令和7年8月版で就労はオプションと確定。採否で頁数が変わる。</t>
+        </is>
+      </c>
+      <c r="E12" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-12</t>
+        </is>
+      </c>
+      <c r="F12" s="35" t="inlineStr">
+        <is>
+          <t>doc05</t>
+        </is>
+      </c>
+      <c r="G12" s="35" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H8" s="31" t="inlineStr"/>
-    </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="H12" s="34" t="inlineStr"/>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B9" s="30" t="inlineStr">
+      <c r="B13" s="33" t="inlineStr">
         <is>
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C9" s="31" t="inlineStr">
-        <is>
-          <t>在宅介護実態調査 約150人の抽出基準（要支援を含むか／施設入所者の除外方法）</t>
-        </is>
-      </c>
-      <c r="D9" s="31" t="inlineStr">
-        <is>
-          <t>同上。手法Ⅲの対象定義に直結。</t>
-        </is>
-      </c>
-      <c r="E9" s="32" t="inlineStr">
-        <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
-        </is>
-      </c>
-      <c r="F9" s="32" t="inlineStr">
-        <is>
-          <t>doc01-2</t>
-        </is>
-      </c>
-      <c r="G9" s="32" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
+        <is>
+          <t>村独自設問の採否（除雪・在宅医療・成年後見・歯科受診・服薬ほか）</t>
+        </is>
+      </c>
+      <c r="D13" s="34" t="inlineStr">
+        <is>
+          <t>第9期との時系列比較を優先するか、新規論点を入れるかの判断。</t>
+        </is>
+      </c>
+      <c r="E13" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-13</t>
+        </is>
+      </c>
+      <c r="F13" s="35" t="inlineStr">
+        <is>
+          <t>doc03</t>
+        </is>
+      </c>
+      <c r="G13" s="35" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H9" s="31" t="inlineStr"/>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="H13" s="34" t="inlineStr"/>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B14" s="33" t="inlineStr">
         <is>
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
-        <is>
-          <t>オプション項目の採否（「問6 就労について」ほか）</t>
-        </is>
-      </c>
-      <c r="D10" s="31" t="inlineStr">
-        <is>
-          <t>令和7年8月版で就労はオプションと確定。採否で頁数が変わる。</t>
-        </is>
-      </c>
-      <c r="E10" s="32" t="inlineStr">
-        <is>
-          <t>Ⅰ-12</t>
-        </is>
-      </c>
-      <c r="F10" s="32" t="inlineStr">
-        <is>
-          <t>doc05</t>
-        </is>
-      </c>
-      <c r="G10" s="32" t="inlineStr">
+      <c r="C14" s="34" t="inlineStr">
+        <is>
+          <t>ウェブ回答フォームの仕様（回答期限・村HP掲載の有無・二次元コード印字位置）</t>
+        </is>
+      </c>
+      <c r="D14" s="34" t="inlineStr">
+        <is>
+          <t>入稿データ作成の前提。</t>
+        </is>
+      </c>
+      <c r="E14" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-16,Ⅰ-17</t>
+        </is>
+      </c>
+      <c r="F14" s="35" t="inlineStr">
+        <is>
+          <t>doc01-8</t>
+        </is>
+      </c>
+      <c r="G14" s="35" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H10" s="31" t="inlineStr"/>
-    </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="H14" s="34" t="inlineStr"/>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B11" s="30" t="inlineStr">
+      <c r="B15" s="33" t="inlineStr">
         <is>
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C11" s="31" t="inlineStr">
-        <is>
-          <t>村独自設問の採否（除雪・在宅医療・成年後見・歯科受診・服薬ほか）</t>
-        </is>
-      </c>
-      <c r="D11" s="31" t="inlineStr">
-        <is>
-          <t>第9期との時系列比較を優先するか、新規論点を入れるかの判断。</t>
-        </is>
-      </c>
-      <c r="E11" s="32" t="inlineStr">
-        <is>
-          <t>Ⅰ-13</t>
-        </is>
-      </c>
-      <c r="F11" s="32" t="inlineStr">
-        <is>
-          <t>doc03</t>
-        </is>
-      </c>
-      <c r="G11" s="32" t="inlineStr">
+      <c r="C15" s="34" t="inlineStr">
+        <is>
+          <t>★発送日の確定（9/17前倒し／9/18のまま／9/24後ろ倒し）と回収期限</t>
+        </is>
+      </c>
+      <c r="D15" s="34" t="inlineStr">
+        <is>
+          <t>★議事録は「9月18日頃」とするのみで、5連休の論点に触れていない。9/17（木）への前倒し可否と回収期限を9/3の第1稿提出時に併せて提起する。</t>
+        </is>
+      </c>
+      <c r="E15" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-29,Ⅰ-32</t>
+        </is>
+      </c>
+      <c r="F15" s="35" t="inlineStr">
+        <is>
+          <t>doc19 指-1／doc22 A-4</t>
+        </is>
+      </c>
+      <c r="G15" s="35" t="inlineStr">
+        <is>
+          <t>再提起</t>
+        </is>
+      </c>
+      <c r="H15" s="34" t="inlineStr"/>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C16" s="34" t="inlineStr">
+        <is>
+          <t>★ウェブ回答フォームにGoogleフォームを用いることの可否</t>
+        </is>
+      </c>
+      <c r="D16" s="34" t="inlineStr">
+        <is>
+          <t>★通信の暗号化とデータの保存先は別の論点。回答データが村外サーバに保存される。個人情報保護条例上の取扱いと、重複排除の実装・エクスポート後の元データ削除・公開期間管理の確認が必要。</t>
+        </is>
+      </c>
+      <c r="E16" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-16,Ⅰ-18</t>
+        </is>
+      </c>
+      <c r="F16" s="35" t="inlineStr">
+        <is>
+          <t>doc19 追-3</t>
+        </is>
+      </c>
+      <c r="G16" s="35" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H11" s="31" t="inlineStr"/>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="H16" s="34" t="inlineStr"/>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="32" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B12" s="30" t="inlineStr">
+      <c r="B17" s="33" t="inlineStr">
         <is>
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C12" s="31" t="inlineStr">
+      <c r="C17" s="34" t="inlineStr">
+        <is>
+          <t>調査票の印刷頁数の調整方針（仕様書はニーズ約12頁／在宅約8頁）</t>
+        </is>
+      </c>
+      <c r="D17" s="34" t="inlineStr">
+        <is>
+          <t>現在の調査票案は設問数が多く、レイアウト調整か設問の絞り込みが必要になる可能性。オプション項目の採否と一体。</t>
+        </is>
+      </c>
+      <c r="E17" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-20,Ⅰ-21</t>
+        </is>
+      </c>
+      <c r="F17" s="35" t="inlineStr">
+        <is>
+          <t>doc19 S-5</t>
+        </is>
+      </c>
+      <c r="G17" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H17" s="34" t="inlineStr"/>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B18" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C18" s="34" t="inlineStr">
+        <is>
+          <t>依頼状の差出人名義（村名義／村長名）</t>
+        </is>
+      </c>
+      <c r="D18" s="34" t="inlineStr">
+        <is>
+          <t>障がい福祉計画は村名義。回収率に影響し得るため村長名を推奨するが村の慣行による。</t>
+        </is>
+      </c>
+      <c r="E18" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-14</t>
+        </is>
+      </c>
+      <c r="F18" s="35" t="inlineStr">
+        <is>
+          <t>doc19 追-4</t>
+        </is>
+      </c>
+      <c r="G18" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H18" s="34" t="inlineStr"/>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C19" s="34" t="inlineStr">
+        <is>
+          <t>調査票の印刷部数（予備を何部見込むか）</t>
+        </is>
+      </c>
+      <c r="D19" s="34" t="inlineStr">
+        <is>
+          <t>約1,000部＋予備。発送後の追加印刷は工程上困難。</t>
+        </is>
+      </c>
+      <c r="E19" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-21,Ⅰ-22</t>
+        </is>
+      </c>
+      <c r="F19" s="35" t="inlineStr">
+        <is>
+          <t>doc19 追-5</t>
+        </is>
+      </c>
+      <c r="G19" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H19" s="34" t="inlineStr"/>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B20" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C20" s="34" t="inlineStr">
+        <is>
+          <t>在宅介護実態調査 問8・問9の基準月</t>
+        </is>
+      </c>
+      <c r="D20" s="34" t="inlineStr">
+        <is>
+          <t>発送月の前月が通常。発送日の確定とセット。</t>
+        </is>
+      </c>
+      <c r="E20" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F20" s="35" t="inlineStr">
+        <is>
+          <t>doc19 追-2</t>
+        </is>
+      </c>
+      <c r="G20" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H20" s="34" t="inlineStr"/>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C21" s="34" t="inlineStr">
+        <is>
+          <t>★給付費適正化「主要3事業の全て実施」が令和7年度6点→令和8年度0点に低下した理由</t>
+        </is>
+      </c>
+      <c r="D21" s="34" t="inlineStr">
+        <is>
+          <t>★全国該当率96.9%の指標。縦覧点検は4帳票満点のため、①要介護認定の適正化 か ②ケアプラン等の点検 のいずれかが実施されなくなった可能性。取組の後退か調査票の記載漏れかで対応が変わる。</t>
+        </is>
+      </c>
+      <c r="E21" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F21" s="35" t="inlineStr">
+        <is>
+          <t>doc20§8-2 K-61</t>
+        </is>
+      </c>
+      <c r="G21" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H21" s="34" t="inlineStr"/>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C22" s="34" t="inlineStr">
+        <is>
+          <t>★福祉用具購入費・住宅改修費へのリハビリ専門職の関与（配点8点）が令和7年度8点→令和8年度0点に低下した理由</t>
+        </is>
+      </c>
+      <c r="D22" s="34" t="inlineStr">
+        <is>
+          <t>★アと合わせ14点が1年で失われている。仕組みが失われたのか調査票の記載によるものかを確認。</t>
+        </is>
+      </c>
+      <c r="E22" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F22" s="35" t="inlineStr">
+        <is>
+          <t>doc20§8-2 K-61b</t>
+        </is>
+      </c>
+      <c r="G22" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H22" s="34" t="inlineStr"/>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C23" s="34" t="inlineStr">
+        <is>
+          <t>認知症サポーター養成数・認知症地域支援推進員の配置と活動内容・チームオレンジの整備予定</t>
+        </is>
+      </c>
+      <c r="D23" s="34" t="inlineStr">
+        <is>
+          <t>★支援交付金目標Ⅱ（認知症総合支援）は32/100点で全国平均51.1点を19点下回る唯一の目標。3か年で唯一低下局面があった。</t>
+        </is>
+      </c>
+      <c r="E23" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-68</t>
+        </is>
+      </c>
+      <c r="F23" s="35" t="inlineStr">
+        <is>
+          <t>doc20§6-2 K-62</t>
+        </is>
+      </c>
+      <c r="G23" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H23" s="34" t="inlineStr"/>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C24" s="34" t="inlineStr">
+        <is>
+          <t>難聴高齢者の早期発見・早期介入の取組（健診での聴力チェック等）の有無</t>
+        </is>
+      </c>
+      <c r="D24" s="34" t="inlineStr">
+        <is>
+          <t>令和8年度評価で配点10点が0点（全国該当率48.8〜68.9%）。保健事業との連携で取得可能。</t>
+        </is>
+      </c>
+      <c r="E24" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-68</t>
+        </is>
+      </c>
+      <c r="F24" s="35" t="inlineStr">
+        <is>
+          <t>doc20§6-2 K-63</t>
+        </is>
+      </c>
+      <c r="G24" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H24" s="34" t="inlineStr"/>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C25" s="34" t="inlineStr">
+        <is>
+          <t>在宅医療・介護連携推進事業の実施体制（村単独か会津圏域か）と課題・対応策の検討の場</t>
+        </is>
+      </c>
+      <c r="D25" s="34" t="inlineStr">
+        <is>
+          <t>支援交付金目標Ⅲの「課題・対応策の検討」ア・エが0点（配点計10点、全国該当率57〜72%）。</t>
+        </is>
+      </c>
+      <c r="E25" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-54</t>
+        </is>
+      </c>
+      <c r="F25" s="35" t="inlineStr">
+        <is>
+          <t>doc20§6-2 K-64</t>
+        </is>
+      </c>
+      <c r="G25" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H25" s="34" t="inlineStr"/>
+    </row>
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B26" s="33" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C26" s="34" t="inlineStr">
+        <is>
+          <t>★施設サービスが伸びない要因「重度化による病院への転院」の裏づけデータ</t>
+        </is>
+      </c>
+      <c r="D26" s="34" t="inlineStr">
+        <is>
+          <t>★議事録で示された村の見解。当方は村内施設ゼロ・村外施設依存の文脈で解釈していたため、素案の記述を修正する必要がある。KDB・給付実績で確認したい。</t>
+        </is>
+      </c>
+      <c r="E26" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-55</t>
+        </is>
+      </c>
+      <c r="F26" s="35" t="inlineStr">
+        <is>
+          <t>doc22 K-75</t>
+        </is>
+      </c>
+      <c r="G26" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H26" s="34" t="inlineStr"/>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B27" s="33" t="inlineStr">
+        <is>
+          <t>体制</t>
+        </is>
+      </c>
+      <c r="C27" s="34" t="inlineStr">
+        <is>
+          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
+        </is>
+      </c>
+      <c r="D27" s="34" t="inlineStr">
+        <is>
+          <t>連絡体制表の確定。第9期概要版の発行は住民課。</t>
+        </is>
+      </c>
+      <c r="E27" s="35" t="inlineStr">
+        <is>
+          <t>０-04</t>
+        </is>
+      </c>
+      <c r="F27" s="35" t="inlineStr">
+        <is>
+          <t>doc01-1</t>
+        </is>
+      </c>
+      <c r="G27" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H27" s="34" t="inlineStr"/>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B28" s="33" t="inlineStr">
+        <is>
+          <t>体制</t>
+        </is>
+      </c>
+      <c r="C28" s="34" t="inlineStr">
+        <is>
+          <t>契約締結日・契約書の取り交わし状況</t>
+        </is>
+      </c>
+      <c r="D28" s="34" t="inlineStr">
+        <is>
+          <t>業務開始日の確定。</t>
+        </is>
+      </c>
+      <c r="E28" s="35" t="inlineStr">
+        <is>
+          <t>０-02</t>
+        </is>
+      </c>
+      <c r="F28" s="35" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G28" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H28" s="34" t="inlineStr"/>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B29" s="33" t="inlineStr">
+        <is>
+          <t>体制</t>
+        </is>
+      </c>
+      <c r="C29" s="34" t="inlineStr">
+        <is>
+          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
+        </is>
+      </c>
+      <c r="D29" s="34" t="inlineStr">
+        <is>
+          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
+        </is>
+      </c>
+      <c r="E29" s="35" t="inlineStr">
+        <is>
+          <t>０-06</t>
+        </is>
+      </c>
+      <c r="F29" s="35" t="inlineStr">
+        <is>
+          <t>doc19 追-12</t>
+        </is>
+      </c>
+      <c r="G29" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H29" s="34" t="inlineStr"/>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t>体制</t>
+        </is>
+      </c>
+      <c r="C30" s="34" t="inlineStr">
+        <is>
+          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
+        </is>
+      </c>
+      <c r="D30" s="34" t="inlineStr">
+        <is>
+          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
+        </is>
+      </c>
+      <c r="E30" s="35" t="inlineStr">
+        <is>
+          <t>Ⅴ-96</t>
+        </is>
+      </c>
+      <c r="F30" s="35" t="inlineStr">
+        <is>
+          <t>doc22 K-78</t>
+        </is>
+      </c>
+      <c r="G30" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H30" s="34" t="inlineStr"/>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B31" s="33" t="inlineStr">
+        <is>
+          <t>委員会</t>
+        </is>
+      </c>
+      <c r="C31" s="34" t="inlineStr">
+        <is>
+          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
+        </is>
+      </c>
+      <c r="D31" s="34" t="inlineStr">
+        <is>
+          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
+        </is>
+      </c>
+      <c r="E31" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-80,Ⅱ-81</t>
+        </is>
+      </c>
+      <c r="F31" s="35" t="inlineStr">
+        <is>
+          <t>doc01-6,doc19 追-15</t>
+        </is>
+      </c>
+      <c r="G31" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H31" s="34" t="inlineStr"/>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B32" s="33" t="inlineStr">
+        <is>
+          <t>成果品</t>
+        </is>
+      </c>
+      <c r="C32" s="34" t="inlineStr">
+        <is>
+          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
+        </is>
+      </c>
+      <c r="D32" s="34" t="inlineStr">
+        <is>
+          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
+        </is>
+      </c>
+      <c r="E32" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-76,Ⅱ-77</t>
+        </is>
+      </c>
+      <c r="F32" s="35" t="inlineStr">
+        <is>
+          <t>doc01-7,doc19 指-3</t>
+        </is>
+      </c>
+      <c r="G32" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H32" s="34" t="inlineStr"/>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B33" s="33" t="inlineStr">
+        <is>
+          <t>成果品</t>
+        </is>
+      </c>
+      <c r="C33" s="34" t="inlineStr">
+        <is>
+          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
+        </is>
+      </c>
+      <c r="D33" s="34" t="inlineStr">
+        <is>
+          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
+        </is>
+      </c>
+      <c r="E33" s="35" t="inlineStr">
+        <is>
+          <t>Ⅳ-92</t>
+        </is>
+      </c>
+      <c r="F33" s="35" t="inlineStr">
+        <is>
+          <t>doc22 K-79</t>
+        </is>
+      </c>
+      <c r="G33" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H33" s="34" t="inlineStr"/>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B34" s="33" t="inlineStr">
+        <is>
+          <t>方針</t>
+        </is>
+      </c>
+      <c r="C34" s="34" t="inlineStr">
+        <is>
+          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
+        </is>
+      </c>
+      <c r="D34" s="34" t="inlineStr">
+        <is>
+          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
+        </is>
+      </c>
+      <c r="E34" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F34" s="35" t="inlineStr">
+        <is>
+          <t>doc20§6-2 K-66</t>
+        </is>
+      </c>
+      <c r="G34" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H34" s="34" t="inlineStr"/>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B35" s="33" t="inlineStr">
+        <is>
+          <t>方針</t>
+        </is>
+      </c>
+      <c r="C35" s="34" t="inlineStr">
+        <is>
+          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
+        </is>
+      </c>
+      <c r="D35" s="34" t="inlineStr">
+        <is>
+          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
+        </is>
+      </c>
+      <c r="E35" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-62</t>
+        </is>
+      </c>
+      <c r="F35" s="35" t="inlineStr">
+        <is>
+          <t>doc22 K-81</t>
+        </is>
+      </c>
+      <c r="G35" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H35" s="34" t="inlineStr"/>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B36" s="33" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C36" s="34" t="inlineStr">
+        <is>
+          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
+        </is>
+      </c>
+      <c r="D36" s="34" t="inlineStr">
+        <is>
+          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
+        </is>
+      </c>
+      <c r="E36" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F36" s="35" t="inlineStr">
+        <is>
+          <t>doc21§5 K-69</t>
+        </is>
+      </c>
+      <c r="G36" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H36" s="34" t="inlineStr"/>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B37" s="33" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C37" s="34" t="inlineStr">
+        <is>
+          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
+        </is>
+      </c>
+      <c r="D37" s="34" t="inlineStr">
+        <is>
+          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
+        </is>
+      </c>
+      <c r="E37" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F37" s="35" t="inlineStr">
+        <is>
+          <t>doc21§5 K-70</t>
+        </is>
+      </c>
+      <c r="G37" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H37" s="34" t="inlineStr"/>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B38" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C38" s="34" t="inlineStr">
         <is>
           <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
         </is>
       </c>
-      <c r="D12" s="31" t="inlineStr">
-        <is>
-          <t>第10期の新規要件。ラベル発注前に確定が必要。</t>
-        </is>
-      </c>
-      <c r="E12" s="32" t="inlineStr">
+      <c r="D38" s="34" t="inlineStr">
+        <is>
+          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
+        </is>
+      </c>
+      <c r="E38" s="35" t="inlineStr">
         <is>
           <t>Ⅰ-19,Ⅰ-25</t>
         </is>
       </c>
-      <c r="F12" s="32" t="inlineStr">
-        <is>
-          <t>doc01</t>
-        </is>
-      </c>
-      <c r="G12" s="32" t="inlineStr">
+      <c r="F38" s="35" t="inlineStr">
+        <is>
+          <t>doc22 §1</t>
+        </is>
+      </c>
+      <c r="G38" s="35" t="inlineStr">
+        <is>
+          <t>一部回答</t>
+        </is>
+      </c>
+      <c r="H38" s="34" t="inlineStr"/>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C39" s="25" t="inlineStr">
+        <is>
+          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
+        </is>
+      </c>
+      <c r="D39" s="25" t="inlineStr">
+        <is>
+          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
+        </is>
+      </c>
+      <c r="E39" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-63,Ⅱ-64</t>
+        </is>
+      </c>
+      <c r="F39" s="23" t="inlineStr">
+        <is>
+          <t>doc02§22,doc08§8</t>
+        </is>
+      </c>
+      <c r="G39" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H12" s="31" t="inlineStr"/>
-    </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="29" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B13" s="30" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C13" s="31" t="inlineStr">
-        <is>
-          <t>ウェブ回答フォームの仕様（回答期限・村HP掲載の有無・二次元コード印字位置）</t>
-        </is>
-      </c>
-      <c r="D13" s="31" t="inlineStr">
-        <is>
-          <t>入稿データ作成の前提。</t>
-        </is>
-      </c>
-      <c r="E13" s="32" t="inlineStr">
-        <is>
-          <t>Ⅰ-16,Ⅰ-17</t>
-        </is>
-      </c>
-      <c r="F13" s="32" t="inlineStr">
-        <is>
-          <t>doc01-8</t>
-        </is>
-      </c>
-      <c r="G13" s="32" t="inlineStr">
+      <c r="H39" s="25" t="inlineStr"/>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B40" s="24" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C40" s="25" t="inlineStr">
+        <is>
+          <t>令和6年度決算および令和7年度の給付費見込</t>
+        </is>
+      </c>
+      <c r="D40" s="25" t="inlineStr">
+        <is>
+          <t>第9期の計画値と実績の乖離を確定させるために必要。</t>
+        </is>
+      </c>
+      <c r="E40" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-55,Ⅱ-56</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="inlineStr">
+        <is>
+          <t>doc08§8-1</t>
+        </is>
+      </c>
+      <c r="G40" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H13" s="31" t="inlineStr"/>
-    </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="29" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B14" s="30" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C14" s="31" t="inlineStr">
-        <is>
-          <t>★調査の基準日（ニーズ調査・在宅介護実態調査）</t>
-        </is>
-      </c>
-      <c r="D14" s="31" t="inlineStr">
-        <is>
-          <t>資料が空欄。基準日が決まらないと村が対象者を抽出できない。第9期は令和5年8月1日基準。</t>
-        </is>
-      </c>
-      <c r="E14" s="32" t="inlineStr">
-        <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
-        </is>
-      </c>
-      <c r="F14" s="32" t="inlineStr">
-        <is>
-          <t>doc19 追-1</t>
-        </is>
-      </c>
-      <c r="G14" s="32" t="inlineStr">
+      <c r="H40" s="25" t="inlineStr"/>
+    </row>
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B41" s="24" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C41" s="25" t="inlineStr">
+        <is>
+          <t>通いの場の実数（令和3〜7年度）</t>
+        </is>
+      </c>
+      <c r="D41" s="25" t="inlineStr">
+        <is>
+          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。</t>
+        </is>
+      </c>
+      <c r="E41" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F41" s="23" t="inlineStr">
+        <is>
+          <t>doc02§16,§22</t>
+        </is>
+      </c>
+      <c r="G41" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H14" s="31" t="inlineStr"/>
-    </row>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="29" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B15" s="30" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C15" s="31" t="inlineStr">
-        <is>
-          <t>★発送日の確定（9/17前倒し／9/18のまま／9/24後ろ倒し）と回収期限</t>
-        </is>
-      </c>
-      <c r="D15" s="31" t="inlineStr">
-        <is>
-          <t>★9/18は金曜で翌日から9/19〜23の5連休。配達が連休明けにずれる可能性。以降の全工程を左右する。</t>
-        </is>
-      </c>
-      <c r="E15" s="32" t="inlineStr">
-        <is>
-          <t>Ⅰ-29,Ⅰ-32</t>
-        </is>
-      </c>
-      <c r="F15" s="32" t="inlineStr">
-        <is>
-          <t>doc19 指-1</t>
-        </is>
-      </c>
-      <c r="G15" s="32" t="inlineStr">
+      <c r="H41" s="25" t="inlineStr"/>
+    </row>
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B42" s="24" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C42" s="25" t="inlineStr">
+        <is>
+          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
+        </is>
+      </c>
+      <c r="D42" s="25" t="inlineStr">
+        <is>
+          <t>見える化に該当データがない。第9期は基本目標4-4に位置づけ。</t>
+        </is>
+      </c>
+      <c r="E42" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-68,Ⅱ-69</t>
+        </is>
+      </c>
+      <c r="F42" s="23" t="inlineStr">
+        <is>
+          <t>doc08§8-5</t>
+        </is>
+      </c>
+      <c r="G42" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H15" s="31" t="inlineStr"/>
-    </row>
-    <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="29" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B16" s="30" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C16" s="31" t="inlineStr">
-        <is>
-          <t>★ウェブ回答フォームにGoogleフォームを用いることの可否</t>
-        </is>
-      </c>
-      <c r="D16" s="31" t="inlineStr">
-        <is>
-          <t>★通信の暗号化とデータの保存先は別の論点。回答データが村外サーバに保存される。個人情報保護条例上の取扱いと、重複排除の実装・エクスポート後の元データ削除・公開期間管理の確認が必要。</t>
-        </is>
-      </c>
-      <c r="E16" s="32" t="inlineStr">
-        <is>
-          <t>Ⅰ-16,Ⅰ-18</t>
-        </is>
-      </c>
-      <c r="F16" s="32" t="inlineStr">
-        <is>
-          <t>doc19 追-3</t>
-        </is>
-      </c>
-      <c r="G16" s="32" t="inlineStr">
+      <c r="H42" s="25" t="inlineStr"/>
+    </row>
+    <row r="43" ht="34" customHeight="1">
+      <c r="A43" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C43" s="25" t="inlineStr">
+        <is>
+          <t>高齢者福祉事業（村単独事業）の実績資料</t>
+        </is>
+      </c>
+      <c r="D43" s="25" t="inlineStr">
+        <is>
+          <t>現行計画の評価に必要。</t>
+        </is>
+      </c>
+      <c r="E43" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-53,Ⅱ-54</t>
+        </is>
+      </c>
+      <c r="F43" s="23" t="inlineStr">
+        <is>
+          <t>doc01-11</t>
+        </is>
+      </c>
+      <c r="G43" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H16" s="31" t="inlineStr"/>
-    </row>
-    <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="29" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B17" s="30" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C17" s="31" t="inlineStr">
-        <is>
-          <t>調査票の印刷頁数の調整方針（仕様書はニーズ約12頁／在宅約8頁）</t>
-        </is>
-      </c>
-      <c r="D17" s="31" t="inlineStr">
-        <is>
-          <t>現在の調査票案は設問数が多く、レイアウト調整か設問の絞り込みが必要になる可能性。オプション項目の採否と一体。</t>
-        </is>
-      </c>
-      <c r="E17" s="32" t="inlineStr">
-        <is>
-          <t>Ⅰ-20,Ⅰ-21</t>
-        </is>
-      </c>
-      <c r="F17" s="32" t="inlineStr">
-        <is>
-          <t>doc19 S-5</t>
-        </is>
-      </c>
-      <c r="G17" s="32" t="inlineStr">
+      <c r="H43" s="25" t="inlineStr"/>
+    </row>
+    <row r="44" ht="34" customHeight="1">
+      <c r="A44" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C44" s="25" t="inlineStr">
+        <is>
+          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
+        </is>
+      </c>
+      <c r="D44" s="25" t="inlineStr">
+        <is>
+          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
+        </is>
+      </c>
+      <c r="E44" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-58,Ⅱ-59</t>
+        </is>
+      </c>
+      <c r="F44" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-9</t>
+        </is>
+      </c>
+      <c r="G44" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H17" s="31" t="inlineStr"/>
-    </row>
-    <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="29" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B18" s="30" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C18" s="31" t="inlineStr">
-        <is>
-          <t>依頼状の差出人名義（村名義／村長名）</t>
-        </is>
-      </c>
-      <c r="D18" s="31" t="inlineStr">
-        <is>
-          <t>障がい福祉計画は村名義。回収率に影響し得るため村長名を推奨するが村の慣行による。</t>
-        </is>
-      </c>
-      <c r="E18" s="32" t="inlineStr">
-        <is>
-          <t>Ⅰ-14</t>
-        </is>
-      </c>
-      <c r="F18" s="32" t="inlineStr">
-        <is>
-          <t>doc19 追-4</t>
-        </is>
-      </c>
-      <c r="G18" s="32" t="inlineStr">
+      <c r="H44" s="25" t="inlineStr"/>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C45" s="25" t="inlineStr">
+        <is>
+          <t>介護保険事業状況報告（月報・年報）の原データの提供可否</t>
+        </is>
+      </c>
+      <c r="D45" s="25" t="inlineStr">
+        <is>
+          <t>見える化に収録されていない項目（サービス種類別利用者数の月次推移等）が扱えるようになる。</t>
+        </is>
+      </c>
+      <c r="E45" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-55</t>
+        </is>
+      </c>
+      <c r="F45" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-10</t>
+        </is>
+      </c>
+      <c r="G45" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H18" s="31" t="inlineStr"/>
-    </row>
-    <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="29" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B19" s="30" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C19" s="31" t="inlineStr">
-        <is>
-          <t>調査票の印刷部数（予備を何部見込むか）</t>
-        </is>
-      </c>
-      <c r="D19" s="31" t="inlineStr">
-        <is>
-          <t>約1,000部＋予備。発送後の追加印刷は工程上困難。</t>
-        </is>
-      </c>
-      <c r="E19" s="32" t="inlineStr">
-        <is>
-          <t>Ⅰ-21,Ⅰ-22</t>
-        </is>
-      </c>
-      <c r="F19" s="32" t="inlineStr">
-        <is>
-          <t>doc19 追-5</t>
-        </is>
-      </c>
-      <c r="G19" s="32" t="inlineStr">
+      <c r="H45" s="25" t="inlineStr"/>
+    </row>
+    <row r="46" ht="34" customHeight="1">
+      <c r="A46" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B46" s="24" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C46" s="25" t="inlineStr">
+        <is>
+          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
+        </is>
+      </c>
+      <c r="D46" s="25" t="inlineStr">
+        <is>
+          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
+        </is>
+      </c>
+      <c r="E46" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-54</t>
+        </is>
+      </c>
+      <c r="F46" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-11</t>
+        </is>
+      </c>
+      <c r="G46" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H19" s="31" t="inlineStr"/>
-    </row>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="29" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B20" s="30" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C20" s="31" t="inlineStr">
-        <is>
-          <t>在宅介護実態調査 問8・問9の基準月</t>
-        </is>
-      </c>
-      <c r="D20" s="31" t="inlineStr">
-        <is>
-          <t>発送月の前月が通常。発送日の確定とセット。</t>
-        </is>
-      </c>
-      <c r="E20" s="32" t="inlineStr">
-        <is>
-          <t>Ⅰ-10</t>
-        </is>
-      </c>
-      <c r="F20" s="32" t="inlineStr">
-        <is>
-          <t>doc19 追-2</t>
-        </is>
-      </c>
-      <c r="G20" s="32" t="inlineStr">
+      <c r="H46" s="25" t="inlineStr"/>
+    </row>
+    <row r="47" ht="34" customHeight="1">
+      <c r="A47" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C47" s="25" t="inlineStr">
+        <is>
+          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
+        </is>
+      </c>
+      <c r="D47" s="25" t="inlineStr">
+        <is>
+          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
+        </is>
+      </c>
+      <c r="E47" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-53,Ⅱ-54</t>
+        </is>
+      </c>
+      <c r="F47" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-11</t>
+        </is>
+      </c>
+      <c r="G47" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H20" s="31" t="inlineStr"/>
-    </row>
-    <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="33" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B21" s="30" t="inlineStr">
+      <c r="H47" s="25" t="inlineStr"/>
+    </row>
+    <row r="48" ht="34" customHeight="1">
+      <c r="A48" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B48" s="24" t="inlineStr">
         <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="C21" s="31" t="inlineStr">
-        <is>
-          <t>★給付費適正化「主要3事業の全て実施」が令和7年度6点→令和8年度0点に低下した理由</t>
-        </is>
-      </c>
-      <c r="D21" s="31" t="inlineStr">
-        <is>
-          <t>★全国該当率96.9%の指標。縦覧点検は4帳票満点のため、①要介護認定の適正化 か ②ケアプラン等の点検 のいずれかが実施されなくなった可能性。取組の後退か調査票の記載漏れかで対応が変わる。</t>
-        </is>
-      </c>
-      <c r="E21" s="32" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F21" s="32" t="inlineStr">
-        <is>
-          <t>doc20§8-2 K-61</t>
-        </is>
-      </c>
-      <c r="G21" s="32" t="inlineStr">
+      <c r="C48" s="25" t="inlineStr">
+        <is>
+          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
+        </is>
+      </c>
+      <c r="D48" s="25" t="inlineStr">
+        <is>
+          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
+        </is>
+      </c>
+      <c r="E48" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-54</t>
+        </is>
+      </c>
+      <c r="F48" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-11</t>
+        </is>
+      </c>
+      <c r="G48" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H21" s="31" t="inlineStr"/>
-    </row>
-    <row r="22" ht="34" customHeight="1">
-      <c r="A22" s="33" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B22" s="30" t="inlineStr">
+      <c r="H48" s="25" t="inlineStr"/>
+    </row>
+    <row r="49" ht="34" customHeight="1">
+      <c r="A49" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B49" s="24" t="inlineStr">
         <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="C22" s="31" t="inlineStr">
-        <is>
-          <t>★福祉用具購入費・住宅改修費へのリハビリ専門職の関与（配点8点）が令和7年度8点→令和8年度0点に低下した理由</t>
-        </is>
-      </c>
-      <c r="D22" s="31" t="inlineStr">
-        <is>
-          <t>★アと合わせ14点が1年で失われている。仕組みが失われたのか調査票の記載によるものかを確認。</t>
-        </is>
-      </c>
-      <c r="E22" s="32" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F22" s="32" t="inlineStr">
-        <is>
-          <t>doc20§8-2 K-61b</t>
-        </is>
-      </c>
-      <c r="G22" s="32" t="inlineStr">
+      <c r="C49" s="25" t="inlineStr">
+        <is>
+          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
+        </is>
+      </c>
+      <c r="D49" s="25" t="inlineStr">
+        <is>
+          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
+        </is>
+      </c>
+      <c r="E49" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-54</t>
+        </is>
+      </c>
+      <c r="F49" s="23" t="inlineStr">
+        <is>
+          <t>doc20§6-2 K-65</t>
+        </is>
+      </c>
+      <c r="G49" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H22" s="31" t="inlineStr"/>
-    </row>
-    <row r="23" ht="34" customHeight="1">
-      <c r="A23" s="33" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B23" s="30" t="inlineStr">
+      <c r="H49" s="25" t="inlineStr"/>
+    </row>
+    <row r="50" ht="34" customHeight="1">
+      <c r="A50" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B50" s="24" t="inlineStr">
         <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="C23" s="31" t="inlineStr">
-        <is>
-          <t>認知症サポーター養成数・認知症地域支援推進員の配置と活動内容・チームオレンジの整備予定</t>
-        </is>
-      </c>
-      <c r="D23" s="31" t="inlineStr">
-        <is>
-          <t>★支援交付金目標Ⅱ（認知症総合支援）は32/100点で全国平均51.1点を19点下回る唯一の目標。3か年で唯一低下局面があった。</t>
-        </is>
-      </c>
-      <c r="E23" s="32" t="inlineStr">
-        <is>
-          <t>Ⅱ-68</t>
-        </is>
-      </c>
-      <c r="F23" s="32" t="inlineStr">
-        <is>
-          <t>doc20§6-2 K-62</t>
-        </is>
-      </c>
-      <c r="G23" s="32" t="inlineStr">
+      <c r="C50" s="25" t="inlineStr">
+        <is>
+          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
+        </is>
+      </c>
+      <c r="D50" s="25" t="inlineStr">
+        <is>
+          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
+        </is>
+      </c>
+      <c r="E50" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F50" s="23" t="inlineStr">
+        <is>
+          <t>doc21§5 K-68</t>
+        </is>
+      </c>
+      <c r="G50" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H23" s="31" t="inlineStr"/>
-    </row>
-    <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="33" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B24" s="30" t="inlineStr">
+      <c r="H50" s="25" t="inlineStr"/>
+    </row>
+    <row r="51" ht="34" customHeight="1">
+      <c r="A51" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B51" s="24" t="inlineStr">
         <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="C24" s="31" t="inlineStr">
-        <is>
-          <t>難聴高齢者の早期発見・早期介入の取組（健診での聴力チェック等）の有無</t>
-        </is>
-      </c>
-      <c r="D24" s="31" t="inlineStr">
-        <is>
-          <t>令和8年度評価で配点10点が0点（全国該当率48.8〜68.9%）。保健事業との連携で取得可能。</t>
-        </is>
-      </c>
-      <c r="E24" s="32" t="inlineStr">
-        <is>
-          <t>Ⅱ-68</t>
-        </is>
-      </c>
-      <c r="F24" s="32" t="inlineStr">
-        <is>
-          <t>doc20§6-2 K-63</t>
-        </is>
-      </c>
-      <c r="G24" s="32" t="inlineStr">
+      <c r="C51" s="25" t="inlineStr">
+        <is>
+          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
+        </is>
+      </c>
+      <c r="D51" s="25" t="inlineStr">
+        <is>
+          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
+        </is>
+      </c>
+      <c r="E51" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-53</t>
+        </is>
+      </c>
+      <c r="F51" s="23" t="inlineStr">
+        <is>
+          <t>doc21§5 K-71</t>
+        </is>
+      </c>
+      <c r="G51" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H24" s="31" t="inlineStr"/>
-    </row>
-    <row r="25" ht="34" customHeight="1">
-      <c r="A25" s="33" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B25" s="30" t="inlineStr">
+      <c r="H51" s="25" t="inlineStr"/>
+    </row>
+    <row r="52" ht="34" customHeight="1">
+      <c r="A52" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B52" s="24" t="inlineStr">
         <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="C25" s="31" t="inlineStr">
-        <is>
-          <t>在宅医療・介護連携推進事業の実施体制（村単独か会津圏域か）と課題・対応策の検討の場</t>
-        </is>
-      </c>
-      <c r="D25" s="31" t="inlineStr">
-        <is>
-          <t>支援交付金目標Ⅲの「課題・対応策の検討」ア・エが0点（配点計10点、全国該当率57〜72%）。</t>
-        </is>
-      </c>
-      <c r="E25" s="32" t="inlineStr">
+      <c r="C52" s="25" t="inlineStr">
+        <is>
+          <t>シルバー人材センターの会員数・受注実績</t>
+        </is>
+      </c>
+      <c r="D52" s="25" t="inlineStr">
+        <is>
+          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
+        </is>
+      </c>
+      <c r="E52" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-53</t>
+        </is>
+      </c>
+      <c r="F52" s="23" t="inlineStr">
+        <is>
+          <t>doc21§5 K-72</t>
+        </is>
+      </c>
+      <c r="G52" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H52" s="25" t="inlineStr"/>
+    </row>
+    <row r="53" ht="34" customHeight="1">
+      <c r="A53" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B53" s="24" t="inlineStr">
+        <is>
+          <t>体制</t>
+        </is>
+      </c>
+      <c r="C53" s="25" t="inlineStr">
+        <is>
+          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
+        </is>
+      </c>
+      <c r="D53" s="25" t="inlineStr">
+        <is>
+          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
+        </is>
+      </c>
+      <c r="E53" s="23" t="inlineStr">
+        <is>
+          <t>Ⅴ-95</t>
+        </is>
+      </c>
+      <c r="F53" s="23" t="inlineStr">
+        <is>
+          <t>doc20§6-2 K-67</t>
+        </is>
+      </c>
+      <c r="G53" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H53" s="25" t="inlineStr"/>
+    </row>
+    <row r="54" ht="34" customHeight="1">
+      <c r="A54" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B54" s="24" t="inlineStr">
+        <is>
+          <t>成果品</t>
+        </is>
+      </c>
+      <c r="C54" s="25" t="inlineStr">
+        <is>
+          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
+        </is>
+      </c>
+      <c r="D54" s="25" t="inlineStr">
+        <is>
+          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
+        </is>
+      </c>
+      <c r="E54" s="23" t="inlineStr">
+        <is>
+          <t>Ⅳ-92</t>
+        </is>
+      </c>
+      <c r="F54" s="23" t="inlineStr">
+        <is>
+          <t>doc19 指-5</t>
+        </is>
+      </c>
+      <c r="G54" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H54" s="25" t="inlineStr"/>
+    </row>
+    <row r="55" ht="34" customHeight="1">
+      <c r="A55" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B55" s="24" t="inlineStr">
+        <is>
+          <t>成果品</t>
+        </is>
+      </c>
+      <c r="C55" s="25" t="inlineStr">
+        <is>
+          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
+        </is>
+      </c>
+      <c r="D55" s="25" t="inlineStr">
+        <is>
+          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
+        </is>
+      </c>
+      <c r="E55" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-108</t>
+        </is>
+      </c>
+      <c r="F55" s="23" t="inlineStr">
+        <is>
+          <t>doc22 K-80</t>
+        </is>
+      </c>
+      <c r="G55" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H55" s="25" t="inlineStr"/>
+    </row>
+    <row r="56" ht="34" customHeight="1">
+      <c r="A56" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B56" s="24" t="inlineStr">
+        <is>
+          <t>方針</t>
+        </is>
+      </c>
+      <c r="C56" s="25" t="inlineStr">
+        <is>
+          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
+        </is>
+      </c>
+      <c r="D56" s="25" t="inlineStr">
+        <is>
+          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
+        </is>
+      </c>
+      <c r="E56" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-59</t>
+        </is>
+      </c>
+      <c r="F56" s="23" t="inlineStr">
+        <is>
+          <t>doc09§4,§10</t>
+        </is>
+      </c>
+      <c r="G56" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H56" s="25" t="inlineStr"/>
+    </row>
+    <row r="57" ht="34" customHeight="1">
+      <c r="A57" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B57" s="24" t="inlineStr">
+        <is>
+          <t>方針</t>
+        </is>
+      </c>
+      <c r="C57" s="25" t="inlineStr">
+        <is>
+          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
+        </is>
+      </c>
+      <c r="D57" s="25" t="inlineStr">
+        <is>
+          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
+        </is>
+      </c>
+      <c r="E57" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-64</t>
+        </is>
+      </c>
+      <c r="F57" s="23" t="inlineStr">
+        <is>
+          <t>doc09§8,§10</t>
+        </is>
+      </c>
+      <c r="G57" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H57" s="25" t="inlineStr"/>
+    </row>
+    <row r="58" ht="34" customHeight="1">
+      <c r="A58" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B58" s="24" t="inlineStr">
+        <is>
+          <t>方針</t>
+        </is>
+      </c>
+      <c r="C58" s="25" t="inlineStr">
+        <is>
+          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
+        </is>
+      </c>
+      <c r="D58" s="25" t="inlineStr">
+        <is>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
+        </is>
+      </c>
+      <c r="E58" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-67,Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F58" s="23" t="inlineStr">
+        <is>
+          <t>doc02§17,doc07,doc18 4-1</t>
+        </is>
+      </c>
+      <c r="G58" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H58" s="25" t="inlineStr"/>
+    </row>
+    <row r="59" ht="34" customHeight="1">
+      <c r="A59" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B59" s="24" t="inlineStr">
+        <is>
+          <t>方針</t>
+        </is>
+      </c>
+      <c r="C59" s="25" t="inlineStr">
+        <is>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
+        </is>
+      </c>
+      <c r="D59" s="25" t="inlineStr">
+        <is>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
+        </is>
+      </c>
+      <c r="E59" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-56,Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F59" s="23" t="inlineStr">
+        <is>
+          <t>doc17 C-1,doc02§20-2</t>
+        </is>
+      </c>
+      <c r="G59" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H59" s="25" t="inlineStr"/>
+    </row>
+    <row r="60" ht="34" customHeight="1">
+      <c r="A60" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B60" s="24" t="inlineStr">
+        <is>
+          <t>方針</t>
+        </is>
+      </c>
+      <c r="C60" s="25" t="inlineStr">
+        <is>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+        </is>
+      </c>
+      <c r="D60" s="25" t="inlineStr">
+        <is>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+        </is>
+      </c>
+      <c r="E60" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-60,Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F60" s="23" t="inlineStr">
+        <is>
+          <t>doc13§6</t>
+        </is>
+      </c>
+      <c r="G60" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H60" s="25" t="inlineStr"/>
+    </row>
+    <row r="61" ht="34" customHeight="1">
+      <c r="A61" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B61" s="24" t="inlineStr">
+        <is>
+          <t>方針</t>
+        </is>
+      </c>
+      <c r="C61" s="25" t="inlineStr">
+        <is>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+        </is>
+      </c>
+      <c r="D61" s="25" t="inlineStr">
+        <is>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
+        </is>
+      </c>
+      <c r="E61" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-63,Ⅱ-64</t>
+        </is>
+      </c>
+      <c r="F61" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-14</t>
+        </is>
+      </c>
+      <c r="G61" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H61" s="25" t="inlineStr"/>
+    </row>
+    <row r="62" ht="34" customHeight="1">
+      <c r="A62" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B62" s="24" t="inlineStr">
+        <is>
+          <t>方針</t>
+        </is>
+      </c>
+      <c r="C62" s="25" t="inlineStr">
+        <is>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+        </is>
+      </c>
+      <c r="D62" s="25" t="inlineStr">
+        <is>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+        </is>
+      </c>
+      <c r="E62" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-67,Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F62" s="23" t="inlineStr">
+        <is>
+          <t>doc19 §3</t>
+        </is>
+      </c>
+      <c r="G62" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H62" s="25" t="inlineStr"/>
+    </row>
+    <row r="63" ht="34" customHeight="1">
+      <c r="A63" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B63" s="24" t="inlineStr">
+        <is>
+          <t>方針</t>
+        </is>
+      </c>
+      <c r="C63" s="25" t="inlineStr">
+        <is>
+          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
+        </is>
+      </c>
+      <c r="D63" s="25" t="inlineStr">
+        <is>
+          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
+        </is>
+      </c>
+      <c r="E63" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-53</t>
+        </is>
+      </c>
+      <c r="F63" s="23" t="inlineStr">
+        <is>
+          <t>doc21§5 K-73</t>
+        </is>
+      </c>
+      <c r="G63" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H63" s="25" t="inlineStr"/>
+    </row>
+    <row r="64" ht="34" customHeight="1">
+      <c r="A64" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B64" s="24" t="inlineStr">
+        <is>
+          <t>疑義</t>
+        </is>
+      </c>
+      <c r="C64" s="25" t="inlineStr">
+        <is>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+        </is>
+      </c>
+      <c r="D64" s="25" t="inlineStr">
+        <is>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+        </is>
+      </c>
+      <c r="E64" s="23" t="inlineStr">
         <is>
           <t>Ⅱ-54</t>
         </is>
       </c>
-      <c r="F25" s="32" t="inlineStr">
-        <is>
-          <t>doc20§6-2 K-64</t>
-        </is>
-      </c>
-      <c r="G25" s="32" t="inlineStr">
+      <c r="F64" s="23" t="inlineStr">
+        <is>
+          <t>doc07§4</t>
+        </is>
+      </c>
+      <c r="G64" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H25" s="31" t="inlineStr"/>
-    </row>
-    <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="33" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B26" s="30" t="inlineStr">
-        <is>
-          <t>体制</t>
-        </is>
-      </c>
-      <c r="C26" s="31" t="inlineStr">
-        <is>
-          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
-        </is>
-      </c>
-      <c r="D26" s="31" t="inlineStr">
-        <is>
-          <t>連絡体制表の確定。第9期概要版の発行は住民課。</t>
-        </is>
-      </c>
-      <c r="E26" s="32" t="inlineStr">
-        <is>
-          <t>０-04</t>
-        </is>
-      </c>
-      <c r="F26" s="32" t="inlineStr">
-        <is>
-          <t>doc01-1</t>
-        </is>
-      </c>
-      <c r="G26" s="32" t="inlineStr">
+      <c r="H64" s="25" t="inlineStr"/>
+    </row>
+    <row r="65" ht="34" customHeight="1">
+      <c r="A65" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B65" s="24" t="inlineStr">
+        <is>
+          <t>疑義</t>
+        </is>
+      </c>
+      <c r="C65" s="25" t="inlineStr">
+        <is>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+        </is>
+      </c>
+      <c r="D65" s="25" t="inlineStr">
+        <is>
+          <t>評価指標の読み方に影響。</t>
+        </is>
+      </c>
+      <c r="E65" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-54</t>
+        </is>
+      </c>
+      <c r="F65" s="23" t="inlineStr">
+        <is>
+          <t>doc07§8-4</t>
+        </is>
+      </c>
+      <c r="G65" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H26" s="31" t="inlineStr"/>
-    </row>
-    <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="33" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B27" s="30" t="inlineStr">
-        <is>
-          <t>体制</t>
-        </is>
-      </c>
-      <c r="C27" s="31" t="inlineStr">
-        <is>
-          <t>契約締結日・契約書の取り交わし状況</t>
-        </is>
-      </c>
-      <c r="D27" s="31" t="inlineStr">
-        <is>
-          <t>業務開始日の確定。</t>
-        </is>
-      </c>
-      <c r="E27" s="32" t="inlineStr">
-        <is>
-          <t>０-02</t>
-        </is>
-      </c>
-      <c r="F27" s="32" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="G27" s="32" t="inlineStr">
+      <c r="H65" s="25" t="inlineStr"/>
+    </row>
+    <row r="66" ht="34" customHeight="1">
+      <c r="A66" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B66" s="24" t="inlineStr">
+        <is>
+          <t>疑義</t>
+        </is>
+      </c>
+      <c r="C66" s="25" t="inlineStr">
+        <is>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+        </is>
+      </c>
+      <c r="D66" s="25" t="inlineStr">
+        <is>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+        </is>
+      </c>
+      <c r="E66" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-55,Ⅱ-56</t>
+        </is>
+      </c>
+      <c r="F66" s="23" t="inlineStr">
+        <is>
+          <t>doc08§4,§8-2</t>
+        </is>
+      </c>
+      <c r="G66" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H27" s="31" t="inlineStr"/>
-    </row>
-    <row r="28" ht="34" customHeight="1">
-      <c r="A28" s="33" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B28" s="30" t="inlineStr">
-        <is>
-          <t>体制</t>
-        </is>
-      </c>
-      <c r="C28" s="31" t="inlineStr">
-        <is>
-          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
-        </is>
-      </c>
-      <c r="D28" s="31" t="inlineStr">
-        <is>
-          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
-        </is>
-      </c>
-      <c r="E28" s="32" t="inlineStr">
-        <is>
-          <t>０-06</t>
-        </is>
-      </c>
-      <c r="F28" s="32" t="inlineStr">
-        <is>
-          <t>doc19 追-12</t>
-        </is>
-      </c>
-      <c r="G28" s="32" t="inlineStr">
+      <c r="H66" s="25" t="inlineStr"/>
+    </row>
+    <row r="67" ht="34" customHeight="1">
+      <c r="A67" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B67" s="24" t="inlineStr">
+        <is>
+          <t>疑義</t>
+        </is>
+      </c>
+      <c r="C67" s="25" t="inlineStr">
+        <is>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+        </is>
+      </c>
+      <c r="D67" s="25" t="inlineStr">
+        <is>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+        </is>
+      </c>
+      <c r="E67" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-55</t>
+        </is>
+      </c>
+      <c r="F67" s="23" t="inlineStr">
+        <is>
+          <t>doc02§20-1</t>
+        </is>
+      </c>
+      <c r="G67" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H28" s="31" t="inlineStr"/>
-    </row>
-    <row r="29" ht="34" customHeight="1">
-      <c r="A29" s="33" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B29" s="30" t="inlineStr">
-        <is>
-          <t>委員会</t>
-        </is>
-      </c>
-      <c r="C29" s="31" t="inlineStr">
-        <is>
-          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
-        </is>
-      </c>
-      <c r="D29" s="31" t="inlineStr">
-        <is>
-          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
-        </is>
-      </c>
-      <c r="E29" s="32" t="inlineStr">
-        <is>
-          <t>Ⅱ-80,Ⅱ-81</t>
-        </is>
-      </c>
-      <c r="F29" s="32" t="inlineStr">
-        <is>
-          <t>doc01-6,doc19 追-15</t>
-        </is>
-      </c>
-      <c r="G29" s="32" t="inlineStr">
+      <c r="H67" s="25" t="inlineStr"/>
+    </row>
+    <row r="68" ht="34" customHeight="1">
+      <c r="A68" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B68" s="24" t="inlineStr">
+        <is>
+          <t>素案</t>
+        </is>
+      </c>
+      <c r="C68" s="25" t="inlineStr">
+        <is>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+        </is>
+      </c>
+      <c r="D68" s="25" t="inlineStr">
+        <is>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+        </is>
+      </c>
+      <c r="E68" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F68" s="23" t="inlineStr">
+        <is>
+          <t>doc15,doc18</t>
+        </is>
+      </c>
+      <c r="G68" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H29" s="31" t="inlineStr"/>
-    </row>
-    <row r="30" ht="34" customHeight="1">
-      <c r="A30" s="33" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B30" s="30" t="inlineStr">
-        <is>
-          <t>成果品</t>
-        </is>
-      </c>
-      <c r="C30" s="31" t="inlineStr">
-        <is>
-          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
-        </is>
-      </c>
-      <c r="D30" s="31" t="inlineStr">
-        <is>
-          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
-        </is>
-      </c>
-      <c r="E30" s="32" t="inlineStr">
-        <is>
-          <t>Ⅱ-76,Ⅱ-77</t>
-        </is>
-      </c>
-      <c r="F30" s="32" t="inlineStr">
-        <is>
-          <t>doc01-7,doc19 指-3</t>
-        </is>
-      </c>
-      <c r="G30" s="32" t="inlineStr">
+      <c r="H68" s="25" t="inlineStr"/>
+    </row>
+    <row r="69" ht="34" customHeight="1">
+      <c r="A69" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B69" s="24" t="inlineStr">
+        <is>
+          <t>素案</t>
+        </is>
+      </c>
+      <c r="C69" s="25" t="inlineStr">
+        <is>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+        </is>
+      </c>
+      <c r="D69" s="25" t="inlineStr">
+        <is>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+        </is>
+      </c>
+      <c r="E69" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-71,Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F69" s="23" t="inlineStr">
+        <is>
+          <t>doc14§5,doc18 3-1</t>
+        </is>
+      </c>
+      <c r="G69" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H30" s="31" t="inlineStr"/>
-    </row>
-    <row r="31" ht="34" customHeight="1">
-      <c r="A31" s="33" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B31" s="30" t="inlineStr">
-        <is>
-          <t>方針</t>
-        </is>
-      </c>
-      <c r="C31" s="31" t="inlineStr">
-        <is>
-          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
-        </is>
-      </c>
-      <c r="D31" s="31" t="inlineStr">
-        <is>
-          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
-        </is>
-      </c>
-      <c r="E31" s="32" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F31" s="32" t="inlineStr">
-        <is>
-          <t>doc20§6-2 K-66</t>
-        </is>
-      </c>
-      <c r="G31" s="32" t="inlineStr">
+      <c r="H69" s="25" t="inlineStr"/>
+    </row>
+    <row r="70" ht="34" customHeight="1">
+      <c r="A70" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B70" s="24" t="inlineStr">
+        <is>
+          <t>素案</t>
+        </is>
+      </c>
+      <c r="C70" s="25" t="inlineStr">
+        <is>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+        </is>
+      </c>
+      <c r="D70" s="25" t="inlineStr">
+        <is>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+        </is>
+      </c>
+      <c r="E70" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-71,Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F70" s="23" t="inlineStr">
+        <is>
+          <t>doc14§5,doc15,doc18 4-5</t>
+        </is>
+      </c>
+      <c r="G70" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H31" s="31" t="inlineStr"/>
-    </row>
-    <row r="32" ht="34" customHeight="1">
-      <c r="A32" s="33" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B32" s="30" t="inlineStr">
+      <c r="H70" s="25" t="inlineStr"/>
+    </row>
+    <row r="71" ht="34" customHeight="1">
+      <c r="A71" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B71" s="24" t="inlineStr">
+        <is>
+          <t>素案</t>
+        </is>
+      </c>
+      <c r="C71" s="25" t="inlineStr">
+        <is>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+        </is>
+      </c>
+      <c r="D71" s="25" t="inlineStr">
+        <is>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+        </is>
+      </c>
+      <c r="E71" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F71" s="23" t="inlineStr">
+        <is>
+          <t>doc17 B-3,doc18 4-3</t>
+        </is>
+      </c>
+      <c r="G71" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H71" s="25" t="inlineStr"/>
+    </row>
+    <row r="72" ht="34" customHeight="1">
+      <c r="A72" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B72" s="24" t="inlineStr">
+        <is>
+          <t>素案</t>
+        </is>
+      </c>
+      <c r="C72" s="25" t="inlineStr">
+        <is>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+        </is>
+      </c>
+      <c r="D72" s="25" t="inlineStr">
+        <is>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+        </is>
+      </c>
+      <c r="E72" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F72" s="23" t="inlineStr">
+        <is>
+          <t>doc17 A-1,doc18 2-9</t>
+        </is>
+      </c>
+      <c r="G72" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H72" s="25" t="inlineStr"/>
+    </row>
+    <row r="73" ht="34" customHeight="1">
+      <c r="A73" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B73" s="24" t="inlineStr">
+        <is>
+          <t>素案</t>
+        </is>
+      </c>
+      <c r="C73" s="25" t="inlineStr">
+        <is>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+        </is>
+      </c>
+      <c r="D73" s="25" t="inlineStr">
+        <is>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+        </is>
+      </c>
+      <c r="E73" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-64,Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F73" s="23" t="inlineStr">
+        <is>
+          <t>doc17 A-1,doc18 5-7</t>
+        </is>
+      </c>
+      <c r="G73" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H73" s="25" t="inlineStr"/>
+    </row>
+    <row r="74" ht="34" customHeight="1">
+      <c r="A74" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B74" s="24" t="inlineStr">
         <is>
           <t>計画構成</t>
         </is>
       </c>
-      <c r="C32" s="31" t="inlineStr">
-        <is>
-          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
-        </is>
-      </c>
-      <c r="D32" s="31" t="inlineStr">
-        <is>
-          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
-        </is>
-      </c>
-      <c r="E32" s="32" t="inlineStr">
+      <c r="C74" s="25" t="inlineStr">
+        <is>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
+        </is>
+      </c>
+      <c r="D74" s="25" t="inlineStr">
+        <is>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+        </is>
+      </c>
+      <c r="E74" s="23" t="inlineStr">
         <is>
           <t>Ⅱ-72</t>
         </is>
       </c>
-      <c r="F32" s="32" t="inlineStr">
-        <is>
-          <t>doc21§5 K-69</t>
-        </is>
-      </c>
-      <c r="G32" s="32" t="inlineStr">
+      <c r="F74" s="23" t="inlineStr">
+        <is>
+          <t>doc08§8-4</t>
+        </is>
+      </c>
+      <c r="G74" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H32" s="31" t="inlineStr"/>
-    </row>
-    <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="33" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B33" s="30" t="inlineStr">
+      <c r="H74" s="25" t="inlineStr"/>
+    </row>
+    <row r="75" ht="34" customHeight="1">
+      <c r="A75" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B75" s="24" t="inlineStr">
         <is>
           <t>計画構成</t>
         </is>
       </c>
-      <c r="C33" s="31" t="inlineStr">
-        <is>
-          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
-        </is>
-      </c>
-      <c r="D33" s="31" t="inlineStr">
-        <is>
-          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
-        </is>
-      </c>
-      <c r="E33" s="32" t="inlineStr">
+      <c r="C75" s="25" t="inlineStr">
+        <is>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+        </is>
+      </c>
+      <c r="D75" s="25" t="inlineStr">
+        <is>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+        </is>
+      </c>
+      <c r="E75" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-73,Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F75" s="23" t="inlineStr">
+        <is>
+          <t>doc01-5,doc18 1-2</t>
+        </is>
+      </c>
+      <c r="G75" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H75" s="25" t="inlineStr"/>
+    </row>
+    <row r="76" ht="34" customHeight="1">
+      <c r="A76" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B76" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C76" s="25" t="inlineStr">
+        <is>
+          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+        </is>
+      </c>
+      <c r="D76" s="25" t="inlineStr">
+        <is>
+          <t>施策の書きぶりに影響。</t>
+        </is>
+      </c>
+      <c r="E76" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-71,Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F76" s="23" t="inlineStr">
+        <is>
+          <t>doc01-12</t>
+        </is>
+      </c>
+      <c r="G76" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H76" s="25" t="inlineStr"/>
+    </row>
+    <row r="77" ht="34" customHeight="1">
+      <c r="A77" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B77" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C77" s="25" t="inlineStr">
+        <is>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+        </is>
+      </c>
+      <c r="D77" s="25" t="inlineStr">
+        <is>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+        </is>
+      </c>
+      <c r="E77" s="23" t="inlineStr">
         <is>
           <t>Ⅱ-72</t>
         </is>
       </c>
-      <c r="F33" s="32" t="inlineStr">
-        <is>
-          <t>doc21§5 K-70</t>
-        </is>
-      </c>
-      <c r="G33" s="32" t="inlineStr">
+      <c r="F77" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-13</t>
+        </is>
+      </c>
+      <c r="G77" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H33" s="31" t="inlineStr"/>
-    </row>
-    <row r="34" ht="34" customHeight="1">
-      <c r="A34" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B34" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C34" s="25" t="inlineStr">
-        <is>
-          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
-        </is>
-      </c>
-      <c r="D34" s="25" t="inlineStr">
-        <is>
-          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
-        </is>
-      </c>
-      <c r="E34" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F34" s="23" t="inlineStr">
-        <is>
-          <t>doc02§22,doc08§8</t>
-        </is>
-      </c>
-      <c r="G34" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H34" s="25" t="inlineStr"/>
-    </row>
-    <row r="35" ht="34" customHeight="1">
-      <c r="A35" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B35" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C35" s="25" t="inlineStr">
-        <is>
-          <t>令和6年度決算および令和7年度の給付費見込</t>
-        </is>
-      </c>
-      <c r="D35" s="25" t="inlineStr">
-        <is>
-          <t>第9期の計画値と実績の乖離を確定させるために必要。</t>
-        </is>
-      </c>
-      <c r="E35" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
-        </is>
-      </c>
-      <c r="F35" s="23" t="inlineStr">
-        <is>
-          <t>doc08§8-1</t>
-        </is>
-      </c>
-      <c r="G35" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H35" s="25" t="inlineStr"/>
-    </row>
-    <row r="36" ht="34" customHeight="1">
-      <c r="A36" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B36" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C36" s="25" t="inlineStr">
-        <is>
-          <t>通いの場の実数（令和3〜7年度）</t>
-        </is>
-      </c>
-      <c r="D36" s="25" t="inlineStr">
-        <is>
-          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。</t>
-        </is>
-      </c>
-      <c r="E36" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F36" s="23" t="inlineStr">
-        <is>
-          <t>doc02§16,§22</t>
-        </is>
-      </c>
-      <c r="G36" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H36" s="25" t="inlineStr"/>
-    </row>
-    <row r="37" ht="34" customHeight="1">
-      <c r="A37" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B37" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C37" s="25" t="inlineStr">
-        <is>
-          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
-        </is>
-      </c>
-      <c r="D37" s="25" t="inlineStr">
-        <is>
-          <t>見える化に該当データがない。第9期は基本目標4-4に位置づけ。</t>
-        </is>
-      </c>
-      <c r="E37" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-68,Ⅱ-69</t>
-        </is>
-      </c>
-      <c r="F37" s="23" t="inlineStr">
-        <is>
-          <t>doc08§8-5</t>
-        </is>
-      </c>
-      <c r="G37" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H37" s="25" t="inlineStr"/>
-    </row>
-    <row r="38" ht="34" customHeight="1">
-      <c r="A38" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B38" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C38" s="25" t="inlineStr">
-        <is>
-          <t>高齢者福祉事業（村単独事業）の実績資料</t>
-        </is>
-      </c>
-      <c r="D38" s="25" t="inlineStr">
-        <is>
-          <t>現行計画の評価に必要。</t>
-        </is>
-      </c>
-      <c r="E38" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
-        </is>
-      </c>
-      <c r="F38" s="23" t="inlineStr">
-        <is>
-          <t>doc01-11</t>
-        </is>
-      </c>
-      <c r="G38" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H38" s="25" t="inlineStr"/>
-    </row>
-    <row r="39" ht="34" customHeight="1">
-      <c r="A39" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B39" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C39" s="25" t="inlineStr">
-        <is>
-          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
-        </is>
-      </c>
-      <c r="D39" s="25" t="inlineStr">
-        <is>
-          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
-        </is>
-      </c>
-      <c r="E39" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-58,Ⅱ-59</t>
-        </is>
-      </c>
-      <c r="F39" s="23" t="inlineStr">
-        <is>
-          <t>doc19 追-9</t>
-        </is>
-      </c>
-      <c r="G39" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H39" s="25" t="inlineStr"/>
-    </row>
-    <row r="40" ht="34" customHeight="1">
-      <c r="A40" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B40" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C40" s="25" t="inlineStr">
-        <is>
-          <t>介護保険事業状況報告（月報・年報）の原データの提供可否</t>
-        </is>
-      </c>
-      <c r="D40" s="25" t="inlineStr">
-        <is>
-          <t>見える化に収録されていない項目（サービス種類別利用者数の月次推移等）が扱えるようになる。</t>
-        </is>
-      </c>
-      <c r="E40" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-55</t>
-        </is>
-      </c>
-      <c r="F40" s="23" t="inlineStr">
-        <is>
-          <t>doc19 追-10</t>
-        </is>
-      </c>
-      <c r="G40" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H40" s="25" t="inlineStr"/>
-    </row>
-    <row r="41" ht="34" customHeight="1">
-      <c r="A41" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B41" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C41" s="25" t="inlineStr">
-        <is>
-          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
-        </is>
-      </c>
-      <c r="D41" s="25" t="inlineStr">
-        <is>
-          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
-        </is>
-      </c>
-      <c r="E41" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-54</t>
-        </is>
-      </c>
-      <c r="F41" s="23" t="inlineStr">
-        <is>
-          <t>doc19 追-11</t>
-        </is>
-      </c>
-      <c r="G41" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H41" s="25" t="inlineStr"/>
-    </row>
-    <row r="42" ht="34" customHeight="1">
-      <c r="A42" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B42" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C42" s="25" t="inlineStr">
-        <is>
-          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
-        </is>
-      </c>
-      <c r="D42" s="25" t="inlineStr">
-        <is>
-          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
-        </is>
-      </c>
-      <c r="E42" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
-        </is>
-      </c>
-      <c r="F42" s="23" t="inlineStr">
-        <is>
-          <t>doc19 追-11</t>
-        </is>
-      </c>
-      <c r="G42" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H42" s="25" t="inlineStr"/>
-    </row>
-    <row r="43" ht="34" customHeight="1">
-      <c r="A43" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B43" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C43" s="25" t="inlineStr">
-        <is>
-          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
-        </is>
-      </c>
-      <c r="D43" s="25" t="inlineStr">
-        <is>
-          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
-        </is>
-      </c>
-      <c r="E43" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-54</t>
-        </is>
-      </c>
-      <c r="F43" s="23" t="inlineStr">
-        <is>
-          <t>doc19 追-11</t>
-        </is>
-      </c>
-      <c r="G43" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H43" s="25" t="inlineStr"/>
-    </row>
-    <row r="44" ht="34" customHeight="1">
-      <c r="A44" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B44" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C44" s="25" t="inlineStr">
-        <is>
-          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
-        </is>
-      </c>
-      <c r="D44" s="25" t="inlineStr">
-        <is>
-          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
-        </is>
-      </c>
-      <c r="E44" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-54</t>
-        </is>
-      </c>
-      <c r="F44" s="23" t="inlineStr">
-        <is>
-          <t>doc20§6-2 K-65</t>
-        </is>
-      </c>
-      <c r="G44" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H44" s="25" t="inlineStr"/>
-    </row>
-    <row r="45" ht="34" customHeight="1">
-      <c r="A45" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B45" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C45" s="25" t="inlineStr">
-        <is>
-          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
-        </is>
-      </c>
-      <c r="D45" s="25" t="inlineStr">
-        <is>
-          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
-        </is>
-      </c>
-      <c r="E45" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-72</t>
-        </is>
-      </c>
-      <c r="F45" s="23" t="inlineStr">
-        <is>
-          <t>doc21§5 K-68</t>
-        </is>
-      </c>
-      <c r="G45" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H45" s="25" t="inlineStr"/>
-    </row>
-    <row r="46" ht="34" customHeight="1">
-      <c r="A46" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B46" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C46" s="25" t="inlineStr">
-        <is>
-          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
-        </is>
-      </c>
-      <c r="D46" s="25" t="inlineStr">
-        <is>
-          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
-        </is>
-      </c>
-      <c r="E46" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-53</t>
-        </is>
-      </c>
-      <c r="F46" s="23" t="inlineStr">
-        <is>
-          <t>doc21§5 K-71</t>
-        </is>
-      </c>
-      <c r="G46" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H46" s="25" t="inlineStr"/>
-    </row>
-    <row r="47" ht="34" customHeight="1">
-      <c r="A47" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B47" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C47" s="25" t="inlineStr">
-        <is>
-          <t>シルバー人材センターの会員数・受注実績</t>
-        </is>
-      </c>
-      <c r="D47" s="25" t="inlineStr">
-        <is>
-          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
-        </is>
-      </c>
-      <c r="E47" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-53</t>
-        </is>
-      </c>
-      <c r="F47" s="23" t="inlineStr">
-        <is>
-          <t>doc21§5 K-72</t>
-        </is>
-      </c>
-      <c r="G47" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H47" s="25" t="inlineStr"/>
-    </row>
-    <row r="48" ht="34" customHeight="1">
-      <c r="A48" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B48" s="24" t="inlineStr">
-        <is>
-          <t>体制</t>
-        </is>
-      </c>
-      <c r="C48" s="25" t="inlineStr">
-        <is>
-          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
-        </is>
-      </c>
-      <c r="D48" s="25" t="inlineStr">
-        <is>
-          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
-        </is>
-      </c>
-      <c r="E48" s="23" t="inlineStr">
-        <is>
-          <t>Ⅴ-95</t>
-        </is>
-      </c>
-      <c r="F48" s="23" t="inlineStr">
-        <is>
-          <t>doc20§6-2 K-67</t>
-        </is>
-      </c>
-      <c r="G48" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H48" s="25" t="inlineStr"/>
-    </row>
-    <row r="49" ht="34" customHeight="1">
-      <c r="A49" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B49" s="24" t="inlineStr">
-        <is>
-          <t>成果品</t>
-        </is>
-      </c>
-      <c r="C49" s="25" t="inlineStr">
-        <is>
-          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
-        </is>
-      </c>
-      <c r="D49" s="25" t="inlineStr">
-        <is>
-          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
-        </is>
-      </c>
-      <c r="E49" s="23" t="inlineStr">
-        <is>
-          <t>Ⅳ-92</t>
-        </is>
-      </c>
-      <c r="F49" s="23" t="inlineStr">
-        <is>
-          <t>doc19 指-5</t>
-        </is>
-      </c>
-      <c r="G49" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H49" s="25" t="inlineStr"/>
-    </row>
-    <row r="50" ht="34" customHeight="1">
-      <c r="A50" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B50" s="24" t="inlineStr">
-        <is>
-          <t>方針</t>
-        </is>
-      </c>
-      <c r="C50" s="25" t="inlineStr">
-        <is>
-          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
-        </is>
-      </c>
-      <c r="D50" s="25" t="inlineStr">
-        <is>
-          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
-        </is>
-      </c>
-      <c r="E50" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-59</t>
-        </is>
-      </c>
-      <c r="F50" s="23" t="inlineStr">
-        <is>
-          <t>doc09§4,§10</t>
-        </is>
-      </c>
-      <c r="G50" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H50" s="25" t="inlineStr"/>
-    </row>
-    <row r="51" ht="34" customHeight="1">
-      <c r="A51" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B51" s="24" t="inlineStr">
-        <is>
-          <t>方針</t>
-        </is>
-      </c>
-      <c r="C51" s="25" t="inlineStr">
-        <is>
-          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
-        </is>
-      </c>
-      <c r="D51" s="25" t="inlineStr">
-        <is>
-          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
-        </is>
-      </c>
-      <c r="E51" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F51" s="23" t="inlineStr">
-        <is>
-          <t>doc09§8,§10</t>
-        </is>
-      </c>
-      <c r="G51" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H51" s="25" t="inlineStr"/>
-    </row>
-    <row r="52" ht="34" customHeight="1">
-      <c r="A52" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B52" s="24" t="inlineStr">
-        <is>
-          <t>方針</t>
-        </is>
-      </c>
-      <c r="C52" s="25" t="inlineStr">
-        <is>
-          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
-        </is>
-      </c>
-      <c r="D52" s="25" t="inlineStr">
-        <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
-        </is>
-      </c>
-      <c r="E52" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
-        </is>
-      </c>
-      <c r="F52" s="23" t="inlineStr">
-        <is>
-          <t>doc02§17,doc07,doc18 4-1</t>
-        </is>
-      </c>
-      <c r="G52" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H52" s="25" t="inlineStr"/>
-    </row>
-    <row r="53" ht="34" customHeight="1">
-      <c r="A53" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B53" s="24" t="inlineStr">
-        <is>
-          <t>方針</t>
-        </is>
-      </c>
-      <c r="C53" s="25" t="inlineStr">
-        <is>
-          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
-        </is>
-      </c>
-      <c r="D53" s="25" t="inlineStr">
-        <is>
-          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
-        </is>
-      </c>
-      <c r="E53" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-56,Ⅱ-75</t>
-        </is>
-      </c>
-      <c r="F53" s="23" t="inlineStr">
-        <is>
-          <t>doc17 C-1,doc02§20-2</t>
-        </is>
-      </c>
-      <c r="G53" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H53" s="25" t="inlineStr"/>
-    </row>
-    <row r="54" ht="34" customHeight="1">
-      <c r="A54" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B54" s="24" t="inlineStr">
-        <is>
-          <t>方針</t>
-        </is>
-      </c>
-      <c r="C54" s="25" t="inlineStr">
-        <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
-        </is>
-      </c>
-      <c r="D54" s="25" t="inlineStr">
-        <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
-        </is>
-      </c>
-      <c r="E54" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F54" s="23" t="inlineStr">
-        <is>
-          <t>doc13§6</t>
-        </is>
-      </c>
-      <c r="G54" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H54" s="25" t="inlineStr"/>
-    </row>
-    <row r="55" ht="34" customHeight="1">
-      <c r="A55" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B55" s="24" t="inlineStr">
-        <is>
-          <t>方針</t>
-        </is>
-      </c>
-      <c r="C55" s="25" t="inlineStr">
-        <is>
-          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
-        </is>
-      </c>
-      <c r="D55" s="25" t="inlineStr">
-        <is>
-          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
-        </is>
-      </c>
-      <c r="E55" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F55" s="23" t="inlineStr">
-        <is>
-          <t>doc19 追-14</t>
-        </is>
-      </c>
-      <c r="G55" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H55" s="25" t="inlineStr"/>
-    </row>
-    <row r="56" ht="34" customHeight="1">
-      <c r="A56" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B56" s="24" t="inlineStr">
-        <is>
-          <t>方針</t>
-        </is>
-      </c>
-      <c r="C56" s="25" t="inlineStr">
-        <is>
-          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
-        </is>
-      </c>
-      <c r="D56" s="25" t="inlineStr">
-        <is>
-          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
-        </is>
-      </c>
-      <c r="E56" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
-        </is>
-      </c>
-      <c r="F56" s="23" t="inlineStr">
-        <is>
-          <t>doc19 §3</t>
-        </is>
-      </c>
-      <c r="G56" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H56" s="25" t="inlineStr"/>
-    </row>
-    <row r="57" ht="34" customHeight="1">
-      <c r="A57" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B57" s="24" t="inlineStr">
-        <is>
-          <t>方針</t>
-        </is>
-      </c>
-      <c r="C57" s="25" t="inlineStr">
-        <is>
-          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
-        </is>
-      </c>
-      <c r="D57" s="25" t="inlineStr">
-        <is>
-          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
-        </is>
-      </c>
-      <c r="E57" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-53</t>
-        </is>
-      </c>
-      <c r="F57" s="23" t="inlineStr">
-        <is>
-          <t>doc21§5 K-73</t>
-        </is>
-      </c>
-      <c r="G57" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H57" s="25" t="inlineStr"/>
-    </row>
-    <row r="58" ht="34" customHeight="1">
-      <c r="A58" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B58" s="24" t="inlineStr">
-        <is>
-          <t>疑義</t>
-        </is>
-      </c>
-      <c r="C58" s="25" t="inlineStr">
-        <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
-        </is>
-      </c>
-      <c r="D58" s="25" t="inlineStr">
-        <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
-        </is>
-      </c>
-      <c r="E58" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-54</t>
-        </is>
-      </c>
-      <c r="F58" s="23" t="inlineStr">
-        <is>
-          <t>doc07§4</t>
-        </is>
-      </c>
-      <c r="G58" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H58" s="25" t="inlineStr"/>
-    </row>
-    <row r="59" ht="34" customHeight="1">
-      <c r="A59" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B59" s="24" t="inlineStr">
-        <is>
-          <t>疑義</t>
-        </is>
-      </c>
-      <c r="C59" s="25" t="inlineStr">
-        <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
-        </is>
-      </c>
-      <c r="D59" s="25" t="inlineStr">
-        <is>
-          <t>評価指標の読み方に影響。</t>
-        </is>
-      </c>
-      <c r="E59" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-54</t>
-        </is>
-      </c>
-      <c r="F59" s="23" t="inlineStr">
-        <is>
-          <t>doc07§8-4</t>
-        </is>
-      </c>
-      <c r="G59" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H59" s="25" t="inlineStr"/>
-    </row>
-    <row r="60" ht="34" customHeight="1">
-      <c r="A60" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B60" s="24" t="inlineStr">
-        <is>
-          <t>疑義</t>
-        </is>
-      </c>
-      <c r="C60" s="25" t="inlineStr">
-        <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
-        </is>
-      </c>
-      <c r="D60" s="25" t="inlineStr">
-        <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
-        </is>
-      </c>
-      <c r="E60" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
-        </is>
-      </c>
-      <c r="F60" s="23" t="inlineStr">
-        <is>
-          <t>doc08§4,§8-2</t>
-        </is>
-      </c>
-      <c r="G60" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H60" s="25" t="inlineStr"/>
-    </row>
-    <row r="61" ht="34" customHeight="1">
-      <c r="A61" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B61" s="24" t="inlineStr">
-        <is>
-          <t>疑義</t>
-        </is>
-      </c>
-      <c r="C61" s="25" t="inlineStr">
-        <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
-        </is>
-      </c>
-      <c r="D61" s="25" t="inlineStr">
-        <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
-        </is>
-      </c>
-      <c r="E61" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-55</t>
-        </is>
-      </c>
-      <c r="F61" s="23" t="inlineStr">
-        <is>
-          <t>doc02§20-1</t>
-        </is>
-      </c>
-      <c r="G61" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H61" s="25" t="inlineStr"/>
-    </row>
-    <row r="62" ht="34" customHeight="1">
-      <c r="A62" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B62" s="24" t="inlineStr">
-        <is>
-          <t>素案</t>
-        </is>
-      </c>
-      <c r="C62" s="25" t="inlineStr">
-        <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
-        </is>
-      </c>
-      <c r="D62" s="25" t="inlineStr">
-        <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
-        </is>
-      </c>
-      <c r="E62" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-75</t>
-        </is>
-      </c>
-      <c r="F62" s="23" t="inlineStr">
-        <is>
-          <t>doc15,doc18</t>
-        </is>
-      </c>
-      <c r="G62" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H62" s="25" t="inlineStr"/>
-    </row>
-    <row r="63" ht="34" customHeight="1">
-      <c r="A63" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B63" s="24" t="inlineStr">
-        <is>
-          <t>素案</t>
-        </is>
-      </c>
-      <c r="C63" s="25" t="inlineStr">
-        <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
-        </is>
-      </c>
-      <c r="D63" s="25" t="inlineStr">
-        <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
-        </is>
-      </c>
-      <c r="E63" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
-        </is>
-      </c>
-      <c r="F63" s="23" t="inlineStr">
-        <is>
-          <t>doc14§5,doc18 3-1</t>
-        </is>
-      </c>
-      <c r="G63" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H63" s="25" t="inlineStr"/>
-    </row>
-    <row r="64" ht="34" customHeight="1">
-      <c r="A64" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B64" s="24" t="inlineStr">
-        <is>
-          <t>素案</t>
-        </is>
-      </c>
-      <c r="C64" s="25" t="inlineStr">
-        <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
-        </is>
-      </c>
-      <c r="D64" s="25" t="inlineStr">
-        <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
-        </is>
-      </c>
-      <c r="E64" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
-        </is>
-      </c>
-      <c r="F64" s="23" t="inlineStr">
-        <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
-        </is>
-      </c>
-      <c r="G64" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H64" s="25" t="inlineStr"/>
-    </row>
-    <row r="65" ht="34" customHeight="1">
-      <c r="A65" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B65" s="24" t="inlineStr">
-        <is>
-          <t>素案</t>
-        </is>
-      </c>
-      <c r="C65" s="25" t="inlineStr">
-        <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
-        </is>
-      </c>
-      <c r="D65" s="25" t="inlineStr">
-        <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
-        </is>
-      </c>
-      <c r="E65" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-75</t>
-        </is>
-      </c>
-      <c r="F65" s="23" t="inlineStr">
-        <is>
-          <t>doc17 B-3,doc18 4-3</t>
-        </is>
-      </c>
-      <c r="G65" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H65" s="25" t="inlineStr"/>
-    </row>
-    <row r="66" ht="34" customHeight="1">
-      <c r="A66" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B66" s="24" t="inlineStr">
-        <is>
-          <t>素案</t>
-        </is>
-      </c>
-      <c r="C66" s="25" t="inlineStr">
-        <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
-        </is>
-      </c>
-      <c r="D66" s="25" t="inlineStr">
-        <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
-        </is>
-      </c>
-      <c r="E66" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-75</t>
-        </is>
-      </c>
-      <c r="F66" s="23" t="inlineStr">
-        <is>
-          <t>doc17 A-1,doc18 2-9</t>
-        </is>
-      </c>
-      <c r="G66" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H66" s="25" t="inlineStr"/>
-    </row>
-    <row r="67" ht="34" customHeight="1">
-      <c r="A67" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B67" s="24" t="inlineStr">
-        <is>
-          <t>素案</t>
-        </is>
-      </c>
-      <c r="C67" s="25" t="inlineStr">
-        <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
-        </is>
-      </c>
-      <c r="D67" s="25" t="inlineStr">
-        <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
-        </is>
-      </c>
-      <c r="E67" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
-        </is>
-      </c>
-      <c r="F67" s="23" t="inlineStr">
-        <is>
-          <t>doc17 A-1,doc18 5-7</t>
-        </is>
-      </c>
-      <c r="G67" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H67" s="25" t="inlineStr"/>
-    </row>
-    <row r="68" ht="34" customHeight="1">
-      <c r="A68" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B68" s="24" t="inlineStr">
-        <is>
-          <t>計画構成</t>
-        </is>
-      </c>
-      <c r="C68" s="25" t="inlineStr">
-        <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
-        </is>
-      </c>
-      <c r="D68" s="25" t="inlineStr">
-        <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
-        </is>
-      </c>
-      <c r="E68" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-72</t>
-        </is>
-      </c>
-      <c r="F68" s="23" t="inlineStr">
-        <is>
-          <t>doc08§8-4</t>
-        </is>
-      </c>
-      <c r="G68" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H68" s="25" t="inlineStr"/>
-    </row>
-    <row r="69" ht="34" customHeight="1">
-      <c r="A69" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B69" s="24" t="inlineStr">
-        <is>
-          <t>計画構成</t>
-        </is>
-      </c>
-      <c r="C69" s="25" t="inlineStr">
-        <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
-        </is>
-      </c>
-      <c r="D69" s="25" t="inlineStr">
-        <is>
-          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
-        </is>
-      </c>
-      <c r="E69" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-73,Ⅱ-75</t>
-        </is>
-      </c>
-      <c r="F69" s="23" t="inlineStr">
-        <is>
-          <t>doc01-5,doc18 1-2</t>
-        </is>
-      </c>
-      <c r="G69" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H69" s="25" t="inlineStr"/>
-    </row>
-    <row r="70" ht="34" customHeight="1">
-      <c r="A70" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B70" s="24" t="inlineStr">
-        <is>
-          <t>計画構成</t>
-        </is>
-      </c>
-      <c r="C70" s="25" t="inlineStr">
-        <is>
-          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
-        </is>
-      </c>
-      <c r="D70" s="25" t="inlineStr">
-        <is>
-          <t>施策の書きぶりに影響。</t>
-        </is>
-      </c>
-      <c r="E70" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-71,Ⅱ-72</t>
-        </is>
-      </c>
-      <c r="F70" s="23" t="inlineStr">
-        <is>
-          <t>doc01-12</t>
-        </is>
-      </c>
-      <c r="G70" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H70" s="25" t="inlineStr"/>
-    </row>
-    <row r="71" ht="34" customHeight="1">
-      <c r="A71" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B71" s="24" t="inlineStr">
-        <is>
-          <t>計画構成</t>
-        </is>
-      </c>
-      <c r="C71" s="25" t="inlineStr">
-        <is>
-          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
-        </is>
-      </c>
-      <c r="D71" s="25" t="inlineStr">
-        <is>
-          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
-        </is>
-      </c>
-      <c r="E71" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-72</t>
-        </is>
-      </c>
-      <c r="F71" s="23" t="inlineStr">
-        <is>
-          <t>doc19 追-13</t>
-        </is>
-      </c>
-      <c r="G71" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H71" s="25" t="inlineStr"/>
-    </row>
-    <row r="72" ht="34" customHeight="1">
-      <c r="A72" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B72" s="24" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C72" s="25" t="inlineStr">
-        <is>
-          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
-        </is>
-      </c>
-      <c r="D72" s="25" t="inlineStr">
-        <is>
-          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
-        </is>
-      </c>
-      <c r="E72" s="23" t="inlineStr">
-        <is>
-          <t>Ⅰ-31</t>
-        </is>
-      </c>
-      <c r="F72" s="23" t="inlineStr">
-        <is>
-          <t>doc19 追-6</t>
-        </is>
-      </c>
-      <c r="G72" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H72" s="25" t="inlineStr"/>
-    </row>
-    <row r="73" ht="34" customHeight="1">
-      <c r="A73" s="34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B73" s="24" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C73" s="25" t="inlineStr">
-        <is>
-          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
-        </is>
-      </c>
-      <c r="D73" s="25" t="inlineStr">
-        <is>
-          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
-        </is>
-      </c>
-      <c r="E73" s="23" t="inlineStr">
-        <is>
-          <t>Ⅰ-40,Ⅰ-42</t>
-        </is>
-      </c>
-      <c r="F73" s="23" t="inlineStr">
-        <is>
-          <t>doc19 追-7</t>
-        </is>
-      </c>
-      <c r="G73" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H73" s="25" t="inlineStr"/>
-    </row>
-    <row r="74" ht="34" customHeight="1">
-      <c r="A74" s="35" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B74" s="24" t="inlineStr">
-        <is>
-          <t>成果品</t>
-        </is>
-      </c>
-      <c r="C74" s="25" t="inlineStr">
-        <is>
-          <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
-        </is>
-      </c>
-      <c r="D74" s="25" t="inlineStr">
-        <is>
-          <t>第9期はA4・本文104頁・全6章＋資料編。</t>
-        </is>
-      </c>
-      <c r="E74" s="23" t="inlineStr">
-        <is>
-          <t>Ⅳ-89</t>
-        </is>
-      </c>
-      <c r="F74" s="23" t="inlineStr">
-        <is>
-          <t>doc01-10</t>
-        </is>
-      </c>
-      <c r="G74" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H74" s="25" t="inlineStr"/>
-    </row>
-    <row r="75" ht="34" customHeight="1">
-      <c r="A75" s="35" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B75" s="24" t="inlineStr">
-        <is>
-          <t>成果品</t>
-        </is>
-      </c>
-      <c r="C75" s="25" t="inlineStr">
-        <is>
-          <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
-        </is>
-      </c>
-      <c r="D75" s="25" t="inlineStr">
-        <is>
-          <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
-        </is>
-      </c>
-      <c r="E75" s="23" t="inlineStr">
-        <is>
-          <t>Ⅳ-92</t>
-        </is>
-      </c>
-      <c r="F75" s="23" t="inlineStr">
-        <is>
-          <t>doc01-10,doc08</t>
-        </is>
-      </c>
-      <c r="G75" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H75" s="25" t="inlineStr"/>
-    </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="36" t="inlineStr">
-        <is>
-          <t>■ 解決済み（記録）</t>
-        </is>
-      </c>
+      <c r="H77" s="25" t="inlineStr"/>
     </row>
     <row r="78" ht="34" customHeight="1">
       <c r="A78" s="37" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B78" s="38" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C78" s="39" t="inlineStr">
-        <is>
-          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
-        </is>
-      </c>
-      <c r="D78" s="39" t="inlineStr">
-        <is>
-          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
-        </is>
-      </c>
-      <c r="E78" s="37" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F78" s="37" t="inlineStr">
-        <is>
-          <t>doc20§3,§4</t>
-        </is>
-      </c>
-      <c r="G78" s="37" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H78" s="39" t="inlineStr"/>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B78" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C78" s="25" t="inlineStr">
+        <is>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+        </is>
+      </c>
+      <c r="D78" s="25" t="inlineStr">
+        <is>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+        </is>
+      </c>
+      <c r="E78" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-31</t>
+        </is>
+      </c>
+      <c r="F78" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-6</t>
+        </is>
+      </c>
+      <c r="G78" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H78" s="25" t="inlineStr"/>
     </row>
     <row r="79" ht="34" customHeight="1">
       <c r="A79" s="37" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B79" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C79" s="25" t="inlineStr">
+        <is>
+          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+        </is>
+      </c>
+      <c r="D79" s="25" t="inlineStr">
+        <is>
+          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+        </is>
+      </c>
+      <c r="E79" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-40,Ⅰ-42</t>
+        </is>
+      </c>
+      <c r="F79" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-7</t>
+        </is>
+      </c>
+      <c r="G79" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H79" s="25" t="inlineStr"/>
+    </row>
+    <row r="80" ht="34" customHeight="1">
+      <c r="A80" s="38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B80" s="24" t="inlineStr">
+        <is>
+          <t>成果品</t>
+        </is>
+      </c>
+      <c r="C80" s="25" t="inlineStr">
+        <is>
+          <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
+        </is>
+      </c>
+      <c r="D80" s="25" t="inlineStr">
+        <is>
+          <t>第9期はA4・本文104頁・全6章＋資料編。</t>
+        </is>
+      </c>
+      <c r="E80" s="23" t="inlineStr">
+        <is>
+          <t>Ⅳ-89</t>
+        </is>
+      </c>
+      <c r="F80" s="23" t="inlineStr">
+        <is>
+          <t>doc01-10</t>
+        </is>
+      </c>
+      <c r="G80" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H80" s="25" t="inlineStr"/>
+    </row>
+    <row r="81" ht="34" customHeight="1">
+      <c r="A81" s="38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B81" s="24" t="inlineStr">
+        <is>
+          <t>成果品</t>
+        </is>
+      </c>
+      <c r="C81" s="25" t="inlineStr">
+        <is>
+          <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
+        </is>
+      </c>
+      <c r="D81" s="25" t="inlineStr">
+        <is>
+          <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
+        </is>
+      </c>
+      <c r="E81" s="23" t="inlineStr">
+        <is>
+          <t>Ⅳ-92</t>
+        </is>
+      </c>
+      <c r="F81" s="23" t="inlineStr">
+        <is>
+          <t>doc01-10,doc08</t>
+        </is>
+      </c>
+      <c r="G81" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H81" s="25" t="inlineStr"/>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="39" t="inlineStr">
+        <is>
+          <t>■ 解決済み（記録）</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="34" customHeight="1">
+      <c r="A84" s="40" t="inlineStr">
+        <is>
           <t>―</t>
         </is>
       </c>
-      <c r="B79" s="38" t="inlineStr">
+      <c r="B84" s="41" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C84" s="42" t="inlineStr">
+        <is>
+          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
+        </is>
+      </c>
+      <c r="D84" s="42" t="inlineStr">
+        <is>
+          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
+        </is>
+      </c>
+      <c r="E84" s="40" t="inlineStr">
+        <is>
+          <t>Ⅰ-08,Ⅰ-24</t>
+        </is>
+      </c>
+      <c r="F84" s="40" t="inlineStr">
+        <is>
+          <t>doc22 §1</t>
+        </is>
+      </c>
+      <c r="G84" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H84" s="42" t="inlineStr"/>
+    </row>
+    <row r="85" ht="34" customHeight="1">
+      <c r="A85" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B85" s="41" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C85" s="42" t="inlineStr">
+        <is>
+          <t>在宅介護実態調査 約150人の抽出基準</t>
+        </is>
+      </c>
+      <c r="D85" s="42" t="inlineStr">
+        <is>
+          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
+        </is>
+      </c>
+      <c r="E85" s="40" t="inlineStr">
+        <is>
+          <t>Ⅰ-08,Ⅰ-24</t>
+        </is>
+      </c>
+      <c r="F85" s="40" t="inlineStr">
+        <is>
+          <t>doc22 §1</t>
+        </is>
+      </c>
+      <c r="G85" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H85" s="42" t="inlineStr"/>
+    </row>
+    <row r="86" ht="34" customHeight="1">
+      <c r="A86" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B86" s="41" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C86" s="42" t="inlineStr">
+        <is>
+          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
+        </is>
+      </c>
+      <c r="D86" s="42" t="inlineStr">
+        <is>
+          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
+        </is>
+      </c>
+      <c r="E86" s="40" t="inlineStr">
+        <is>
+          <t>Ⅰ-25,Ⅰ-26</t>
+        </is>
+      </c>
+      <c r="F86" s="40" t="inlineStr">
+        <is>
+          <t>doc22 §1</t>
+        </is>
+      </c>
+      <c r="G86" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H86" s="42" t="inlineStr"/>
+    </row>
+    <row r="87" ht="34" customHeight="1">
+      <c r="A87" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B87" s="41" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C87" s="42" t="inlineStr">
+        <is>
+          <t>整合を図る関連計画の範囲</t>
+        </is>
+      </c>
+      <c r="D87" s="42" t="inlineStr">
+        <is>
+          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+        </is>
+      </c>
+      <c r="E87" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F87" s="40" t="inlineStr">
+        <is>
+          <t>doc22 §1</t>
+        </is>
+      </c>
+      <c r="G87" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H87" s="42" t="inlineStr"/>
+    </row>
+    <row r="88" ht="34" customHeight="1">
+      <c r="A88" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B88" s="41" t="inlineStr">
         <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="C79" s="39" t="inlineStr">
+      <c r="C88" s="42" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+        </is>
+      </c>
+      <c r="D88" s="42" t="inlineStr">
+        <is>
+          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+        </is>
+      </c>
+      <c r="E88" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F88" s="40" t="inlineStr">
+        <is>
+          <t>doc20§3,§4</t>
+        </is>
+      </c>
+      <c r="G88" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H88" s="42" t="inlineStr"/>
+    </row>
+    <row r="89" ht="34" customHeight="1">
+      <c r="A89" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B89" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C89" s="42" t="inlineStr">
         <is>
           <t>交付要綱の配点表（満点）</t>
         </is>
       </c>
-      <c r="D79" s="39" t="inlineStr">
+      <c r="D89" s="42" t="inlineStr">
         <is>
           <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
         </is>
       </c>
-      <c r="E79" s="37" t="inlineStr">
+      <c r="E89" s="40" t="inlineStr">
         <is>
           <t>Ⅱ-65</t>
         </is>
       </c>
-      <c r="F79" s="37" t="inlineStr">
+      <c r="F89" s="40" t="inlineStr">
         <is>
           <t>doc20§2</t>
         </is>
       </c>
-      <c r="G79" s="37" t="inlineStr">
+      <c r="G89" s="40" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H79" s="39" t="inlineStr"/>
-    </row>
-    <row r="80" ht="34" customHeight="1">
-      <c r="A80" s="37" t="inlineStr">
+      <c r="H89" s="42" t="inlineStr"/>
+    </row>
+    <row r="90" ht="34" customHeight="1">
+      <c r="A90" s="40" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="B80" s="38" t="inlineStr">
+      <c r="B90" s="41" t="inlineStr">
         <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="C80" s="39" t="inlineStr">
+      <c r="C90" s="42" t="inlineStr">
         <is>
           <t>令和6年度・令和7年度の交付金評価結果</t>
         </is>
       </c>
-      <c r="D80" s="39" t="inlineStr">
+      <c r="D90" s="42" t="inlineStr">
         <is>
           <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
         </is>
       </c>
-      <c r="E80" s="37" t="inlineStr">
+      <c r="E90" s="40" t="inlineStr">
         <is>
           <t>Ⅱ-65</t>
         </is>
       </c>
-      <c r="F80" s="37" t="inlineStr">
+      <c r="F90" s="40" t="inlineStr">
         <is>
           <t>doc20§3-1</t>
         </is>
       </c>
-      <c r="G80" s="37" t="inlineStr">
+      <c r="G90" s="40" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H80" s="39" t="inlineStr"/>
-    </row>
-    <row r="81" ht="34" customHeight="1">
-      <c r="A81" s="37" t="inlineStr">
+      <c r="H90" s="42" t="inlineStr"/>
+    </row>
+    <row r="91" ht="34" customHeight="1">
+      <c r="A91" s="40" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="B81" s="38" t="inlineStr">
+      <c r="B91" s="41" t="inlineStr">
         <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="C81" s="39" t="inlineStr">
+      <c r="C91" s="42" t="inlineStr">
         <is>
           <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
         </is>
       </c>
-      <c r="D81" s="39" t="inlineStr">
+      <c r="D91" s="42" t="inlineStr">
         <is>
           <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
         </is>
       </c>
-      <c r="E81" s="37" t="inlineStr">
+      <c r="E91" s="40" t="inlineStr">
         <is>
           <t>Ⅱ-56,Ⅱ-58</t>
         </is>
       </c>
-      <c r="F81" s="37" t="inlineStr">
+      <c r="F91" s="40" t="inlineStr">
         <is>
           <t>doc09</t>
         </is>
       </c>
-      <c r="G81" s="37" t="inlineStr">
+      <c r="G91" s="40" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H81" s="39" t="inlineStr"/>
-    </row>
-    <row r="82" ht="34" customHeight="1">
-      <c r="A82" s="37" t="inlineStr">
+      <c r="H91" s="42" t="inlineStr"/>
+    </row>
+    <row r="92" ht="34" customHeight="1">
+      <c r="A92" s="40" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="B82" s="38" t="inlineStr">
+      <c r="B92" s="41" t="inlineStr">
         <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="C82" s="39" t="inlineStr">
+      <c r="C92" s="42" t="inlineStr">
         <is>
           <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
         </is>
       </c>
-      <c r="D82" s="39" t="inlineStr">
+      <c r="D92" s="42" t="inlineStr">
         <is>
           <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
         </is>
       </c>
-      <c r="E82" s="37" t="inlineStr">
+      <c r="E92" s="40" t="inlineStr">
         <is>
           <t>Ⅱ-59</t>
         </is>
       </c>
-      <c r="F82" s="37" t="inlineStr">
+      <c r="F92" s="40" t="inlineStr">
         <is>
           <t>doc02§20-2</t>
         </is>
       </c>
-      <c r="G82" s="37" t="inlineStr">
+      <c r="G92" s="40" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H82" s="39" t="inlineStr"/>
-    </row>
-    <row r="83" ht="34" customHeight="1">
-      <c r="A83" s="37" t="inlineStr">
+      <c r="H92" s="42" t="inlineStr"/>
+    </row>
+    <row r="93" ht="34" customHeight="1">
+      <c r="A93" s="40" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="B83" s="38" t="inlineStr">
+      <c r="B93" s="41" t="inlineStr">
         <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="C83" s="39" t="inlineStr">
+      <c r="C93" s="42" t="inlineStr">
         <is>
           <t>国の指針・様式の更新有無</t>
         </is>
       </c>
-      <c r="D83" s="39" t="inlineStr">
+      <c r="D93" s="42" t="inlineStr">
         <is>
           <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
-      <c r="E83" s="37" t="inlineStr">
+      <c r="E93" s="40" t="inlineStr">
         <is>
           <t>Ⅰ-11</t>
         </is>
       </c>
-      <c r="F83" s="37" t="inlineStr">
+      <c r="F93" s="40" t="inlineStr">
         <is>
           <t>doc04,doc05</t>
         </is>
       </c>
-      <c r="G83" s="37" t="inlineStr">
+      <c r="G93" s="40" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H83" s="39" t="inlineStr"/>
+      <c r="H93" s="42" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H75"/>
+  <autoFilter ref="A4:H81"/>
   <mergeCells count="3">
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A77:H77"/>
+    <mergeCell ref="A83:H83"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9901,7 +10534,7 @@
           <t>業務内容・成果品・その他条件</t>
         </is>
       </c>
-      <c r="D5" s="40" t="n">
+      <c r="D5" s="43" t="n">
         <v>46259</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -9931,7 +10564,7 @@
           <t>本文104頁・全6章＋資料編</t>
         </is>
       </c>
-      <c r="D6" s="40" t="n">
+      <c r="D6" s="43" t="n">
         <v>46259</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -9961,7 +10594,7 @@
           <t>基本理念・基本目標・数値①〜⑦・施策体系図</t>
         </is>
       </c>
-      <c r="D7" s="40" t="n">
+      <c r="D7" s="43" t="n">
         <v>46265</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -9976,64 +10609,64 @@
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="32" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>現行計画</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>★北塩原村第五次総合振興計画（2017〜2026）</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>上位計画。第六次の策定状況も要確認</t>
         </is>
       </c>
-      <c r="D8" s="32" t="inlineStr">
+      <c r="D8" s="35" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E8" s="31" t="inlineStr">
+      <c r="E8" s="34" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F8" s="32" t="inlineStr">
+      <c r="F8" s="35" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>現行計画</t>
         </is>
       </c>
-      <c r="B9" s="31" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>★第3次健康きたしおばら21</t>
         </is>
       </c>
-      <c r="C9" s="31" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>関連計画</t>
         </is>
       </c>
-      <c r="D9" s="32" t="inlineStr">
+      <c r="D9" s="35" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E9" s="31" t="inlineStr">
+      <c r="E9" s="34" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F9" s="32" t="inlineStr">
+      <c r="F9" s="35" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
@@ -10055,7 +10688,7 @@
           <t>2版をレビュー済</t>
         </is>
       </c>
-      <c r="D10" s="40" t="n">
+      <c r="D10" s="43" t="n">
         <v>46259</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -10085,7 +10718,7 @@
           <t>修正案まで受領</t>
         </is>
       </c>
-      <c r="D11" s="40" t="n">
+      <c r="D11" s="43" t="n">
         <v>46259</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -10115,7 +10748,7 @@
           <t>逐条突合の基礎。要確認0件で完了</t>
         </is>
       </c>
-      <c r="D12" s="40" t="n">
+      <c r="D12" s="43" t="n">
         <v>46261</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -10145,7 +10778,7 @@
           <t>第1号被保険者数・認定者数・認定率ほか</t>
         </is>
       </c>
-      <c r="D13" s="40" t="n">
+      <c r="D13" s="43" t="n">
         <v>46259</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -10175,7 +10808,7 @@
           <t>第1号被保険者1人あたり給付月額ほか</t>
         </is>
       </c>
-      <c r="D14" s="40" t="n">
+      <c r="D14" s="43" t="n">
         <v>46265</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -10205,7 +10838,7 @@
           <t>村内施設ゼロを確認</t>
         </is>
       </c>
-      <c r="D15" s="40" t="n">
+      <c r="D15" s="43" t="n">
         <v>46265</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -10235,7 +10868,7 @@
           <t>定員は平成30年度以降据置</t>
         </is>
       </c>
-      <c r="D16" s="40" t="n">
+      <c r="D16" s="43" t="n">
         <v>46265</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -10265,7 +10898,7 @@
           <t>17系列が実データなし（＝未実施）</t>
         </is>
       </c>
-      <c r="D17" s="40" t="n">
+      <c r="D17" s="43" t="n">
         <v>46265</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -10295,7 +10928,7 @@
           <t>平成26〜令和5年度決算</t>
         </is>
       </c>
-      <c r="D18" s="40" t="n">
+      <c r="D18" s="43" t="n">
         <v>46265</v>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -10325,7 +10958,7 @@
           <t>令和3〜5年度。0点項目21件を抽出</t>
         </is>
       </c>
-      <c r="D19" s="40" t="n">
+      <c r="D19" s="43" t="n">
         <v>46265</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -10355,7 +10988,7 @@
           <t>令和5年度</t>
         </is>
       </c>
-      <c r="D20" s="40" t="n">
+      <c r="D20" s="43" t="n">
         <v>46265</v>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -10385,7 +11018,7 @@
           <t>県平均・全国平均・県内順位・全国順位</t>
         </is>
       </c>
-      <c r="D21" s="40" t="n">
+      <c r="D21" s="43" t="n">
         <v>46265</v>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -10400,160 +11033,160 @@
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="32" t="inlineStr">
+      <c r="A22" s="35" t="inlineStr">
         <is>
           <t>村データ</t>
         </is>
       </c>
-      <c r="B22" s="31" t="inlineStr">
+      <c r="B22" s="34" t="inlineStr">
         <is>
           <t>★介護給付費準備基金の現在高</t>
         </is>
       </c>
-      <c r="C22" s="31" t="inlineStr">
+      <c r="C22" s="34" t="inlineStr">
         <is>
           <t>令和6年度末実績・令和7年度末見込</t>
         </is>
       </c>
-      <c r="D22" s="32" t="inlineStr">
+      <c r="D22" s="35" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E22" s="31" t="inlineStr">
+      <c r="E22" s="34" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F22" s="32" t="inlineStr">
+      <c r="F22" s="35" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="32" t="inlineStr">
+      <c r="A23" s="35" t="inlineStr">
         <is>
           <t>村データ</t>
         </is>
       </c>
-      <c r="B23" s="31" t="inlineStr">
+      <c r="B23" s="34" t="inlineStr">
         <is>
           <t>★令和6年度決算・令和7年度給付費見込</t>
         </is>
       </c>
-      <c r="C23" s="31" t="inlineStr">
+      <c r="C23" s="34" t="inlineStr">
         <is>
           <t>第9期の乖離確定に必要</t>
         </is>
       </c>
-      <c r="D23" s="32" t="inlineStr">
+      <c r="D23" s="35" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E23" s="31" t="inlineStr">
+      <c r="E23" s="34" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F23" s="32" t="inlineStr">
+      <c r="F23" s="35" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="32" t="inlineStr">
+      <c r="A24" s="35" t="inlineStr">
         <is>
           <t>村データ</t>
         </is>
       </c>
-      <c r="B24" s="31" t="inlineStr">
+      <c r="B24" s="34" t="inlineStr">
         <is>
           <t>★通いの場の実数（令和3〜7年度）</t>
         </is>
       </c>
-      <c r="C24" s="31" t="inlineStr">
+      <c r="C24" s="34" t="inlineStr">
         <is>
           <t>見える化は令和2年度で更新停止</t>
         </is>
       </c>
-      <c r="D24" s="32" t="inlineStr">
+      <c r="D24" s="35" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E24" s="31" t="inlineStr">
+      <c r="E24" s="34" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F24" s="32" t="inlineStr">
+      <c r="F24" s="35" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="32" t="inlineStr">
+      <c r="A25" s="35" t="inlineStr">
         <is>
           <t>村データ</t>
         </is>
       </c>
-      <c r="B25" s="31" t="inlineStr">
+      <c r="B25" s="34" t="inlineStr">
         <is>
           <t>★高齢者福祉事業（村単独事業）の実績</t>
         </is>
       </c>
-      <c r="C25" s="31" t="inlineStr">
+      <c r="C25" s="34" t="inlineStr">
         <is>
           <t>現行計画の評価に必要</t>
         </is>
       </c>
-      <c r="D25" s="32" t="inlineStr">
+      <c r="D25" s="35" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E25" s="31" t="inlineStr">
+      <c r="E25" s="34" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F25" s="32" t="inlineStr">
+      <c r="F25" s="35" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="32" t="inlineStr">
+      <c r="A26" s="35" t="inlineStr">
         <is>
           <t>村データ</t>
         </is>
       </c>
-      <c r="B26" s="31" t="inlineStr">
+      <c r="B26" s="34" t="inlineStr">
         <is>
           <t>★成年後見制度の利用実態・市民後見人養成実績</t>
         </is>
       </c>
-      <c r="C26" s="31" t="inlineStr">
+      <c r="C26" s="34" t="inlineStr">
         <is>
           <t>見える化に該当データなし</t>
         </is>
       </c>
-      <c r="D26" s="32" t="inlineStr">
+      <c r="D26" s="35" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E26" s="31" t="inlineStr">
+      <c r="E26" s="34" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F26" s="32" t="inlineStr">
+      <c r="F26" s="35" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
@@ -10575,7 +11208,7 @@
           <t>全17頁。推進400点・支援400点、目標Ⅰ〜Ⅳ各100点</t>
         </is>
       </c>
-      <c r="D27" s="40" t="n">
+      <c r="D27" s="43" t="n">
         <v>46267</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -10605,7 +11238,7 @@
           <t>全国1,741市町村。村は第398行。合計295点</t>
         </is>
       </c>
-      <c r="D28" s="40" t="n">
+      <c r="D28" s="43" t="n">
         <v>46267</v>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -10635,7 +11268,7 @@
           <t>合計339点。全国平均435.0点</t>
         </is>
       </c>
-      <c r="D29" s="40" t="n">
+      <c r="D29" s="43" t="n">
         <v>46267</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -10665,7 +11298,7 @@
           <t>合計447点。全国平均455.1点／全国1,005位／県内34位</t>
         </is>
       </c>
-      <c r="D30" s="40" t="n">
+      <c r="D30" s="43" t="n">
         <v>46267</v>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -10695,7 +11328,7 @@
           <t>全112頁。2018〜2027年度。7z分割書庫4分割で受領</t>
         </is>
       </c>
-      <c r="D31" s="40" t="n">
+      <c r="D31" s="43" t="n">
         <v>46267</v>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -10710,32 +11343,32 @@
       </c>
     </row>
     <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="32" t="inlineStr">
+      <c r="A32" s="35" t="inlineStr">
         <is>
           <t>村データ</t>
         </is>
       </c>
-      <c r="B32" s="31" t="inlineStr">
+      <c r="B32" s="34" t="inlineStr">
         <is>
           <t>★要介護認定データ（調査票との関連付け用）</t>
         </is>
       </c>
-      <c r="C32" s="31" t="inlineStr">
+      <c r="C32" s="34" t="inlineStr">
         <is>
           <t>仕様書4Ⅰ(5)。調査回収後に必要</t>
         </is>
       </c>
-      <c r="D32" s="32" t="inlineStr">
+      <c r="D32" s="35" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E32" s="31" t="inlineStr">
+      <c r="E32" s="34" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F32" s="32" t="inlineStr">
+      <c r="F32" s="35" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
@@ -10757,7 +11390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I55"/>
+  <dimension ref="B2:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -10771,849 +11404,907 @@
   </cols>
   <sheetData>
     <row r="2" ht="26" customHeight="1">
-      <c r="B2" s="41" t="inlineStr">
+      <c r="B2" s="44" t="inlineStr">
         <is>
           <t>凡例・入力ルール／進捗集計</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="36" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>■ 入力する列（ここだけ編集してください）</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="42" t="inlineStr">
+      <c r="B5" s="45" t="inlineStr">
         <is>
           <t>予定開始・予定完了</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr">
+      <c r="C5" s="46" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="D5" s="43" t="inlineStr">
+      <c r="D5" s="46" t="inlineStr">
         <is>
           <t>yyyy/mm/dd 形式で入力します。村との協議で工程が固まり次第、入力してください。</t>
         </is>
       </c>
-      <c r="E5" s="44" t="n"/>
-      <c r="F5" s="44" t="n"/>
-      <c r="G5" s="44" t="n"/>
-      <c r="H5" s="44" t="n"/>
+      <c r="E5" s="47" t="n"/>
+      <c r="F5" s="47" t="n"/>
+      <c r="G5" s="47" t="n"/>
+      <c r="H5" s="47" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B6" s="45" t="inlineStr">
         <is>
           <t>実績開始・実績完了</t>
         </is>
       </c>
-      <c r="C6" s="43" t="inlineStr">
+      <c r="C6" s="46" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="D6" s="43" t="inlineStr">
+      <c r="D6" s="46" t="inlineStr">
         <is>
           <t>着手日・完了日を実績として入力します。</t>
         </is>
       </c>
-      <c r="E6" s="44" t="n"/>
-      <c r="F6" s="44" t="n"/>
-      <c r="G6" s="44" t="n"/>
-      <c r="H6" s="44" t="n"/>
+      <c r="E6" s="47" t="n"/>
+      <c r="F6" s="47" t="n"/>
+      <c r="G6" s="47" t="n"/>
+      <c r="H6" s="47" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="42" t="inlineStr">
+      <c r="B7" s="45" t="inlineStr">
         <is>
           <t>進捗率</t>
         </is>
       </c>
-      <c r="C7" s="43" t="inlineStr">
+      <c r="C7" s="46" t="inlineStr">
         <is>
           <t>％</t>
         </is>
       </c>
-      <c r="D7" s="43" t="inlineStr">
+      <c r="D7" s="46" t="inlineStr">
         <is>
           <t>0〜100% を入力します。完了時は 100%。</t>
         </is>
       </c>
-      <c r="E7" s="44" t="n"/>
-      <c r="F7" s="44" t="n"/>
-      <c r="G7" s="44" t="n"/>
-      <c r="H7" s="44" t="n"/>
+      <c r="E7" s="47" t="n"/>
+      <c r="F7" s="47" t="n"/>
+      <c r="G7" s="47" t="n"/>
+      <c r="H7" s="47" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="42" t="inlineStr">
+      <c r="B8" s="45" t="inlineStr">
         <is>
           <t>ステータス</t>
         </is>
       </c>
-      <c r="C8" s="43" t="inlineStr">
+      <c r="C8" s="46" t="inlineStr">
         <is>
           <t>選択</t>
         </is>
       </c>
-      <c r="D8" s="43" t="inlineStr">
+      <c r="D8" s="46" t="inlineStr">
         <is>
           <t>未着手／着手／確認中／完了／保留／対象外 から選択します。</t>
         </is>
       </c>
-      <c r="E8" s="44" t="n"/>
-      <c r="F8" s="44" t="n"/>
-      <c r="G8" s="44" t="n"/>
-      <c r="H8" s="44" t="n"/>
+      <c r="E8" s="47" t="n"/>
+      <c r="F8" s="47" t="n"/>
+      <c r="G8" s="47" t="n"/>
+      <c r="H8" s="47" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="42" t="inlineStr">
+      <c r="B9" s="45" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="C9" s="43" t="inlineStr">
+      <c r="C9" s="46" t="inlineStr">
         <is>
           <t>自由</t>
         </is>
       </c>
-      <c r="D9" s="43" t="inlineStr">
+      <c r="D9" s="46" t="inlineStr">
         <is>
           <t>課題・懸案・村への確認事項などを記入します。</t>
         </is>
       </c>
-      <c r="E9" s="44" t="n"/>
-      <c r="F9" s="44" t="n"/>
-      <c r="G9" s="44" t="n"/>
-      <c r="H9" s="44" t="n"/>
+      <c r="E9" s="47" t="n"/>
+      <c r="F9" s="47" t="n"/>
+      <c r="G9" s="47" t="n"/>
+      <c r="H9" s="47" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="36" t="inlineStr">
+      <c r="B11" s="39" t="inlineStr">
         <is>
           <t>■ 行の塗り分け</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="45" t="inlineStr">
+      <c r="B12" s="48" t="inlineStr">
         <is>
           <t>薄い緑</t>
         </is>
       </c>
-      <c r="C12" s="43" t="inlineStr">
+      <c r="C12" s="46" t="inlineStr">
         <is>
           <t>完了した作業です。</t>
         </is>
       </c>
-      <c r="D12" s="44" t="n"/>
-      <c r="E12" s="44" t="n"/>
-      <c r="F12" s="44" t="n"/>
-      <c r="G12" s="44" t="n"/>
-      <c r="H12" s="44" t="n"/>
+      <c r="D12" s="47" t="n"/>
+      <c r="E12" s="47" t="n"/>
+      <c r="F12" s="47" t="n"/>
+      <c r="G12" s="47" t="n"/>
+      <c r="H12" s="47" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="46" t="inlineStr">
+      <c r="B13" s="49" t="inlineStr">
         <is>
           <t>薄い黄</t>
         </is>
       </c>
-      <c r="C13" s="43" t="inlineStr">
+      <c r="C13" s="46" t="inlineStr">
         <is>
           <t>着手中・確認中の作業、または北塩原村が担当する作業です。</t>
         </is>
       </c>
-      <c r="D13" s="44" t="n"/>
-      <c r="E13" s="44" t="n"/>
-      <c r="F13" s="44" t="n"/>
-      <c r="G13" s="44" t="n"/>
-      <c r="H13" s="44" t="n"/>
+      <c r="D13" s="47" t="n"/>
+      <c r="E13" s="47" t="n"/>
+      <c r="F13" s="47" t="n"/>
+      <c r="G13" s="47" t="n"/>
+      <c r="H13" s="47" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="47" t="inlineStr">
+      <c r="B14" s="50" t="inlineStr">
         <is>
           <t>薄い赤</t>
         </is>
       </c>
-      <c r="C14" s="43" t="inlineStr">
+      <c r="C14" s="46" t="inlineStr">
         <is>
           <t>「村への確認事項」シートの優先度S・A、および未受領の資料です。</t>
         </is>
       </c>
-      <c r="D14" s="44" t="n"/>
-      <c r="E14" s="44" t="n"/>
-      <c r="F14" s="44" t="n"/>
-      <c r="G14" s="44" t="n"/>
-      <c r="H14" s="44" t="n"/>
+      <c r="D14" s="47" t="n"/>
+      <c r="E14" s="47" t="n"/>
+      <c r="F14" s="47" t="n"/>
+      <c r="G14" s="47" t="n"/>
+      <c r="H14" s="47" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="36" t="inlineStr">
+      <c r="B16" s="39" t="inlineStr">
         <is>
           <t>■ 進捗集計（WBSシートから自動集計されます）</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="48" t="inlineStr">
+      <c r="B17" s="51" t="inlineStr">
         <is>
           <t>大分類</t>
         </is>
       </c>
-      <c r="C17" s="48" t="inlineStr">
+      <c r="C17" s="51" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="D17" s="48" t="inlineStr">
+      <c r="D17" s="51" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="E17" s="48" t="inlineStr">
+      <c r="E17" s="51" t="inlineStr">
         <is>
           <t>着手</t>
         </is>
       </c>
-      <c r="F17" s="48" t="inlineStr">
+      <c r="F17" s="51" t="inlineStr">
         <is>
           <t>確認中</t>
         </is>
       </c>
-      <c r="G17" s="48" t="inlineStr">
+      <c r="G17" s="51" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="H17" s="48" t="inlineStr">
+      <c r="H17" s="51" t="inlineStr">
         <is>
           <t>保留</t>
         </is>
       </c>
-      <c r="I17" s="48" t="inlineStr">
+      <c r="I17" s="51" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="43" t="inlineStr">
+      <c r="B18" s="46" t="inlineStr">
         <is>
           <t>０ 契約・立上げ</t>
         </is>
       </c>
-      <c r="C18" s="49">
-        <f>COUNTIF('WBS・進捗管理'!$B$5:$B$101,$B18)</f>
+      <c r="C18" s="52">
+        <f>COUNTIF('WBS・進捗管理'!$B$5:$B$104,$B18)</f>
         <v/>
       </c>
-      <c r="D18" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B18,'WBS・進捗管理'!$O$5:$O$101,D$17)</f>
+      <c r="D18" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B18,'WBS・進捗管理'!$O$5:$O$104,D$17)</f>
         <v/>
       </c>
-      <c r="E18" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B18,'WBS・進捗管理'!$O$5:$O$101,E$17)</f>
+      <c r="E18" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B18,'WBS・進捗管理'!$O$5:$O$104,E$17)</f>
         <v/>
       </c>
-      <c r="F18" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B18,'WBS・進捗管理'!$O$5:$O$101,F$17)</f>
+      <c r="F18" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B18,'WBS・進捗管理'!$O$5:$O$104,F$17)</f>
         <v/>
       </c>
-      <c r="G18" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B18,'WBS・進捗管理'!$O$5:$O$101,G$17)</f>
+      <c r="G18" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B18,'WBS・進捗管理'!$O$5:$O$104,G$17)</f>
         <v/>
       </c>
-      <c r="H18" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B18,'WBS・進捗管理'!$O$5:$O$101,H$17)</f>
+      <c r="H18" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B18,'WBS・進捗管理'!$O$5:$O$104,H$17)</f>
         <v/>
       </c>
-      <c r="I18" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B18,'WBS・進捗管理'!$O$5:$O$101,I$17)</f>
+      <c r="I18" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B18,'WBS・進捗管理'!$O$5:$O$104,I$17)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="43" t="inlineStr">
+      <c r="B19" s="46" t="inlineStr">
         <is>
           <t>Ⅰ ニーズ調査</t>
         </is>
       </c>
-      <c r="C19" s="49">
-        <f>COUNTIF('WBS・進捗管理'!$B$5:$B$101,$B19)</f>
+      <c r="C19" s="52">
+        <f>COUNTIF('WBS・進捗管理'!$B$5:$B$104,$B19)</f>
         <v/>
       </c>
-      <c r="D19" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B19,'WBS・進捗管理'!$O$5:$O$101,D$17)</f>
+      <c r="D19" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B19,'WBS・進捗管理'!$O$5:$O$104,D$17)</f>
         <v/>
       </c>
-      <c r="E19" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B19,'WBS・進捗管理'!$O$5:$O$101,E$17)</f>
+      <c r="E19" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B19,'WBS・進捗管理'!$O$5:$O$104,E$17)</f>
         <v/>
       </c>
-      <c r="F19" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B19,'WBS・進捗管理'!$O$5:$O$101,F$17)</f>
+      <c r="F19" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B19,'WBS・進捗管理'!$O$5:$O$104,F$17)</f>
         <v/>
       </c>
-      <c r="G19" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B19,'WBS・進捗管理'!$O$5:$O$101,G$17)</f>
+      <c r="G19" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B19,'WBS・進捗管理'!$O$5:$O$104,G$17)</f>
         <v/>
       </c>
-      <c r="H19" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B19,'WBS・進捗管理'!$O$5:$O$101,H$17)</f>
+      <c r="H19" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B19,'WBS・進捗管理'!$O$5:$O$104,H$17)</f>
         <v/>
       </c>
-      <c r="I19" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B19,'WBS・進捗管理'!$O$5:$O$101,I$17)</f>
+      <c r="I19" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B19,'WBS・進捗管理'!$O$5:$O$104,I$17)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="43" t="inlineStr">
+      <c r="B20" s="46" t="inlineStr">
         <is>
           <t>Ⅱ 計画策定</t>
         </is>
       </c>
-      <c r="C20" s="49">
-        <f>COUNTIF('WBS・進捗管理'!$B$5:$B$101,$B20)</f>
+      <c r="C20" s="52">
+        <f>COUNTIF('WBS・進捗管理'!$B$5:$B$104,$B20)</f>
         <v/>
       </c>
-      <c r="D20" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B20,'WBS・進捗管理'!$O$5:$O$101,D$17)</f>
+      <c r="D20" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B20,'WBS・進捗管理'!$O$5:$O$104,D$17)</f>
         <v/>
       </c>
-      <c r="E20" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B20,'WBS・進捗管理'!$O$5:$O$101,E$17)</f>
+      <c r="E20" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B20,'WBS・進捗管理'!$O$5:$O$104,E$17)</f>
         <v/>
       </c>
-      <c r="F20" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B20,'WBS・進捗管理'!$O$5:$O$101,F$17)</f>
+      <c r="F20" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B20,'WBS・進捗管理'!$O$5:$O$104,F$17)</f>
         <v/>
       </c>
-      <c r="G20" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B20,'WBS・進捗管理'!$O$5:$O$101,G$17)</f>
+      <c r="G20" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B20,'WBS・進捗管理'!$O$5:$O$104,G$17)</f>
         <v/>
       </c>
-      <c r="H20" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B20,'WBS・進捗管理'!$O$5:$O$101,H$17)</f>
+      <c r="H20" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B20,'WBS・進捗管理'!$O$5:$O$104,H$17)</f>
         <v/>
       </c>
-      <c r="I20" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B20,'WBS・進捗管理'!$O$5:$O$101,I$17)</f>
+      <c r="I20" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B20,'WBS・進捗管理'!$O$5:$O$104,I$17)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="43" t="inlineStr">
+      <c r="B21" s="46" t="inlineStr">
         <is>
           <t>Ⅲ 打合せ等</t>
         </is>
       </c>
-      <c r="C21" s="49">
-        <f>COUNTIF('WBS・進捗管理'!$B$5:$B$101,$B21)</f>
+      <c r="C21" s="52">
+        <f>COUNTIF('WBS・進捗管理'!$B$5:$B$104,$B21)</f>
         <v/>
       </c>
-      <c r="D21" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B21,'WBS・進捗管理'!$O$5:$O$101,D$17)</f>
+      <c r="D21" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B21,'WBS・進捗管理'!$O$5:$O$104,D$17)</f>
         <v/>
       </c>
-      <c r="E21" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B21,'WBS・進捗管理'!$O$5:$O$101,E$17)</f>
+      <c r="E21" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B21,'WBS・進捗管理'!$O$5:$O$104,E$17)</f>
         <v/>
       </c>
-      <c r="F21" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B21,'WBS・進捗管理'!$O$5:$O$101,F$17)</f>
+      <c r="F21" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B21,'WBS・進捗管理'!$O$5:$O$104,F$17)</f>
         <v/>
       </c>
-      <c r="G21" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B21,'WBS・進捗管理'!$O$5:$O$101,G$17)</f>
+      <c r="G21" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B21,'WBS・進捗管理'!$O$5:$O$104,G$17)</f>
         <v/>
       </c>
-      <c r="H21" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B21,'WBS・進捗管理'!$O$5:$O$101,H$17)</f>
+      <c r="H21" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B21,'WBS・進捗管理'!$O$5:$O$104,H$17)</f>
         <v/>
       </c>
-      <c r="I21" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B21,'WBS・進捗管理'!$O$5:$O$101,I$17)</f>
+      <c r="I21" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B21,'WBS・進捗管理'!$O$5:$O$104,I$17)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="43" t="inlineStr">
+      <c r="B22" s="46" t="inlineStr">
         <is>
           <t>Ⅳ 成果品・納品</t>
         </is>
       </c>
-      <c r="C22" s="49">
-        <f>COUNTIF('WBS・進捗管理'!$B$5:$B$101,$B22)</f>
+      <c r="C22" s="52">
+        <f>COUNTIF('WBS・進捗管理'!$B$5:$B$104,$B22)</f>
         <v/>
       </c>
-      <c r="D22" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B22,'WBS・進捗管理'!$O$5:$O$101,D$17)</f>
+      <c r="D22" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B22,'WBS・進捗管理'!$O$5:$O$104,D$17)</f>
         <v/>
       </c>
-      <c r="E22" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B22,'WBS・進捗管理'!$O$5:$O$101,E$17)</f>
+      <c r="E22" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B22,'WBS・進捗管理'!$O$5:$O$104,E$17)</f>
         <v/>
       </c>
-      <c r="F22" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B22,'WBS・進捗管理'!$O$5:$O$101,F$17)</f>
+      <c r="F22" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B22,'WBS・進捗管理'!$O$5:$O$104,F$17)</f>
         <v/>
       </c>
-      <c r="G22" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B22,'WBS・進捗管理'!$O$5:$O$101,G$17)</f>
+      <c r="G22" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B22,'WBS・進捗管理'!$O$5:$O$104,G$17)</f>
         <v/>
       </c>
-      <c r="H22" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B22,'WBS・進捗管理'!$O$5:$O$101,H$17)</f>
+      <c r="H22" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B22,'WBS・進捗管理'!$O$5:$O$104,H$17)</f>
         <v/>
       </c>
-      <c r="I22" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B22,'WBS・進捗管理'!$O$5:$O$101,I$17)</f>
+      <c r="I22" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B22,'WBS・進捗管理'!$O$5:$O$104,I$17)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="43" t="inlineStr">
+      <c r="B23" s="46" t="inlineStr">
         <is>
           <t>Ⅴ 管理</t>
         </is>
       </c>
-      <c r="C23" s="49">
-        <f>COUNTIF('WBS・進捗管理'!$B$5:$B$101,$B23)</f>
+      <c r="C23" s="52">
+        <f>COUNTIF('WBS・進捗管理'!$B$5:$B$104,$B23)</f>
         <v/>
       </c>
-      <c r="D23" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B23,'WBS・進捗管理'!$O$5:$O$101,D$17)</f>
+      <c r="D23" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B23,'WBS・進捗管理'!$O$5:$O$104,D$17)</f>
         <v/>
       </c>
-      <c r="E23" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B23,'WBS・進捗管理'!$O$5:$O$101,E$17)</f>
+      <c r="E23" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B23,'WBS・進捗管理'!$O$5:$O$104,E$17)</f>
         <v/>
       </c>
-      <c r="F23" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B23,'WBS・進捗管理'!$O$5:$O$101,F$17)</f>
+      <c r="F23" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B23,'WBS・進捗管理'!$O$5:$O$104,F$17)</f>
         <v/>
       </c>
-      <c r="G23" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B23,'WBS・進捗管理'!$O$5:$O$101,G$17)</f>
+      <c r="G23" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B23,'WBS・進捗管理'!$O$5:$O$104,G$17)</f>
         <v/>
       </c>
-      <c r="H23" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B23,'WBS・進捗管理'!$O$5:$O$101,H$17)</f>
+      <c r="H23" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B23,'WBS・進捗管理'!$O$5:$O$104,H$17)</f>
         <v/>
       </c>
-      <c r="I23" s="49">
-        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$101,$B23,'WBS・進捗管理'!$O$5:$O$101,I$17)</f>
+      <c r="I23" s="52">
+        <f>COUNTIFS('WBS・進捗管理'!$B$5:$B$104,$B23,'WBS・進捗管理'!$O$5:$O$104,I$17)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="50" t="inlineStr">
+      <c r="B24" s="53" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="C24" s="51">
+      <c r="C24" s="54">
         <f>SUM(C18:C23)</f>
         <v/>
       </c>
-      <c r="D24" s="51">
+      <c r="D24" s="54">
         <f>SUM(D18:D23)</f>
         <v/>
       </c>
-      <c r="E24" s="51">
+      <c r="E24" s="54">
         <f>SUM(E18:E23)</f>
         <v/>
       </c>
-      <c r="F24" s="51">
+      <c r="F24" s="54">
         <f>SUM(F18:F23)</f>
         <v/>
       </c>
-      <c r="G24" s="51">
+      <c r="G24" s="54">
         <f>SUM(G18:G23)</f>
         <v/>
       </c>
-      <c r="H24" s="51">
+      <c r="H24" s="54">
         <f>SUM(H18:H23)</f>
         <v/>
       </c>
-      <c r="I24" s="51">
+      <c r="I24" s="54">
         <f>SUM(I18:I23)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="36" t="inlineStr">
+      <c r="B26" s="39" t="inlineStr">
         <is>
           <t>■ 主要指標</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="52" t="inlineStr">
-        <is>
-          <t>全体進捗率（平均）</t>
-        </is>
-      </c>
-      <c r="C27" s="53">
-        <f>AVERAGE('WBS・進捗管理'!$N$5:$N$101)</f>
+      <c r="B27" s="55" t="inlineStr">
+        <is>
+          <t>全体進捗率（対象外を除く）</t>
+        </is>
+      </c>
+      <c r="C27" s="56">
+        <f>AVERAGEIF('WBS・進捗管理'!$O$5:$O$104,"&lt;&gt;対象外",'WBS・進捗管理'!$N$5:$N$104)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="52" t="inlineStr">
+      <c r="B28" s="55" t="inlineStr">
         <is>
           <t>作業総数</t>
         </is>
       </c>
-      <c r="C28" s="54">
-        <f>COUNTA('WBS・進捗管理'!$A$5:$A$101)</f>
+      <c r="C28" s="57">
+        <f>COUNTA('WBS・進捗管理'!$A$5:$A$104)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="52" t="inlineStr">
+      <c r="B29" s="55" t="inlineStr">
         <is>
           <t>完了した作業</t>
         </is>
       </c>
-      <c r="C29" s="54">
-        <f>COUNTIF('WBS・進捗管理'!$O$5:$O$101,"完了")</f>
+      <c r="C29" s="57">
+        <f>COUNTIF('WBS・進捗管理'!$O$5:$O$104,"完了")</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="52" t="inlineStr">
+      <c r="B30" s="55" t="inlineStr">
         <is>
           <t>着手・確認中の作業</t>
         </is>
       </c>
-      <c r="C30" s="54">
-        <f>COUNTIF('WBS・進捗管理'!$O$5:$O$101,"着手")+COUNTIF('WBS・進捗管理'!$O$5:$O$101,"確認中")</f>
+      <c r="C30" s="57">
+        <f>COUNTIF('WBS・進捗管理'!$O$5:$O$104,"着手")+COUNTIF('WBS・進捗管理'!$O$5:$O$104,"確認中")</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="52" t="inlineStr">
+      <c r="B31" s="55" t="inlineStr">
         <is>
           <t>未着手の作業</t>
         </is>
       </c>
-      <c r="C31" s="54">
-        <f>COUNTIF('WBS・進捗管理'!$O$5:$O$101,"未着手")</f>
+      <c r="C31" s="57">
+        <f>COUNTIF('WBS・進捗管理'!$O$5:$O$104,"未着手")</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="52" t="inlineStr">
+      <c r="B32" s="55" t="inlineStr">
+        <is>
+          <t>対象外の作業</t>
+        </is>
+      </c>
+      <c r="C32" s="57">
+        <f>COUNTIF('WBS・進捗管理'!$O$5:$O$104,"対象外")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="55" t="inlineStr">
         <is>
           <t>村への確認事項（優先度S）</t>
         </is>
       </c>
-      <c r="C32" s="54">
+      <c r="C33" s="57">
         <f>COUNTIF('村への確認事項'!$A:$A,"S")</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="52" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="55" t="inlineStr">
         <is>
           <t>村への確認事項（優先度A）</t>
         </is>
       </c>
-      <c r="C33" s="54">
+      <c r="C34" s="57">
         <f>COUNTIF('村への確認事項'!$A:$A,"A")</f>
         <v/>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="52" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="55" t="inlineStr">
         <is>
           <t>村への確認事項（未依頼）</t>
         </is>
       </c>
-      <c r="C34" s="54">
+      <c r="C35" s="57">
         <f>COUNTIF('村への確認事項'!$G:$G,"未依頼")</f>
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="52" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="55" t="inlineStr">
         <is>
           <t>未受領の資料・データ</t>
         </is>
       </c>
-      <c r="C35" s="54">
+      <c r="C36" s="57">
         <f>COUNTIF('受領資料・データ管理'!$F:$F,"未受領")</f>
         <v/>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="36" t="inlineStr">
-        <is>
-          <t>■ 直近のマイルストーン（基準日 令和8年9月2日）</t>
-        </is>
-      </c>
-    </row>
     <row r="38">
-      <c r="B38" s="55" t="inlineStr"/>
-      <c r="C38" s="55" t="inlineStr">
+      <c r="B38" s="39" t="inlineStr">
+        <is>
+          <t>■ マイルストーン（令和8年9月1日 キックオフ議事録により確定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="58" t="inlineStr"/>
+      <c r="C39" s="58" t="inlineStr">
         <is>
           <t>期日</t>
         </is>
       </c>
-      <c r="D38" s="55" t="inlineStr">
+      <c r="D39" s="58" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="E38" s="55" t="inlineStr">
+      <c r="E39" s="58" t="inlineStr">
         <is>
           <t>留意点</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="56" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="23" t="inlineStr"/>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>令和8年9月1日（火）</t>
+        </is>
+      </c>
+      <c r="D40" s="24" t="inlineStr">
+        <is>
+          <t>キックオフ会議</t>
+        </is>
+      </c>
+      <c r="E40" s="25" t="inlineStr">
+        <is>
+          <t>完了。議事録を受領（doc22）。S項目16件のうち9件が決着</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="59" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="C39" s="57" t="inlineStr">
-        <is>
-          <t>令和8年9月1日（火）</t>
-        </is>
-      </c>
-      <c r="D39" s="57" t="inlineStr">
-        <is>
-          <t>キックオフ会議（資料上の予定日）</t>
-        </is>
-      </c>
-      <c r="E39" s="58" t="inlineStr">
-        <is>
-          <t>経過・結果未確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="56" t="inlineStr">
+      <c r="C41" s="60" t="inlineStr">
+        <is>
+          <t>令和8年9月3日（木）</t>
+        </is>
+      </c>
+      <c r="D41" s="60" t="inlineStr">
+        <is>
+          <t>調査票 第1稿の提出</t>
+        </is>
+      </c>
+      <c r="E41" s="61" t="inlineStr">
+        <is>
+          <t>★議事録で確定。未決事項は選択肢併記で提出</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="59" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="C40" s="57" t="inlineStr">
-        <is>
-          <t>令和8年9月9日（水）</t>
-        </is>
-      </c>
-      <c r="D40" s="57" t="inlineStr">
-        <is>
-          <t>調査票の入稿</t>
-        </is>
-      </c>
-      <c r="E40" s="58" t="inlineStr">
-        <is>
-          <t>残り7日。優先度Sの決着が前提</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="23" t="inlineStr"/>
-      <c r="C41" s="24" t="inlineStr">
-        <is>
-          <t>令和8年9月11日（金）</t>
-        </is>
-      </c>
-      <c r="D41" s="24" t="inlineStr">
-        <is>
-          <t>宛名ラベル・配布用封筒の提供（前倒し案）</t>
-        </is>
-      </c>
-      <c r="E41" s="25" t="inlineStr">
-        <is>
-          <t>村。原案は9/14</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="23" t="inlineStr"/>
-      <c r="C42" s="24" t="inlineStr">
+      <c r="C42" s="60" t="inlineStr">
+        <is>
+          <t>令和8年9月9日（水）頃</t>
+        </is>
+      </c>
+      <c r="D42" s="60" t="inlineStr">
+        <is>
+          <t>調査票の最終校了・印刷依頼</t>
+        </is>
+      </c>
+      <c r="E42" s="61" t="inlineStr">
+        <is>
+          <t>★Webフォームの実装方法が未決だと間に合わない恐れ</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="23" t="inlineStr"/>
+      <c r="C43" s="24" t="inlineStr">
+        <is>
+          <t>令和8年9月14日（月）</t>
+        </is>
+      </c>
+      <c r="D43" s="24" t="inlineStr">
+        <is>
+          <t>宛名ラベル・配布用封筒の提供</t>
+        </is>
+      </c>
+      <c r="E43" s="25" t="inlineStr">
+        <is>
+          <t>村。9/11への前倒しを要請</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="23" t="inlineStr"/>
+      <c r="C44" s="24" t="inlineStr">
         <is>
           <t>令和8年9月16〜17日</t>
         </is>
       </c>
-      <c r="D42" s="24" t="inlineStr">
+      <c r="D44" s="24" t="inlineStr">
         <is>
           <t>宛名貼付・封入・封緘</t>
         </is>
       </c>
-      <c r="E42" s="25" t="inlineStr">
+      <c r="E44" s="25" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="56" t="inlineStr">
+    <row r="45">
+      <c r="B45" s="59" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="C43" s="57" t="inlineStr">
-        <is>
-          <t>令和8年9月18日（金）</t>
-        </is>
-      </c>
-      <c r="D43" s="57" t="inlineStr">
-        <is>
-          <t>発送（案）</t>
-        </is>
-      </c>
-      <c r="E43" s="58" t="inlineStr">
+      <c r="C45" s="60" t="inlineStr">
+        <is>
+          <t>令和8年9月18日（金）頃</t>
+        </is>
+      </c>
+      <c r="D45" s="60" t="inlineStr">
+        <is>
+          <t>アンケート発送</t>
+        </is>
+      </c>
+      <c r="E45" s="61" t="inlineStr">
         <is>
           <t>★5連休（9/19〜9/23）の直前。9/17前倒しを協議</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="56" t="inlineStr">
+    <row r="46">
+      <c r="B46" s="59" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="C44" s="57" t="inlineStr">
+      <c r="C46" s="60" t="inlineStr">
         <is>
           <t>令和8年9月30日（水）</t>
         </is>
       </c>
-      <c r="D44" s="57" t="inlineStr">
+      <c r="D46" s="60" t="inlineStr">
         <is>
           <t>策定委員会 現委員の任期満了</t>
         </is>
       </c>
-      <c r="E44" s="58" t="inlineStr">
-        <is>
-          <t>★10月中の改選・委嘱が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="23" t="inlineStr"/>
-      <c r="C45" s="24" t="inlineStr">
-        <is>
-          <t>令和8年10月上旬</t>
-        </is>
-      </c>
-      <c r="D45" s="24" t="inlineStr">
-        <is>
-          <t>督促（リマインド）の要否判断</t>
-        </is>
-      </c>
-      <c r="E45" s="25" t="inlineStr">
-        <is>
-          <t>第9期の在宅調査回収率45.8%を踏まえ</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="23" t="inlineStr"/>
-      <c r="C46" s="24" t="inlineStr">
+      <c r="E46" s="61" t="inlineStr">
+        <is>
+          <t>★議事録で触れられず。第2回（11月）には改選が前提</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="23" t="inlineStr"/>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>令和8年10月</t>
+        </is>
+      </c>
+      <c r="D47" s="24" t="inlineStr">
+        <is>
+          <t>回収・データ入力</t>
+        </is>
+      </c>
+      <c r="E47" s="25" t="inlineStr">
+        <is>
+          <t>村が100件程度集まるごとに随時送付</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="59" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="C48" s="60" t="inlineStr">
         <is>
           <t>令和8年11月</t>
         </is>
       </c>
-      <c r="D46" s="24" t="inlineStr">
-        <is>
-          <t>第1回策定委員会</t>
-        </is>
-      </c>
-      <c r="E46" s="25" t="inlineStr">
-        <is>
-          <t>委員改選の完了が前提</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="56" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="C47" s="57" t="inlineStr">
-        <is>
-          <t>令和8年12月中旬</t>
-        </is>
-      </c>
-      <c r="D47" s="57" t="inlineStr">
+      <c r="D48" s="60" t="inlineStr">
         <is>
           <t>第2回策定委員会</t>
         </is>
       </c>
-      <c r="E47" s="58" t="inlineStr">
-        <is>
-          <t>★12月を外すと第3回が3月となり履行期限に間に合わない</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="23" t="inlineStr"/>
-      <c r="C48" s="24" t="inlineStr">
-        <is>
-          <t>令和9年2月</t>
-        </is>
-      </c>
-      <c r="D48" s="24" t="inlineStr">
-        <is>
-          <t>第3回策定委員会</t>
-        </is>
-      </c>
-      <c r="E48" s="25" t="inlineStr"/>
+      <c r="E48" s="61" t="inlineStr">
+        <is>
+          <t>★分析結果・効果検証・骨子・体系・見込量・保険料概算・素案（完成度7割）</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="B49" s="23" t="inlineStr"/>
       <c r="C49" s="24" t="inlineStr">
         <is>
+          <t>令和8年11月〜12月</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="inlineStr">
+        <is>
+          <t>パブリックコメント</t>
+        </is>
+      </c>
+      <c r="E49" s="25" t="inlineStr">
+        <is>
+          <t>第2回委員会の後に実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="23" t="inlineStr"/>
+      <c r="C50" s="24" t="inlineStr">
+        <is>
+          <t>令和9年1月下旬〜2月上旬</t>
+        </is>
+      </c>
+      <c r="D50" s="24" t="inlineStr">
+        <is>
+          <t>第3回策定委員会</t>
+        </is>
+      </c>
+      <c r="E50" s="25" t="inlineStr">
+        <is>
+          <t>パブコメ結果と反映内容を報告。ほぼ完成版の素案で最終合意</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="23" t="inlineStr"/>
+      <c r="C51" s="24" t="inlineStr">
+        <is>
+          <t>令和9年2月末頃</t>
+        </is>
+      </c>
+      <c r="D51" s="24" t="inlineStr">
+        <is>
+          <t>議会全員協議会</t>
+        </is>
+      </c>
+      <c r="E51" s="25" t="inlineStr">
+        <is>
+          <t>概要版（A3両面程度）を用いて説明</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="23" t="inlineStr"/>
+      <c r="C52" s="24" t="inlineStr">
+        <is>
           <t>令和9年3月31日</t>
         </is>
       </c>
-      <c r="D49" s="24" t="inlineStr">
+      <c r="D52" s="24" t="inlineStr">
         <is>
           <t>履行期限（納品・検収）</t>
         </is>
       </c>
-      <c r="E49" s="25" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="B51" s="59" t="inlineStr">
+      <c r="E52" s="25" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="62" t="inlineStr">
         <is>
           <t>※「仕様書該当」欄の凡例：仕様書＝8北保福第483号 別紙／手引き＝厚生労働省の実施の手引き（令和7年8月版）／確認＝本業務での確認事項</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="59" t="inlineStr">
+    <row r="55">
+      <c r="B55" s="62" t="inlineStr">
         <is>
           <t>※ 想定時期は仕様書の履行期限（令和9年3月31日）から逆算した目安です。村との協議結果により確定します。</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" s="59" t="inlineStr">
+    <row r="56">
+      <c r="B56" s="62" t="inlineStr">
         <is>
           <t>※ 令和8年9月19日（土）〜23日（水）は5連休（敬老の日9/21・国民の休日9/22・秋分の日9/23）です。発送・回収工程に影響します。</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="59" t="inlineStr">
-        <is>
-          <t>※ 進捗基準日は令和8年9月2日です。備考欄の doc番号は docs/北塩原村_第10期/ 配下の分析資料に対応します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="59" t="inlineStr">
+    <row r="57">
+      <c r="B57" s="62" t="inlineStr">
+        <is>
+          <t>※ 進捗基準日は令和8年9月2日（キックオフ議事録の反映後）です。備考欄の doc番号は docs/北塩原村_第10期/ 配下の分析資料に対応します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="62" t="inlineStr">
         <is>
           <t>※ マイルストーンの★印は、遅れると後続工程が連鎖的に破綻する項目です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="62" t="inlineStr">
+        <is>
+          <t>※ 第1回策定委員会は受託前に開催済みのため、関連する2作業はステータス「対象外」としています。全体進捗率は対象外を除いて算出しています。</t>
         </is>
       </c>
     </row>
@@ -11629,9 +12320,9 @@
     <mergeCell ref="D5:H5"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B16:H16"/>
+    <mergeCell ref="B38:H38"/>
     <mergeCell ref="B11:H11"/>
     <mergeCell ref="C12:H12"/>
-    <mergeCell ref="B37:H37"/>
     <mergeCell ref="D9:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$81</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="M13" s="14" t="n"/>
       <c r="N13" s="15" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="P13" s="13" t="inlineStr">
         <is>
-          <t>資料B・C・C'をレビューし指摘一覧（村提出用1枚もの）を作成済（doc03・doc04・artifact06）。</t>
+          <t>★第1稿（0828版）を受領し令和7年8月版との全面突合を完了（doc23）。要修正：選択肢の順序が標準と逆になっている7か所（うち2か所は文字列の誤植）、標準様式の残骸3か所、問7の番号繰り上がり。村独自14問の採否を判定し、削除提案は問3(10)の1問のみ。</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="M14" s="14" t="n"/>
       <c r="N14" s="15" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="O14" s="16" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="P14" s="13" t="inlineStr">
         <is>
-          <t>同上。手法Ⅲ標準様式との差分を確定済。</t>
+          <t>★第1稿を受領し手法Ⅲ標準様式との突合を完了（doc23）。要修正：標準の問13「訪問診療」が削除され問13が欠番、前回指摘2件（介護療養型医療施設の削除・傷病の選択肢13/14の入替）が未反映、基準月が空欄。村独自の問0・問6-1は番号体系を壊さない適切な設計。</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="M16" s="14" t="n"/>
       <c r="N16" s="15" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="O16" s="16" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="P16" s="13" t="inlineStr">
         <is>
-          <t>「問6 就労について」は令和7年8月版でオプションと確定。採否は村協議待ち。</t>
+          <t>★第1稿はオプション項目をほぼ全採用。不採用は問7(7)「この1か月間に会った友人・知人の人数」の1問のみだが、番号を繰り上げているため見える化への入力時に対応が崩れる。ICF分析の参加軸に使えるため採用を推奨（doc23§1-2）。</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
       <c r="J17" s="14" t="n"/>
       <c r="K17" s="14" t="n"/>
       <c r="L17" s="14" t="n">
-        <v>46259</v>
+        <v>46267</v>
       </c>
       <c r="M17" s="14" t="n"/>
       <c r="N17" s="15" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
       <c r="O17" s="16" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="P17" s="13" t="inlineStr">
         <is>
-          <t>除雪・在宅医療・成年後見・歯科受診・服薬ほかの論点を整理済。確定は村協議後。</t>
+          <t>★第1稿に村独自14問（ニーズ調査）を確認し、1問ずつ採否を判定（doc23§4）。削除提案は問3(10)「1日に何回食事をとりますか」の1問のみで、他13問は施策・交付金の指標と結びつくため残置を推奨。問7(9)の自由記入3欄は入力コストのため簡素化を提案。在宅調査の問0・問6-1は適切。</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M19" s="14" t="n"/>
       <c r="N19" s="15" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="O19" s="16" t="inlineStr">
         <is>
@@ -6659,66 +6659,68 @@
       </c>
     </row>
     <row r="99" ht="30" customHeight="1">
-      <c r="A99" s="23" t="inlineStr">
+      <c r="A99" s="11" t="inlineStr">
         <is>
           <t>Ⅰ-95</t>
         </is>
       </c>
-      <c r="B99" s="24" t="inlineStr">
+      <c r="B99" s="12" t="inlineStr">
         <is>
           <t>Ⅰ ニーズ調査</t>
         </is>
       </c>
-      <c r="C99" s="24" t="inlineStr">
+      <c r="C99" s="12" t="inlineStr">
         <is>
           <t>Ⅰ-5 集計・分析</t>
         </is>
       </c>
-      <c r="D99" s="25" t="inlineStr">
+      <c r="D99" s="13" t="inlineStr">
         <is>
           <t>ICFの構成要素に基づくクロス分析の設計</t>
         </is>
       </c>
-      <c r="E99" s="23" t="inlineStr">
+      <c r="E99" s="11" t="inlineStr">
         <is>
           <t>確認</t>
         </is>
       </c>
-      <c r="F99" s="23" t="inlineStr">
+      <c r="F99" s="11" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G99" s="25" t="inlineStr">
+      <c r="G99" s="13" t="inlineStr">
         <is>
           <t>分析設計書</t>
         </is>
       </c>
-      <c r="H99" s="25" t="inlineStr">
+      <c r="H99" s="13" t="inlineStr">
         <is>
           <t>★議事録で新規要件。単純なリスク分析ではなくICFの健康度指標で「元気な高齢者」×「地域のニーズ」を分析。調査票設計段階で軸の確保が必要</t>
         </is>
       </c>
-      <c r="I99" s="23" t="inlineStr">
+      <c r="I99" s="11" t="inlineStr">
         <is>
           <t>R8.9上</t>
         </is>
       </c>
-      <c r="J99" s="26" t="n"/>
-      <c r="K99" s="26" t="n"/>
-      <c r="L99" s="26" t="n"/>
-      <c r="M99" s="26" t="n"/>
-      <c r="N99" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P99" s="25" t="inlineStr">
-        <is>
-          <t>★議事録で新規要件。単純なリスク分析ではなくICF（国際生活機能分類）等の健康度指標でクロス分析し、「元気な高齢者」×「地域のニーズ」から共助・互助の必要性を示す。調査票の第1稿段階でクロス軸を確保する必要があるため、9/3までに設問との対応表が要る。</t>
+      <c r="J99" s="14" t="n"/>
+      <c r="K99" s="14" t="n"/>
+      <c r="L99" s="14" t="n">
+        <v>46267</v>
+      </c>
+      <c r="M99" s="14" t="n"/>
+      <c r="N99" s="15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O99" s="16" t="inlineStr">
+        <is>
+          <t>着手</t>
+        </is>
+      </c>
+      <c r="P99" s="13" t="inlineStr">
+        <is>
+          <t>★doc23§3で設計完了。ICF5領域と標準設問の対応表を作成し、5領域すべてが標準の必須＋オプション項目で埋まること＝分析のための独自設問は不要であることを確定。分析案は3案（B:疾病×生活機能の2軸マトリクス〈主軸〉／A:生活機能ベースの4層区分〈施策設計用〉／C:5領域レーダー〈委員会資料〉）。推奨対応は標準オプション問7(7)の採用1件のみ。実装は回収データの受領後。</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7635,7 +7637,7 @@
       </c>
       <c r="D18" s="34" t="inlineStr">
         <is>
-          <t>障がい福祉計画は村名義。回収率に影響し得るため村長名を推奨するが村の慣行による。</t>
+          <t>★第1稿は「北塩原村長　遠藤　和夫」と村長名で作成済み。名義の可否と、あわせて現職の村長名が正しいかの確認が必要（当方が保有する平成30年の資料では別の方が村長）。</t>
         </is>
       </c>
       <c r="E18" s="35" t="inlineStr">
@@ -7645,12 +7647,12 @@
       </c>
       <c r="F18" s="35" t="inlineStr">
         <is>
-          <t>doc19 追-4</t>
+          <t>doc19 追-4／doc23§5</t>
         </is>
       </c>
       <c r="G18" s="35" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H18" s="34" t="inlineStr"/>
@@ -7732,34 +7734,34 @@
       <c r="H20" s="34" t="inlineStr"/>
     </row>
     <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="36" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A21" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
       <c r="B21" s="33" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C21" s="34" t="inlineStr">
         <is>
-          <t>★給付費適正化「主要3事業の全て実施」が令和7年度6点→令和8年度0点に低下した理由</t>
+          <t>★ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
         </is>
       </c>
       <c r="D21" s="34" t="inlineStr">
         <is>
-          <t>★全国該当率96.9%の指標。縦覧点検は4帳票満点のため、①要介護認定の適正化 か ②ケアプラン等の点検 のいずれかが実施されなくなった可能性。取組の後退か調査票の記載漏れかで対応が変わる。</t>
+          <t>★「その他」と「そのような人はいない／不明」の前後が一貫して逆。うち問7(5)「そのような人はいないその他」・問7(7)「いないその他」は文字列が結合した誤植。見える化の登録時に選択肢コードがずれる。手引きは選択肢の改変を明確に禁じている。</t>
         </is>
       </c>
       <c r="E21" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F21" s="35" t="inlineStr">
         <is>
-          <t>doc20§8-2 K-61</t>
+          <t>doc23§1-1</t>
         </is>
       </c>
       <c r="G21" s="35" t="inlineStr">
@@ -7770,34 +7772,34 @@
       <c r="H21" s="34" t="inlineStr"/>
     </row>
     <row r="22" ht="34" customHeight="1">
-      <c r="A22" s="36" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A22" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
       <c r="B22" s="33" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C22" s="34" t="inlineStr">
         <is>
-          <t>★福祉用具購入費・住宅改修費へのリハビリ専門職の関与（配点8点）が令和7年度8点→令和8年度0点に低下した理由</t>
+          <t>★在宅介護実態調査 標準の問13「訪問診療を利用していますか」の復活</t>
         </is>
       </c>
       <c r="D22" s="34" t="inlineStr">
         <is>
-          <t>★アと合わせ14点が1年で失われている。仕組みが失われたのか調査票の記載によるものかを確認。</t>
+          <t>★第1稿で削除され問13が欠番。オプション項目のため不採用は可だが、在宅医療は第10期の重点論点であり、交付金の支援目標Ⅲ（在宅医療・介護連携）が0点である本村で唯一の把握手段。番号が飛ぶと回答者も混乱する。</t>
         </is>
       </c>
       <c r="E22" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F22" s="35" t="inlineStr">
         <is>
-          <t>doc20§8-2 K-61b</t>
+          <t>doc23§2-1</t>
         </is>
       </c>
       <c r="G22" s="35" t="inlineStr">
@@ -7808,34 +7810,34 @@
       <c r="H22" s="34" t="inlineStr"/>
     </row>
     <row r="23" ht="34" customHeight="1">
-      <c r="A23" s="36" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A23" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
       <c r="B23" s="33" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C23" s="34" t="inlineStr">
         <is>
-          <t>認知症サポーター養成数・認知症地域支援推進員の配置と活動内容・チームオレンジの整備予定</t>
+          <t>★在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
         </is>
       </c>
       <c r="D23" s="34" t="inlineStr">
         <is>
-          <t>★支援交付金目標Ⅱ（認知症総合支援）は32/100点で全国平均51.1点を19点下回る唯一の目標。3か年で唯一低下局面があった。</t>
+          <t>★資料C'で指摘済みだが第1稿に未反映。介護療養型医療施設は令和6年3月末で廃止。傷病は標準が「13．眼科・耳鼻科疾患／14．その他」。</t>
         </is>
       </c>
       <c r="E23" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F23" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-62</t>
+          <t>doc23§2-2</t>
         </is>
       </c>
       <c r="G23" s="35" t="inlineStr">
@@ -7846,34 +7848,34 @@
       <c r="H23" s="34" t="inlineStr"/>
     </row>
     <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="36" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A24" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
       <c r="B24" s="33" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C24" s="34" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入の取組（健診での聴力チェック等）の有無</t>
+          <t>★ニーズ調査 問7(7)「この1か月間に会った友人・知人の人数」の採用可否</t>
         </is>
       </c>
       <c r="D24" s="34" t="inlineStr">
         <is>
-          <t>令和8年度評価で配点10点が0点（全国該当率48.8〜68.9%）。保健事業との連携で取得可能。</t>
+          <t>★第1稿では不採用のうえ以降の番号を繰り上げているため、見える化への入力時に設問の対応が崩れる。採用すれば番号ずれが解消し、かつICF分析の「参加」の量的指標としてそのまま使える。</t>
         </is>
       </c>
       <c r="E24" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F24" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-63</t>
+          <t>doc23§1-2</t>
         </is>
       </c>
       <c r="G24" s="35" t="inlineStr">
@@ -7884,34 +7886,34 @@
       <c r="H24" s="34" t="inlineStr"/>
     </row>
     <row r="25" ht="34" customHeight="1">
-      <c r="A25" s="36" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A25" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
       <c r="B25" s="33" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C25" s="34" t="inlineStr">
         <is>
-          <t>在宅医療・介護連携推進事業の実施体制（村単独か会津圏域か）と課題・対応策の検討の場</t>
+          <t>★ニーズ調査 村独自設問14問の採否と頁数（問3(10)の削除・問7(9)の簡素化）</t>
         </is>
       </c>
       <c r="D25" s="34" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲの「課題・対応策の検討」ア・エが0点（配点計10点、全国該当率57〜72%）。</t>
+          <t>★標準約66問＋村独自14問＝約79問。仕様書の目安A4約12頁を超える見込み。削除を提案するのは問3(10)「1日に何回食事をとりますか」の1問のみ（低栄養は問3(1)(7)(8)で把握可能）。他13問は施策・交付金の指標と結びついており残すべき。</t>
         </is>
       </c>
       <c r="E25" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅰ-12,Ⅰ-13</t>
         </is>
       </c>
       <c r="F25" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-64</t>
+          <t>doc23§4</t>
         </is>
       </c>
       <c r="G25" s="35" t="inlineStr">
@@ -7922,34 +7924,34 @@
       <c r="H25" s="34" t="inlineStr"/>
     </row>
     <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="36" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A26" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
       <c r="B26" s="33" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C26" s="34" t="inlineStr">
         <is>
-          <t>★施設サービスが伸びない要因「重度化による病院への転院」の裏づけデータ</t>
+          <t>★現職の村長名・所管課・役場の住所の確認</t>
         </is>
       </c>
       <c r="D26" s="34" t="inlineStr">
         <is>
-          <t>★議事録で示された村の見解。当方は村内施設ゼロ・村外施設依存の文脈で解釈していたため、素案の記述を修正する必要がある。KDB・給付実績で確認したい。</t>
+          <t>★第1稿の依頼状に「北塩原村長 遠藤 和夫」「保健福祉課 福祉係」「大字北山字姥ヶ作3151番地」と記載。当方では現職の村長名を確認できない。所管課は住民課との別が未確認のまま（doc01 確認事項1）。</t>
         </is>
       </c>
       <c r="E26" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅰ-14</t>
         </is>
       </c>
       <c r="F26" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-75</t>
+          <t>doc23§5</t>
         </is>
       </c>
       <c r="G26" s="35" t="inlineStr">
@@ -7967,27 +7969,27 @@
       </c>
       <c r="B27" s="33" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C27" s="34" t="inlineStr">
         <is>
-          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
+          <t>★給付費適正化「主要3事業の全て実施」が令和7年度6点→令和8年度0点に低下した理由</t>
         </is>
       </c>
       <c r="D27" s="34" t="inlineStr">
         <is>
-          <t>連絡体制表の確定。第9期概要版の発行は住民課。</t>
+          <t>★全国該当率96.9%の指標。縦覧点検は4帳票満点のため、①要介護認定の適正化 か ②ケアプラン等の点検 のいずれかが実施されなくなった可能性。取組の後退か調査票の記載漏れかで対応が変わる。</t>
         </is>
       </c>
       <c r="E27" s="35" t="inlineStr">
         <is>
-          <t>０-04</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F27" s="35" t="inlineStr">
         <is>
-          <t>doc01-1</t>
+          <t>doc20§8-2 K-61</t>
         </is>
       </c>
       <c r="G27" s="35" t="inlineStr">
@@ -8005,27 +8007,27 @@
       </c>
       <c r="B28" s="33" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>契約締結日・契約書の取り交わし状況</t>
+          <t>★福祉用具購入費・住宅改修費へのリハビリ専門職の関与（配点8点）が令和7年度8点→令和8年度0点に低下した理由</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>業務開始日の確定。</t>
+          <t>★アと合わせ14点が1年で失われている。仕組みが失われたのか調査票の記載によるものかを確認。</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
         <is>
-          <t>０-02</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F28" s="35" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>doc20§8-2 K-61b</t>
         </is>
       </c>
       <c r="G28" s="35" t="inlineStr">
@@ -8043,27 +8045,27 @@
       </c>
       <c r="B29" s="33" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
+          <t>認知症サポーター養成数・認知症地域支援推進員の配置と活動内容・チームオレンジの整備予定</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
+          <t>★支援交付金目標Ⅱ（認知症総合支援）は32/100点で全国平均51.1点を19点下回る唯一の目標。3か年で唯一低下局面があった。</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
         <is>
-          <t>０-06</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F29" s="35" t="inlineStr">
         <is>
-          <t>doc19 追-12</t>
+          <t>doc20§6-2 K-62</t>
         </is>
       </c>
       <c r="G29" s="35" t="inlineStr">
@@ -8081,27 +8083,27 @@
       </c>
       <c r="B30" s="33" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
+          <t>難聴高齢者の早期発見・早期介入の取組（健診での聴力チェック等）の有無</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
+          <t>令和8年度評価で配点10点が0点（全国該当率48.8〜68.9%）。保健事業との連携で取得可能。</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
         <is>
-          <t>Ⅴ-96</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F30" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-78</t>
+          <t>doc20§6-2 K-63</t>
         </is>
       </c>
       <c r="G30" s="35" t="inlineStr">
@@ -8119,27 +8121,27 @@
       </c>
       <c r="B31" s="33" t="inlineStr">
         <is>
-          <t>委員会</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
+          <t>在宅医療・介護連携推進事業の実施体制（村単独か会津圏域か）と課題・対応策の検討の場</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
+          <t>支援交付金目標Ⅲの「課題・対応策の検討」ア・エが0点（配点計10点、全国該当率57〜72%）。</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-80,Ⅱ-81</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F31" s="35" t="inlineStr">
         <is>
-          <t>doc01-6,doc19 追-15</t>
+          <t>doc20§6-2 K-64</t>
         </is>
       </c>
       <c r="G31" s="35" t="inlineStr">
@@ -8157,27 +8159,27 @@
       </c>
       <c r="B32" s="33" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C32" s="34" t="inlineStr">
         <is>
-          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
+          <t>★施設サービスが伸びない要因「重度化による病院への転院」の裏づけデータ</t>
         </is>
       </c>
       <c r="D32" s="34" t="inlineStr">
         <is>
-          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
+          <t>★議事録で示された村の見解。当方は村内施設ゼロ・村外施設依存の文脈で解釈していたため、素案の記述を修正する必要がある。KDB・給付実績で確認したい。</t>
         </is>
       </c>
       <c r="E32" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-76,Ⅱ-77</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F32" s="35" t="inlineStr">
         <is>
-          <t>doc01-7,doc19 指-3</t>
+          <t>doc22 K-75</t>
         </is>
       </c>
       <c r="G32" s="35" t="inlineStr">
@@ -8195,27 +8197,27 @@
       </c>
       <c r="B33" s="33" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C33" s="34" t="inlineStr">
         <is>
-          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
+          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
         </is>
       </c>
       <c r="D33" s="34" t="inlineStr">
         <is>
-          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
+          <t>連絡体制表の確定。第9期概要版の発行は住民課。</t>
         </is>
       </c>
       <c r="E33" s="35" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>０-04</t>
         </is>
       </c>
       <c r="F33" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-79</t>
+          <t>doc01-1</t>
         </is>
       </c>
       <c r="G33" s="35" t="inlineStr">
@@ -8233,27 +8235,27 @@
       </c>
       <c r="B34" s="33" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C34" s="34" t="inlineStr">
         <is>
-          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
+          <t>契約締結日・契約書の取り交わし状況</t>
         </is>
       </c>
       <c r="D34" s="34" t="inlineStr">
         <is>
-          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
+          <t>業務開始日の確定。</t>
         </is>
       </c>
       <c r="E34" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>０-02</t>
         </is>
       </c>
       <c r="F34" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-66</t>
+          <t>―</t>
         </is>
       </c>
       <c r="G34" s="35" t="inlineStr">
@@ -8271,27 +8273,27 @@
       </c>
       <c r="B35" s="33" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C35" s="34" t="inlineStr">
         <is>
-          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
+          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
         </is>
       </c>
       <c r="D35" s="34" t="inlineStr">
         <is>
-          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
+          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
         </is>
       </c>
       <c r="E35" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-62</t>
+          <t>０-06</t>
         </is>
       </c>
       <c r="F35" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-81</t>
+          <t>doc19 追-12</t>
         </is>
       </c>
       <c r="G35" s="35" t="inlineStr">
@@ -8309,27 +8311,27 @@
       </c>
       <c r="B36" s="33" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C36" s="34" t="inlineStr">
         <is>
-          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
+          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
         </is>
       </c>
       <c r="D36" s="34" t="inlineStr">
         <is>
-          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
+          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
         </is>
       </c>
       <c r="E36" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅴ-96</t>
         </is>
       </c>
       <c r="F36" s="35" t="inlineStr">
         <is>
-          <t>doc21§5 K-69</t>
+          <t>doc22 K-78</t>
         </is>
       </c>
       <c r="G36" s="35" t="inlineStr">
@@ -8347,27 +8349,27 @@
       </c>
       <c r="B37" s="33" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C37" s="34" t="inlineStr">
         <is>
-          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
+          <t>ICF分析は標準設問のみで完結することの確認</t>
         </is>
       </c>
       <c r="D37" s="34" t="inlineStr">
         <is>
-          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
+          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
         </is>
       </c>
       <c r="E37" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅰ-50</t>
         </is>
       </c>
       <c r="F37" s="35" t="inlineStr">
         <is>
-          <t>doc21§5 K-70</t>
+          <t>doc23§3-4</t>
         </is>
       </c>
       <c r="G37" s="35" t="inlineStr">
@@ -8385,301 +8387,301 @@
       </c>
       <c r="B38" s="33" t="inlineStr">
         <is>
+          <t>委員会</t>
+        </is>
+      </c>
+      <c r="C38" s="34" t="inlineStr">
+        <is>
+          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
+        </is>
+      </c>
+      <c r="D38" s="34" t="inlineStr">
+        <is>
+          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
+        </is>
+      </c>
+      <c r="E38" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-80,Ⅱ-81</t>
+        </is>
+      </c>
+      <c r="F38" s="35" t="inlineStr">
+        <is>
+          <t>doc01-6,doc19 追-15</t>
+        </is>
+      </c>
+      <c r="G38" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H38" s="34" t="inlineStr"/>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B39" s="33" t="inlineStr">
+        <is>
+          <t>成果品</t>
+        </is>
+      </c>
+      <c r="C39" s="34" t="inlineStr">
+        <is>
+          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
+        </is>
+      </c>
+      <c r="D39" s="34" t="inlineStr">
+        <is>
+          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
+        </is>
+      </c>
+      <c r="E39" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-76,Ⅱ-77</t>
+        </is>
+      </c>
+      <c r="F39" s="35" t="inlineStr">
+        <is>
+          <t>doc01-7,doc19 指-3</t>
+        </is>
+      </c>
+      <c r="G39" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H39" s="34" t="inlineStr"/>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B40" s="33" t="inlineStr">
+        <is>
+          <t>成果品</t>
+        </is>
+      </c>
+      <c r="C40" s="34" t="inlineStr">
+        <is>
+          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
+        </is>
+      </c>
+      <c r="D40" s="34" t="inlineStr">
+        <is>
+          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
+        </is>
+      </c>
+      <c r="E40" s="35" t="inlineStr">
+        <is>
+          <t>Ⅳ-92</t>
+        </is>
+      </c>
+      <c r="F40" s="35" t="inlineStr">
+        <is>
+          <t>doc22 K-79</t>
+        </is>
+      </c>
+      <c r="G40" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H40" s="34" t="inlineStr"/>
+    </row>
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B41" s="33" t="inlineStr">
+        <is>
+          <t>方針</t>
+        </is>
+      </c>
+      <c r="C41" s="34" t="inlineStr">
+        <is>
+          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
+        </is>
+      </c>
+      <c r="D41" s="34" t="inlineStr">
+        <is>
+          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
+        </is>
+      </c>
+      <c r="E41" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F41" s="35" t="inlineStr">
+        <is>
+          <t>doc20§6-2 K-66</t>
+        </is>
+      </c>
+      <c r="G41" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H41" s="34" t="inlineStr"/>
+    </row>
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B42" s="33" t="inlineStr">
+        <is>
+          <t>方針</t>
+        </is>
+      </c>
+      <c r="C42" s="34" t="inlineStr">
+        <is>
+          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
+        </is>
+      </c>
+      <c r="D42" s="34" t="inlineStr">
+        <is>
+          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
+        </is>
+      </c>
+      <c r="E42" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-62</t>
+        </is>
+      </c>
+      <c r="F42" s="35" t="inlineStr">
+        <is>
+          <t>doc22 K-81</t>
+        </is>
+      </c>
+      <c r="G42" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H42" s="34" t="inlineStr"/>
+    </row>
+    <row r="43" ht="34" customHeight="1">
+      <c r="A43" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B43" s="33" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C43" s="34" t="inlineStr">
+        <is>
+          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
+        </is>
+      </c>
+      <c r="D43" s="34" t="inlineStr">
+        <is>
+          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
+        </is>
+      </c>
+      <c r="E43" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F43" s="35" t="inlineStr">
+        <is>
+          <t>doc21§5 K-69</t>
+        </is>
+      </c>
+      <c r="G43" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H43" s="34" t="inlineStr"/>
+    </row>
+    <row r="44" ht="34" customHeight="1">
+      <c r="A44" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B44" s="33" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C44" s="34" t="inlineStr">
+        <is>
+          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
+        </is>
+      </c>
+      <c r="D44" s="34" t="inlineStr">
+        <is>
+          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
+        </is>
+      </c>
+      <c r="E44" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F44" s="35" t="inlineStr">
+        <is>
+          <t>doc21§5 K-70</t>
+        </is>
+      </c>
+      <c r="G44" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H44" s="34" t="inlineStr"/>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B45" s="33" t="inlineStr">
+        <is>
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C38" s="34" t="inlineStr">
+      <c r="C45" s="34" t="inlineStr">
         <is>
           <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
         </is>
       </c>
-      <c r="D38" s="34" t="inlineStr">
+      <c r="D45" s="34" t="inlineStr">
         <is>
           <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
         </is>
       </c>
-      <c r="E38" s="35" t="inlineStr">
+      <c r="E45" s="35" t="inlineStr">
         <is>
           <t>Ⅰ-19,Ⅰ-25</t>
         </is>
       </c>
-      <c r="F38" s="35" t="inlineStr">
+      <c r="F45" s="35" t="inlineStr">
         <is>
           <t>doc22 §1</t>
         </is>
       </c>
-      <c r="G38" s="35" t="inlineStr">
+      <c r="G45" s="35" t="inlineStr">
         <is>
           <t>一部回答</t>
         </is>
       </c>
-      <c r="H38" s="34" t="inlineStr"/>
-    </row>
-    <row r="39" ht="34" customHeight="1">
-      <c r="A39" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B39" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C39" s="25" t="inlineStr">
-        <is>
-          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
-        </is>
-      </c>
-      <c r="D39" s="25" t="inlineStr">
-        <is>
-          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
-        </is>
-      </c>
-      <c r="E39" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F39" s="23" t="inlineStr">
-        <is>
-          <t>doc02§22,doc08§8</t>
-        </is>
-      </c>
-      <c r="G39" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H39" s="25" t="inlineStr"/>
-    </row>
-    <row r="40" ht="34" customHeight="1">
-      <c r="A40" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B40" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C40" s="25" t="inlineStr">
-        <is>
-          <t>令和6年度決算および令和7年度の給付費見込</t>
-        </is>
-      </c>
-      <c r="D40" s="25" t="inlineStr">
-        <is>
-          <t>第9期の計画値と実績の乖離を確定させるために必要。</t>
-        </is>
-      </c>
-      <c r="E40" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
-        </is>
-      </c>
-      <c r="F40" s="23" t="inlineStr">
-        <is>
-          <t>doc08§8-1</t>
-        </is>
-      </c>
-      <c r="G40" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H40" s="25" t="inlineStr"/>
-    </row>
-    <row r="41" ht="34" customHeight="1">
-      <c r="A41" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B41" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C41" s="25" t="inlineStr">
-        <is>
-          <t>通いの場の実数（令和3〜7年度）</t>
-        </is>
-      </c>
-      <c r="D41" s="25" t="inlineStr">
-        <is>
-          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。</t>
-        </is>
-      </c>
-      <c r="E41" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F41" s="23" t="inlineStr">
-        <is>
-          <t>doc02§16,§22</t>
-        </is>
-      </c>
-      <c r="G41" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H41" s="25" t="inlineStr"/>
-    </row>
-    <row r="42" ht="34" customHeight="1">
-      <c r="A42" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B42" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C42" s="25" t="inlineStr">
-        <is>
-          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
-        </is>
-      </c>
-      <c r="D42" s="25" t="inlineStr">
-        <is>
-          <t>見える化に該当データがない。第9期は基本目標4-4に位置づけ。</t>
-        </is>
-      </c>
-      <c r="E42" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-68,Ⅱ-69</t>
-        </is>
-      </c>
-      <c r="F42" s="23" t="inlineStr">
-        <is>
-          <t>doc08§8-5</t>
-        </is>
-      </c>
-      <c r="G42" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H42" s="25" t="inlineStr"/>
-    </row>
-    <row r="43" ht="34" customHeight="1">
-      <c r="A43" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B43" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C43" s="25" t="inlineStr">
-        <is>
-          <t>高齢者福祉事業（村単独事業）の実績資料</t>
-        </is>
-      </c>
-      <c r="D43" s="25" t="inlineStr">
-        <is>
-          <t>現行計画の評価に必要。</t>
-        </is>
-      </c>
-      <c r="E43" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
-        </is>
-      </c>
-      <c r="F43" s="23" t="inlineStr">
-        <is>
-          <t>doc01-11</t>
-        </is>
-      </c>
-      <c r="G43" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H43" s="25" t="inlineStr"/>
-    </row>
-    <row r="44" ht="34" customHeight="1">
-      <c r="A44" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B44" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C44" s="25" t="inlineStr">
-        <is>
-          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
-        </is>
-      </c>
-      <c r="D44" s="25" t="inlineStr">
-        <is>
-          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
-        </is>
-      </c>
-      <c r="E44" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-58,Ⅱ-59</t>
-        </is>
-      </c>
-      <c r="F44" s="23" t="inlineStr">
-        <is>
-          <t>doc19 追-9</t>
-        </is>
-      </c>
-      <c r="G44" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H44" s="25" t="inlineStr"/>
-    </row>
-    <row r="45" ht="34" customHeight="1">
-      <c r="A45" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B45" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C45" s="25" t="inlineStr">
-        <is>
-          <t>介護保険事業状況報告（月報・年報）の原データの提供可否</t>
-        </is>
-      </c>
-      <c r="D45" s="25" t="inlineStr">
-        <is>
-          <t>見える化に収録されていない項目（サービス種類別利用者数の月次推移等）が扱えるようになる。</t>
-        </is>
-      </c>
-      <c r="E45" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-55</t>
-        </is>
-      </c>
-      <c r="F45" s="23" t="inlineStr">
-        <is>
-          <t>doc19 追-10</t>
-        </is>
-      </c>
-      <c r="G45" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H45" s="25" t="inlineStr"/>
+      <c r="H45" s="34" t="inlineStr"/>
     </row>
     <row r="46" ht="34" customHeight="1">
       <c r="A46" s="37" t="inlineStr">
@@ -8694,22 +8696,22 @@
       </c>
       <c r="C46" s="25" t="inlineStr">
         <is>
-          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
+          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
         </is>
       </c>
       <c r="D46" s="25" t="inlineStr">
         <is>
-          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
+          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
         </is>
       </c>
       <c r="E46" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F46" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc02§22,doc08§8</t>
         </is>
       </c>
       <c r="G46" s="23" t="inlineStr">
@@ -8732,22 +8734,22 @@
       </c>
       <c r="C47" s="25" t="inlineStr">
         <is>
-          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
+          <t>令和6年度決算および令和7年度の給付費見込</t>
         </is>
       </c>
       <c r="D47" s="25" t="inlineStr">
         <is>
-          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
+          <t>第9期の計画値と実績の乖離を確定させるために必要。</t>
         </is>
       </c>
       <c r="E47" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc08§8-1</t>
         </is>
       </c>
       <c r="G47" s="23" t="inlineStr">
@@ -8770,22 +8772,22 @@
       </c>
       <c r="C48" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
+          <t>通いの場の実数（令和3〜7年度）</t>
         </is>
       </c>
       <c r="D48" s="25" t="inlineStr">
         <is>
-          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
+          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。</t>
         </is>
       </c>
       <c r="E48" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F48" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc02§16,§22</t>
         </is>
       </c>
       <c r="G48" s="23" t="inlineStr">
@@ -8808,22 +8810,22 @@
       </c>
       <c r="C49" s="25" t="inlineStr">
         <is>
-          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
+          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
         </is>
       </c>
       <c r="D49" s="25" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
+          <t>見える化に該当データがない。第9期は基本目標4-4に位置づけ。</t>
         </is>
       </c>
       <c r="E49" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-68,Ⅱ-69</t>
         </is>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-65</t>
+          <t>doc08§8-5</t>
         </is>
       </c>
       <c r="G49" s="23" t="inlineStr">
@@ -8846,22 +8848,22 @@
       </c>
       <c r="C50" s="25" t="inlineStr">
         <is>
-          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
+          <t>高齢者福祉事業（村単独事業）の実績資料</t>
         </is>
       </c>
       <c r="D50" s="25" t="inlineStr">
         <is>
-          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
+          <t>現行計画の評価に必要。</t>
         </is>
       </c>
       <c r="E50" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F50" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-68</t>
+          <t>doc01-11</t>
         </is>
       </c>
       <c r="G50" s="23" t="inlineStr">
@@ -8884,22 +8886,22 @@
       </c>
       <c r="C51" s="25" t="inlineStr">
         <is>
-          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
+          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
         </is>
       </c>
       <c r="D51" s="25" t="inlineStr">
         <is>
-          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
+          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
         </is>
       </c>
       <c r="E51" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-58,Ⅱ-59</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-71</t>
+          <t>doc19 追-9</t>
         </is>
       </c>
       <c r="G51" s="23" t="inlineStr">
@@ -8922,22 +8924,22 @@
       </c>
       <c r="C52" s="25" t="inlineStr">
         <is>
-          <t>シルバー人材センターの会員数・受注実績</t>
+          <t>介護保険事業状況報告（月報・年報）の原データの提供可否</t>
         </is>
       </c>
       <c r="D52" s="25" t="inlineStr">
         <is>
-          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
+          <t>見える化に収録されていない項目（サービス種類別利用者数の月次推移等）が扱えるようになる。</t>
         </is>
       </c>
       <c r="E52" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F52" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-72</t>
+          <t>doc19 追-10</t>
         </is>
       </c>
       <c r="G52" s="23" t="inlineStr">
@@ -8955,27 +8957,27 @@
       </c>
       <c r="B53" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C53" s="25" t="inlineStr">
         <is>
-          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
+          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
         </is>
       </c>
       <c r="D53" s="25" t="inlineStr">
         <is>
-          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
+          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
         </is>
       </c>
       <c r="E53" s="23" t="inlineStr">
         <is>
-          <t>Ⅴ-95</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-67</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G53" s="23" t="inlineStr">
@@ -8993,27 +8995,27 @@
       </c>
       <c r="B54" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C54" s="25" t="inlineStr">
         <is>
-          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
+          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
         </is>
       </c>
       <c r="D54" s="25" t="inlineStr">
         <is>
-          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
+          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
         </is>
       </c>
       <c r="E54" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F54" s="23" t="inlineStr">
         <is>
-          <t>doc19 指-5</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G54" s="23" t="inlineStr">
@@ -9031,27 +9033,27 @@
       </c>
       <c r="B55" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C55" s="25" t="inlineStr">
         <is>
-          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
+          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
         </is>
       </c>
       <c r="D55" s="25" t="inlineStr">
         <is>
-          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
+          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
         </is>
       </c>
       <c r="E55" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-108</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t>doc22 K-80</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G55" s="23" t="inlineStr">
@@ -9069,27 +9071,27 @@
       </c>
       <c r="B56" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C56" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
+          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
         </is>
       </c>
       <c r="D56" s="25" t="inlineStr">
         <is>
-          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
+          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
         </is>
       </c>
       <c r="E56" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F56" s="23" t="inlineStr">
         <is>
-          <t>doc09§4,§10</t>
+          <t>doc20§6-2 K-65</t>
         </is>
       </c>
       <c r="G56" s="23" t="inlineStr">
@@ -9107,27 +9109,27 @@
       </c>
       <c r="B57" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C57" s="25" t="inlineStr">
         <is>
-          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
+          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
         </is>
       </c>
       <c r="D57" s="25" t="inlineStr">
         <is>
-          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
+          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
         </is>
       </c>
       <c r="E57" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t>doc09§8,§10</t>
+          <t>doc21§5 K-68</t>
         </is>
       </c>
       <c r="G57" s="23" t="inlineStr">
@@ -9145,27 +9147,27 @@
       </c>
       <c r="B58" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C58" s="25" t="inlineStr">
         <is>
-          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
+          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
         </is>
       </c>
       <c r="D58" s="25" t="inlineStr">
         <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
+          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
         </is>
       </c>
       <c r="E58" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F58" s="23" t="inlineStr">
         <is>
-          <t>doc02§17,doc07,doc18 4-1</t>
+          <t>doc21§5 K-71</t>
         </is>
       </c>
       <c r="G58" s="23" t="inlineStr">
@@ -9183,27 +9185,27 @@
       </c>
       <c r="B59" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C59" s="25" t="inlineStr">
         <is>
-          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
+          <t>シルバー人材センターの会員数・受注実績</t>
         </is>
       </c>
       <c r="D59" s="25" t="inlineStr">
         <is>
-          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
+          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
         </is>
       </c>
       <c r="E59" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
-          <t>doc17 C-1,doc02§20-2</t>
+          <t>doc21§5 K-72</t>
         </is>
       </c>
       <c r="G59" s="23" t="inlineStr">
@@ -9221,27 +9223,27 @@
       </c>
       <c r="B60" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C60" s="25" t="inlineStr">
         <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
         </is>
       </c>
       <c r="D60" s="25" t="inlineStr">
         <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
         </is>
       </c>
       <c r="E60" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
+          <t>Ⅴ-95</t>
         </is>
       </c>
       <c r="F60" s="23" t="inlineStr">
         <is>
-          <t>doc13§6</t>
+          <t>doc20§6-2 K-67</t>
         </is>
       </c>
       <c r="G60" s="23" t="inlineStr">
@@ -9259,27 +9261,27 @@
       </c>
       <c r="B61" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C61" s="25" t="inlineStr">
         <is>
-          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
         </is>
       </c>
       <c r="D61" s="25" t="inlineStr">
         <is>
-          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
+          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
         </is>
       </c>
       <c r="E61" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-14</t>
+          <t>doc19 指-5</t>
         </is>
       </c>
       <c r="G61" s="23" t="inlineStr">
@@ -9297,27 +9299,27 @@
       </c>
       <c r="B62" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C62" s="25" t="inlineStr">
         <is>
-          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
         </is>
       </c>
       <c r="D62" s="25" t="inlineStr">
         <is>
-          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
         </is>
       </c>
       <c r="E62" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-108</t>
         </is>
       </c>
       <c r="F62" s="23" t="inlineStr">
         <is>
-          <t>doc19 §3</t>
+          <t>doc22 K-80</t>
         </is>
       </c>
       <c r="G62" s="23" t="inlineStr">
@@ -9340,22 +9342,22 @@
       </c>
       <c r="C63" s="25" t="inlineStr">
         <is>
-          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
+          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
         </is>
       </c>
       <c r="D63" s="25" t="inlineStr">
         <is>
-          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
+          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
         </is>
       </c>
       <c r="E63" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-73</t>
+          <t>doc09§4,§10</t>
         </is>
       </c>
       <c r="G63" s="23" t="inlineStr">
@@ -9373,27 +9375,27 @@
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C64" s="25" t="inlineStr">
         <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
         </is>
       </c>
       <c r="D64" s="25" t="inlineStr">
         <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
         </is>
       </c>
       <c r="E64" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F64" s="23" t="inlineStr">
         <is>
-          <t>doc07§4</t>
+          <t>doc09§8,§10</t>
         </is>
       </c>
       <c r="G64" s="23" t="inlineStr">
@@ -9411,27 +9413,27 @@
       </c>
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C65" s="25" t="inlineStr">
         <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
         </is>
       </c>
       <c r="D65" s="25" t="inlineStr">
         <is>
-          <t>評価指標の読み方に影響。</t>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
         </is>
       </c>
       <c r="E65" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
-          <t>doc07§8-4</t>
+          <t>doc02§17,doc07,doc18 4-1</t>
         </is>
       </c>
       <c r="G65" s="23" t="inlineStr">
@@ -9449,27 +9451,27 @@
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C66" s="25" t="inlineStr">
         <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
         </is>
       </c>
       <c r="D66" s="25" t="inlineStr">
         <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
         </is>
       </c>
       <c r="E66" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-56,Ⅱ-75</t>
         </is>
       </c>
       <c r="F66" s="23" t="inlineStr">
         <is>
-          <t>doc08§4,§8-2</t>
+          <t>doc17 C-1,doc02§20-2</t>
         </is>
       </c>
       <c r="G66" s="23" t="inlineStr">
@@ -9487,27 +9489,27 @@
       </c>
       <c r="B67" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C67" s="25" t="inlineStr">
         <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
         </is>
       </c>
       <c r="D67" s="25" t="inlineStr">
         <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
         </is>
       </c>
       <c r="E67" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-60,Ⅱ-65</t>
         </is>
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
-          <t>doc02§20-1</t>
+          <t>doc13§6</t>
         </is>
       </c>
       <c r="G67" s="23" t="inlineStr">
@@ -9525,27 +9527,27 @@
       </c>
       <c r="B68" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C68" s="25" t="inlineStr">
         <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
         </is>
       </c>
       <c r="D68" s="25" t="inlineStr">
         <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
         </is>
       </c>
       <c r="E68" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F68" s="23" t="inlineStr">
         <is>
-          <t>doc15,doc18</t>
+          <t>doc19 追-14</t>
         </is>
       </c>
       <c r="G68" s="23" t="inlineStr">
@@ -9563,27 +9565,27 @@
       </c>
       <c r="B69" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C69" s="25" t="inlineStr">
         <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
         </is>
       </c>
       <c r="D69" s="25" t="inlineStr">
         <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
         </is>
       </c>
       <c r="E69" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F69" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc18 3-1</t>
+          <t>doc19 §3</t>
         </is>
       </c>
       <c r="G69" s="23" t="inlineStr">
@@ -9601,27 +9603,27 @@
       </c>
       <c r="B70" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C70" s="25" t="inlineStr">
         <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
         </is>
       </c>
       <c r="D70" s="25" t="inlineStr">
         <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
         </is>
       </c>
       <c r="E70" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F70" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
+          <t>doc21§5 K-73</t>
         </is>
       </c>
       <c r="G70" s="23" t="inlineStr">
@@ -9639,27 +9641,27 @@
       </c>
       <c r="B71" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C71" s="25" t="inlineStr">
         <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
         </is>
       </c>
       <c r="D71" s="25" t="inlineStr">
         <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
         </is>
       </c>
       <c r="E71" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
-          <t>doc17 B-3,doc18 4-3</t>
+          <t>doc07§4</t>
         </is>
       </c>
       <c r="G71" s="23" t="inlineStr">
@@ -9677,27 +9679,27 @@
       </c>
       <c r="B72" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C72" s="25" t="inlineStr">
         <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
         </is>
       </c>
       <c r="D72" s="25" t="inlineStr">
         <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+          <t>評価指標の読み方に影響。</t>
         </is>
       </c>
       <c r="E72" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F72" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 2-9</t>
+          <t>doc07§8-4</t>
         </is>
       </c>
       <c r="G72" s="23" t="inlineStr">
@@ -9715,27 +9717,27 @@
       </c>
       <c r="B73" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C73" s="25" t="inlineStr">
         <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
         </is>
       </c>
       <c r="D73" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
         </is>
       </c>
       <c r="E73" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F73" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 5-7</t>
+          <t>doc08§4,§8-2</t>
         </is>
       </c>
       <c r="G73" s="23" t="inlineStr">
@@ -9753,27 +9755,27 @@
       </c>
       <c r="B74" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C74" s="25" t="inlineStr">
         <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
         </is>
       </c>
       <c r="D74" s="25" t="inlineStr">
         <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
         </is>
       </c>
       <c r="E74" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F74" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-4</t>
+          <t>doc02§20-1</t>
         </is>
       </c>
       <c r="G74" s="23" t="inlineStr">
@@ -9791,27 +9793,27 @@
       </c>
       <c r="B75" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C75" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
         </is>
       </c>
       <c r="D75" s="25" t="inlineStr">
         <is>
-          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
         </is>
       </c>
       <c r="E75" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-73,Ⅱ-75</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F75" s="23" t="inlineStr">
         <is>
-          <t>doc01-5,doc18 1-2</t>
+          <t>doc15,doc18</t>
         </is>
       </c>
       <c r="G75" s="23" t="inlineStr">
@@ -9829,27 +9831,27 @@
       </c>
       <c r="B76" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C76" s="25" t="inlineStr">
         <is>
-          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
         </is>
       </c>
       <c r="D76" s="25" t="inlineStr">
         <is>
-          <t>施策の書きぶりに影響。</t>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
         </is>
       </c>
       <c r="E76" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-72</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F76" s="23" t="inlineStr">
         <is>
-          <t>doc01-12</t>
+          <t>doc14§5,doc18 3-1</t>
         </is>
       </c>
       <c r="G76" s="23" t="inlineStr">
@@ -9867,27 +9869,27 @@
       </c>
       <c r="B77" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C77" s="25" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
         </is>
       </c>
       <c r="D77" s="25" t="inlineStr">
         <is>
-          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
         </is>
       </c>
       <c r="E77" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F77" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-13</t>
+          <t>doc14§5,doc15,doc18 4-5</t>
         </is>
       </c>
       <c r="G77" s="23" t="inlineStr">
@@ -9905,27 +9907,27 @@
       </c>
       <c r="B78" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C78" s="25" t="inlineStr">
         <is>
-          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
         </is>
       </c>
       <c r="D78" s="25" t="inlineStr">
         <is>
-          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
         </is>
       </c>
       <c r="E78" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-31</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F78" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-6</t>
+          <t>doc17 B-3,doc18 4-3</t>
         </is>
       </c>
       <c r="G78" s="23" t="inlineStr">
@@ -9943,422 +9945,422 @@
       </c>
       <c r="B79" s="24" t="inlineStr">
         <is>
+          <t>素案</t>
+        </is>
+      </c>
+      <c r="C79" s="25" t="inlineStr">
+        <is>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+        </is>
+      </c>
+      <c r="D79" s="25" t="inlineStr">
+        <is>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+        </is>
+      </c>
+      <c r="E79" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F79" s="23" t="inlineStr">
+        <is>
+          <t>doc17 A-1,doc18 2-9</t>
+        </is>
+      </c>
+      <c r="G79" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H79" s="25" t="inlineStr"/>
+    </row>
+    <row r="80" ht="34" customHeight="1">
+      <c r="A80" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B80" s="24" t="inlineStr">
+        <is>
+          <t>素案</t>
+        </is>
+      </c>
+      <c r="C80" s="25" t="inlineStr">
+        <is>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+        </is>
+      </c>
+      <c r="D80" s="25" t="inlineStr">
+        <is>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+        </is>
+      </c>
+      <c r="E80" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-64,Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F80" s="23" t="inlineStr">
+        <is>
+          <t>doc17 A-1,doc18 5-7</t>
+        </is>
+      </c>
+      <c r="G80" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H80" s="25" t="inlineStr"/>
+    </row>
+    <row r="81" ht="34" customHeight="1">
+      <c r="A81" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B81" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C81" s="25" t="inlineStr">
+        <is>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
+        </is>
+      </c>
+      <c r="D81" s="25" t="inlineStr">
+        <is>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+        </is>
+      </c>
+      <c r="E81" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F81" s="23" t="inlineStr">
+        <is>
+          <t>doc08§8-4</t>
+        </is>
+      </c>
+      <c r="G81" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H81" s="25" t="inlineStr"/>
+    </row>
+    <row r="82" ht="34" customHeight="1">
+      <c r="A82" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B82" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C82" s="25" t="inlineStr">
+        <is>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+        </is>
+      </c>
+      <c r="D82" s="25" t="inlineStr">
+        <is>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+        </is>
+      </c>
+      <c r="E82" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-73,Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F82" s="23" t="inlineStr">
+        <is>
+          <t>doc01-5,doc18 1-2</t>
+        </is>
+      </c>
+      <c r="G82" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H82" s="25" t="inlineStr"/>
+    </row>
+    <row r="83" ht="34" customHeight="1">
+      <c r="A83" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B83" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C83" s="25" t="inlineStr">
+        <is>
+          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+        </is>
+      </c>
+      <c r="D83" s="25" t="inlineStr">
+        <is>
+          <t>施策の書きぶりに影響。</t>
+        </is>
+      </c>
+      <c r="E83" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-71,Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F83" s="23" t="inlineStr">
+        <is>
+          <t>doc01-12</t>
+        </is>
+      </c>
+      <c r="G83" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H83" s="25" t="inlineStr"/>
+    </row>
+    <row r="84" ht="34" customHeight="1">
+      <c r="A84" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B84" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C84" s="25" t="inlineStr">
+        <is>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+        </is>
+      </c>
+      <c r="D84" s="25" t="inlineStr">
+        <is>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+        </is>
+      </c>
+      <c r="E84" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F84" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-13</t>
+        </is>
+      </c>
+      <c r="G84" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H84" s="25" t="inlineStr"/>
+    </row>
+    <row r="85" ht="34" customHeight="1">
+      <c r="A85" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B85" s="24" t="inlineStr">
+        <is>
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C79" s="25" t="inlineStr">
+      <c r="C85" s="25" t="inlineStr">
+        <is>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+        </is>
+      </c>
+      <c r="D85" s="25" t="inlineStr">
+        <is>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+        </is>
+      </c>
+      <c r="E85" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-31</t>
+        </is>
+      </c>
+      <c r="F85" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-6</t>
+        </is>
+      </c>
+      <c r="G85" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H85" s="25" t="inlineStr"/>
+    </row>
+    <row r="86" ht="34" customHeight="1">
+      <c r="A86" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B86" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C86" s="25" t="inlineStr">
         <is>
           <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
         </is>
       </c>
-      <c r="D79" s="25" t="inlineStr">
+      <c r="D86" s="25" t="inlineStr">
         <is>
           <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
         </is>
       </c>
-      <c r="E79" s="23" t="inlineStr">
+      <c r="E86" s="23" t="inlineStr">
         <is>
           <t>Ⅰ-40,Ⅰ-42</t>
         </is>
       </c>
-      <c r="F79" s="23" t="inlineStr">
+      <c r="F86" s="23" t="inlineStr">
         <is>
           <t>doc19 追-7</t>
         </is>
       </c>
-      <c r="G79" s="23" t="inlineStr">
+      <c r="G86" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H79" s="25" t="inlineStr"/>
-    </row>
-    <row r="80" ht="34" customHeight="1">
-      <c r="A80" s="38" t="inlineStr">
+      <c r="H86" s="25" t="inlineStr"/>
+    </row>
+    <row r="87" ht="34" customHeight="1">
+      <c r="A87" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B87" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C87" s="25" t="inlineStr">
+        <is>
+          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+        </is>
+      </c>
+      <c r="D87" s="25" t="inlineStr">
+        <is>
+          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+        </is>
+      </c>
+      <c r="E87" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-09</t>
+        </is>
+      </c>
+      <c r="F87" s="23" t="inlineStr">
+        <is>
+          <t>doc23§1-3</t>
+        </is>
+      </c>
+      <c r="G87" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H87" s="25" t="inlineStr"/>
+    </row>
+    <row r="88" ht="34" customHeight="1">
+      <c r="A88" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B80" s="24" t="inlineStr">
+      <c r="B88" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C80" s="25" t="inlineStr">
+      <c r="C88" s="25" t="inlineStr">
         <is>
           <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
         </is>
       </c>
-      <c r="D80" s="25" t="inlineStr">
+      <c r="D88" s="25" t="inlineStr">
         <is>
           <t>第9期はA4・本文104頁・全6章＋資料編。</t>
         </is>
       </c>
-      <c r="E80" s="23" t="inlineStr">
+      <c r="E88" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-89</t>
         </is>
       </c>
-      <c r="F80" s="23" t="inlineStr">
+      <c r="F88" s="23" t="inlineStr">
         <is>
           <t>doc01-10</t>
         </is>
       </c>
-      <c r="G80" s="23" t="inlineStr">
+      <c r="G88" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H80" s="25" t="inlineStr"/>
-    </row>
-    <row r="81" ht="34" customHeight="1">
-      <c r="A81" s="38" t="inlineStr">
+      <c r="H88" s="25" t="inlineStr"/>
+    </row>
+    <row r="89" ht="34" customHeight="1">
+      <c r="A89" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B81" s="24" t="inlineStr">
+      <c r="B89" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C81" s="25" t="inlineStr">
+      <c r="C89" s="25" t="inlineStr">
         <is>
           <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
         </is>
       </c>
-      <c r="D81" s="25" t="inlineStr">
+      <c r="D89" s="25" t="inlineStr">
         <is>
           <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
         </is>
       </c>
-      <c r="E81" s="23" t="inlineStr">
+      <c r="E89" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-92</t>
         </is>
       </c>
-      <c r="F81" s="23" t="inlineStr">
+      <c r="F89" s="23" t="inlineStr">
         <is>
           <t>doc01-10,doc08</t>
         </is>
       </c>
-      <c r="G81" s="23" t="inlineStr">
+      <c r="G89" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H81" s="25" t="inlineStr"/>
-    </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="39" t="inlineStr">
+      <c r="H89" s="25" t="inlineStr"/>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="39" t="inlineStr">
         <is>
           <t>■ 解決済み（記録）</t>
         </is>
       </c>
-    </row>
-    <row r="84" ht="34" customHeight="1">
-      <c r="A84" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B84" s="41" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C84" s="42" t="inlineStr">
-        <is>
-          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
-        </is>
-      </c>
-      <c r="D84" s="42" t="inlineStr">
-        <is>
-          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
-        </is>
-      </c>
-      <c r="E84" s="40" t="inlineStr">
-        <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
-        </is>
-      </c>
-      <c r="F84" s="40" t="inlineStr">
-        <is>
-          <t>doc22 §1</t>
-        </is>
-      </c>
-      <c r="G84" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H84" s="42" t="inlineStr"/>
-    </row>
-    <row r="85" ht="34" customHeight="1">
-      <c r="A85" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B85" s="41" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C85" s="42" t="inlineStr">
-        <is>
-          <t>在宅介護実態調査 約150人の抽出基準</t>
-        </is>
-      </c>
-      <c r="D85" s="42" t="inlineStr">
-        <is>
-          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
-        </is>
-      </c>
-      <c r="E85" s="40" t="inlineStr">
-        <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
-        </is>
-      </c>
-      <c r="F85" s="40" t="inlineStr">
-        <is>
-          <t>doc22 §1</t>
-        </is>
-      </c>
-      <c r="G85" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H85" s="42" t="inlineStr"/>
-    </row>
-    <row r="86" ht="34" customHeight="1">
-      <c r="A86" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B86" s="41" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C86" s="42" t="inlineStr">
-        <is>
-          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
-        </is>
-      </c>
-      <c r="D86" s="42" t="inlineStr">
-        <is>
-          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
-        </is>
-      </c>
-      <c r="E86" s="40" t="inlineStr">
-        <is>
-          <t>Ⅰ-25,Ⅰ-26</t>
-        </is>
-      </c>
-      <c r="F86" s="40" t="inlineStr">
-        <is>
-          <t>doc22 §1</t>
-        </is>
-      </c>
-      <c r="G86" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H86" s="42" t="inlineStr"/>
-    </row>
-    <row r="87" ht="34" customHeight="1">
-      <c r="A87" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B87" s="41" t="inlineStr">
-        <is>
-          <t>計画構成</t>
-        </is>
-      </c>
-      <c r="C87" s="42" t="inlineStr">
-        <is>
-          <t>整合を図る関連計画の範囲</t>
-        </is>
-      </c>
-      <c r="D87" s="42" t="inlineStr">
-        <is>
-          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
-        </is>
-      </c>
-      <c r="E87" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-72</t>
-        </is>
-      </c>
-      <c r="F87" s="40" t="inlineStr">
-        <is>
-          <t>doc22 §1</t>
-        </is>
-      </c>
-      <c r="G87" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H87" s="42" t="inlineStr"/>
-    </row>
-    <row r="88" ht="34" customHeight="1">
-      <c r="A88" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B88" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C88" s="42" t="inlineStr">
-        <is>
-          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
-        </is>
-      </c>
-      <c r="D88" s="42" t="inlineStr">
-        <is>
-          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
-        </is>
-      </c>
-      <c r="E88" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F88" s="40" t="inlineStr">
-        <is>
-          <t>doc20§3,§4</t>
-        </is>
-      </c>
-      <c r="G88" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H88" s="42" t="inlineStr"/>
-    </row>
-    <row r="89" ht="34" customHeight="1">
-      <c r="A89" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B89" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C89" s="42" t="inlineStr">
-        <is>
-          <t>交付要綱の配点表（満点）</t>
-        </is>
-      </c>
-      <c r="D89" s="42" t="inlineStr">
-        <is>
-          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
-        </is>
-      </c>
-      <c r="E89" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F89" s="40" t="inlineStr">
-        <is>
-          <t>doc20§2</t>
-        </is>
-      </c>
-      <c r="G89" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H89" s="42" t="inlineStr"/>
-    </row>
-    <row r="90" ht="34" customHeight="1">
-      <c r="A90" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B90" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C90" s="42" t="inlineStr">
-        <is>
-          <t>令和6年度・令和7年度の交付金評価結果</t>
-        </is>
-      </c>
-      <c r="D90" s="42" t="inlineStr">
-        <is>
-          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
-        </is>
-      </c>
-      <c r="E90" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F90" s="40" t="inlineStr">
-        <is>
-          <t>doc20§3-1</t>
-        </is>
-      </c>
-      <c r="G90" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H90" s="42" t="inlineStr"/>
-    </row>
-    <row r="91" ht="34" customHeight="1">
-      <c r="A91" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B91" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C91" s="42" t="inlineStr">
-        <is>
-          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
-        </is>
-      </c>
-      <c r="D91" s="42" t="inlineStr">
-        <is>
-          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
-        </is>
-      </c>
-      <c r="E91" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-56,Ⅱ-58</t>
-        </is>
-      </c>
-      <c r="F91" s="40" t="inlineStr">
-        <is>
-          <t>doc09</t>
-        </is>
-      </c>
-      <c r="G91" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H91" s="42" t="inlineStr"/>
     </row>
     <row r="92" ht="34" customHeight="1">
       <c r="A92" s="40" t="inlineStr">
@@ -10368,27 +10370,27 @@
       </c>
       <c r="B92" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C92" s="42" t="inlineStr">
         <is>
-          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="D92" s="42" t="inlineStr">
         <is>
-          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
         </is>
       </c>
       <c r="E92" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F92" s="40" t="inlineStr">
         <is>
-          <t>doc02§20-2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G92" s="40" t="inlineStr">
@@ -10406,48 +10408,352 @@
       </c>
       <c r="B93" s="41" t="inlineStr">
         <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C93" s="42" t="inlineStr">
+        <is>
+          <t>在宅介護実態調査 約150人の抽出基準</t>
+        </is>
+      </c>
+      <c r="D93" s="42" t="inlineStr">
+        <is>
+          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
+        </is>
+      </c>
+      <c r="E93" s="40" t="inlineStr">
+        <is>
+          <t>Ⅰ-08,Ⅰ-24</t>
+        </is>
+      </c>
+      <c r="F93" s="40" t="inlineStr">
+        <is>
+          <t>doc22 §1</t>
+        </is>
+      </c>
+      <c r="G93" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H93" s="42" t="inlineStr"/>
+    </row>
+    <row r="94" ht="34" customHeight="1">
+      <c r="A94" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B94" s="41" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C94" s="42" t="inlineStr">
+        <is>
+          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
+        </is>
+      </c>
+      <c r="D94" s="42" t="inlineStr">
+        <is>
+          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
+        </is>
+      </c>
+      <c r="E94" s="40" t="inlineStr">
+        <is>
+          <t>Ⅰ-25,Ⅰ-26</t>
+        </is>
+      </c>
+      <c r="F94" s="40" t="inlineStr">
+        <is>
+          <t>doc22 §1</t>
+        </is>
+      </c>
+      <c r="G94" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H94" s="42" t="inlineStr"/>
+    </row>
+    <row r="95" ht="34" customHeight="1">
+      <c r="A95" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B95" s="41" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C95" s="42" t="inlineStr">
+        <is>
+          <t>整合を図る関連計画の範囲</t>
+        </is>
+      </c>
+      <c r="D95" s="42" t="inlineStr">
+        <is>
+          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+        </is>
+      </c>
+      <c r="E95" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F95" s="40" t="inlineStr">
+        <is>
+          <t>doc22 §1</t>
+        </is>
+      </c>
+      <c r="G95" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H95" s="42" t="inlineStr"/>
+    </row>
+    <row r="96" ht="34" customHeight="1">
+      <c r="A96" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B96" s="41" t="inlineStr">
+        <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="C93" s="42" t="inlineStr">
+      <c r="C96" s="42" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+        </is>
+      </c>
+      <c r="D96" s="42" t="inlineStr">
+        <is>
+          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+        </is>
+      </c>
+      <c r="E96" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F96" s="40" t="inlineStr">
+        <is>
+          <t>doc20§3,§4</t>
+        </is>
+      </c>
+      <c r="G96" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H96" s="42" t="inlineStr"/>
+    </row>
+    <row r="97" ht="34" customHeight="1">
+      <c r="A97" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B97" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C97" s="42" t="inlineStr">
+        <is>
+          <t>交付要綱の配点表（満点）</t>
+        </is>
+      </c>
+      <c r="D97" s="42" t="inlineStr">
+        <is>
+          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+        </is>
+      </c>
+      <c r="E97" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F97" s="40" t="inlineStr">
+        <is>
+          <t>doc20§2</t>
+        </is>
+      </c>
+      <c r="G97" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H97" s="42" t="inlineStr"/>
+    </row>
+    <row r="98" ht="34" customHeight="1">
+      <c r="A98" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B98" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C98" s="42" t="inlineStr">
+        <is>
+          <t>令和6年度・令和7年度の交付金評価結果</t>
+        </is>
+      </c>
+      <c r="D98" s="42" t="inlineStr">
+        <is>
+          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+        </is>
+      </c>
+      <c r="E98" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F98" s="40" t="inlineStr">
+        <is>
+          <t>doc20§3-1</t>
+        </is>
+      </c>
+      <c r="G98" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H98" s="42" t="inlineStr"/>
+    </row>
+    <row r="99" ht="34" customHeight="1">
+      <c r="A99" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B99" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C99" s="42" t="inlineStr">
+        <is>
+          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+        </is>
+      </c>
+      <c r="D99" s="42" t="inlineStr">
+        <is>
+          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+        </is>
+      </c>
+      <c r="E99" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-56,Ⅱ-58</t>
+        </is>
+      </c>
+      <c r="F99" s="40" t="inlineStr">
+        <is>
+          <t>doc09</t>
+        </is>
+      </c>
+      <c r="G99" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H99" s="42" t="inlineStr"/>
+    </row>
+    <row r="100" ht="34" customHeight="1">
+      <c r="A100" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B100" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C100" s="42" t="inlineStr">
+        <is>
+          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+        </is>
+      </c>
+      <c r="D100" s="42" t="inlineStr">
+        <is>
+          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+        </is>
+      </c>
+      <c r="E100" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-59</t>
+        </is>
+      </c>
+      <c r="F100" s="40" t="inlineStr">
+        <is>
+          <t>doc02§20-2</t>
+        </is>
+      </c>
+      <c r="G100" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H100" s="42" t="inlineStr"/>
+    </row>
+    <row r="101" ht="34" customHeight="1">
+      <c r="A101" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B101" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C101" s="42" t="inlineStr">
         <is>
           <t>国の指針・様式の更新有無</t>
         </is>
       </c>
-      <c r="D93" s="42" t="inlineStr">
+      <c r="D101" s="42" t="inlineStr">
         <is>
           <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
-      <c r="E93" s="40" t="inlineStr">
+      <c r="E101" s="40" t="inlineStr">
         <is>
           <t>Ⅰ-11</t>
         </is>
       </c>
-      <c r="F93" s="40" t="inlineStr">
+      <c r="F101" s="40" t="inlineStr">
         <is>
           <t>doc04,doc05</t>
         </is>
       </c>
-      <c r="G93" s="40" t="inlineStr">
+      <c r="G101" s="40" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H93" s="42" t="inlineStr"/>
+      <c r="H101" s="42" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H81"/>
+  <autoFilter ref="A4:H89"/>
   <mergeCells count="3">
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A83:H83"/>
+    <mergeCell ref="A91:H91"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10461,7 +10767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11195,17 +11501,17 @@
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>国資料</t>
+          <t>調査票</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>令和8年度 交付金評価指標（市町村分）配点表</t>
+          <t>調査票 第1稿（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>全17頁。推進400点・支援400点、目標Ⅰ〜Ⅳ各100点</t>
+          <t>0828版。令和7年8月版・手法Ⅲ標準様式と全面突合</t>
         </is>
       </c>
       <c r="D27" s="43" t="n">
@@ -11213,7 +11519,7 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>docs/…/20_交付金評価結果分析.md</t>
+          <t>docs/…/23_調査票第1稿レビュー_ICF分析設計.md</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -11230,12 +11536,12 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>令和6年度 該当状況調査票集計表（全国一覧表）</t>
+          <t>令和8年度 交付金評価指標（市町村分）配点表</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>全国1,741市町村。村は第398行。合計295点</t>
+          <t>全17頁。推進400点・支援400点、目標Ⅰ〜Ⅳ各100点</t>
         </is>
       </c>
       <c r="D28" s="43" t="n">
@@ -11260,12 +11566,12 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>令和7年度 該当状況調査票集計表（全国集計・市町村）</t>
+          <t>令和6年度 該当状況調査票集計表（全国一覧表）</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>合計339点。全国平均435.0点</t>
+          <t>全国1,741市町村。村は第398行。合計295点</t>
         </is>
       </c>
       <c r="D29" s="43" t="n">
@@ -11290,12 +11596,12 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>令和8年度 該当状況調査票集計表（全国集計・市町村）</t>
+          <t>令和7年度 該当状況調査票集計表（全国集計・市町村）</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>合計447点。全国平均455.1点／全国1,005位／県内34位</t>
+          <t>合計339点。全国平均435.0点</t>
         </is>
       </c>
       <c r="D30" s="43" t="n">
@@ -11315,17 +11621,17 @@
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>関連計画</t>
+          <t>国資料</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>第四次北塩原村生涯学習推進計画</t>
+          <t>令和8年度 該当状況調査票集計表（全国集計・市町村）</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>全112頁。2018〜2027年度。7z分割書庫4分割で受領</t>
+          <t>合計447点。全国平均455.1点／全国1,005位／県内34位</t>
         </is>
       </c>
       <c r="D31" s="43" t="n">
@@ -11333,49 +11639,79 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
+          <t>docs/…/20_交付金評価結果分析.md</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>関連計画</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>第四次北塩原村生涯学習推進計画</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>全112頁。2018〜2027年度。7z分割書庫4分割で受領</t>
+        </is>
+      </c>
+      <c r="D32" s="43" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
           <t>docs/…/21_関連計画_第四次生涯学習推進計画.md</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>受領済</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="35" t="inlineStr">
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="35" t="inlineStr">
         <is>
           <t>村データ</t>
         </is>
       </c>
-      <c r="B32" s="34" t="inlineStr">
+      <c r="B33" s="34" t="inlineStr">
         <is>
           <t>★要介護認定データ（調査票との関連付け用）</t>
         </is>
       </c>
-      <c r="C32" s="34" t="inlineStr">
+      <c r="C33" s="34" t="inlineStr">
         <is>
           <t>仕様書4Ⅰ(5)。調査回収後に必要</t>
         </is>
       </c>
-      <c r="D32" s="35" t="inlineStr">
+      <c r="D33" s="35" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E32" s="34" t="inlineStr">
+      <c r="E33" s="34" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F32" s="35" t="inlineStr">
+      <c r="F33" s="35" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F32"/>
+  <autoFilter ref="A4:F33"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$94</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3193,176 +3193,194 @@
       <c r="P42" s="20" t="inlineStr"/>
     </row>
     <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="23" t="inlineStr">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>Ⅰ-39</t>
         </is>
       </c>
-      <c r="B43" s="24" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>Ⅰ ニーズ調査</t>
         </is>
       </c>
-      <c r="C43" s="24" t="inlineStr">
+      <c r="C43" s="12" t="inlineStr">
         <is>
           <t>Ⅰ-5 集計・分析</t>
         </is>
       </c>
-      <c r="D43" s="25" t="inlineStr">
+      <c r="D43" s="13" t="inlineStr">
         <is>
           <t>単純集計</t>
         </is>
       </c>
-      <c r="E43" s="23" t="inlineStr">
+      <c r="E43" s="11" t="inlineStr">
         <is>
           <t>仕様書4Ⅰ(6)</t>
         </is>
       </c>
-      <c r="F43" s="23" t="inlineStr">
+      <c r="F43" s="11" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G43" s="25" t="inlineStr">
+      <c r="G43" s="13" t="inlineStr">
         <is>
           <t>集計表</t>
         </is>
       </c>
-      <c r="H43" s="25" t="inlineStr"/>
-      <c r="I43" s="23" t="inlineStr">
+      <c r="H43" s="13" t="inlineStr"/>
+      <c r="I43" s="11" t="inlineStr">
         <is>
           <t>R8.10〜11</t>
         </is>
       </c>
-      <c r="J43" s="26" t="n"/>
-      <c r="K43" s="26" t="n"/>
-      <c r="L43" s="26" t="n"/>
-      <c r="M43" s="26" t="n"/>
-      <c r="N43" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P43" s="25" t="inlineStr"/>
+      <c r="J43" s="14" t="n"/>
+      <c r="K43" s="14" t="n"/>
+      <c r="L43" s="14" t="n">
+        <v>46268</v>
+      </c>
+      <c r="M43" s="14" t="n"/>
+      <c r="N43" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O43" s="16" t="inlineStr">
+        <is>
+          <t>着手</t>
+        </is>
+      </c>
+      <c r="P43" s="13" t="inlineStr">
+        <is>
+          <t>★doc24でアンケート調査報告書の骨子を確定（全7章＋資料編・約118頁）。第Ⅰ部 単純集計編の掲載方式（全体／地区別／年齢階級別／前回比較／コメントの5点セット）と対象設問を確定。集計仕様書の作成は調査票の校了（9/9）後すぐに着手する。</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="18" t="inlineStr">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>Ⅰ-40</t>
         </is>
       </c>
-      <c r="B44" s="19" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>Ⅰ ニーズ調査</t>
         </is>
       </c>
-      <c r="C44" s="19" t="inlineStr">
+      <c r="C44" s="12" t="inlineStr">
         <is>
           <t>Ⅰ-5 集計・分析</t>
         </is>
       </c>
-      <c r="D44" s="20" t="inlineStr">
+      <c r="D44" s="13" t="inlineStr">
         <is>
           <t>基本属性別クロス集計（地区・性別・年齢）</t>
         </is>
       </c>
-      <c r="E44" s="18" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>仕様書4Ⅰ(6)</t>
         </is>
       </c>
-      <c r="F44" s="18" t="inlineStr">
+      <c r="F44" s="11" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G44" s="20" t="inlineStr">
+      <c r="G44" s="13" t="inlineStr">
         <is>
           <t>集計表</t>
         </is>
       </c>
-      <c r="H44" s="20" t="inlineStr"/>
-      <c r="I44" s="18" t="inlineStr">
+      <c r="H44" s="13" t="inlineStr"/>
+      <c r="I44" s="11" t="inlineStr">
         <is>
           <t>R8.10〜11</t>
         </is>
       </c>
-      <c r="J44" s="21" t="n"/>
-      <c r="K44" s="21" t="n"/>
-      <c r="L44" s="21" t="n"/>
-      <c r="M44" s="21" t="n"/>
-      <c r="N44" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="18" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P44" s="20" t="inlineStr"/>
+      <c r="J44" s="14" t="n"/>
+      <c r="K44" s="14" t="n"/>
+      <c r="L44" s="14" t="n">
+        <v>46268</v>
+      </c>
+      <c r="M44" s="14" t="n"/>
+      <c r="N44" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O44" s="16" t="inlineStr">
+        <is>
+          <t>着手</t>
+        </is>
+      </c>
+      <c r="P44" s="13" t="inlineStr">
+        <is>
+          <t>★doc24で全設問を地区別（北山・大塩・桧原・裏磐梯）・年齢階級別（65〜74／75〜84／85歳以上）で集計する方針を確定。移動手段・外出を控える理由・除雪は地区差が大きいと想定され施策の地区別展開の根拠になる。</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="23" t="inlineStr">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>Ⅰ-41</t>
         </is>
       </c>
-      <c r="B45" s="24" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t>Ⅰ ニーズ調査</t>
         </is>
       </c>
-      <c r="C45" s="24" t="inlineStr">
+      <c r="C45" s="12" t="inlineStr">
         <is>
           <t>Ⅰ-5 集計・分析</t>
         </is>
       </c>
-      <c r="D45" s="25" t="inlineStr">
+      <c r="D45" s="13" t="inlineStr">
         <is>
           <t>時系列比較（第8期・第9期との対比）</t>
         </is>
       </c>
-      <c r="E45" s="23" t="inlineStr">
+      <c r="E45" s="11" t="inlineStr">
         <is>
           <t>仕様書4Ⅰ(6)</t>
         </is>
       </c>
-      <c r="F45" s="23" t="inlineStr">
+      <c r="F45" s="11" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G45" s="25" t="inlineStr">
+      <c r="G45" s="13" t="inlineStr">
         <is>
           <t>比較表</t>
         </is>
       </c>
-      <c r="H45" s="25" t="inlineStr">
+      <c r="H45" s="13" t="inlineStr">
         <is>
           <t>村と協議のうえ範囲を決定</t>
         </is>
       </c>
-      <c r="I45" s="23" t="inlineStr">
+      <c r="I45" s="11" t="inlineStr">
         <is>
           <t>R8.10〜11</t>
         </is>
       </c>
-      <c r="J45" s="26" t="n"/>
-      <c r="K45" s="26" t="n"/>
-      <c r="L45" s="26" t="n"/>
-      <c r="M45" s="26" t="n"/>
-      <c r="N45" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P45" s="25" t="inlineStr"/>
+      <c r="J45" s="14" t="n"/>
+      <c r="K45" s="14" t="n"/>
+      <c r="L45" s="14" t="n">
+        <v>46268</v>
+      </c>
+      <c r="M45" s="14" t="n"/>
+      <c r="N45" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O45" s="16" t="inlineStr">
+        <is>
+          <t>確認中</t>
+        </is>
+      </c>
+      <c r="P45" s="13" t="inlineStr">
+        <is>
+          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問を抽出済。対象範囲は村と協議（doc24 K-86）。</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="18" t="inlineStr">
@@ -3425,176 +3443,194 @@
       <c r="P46" s="20" t="inlineStr"/>
     </row>
     <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="23" t="inlineStr">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>Ⅰ-43</t>
         </is>
       </c>
-      <c r="B47" s="24" t="inlineStr">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>Ⅰ ニーズ調査</t>
         </is>
       </c>
-      <c r="C47" s="24" t="inlineStr">
+      <c r="C47" s="12" t="inlineStr">
         <is>
           <t>Ⅰ-5 集計・分析</t>
         </is>
       </c>
-      <c r="D47" s="25" t="inlineStr">
+      <c r="D47" s="13" t="inlineStr">
         <is>
           <t>リスク判定11種の算出</t>
         </is>
       </c>
-      <c r="E47" s="23" t="inlineStr">
+      <c r="E47" s="11" t="inlineStr">
         <is>
           <t>手引き</t>
         </is>
       </c>
-      <c r="F47" s="23" t="inlineStr">
+      <c r="F47" s="11" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G47" s="25" t="inlineStr">
+      <c r="G47" s="13" t="inlineStr">
         <is>
           <t>リスク判定結果</t>
         </is>
       </c>
-      <c r="H47" s="25" t="inlineStr">
+      <c r="H47" s="13" t="inlineStr">
         <is>
           <t>運動器・転倒・閉じこもり・低栄養・口腔・認知・うつ・IADL等</t>
         </is>
       </c>
-      <c r="I47" s="23" t="inlineStr">
+      <c r="I47" s="11" t="inlineStr">
         <is>
           <t>R8.10〜11</t>
         </is>
       </c>
-      <c r="J47" s="26" t="n"/>
-      <c r="K47" s="26" t="n"/>
-      <c r="L47" s="26" t="n"/>
-      <c r="M47" s="26" t="n"/>
-      <c r="N47" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P47" s="25" t="inlineStr"/>
+      <c r="J47" s="14" t="n"/>
+      <c r="K47" s="14" t="n"/>
+      <c r="L47" s="14" t="n">
+        <v>46268</v>
+      </c>
+      <c r="M47" s="14" t="n"/>
+      <c r="N47" s="15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O47" s="16" t="inlineStr">
+        <is>
+          <t>着手</t>
+        </is>
+      </c>
+      <c r="P47" s="13" t="inlineStr">
+        <is>
+          <t>★doc24§4-3で判定に用いる設問を確定（運動器・転倒・閉じこもり・低栄養・口腔・認知・IADL・うつ）。判定基準は見える化システムの算出方法に合わせる（独自基準を作ると全国・県との比較ができなくなるため）。</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="18" t="inlineStr">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>Ⅰ-44</t>
         </is>
       </c>
-      <c r="B48" s="19" t="inlineStr">
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>Ⅰ ニーズ調査</t>
         </is>
       </c>
-      <c r="C48" s="19" t="inlineStr">
+      <c r="C48" s="12" t="inlineStr">
         <is>
           <t>Ⅰ-5 集計・分析</t>
         </is>
       </c>
-      <c r="D48" s="20" t="inlineStr">
+      <c r="D48" s="13" t="inlineStr">
         <is>
           <t>自由記述の整理</t>
         </is>
       </c>
-      <c r="E48" s="18" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>仕様書4Ⅰ(6)</t>
         </is>
       </c>
-      <c r="F48" s="18" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G48" s="20" t="inlineStr">
+      <c r="G48" s="13" t="inlineStr">
         <is>
           <t>自由意見一覧</t>
         </is>
       </c>
-      <c r="H48" s="20" t="inlineStr"/>
-      <c r="I48" s="18" t="inlineStr">
+      <c r="H48" s="13" t="inlineStr"/>
+      <c r="I48" s="11" t="inlineStr">
         <is>
           <t>R8.10〜11</t>
         </is>
       </c>
-      <c r="J48" s="21" t="n"/>
-      <c r="K48" s="21" t="n"/>
-      <c r="L48" s="21" t="n"/>
-      <c r="M48" s="21" t="n"/>
-      <c r="N48" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="18" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P48" s="20" t="inlineStr"/>
+      <c r="J48" s="14" t="n"/>
+      <c r="K48" s="14" t="n"/>
+      <c r="L48" s="14" t="n">
+        <v>46268</v>
+      </c>
+      <c r="M48" s="14" t="n"/>
+      <c r="N48" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O48" s="16" t="inlineStr">
+        <is>
+          <t>着手</t>
+        </is>
+      </c>
+      <c r="P48" s="13" t="inlineStr">
+        <is>
+          <t>★doc24§9で対象設問を確定（問3(9)利用先・問7(9)利用先・問11その他・問4(17)(18)趣味生きがい ほか）。人口2,300人規模では記述から個人が推定され得るため匿名化の方針を村と協議（doc24 K-89）。</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="23" t="inlineStr">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Ⅰ-45</t>
         </is>
       </c>
-      <c r="B49" s="24" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>Ⅰ ニーズ調査</t>
         </is>
       </c>
-      <c r="C49" s="24" t="inlineStr">
+      <c r="C49" s="12" t="inlineStr">
         <is>
           <t>Ⅰ-5 集計・分析</t>
         </is>
       </c>
-      <c r="D49" s="25" t="inlineStr">
+      <c r="D49" s="13" t="inlineStr">
         <is>
           <t>在宅調査の要介護度別・介護者就労状況別分析</t>
         </is>
       </c>
-      <c r="E49" s="23" t="inlineStr">
+      <c r="E49" s="11" t="inlineStr">
         <is>
           <t>仕様書4Ⅰ(6)</t>
         </is>
       </c>
-      <c r="F49" s="23" t="inlineStr">
+      <c r="F49" s="11" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G49" s="25" t="inlineStr">
+      <c r="G49" s="13" t="inlineStr">
         <is>
           <t>分析結果</t>
         </is>
       </c>
-      <c r="H49" s="25" t="inlineStr"/>
-      <c r="I49" s="23" t="inlineStr">
+      <c r="H49" s="13" t="inlineStr"/>
+      <c r="I49" s="11" t="inlineStr">
         <is>
           <t>R8.10〜11</t>
         </is>
       </c>
-      <c r="J49" s="26" t="n"/>
-      <c r="K49" s="26" t="n"/>
-      <c r="L49" s="26" t="n"/>
-      <c r="M49" s="26" t="n"/>
-      <c r="N49" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P49" s="25" t="inlineStr"/>
+      <c r="J49" s="14" t="n"/>
+      <c r="K49" s="14" t="n"/>
+      <c r="L49" s="14" t="n">
+        <v>46268</v>
+      </c>
+      <c r="M49" s="14" t="n"/>
+      <c r="N49" s="15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O49" s="16" t="inlineStr">
+        <is>
+          <t>着手</t>
+        </is>
+      </c>
+      <c r="P49" s="13" t="inlineStr">
+        <is>
+          <t>★doc24§5-2で仕様書4Ⅰ(6)が求めるクロスの設計を確定。軸1＝要介護度3区分、軸2＝主な介護者の勤務形態3区分。中核は「要介護度×就労継続の見通し」。村独自の問6-1（村内に施設があれば）と問6のクロスで施設の潜在需要を測る設計も確定。</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="18" t="inlineStr">
@@ -6707,11 +6743,11 @@
       <c r="J99" s="14" t="n"/>
       <c r="K99" s="14" t="n"/>
       <c r="L99" s="14" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="M99" s="14" t="n"/>
       <c r="N99" s="15" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="O99" s="16" t="inlineStr">
         <is>
@@ -6720,7 +6756,7 @@
       </c>
       <c r="P99" s="13" t="inlineStr">
         <is>
-          <t>★doc23§3で設計完了。ICF5領域と標準設問の対応表を作成し、5領域すべてが標準の必須＋オプション項目で埋まること＝分析のための独自設問は不要であることを確定。分析案は3案（B:疾病×生活機能の2軸マトリクス〈主軸〉／A:生活機能ベースの4層区分〈施策設計用〉／C:5領域レーダー〈委員会資料〉）。推奨対応は標準オプション問7(7)の採用1件のみ。実装は回収データの受領後。</t>
+          <t>★doc23§3で設計完了。ICF5領域と標準設問の対応表を作成し、5領域すべてが標準の必須＋オプション項目で埋まること＝分析のための独自設問は不要であることを確定。分析案は3案（B:疾病×生活機能の2軸マトリクス〈主軸〉／A:生活機能ベースの4層区分〈施策設計用〉／C:5領域レーダー〈委員会資料〉）。推奨対応は標準オプション問7(7)の採用1件のみ。★9/3：手引き（令和7年8月版）に「ICFの構成要素間の相互作用の図」による公式の対応表（図表9）が掲載されていることを確認し、doc23の当方作成表を訂正。ICFによる整理は国が公式に推奨する枠組みであることが確定。実装は回収データの受領後。</t>
         </is>
       </c>
     </row>
@@ -7056,7 +7092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8197,27 +8233,27 @@
       </c>
       <c r="B33" s="33" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C33" s="34" t="inlineStr">
         <is>
-          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
+          <t>★要介護認定データの提供時期と項目（要介護度・認定日・サービス利用状況）</t>
         </is>
       </c>
       <c r="D33" s="34" t="inlineStr">
         <is>
-          <t>連絡体制表の確定。第9期概要版の発行は住民課。</t>
+          <t>★仕様書4Ⅰ(5)。ICF分析の「認定状況×生活機能リスク」表と在宅調査のクロスに必須。目的外利用の手続きの確認を含む。議事録の「元気な軽度者が総合事業を利用している」の検証はこの紐付けでしかできない。</t>
         </is>
       </c>
       <c r="E33" s="35" t="inlineStr">
         <is>
-          <t>０-04</t>
+          <t>Ⅰ-37</t>
         </is>
       </c>
       <c r="F33" s="35" t="inlineStr">
         <is>
-          <t>doc01-1</t>
+          <t>doc24§12 K-87</t>
         </is>
       </c>
       <c r="G33" s="35" t="inlineStr">
@@ -8240,22 +8276,22 @@
       </c>
       <c r="C34" s="34" t="inlineStr">
         <is>
-          <t>契約締結日・契約書の取り交わし状況</t>
+          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
         </is>
       </c>
       <c r="D34" s="34" t="inlineStr">
         <is>
-          <t>業務開始日の確定。</t>
+          <t>連絡体制表の確定。第9期概要版の発行は住民課。</t>
         </is>
       </c>
       <c r="E34" s="35" t="inlineStr">
         <is>
-          <t>０-02</t>
+          <t>０-04</t>
         </is>
       </c>
       <c r="F34" s="35" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>doc01-1</t>
         </is>
       </c>
       <c r="G34" s="35" t="inlineStr">
@@ -8278,22 +8314,22 @@
       </c>
       <c r="C35" s="34" t="inlineStr">
         <is>
-          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
+          <t>契約締結日・契約書の取り交わし状況</t>
         </is>
       </c>
       <c r="D35" s="34" t="inlineStr">
         <is>
-          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
+          <t>業務開始日の確定。</t>
         </is>
       </c>
       <c r="E35" s="35" t="inlineStr">
         <is>
-          <t>０-06</t>
+          <t>０-02</t>
         </is>
       </c>
       <c r="F35" s="35" t="inlineStr">
         <is>
-          <t>doc19 追-12</t>
+          <t>―</t>
         </is>
       </c>
       <c r="G35" s="35" t="inlineStr">
@@ -8316,22 +8352,22 @@
       </c>
       <c r="C36" s="34" t="inlineStr">
         <is>
-          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
+          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
         </is>
       </c>
       <c r="D36" s="34" t="inlineStr">
         <is>
-          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
+          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
         </is>
       </c>
       <c r="E36" s="35" t="inlineStr">
         <is>
-          <t>Ⅴ-96</t>
+          <t>０-06</t>
         </is>
       </c>
       <c r="F36" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-78</t>
+          <t>doc19 追-12</t>
         </is>
       </c>
       <c r="G36" s="35" t="inlineStr">
@@ -8349,27 +8385,27 @@
       </c>
       <c r="B37" s="33" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C37" s="34" t="inlineStr">
         <is>
-          <t>ICF分析は標準設問のみで完結することの確認</t>
+          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
         </is>
       </c>
       <c r="D37" s="34" t="inlineStr">
         <is>
-          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
+          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
         </is>
       </c>
       <c r="E37" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-50</t>
+          <t>Ⅴ-96</t>
         </is>
       </c>
       <c r="F37" s="35" t="inlineStr">
         <is>
-          <t>doc23§3-4</t>
+          <t>doc22 K-78</t>
         </is>
       </c>
       <c r="G37" s="35" t="inlineStr">
@@ -8387,27 +8423,27 @@
       </c>
       <c r="B38" s="33" t="inlineStr">
         <is>
-          <t>委員会</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C38" s="34" t="inlineStr">
         <is>
-          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
+          <t>自由記述の匿名化の方針（削除・置換の範囲）</t>
         </is>
       </c>
       <c r="D38" s="34" t="inlineStr">
         <is>
-          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
+          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。</t>
         </is>
       </c>
       <c r="E38" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-80,Ⅱ-81</t>
+          <t>Ⅴ-96</t>
         </is>
       </c>
       <c r="F38" s="35" t="inlineStr">
         <is>
-          <t>doc01-6,doc19 追-15</t>
+          <t>doc24§12 K-89</t>
         </is>
       </c>
       <c r="G38" s="35" t="inlineStr">
@@ -8425,27 +8461,27 @@
       </c>
       <c r="B39" s="33" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C39" s="34" t="inlineStr">
         <is>
-          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
+          <t>ICF分析は標準設問のみで完結することの確認</t>
         </is>
       </c>
       <c r="D39" s="34" t="inlineStr">
         <is>
-          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
+          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
         </is>
       </c>
       <c r="E39" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-76,Ⅱ-77</t>
+          <t>Ⅰ-50</t>
         </is>
       </c>
       <c r="F39" s="35" t="inlineStr">
         <is>
-          <t>doc01-7,doc19 指-3</t>
+          <t>doc23§3-4</t>
         </is>
       </c>
       <c r="G39" s="35" t="inlineStr">
@@ -8463,27 +8499,27 @@
       </c>
       <c r="B40" s="33" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
+          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
+          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F40" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-79</t>
+          <t>doc24§12 K-86</t>
         </is>
       </c>
       <c r="G40" s="35" t="inlineStr">
@@ -8501,27 +8537,27 @@
       </c>
       <c r="B41" s="33" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>委員会</t>
         </is>
       </c>
       <c r="C41" s="34" t="inlineStr">
         <is>
-          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
+          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
         </is>
       </c>
       <c r="D41" s="34" t="inlineStr">
         <is>
-          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
+          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
         </is>
       </c>
       <c r="E41" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-80,Ⅱ-81</t>
         </is>
       </c>
       <c r="F41" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-66</t>
+          <t>doc01-6,doc19 追-15</t>
         </is>
       </c>
       <c r="G41" s="35" t="inlineStr">
@@ -8539,27 +8575,27 @@
       </c>
       <c r="B42" s="33" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C42" s="34" t="inlineStr">
         <is>
-          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
+          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
         </is>
       </c>
       <c r="D42" s="34" t="inlineStr">
         <is>
-          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
+          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
         </is>
       </c>
       <c r="E42" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-62</t>
+          <t>Ⅱ-76,Ⅱ-77</t>
         </is>
       </c>
       <c r="F42" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-81</t>
+          <t>doc01-7,doc19 指-3</t>
         </is>
       </c>
       <c r="G42" s="35" t="inlineStr">
@@ -8577,27 +8613,27 @@
       </c>
       <c r="B43" s="33" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C43" s="34" t="inlineStr">
         <is>
-          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
+          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
         </is>
       </c>
       <c r="D43" s="34" t="inlineStr">
         <is>
-          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
+          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
         </is>
       </c>
       <c r="E43" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>doc21§5 K-69</t>
+          <t>doc22 K-79</t>
         </is>
       </c>
       <c r="G43" s="35" t="inlineStr">
@@ -8615,27 +8651,27 @@
       </c>
       <c r="B44" s="33" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C44" s="34" t="inlineStr">
         <is>
-          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
+          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
         </is>
       </c>
       <c r="D44" s="34" t="inlineStr">
         <is>
-          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
+          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
         </is>
       </c>
       <c r="E44" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F44" s="35" t="inlineStr">
         <is>
-          <t>doc21§5 K-70</t>
+          <t>doc20§6-2 K-66</t>
         </is>
       </c>
       <c r="G44" s="35" t="inlineStr">
@@ -8653,149 +8689,149 @@
       </c>
       <c r="B45" s="33" t="inlineStr">
         <is>
+          <t>方針</t>
+        </is>
+      </c>
+      <c r="C45" s="34" t="inlineStr">
+        <is>
+          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
+        </is>
+      </c>
+      <c r="D45" s="34" t="inlineStr">
+        <is>
+          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
+        </is>
+      </c>
+      <c r="E45" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-62</t>
+        </is>
+      </c>
+      <c r="F45" s="35" t="inlineStr">
+        <is>
+          <t>doc22 K-81</t>
+        </is>
+      </c>
+      <c r="G45" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H45" s="34" t="inlineStr"/>
+    </row>
+    <row r="46" ht="34" customHeight="1">
+      <c r="A46" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B46" s="33" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C46" s="34" t="inlineStr">
+        <is>
+          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
+        </is>
+      </c>
+      <c r="D46" s="34" t="inlineStr">
+        <is>
+          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
+        </is>
+      </c>
+      <c r="E46" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F46" s="35" t="inlineStr">
+        <is>
+          <t>doc21§5 K-69</t>
+        </is>
+      </c>
+      <c r="G46" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H46" s="34" t="inlineStr"/>
+    </row>
+    <row r="47" ht="34" customHeight="1">
+      <c r="A47" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B47" s="33" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C47" s="34" t="inlineStr">
+        <is>
+          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
+        </is>
+      </c>
+      <c r="D47" s="34" t="inlineStr">
+        <is>
+          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
+        </is>
+      </c>
+      <c r="E47" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F47" s="35" t="inlineStr">
+        <is>
+          <t>doc21§5 K-70</t>
+        </is>
+      </c>
+      <c r="G47" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H47" s="34" t="inlineStr"/>
+    </row>
+    <row r="48" ht="34" customHeight="1">
+      <c r="A48" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B48" s="33" t="inlineStr">
+        <is>
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C45" s="34" t="inlineStr">
+      <c r="C48" s="34" t="inlineStr">
         <is>
           <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
         </is>
       </c>
-      <c r="D45" s="34" t="inlineStr">
+      <c r="D48" s="34" t="inlineStr">
         <is>
           <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
         </is>
       </c>
-      <c r="E45" s="35" t="inlineStr">
+      <c r="E48" s="35" t="inlineStr">
         <is>
           <t>Ⅰ-19,Ⅰ-25</t>
         </is>
       </c>
-      <c r="F45" s="35" t="inlineStr">
+      <c r="F48" s="35" t="inlineStr">
         <is>
           <t>doc22 §1</t>
         </is>
       </c>
-      <c r="G45" s="35" t="inlineStr">
+      <c r="G48" s="35" t="inlineStr">
         <is>
           <t>一部回答</t>
         </is>
       </c>
-      <c r="H45" s="34" t="inlineStr"/>
-    </row>
-    <row r="46" ht="34" customHeight="1">
-      <c r="A46" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B46" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C46" s="25" t="inlineStr">
-        <is>
-          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
-        </is>
-      </c>
-      <c r="D46" s="25" t="inlineStr">
-        <is>
-          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
-        </is>
-      </c>
-      <c r="E46" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F46" s="23" t="inlineStr">
-        <is>
-          <t>doc02§22,doc08§8</t>
-        </is>
-      </c>
-      <c r="G46" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H46" s="25" t="inlineStr"/>
-    </row>
-    <row r="47" ht="34" customHeight="1">
-      <c r="A47" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B47" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C47" s="25" t="inlineStr">
-        <is>
-          <t>令和6年度決算および令和7年度の給付費見込</t>
-        </is>
-      </c>
-      <c r="D47" s="25" t="inlineStr">
-        <is>
-          <t>第9期の計画値と実績の乖離を確定させるために必要。</t>
-        </is>
-      </c>
-      <c r="E47" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
-        </is>
-      </c>
-      <c r="F47" s="23" t="inlineStr">
-        <is>
-          <t>doc08§8-1</t>
-        </is>
-      </c>
-      <c r="G47" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H47" s="25" t="inlineStr"/>
-    </row>
-    <row r="48" ht="34" customHeight="1">
-      <c r="A48" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B48" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C48" s="25" t="inlineStr">
-        <is>
-          <t>通いの場の実数（令和3〜7年度）</t>
-        </is>
-      </c>
-      <c r="D48" s="25" t="inlineStr">
-        <is>
-          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。</t>
-        </is>
-      </c>
-      <c r="E48" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F48" s="23" t="inlineStr">
-        <is>
-          <t>doc02§16,§22</t>
-        </is>
-      </c>
-      <c r="G48" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H48" s="25" t="inlineStr"/>
+      <c r="H48" s="34" t="inlineStr"/>
     </row>
     <row r="49" ht="34" customHeight="1">
       <c r="A49" s="37" t="inlineStr">
@@ -8810,22 +8846,22 @@
       </c>
       <c r="C49" s="25" t="inlineStr">
         <is>
-          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
+          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
         </is>
       </c>
       <c r="D49" s="25" t="inlineStr">
         <is>
-          <t>見える化に該当データがない。第9期は基本目標4-4に位置づけ。</t>
+          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
         </is>
       </c>
       <c r="E49" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-69</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-5</t>
+          <t>doc02§22,doc08§8</t>
         </is>
       </c>
       <c r="G49" s="23" t="inlineStr">
@@ -8848,22 +8884,22 @@
       </c>
       <c r="C50" s="25" t="inlineStr">
         <is>
-          <t>高齢者福祉事業（村単独事業）の実績資料</t>
+          <t>令和6年度決算および令和7年度の給付費見込</t>
         </is>
       </c>
       <c r="D50" s="25" t="inlineStr">
         <is>
-          <t>現行計画の評価に必要。</t>
+          <t>第9期の計画値と実績の乖離を確定させるために必要。</t>
         </is>
       </c>
       <c r="E50" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F50" s="23" t="inlineStr">
         <is>
-          <t>doc01-11</t>
+          <t>doc08§8-1</t>
         </is>
       </c>
       <c r="G50" s="23" t="inlineStr">
@@ -8886,22 +8922,22 @@
       </c>
       <c r="C51" s="25" t="inlineStr">
         <is>
-          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
+          <t>通いの場の実数（令和3〜7年度）</t>
         </is>
       </c>
       <c r="D51" s="25" t="inlineStr">
         <is>
-          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
+          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。</t>
         </is>
       </c>
       <c r="E51" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-58,Ⅱ-59</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-9</t>
+          <t>doc02§16,§22</t>
         </is>
       </c>
       <c r="G51" s="23" t="inlineStr">
@@ -8924,22 +8960,22 @@
       </c>
       <c r="C52" s="25" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告（月報・年報）の原データの提供可否</t>
+          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
         </is>
       </c>
       <c r="D52" s="25" t="inlineStr">
         <is>
-          <t>見える化に収録されていない項目（サービス種類別利用者数の月次推移等）が扱えるようになる。</t>
+          <t>見える化に該当データがない。第9期は基本目標4-4に位置づけ。</t>
         </is>
       </c>
       <c r="E52" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-68,Ⅱ-69</t>
         </is>
       </c>
       <c r="F52" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-10</t>
+          <t>doc08§8-5</t>
         </is>
       </c>
       <c r="G52" s="23" t="inlineStr">
@@ -8962,22 +8998,22 @@
       </c>
       <c r="C53" s="25" t="inlineStr">
         <is>
-          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
+          <t>高齢者福祉事業（村単独事業）の実績資料</t>
         </is>
       </c>
       <c r="D53" s="25" t="inlineStr">
         <is>
-          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
+          <t>現行計画の評価に必要。</t>
         </is>
       </c>
       <c r="E53" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc01-11</t>
         </is>
       </c>
       <c r="G53" s="23" t="inlineStr">
@@ -9000,22 +9036,22 @@
       </c>
       <c r="C54" s="25" t="inlineStr">
         <is>
-          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
+          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
         </is>
       </c>
       <c r="D54" s="25" t="inlineStr">
         <is>
-          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
+          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
         </is>
       </c>
       <c r="E54" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-58,Ⅱ-59</t>
         </is>
       </c>
       <c r="F54" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc19 追-9</t>
         </is>
       </c>
       <c r="G54" s="23" t="inlineStr">
@@ -9038,22 +9074,22 @@
       </c>
       <c r="C55" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
+          <t>介護保険事業状況報告（月報・年報）の原データの提供可否</t>
         </is>
       </c>
       <c r="D55" s="25" t="inlineStr">
         <is>
-          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
+          <t>見える化に収録されていない項目（サービス種類別利用者数の月次推移等）が扱えるようになる。</t>
         </is>
       </c>
       <c r="E55" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc19 追-10</t>
         </is>
       </c>
       <c r="G55" s="23" t="inlineStr">
@@ -9076,12 +9112,12 @@
       </c>
       <c r="C56" s="25" t="inlineStr">
         <is>
-          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
+          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
         </is>
       </c>
       <c r="D56" s="25" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
+          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
         </is>
       </c>
       <c r="E56" s="23" t="inlineStr">
@@ -9091,7 +9127,7 @@
       </c>
       <c r="F56" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-65</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G56" s="23" t="inlineStr">
@@ -9114,22 +9150,22 @@
       </c>
       <c r="C57" s="25" t="inlineStr">
         <is>
-          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
+          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
         </is>
       </c>
       <c r="D57" s="25" t="inlineStr">
         <is>
-          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
+          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
         </is>
       </c>
       <c r="E57" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-68</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G57" s="23" t="inlineStr">
@@ -9152,22 +9188,22 @@
       </c>
       <c r="C58" s="25" t="inlineStr">
         <is>
-          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
+          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
         </is>
       </c>
       <c r="D58" s="25" t="inlineStr">
         <is>
-          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
+          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
         </is>
       </c>
       <c r="E58" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F58" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-71</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G58" s="23" t="inlineStr">
@@ -9190,22 +9226,22 @@
       </c>
       <c r="C59" s="25" t="inlineStr">
         <is>
-          <t>シルバー人材センターの会員数・受注実績</t>
+          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
         </is>
       </c>
       <c r="D59" s="25" t="inlineStr">
         <is>
-          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
+          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
         </is>
       </c>
       <c r="E59" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-72</t>
+          <t>doc20§6-2 K-65</t>
         </is>
       </c>
       <c r="G59" s="23" t="inlineStr">
@@ -9223,27 +9259,27 @@
       </c>
       <c r="B60" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C60" s="25" t="inlineStr">
         <is>
-          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
+          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
         </is>
       </c>
       <c r="D60" s="25" t="inlineStr">
         <is>
-          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
+          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
         </is>
       </c>
       <c r="E60" s="23" t="inlineStr">
         <is>
-          <t>Ⅴ-95</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F60" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-67</t>
+          <t>doc21§5 K-68</t>
         </is>
       </c>
       <c r="G60" s="23" t="inlineStr">
@@ -9261,27 +9297,27 @@
       </c>
       <c r="B61" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C61" s="25" t="inlineStr">
         <is>
-          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
+          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
         </is>
       </c>
       <c r="D61" s="25" t="inlineStr">
         <is>
-          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
+          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
         </is>
       </c>
       <c r="E61" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t>doc19 指-5</t>
+          <t>doc21§5 K-71</t>
         </is>
       </c>
       <c r="G61" s="23" t="inlineStr">
@@ -9299,27 +9335,27 @@
       </c>
       <c r="B62" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C62" s="25" t="inlineStr">
         <is>
-          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
+          <t>シルバー人材センターの会員数・受注実績</t>
         </is>
       </c>
       <c r="D62" s="25" t="inlineStr">
         <is>
-          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
+          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
         </is>
       </c>
       <c r="E62" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-108</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F62" s="23" t="inlineStr">
         <is>
-          <t>doc22 K-80</t>
+          <t>doc21§5 K-72</t>
         </is>
       </c>
       <c r="G62" s="23" t="inlineStr">
@@ -9337,27 +9373,27 @@
       </c>
       <c r="B63" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C63" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
+          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
         </is>
       </c>
       <c r="D63" s="25" t="inlineStr">
         <is>
-          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
+          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
         </is>
       </c>
       <c r="E63" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅴ-95</t>
         </is>
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
-          <t>doc09§4,§10</t>
+          <t>doc20§6-2 K-67</t>
         </is>
       </c>
       <c r="G63" s="23" t="inlineStr">
@@ -9375,27 +9411,27 @@
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C64" s="25" t="inlineStr">
         <is>
-          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
+          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
         </is>
       </c>
       <c r="D64" s="25" t="inlineStr">
         <is>
-          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
+          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
         </is>
       </c>
       <c r="E64" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F64" s="23" t="inlineStr">
         <is>
-          <t>doc09§8,§10</t>
+          <t>doc19 指-5</t>
         </is>
       </c>
       <c r="G64" s="23" t="inlineStr">
@@ -9413,27 +9449,27 @@
       </c>
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C65" s="25" t="inlineStr">
         <is>
-          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
+          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
         </is>
       </c>
       <c r="D65" s="25" t="inlineStr">
         <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
+          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
         </is>
       </c>
       <c r="E65" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-108</t>
         </is>
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
-          <t>doc02§17,doc07,doc18 4-1</t>
+          <t>doc22 K-80</t>
         </is>
       </c>
       <c r="G65" s="23" t="inlineStr">
@@ -9451,27 +9487,27 @@
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C66" s="25" t="inlineStr">
         <is>
-          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
+          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
         </is>
       </c>
       <c r="D66" s="25" t="inlineStr">
         <is>
-          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
+          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
         </is>
       </c>
       <c r="E66" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-75</t>
+          <t>Ⅳ-90</t>
         </is>
       </c>
       <c r="F66" s="23" t="inlineStr">
         <is>
-          <t>doc17 C-1,doc02§20-2</t>
+          <t>doc24§12 K-88</t>
         </is>
       </c>
       <c r="G66" s="23" t="inlineStr">
@@ -9494,22 +9530,22 @@
       </c>
       <c r="C67" s="25" t="inlineStr">
         <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
         </is>
       </c>
       <c r="D67" s="25" t="inlineStr">
         <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
         </is>
       </c>
       <c r="E67" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
-          <t>doc13§6</t>
+          <t>doc09§4,§10</t>
         </is>
       </c>
       <c r="G67" s="23" t="inlineStr">
@@ -9532,22 +9568,22 @@
       </c>
       <c r="C68" s="25" t="inlineStr">
         <is>
-          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
         </is>
       </c>
       <c r="D68" s="25" t="inlineStr">
         <is>
-          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
+          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
         </is>
       </c>
       <c r="E68" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F68" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-14</t>
+          <t>doc09§8,§10</t>
         </is>
       </c>
       <c r="G68" s="23" t="inlineStr">
@@ -9570,12 +9606,12 @@
       </c>
       <c r="C69" s="25" t="inlineStr">
         <is>
-          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
         </is>
       </c>
       <c r="D69" s="25" t="inlineStr">
         <is>
-          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
         </is>
       </c>
       <c r="E69" s="23" t="inlineStr">
@@ -9585,7 +9621,7 @@
       </c>
       <c r="F69" s="23" t="inlineStr">
         <is>
-          <t>doc19 §3</t>
+          <t>doc02§17,doc07,doc18 4-1</t>
         </is>
       </c>
       <c r="G69" s="23" t="inlineStr">
@@ -9608,22 +9644,22 @@
       </c>
       <c r="C70" s="25" t="inlineStr">
         <is>
-          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
         </is>
       </c>
       <c r="D70" s="25" t="inlineStr">
         <is>
-          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
         </is>
       </c>
       <c r="E70" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-56,Ⅱ-75</t>
         </is>
       </c>
       <c r="F70" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-73</t>
+          <t>doc17 C-1,doc02§20-2</t>
         </is>
       </c>
       <c r="G70" s="23" t="inlineStr">
@@ -9641,27 +9677,27 @@
       </c>
       <c r="B71" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C71" s="25" t="inlineStr">
         <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
         </is>
       </c>
       <c r="D71" s="25" t="inlineStr">
         <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
         </is>
       </c>
       <c r="E71" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-60,Ⅱ-65</t>
         </is>
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
-          <t>doc07§4</t>
+          <t>doc13§6</t>
         </is>
       </c>
       <c r="G71" s="23" t="inlineStr">
@@ -9679,27 +9715,27 @@
       </c>
       <c r="B72" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C72" s="25" t="inlineStr">
         <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
         </is>
       </c>
       <c r="D72" s="25" t="inlineStr">
         <is>
-          <t>評価指標の読み方に影響。</t>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
         </is>
       </c>
       <c r="E72" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F72" s="23" t="inlineStr">
         <is>
-          <t>doc07§8-4</t>
+          <t>doc19 追-14</t>
         </is>
       </c>
       <c r="G72" s="23" t="inlineStr">
@@ -9717,27 +9753,27 @@
       </c>
       <c r="B73" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C73" s="25" t="inlineStr">
         <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
         </is>
       </c>
       <c r="D73" s="25" t="inlineStr">
         <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
         </is>
       </c>
       <c r="E73" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F73" s="23" t="inlineStr">
         <is>
-          <t>doc08§4,§8-2</t>
+          <t>doc19 §3</t>
         </is>
       </c>
       <c r="G73" s="23" t="inlineStr">
@@ -9755,27 +9791,27 @@
       </c>
       <c r="B74" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C74" s="25" t="inlineStr">
         <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
         </is>
       </c>
       <c r="D74" s="25" t="inlineStr">
         <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
         </is>
       </c>
       <c r="E74" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F74" s="23" t="inlineStr">
         <is>
-          <t>doc02§20-1</t>
+          <t>doc21§5 K-73</t>
         </is>
       </c>
       <c r="G74" s="23" t="inlineStr">
@@ -9793,27 +9829,27 @@
       </c>
       <c r="B75" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C75" s="25" t="inlineStr">
         <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
         </is>
       </c>
       <c r="D75" s="25" t="inlineStr">
         <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
         </is>
       </c>
       <c r="E75" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-105</t>
         </is>
       </c>
       <c r="F75" s="23" t="inlineStr">
         <is>
-          <t>doc15,doc18</t>
+          <t>doc24§12 K-90</t>
         </is>
       </c>
       <c r="G75" s="23" t="inlineStr">
@@ -9831,27 +9867,27 @@
       </c>
       <c r="B76" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C76" s="25" t="inlineStr">
         <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
         </is>
       </c>
       <c r="D76" s="25" t="inlineStr">
         <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
         </is>
       </c>
       <c r="E76" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F76" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc18 3-1</t>
+          <t>doc07§4</t>
         </is>
       </c>
       <c r="G76" s="23" t="inlineStr">
@@ -9869,27 +9905,27 @@
       </c>
       <c r="B77" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C77" s="25" t="inlineStr">
         <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
         </is>
       </c>
       <c r="D77" s="25" t="inlineStr">
         <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+          <t>評価指標の読み方に影響。</t>
         </is>
       </c>
       <c r="E77" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F77" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
+          <t>doc07§8-4</t>
         </is>
       </c>
       <c r="G77" s="23" t="inlineStr">
@@ -9907,27 +9943,27 @@
       </c>
       <c r="B78" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C78" s="25" t="inlineStr">
         <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
         </is>
       </c>
       <c r="D78" s="25" t="inlineStr">
         <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
         </is>
       </c>
       <c r="E78" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F78" s="23" t="inlineStr">
         <is>
-          <t>doc17 B-3,doc18 4-3</t>
+          <t>doc08§4,§8-2</t>
         </is>
       </c>
       <c r="G78" s="23" t="inlineStr">
@@ -9945,27 +9981,27 @@
       </c>
       <c r="B79" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C79" s="25" t="inlineStr">
         <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
         </is>
       </c>
       <c r="D79" s="25" t="inlineStr">
         <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
         </is>
       </c>
       <c r="E79" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 2-9</t>
+          <t>doc02§20-1</t>
         </is>
       </c>
       <c r="G79" s="23" t="inlineStr">
@@ -9988,22 +10024,22 @@
       </c>
       <c r="C80" s="25" t="inlineStr">
         <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
         </is>
       </c>
       <c r="D80" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
         </is>
       </c>
       <c r="E80" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F80" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 5-7</t>
+          <t>doc15,doc18</t>
         </is>
       </c>
       <c r="G80" s="23" t="inlineStr">
@@ -10021,27 +10057,27 @@
       </c>
       <c r="B81" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C81" s="25" t="inlineStr">
         <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
         </is>
       </c>
       <c r="D81" s="25" t="inlineStr">
         <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
         </is>
       </c>
       <c r="E81" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-4</t>
+          <t>doc14§5,doc18 3-1</t>
         </is>
       </c>
       <c r="G81" s="23" t="inlineStr">
@@ -10059,27 +10095,27 @@
       </c>
       <c r="B82" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C82" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
         </is>
       </c>
       <c r="D82" s="25" t="inlineStr">
         <is>
-          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
         </is>
       </c>
       <c r="E82" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-73,Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F82" s="23" t="inlineStr">
         <is>
-          <t>doc01-5,doc18 1-2</t>
+          <t>doc14§5,doc15,doc18 4-5</t>
         </is>
       </c>
       <c r="G82" s="23" t="inlineStr">
@@ -10097,27 +10133,27 @@
       </c>
       <c r="B83" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C83" s="25" t="inlineStr">
         <is>
-          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
         </is>
       </c>
       <c r="D83" s="25" t="inlineStr">
         <is>
-          <t>施策の書きぶりに影響。</t>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
         </is>
       </c>
       <c r="E83" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-72</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t>doc01-12</t>
+          <t>doc17 B-3,doc18 4-3</t>
         </is>
       </c>
       <c r="G83" s="23" t="inlineStr">
@@ -10135,27 +10171,27 @@
       </c>
       <c r="B84" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C84" s="25" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
         </is>
       </c>
       <c r="D84" s="25" t="inlineStr">
         <is>
-          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
         </is>
       </c>
       <c r="E84" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F84" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-13</t>
+          <t>doc17 A-1,doc18 2-9</t>
         </is>
       </c>
       <c r="G84" s="23" t="inlineStr">
@@ -10173,27 +10209,27 @@
       </c>
       <c r="B85" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C85" s="25" t="inlineStr">
         <is>
-          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
         </is>
       </c>
       <c r="D85" s="25" t="inlineStr">
         <is>
-          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
         </is>
       </c>
       <c r="E85" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-31</t>
+          <t>Ⅱ-64,Ⅱ-75</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-6</t>
+          <t>doc17 A-1,doc18 5-7</t>
         </is>
       </c>
       <c r="G85" s="23" t="inlineStr">
@@ -10211,27 +10247,27 @@
       </c>
       <c r="B86" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C86" s="25" t="inlineStr">
         <is>
-          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
         </is>
       </c>
       <c r="D86" s="25" t="inlineStr">
         <is>
-          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
         </is>
       </c>
       <c r="E86" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-40,Ⅰ-42</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F86" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-7</t>
+          <t>doc08§8-4</t>
         </is>
       </c>
       <c r="G86" s="23" t="inlineStr">
@@ -10249,308 +10285,308 @@
       </c>
       <c r="B87" s="24" t="inlineStr">
         <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C87" s="25" t="inlineStr">
+        <is>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+        </is>
+      </c>
+      <c r="D87" s="25" t="inlineStr">
+        <is>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+        </is>
+      </c>
+      <c r="E87" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-73,Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F87" s="23" t="inlineStr">
+        <is>
+          <t>doc01-5,doc18 1-2</t>
+        </is>
+      </c>
+      <c r="G87" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H87" s="25" t="inlineStr"/>
+    </row>
+    <row r="88" ht="34" customHeight="1">
+      <c r="A88" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B88" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C88" s="25" t="inlineStr">
+        <is>
+          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+        </is>
+      </c>
+      <c r="D88" s="25" t="inlineStr">
+        <is>
+          <t>施策の書きぶりに影響。</t>
+        </is>
+      </c>
+      <c r="E88" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-71,Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F88" s="23" t="inlineStr">
+        <is>
+          <t>doc01-12</t>
+        </is>
+      </c>
+      <c r="G88" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H88" s="25" t="inlineStr"/>
+    </row>
+    <row r="89" ht="34" customHeight="1">
+      <c r="A89" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B89" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C89" s="25" t="inlineStr">
+        <is>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+        </is>
+      </c>
+      <c r="D89" s="25" t="inlineStr">
+        <is>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+        </is>
+      </c>
+      <c r="E89" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F89" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-13</t>
+        </is>
+      </c>
+      <c r="G89" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H89" s="25" t="inlineStr"/>
+    </row>
+    <row r="90" ht="34" customHeight="1">
+      <c r="A90" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B90" s="24" t="inlineStr">
+        <is>
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C87" s="25" t="inlineStr">
+      <c r="C90" s="25" t="inlineStr">
+        <is>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+        </is>
+      </c>
+      <c r="D90" s="25" t="inlineStr">
+        <is>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+        </is>
+      </c>
+      <c r="E90" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-31</t>
+        </is>
+      </c>
+      <c r="F90" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-6</t>
+        </is>
+      </c>
+      <c r="G90" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H90" s="25" t="inlineStr"/>
+    </row>
+    <row r="91" ht="34" customHeight="1">
+      <c r="A91" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B91" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C91" s="25" t="inlineStr">
+        <is>
+          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+        </is>
+      </c>
+      <c r="D91" s="25" t="inlineStr">
+        <is>
+          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+        </is>
+      </c>
+      <c r="E91" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-40,Ⅰ-42</t>
+        </is>
+      </c>
+      <c r="F91" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-7</t>
+        </is>
+      </c>
+      <c r="G91" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H91" s="25" t="inlineStr"/>
+    </row>
+    <row r="92" ht="34" customHeight="1">
+      <c r="A92" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B92" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C92" s="25" t="inlineStr">
         <is>
           <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
         </is>
       </c>
-      <c r="D87" s="25" t="inlineStr">
+      <c r="D92" s="25" t="inlineStr">
         <is>
           <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
         </is>
       </c>
-      <c r="E87" s="23" t="inlineStr">
+      <c r="E92" s="23" t="inlineStr">
         <is>
           <t>Ⅰ-09</t>
         </is>
       </c>
-      <c r="F87" s="23" t="inlineStr">
+      <c r="F92" s="23" t="inlineStr">
         <is>
           <t>doc23§1-3</t>
         </is>
       </c>
-      <c r="G87" s="23" t="inlineStr">
+      <c r="G92" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H87" s="25" t="inlineStr"/>
-    </row>
-    <row r="88" ht="34" customHeight="1">
-      <c r="A88" s="38" t="inlineStr">
+      <c r="H92" s="25" t="inlineStr"/>
+    </row>
+    <row r="93" ht="34" customHeight="1">
+      <c r="A93" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B88" s="24" t="inlineStr">
+      <c r="B93" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C88" s="25" t="inlineStr">
+      <c r="C93" s="25" t="inlineStr">
         <is>
           <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
         </is>
       </c>
-      <c r="D88" s="25" t="inlineStr">
+      <c r="D93" s="25" t="inlineStr">
         <is>
           <t>第9期はA4・本文104頁・全6章＋資料編。</t>
         </is>
       </c>
-      <c r="E88" s="23" t="inlineStr">
+      <c r="E93" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-89</t>
         </is>
       </c>
-      <c r="F88" s="23" t="inlineStr">
+      <c r="F93" s="23" t="inlineStr">
         <is>
           <t>doc01-10</t>
         </is>
       </c>
-      <c r="G88" s="23" t="inlineStr">
+      <c r="G93" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H88" s="25" t="inlineStr"/>
-    </row>
-    <row r="89" ht="34" customHeight="1">
-      <c r="A89" s="38" t="inlineStr">
+      <c r="H93" s="25" t="inlineStr"/>
+    </row>
+    <row r="94" ht="34" customHeight="1">
+      <c r="A94" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B89" s="24" t="inlineStr">
+      <c r="B94" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C89" s="25" t="inlineStr">
+      <c r="C94" s="25" t="inlineStr">
         <is>
           <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
         </is>
       </c>
-      <c r="D89" s="25" t="inlineStr">
+      <c r="D94" s="25" t="inlineStr">
         <is>
           <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
         </is>
       </c>
-      <c r="E89" s="23" t="inlineStr">
+      <c r="E94" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-92</t>
         </is>
       </c>
-      <c r="F89" s="23" t="inlineStr">
+      <c r="F94" s="23" t="inlineStr">
         <is>
           <t>doc01-10,doc08</t>
         </is>
       </c>
-      <c r="G89" s="23" t="inlineStr">
+      <c r="G94" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H89" s="25" t="inlineStr"/>
-    </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="39" t="inlineStr">
+      <c r="H94" s="25" t="inlineStr"/>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="39" t="inlineStr">
         <is>
           <t>■ 解決済み（記録）</t>
         </is>
       </c>
-    </row>
-    <row r="92" ht="34" customHeight="1">
-      <c r="A92" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B92" s="41" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C92" s="42" t="inlineStr">
-        <is>
-          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
-        </is>
-      </c>
-      <c r="D92" s="42" t="inlineStr">
-        <is>
-          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
-        </is>
-      </c>
-      <c r="E92" s="40" t="inlineStr">
-        <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
-        </is>
-      </c>
-      <c r="F92" s="40" t="inlineStr">
-        <is>
-          <t>doc22 §1</t>
-        </is>
-      </c>
-      <c r="G92" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H92" s="42" t="inlineStr"/>
-    </row>
-    <row r="93" ht="34" customHeight="1">
-      <c r="A93" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B93" s="41" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C93" s="42" t="inlineStr">
-        <is>
-          <t>在宅介護実態調査 約150人の抽出基準</t>
-        </is>
-      </c>
-      <c r="D93" s="42" t="inlineStr">
-        <is>
-          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
-        </is>
-      </c>
-      <c r="E93" s="40" t="inlineStr">
-        <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
-        </is>
-      </c>
-      <c r="F93" s="40" t="inlineStr">
-        <is>
-          <t>doc22 §1</t>
-        </is>
-      </c>
-      <c r="G93" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H93" s="42" t="inlineStr"/>
-    </row>
-    <row r="94" ht="34" customHeight="1">
-      <c r="A94" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B94" s="41" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C94" s="42" t="inlineStr">
-        <is>
-          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
-        </is>
-      </c>
-      <c r="D94" s="42" t="inlineStr">
-        <is>
-          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
-        </is>
-      </c>
-      <c r="E94" s="40" t="inlineStr">
-        <is>
-          <t>Ⅰ-25,Ⅰ-26</t>
-        </is>
-      </c>
-      <c r="F94" s="40" t="inlineStr">
-        <is>
-          <t>doc22 §1</t>
-        </is>
-      </c>
-      <c r="G94" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H94" s="42" t="inlineStr"/>
-    </row>
-    <row r="95" ht="34" customHeight="1">
-      <c r="A95" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B95" s="41" t="inlineStr">
-        <is>
-          <t>計画構成</t>
-        </is>
-      </c>
-      <c r="C95" s="42" t="inlineStr">
-        <is>
-          <t>整合を図る関連計画の範囲</t>
-        </is>
-      </c>
-      <c r="D95" s="42" t="inlineStr">
-        <is>
-          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
-        </is>
-      </c>
-      <c r="E95" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-72</t>
-        </is>
-      </c>
-      <c r="F95" s="40" t="inlineStr">
-        <is>
-          <t>doc22 §1</t>
-        </is>
-      </c>
-      <c r="G95" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H95" s="42" t="inlineStr"/>
-    </row>
-    <row r="96" ht="34" customHeight="1">
-      <c r="A96" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B96" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C96" s="42" t="inlineStr">
-        <is>
-          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
-        </is>
-      </c>
-      <c r="D96" s="42" t="inlineStr">
-        <is>
-          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
-        </is>
-      </c>
-      <c r="E96" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F96" s="40" t="inlineStr">
-        <is>
-          <t>doc20§3,§4</t>
-        </is>
-      </c>
-      <c r="G96" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H96" s="42" t="inlineStr"/>
     </row>
     <row r="97" ht="34" customHeight="1">
       <c r="A97" s="40" t="inlineStr">
@@ -10560,27 +10596,27 @@
       </c>
       <c r="B97" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C97" s="42" t="inlineStr">
         <is>
-          <t>交付要綱の配点表（満点）</t>
+          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="D97" s="42" t="inlineStr">
         <is>
-          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
         </is>
       </c>
       <c r="E97" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F97" s="40" t="inlineStr">
         <is>
-          <t>doc20§2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G97" s="40" t="inlineStr">
@@ -10598,27 +10634,27 @@
       </c>
       <c r="B98" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C98" s="42" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の交付金評価結果</t>
+          <t>在宅介護実態調査 約150人の抽出基準</t>
         </is>
       </c>
       <c r="D98" s="42" t="inlineStr">
         <is>
-          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
         </is>
       </c>
       <c r="E98" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F98" s="40" t="inlineStr">
         <is>
-          <t>doc20§3-1</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G98" s="40" t="inlineStr">
@@ -10636,27 +10672,27 @@
       </c>
       <c r="B99" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C99" s="42" t="inlineStr">
         <is>
-          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
         </is>
       </c>
       <c r="D99" s="42" t="inlineStr">
         <is>
-          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
         </is>
       </c>
       <c r="E99" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-58</t>
+          <t>Ⅰ-25,Ⅰ-26</t>
         </is>
       </c>
       <c r="F99" s="40" t="inlineStr">
         <is>
-          <t>doc09</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G99" s="40" t="inlineStr">
@@ -10674,27 +10710,27 @@
       </c>
       <c r="B100" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C100" s="42" t="inlineStr">
         <is>
-          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+          <t>整合を図る関連計画の範囲</t>
         </is>
       </c>
       <c r="D100" s="42" t="inlineStr">
         <is>
-          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
         </is>
       </c>
       <c r="E100" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F100" s="40" t="inlineStr">
         <is>
-          <t>doc02§20-2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G100" s="40" t="inlineStr">
@@ -10717,43 +10753,233 @@
       </c>
       <c r="C101" s="42" t="inlineStr">
         <is>
+          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+        </is>
+      </c>
+      <c r="D101" s="42" t="inlineStr">
+        <is>
+          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+        </is>
+      </c>
+      <c r="E101" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F101" s="40" t="inlineStr">
+        <is>
+          <t>doc20§3,§4</t>
+        </is>
+      </c>
+      <c r="G101" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H101" s="42" t="inlineStr"/>
+    </row>
+    <row r="102" ht="34" customHeight="1">
+      <c r="A102" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B102" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C102" s="42" t="inlineStr">
+        <is>
+          <t>交付要綱の配点表（満点）</t>
+        </is>
+      </c>
+      <c r="D102" s="42" t="inlineStr">
+        <is>
+          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+        </is>
+      </c>
+      <c r="E102" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F102" s="40" t="inlineStr">
+        <is>
+          <t>doc20§2</t>
+        </is>
+      </c>
+      <c r="G102" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H102" s="42" t="inlineStr"/>
+    </row>
+    <row r="103" ht="34" customHeight="1">
+      <c r="A103" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B103" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C103" s="42" t="inlineStr">
+        <is>
+          <t>令和6年度・令和7年度の交付金評価結果</t>
+        </is>
+      </c>
+      <c r="D103" s="42" t="inlineStr">
+        <is>
+          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+        </is>
+      </c>
+      <c r="E103" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F103" s="40" t="inlineStr">
+        <is>
+          <t>doc20§3-1</t>
+        </is>
+      </c>
+      <c r="G103" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H103" s="42" t="inlineStr"/>
+    </row>
+    <row r="104" ht="34" customHeight="1">
+      <c r="A104" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B104" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C104" s="42" t="inlineStr">
+        <is>
+          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+        </is>
+      </c>
+      <c r="D104" s="42" t="inlineStr">
+        <is>
+          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+        </is>
+      </c>
+      <c r="E104" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-56,Ⅱ-58</t>
+        </is>
+      </c>
+      <c r="F104" s="40" t="inlineStr">
+        <is>
+          <t>doc09</t>
+        </is>
+      </c>
+      <c r="G104" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H104" s="42" t="inlineStr"/>
+    </row>
+    <row r="105" ht="34" customHeight="1">
+      <c r="A105" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B105" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C105" s="42" t="inlineStr">
+        <is>
+          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+        </is>
+      </c>
+      <c r="D105" s="42" t="inlineStr">
+        <is>
+          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+        </is>
+      </c>
+      <c r="E105" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-59</t>
+        </is>
+      </c>
+      <c r="F105" s="40" t="inlineStr">
+        <is>
+          <t>doc02§20-2</t>
+        </is>
+      </c>
+      <c r="G105" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H105" s="42" t="inlineStr"/>
+    </row>
+    <row r="106" ht="34" customHeight="1">
+      <c r="A106" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B106" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C106" s="42" t="inlineStr">
+        <is>
           <t>国の指針・様式の更新有無</t>
         </is>
       </c>
-      <c r="D101" s="42" t="inlineStr">
+      <c r="D106" s="42" t="inlineStr">
         <is>
           <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
-      <c r="E101" s="40" t="inlineStr">
+      <c r="E106" s="40" t="inlineStr">
         <is>
           <t>Ⅰ-11</t>
         </is>
       </c>
-      <c r="F101" s="40" t="inlineStr">
+      <c r="F106" s="40" t="inlineStr">
         <is>
           <t>doc04,doc05</t>
         </is>
       </c>
-      <c r="G101" s="40" t="inlineStr">
+      <c r="G106" s="40" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H101" s="42" t="inlineStr"/>
+      <c r="H106" s="42" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H89"/>
+  <autoFilter ref="A4:H94"/>
   <mergeCells count="3">
+    <mergeCell ref="A96:H96"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A91:H91"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$94</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2897,120 +2897,132 @@
       <c r="P37" s="25" t="inlineStr"/>
     </row>
     <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="18" t="inlineStr">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Ⅰ-34</t>
         </is>
       </c>
-      <c r="B38" s="19" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>Ⅰ ニーズ調査</t>
         </is>
       </c>
-      <c r="C38" s="19" t="inlineStr">
+      <c r="C38" s="12" t="inlineStr">
         <is>
           <t>Ⅰ-4 データ入力</t>
         </is>
       </c>
-      <c r="D38" s="20" t="inlineStr">
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>用紙回答のデータ入力</t>
         </is>
       </c>
-      <c r="E38" s="18" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>仕様書4Ⅰ(5)</t>
         </is>
       </c>
-      <c r="F38" s="18" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G38" s="20" t="inlineStr">
+      <c r="G38" s="13" t="inlineStr">
         <is>
           <t>入力データ</t>
         </is>
       </c>
-      <c r="H38" s="20" t="inlineStr">
+      <c r="H38" s="13" t="inlineStr">
         <is>
           <t>厚労省提示の集計ファイル様式</t>
         </is>
       </c>
-      <c r="I38" s="18" t="inlineStr">
+      <c r="I38" s="11" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J38" s="21" t="n"/>
-      <c r="K38" s="21" t="n"/>
-      <c r="L38" s="21" t="n"/>
-      <c r="M38" s="21" t="n"/>
-      <c r="N38" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="18" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P38" s="20" t="inlineStr"/>
+      <c r="J38" s="14" t="n"/>
+      <c r="K38" s="14" t="n"/>
+      <c r="L38" s="14" t="n">
+        <v>46268</v>
+      </c>
+      <c r="M38" s="14" t="n"/>
+      <c r="N38" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O38" s="16" t="inlineStr">
+        <is>
+          <t>着手</t>
+        </is>
+      </c>
+      <c r="P38" s="13" t="inlineStr">
+        <is>
+          <t>★doc25§6-2で入力上の留意点6件を確定（複数回答は選択肢ごとに0-1の横持ち／自由記述は原文保持／小分け送付に対応した受付日・ロット番号の記録 ほか）。入力体制は村と要協議（K-93）。</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="23" t="inlineStr">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Ⅰ-35</t>
         </is>
       </c>
-      <c r="B39" s="24" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>Ⅰ ニーズ調査</t>
         </is>
       </c>
-      <c r="C39" s="24" t="inlineStr">
+      <c r="C39" s="12" t="inlineStr">
         <is>
           <t>Ⅰ-4 データ入力</t>
         </is>
       </c>
-      <c r="D39" s="25" t="inlineStr">
+      <c r="D39" s="13" t="inlineStr">
         <is>
           <t>ウェブ回答データの取込</t>
         </is>
       </c>
-      <c r="E39" s="23" t="inlineStr">
+      <c r="E39" s="11" t="inlineStr">
         <is>
           <t>仕様書4Ⅰ(5)</t>
         </is>
       </c>
-      <c r="F39" s="23" t="inlineStr">
+      <c r="F39" s="11" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G39" s="25" t="inlineStr">
+      <c r="G39" s="13" t="inlineStr">
         <is>
           <t>入力データ</t>
         </is>
       </c>
-      <c r="H39" s="25" t="inlineStr"/>
-      <c r="I39" s="23" t="inlineStr">
+      <c r="H39" s="13" t="inlineStr"/>
+      <c r="I39" s="11" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="J39" s="26" t="n"/>
-      <c r="K39" s="26" t="n"/>
-      <c r="L39" s="26" t="n"/>
-      <c r="M39" s="26" t="n"/>
-      <c r="N39" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P39" s="25" t="inlineStr"/>
+      <c r="J39" s="14" t="n"/>
+      <c r="K39" s="14" t="n"/>
+      <c r="L39" s="14" t="n">
+        <v>46268</v>
+      </c>
+      <c r="M39" s="14" t="n"/>
+      <c r="N39" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O39" s="16" t="inlineStr">
+        <is>
+          <t>着手</t>
+        </is>
+      </c>
+      <c r="P39" s="13" t="inlineStr">
+        <is>
+          <t>★doc25§6-1でデータレイアウトを確定（管理番号・回答方法・受付日・地区・性別・年齢・認定状況・認定日＋各設問＋派生変数）。紙とWebを同一レイアウトに揃える。Webは必須入力により無回答率が構造的に異なるため回答方法別の集計を必ず1回行う。</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="18" t="inlineStr">
@@ -3241,7 +3253,7 @@
       </c>
       <c r="M43" s="14" t="n"/>
       <c r="N43" s="15" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="O43" s="16" t="inlineStr">
         <is>
@@ -3303,7 +3315,7 @@
       </c>
       <c r="M44" s="14" t="n"/>
       <c r="N44" s="15" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="O44" s="16" t="inlineStr">
         <is>
@@ -3383,64 +3395,70 @@
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="18" t="inlineStr">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>Ⅰ-42</t>
         </is>
       </c>
-      <c r="B46" s="19" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>Ⅰ ニーズ調査</t>
         </is>
       </c>
-      <c r="C46" s="19" t="inlineStr">
+      <c r="C46" s="12" t="inlineStr">
         <is>
           <t>Ⅰ-5 集計・分析</t>
         </is>
       </c>
-      <c r="D46" s="20" t="inlineStr">
+      <c r="D46" s="13" t="inlineStr">
         <is>
           <t>設問間クロス集計</t>
         </is>
       </c>
-      <c r="E46" s="18" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>仕様書4Ⅰ(6)</t>
         </is>
       </c>
-      <c r="F46" s="18" t="inlineStr">
+      <c r="F46" s="11" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G46" s="20" t="inlineStr">
+      <c r="G46" s="13" t="inlineStr">
         <is>
           <t>集計表</t>
         </is>
       </c>
-      <c r="H46" s="20" t="inlineStr">
+      <c r="H46" s="13" t="inlineStr">
         <is>
           <t>村と協議のうえ設計</t>
         </is>
       </c>
-      <c r="I46" s="18" t="inlineStr">
+      <c r="I46" s="11" t="inlineStr">
         <is>
           <t>R8.10〜11</t>
         </is>
       </c>
-      <c r="J46" s="21" t="n"/>
-      <c r="K46" s="21" t="n"/>
-      <c r="L46" s="21" t="n"/>
-      <c r="M46" s="21" t="n"/>
-      <c r="N46" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="18" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P46" s="20" t="inlineStr"/>
+      <c r="J46" s="14" t="n"/>
+      <c r="K46" s="14" t="n"/>
+      <c r="L46" s="14" t="n">
+        <v>46268</v>
+      </c>
+      <c r="M46" s="14" t="n"/>
+      <c r="N46" s="15" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O46" s="16" t="inlineStr">
+        <is>
+          <t>着手</t>
+        </is>
+      </c>
+      <c r="P46" s="13" t="inlineStr">
+        <is>
+          <t>★doc25／output/07_集計仕様書.xlsx でクロス表20件を定義（うち★10件が分析編の中核）。X-01疾病数×リスク該当領域数、X-02認定状況×リスク、X-03生活機能4層×参加意向、X-04支え合いの受領×提供、X-15施設入所検討×村内施設、X-16要介護度×就労継続。X-02とX-03は村からの認定データ（K-87）が前提。</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
@@ -3495,7 +3513,7 @@
       </c>
       <c r="M47" s="14" t="n"/>
       <c r="N47" s="15" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="O47" s="16" t="inlineStr">
         <is>
@@ -3619,7 +3637,7 @@
       </c>
       <c r="M49" s="14" t="n"/>
       <c r="N49" s="15" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="O49" s="16" t="inlineStr">
         <is>
@@ -3633,64 +3651,70 @@
       </c>
     </row>
     <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="18" t="inlineStr">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>Ⅰ-46</t>
         </is>
       </c>
-      <c r="B50" s="19" t="inlineStr">
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>Ⅰ ニーズ調査</t>
         </is>
       </c>
-      <c r="C50" s="19" t="inlineStr">
+      <c r="C50" s="12" t="inlineStr">
         <is>
           <t>Ⅰ-5 集計・分析</t>
         </is>
       </c>
-      <c r="D50" s="20" t="inlineStr">
+      <c r="D50" s="13" t="inlineStr">
         <is>
           <t>見える化システム登録用データの作成</t>
         </is>
       </c>
-      <c r="E50" s="18" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t>手引き</t>
         </is>
       </c>
-      <c r="F50" s="18" t="inlineStr">
+      <c r="F50" s="11" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G50" s="20" t="inlineStr">
+      <c r="G50" s="13" t="inlineStr">
         <is>
           <t>登録用データ</t>
         </is>
       </c>
-      <c r="H50" s="20" t="inlineStr">
+      <c r="H50" s="13" t="inlineStr">
         <is>
           <t>標準様式の項目順に並べ替えが必要</t>
         </is>
       </c>
-      <c r="I50" s="18" t="inlineStr">
+      <c r="I50" s="11" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J50" s="21" t="n"/>
-      <c r="K50" s="21" t="n"/>
-      <c r="L50" s="21" t="n"/>
-      <c r="M50" s="21" t="n"/>
-      <c r="N50" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="18" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P50" s="20" t="inlineStr"/>
+      <c r="J50" s="14" t="n"/>
+      <c r="K50" s="14" t="n"/>
+      <c r="L50" s="14" t="n">
+        <v>46268</v>
+      </c>
+      <c r="M50" s="14" t="n"/>
+      <c r="N50" s="15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O50" s="16" t="inlineStr">
+        <is>
+          <t>着手</t>
+        </is>
+      </c>
+      <c r="P50" s="13" t="inlineStr">
+        <is>
+          <t>★doc25§6-3で方針を確定。村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルとして作成する。並べ替え表は集計プログラムに組み込む。登録作業の分担は村と要協議（K-94）。</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="23" t="inlineStr">
@@ -5963,64 +5987,70 @@
       </c>
     </row>
     <row r="87" ht="30" customHeight="1">
-      <c r="A87" s="23" t="inlineStr">
+      <c r="A87" s="11" t="inlineStr">
         <is>
           <t>Ⅱ-83</t>
         </is>
       </c>
-      <c r="B87" s="24" t="inlineStr">
+      <c r="B87" s="12" t="inlineStr">
         <is>
           <t>Ⅱ 計画策定</t>
         </is>
       </c>
-      <c r="C87" s="24" t="inlineStr">
+      <c r="C87" s="12" t="inlineStr">
         <is>
           <t>Ⅱ-8 策定委員会支援</t>
         </is>
       </c>
-      <c r="D87" s="25" t="inlineStr">
+      <c r="D87" s="13" t="inlineStr">
         <is>
           <t>第2回 会議資料の作成</t>
         </is>
       </c>
-      <c r="E87" s="23" t="inlineStr">
+      <c r="E87" s="11" t="inlineStr">
         <is>
           <t>仕様書4Ⅱ(8)</t>
         </is>
       </c>
-      <c r="F87" s="23" t="inlineStr">
+      <c r="F87" s="11" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G87" s="25" t="inlineStr">
+      <c r="G87" s="13" t="inlineStr">
         <is>
           <t>会議資料</t>
         </is>
       </c>
-      <c r="H87" s="25" t="inlineStr">
+      <c r="H87" s="13" t="inlineStr">
         <is>
           <t>★アンケート分析結果・第9期の効果検証（R7実績まで）・骨子・施策体系・見込量・保険料概算・素案（完成度7割）</t>
         </is>
       </c>
-      <c r="I87" s="23" t="inlineStr">
+      <c r="I87" s="11" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J87" s="26" t="n"/>
-      <c r="K87" s="26" t="n"/>
-      <c r="L87" s="26" t="n"/>
-      <c r="M87" s="26" t="n"/>
-      <c r="N87" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P87" s="25" t="inlineStr"/>
+      <c r="J87" s="14" t="n"/>
+      <c r="K87" s="14" t="n"/>
+      <c r="L87" s="14" t="n">
+        <v>46268</v>
+      </c>
+      <c r="M87" s="14" t="n"/>
+      <c r="N87" s="15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O87" s="16" t="inlineStr">
+        <is>
+          <t>着手</t>
+        </is>
+      </c>
+      <c r="P87" s="13" t="inlineStr">
+        <is>
+          <t>★doc26で資料構成を確定（資料1〜8・約53頁＋素案別冊）。合意を得たい事項5点（基本理念・基本目標／施策体系／サービス見込み量の考え方／保険料の方向性／成果目標・活動指標）を先頭に置く構成。資料2（第9期の評価）と資料5〜7の骨格は調査結果を待たずに10月中に作成可能。</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="18" t="inlineStr">
@@ -7092,7 +7122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H106"/>
+  <dimension ref="A1:H114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8005,27 +8035,27 @@
       </c>
       <c r="B27" s="33" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>スケジュール</t>
         </is>
       </c>
       <c r="C27" s="34" t="inlineStr">
         <is>
-          <t>★給付費適正化「主要3事業の全て実施」が令和7年度6点→令和8年度0点に低下した理由</t>
+          <t>★第2回策定委員会の開催日（11月のいつか）</t>
         </is>
       </c>
       <c r="D27" s="34" t="inlineStr">
         <is>
-          <t>★全国該当率96.9%の指標。縦覧点検は4帳票満点のため、①要介護認定の適正化 か ②ケアプラン等の点検 のいずれかが実施されなくなった可能性。取組の後退か調査票の記載漏れかで対応が変わる。</t>
+          <t>★資料の事前送付の期限が決まる。素案約90頁を当日配付では読めないため事前送付が前提。</t>
         </is>
       </c>
       <c r="E27" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-105</t>
         </is>
       </c>
       <c r="F27" s="35" t="inlineStr">
         <is>
-          <t>doc20§8-2 K-61</t>
+          <t>doc26§10 K-95</t>
         </is>
       </c>
       <c r="G27" s="35" t="inlineStr">
@@ -8048,12 +8078,12 @@
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>★福祉用具購入費・住宅改修費へのリハビリ専門職の関与（配点8点）が令和7年度8点→令和8年度0点に低下した理由</t>
+          <t>★給付費適正化「主要3事業の全て実施」が令和7年度6点→令和8年度0点に低下した理由</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>★アと合わせ14点が1年で失われている。仕組みが失われたのか調査票の記載によるものかを確認。</t>
+          <t>★全国該当率96.9%の指標。縦覧点検は4帳票満点のため、①要介護認定の適正化 か ②ケアプラン等の点検 のいずれかが実施されなくなった可能性。取組の後退か調査票の記載漏れかで対応が変わる。</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -8063,7 +8093,7 @@
       </c>
       <c r="F28" s="35" t="inlineStr">
         <is>
-          <t>doc20§8-2 K-61b</t>
+          <t>doc20§8-2 K-61</t>
         </is>
       </c>
       <c r="G28" s="35" t="inlineStr">
@@ -8086,22 +8116,22 @@
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>認知症サポーター養成数・認知症地域支援推進員の配置と活動内容・チームオレンジの整備予定</t>
+          <t>★福祉用具購入費・住宅改修費へのリハビリ専門職の関与（配点8点）が令和7年度8点→令和8年度0点に低下した理由</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>★支援交付金目標Ⅱ（認知症総合支援）は32/100点で全国平均51.1点を19点下回る唯一の目標。3か年で唯一低下局面があった。</t>
+          <t>★アと合わせ14点が1年で失われている。仕組みが失われたのか調査票の記載によるものかを確認。</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F29" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-62</t>
+          <t>doc20§8-2 K-61b</t>
         </is>
       </c>
       <c r="G29" s="35" t="inlineStr">
@@ -8124,12 +8154,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入の取組（健診での聴力チェック等）の有無</t>
+          <t>認知症サポーター養成数・認知症地域支援推進員の配置と活動内容・チームオレンジの整備予定</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>令和8年度評価で配点10点が0点（全国該当率48.8〜68.9%）。保健事業との連携で取得可能。</t>
+          <t>★支援交付金目標Ⅱ（認知症総合支援）は32/100点で全国平均51.1点を19点下回る唯一の目標。3か年で唯一低下局面があった。</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -8139,7 +8169,7 @@
       </c>
       <c r="F30" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-63</t>
+          <t>doc20§6-2 K-62</t>
         </is>
       </c>
       <c r="G30" s="35" t="inlineStr">
@@ -8162,22 +8192,22 @@
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>在宅医療・介護連携推進事業の実施体制（村単独か会津圏域か）と課題・対応策の検討の場</t>
+          <t>難聴高齢者の早期発見・早期介入の取組（健診での聴力チェック等）の有無</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲの「課題・対応策の検討」ア・エが0点（配点計10点、全国該当率57〜72%）。</t>
+          <t>令和8年度評価で配点10点が0点（全国該当率48.8〜68.9%）。保健事業との連携で取得可能。</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F31" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-64</t>
+          <t>doc20§6-2 K-63</t>
         </is>
       </c>
       <c r="G31" s="35" t="inlineStr">
@@ -8200,22 +8230,22 @@
       </c>
       <c r="C32" s="34" t="inlineStr">
         <is>
-          <t>★施設サービスが伸びない要因「重度化による病院への転院」の裏づけデータ</t>
+          <t>在宅医療・介護連携推進事業の実施体制（村単独か会津圏域か）と課題・対応策の検討の場</t>
         </is>
       </c>
       <c r="D32" s="34" t="inlineStr">
         <is>
-          <t>★議事録で示された村の見解。当方は村内施設ゼロ・村外施設依存の文脈で解釈していたため、素案の記述を修正する必要がある。KDB・給付実績で確認したい。</t>
+          <t>支援交付金目標Ⅲの「課題・対応策の検討」ア・エが0点（配点計10点、全国該当率57〜72%）。</t>
         </is>
       </c>
       <c r="E32" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F32" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-75</t>
+          <t>doc20§6-2 K-64</t>
         </is>
       </c>
       <c r="G32" s="35" t="inlineStr">
@@ -8238,22 +8268,22 @@
       </c>
       <c r="C33" s="34" t="inlineStr">
         <is>
-          <t>★要介護認定データの提供時期と項目（要介護度・認定日・サービス利用状況）</t>
+          <t>★施設サービスが伸びない要因「重度化による病院への転院」の裏づけデータ</t>
         </is>
       </c>
       <c r="D33" s="34" t="inlineStr">
         <is>
-          <t>★仕様書4Ⅰ(5)。ICF分析の「認定状況×生活機能リスク」表と在宅調査のクロスに必須。目的外利用の手続きの確認を含む。議事録の「元気な軽度者が総合事業を利用している」の検証はこの紐付けでしかできない。</t>
+          <t>★議事録で示された村の見解。当方は村内施設ゼロ・村外施設依存の文脈で解釈していたため、素案の記述を修正する必要がある。KDB・給付実績で確認したい。</t>
         </is>
       </c>
       <c r="E33" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-37</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F33" s="35" t="inlineStr">
         <is>
-          <t>doc24§12 K-87</t>
+          <t>doc22 K-75</t>
         </is>
       </c>
       <c r="G33" s="35" t="inlineStr">
@@ -8271,27 +8301,27 @@
       </c>
       <c r="B34" s="33" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C34" s="34" t="inlineStr">
         <is>
-          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
+          <t>★要介護認定データの提供時期と項目（要介護度・認定日・サービス利用状況）</t>
         </is>
       </c>
       <c r="D34" s="34" t="inlineStr">
         <is>
-          <t>連絡体制表の確定。第9期概要版の発行は住民課。</t>
+          <t>★仕様書4Ⅰ(5)。ICF分析の「認定状況×生活機能リスク」表と在宅調査のクロスに必須。目的外利用の手続きの確認を含む。議事録の「元気な軽度者が総合事業を利用している」の検証はこの紐付けでしかできない。</t>
         </is>
       </c>
       <c r="E34" s="35" t="inlineStr">
         <is>
-          <t>０-04</t>
+          <t>Ⅰ-37</t>
         </is>
       </c>
       <c r="F34" s="35" t="inlineStr">
         <is>
-          <t>doc01-1</t>
+          <t>doc24§12 K-87</t>
         </is>
       </c>
       <c r="G34" s="35" t="inlineStr">
@@ -8314,22 +8344,22 @@
       </c>
       <c r="C35" s="34" t="inlineStr">
         <is>
-          <t>契約締結日・契約書の取り交わし状況</t>
+          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
         </is>
       </c>
       <c r="D35" s="34" t="inlineStr">
         <is>
-          <t>業務開始日の確定。</t>
+          <t>連絡体制表の確定。第9期概要版の発行は住民課。</t>
         </is>
       </c>
       <c r="E35" s="35" t="inlineStr">
         <is>
-          <t>０-02</t>
+          <t>０-04</t>
         </is>
       </c>
       <c r="F35" s="35" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>doc01-1</t>
         </is>
       </c>
       <c r="G35" s="35" t="inlineStr">
@@ -8352,22 +8382,22 @@
       </c>
       <c r="C36" s="34" t="inlineStr">
         <is>
-          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
+          <t>契約締結日・契約書の取り交わし状況</t>
         </is>
       </c>
       <c r="D36" s="34" t="inlineStr">
         <is>
-          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
+          <t>業務開始日の確定。</t>
         </is>
       </c>
       <c r="E36" s="35" t="inlineStr">
         <is>
-          <t>０-06</t>
+          <t>０-02</t>
         </is>
       </c>
       <c r="F36" s="35" t="inlineStr">
         <is>
-          <t>doc19 追-12</t>
+          <t>―</t>
         </is>
       </c>
       <c r="G36" s="35" t="inlineStr">
@@ -8390,22 +8420,22 @@
       </c>
       <c r="C37" s="34" t="inlineStr">
         <is>
-          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
+          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
         </is>
       </c>
       <c r="D37" s="34" t="inlineStr">
         <is>
-          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
+          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
         </is>
       </c>
       <c r="E37" s="35" t="inlineStr">
         <is>
-          <t>Ⅴ-96</t>
+          <t>０-06</t>
         </is>
       </c>
       <c r="F37" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-78</t>
+          <t>doc19 追-12</t>
         </is>
       </c>
       <c r="G37" s="35" t="inlineStr">
@@ -8428,12 +8458,12 @@
       </c>
       <c r="C38" s="34" t="inlineStr">
         <is>
-          <t>自由記述の匿名化の方針（削除・置換の範囲）</t>
+          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
         </is>
       </c>
       <c r="D38" s="34" t="inlineStr">
         <is>
-          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。</t>
+          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
         </is>
       </c>
       <c r="E38" s="35" t="inlineStr">
@@ -8443,7 +8473,7 @@
       </c>
       <c r="F38" s="35" t="inlineStr">
         <is>
-          <t>doc24§12 K-89</t>
+          <t>doc22 K-78</t>
         </is>
       </c>
       <c r="G38" s="35" t="inlineStr">
@@ -8461,27 +8491,27 @@
       </c>
       <c r="B39" s="33" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C39" s="34" t="inlineStr">
         <is>
-          <t>ICF分析は標準設問のみで完結することの確認</t>
+          <t>自由記述の匿名化の方針（削除・置換の範囲）</t>
         </is>
       </c>
       <c r="D39" s="34" t="inlineStr">
         <is>
-          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
+          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。</t>
         </is>
       </c>
       <c r="E39" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-50</t>
+          <t>Ⅴ-96</t>
         </is>
       </c>
       <c r="F39" s="35" t="inlineStr">
         <is>
-          <t>doc23§3-4</t>
+          <t>doc24§12 K-89</t>
         </is>
       </c>
       <c r="G39" s="35" t="inlineStr">
@@ -8499,27 +8529,27 @@
       </c>
       <c r="B40" s="33" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
+          <t>第2回策定委員会の資料の事前送付の可否と時期</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
+          <t>素案（完成度7割・約90頁）は別冊として事前送付する前提で資料を設計している。</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅱ-105</t>
         </is>
       </c>
       <c r="F40" s="35" t="inlineStr">
         <is>
-          <t>doc24§12 K-86</t>
+          <t>doc26§10 K-97</t>
         </is>
       </c>
       <c r="G40" s="35" t="inlineStr">
@@ -8537,27 +8567,27 @@
       </c>
       <c r="B41" s="33" t="inlineStr">
         <is>
-          <t>委員会</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C41" s="34" t="inlineStr">
         <is>
-          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
+          <t>ICF分析は標準設問のみで完結することの確認</t>
         </is>
       </c>
       <c r="D41" s="34" t="inlineStr">
         <is>
-          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
+          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
         </is>
       </c>
       <c r="E41" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-80,Ⅱ-81</t>
+          <t>Ⅰ-50</t>
         </is>
       </c>
       <c r="F41" s="35" t="inlineStr">
         <is>
-          <t>doc01-6,doc19 追-15</t>
+          <t>doc23§3-4</t>
         </is>
       </c>
       <c r="G41" s="35" t="inlineStr">
@@ -8575,27 +8605,27 @@
       </c>
       <c r="B42" s="33" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C42" s="34" t="inlineStr">
         <is>
-          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
+          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
         </is>
       </c>
       <c r="D42" s="34" t="inlineStr">
         <is>
-          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
+          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
         </is>
       </c>
       <c r="E42" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-76,Ⅱ-77</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F42" s="35" t="inlineStr">
         <is>
-          <t>doc01-7,doc19 指-3</t>
+          <t>doc24§12 K-86</t>
         </is>
       </c>
       <c r="G42" s="35" t="inlineStr">
@@ -8613,27 +8643,27 @@
       </c>
       <c r="B43" s="33" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C43" s="34" t="inlineStr">
         <is>
-          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
+          <t>★リスク判定10種の該当基準（見える化システムの算出方法との突合）</t>
         </is>
       </c>
       <c r="D43" s="34" t="inlineStr">
         <is>
-          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
+          <t>★手引きに該当基準の明記があるのはBMI 18.5以下のみ。他9種は基本チェックリストに準じた案を置いているが、独自基準では全国・県と比較できない。手引きは算出方法が将来更新され得るとも記載しており、第9期の基準の流用も不可。</t>
         </is>
       </c>
       <c r="E43" s="35" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅰ-46</t>
         </is>
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-79</t>
+          <t>doc25§4-2 K-91</t>
         </is>
       </c>
       <c r="G43" s="35" t="inlineStr">
@@ -8651,27 +8681,27 @@
       </c>
       <c r="B44" s="33" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>委員会</t>
         </is>
       </c>
       <c r="C44" s="34" t="inlineStr">
         <is>
-          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
+          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
         </is>
       </c>
       <c r="D44" s="34" t="inlineStr">
         <is>
-          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
+          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
         </is>
       </c>
       <c r="E44" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-80,Ⅱ-81</t>
         </is>
       </c>
       <c r="F44" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-66</t>
+          <t>doc01-6,doc19 追-15</t>
         </is>
       </c>
       <c r="G44" s="35" t="inlineStr">
@@ -8689,27 +8719,27 @@
       </c>
       <c r="B45" s="33" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C45" s="34" t="inlineStr">
         <is>
-          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
+          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
         </is>
       </c>
       <c r="D45" s="34" t="inlineStr">
         <is>
-          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
+          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
         </is>
       </c>
       <c r="E45" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-62</t>
+          <t>Ⅱ-76,Ⅱ-77</t>
         </is>
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-81</t>
+          <t>doc01-7,doc19 指-3</t>
         </is>
       </c>
       <c r="G45" s="35" t="inlineStr">
@@ -8727,27 +8757,27 @@
       </c>
       <c r="B46" s="33" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C46" s="34" t="inlineStr">
         <is>
-          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
+          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
         </is>
       </c>
       <c r="D46" s="34" t="inlineStr">
         <is>
-          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
+          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
         </is>
       </c>
       <c r="E46" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F46" s="35" t="inlineStr">
         <is>
-          <t>doc21§5 K-69</t>
+          <t>doc22 K-79</t>
         </is>
       </c>
       <c r="G46" s="35" t="inlineStr">
@@ -8765,27 +8795,27 @@
       </c>
       <c r="B47" s="33" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C47" s="34" t="inlineStr">
         <is>
-          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
+          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
         </is>
       </c>
       <c r="D47" s="34" t="inlineStr">
         <is>
-          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
+          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
         </is>
       </c>
       <c r="E47" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>doc21§5 K-70</t>
+          <t>doc20§6-2 K-66</t>
         </is>
       </c>
       <c r="G47" s="35" t="inlineStr">
@@ -8803,225 +8833,225 @@
       </c>
       <c r="B48" s="33" t="inlineStr">
         <is>
+          <t>方針</t>
+        </is>
+      </c>
+      <c r="C48" s="34" t="inlineStr">
+        <is>
+          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
+        </is>
+      </c>
+      <c r="D48" s="34" t="inlineStr">
+        <is>
+          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
+        </is>
+      </c>
+      <c r="E48" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-62</t>
+        </is>
+      </c>
+      <c r="F48" s="35" t="inlineStr">
+        <is>
+          <t>doc22 K-81</t>
+        </is>
+      </c>
+      <c r="G48" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H48" s="34" t="inlineStr"/>
+    </row>
+    <row r="49" ht="34" customHeight="1">
+      <c r="A49" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B49" s="33" t="inlineStr">
+        <is>
+          <t>方針</t>
+        </is>
+      </c>
+      <c r="C49" s="34" t="inlineStr">
+        <is>
+          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
+        </is>
+      </c>
+      <c r="D49" s="34" t="inlineStr">
+        <is>
+          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
+        </is>
+      </c>
+      <c r="E49" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-70</t>
+        </is>
+      </c>
+      <c r="F49" s="35" t="inlineStr">
+        <is>
+          <t>doc26§10 K-98</t>
+        </is>
+      </c>
+      <c r="G49" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H49" s="34" t="inlineStr"/>
+    </row>
+    <row r="50" ht="34" customHeight="1">
+      <c r="A50" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B50" s="33" t="inlineStr">
+        <is>
+          <t>方針</t>
+        </is>
+      </c>
+      <c r="C50" s="34" t="inlineStr">
+        <is>
+          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
+        </is>
+      </c>
+      <c r="D50" s="34" t="inlineStr">
+        <is>
+          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。</t>
+        </is>
+      </c>
+      <c r="E50" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-64</t>
+        </is>
+      </c>
+      <c r="F50" s="35" t="inlineStr">
+        <is>
+          <t>doc26§10 K-99</t>
+        </is>
+      </c>
+      <c r="G50" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H50" s="34" t="inlineStr"/>
+    </row>
+    <row r="51" ht="34" customHeight="1">
+      <c r="A51" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B51" s="33" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C51" s="34" t="inlineStr">
+        <is>
+          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
+        </is>
+      </c>
+      <c r="D51" s="34" t="inlineStr">
+        <is>
+          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
+        </is>
+      </c>
+      <c r="E51" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F51" s="35" t="inlineStr">
+        <is>
+          <t>doc21§5 K-69</t>
+        </is>
+      </c>
+      <c r="G51" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H51" s="34" t="inlineStr"/>
+    </row>
+    <row r="52" ht="34" customHeight="1">
+      <c r="A52" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B52" s="33" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C52" s="34" t="inlineStr">
+        <is>
+          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
+        </is>
+      </c>
+      <c r="D52" s="34" t="inlineStr">
+        <is>
+          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
+        </is>
+      </c>
+      <c r="E52" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F52" s="35" t="inlineStr">
+        <is>
+          <t>doc21§5 K-70</t>
+        </is>
+      </c>
+      <c r="G52" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H52" s="34" t="inlineStr"/>
+    </row>
+    <row r="53" ht="34" customHeight="1">
+      <c r="A53" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B53" s="33" t="inlineStr">
+        <is>
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C48" s="34" t="inlineStr">
+      <c r="C53" s="34" t="inlineStr">
         <is>
           <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
         </is>
       </c>
-      <c r="D48" s="34" t="inlineStr">
+      <c r="D53" s="34" t="inlineStr">
         <is>
           <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
         </is>
       </c>
-      <c r="E48" s="35" t="inlineStr">
+      <c r="E53" s="35" t="inlineStr">
         <is>
           <t>Ⅰ-19,Ⅰ-25</t>
         </is>
       </c>
-      <c r="F48" s="35" t="inlineStr">
+      <c r="F53" s="35" t="inlineStr">
         <is>
           <t>doc22 §1</t>
         </is>
       </c>
-      <c r="G48" s="35" t="inlineStr">
+      <c r="G53" s="35" t="inlineStr">
         <is>
           <t>一部回答</t>
         </is>
       </c>
-      <c r="H48" s="34" t="inlineStr"/>
-    </row>
-    <row r="49" ht="34" customHeight="1">
-      <c r="A49" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B49" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C49" s="25" t="inlineStr">
-        <is>
-          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
-        </is>
-      </c>
-      <c r="D49" s="25" t="inlineStr">
-        <is>
-          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
-        </is>
-      </c>
-      <c r="E49" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F49" s="23" t="inlineStr">
-        <is>
-          <t>doc02§22,doc08§8</t>
-        </is>
-      </c>
-      <c r="G49" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H49" s="25" t="inlineStr"/>
-    </row>
-    <row r="50" ht="34" customHeight="1">
-      <c r="A50" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B50" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C50" s="25" t="inlineStr">
-        <is>
-          <t>令和6年度決算および令和7年度の給付費見込</t>
-        </is>
-      </c>
-      <c r="D50" s="25" t="inlineStr">
-        <is>
-          <t>第9期の計画値と実績の乖離を確定させるために必要。</t>
-        </is>
-      </c>
-      <c r="E50" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
-        </is>
-      </c>
-      <c r="F50" s="23" t="inlineStr">
-        <is>
-          <t>doc08§8-1</t>
-        </is>
-      </c>
-      <c r="G50" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H50" s="25" t="inlineStr"/>
-    </row>
-    <row r="51" ht="34" customHeight="1">
-      <c r="A51" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B51" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C51" s="25" t="inlineStr">
-        <is>
-          <t>通いの場の実数（令和3〜7年度）</t>
-        </is>
-      </c>
-      <c r="D51" s="25" t="inlineStr">
-        <is>
-          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。</t>
-        </is>
-      </c>
-      <c r="E51" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F51" s="23" t="inlineStr">
-        <is>
-          <t>doc02§16,§22</t>
-        </is>
-      </c>
-      <c r="G51" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H51" s="25" t="inlineStr"/>
-    </row>
-    <row r="52" ht="34" customHeight="1">
-      <c r="A52" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B52" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C52" s="25" t="inlineStr">
-        <is>
-          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
-        </is>
-      </c>
-      <c r="D52" s="25" t="inlineStr">
-        <is>
-          <t>見える化に該当データがない。第9期は基本目標4-4に位置づけ。</t>
-        </is>
-      </c>
-      <c r="E52" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-68,Ⅱ-69</t>
-        </is>
-      </c>
-      <c r="F52" s="23" t="inlineStr">
-        <is>
-          <t>doc08§8-5</t>
-        </is>
-      </c>
-      <c r="G52" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H52" s="25" t="inlineStr"/>
-    </row>
-    <row r="53" ht="34" customHeight="1">
-      <c r="A53" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B53" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C53" s="25" t="inlineStr">
-        <is>
-          <t>高齢者福祉事業（村単独事業）の実績資料</t>
-        </is>
-      </c>
-      <c r="D53" s="25" t="inlineStr">
-        <is>
-          <t>現行計画の評価に必要。</t>
-        </is>
-      </c>
-      <c r="E53" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
-        </is>
-      </c>
-      <c r="F53" s="23" t="inlineStr">
-        <is>
-          <t>doc01-11</t>
-        </is>
-      </c>
-      <c r="G53" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H53" s="25" t="inlineStr"/>
+      <c r="H53" s="34" t="inlineStr"/>
     </row>
     <row r="54" ht="34" customHeight="1">
       <c r="A54" s="37" t="inlineStr">
@@ -9036,22 +9066,22 @@
       </c>
       <c r="C54" s="25" t="inlineStr">
         <is>
-          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
+          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
         </is>
       </c>
       <c r="D54" s="25" t="inlineStr">
         <is>
-          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
+          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
         </is>
       </c>
       <c r="E54" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-58,Ⅱ-59</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F54" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-9</t>
+          <t>doc02§22,doc08§8</t>
         </is>
       </c>
       <c r="G54" s="23" t="inlineStr">
@@ -9074,22 +9104,22 @@
       </c>
       <c r="C55" s="25" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告（月報・年報）の原データの提供可否</t>
+          <t>令和6年度決算および令和7年度の給付費見込</t>
         </is>
       </c>
       <c r="D55" s="25" t="inlineStr">
         <is>
-          <t>見える化に収録されていない項目（サービス種類別利用者数の月次推移等）が扱えるようになる。</t>
+          <t>第9期の計画値と実績の乖離を確定させるために必要。</t>
         </is>
       </c>
       <c r="E55" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-10</t>
+          <t>doc08§8-1</t>
         </is>
       </c>
       <c r="G55" s="23" t="inlineStr">
@@ -9112,22 +9142,22 @@
       </c>
       <c r="C56" s="25" t="inlineStr">
         <is>
-          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
+          <t>通いの場の実数（令和3〜7年度）</t>
         </is>
       </c>
       <c r="D56" s="25" t="inlineStr">
         <is>
-          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
+          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。</t>
         </is>
       </c>
       <c r="E56" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F56" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc02§16,§22</t>
         </is>
       </c>
       <c r="G56" s="23" t="inlineStr">
@@ -9150,22 +9180,22 @@
       </c>
       <c r="C57" s="25" t="inlineStr">
         <is>
-          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
+          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
         </is>
       </c>
       <c r="D57" s="25" t="inlineStr">
         <is>
-          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
+          <t>見える化に該当データがない。第9期は基本目標4-4に位置づけ。</t>
         </is>
       </c>
       <c r="E57" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-68,Ⅱ-69</t>
         </is>
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc08§8-5</t>
         </is>
       </c>
       <c r="G57" s="23" t="inlineStr">
@@ -9188,22 +9218,22 @@
       </c>
       <c r="C58" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
+          <t>高齢者福祉事業（村単独事業）の実績資料</t>
         </is>
       </c>
       <c r="D58" s="25" t="inlineStr">
         <is>
-          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
+          <t>現行計画の評価に必要。</t>
         </is>
       </c>
       <c r="E58" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F58" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc01-11</t>
         </is>
       </c>
       <c r="G58" s="23" t="inlineStr">
@@ -9226,22 +9256,22 @@
       </c>
       <c r="C59" s="25" t="inlineStr">
         <is>
-          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
+          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
         </is>
       </c>
       <c r="D59" s="25" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
+          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
         </is>
       </c>
       <c r="E59" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-58,Ⅱ-59</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-65</t>
+          <t>doc19 追-9</t>
         </is>
       </c>
       <c r="G59" s="23" t="inlineStr">
@@ -9264,22 +9294,22 @@
       </c>
       <c r="C60" s="25" t="inlineStr">
         <is>
-          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
+          <t>介護保険事業状況報告（月報・年報）の原データの提供可否</t>
         </is>
       </c>
       <c r="D60" s="25" t="inlineStr">
         <is>
-          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
+          <t>見える化に収録されていない項目（サービス種類別利用者数の月次推移等）が扱えるようになる。</t>
         </is>
       </c>
       <c r="E60" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F60" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-68</t>
+          <t>doc19 追-10</t>
         </is>
       </c>
       <c r="G60" s="23" t="inlineStr">
@@ -9302,22 +9332,22 @@
       </c>
       <c r="C61" s="25" t="inlineStr">
         <is>
-          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
+          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
         </is>
       </c>
       <c r="D61" s="25" t="inlineStr">
         <is>
-          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
+          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
         </is>
       </c>
       <c r="E61" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-71</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G61" s="23" t="inlineStr">
@@ -9340,22 +9370,22 @@
       </c>
       <c r="C62" s="25" t="inlineStr">
         <is>
-          <t>シルバー人材センターの会員数・受注実績</t>
+          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
         </is>
       </c>
       <c r="D62" s="25" t="inlineStr">
         <is>
-          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
+          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
         </is>
       </c>
       <c r="E62" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F62" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-72</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G62" s="23" t="inlineStr">
@@ -9373,27 +9403,27 @@
       </c>
       <c r="B63" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C63" s="25" t="inlineStr">
         <is>
-          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
+          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
         </is>
       </c>
       <c r="D63" s="25" t="inlineStr">
         <is>
-          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
+          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
         </is>
       </c>
       <c r="E63" s="23" t="inlineStr">
         <is>
-          <t>Ⅴ-95</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-67</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G63" s="23" t="inlineStr">
@@ -9411,27 +9441,27 @@
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C64" s="25" t="inlineStr">
         <is>
-          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
+          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
         </is>
       </c>
       <c r="D64" s="25" t="inlineStr">
         <is>
-          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
+          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
         </is>
       </c>
       <c r="E64" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F64" s="23" t="inlineStr">
         <is>
-          <t>doc19 指-5</t>
+          <t>doc20§6-2 K-65</t>
         </is>
       </c>
       <c r="G64" s="23" t="inlineStr">
@@ -9449,27 +9479,27 @@
       </c>
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C65" s="25" t="inlineStr">
         <is>
-          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
+          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
         </is>
       </c>
       <c r="D65" s="25" t="inlineStr">
         <is>
-          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
+          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
         </is>
       </c>
       <c r="E65" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-108</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
-          <t>doc22 K-80</t>
+          <t>doc21§5 K-68</t>
         </is>
       </c>
       <c r="G65" s="23" t="inlineStr">
@@ -9487,27 +9517,27 @@
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C66" s="25" t="inlineStr">
         <is>
-          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
+          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
         </is>
       </c>
       <c r="D66" s="25" t="inlineStr">
         <is>
-          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
+          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
         </is>
       </c>
       <c r="E66" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-90</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F66" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-88</t>
+          <t>doc21§5 K-71</t>
         </is>
       </c>
       <c r="G66" s="23" t="inlineStr">
@@ -9525,27 +9555,27 @@
       </c>
       <c r="B67" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C67" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
+          <t>シルバー人材センターの会員数・受注実績</t>
         </is>
       </c>
       <c r="D67" s="25" t="inlineStr">
         <is>
-          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
+          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
         </is>
       </c>
       <c r="E67" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
-          <t>doc09§4,§10</t>
+          <t>doc21§5 K-72</t>
         </is>
       </c>
       <c r="G67" s="23" t="inlineStr">
@@ -9563,27 +9593,27 @@
       </c>
       <c r="B68" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C68" s="25" t="inlineStr">
         <is>
-          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
+          <t>第9期調査の集計基準・集計表の提供</t>
         </is>
       </c>
       <c r="D68" s="25" t="inlineStr">
         <is>
-          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
+          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
         </is>
       </c>
       <c r="E68" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F68" s="23" t="inlineStr">
         <is>
-          <t>doc09§8,§10</t>
+          <t>doc25§8 K-92</t>
         </is>
       </c>
       <c r="G68" s="23" t="inlineStr">
@@ -9601,27 +9631,27 @@
       </c>
       <c r="B69" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C69" s="25" t="inlineStr">
         <is>
-          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
+          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
         </is>
       </c>
       <c r="D69" s="25" t="inlineStr">
         <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
+          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
         </is>
       </c>
       <c r="E69" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅴ-95</t>
         </is>
       </c>
       <c r="F69" s="23" t="inlineStr">
         <is>
-          <t>doc02§17,doc07,doc18 4-1</t>
+          <t>doc20§6-2 K-67</t>
         </is>
       </c>
       <c r="G69" s="23" t="inlineStr">
@@ -9639,27 +9669,27 @@
       </c>
       <c r="B70" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C70" s="25" t="inlineStr">
         <is>
-          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
+          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
         </is>
       </c>
       <c r="D70" s="25" t="inlineStr">
         <is>
-          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
+          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
         </is>
       </c>
       <c r="E70" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-75</t>
+          <t>Ⅰ-35</t>
         </is>
       </c>
       <c r="F70" s="23" t="inlineStr">
         <is>
-          <t>doc17 C-1,doc02§20-2</t>
+          <t>doc25§8 K-93</t>
         </is>
       </c>
       <c r="G70" s="23" t="inlineStr">
@@ -9677,27 +9707,27 @@
       </c>
       <c r="B71" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C71" s="25" t="inlineStr">
         <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
         </is>
       </c>
       <c r="D71" s="25" t="inlineStr">
         <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
         </is>
       </c>
       <c r="E71" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
+          <t>Ⅰ-48</t>
         </is>
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
-          <t>doc13§6</t>
+          <t>doc25§8 K-94</t>
         </is>
       </c>
       <c r="G71" s="23" t="inlineStr">
@@ -9715,27 +9745,27 @@
       </c>
       <c r="B72" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C72" s="25" t="inlineStr">
         <is>
-          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
         </is>
       </c>
       <c r="D72" s="25" t="inlineStr">
         <is>
-          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
+          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
         </is>
       </c>
       <c r="E72" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F72" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-14</t>
+          <t>doc19 指-5</t>
         </is>
       </c>
       <c r="G72" s="23" t="inlineStr">
@@ -9753,27 +9783,27 @@
       </c>
       <c r="B73" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C73" s="25" t="inlineStr">
         <is>
-          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
         </is>
       </c>
       <c r="D73" s="25" t="inlineStr">
         <is>
-          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
         </is>
       </c>
       <c r="E73" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-108</t>
         </is>
       </c>
       <c r="F73" s="23" t="inlineStr">
         <is>
-          <t>doc19 §3</t>
+          <t>doc22 K-80</t>
         </is>
       </c>
       <c r="G73" s="23" t="inlineStr">
@@ -9791,27 +9821,27 @@
       </c>
       <c r="B74" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C74" s="25" t="inlineStr">
         <is>
-          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
+          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
         </is>
       </c>
       <c r="D74" s="25" t="inlineStr">
         <is>
-          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
+          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
         </is>
       </c>
       <c r="E74" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅳ-90</t>
         </is>
       </c>
       <c r="F74" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-73</t>
+          <t>doc24§12 K-88</t>
         </is>
       </c>
       <c r="G74" s="23" t="inlineStr">
@@ -9834,22 +9864,22 @@
       </c>
       <c r="C75" s="25" t="inlineStr">
         <is>
-          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
+          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
         </is>
       </c>
       <c r="D75" s="25" t="inlineStr">
         <is>
-          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
+          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
         </is>
       </c>
       <c r="E75" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-105</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F75" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-90</t>
+          <t>doc09§4,§10</t>
         </is>
       </c>
       <c r="G75" s="23" t="inlineStr">
@@ -9867,27 +9897,27 @@
       </c>
       <c r="B76" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C76" s="25" t="inlineStr">
         <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
         </is>
       </c>
       <c r="D76" s="25" t="inlineStr">
         <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
         </is>
       </c>
       <c r="E76" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F76" s="23" t="inlineStr">
         <is>
-          <t>doc07§4</t>
+          <t>doc09§8,§10</t>
         </is>
       </c>
       <c r="G76" s="23" t="inlineStr">
@@ -9905,27 +9935,27 @@
       </c>
       <c r="B77" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C77" s="25" t="inlineStr">
         <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
         </is>
       </c>
       <c r="D77" s="25" t="inlineStr">
         <is>
-          <t>評価指標の読み方に影響。</t>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
         </is>
       </c>
       <c r="E77" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F77" s="23" t="inlineStr">
         <is>
-          <t>doc07§8-4</t>
+          <t>doc02§17,doc07,doc18 4-1</t>
         </is>
       </c>
       <c r="G77" s="23" t="inlineStr">
@@ -9943,27 +9973,27 @@
       </c>
       <c r="B78" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C78" s="25" t="inlineStr">
         <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
         </is>
       </c>
       <c r="D78" s="25" t="inlineStr">
         <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
         </is>
       </c>
       <c r="E78" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-56,Ⅱ-75</t>
         </is>
       </c>
       <c r="F78" s="23" t="inlineStr">
         <is>
-          <t>doc08§4,§8-2</t>
+          <t>doc17 C-1,doc02§20-2</t>
         </is>
       </c>
       <c r="G78" s="23" t="inlineStr">
@@ -9981,27 +10011,27 @@
       </c>
       <c r="B79" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C79" s="25" t="inlineStr">
         <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
         </is>
       </c>
       <c r="D79" s="25" t="inlineStr">
         <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
         </is>
       </c>
       <c r="E79" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-60,Ⅱ-65</t>
         </is>
       </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
-          <t>doc02§20-1</t>
+          <t>doc13§6</t>
         </is>
       </c>
       <c r="G79" s="23" t="inlineStr">
@@ -10019,27 +10049,27 @@
       </c>
       <c r="B80" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C80" s="25" t="inlineStr">
         <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
         </is>
       </c>
       <c r="D80" s="25" t="inlineStr">
         <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
         </is>
       </c>
       <c r="E80" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F80" s="23" t="inlineStr">
         <is>
-          <t>doc15,doc18</t>
+          <t>doc19 追-14</t>
         </is>
       </c>
       <c r="G80" s="23" t="inlineStr">
@@ -10057,27 +10087,27 @@
       </c>
       <c r="B81" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C81" s="25" t="inlineStr">
         <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
         </is>
       </c>
       <c r="D81" s="25" t="inlineStr">
         <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
         </is>
       </c>
       <c r="E81" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc18 3-1</t>
+          <t>doc19 §3</t>
         </is>
       </c>
       <c r="G81" s="23" t="inlineStr">
@@ -10095,27 +10125,27 @@
       </c>
       <c r="B82" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C82" s="25" t="inlineStr">
         <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
         </is>
       </c>
       <c r="D82" s="25" t="inlineStr">
         <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
         </is>
       </c>
       <c r="E82" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F82" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
+          <t>doc21§5 K-73</t>
         </is>
       </c>
       <c r="G82" s="23" t="inlineStr">
@@ -10133,27 +10163,27 @@
       </c>
       <c r="B83" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C83" s="25" t="inlineStr">
         <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
         </is>
       </c>
       <c r="D83" s="25" t="inlineStr">
         <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
         </is>
       </c>
       <c r="E83" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-105</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t>doc17 B-3,doc18 4-3</t>
+          <t>doc24§12 K-90</t>
         </is>
       </c>
       <c r="G83" s="23" t="inlineStr">
@@ -10171,27 +10201,27 @@
       </c>
       <c r="B84" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C84" s="25" t="inlineStr">
         <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
         </is>
       </c>
       <c r="D84" s="25" t="inlineStr">
         <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
         </is>
       </c>
       <c r="E84" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F84" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 2-9</t>
+          <t>doc07§4</t>
         </is>
       </c>
       <c r="G84" s="23" t="inlineStr">
@@ -10209,27 +10239,27 @@
       </c>
       <c r="B85" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C85" s="25" t="inlineStr">
         <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
         </is>
       </c>
       <c r="D85" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+          <t>評価指標の読み方に影響。</t>
         </is>
       </c>
       <c r="E85" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 5-7</t>
+          <t>doc07§8-4</t>
         </is>
       </c>
       <c r="G85" s="23" t="inlineStr">
@@ -10247,27 +10277,27 @@
       </c>
       <c r="B86" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C86" s="25" t="inlineStr">
         <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
         </is>
       </c>
       <c r="D86" s="25" t="inlineStr">
         <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
         </is>
       </c>
       <c r="E86" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F86" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-4</t>
+          <t>doc08§4,§8-2</t>
         </is>
       </c>
       <c r="G86" s="23" t="inlineStr">
@@ -10285,27 +10315,27 @@
       </c>
       <c r="B87" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C87" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
         </is>
       </c>
       <c r="D87" s="25" t="inlineStr">
         <is>
-          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
         </is>
       </c>
       <c r="E87" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-73,Ⅱ-75</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr">
         <is>
-          <t>doc01-5,doc18 1-2</t>
+          <t>doc02§20-1</t>
         </is>
       </c>
       <c r="G87" s="23" t="inlineStr">
@@ -10323,27 +10353,27 @@
       </c>
       <c r="B88" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C88" s="25" t="inlineStr">
         <is>
-          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
         </is>
       </c>
       <c r="D88" s="25" t="inlineStr">
         <is>
-          <t>施策の書きぶりに影響。</t>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
         </is>
       </c>
       <c r="E88" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-72</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F88" s="23" t="inlineStr">
         <is>
-          <t>doc01-12</t>
+          <t>doc15,doc18</t>
         </is>
       </c>
       <c r="G88" s="23" t="inlineStr">
@@ -10361,27 +10391,27 @@
       </c>
       <c r="B89" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C89" s="25" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
         </is>
       </c>
       <c r="D89" s="25" t="inlineStr">
         <is>
-          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
         </is>
       </c>
       <c r="E89" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-13</t>
+          <t>doc14§5,doc18 3-1</t>
         </is>
       </c>
       <c r="G89" s="23" t="inlineStr">
@@ -10399,27 +10429,27 @@
       </c>
       <c r="B90" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C90" s="25" t="inlineStr">
         <is>
-          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
         </is>
       </c>
       <c r="D90" s="25" t="inlineStr">
         <is>
-          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
         </is>
       </c>
       <c r="E90" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-31</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F90" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-6</t>
+          <t>doc14§5,doc15,doc18 4-5</t>
         </is>
       </c>
       <c r="G90" s="23" t="inlineStr">
@@ -10437,27 +10467,27 @@
       </c>
       <c r="B91" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C91" s="25" t="inlineStr">
         <is>
-          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
         </is>
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-40,Ⅰ-42</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-7</t>
+          <t>doc17 B-3,doc18 4-3</t>
         </is>
       </c>
       <c r="G91" s="23" t="inlineStr">
@@ -10475,422 +10505,422 @@
       </c>
       <c r="B92" s="24" t="inlineStr">
         <is>
+          <t>素案</t>
+        </is>
+      </c>
+      <c r="C92" s="25" t="inlineStr">
+        <is>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+        </is>
+      </c>
+      <c r="D92" s="25" t="inlineStr">
+        <is>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+        </is>
+      </c>
+      <c r="E92" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F92" s="23" t="inlineStr">
+        <is>
+          <t>doc17 A-1,doc18 2-9</t>
+        </is>
+      </c>
+      <c r="G92" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H92" s="25" t="inlineStr"/>
+    </row>
+    <row r="93" ht="34" customHeight="1">
+      <c r="A93" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B93" s="24" t="inlineStr">
+        <is>
+          <t>素案</t>
+        </is>
+      </c>
+      <c r="C93" s="25" t="inlineStr">
+        <is>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+        </is>
+      </c>
+      <c r="D93" s="25" t="inlineStr">
+        <is>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+        </is>
+      </c>
+      <c r="E93" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-64,Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F93" s="23" t="inlineStr">
+        <is>
+          <t>doc17 A-1,doc18 5-7</t>
+        </is>
+      </c>
+      <c r="G93" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H93" s="25" t="inlineStr"/>
+    </row>
+    <row r="94" ht="34" customHeight="1">
+      <c r="A94" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B94" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C94" s="25" t="inlineStr">
+        <is>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
+        </is>
+      </c>
+      <c r="D94" s="25" t="inlineStr">
+        <is>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+        </is>
+      </c>
+      <c r="E94" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F94" s="23" t="inlineStr">
+        <is>
+          <t>doc08§8-4</t>
+        </is>
+      </c>
+      <c r="G94" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H94" s="25" t="inlineStr"/>
+    </row>
+    <row r="95" ht="34" customHeight="1">
+      <c r="A95" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B95" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C95" s="25" t="inlineStr">
+        <is>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+        </is>
+      </c>
+      <c r="D95" s="25" t="inlineStr">
+        <is>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+        </is>
+      </c>
+      <c r="E95" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-73,Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F95" s="23" t="inlineStr">
+        <is>
+          <t>doc01-5,doc18 1-2</t>
+        </is>
+      </c>
+      <c r="G95" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H95" s="25" t="inlineStr"/>
+    </row>
+    <row r="96" ht="34" customHeight="1">
+      <c r="A96" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B96" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C96" s="25" t="inlineStr">
+        <is>
+          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+        </is>
+      </c>
+      <c r="D96" s="25" t="inlineStr">
+        <is>
+          <t>施策の書きぶりに影響。</t>
+        </is>
+      </c>
+      <c r="E96" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-71,Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F96" s="23" t="inlineStr">
+        <is>
+          <t>doc01-12</t>
+        </is>
+      </c>
+      <c r="G96" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H96" s="25" t="inlineStr"/>
+    </row>
+    <row r="97" ht="34" customHeight="1">
+      <c r="A97" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B97" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C97" s="25" t="inlineStr">
+        <is>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+        </is>
+      </c>
+      <c r="D97" s="25" t="inlineStr">
+        <is>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+        </is>
+      </c>
+      <c r="E97" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F97" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-13</t>
+        </is>
+      </c>
+      <c r="G97" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H97" s="25" t="inlineStr"/>
+    </row>
+    <row r="98" ht="34" customHeight="1">
+      <c r="A98" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B98" s="24" t="inlineStr">
+        <is>
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C92" s="25" t="inlineStr">
+      <c r="C98" s="25" t="inlineStr">
+        <is>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+        </is>
+      </c>
+      <c r="D98" s="25" t="inlineStr">
+        <is>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+        </is>
+      </c>
+      <c r="E98" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-31</t>
+        </is>
+      </c>
+      <c r="F98" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-6</t>
+        </is>
+      </c>
+      <c r="G98" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H98" s="25" t="inlineStr"/>
+    </row>
+    <row r="99" ht="34" customHeight="1">
+      <c r="A99" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B99" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C99" s="25" t="inlineStr">
+        <is>
+          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+        </is>
+      </c>
+      <c r="D99" s="25" t="inlineStr">
+        <is>
+          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+        </is>
+      </c>
+      <c r="E99" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-40,Ⅰ-42</t>
+        </is>
+      </c>
+      <c r="F99" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-7</t>
+        </is>
+      </c>
+      <c r="G99" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H99" s="25" t="inlineStr"/>
+    </row>
+    <row r="100" ht="34" customHeight="1">
+      <c r="A100" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B100" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C100" s="25" t="inlineStr">
         <is>
           <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
         </is>
       </c>
-      <c r="D92" s="25" t="inlineStr">
+      <c r="D100" s="25" t="inlineStr">
         <is>
           <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
         </is>
       </c>
-      <c r="E92" s="23" t="inlineStr">
+      <c r="E100" s="23" t="inlineStr">
         <is>
           <t>Ⅰ-09</t>
         </is>
       </c>
-      <c r="F92" s="23" t="inlineStr">
+      <c r="F100" s="23" t="inlineStr">
         <is>
           <t>doc23§1-3</t>
         </is>
       </c>
-      <c r="G92" s="23" t="inlineStr">
+      <c r="G100" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H92" s="25" t="inlineStr"/>
-    </row>
-    <row r="93" ht="34" customHeight="1">
-      <c r="A93" s="38" t="inlineStr">
+      <c r="H100" s="25" t="inlineStr"/>
+    </row>
+    <row r="101" ht="34" customHeight="1">
+      <c r="A101" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B93" s="24" t="inlineStr">
+      <c r="B101" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C93" s="25" t="inlineStr">
+      <c r="C101" s="25" t="inlineStr">
         <is>
           <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
         </is>
       </c>
-      <c r="D93" s="25" t="inlineStr">
+      <c r="D101" s="25" t="inlineStr">
         <is>
           <t>第9期はA4・本文104頁・全6章＋資料編。</t>
         </is>
       </c>
-      <c r="E93" s="23" t="inlineStr">
+      <c r="E101" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-89</t>
         </is>
       </c>
-      <c r="F93" s="23" t="inlineStr">
+      <c r="F101" s="23" t="inlineStr">
         <is>
           <t>doc01-10</t>
         </is>
       </c>
-      <c r="G93" s="23" t="inlineStr">
+      <c r="G101" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H93" s="25" t="inlineStr"/>
-    </row>
-    <row r="94" ht="34" customHeight="1">
-      <c r="A94" s="38" t="inlineStr">
+      <c r="H101" s="25" t="inlineStr"/>
+    </row>
+    <row r="102" ht="34" customHeight="1">
+      <c r="A102" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B94" s="24" t="inlineStr">
+      <c r="B102" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C94" s="25" t="inlineStr">
+      <c r="C102" s="25" t="inlineStr">
         <is>
           <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
         </is>
       </c>
-      <c r="D94" s="25" t="inlineStr">
+      <c r="D102" s="25" t="inlineStr">
         <is>
           <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
         </is>
       </c>
-      <c r="E94" s="23" t="inlineStr">
+      <c r="E102" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-92</t>
         </is>
       </c>
-      <c r="F94" s="23" t="inlineStr">
+      <c r="F102" s="23" t="inlineStr">
         <is>
           <t>doc01-10,doc08</t>
         </is>
       </c>
-      <c r="G94" s="23" t="inlineStr">
+      <c r="G102" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H94" s="25" t="inlineStr"/>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="39" t="inlineStr">
+      <c r="H102" s="25" t="inlineStr"/>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="39" t="inlineStr">
         <is>
           <t>■ 解決済み（記録）</t>
         </is>
       </c>
-    </row>
-    <row r="97" ht="34" customHeight="1">
-      <c r="A97" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B97" s="41" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C97" s="42" t="inlineStr">
-        <is>
-          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
-        </is>
-      </c>
-      <c r="D97" s="42" t="inlineStr">
-        <is>
-          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
-        </is>
-      </c>
-      <c r="E97" s="40" t="inlineStr">
-        <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
-        </is>
-      </c>
-      <c r="F97" s="40" t="inlineStr">
-        <is>
-          <t>doc22 §1</t>
-        </is>
-      </c>
-      <c r="G97" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H97" s="42" t="inlineStr"/>
-    </row>
-    <row r="98" ht="34" customHeight="1">
-      <c r="A98" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B98" s="41" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C98" s="42" t="inlineStr">
-        <is>
-          <t>在宅介護実態調査 約150人の抽出基準</t>
-        </is>
-      </c>
-      <c r="D98" s="42" t="inlineStr">
-        <is>
-          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
-        </is>
-      </c>
-      <c r="E98" s="40" t="inlineStr">
-        <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
-        </is>
-      </c>
-      <c r="F98" s="40" t="inlineStr">
-        <is>
-          <t>doc22 §1</t>
-        </is>
-      </c>
-      <c r="G98" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H98" s="42" t="inlineStr"/>
-    </row>
-    <row r="99" ht="34" customHeight="1">
-      <c r="A99" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B99" s="41" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C99" s="42" t="inlineStr">
-        <is>
-          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
-        </is>
-      </c>
-      <c r="D99" s="42" t="inlineStr">
-        <is>
-          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
-        </is>
-      </c>
-      <c r="E99" s="40" t="inlineStr">
-        <is>
-          <t>Ⅰ-25,Ⅰ-26</t>
-        </is>
-      </c>
-      <c r="F99" s="40" t="inlineStr">
-        <is>
-          <t>doc22 §1</t>
-        </is>
-      </c>
-      <c r="G99" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H99" s="42" t="inlineStr"/>
-    </row>
-    <row r="100" ht="34" customHeight="1">
-      <c r="A100" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B100" s="41" t="inlineStr">
-        <is>
-          <t>計画構成</t>
-        </is>
-      </c>
-      <c r="C100" s="42" t="inlineStr">
-        <is>
-          <t>整合を図る関連計画の範囲</t>
-        </is>
-      </c>
-      <c r="D100" s="42" t="inlineStr">
-        <is>
-          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
-        </is>
-      </c>
-      <c r="E100" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-72</t>
-        </is>
-      </c>
-      <c r="F100" s="40" t="inlineStr">
-        <is>
-          <t>doc22 §1</t>
-        </is>
-      </c>
-      <c r="G100" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H100" s="42" t="inlineStr"/>
-    </row>
-    <row r="101" ht="34" customHeight="1">
-      <c r="A101" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B101" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C101" s="42" t="inlineStr">
-        <is>
-          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
-        </is>
-      </c>
-      <c r="D101" s="42" t="inlineStr">
-        <is>
-          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
-        </is>
-      </c>
-      <c r="E101" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F101" s="40" t="inlineStr">
-        <is>
-          <t>doc20§3,§4</t>
-        </is>
-      </c>
-      <c r="G101" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H101" s="42" t="inlineStr"/>
-    </row>
-    <row r="102" ht="34" customHeight="1">
-      <c r="A102" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B102" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C102" s="42" t="inlineStr">
-        <is>
-          <t>交付要綱の配点表（満点）</t>
-        </is>
-      </c>
-      <c r="D102" s="42" t="inlineStr">
-        <is>
-          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
-        </is>
-      </c>
-      <c r="E102" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F102" s="40" t="inlineStr">
-        <is>
-          <t>doc20§2</t>
-        </is>
-      </c>
-      <c r="G102" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H102" s="42" t="inlineStr"/>
-    </row>
-    <row r="103" ht="34" customHeight="1">
-      <c r="A103" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B103" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C103" s="42" t="inlineStr">
-        <is>
-          <t>令和6年度・令和7年度の交付金評価結果</t>
-        </is>
-      </c>
-      <c r="D103" s="42" t="inlineStr">
-        <is>
-          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
-        </is>
-      </c>
-      <c r="E103" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F103" s="40" t="inlineStr">
-        <is>
-          <t>doc20§3-1</t>
-        </is>
-      </c>
-      <c r="G103" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H103" s="42" t="inlineStr"/>
-    </row>
-    <row r="104" ht="34" customHeight="1">
-      <c r="A104" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B104" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C104" s="42" t="inlineStr">
-        <is>
-          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
-        </is>
-      </c>
-      <c r="D104" s="42" t="inlineStr">
-        <is>
-          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
-        </is>
-      </c>
-      <c r="E104" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-56,Ⅱ-58</t>
-        </is>
-      </c>
-      <c r="F104" s="40" t="inlineStr">
-        <is>
-          <t>doc09</t>
-        </is>
-      </c>
-      <c r="G104" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H104" s="42" t="inlineStr"/>
     </row>
     <row r="105" ht="34" customHeight="1">
       <c r="A105" s="40" t="inlineStr">
@@ -10900,27 +10930,27 @@
       </c>
       <c r="B105" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C105" s="42" t="inlineStr">
         <is>
-          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="D105" s="42" t="inlineStr">
         <is>
-          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
         </is>
       </c>
       <c r="E105" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F105" s="40" t="inlineStr">
         <is>
-          <t>doc02§20-2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G105" s="40" t="inlineStr">
@@ -10938,48 +10968,352 @@
       </c>
       <c r="B106" s="41" t="inlineStr">
         <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C106" s="42" t="inlineStr">
+        <is>
+          <t>在宅介護実態調査 約150人の抽出基準</t>
+        </is>
+      </c>
+      <c r="D106" s="42" t="inlineStr">
+        <is>
+          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
+        </is>
+      </c>
+      <c r="E106" s="40" t="inlineStr">
+        <is>
+          <t>Ⅰ-08,Ⅰ-24</t>
+        </is>
+      </c>
+      <c r="F106" s="40" t="inlineStr">
+        <is>
+          <t>doc22 §1</t>
+        </is>
+      </c>
+      <c r="G106" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H106" s="42" t="inlineStr"/>
+    </row>
+    <row r="107" ht="34" customHeight="1">
+      <c r="A107" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B107" s="41" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C107" s="42" t="inlineStr">
+        <is>
+          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
+        </is>
+      </c>
+      <c r="D107" s="42" t="inlineStr">
+        <is>
+          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
+        </is>
+      </c>
+      <c r="E107" s="40" t="inlineStr">
+        <is>
+          <t>Ⅰ-25,Ⅰ-26</t>
+        </is>
+      </c>
+      <c r="F107" s="40" t="inlineStr">
+        <is>
+          <t>doc22 §1</t>
+        </is>
+      </c>
+      <c r="G107" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H107" s="42" t="inlineStr"/>
+    </row>
+    <row r="108" ht="34" customHeight="1">
+      <c r="A108" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B108" s="41" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C108" s="42" t="inlineStr">
+        <is>
+          <t>整合を図る関連計画の範囲</t>
+        </is>
+      </c>
+      <c r="D108" s="42" t="inlineStr">
+        <is>
+          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+        </is>
+      </c>
+      <c r="E108" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F108" s="40" t="inlineStr">
+        <is>
+          <t>doc22 §1</t>
+        </is>
+      </c>
+      <c r="G108" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H108" s="42" t="inlineStr"/>
+    </row>
+    <row r="109" ht="34" customHeight="1">
+      <c r="A109" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B109" s="41" t="inlineStr">
+        <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="C106" s="42" t="inlineStr">
+      <c r="C109" s="42" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+        </is>
+      </c>
+      <c r="D109" s="42" t="inlineStr">
+        <is>
+          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+        </is>
+      </c>
+      <c r="E109" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F109" s="40" t="inlineStr">
+        <is>
+          <t>doc20§3,§4</t>
+        </is>
+      </c>
+      <c r="G109" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H109" s="42" t="inlineStr"/>
+    </row>
+    <row r="110" ht="34" customHeight="1">
+      <c r="A110" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B110" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C110" s="42" t="inlineStr">
+        <is>
+          <t>交付要綱の配点表（満点）</t>
+        </is>
+      </c>
+      <c r="D110" s="42" t="inlineStr">
+        <is>
+          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+        </is>
+      </c>
+      <c r="E110" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F110" s="40" t="inlineStr">
+        <is>
+          <t>doc20§2</t>
+        </is>
+      </c>
+      <c r="G110" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H110" s="42" t="inlineStr"/>
+    </row>
+    <row r="111" ht="34" customHeight="1">
+      <c r="A111" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B111" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C111" s="42" t="inlineStr">
+        <is>
+          <t>令和6年度・令和7年度の交付金評価結果</t>
+        </is>
+      </c>
+      <c r="D111" s="42" t="inlineStr">
+        <is>
+          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+        </is>
+      </c>
+      <c r="E111" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F111" s="40" t="inlineStr">
+        <is>
+          <t>doc20§3-1</t>
+        </is>
+      </c>
+      <c r="G111" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H111" s="42" t="inlineStr"/>
+    </row>
+    <row r="112" ht="34" customHeight="1">
+      <c r="A112" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B112" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C112" s="42" t="inlineStr">
+        <is>
+          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+        </is>
+      </c>
+      <c r="D112" s="42" t="inlineStr">
+        <is>
+          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+        </is>
+      </c>
+      <c r="E112" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-56,Ⅱ-58</t>
+        </is>
+      </c>
+      <c r="F112" s="40" t="inlineStr">
+        <is>
+          <t>doc09</t>
+        </is>
+      </c>
+      <c r="G112" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H112" s="42" t="inlineStr"/>
+    </row>
+    <row r="113" ht="34" customHeight="1">
+      <c r="A113" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B113" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C113" s="42" t="inlineStr">
+        <is>
+          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+        </is>
+      </c>
+      <c r="D113" s="42" t="inlineStr">
+        <is>
+          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+        </is>
+      </c>
+      <c r="E113" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-59</t>
+        </is>
+      </c>
+      <c r="F113" s="40" t="inlineStr">
+        <is>
+          <t>doc02§20-2</t>
+        </is>
+      </c>
+      <c r="G113" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H113" s="42" t="inlineStr"/>
+    </row>
+    <row r="114" ht="34" customHeight="1">
+      <c r="A114" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B114" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C114" s="42" t="inlineStr">
         <is>
           <t>国の指針・様式の更新有無</t>
         </is>
       </c>
-      <c r="D106" s="42" t="inlineStr">
+      <c r="D114" s="42" t="inlineStr">
         <is>
           <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
-      <c r="E106" s="40" t="inlineStr">
+      <c r="E114" s="40" t="inlineStr">
         <is>
           <t>Ⅰ-11</t>
         </is>
       </c>
-      <c r="F106" s="40" t="inlineStr">
+      <c r="F114" s="40" t="inlineStr">
         <is>
           <t>doc04,doc05</t>
         </is>
       </c>
-      <c r="G106" s="40" t="inlineStr">
+      <c r="G114" s="40" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H106" s="42" t="inlineStr"/>
+      <c r="H114" s="42" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H94"/>
+  <autoFilter ref="A4:H102"/>
   <mergeCells count="3">
-    <mergeCell ref="A96:H96"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A104:H104"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10993,7 +11327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11727,77 +12061,77 @@
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>調査票</t>
+          <t>成果物</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>調査票 第1稿（ニーズ調査・在宅介護実態調査）</t>
+          <t>集計仕様書（output/07_集計仕様書.xlsx）</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>0828版。令和7年8月版・手法Ⅲ標準様式と全面突合</t>
+          <t>6シート。ニーズ80設問・在宅26設問・派生変数20・クロス表20</t>
         </is>
       </c>
       <c r="D27" s="43" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>docs/…/23_調査票第1稿レビュー_ICF分析設計.md</t>
+          <t>docs/…/25_集計仕様書.md</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>受領済</t>
+          <t>作成済</t>
         </is>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>国資料</t>
+          <t>成果物</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>令和8年度 交付金評価指標（市町村分）配点表</t>
+          <t>第2回策定委員会 資料構成（doc26）</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>全17頁。推進400点・支援400点、目標Ⅰ〜Ⅳ各100点</t>
+          <t>資料1〜8・約53頁＋素案別冊。合意事項5点</t>
         </is>
       </c>
       <c r="D28" s="43" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>docs/…/20_交付金評価結果分析.md</t>
+          <t>docs/…/26_第2回策定委員会_資料構成.md</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>受領済</t>
+          <t>作成済</t>
         </is>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>国資料</t>
+          <t>調査票</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>令和6年度 該当状況調査票集計表（全国一覧表）</t>
+          <t>調査票 第1稿（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>全国1,741市町村。村は第398行。合計295点</t>
+          <t>0828版。令和7年8月版・手法Ⅲ標準様式と全面突合</t>
         </is>
       </c>
       <c r="D29" s="43" t="n">
@@ -11805,7 +12139,7 @@
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>docs/…/20_交付金評価結果分析.md</t>
+          <t>docs/…/23_調査票第1稿レビュー_ICF分析設計.md</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -11822,12 +12156,12 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>令和7年度 該当状況調査票集計表（全国集計・市町村）</t>
+          <t>令和8年度 交付金評価指標（市町村分）配点表</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>合計339点。全国平均435.0点</t>
+          <t>全17頁。推進400点・支援400点、目標Ⅰ〜Ⅳ各100点</t>
         </is>
       </c>
       <c r="D30" s="43" t="n">
@@ -11852,12 +12186,12 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>令和8年度 該当状況調査票集計表（全国集計・市町村）</t>
+          <t>令和6年度 該当状況調査票集計表（全国一覧表）</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>合計447点。全国平均455.1点／全国1,005位／県内34位</t>
+          <t>全国1,741市町村。村は第398行。合計295点</t>
         </is>
       </c>
       <c r="D31" s="43" t="n">
@@ -11877,17 +12211,17 @@
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>関連計画</t>
+          <t>国資料</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>第四次北塩原村生涯学習推進計画</t>
+          <t>令和7年度 該当状況調査票集計表（全国集計・市町村）</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>全112頁。2018〜2027年度。7z分割書庫4分割で受領</t>
+          <t>合計339点。全国平均435.0点</t>
         </is>
       </c>
       <c r="D32" s="43" t="n">
@@ -11895,49 +12229,109 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
+          <t>docs/…/20_交付金評価結果分析.md</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>国資料</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>令和8年度 該当状況調査票集計表（全国集計・市町村）</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>合計447点。全国平均455.1点／全国1,005位／県内34位</t>
+        </is>
+      </c>
+      <c r="D33" s="43" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>docs/…/20_交付金評価結果分析.md</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>関連計画</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>第四次北塩原村生涯学習推進計画</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>全112頁。2018〜2027年度。7z分割書庫4分割で受領</t>
+        </is>
+      </c>
+      <c r="D34" s="43" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
           <t>docs/…/21_関連計画_第四次生涯学習推進計画.md</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>受領済</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="35" t="inlineStr">
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="35" t="inlineStr">
         <is>
           <t>村データ</t>
         </is>
       </c>
-      <c r="B33" s="34" t="inlineStr">
+      <c r="B35" s="34" t="inlineStr">
         <is>
           <t>★要介護認定データ（調査票との関連付け用）</t>
         </is>
       </c>
-      <c r="C33" s="34" t="inlineStr">
+      <c r="C35" s="34" t="inlineStr">
         <is>
           <t>仕様書4Ⅰ(5)。調査回収後に必要</t>
         </is>
       </c>
-      <c r="D33" s="35" t="inlineStr">
+      <c r="D35" s="35" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E33" s="34" t="inlineStr">
+      <c r="E35" s="34" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F33" s="35" t="inlineStr">
+      <c r="F35" s="35" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F33"/>
+  <autoFilter ref="A4:F35"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$104</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$102</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4647,11 +4647,11 @@
       <c r="J65" s="14" t="n"/>
       <c r="K65" s="14" t="n"/>
       <c r="L65" s="14" t="n">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="M65" s="14" t="n"/>
       <c r="N65" s="15" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="O65" s="16" t="inlineStr">
         <is>
@@ -4845,11 +4845,11 @@
       <c r="J68" s="14" t="n"/>
       <c r="K68" s="14" t="n"/>
       <c r="L68" s="14" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="M68" s="14" t="n"/>
       <c r="N68" s="15" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="O68" s="16" t="inlineStr">
         <is>
@@ -4911,11 +4911,11 @@
       <c r="J69" s="14" t="n"/>
       <c r="K69" s="14" t="n"/>
       <c r="L69" s="14" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="M69" s="14" t="n"/>
       <c r="N69" s="15" t="n">
-        <v>0.55</v>
+        <v>0.7</v>
       </c>
       <c r="O69" s="16" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
       </c>
       <c r="P69" s="13" t="inlineStr">
         <is>
-          <t>★交付金の配点表・全国集計3か年の受領により、満点・全国平均・県平均・全国順位が判明（doc20）。目標値設定の前提が整った。取りこぼし32項目・配点122点を特定。国ワークシートに依存しない指標から先に確定できる。指標案8件は doc07§7。</t>
+          <t>★交付金の配点表・全国集計3か年の受領により、満点・全国平均・県平均・全国順位が判明（doc20）。★9/3：資料7として成果目標6指標・活動指標13指標を設定し、うち11指標の現状値を確定（通いの場23か所281人・参加率12.2%、多様なサービス事業費割合0.0%、サポーター約237人、ステップアップ講座0人、縦覧点検4帳票、給付費通知300件/年、地域ケア会議年6回、SC参加割合50.0%、認定率21.1%、要支援1が51人 ほか）。目標値は調査結果の確定後に設定。交付金の得点は数値目標に置かず進捗管理の仕組みを書く方針。</t>
         </is>
       </c>
     </row>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="M87" s="14" t="n"/>
       <c r="N87" s="15" t="n">
-        <v>0.25</v>
+        <v>0.55</v>
       </c>
       <c r="O87" s="16" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="P87" s="13" t="inlineStr">
         <is>
-          <t>★doc26で資料構成を確定（資料1〜8・約53頁＋素案別冊）。合意を得たい事項5点（基本理念・基本目標／施策体系／サービス見込み量の考え方／保険料の方向性／成果目標・活動指標）を先頭に置く構成。資料2（第9期の評価）と資料5〜7の骨格は調査結果を待たずに10月中に作成可能。</t>
+          <t>★doc26で資料構成を確定（資料1〜8・約53頁＋素案別冊）。合意を得たい事項5点を先頭に置く構成。★9/3：output/08_第2回策定委員会資料.docx として資料2（本体完成）・資料5（骨格）・資料6（骨格）・資料7（本体完成）を作成（26表・A4約30頁）。残るは資料3（調査結果速報）と資料4（施策体系）で、いずれも調査結果の確定後。LibreOfficeが動作しないためレイアウトの目視確認は未実施。</t>
         </is>
       </c>
     </row>
@@ -11327,7 +11327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12066,12 +12066,12 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>集計仕様書（output/07_集計仕様書.xlsx）</t>
+          <t>第2回策定委員会 資料2・5・6・7（output/08_第2回策定委員会資料.docx）</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>6シート。ニーズ80設問・在宅26設問・派生変数20・クロス表20</t>
+          <t>26表・A4約30頁。資料2と7は本体完成、資料5と6は骨格</t>
         </is>
       </c>
       <c r="D27" s="43" t="n">
@@ -12079,7 +12079,7 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>docs/…/25_集計仕様書.md</t>
+          <t>docs/…/26_第2回策定委員会_資料構成.md §11</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -12096,12 +12096,12 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>第2回策定委員会 資料構成（doc26）</t>
+          <t>集計仕様書（output/07_集計仕様書.xlsx）</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>資料1〜8・約53頁＋素案別冊。合意事項5点</t>
+          <t>6シート。ニーズ80設問・在宅26設問・派生変数20・クロス表20</t>
         </is>
       </c>
       <c r="D28" s="43" t="n">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>docs/…/26_第2回策定委員会_資料構成.md</t>
+          <t>docs/…/25_集計仕様書.md</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -12121,47 +12121,47 @@
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>調査票</t>
+          <t>成果物</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>調査票 第1稿（ニーズ調査・在宅介護実態調査）</t>
+          <t>第2回策定委員会 資料構成（doc26）</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>0828版。令和7年8月版・手法Ⅲ標準様式と全面突合</t>
+          <t>資料1〜8・約53頁＋素案別冊。合意事項5点</t>
         </is>
       </c>
       <c r="D29" s="43" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>docs/…/23_調査票第1稿レビュー_ICF分析設計.md</t>
+          <t>docs/…/26_第2回策定委員会_資料構成.md</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>受領済</t>
+          <t>作成済</t>
         </is>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>国資料</t>
+          <t>調査票</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>令和8年度 交付金評価指標（市町村分）配点表</t>
+          <t>調査票 第1稿（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>全17頁。推進400点・支援400点、目標Ⅰ〜Ⅳ各100点</t>
+          <t>0828版。令和7年8月版・手法Ⅲ標準様式と全面突合</t>
         </is>
       </c>
       <c r="D30" s="43" t="n">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>docs/…/20_交付金評価結果分析.md</t>
+          <t>docs/…/23_調査票第1稿レビュー_ICF分析設計.md</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -12186,12 +12186,12 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>令和6年度 該当状況調査票集計表（全国一覧表）</t>
+          <t>令和8年度 交付金評価指標（市町村分）配点表</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>全国1,741市町村。村は第398行。合計295点</t>
+          <t>全17頁。推進400点・支援400点、目標Ⅰ〜Ⅳ各100点</t>
         </is>
       </c>
       <c r="D31" s="43" t="n">
@@ -12216,12 +12216,12 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>令和7年度 該当状況調査票集計表（全国集計・市町村）</t>
+          <t>令和6年度 該当状況調査票集計表（全国一覧表）</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>合計339点。全国平均435.0点</t>
+          <t>全国1,741市町村。村は第398行。合計295点</t>
         </is>
       </c>
       <c r="D32" s="43" t="n">
@@ -12246,12 +12246,12 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>令和8年度 該当状況調査票集計表（全国集計・市町村）</t>
+          <t>令和7年度 該当状況調査票集計表（全国集計・市町村）</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>合計447点。全国平均455.1点／全国1,005位／県内34位</t>
+          <t>合計339点。全国平均435.0点</t>
         </is>
       </c>
       <c r="D33" s="43" t="n">
@@ -12271,17 +12271,17 @@
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>関連計画</t>
+          <t>国資料</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>第四次北塩原村生涯学習推進計画</t>
+          <t>令和8年度 該当状況調査票集計表（全国集計・市町村）</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>全112頁。2018〜2027年度。7z分割書庫4分割で受領</t>
+          <t>合計447点。全国平均455.1点／全国1,005位／県内34位</t>
         </is>
       </c>
       <c r="D34" s="43" t="n">
@@ -12289,49 +12289,79 @@
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
+          <t>docs/…/20_交付金評価結果分析.md</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>関連計画</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>第四次北塩原村生涯学習推進計画</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>全112頁。2018〜2027年度。7z分割書庫4分割で受領</t>
+        </is>
+      </c>
+      <c r="D35" s="43" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
           <t>docs/…/21_関連計画_第四次生涯学習推進計画.md</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>受領済</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="35" t="inlineStr">
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="35" t="inlineStr">
         <is>
           <t>村データ</t>
         </is>
       </c>
-      <c r="B35" s="34" t="inlineStr">
+      <c r="B36" s="34" t="inlineStr">
         <is>
           <t>★要介護認定データ（調査票との関連付け用）</t>
         </is>
       </c>
-      <c r="C35" s="34" t="inlineStr">
+      <c r="C36" s="34" t="inlineStr">
         <is>
           <t>仕様書4Ⅰ(5)。調査回収後に必要</t>
         </is>
       </c>
-      <c r="D35" s="35" t="inlineStr">
+      <c r="D36" s="35" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E35" s="34" t="inlineStr">
+      <c r="E36" s="34" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F35" s="35" t="inlineStr">
+      <c r="F36" s="35" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F35"/>
+  <autoFilter ref="A4:F36"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -5287,11 +5287,11 @@
       <c r="J75" s="14" t="n"/>
       <c r="K75" s="14" t="n"/>
       <c r="L75" s="14" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="M75" s="14" t="n"/>
       <c r="N75" s="15" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="O75" s="16" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="P75" s="13" t="inlineStr">
         <is>
-          <t>doc14・doc18で施策体系（基本目標5本・施策28本）を確定。施策3-5「介護給付の適正化」を交付金配点表に基づき全面改訂（主要3事業への再編・縦覧点検4帳票満点の事実を反映）。基本目標5の独立可否は村と要協議。</t>
+          <t>doc14・doc18で施策体系（基本目標5本・施策28本）を確定。施策3-5「介護給付の適正化」を交付金配点表に基づき全面改訂（主要3事業への再編・縦覧点検4帳票満点の事実を反映）。基本目標5の独立可否は村と要協議。★9/4：資料4として委員会に諮る形に整理（基本目標5本・施策28本、区分別内訳は継続10／継続強化1／強化6／改称1／新規10）。新設10施策の根拠を1件ずつ明示。</t>
         </is>
       </c>
     </row>
@@ -6035,11 +6035,11 @@
       <c r="J87" s="14" t="n"/>
       <c r="K87" s="14" t="n"/>
       <c r="L87" s="14" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="M87" s="14" t="n"/>
       <c r="N87" s="15" t="n">
-        <v>0.55</v>
+        <v>0.7</v>
       </c>
       <c r="O87" s="16" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="P87" s="13" t="inlineStr">
         <is>
-          <t>★doc26で資料構成を確定（資料1〜8・約53頁＋素案別冊）。合意を得たい事項5点を先頭に置く構成。★9/3：output/08_第2回策定委員会資料.docx として資料2（本体完成）・資料5（骨格）・資料6（骨格）・資料7（本体完成）を作成（26表・A4約30頁）。残るは資料3（調査結果速報）と資料4（施策体系）で、いずれも調査結果の確定後。LibreOfficeが動作しないためレイアウトの目視確認は未実施。</t>
+          <t>★doc26で資料構成を確定（資料1〜8・約53頁＋素案別冊）。合意を得たい事項5点を先頭に置く構成。★9/3：output/08_第2回策定委員会資料.docx として資料2（本体完成）・資料5（骨格）・資料6（骨格）・資料7（本体完成）を作成。★9/4：資料4（第10期の基本理念・基本目標・施策体系）を追加し本体完成（全体で39表・A4約40頁）。基本理念は2案併記、基本目標5本、施策28本（新規10）。残るは資料3（調査結果速報）のみで、調査結果の確定後に作成。資料4に差し込む住民ニーズの数値も資料3から供給する。LibreOfficeが動作しないためレイアウトの目視確認は未実施。</t>
         </is>
       </c>
     </row>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$102</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1405,11 +1405,11 @@
       <c r="J13" s="14" t="n"/>
       <c r="K13" s="14" t="n"/>
       <c r="L13" s="14" t="n">
-        <v>46259</v>
+        <v>46269</v>
       </c>
       <c r="M13" s="14" t="n"/>
       <c r="N13" s="15" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="P13" s="13" t="inlineStr">
         <is>
-          <t>★第1稿（0828版）を受領し令和7年8月版との全面突合を完了（doc23）。要修正：選択肢の順序が標準と逆になっている7か所（うち2か所は文字列の誤植）、標準様式の残骸3か所、問7の番号繰り上がり。村独自14問の採否を判定し、削除提案は問3(10)の1問のみ。</t>
+          <t>★第1稿（0828版）を受領し令和7年8月版との全面突合を完了（doc23）。要修正：選択肢の順序が標準と逆になっている7か所（うち2か所は文字列の誤植）、標準様式の残骸3か所、問7の番号繰り上がり。村独自14問の採否を判定し、削除提案は問3(10)の1問のみ。★9/4：第2稿（0904版）を確認。指摘13件のうち11件が反映。ルビを57→105か所に拡充、通いの場の名称を現行事業名に修正、自由記述欄を新設。未対応は問1(2)①の選択肢順序と問7(7)の採用可否の2件。新たに保険外サービスの選択肢の不統一と個人情報の説明文の後退を検出（doc27）。</t>
         </is>
       </c>
     </row>
@@ -1471,11 +1471,11 @@
       <c r="J14" s="14" t="n"/>
       <c r="K14" s="14" t="n"/>
       <c r="L14" s="14" t="n">
-        <v>46259</v>
+        <v>46269</v>
       </c>
       <c r="M14" s="14" t="n"/>
       <c r="N14" s="15" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="O14" s="16" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="P14" s="13" t="inlineStr">
         <is>
-          <t>★第1稿を受領し手法Ⅲ標準様式との突合を完了（doc23）。要修正：標準の問13「訪問診療」が削除され問13が欠番、前回指摘2件（介護療養型医療施設の削除・傷病の選択肢13/14の入替）が未反映、基準月が空欄。村独自の問0・問6-1は番号体系を壊さない適切な設計。</t>
+          <t>★第1稿を受領し手法Ⅲ標準様式との突合を完了（doc23）。要修正：標準の問13「訪問診療」が削除され問13が欠番、前回指摘2件（介護療養型医療施設の削除・傷病の選択肢13/14の入替）が未反映、基準月が空欄。村独自の問0・問6-1は番号体系を壊さない適切な設計。★9/4：第2稿で介護療養型医療施設の削除・傷病の選択肢13/14・基準月（問8）・訪問診療の復活がすべて反映。ただし訪問診療の番号が問12となり問12が重複・問13が欠番、問9の基準月が未修正、B票の案内文1行が削除された（doc27§3・§5-3）。</t>
         </is>
       </c>
     </row>
@@ -1797,11 +1797,11 @@
       <c r="J19" s="14" t="n"/>
       <c r="K19" s="14" t="n"/>
       <c r="L19" s="14" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="M19" s="14" t="n"/>
       <c r="N19" s="15" t="n">
-        <v>0.45</v>
+        <v>0.65</v>
       </c>
       <c r="O19" s="16" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P19" s="13" t="inlineStr">
         <is>
-          <t>★議事録により9/3に第1稿提出、9/9頃に最終校了と確定。未決事項（手法・オプション項目・独自設問・依頼状名義・部数）は選択肢併記で提出する。</t>
+          <t>★議事録により9/3に第1稿提出、9/9頃に最終校了と確定。未決事項（手法・オプション項目・独自設問・依頼状名義・部数）は選択肢併記で提出する。★9/4：第2稿を受領しレビュー完了（doc27）。校了までの修正リスト11件を優先度付きで整理。必須3件（在宅の問13の番号・問9の基準月・ニーズ問1(2)①の選択肢順序）。</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H114"/>
+  <dimension ref="A1:H123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7812,12 +7812,12 @@
       </c>
       <c r="C21" s="34" t="inlineStr">
         <is>
-          <t>★ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
+          <t>★ニーズ調査 問7(7)「この1か月間に会った友人・知人の人数」の採用可否</t>
         </is>
       </c>
       <c r="D21" s="34" t="inlineStr">
         <is>
-          <t>★「その他」と「そのような人はいない／不明」の前後が一貫して逆。うち問7(5)「そのような人はいないその他」・問7(7)「いないその他」は文字列が結合した誤植。見える化の登録時に選択肢コードがずれる。手引きは選択肢の改変を明確に禁じている。</t>
+          <t>★第1稿では不採用のうえ以降の番号を繰り上げているため、見える化への入力時に設問の対応が崩れる。採用すれば番号ずれが解消し、かつICF分析の「参加」の量的指標としてそのまま使える。</t>
         </is>
       </c>
       <c r="E21" s="35" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="F21" s="35" t="inlineStr">
         <is>
-          <t>doc23§1-1</t>
+          <t>doc23§1-2</t>
         </is>
       </c>
       <c r="G21" s="35" t="inlineStr">
@@ -7850,22 +7850,22 @@
       </c>
       <c r="C22" s="34" t="inlineStr">
         <is>
-          <t>★在宅介護実態調査 標準の問13「訪問診療を利用していますか」の復活</t>
+          <t>★ニーズ調査 村独自設問14問の採否と頁数（問3(10)の削除・問7(9)の簡素化）</t>
         </is>
       </c>
       <c r="D22" s="34" t="inlineStr">
         <is>
-          <t>★第1稿で削除され問13が欠番。オプション項目のため不採用は可だが、在宅医療は第10期の重点論点であり、交付金の支援目標Ⅲ（在宅医療・介護連携）が0点である本村で唯一の把握手段。番号が飛ぶと回答者も混乱する。</t>
+          <t>★標準約66問＋村独自14問＝約79問。仕様書の目安A4約12頁を超える見込み。削除を提案するのは問3(10)「1日に何回食事をとりますか」の1問のみ（低栄養は問3(1)(7)(8)で把握可能）。他13問は施策・交付金の指標と結びついており残すべき。</t>
         </is>
       </c>
       <c r="E22" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-12,Ⅰ-13</t>
         </is>
       </c>
       <c r="F22" s="35" t="inlineStr">
         <is>
-          <t>doc23§2-1</t>
+          <t>doc23§4</t>
         </is>
       </c>
       <c r="G22" s="35" t="inlineStr">
@@ -7888,22 +7888,22 @@
       </c>
       <c r="C23" s="34" t="inlineStr">
         <is>
-          <t>★在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
+          <t>★現職の村長名・所管課・役場の住所の確認</t>
         </is>
       </c>
       <c r="D23" s="34" t="inlineStr">
         <is>
-          <t>★資料C'で指摘済みだが第1稿に未反映。介護療養型医療施設は令和6年3月末で廃止。傷病は標準が「13．眼科・耳鼻科疾患／14．その他」。</t>
+          <t>★第1稿の依頼状に「北塩原村長 遠藤 和夫」「保健福祉課 福祉係」「大字北山字姥ヶ作3151番地」と記載。当方では現職の村長名を確認できない。所管課は住民課との別が未確認のまま（doc01 確認事項1）。</t>
         </is>
       </c>
       <c r="E23" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-14</t>
         </is>
       </c>
       <c r="F23" s="35" t="inlineStr">
         <is>
-          <t>doc23§2-2</t>
+          <t>doc23§5</t>
         </is>
       </c>
       <c r="G23" s="35" t="inlineStr">
@@ -7926,22 +7926,22 @@
       </c>
       <c r="C24" s="34" t="inlineStr">
         <is>
-          <t>★ニーズ調査 問7(7)「この1か月間に会った友人・知人の人数」の採用可否</t>
+          <t>★【必須】在宅A票 訪問診療の設問を問13に直す（問12が重複し問13が欠番）</t>
         </is>
       </c>
       <c r="D24" s="34" t="inlineStr">
         <is>
-          <t>★第1稿では不採用のうえ以降の番号を繰り上げているため、見える化への入力時に設問の対応が崩れる。採用すれば番号ずれが解消し、かつICF分析の「参加」の量的指標としてそのまま使える。</t>
+          <t>★第2稿で訪問診療が復活したが番号が問12となり、今後必要と感じる支援（問12）と重複している。回答者が混乱し集計時に設問を特定できない。9/9の校了までに必ず修正。</t>
         </is>
       </c>
       <c r="E24" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F24" s="35" t="inlineStr">
         <is>
-          <t>doc23§1-2</t>
+          <t>doc27§3-1</t>
         </is>
       </c>
       <c r="G24" s="35" t="inlineStr">
@@ -7964,22 +7964,22 @@
       </c>
       <c r="C25" s="34" t="inlineStr">
         <is>
-          <t>★ニーズ調査 村独自設問14問の採否と頁数（問3(10)の削除・問7(9)の簡素化）</t>
+          <t>★【必須】在宅A票 問9の基準月を「令和8年8月」に修正</t>
         </is>
       </c>
       <c r="D25" s="34" t="inlineStr">
         <is>
-          <t>★標準約66問＋村独自14問＝約79問。仕様書の目安A4約12頁を超える見込み。削除を提案するのは問3(10)「1日に何回食事をとりますか」の1問のみ（低栄養は問3(1)(7)(8)で把握可能）。他13問は施策・交付金の指標と結びついており残すべき。</t>
+          <t>★問8は修正されたが問9が「令和●年●月」のまま。</t>
         </is>
       </c>
       <c r="E25" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-12,Ⅰ-13</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F25" s="35" t="inlineStr">
         <is>
-          <t>doc23§4</t>
+          <t>doc27§3-2</t>
         </is>
       </c>
       <c r="G25" s="35" t="inlineStr">
@@ -8002,22 +8002,22 @@
       </c>
       <c r="C26" s="34" t="inlineStr">
         <is>
-          <t>★現職の村長名・所管課・役場の住所の確認</t>
+          <t>★【必須】ニーズ 問1(2)① 選択肢14・15を「14．その他／15．不明」に修正</t>
         </is>
       </c>
       <c r="D26" s="34" t="inlineStr">
         <is>
-          <t>★第1稿の依頼状に「北塩原村長 遠藤 和夫」「保健福祉課 福祉係」「大字北山字姥ヶ作3151番地」と記載。当方では現職の村長名を確認できない。所管課は住民課との別が未確認のまま（doc01 確認事項1）。</t>
+          <t>★選択肢の順序の修正7か所のうち、この1か所のみ修正漏れ。標準は13．高齢による衰弱／14．その他（　）／15．不明。</t>
         </is>
       </c>
       <c r="E26" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F26" s="35" t="inlineStr">
         <is>
-          <t>doc23§5</t>
+          <t>doc27§2-1</t>
         </is>
       </c>
       <c r="G26" s="35" t="inlineStr">
@@ -9054,156 +9054,156 @@
       <c r="H53" s="34" t="inlineStr"/>
     </row>
     <row r="54" ht="34" customHeight="1">
-      <c r="A54" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B54" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C54" s="25" t="inlineStr">
-        <is>
-          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
-        </is>
-      </c>
-      <c r="D54" s="25" t="inlineStr">
-        <is>
-          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
-        </is>
-      </c>
-      <c r="E54" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F54" s="23" t="inlineStr">
-        <is>
-          <t>doc02§22,doc08§8</t>
-        </is>
-      </c>
-      <c r="G54" s="23" t="inlineStr">
+      <c r="A54" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B54" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C54" s="34" t="inlineStr">
+        <is>
+          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
+        </is>
+      </c>
+      <c r="D54" s="34" t="inlineStr">
+        <is>
+          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
+        </is>
+      </c>
+      <c r="E54" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-09,Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F54" s="35" t="inlineStr">
+        <is>
+          <t>doc27§3-3</t>
+        </is>
+      </c>
+      <c r="G54" s="35" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H54" s="25" t="inlineStr"/>
+      <c r="H54" s="34" t="inlineStr"/>
     </row>
     <row r="55" ht="34" customHeight="1">
-      <c r="A55" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B55" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C55" s="25" t="inlineStr">
-        <is>
-          <t>令和6年度決算および令和7年度の給付費見込</t>
-        </is>
-      </c>
-      <c r="D55" s="25" t="inlineStr">
-        <is>
-          <t>第9期の計画値と実績の乖離を確定させるために必要。</t>
-        </is>
-      </c>
-      <c r="E55" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
-        </is>
-      </c>
-      <c r="F55" s="23" t="inlineStr">
-        <is>
-          <t>doc08§8-1</t>
-        </is>
-      </c>
-      <c r="G55" s="23" t="inlineStr">
+      <c r="A55" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B55" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C55" s="34" t="inlineStr">
+        <is>
+          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
+        </is>
+      </c>
+      <c r="D55" s="34" t="inlineStr">
+        <is>
+          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
+        </is>
+      </c>
+      <c r="E55" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-09,Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F55" s="35" t="inlineStr">
+        <is>
+          <t>doc27§5-2</t>
+        </is>
+      </c>
+      <c r="G55" s="35" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H55" s="25" t="inlineStr"/>
+      <c r="H55" s="34" t="inlineStr"/>
     </row>
     <row r="56" ht="34" customHeight="1">
-      <c r="A56" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B56" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C56" s="25" t="inlineStr">
-        <is>
-          <t>通いの場の実数（令和3〜7年度）</t>
-        </is>
-      </c>
-      <c r="D56" s="25" t="inlineStr">
-        <is>
-          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。</t>
-        </is>
-      </c>
-      <c r="E56" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F56" s="23" t="inlineStr">
-        <is>
-          <t>doc02§16,§22</t>
-        </is>
-      </c>
-      <c r="G56" s="23" t="inlineStr">
+      <c r="A56" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B56" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C56" s="34" t="inlineStr">
+        <is>
+          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+        </is>
+      </c>
+      <c r="D56" s="34" t="inlineStr">
+        <is>
+          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+        </is>
+      </c>
+      <c r="E56" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F56" s="35" t="inlineStr">
+        <is>
+          <t>doc27§5-3</t>
+        </is>
+      </c>
+      <c r="G56" s="35" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H56" s="25" t="inlineStr"/>
+      <c r="H56" s="34" t="inlineStr"/>
     </row>
     <row r="57" ht="34" customHeight="1">
-      <c r="A57" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B57" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C57" s="25" t="inlineStr">
-        <is>
-          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
-        </is>
-      </c>
-      <c r="D57" s="25" t="inlineStr">
-        <is>
-          <t>見える化に該当データがない。第9期は基本目標4-4に位置づけ。</t>
-        </is>
-      </c>
-      <c r="E57" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-68,Ⅱ-69</t>
-        </is>
-      </c>
-      <c r="F57" s="23" t="inlineStr">
-        <is>
-          <t>doc08§8-5</t>
-        </is>
-      </c>
-      <c r="G57" s="23" t="inlineStr">
+      <c r="A57" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B57" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C57" s="34" t="inlineStr">
+        <is>
+          <t>調査票のレイアウトの目視確認3点（幸福度の記入欄／宛名ラベル枠／頁数）</t>
+        </is>
+      </c>
+      <c r="D57" s="34" t="inlineStr">
+        <is>
+          <t>★当方の環境ではdocxからPDFへの変換ができずレイアウトを確認できない。ニーズ問8(2)の記入枠、表紙から削除された宛名ラベル枠と「第10期」表記、ルビ追加による頁数の増加を村側でご確認いただきたい。</t>
+        </is>
+      </c>
+      <c r="E57" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-20</t>
+        </is>
+      </c>
+      <c r="F57" s="35" t="inlineStr">
+        <is>
+          <t>doc27§6</t>
+        </is>
+      </c>
+      <c r="G57" s="35" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H57" s="25" t="inlineStr"/>
+      <c r="H57" s="34" t="inlineStr"/>
     </row>
     <row r="58" ht="34" customHeight="1">
       <c r="A58" s="37" t="inlineStr">
@@ -9218,22 +9218,22 @@
       </c>
       <c r="C58" s="25" t="inlineStr">
         <is>
-          <t>高齢者福祉事業（村単独事業）の実績資料</t>
+          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
         </is>
       </c>
       <c r="D58" s="25" t="inlineStr">
         <is>
-          <t>現行計画の評価に必要。</t>
+          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
         </is>
       </c>
       <c r="E58" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F58" s="23" t="inlineStr">
         <is>
-          <t>doc01-11</t>
+          <t>doc02§22,doc08§8</t>
         </is>
       </c>
       <c r="G58" s="23" t="inlineStr">
@@ -9256,22 +9256,22 @@
       </c>
       <c r="C59" s="25" t="inlineStr">
         <is>
-          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
+          <t>令和6年度決算および令和7年度の給付費見込</t>
         </is>
       </c>
       <c r="D59" s="25" t="inlineStr">
         <is>
-          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
+          <t>第9期の計画値と実績の乖離を確定させるために必要。</t>
         </is>
       </c>
       <c r="E59" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-58,Ⅱ-59</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-9</t>
+          <t>doc08§8-1</t>
         </is>
       </c>
       <c r="G59" s="23" t="inlineStr">
@@ -9294,22 +9294,22 @@
       </c>
       <c r="C60" s="25" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告（月報・年報）の原データの提供可否</t>
+          <t>通いの場の実数（令和3〜7年度）</t>
         </is>
       </c>
       <c r="D60" s="25" t="inlineStr">
         <is>
-          <t>見える化に収録されていない項目（サービス種類別利用者数の月次推移等）が扱えるようになる。</t>
+          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。</t>
         </is>
       </c>
       <c r="E60" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F60" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-10</t>
+          <t>doc02§16,§22</t>
         </is>
       </c>
       <c r="G60" s="23" t="inlineStr">
@@ -9332,22 +9332,22 @@
       </c>
       <c r="C61" s="25" t="inlineStr">
         <is>
-          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
+          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
         </is>
       </c>
       <c r="D61" s="25" t="inlineStr">
         <is>
-          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
+          <t>見える化に該当データがない。第9期は基本目標4-4に位置づけ。</t>
         </is>
       </c>
       <c r="E61" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-68,Ⅱ-69</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc08§8-5</t>
         </is>
       </c>
       <c r="G61" s="23" t="inlineStr">
@@ -9370,12 +9370,12 @@
       </c>
       <c r="C62" s="25" t="inlineStr">
         <is>
-          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
+          <t>高齢者福祉事業（村単独事業）の実績資料</t>
         </is>
       </c>
       <c r="D62" s="25" t="inlineStr">
         <is>
-          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
+          <t>現行計画の評価に必要。</t>
         </is>
       </c>
       <c r="E62" s="23" t="inlineStr">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="F62" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc01-11</t>
         </is>
       </c>
       <c r="G62" s="23" t="inlineStr">
@@ -9408,22 +9408,22 @@
       </c>
       <c r="C63" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
+          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
         </is>
       </c>
       <c r="D63" s="25" t="inlineStr">
         <is>
-          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
+          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
         </is>
       </c>
       <c r="E63" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-58,Ⅱ-59</t>
         </is>
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc19 追-9</t>
         </is>
       </c>
       <c r="G63" s="23" t="inlineStr">
@@ -9446,22 +9446,22 @@
       </c>
       <c r="C64" s="25" t="inlineStr">
         <is>
-          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
+          <t>介護保険事業状況報告（月報・年報）の原データの提供可否</t>
         </is>
       </c>
       <c r="D64" s="25" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
+          <t>見える化に収録されていない項目（サービス種類別利用者数の月次推移等）が扱えるようになる。</t>
         </is>
       </c>
       <c r="E64" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F64" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-65</t>
+          <t>doc19 追-10</t>
         </is>
       </c>
       <c r="G64" s="23" t="inlineStr">
@@ -9484,22 +9484,22 @@
       </c>
       <c r="C65" s="25" t="inlineStr">
         <is>
-          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
+          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
         </is>
       </c>
       <c r="D65" s="25" t="inlineStr">
         <is>
-          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
+          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
         </is>
       </c>
       <c r="E65" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-68</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G65" s="23" t="inlineStr">
@@ -9522,22 +9522,22 @@
       </c>
       <c r="C66" s="25" t="inlineStr">
         <is>
-          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
+          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
         </is>
       </c>
       <c r="D66" s="25" t="inlineStr">
         <is>
-          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
+          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
         </is>
       </c>
       <c r="E66" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F66" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-71</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G66" s="23" t="inlineStr">
@@ -9560,22 +9560,22 @@
       </c>
       <c r="C67" s="25" t="inlineStr">
         <is>
-          <t>シルバー人材センターの会員数・受注実績</t>
+          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
         </is>
       </c>
       <c r="D67" s="25" t="inlineStr">
         <is>
-          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
+          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
         </is>
       </c>
       <c r="E67" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-72</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G67" s="23" t="inlineStr">
@@ -9598,22 +9598,22 @@
       </c>
       <c r="C68" s="25" t="inlineStr">
         <is>
-          <t>第9期調査の集計基準・集計表の提供</t>
+          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
         </is>
       </c>
       <c r="D68" s="25" t="inlineStr">
         <is>
-          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
+          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
         </is>
       </c>
       <c r="E68" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F68" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-92</t>
+          <t>doc20§6-2 K-65</t>
         </is>
       </c>
       <c r="G68" s="23" t="inlineStr">
@@ -9631,27 +9631,27 @@
       </c>
       <c r="B69" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C69" s="25" t="inlineStr">
         <is>
-          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
+          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
         </is>
       </c>
       <c r="D69" s="25" t="inlineStr">
         <is>
-          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
+          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
         </is>
       </c>
       <c r="E69" s="23" t="inlineStr">
         <is>
-          <t>Ⅴ-95</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F69" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-67</t>
+          <t>doc21§5 K-68</t>
         </is>
       </c>
       <c r="G69" s="23" t="inlineStr">
@@ -9669,27 +9669,27 @@
       </c>
       <c r="B70" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C70" s="25" t="inlineStr">
         <is>
-          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
+          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
         </is>
       </c>
       <c r="D70" s="25" t="inlineStr">
         <is>
-          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
+          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
         </is>
       </c>
       <c r="E70" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-35</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F70" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-93</t>
+          <t>doc21§5 K-71</t>
         </is>
       </c>
       <c r="G70" s="23" t="inlineStr">
@@ -9707,27 +9707,27 @@
       </c>
       <c r="B71" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C71" s="25" t="inlineStr">
         <is>
-          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
+          <t>シルバー人材センターの会員数・受注実績</t>
         </is>
       </c>
       <c r="D71" s="25" t="inlineStr">
         <is>
-          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
+          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
         </is>
       </c>
       <c r="E71" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-48</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-94</t>
+          <t>doc21§5 K-72</t>
         </is>
       </c>
       <c r="G71" s="23" t="inlineStr">
@@ -9745,27 +9745,27 @@
       </c>
       <c r="B72" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C72" s="25" t="inlineStr">
         <is>
-          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
+          <t>第9期調査の集計基準・集計表の提供</t>
         </is>
       </c>
       <c r="D72" s="25" t="inlineStr">
         <is>
-          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
+          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
         </is>
       </c>
       <c r="E72" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F72" s="23" t="inlineStr">
         <is>
-          <t>doc19 指-5</t>
+          <t>doc25§8 K-92</t>
         </is>
       </c>
       <c r="G72" s="23" t="inlineStr">
@@ -9783,27 +9783,27 @@
       </c>
       <c r="B73" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C73" s="25" t="inlineStr">
         <is>
-          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
+          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
         </is>
       </c>
       <c r="D73" s="25" t="inlineStr">
         <is>
-          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
+          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
         </is>
       </c>
       <c r="E73" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-108</t>
+          <t>Ⅴ-95</t>
         </is>
       </c>
       <c r="F73" s="23" t="inlineStr">
         <is>
-          <t>doc22 K-80</t>
+          <t>doc20§6-2 K-67</t>
         </is>
       </c>
       <c r="G73" s="23" t="inlineStr">
@@ -9821,27 +9821,27 @@
       </c>
       <c r="B74" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C74" s="25" t="inlineStr">
         <is>
-          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
+          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
         </is>
       </c>
       <c r="D74" s="25" t="inlineStr">
         <is>
-          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
+          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
         </is>
       </c>
       <c r="E74" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-90</t>
+          <t>Ⅰ-35</t>
         </is>
       </c>
       <c r="F74" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-88</t>
+          <t>doc25§8 K-93</t>
         </is>
       </c>
       <c r="G74" s="23" t="inlineStr">
@@ -9859,27 +9859,27 @@
       </c>
       <c r="B75" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C75" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
+          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
         </is>
       </c>
       <c r="D75" s="25" t="inlineStr">
         <is>
-          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
+          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
         </is>
       </c>
       <c r="E75" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅰ-48</t>
         </is>
       </c>
       <c r="F75" s="23" t="inlineStr">
         <is>
-          <t>doc09§4,§10</t>
+          <t>doc25§8 K-94</t>
         </is>
       </c>
       <c r="G75" s="23" t="inlineStr">
@@ -9897,27 +9897,27 @@
       </c>
       <c r="B76" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C76" s="25" t="inlineStr">
         <is>
-          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
+          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
         </is>
       </c>
       <c r="D76" s="25" t="inlineStr">
         <is>
-          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
+          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
         </is>
       </c>
       <c r="E76" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F76" s="23" t="inlineStr">
         <is>
-          <t>doc09§8,§10</t>
+          <t>doc19 指-5</t>
         </is>
       </c>
       <c r="G76" s="23" t="inlineStr">
@@ -9935,27 +9935,27 @@
       </c>
       <c r="B77" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C77" s="25" t="inlineStr">
         <is>
-          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
+          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
         </is>
       </c>
       <c r="D77" s="25" t="inlineStr">
         <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
+          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
         </is>
       </c>
       <c r="E77" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-108</t>
         </is>
       </c>
       <c r="F77" s="23" t="inlineStr">
         <is>
-          <t>doc02§17,doc07,doc18 4-1</t>
+          <t>doc22 K-80</t>
         </is>
       </c>
       <c r="G77" s="23" t="inlineStr">
@@ -9973,27 +9973,27 @@
       </c>
       <c r="B78" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C78" s="25" t="inlineStr">
         <is>
-          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
+          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
         </is>
       </c>
       <c r="D78" s="25" t="inlineStr">
         <is>
-          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
+          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
         </is>
       </c>
       <c r="E78" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-75</t>
+          <t>Ⅳ-90</t>
         </is>
       </c>
       <c r="F78" s="23" t="inlineStr">
         <is>
-          <t>doc17 C-1,doc02§20-2</t>
+          <t>doc24§12 K-88</t>
         </is>
       </c>
       <c r="G78" s="23" t="inlineStr">
@@ -10016,22 +10016,22 @@
       </c>
       <c r="C79" s="25" t="inlineStr">
         <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
         </is>
       </c>
       <c r="D79" s="25" t="inlineStr">
         <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
         </is>
       </c>
       <c r="E79" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
-          <t>doc13§6</t>
+          <t>doc09§4,§10</t>
         </is>
       </c>
       <c r="G79" s="23" t="inlineStr">
@@ -10054,22 +10054,22 @@
       </c>
       <c r="C80" s="25" t="inlineStr">
         <is>
-          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
         </is>
       </c>
       <c r="D80" s="25" t="inlineStr">
         <is>
-          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
+          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
         </is>
       </c>
       <c r="E80" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F80" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-14</t>
+          <t>doc09§8,§10</t>
         </is>
       </c>
       <c r="G80" s="23" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="C81" s="25" t="inlineStr">
         <is>
-          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
         </is>
       </c>
       <c r="D81" s="25" t="inlineStr">
         <is>
-          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
         </is>
       </c>
       <c r="E81" s="23" t="inlineStr">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t>doc19 §3</t>
+          <t>doc02§17,doc07,doc18 4-1</t>
         </is>
       </c>
       <c r="G81" s="23" t="inlineStr">
@@ -10130,22 +10130,22 @@
       </c>
       <c r="C82" s="25" t="inlineStr">
         <is>
-          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
         </is>
       </c>
       <c r="D82" s="25" t="inlineStr">
         <is>
-          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
         </is>
       </c>
       <c r="E82" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-56,Ⅱ-75</t>
         </is>
       </c>
       <c r="F82" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-73</t>
+          <t>doc17 C-1,doc02§20-2</t>
         </is>
       </c>
       <c r="G82" s="23" t="inlineStr">
@@ -10168,22 +10168,22 @@
       </c>
       <c r="C83" s="25" t="inlineStr">
         <is>
-          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
         </is>
       </c>
       <c r="D83" s="25" t="inlineStr">
         <is>
-          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
         </is>
       </c>
       <c r="E83" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-105</t>
+          <t>Ⅱ-60,Ⅱ-65</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-90</t>
+          <t>doc13§6</t>
         </is>
       </c>
       <c r="G83" s="23" t="inlineStr">
@@ -10201,27 +10201,27 @@
       </c>
       <c r="B84" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C84" s="25" t="inlineStr">
         <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
         </is>
       </c>
       <c r="D84" s="25" t="inlineStr">
         <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
         </is>
       </c>
       <c r="E84" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F84" s="23" t="inlineStr">
         <is>
-          <t>doc07§4</t>
+          <t>doc19 追-14</t>
         </is>
       </c>
       <c r="G84" s="23" t="inlineStr">
@@ -10239,27 +10239,27 @@
       </c>
       <c r="B85" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C85" s="25" t="inlineStr">
         <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
         </is>
       </c>
       <c r="D85" s="25" t="inlineStr">
         <is>
-          <t>評価指標の読み方に影響。</t>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
         </is>
       </c>
       <c r="E85" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t>doc07§8-4</t>
+          <t>doc19 §3</t>
         </is>
       </c>
       <c r="G85" s="23" t="inlineStr">
@@ -10277,27 +10277,27 @@
       </c>
       <c r="B86" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C86" s="25" t="inlineStr">
         <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
         </is>
       </c>
       <c r="D86" s="25" t="inlineStr">
         <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
         </is>
       </c>
       <c r="E86" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F86" s="23" t="inlineStr">
         <is>
-          <t>doc08§4,§8-2</t>
+          <t>doc21§5 K-73</t>
         </is>
       </c>
       <c r="G86" s="23" t="inlineStr">
@@ -10315,27 +10315,27 @@
       </c>
       <c r="B87" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C87" s="25" t="inlineStr">
         <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
         </is>
       </c>
       <c r="D87" s="25" t="inlineStr">
         <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
         </is>
       </c>
       <c r="E87" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-105</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr">
         <is>
-          <t>doc02§20-1</t>
+          <t>doc24§12 K-90</t>
         </is>
       </c>
       <c r="G87" s="23" t="inlineStr">
@@ -10353,27 +10353,27 @@
       </c>
       <c r="B88" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C88" s="25" t="inlineStr">
         <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
         </is>
       </c>
       <c r="D88" s="25" t="inlineStr">
         <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
         </is>
       </c>
       <c r="E88" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F88" s="23" t="inlineStr">
         <is>
-          <t>doc15,doc18</t>
+          <t>doc07§4</t>
         </is>
       </c>
       <c r="G88" s="23" t="inlineStr">
@@ -10391,27 +10391,27 @@
       </c>
       <c r="B89" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C89" s="25" t="inlineStr">
         <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
         </is>
       </c>
       <c r="D89" s="25" t="inlineStr">
         <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+          <t>評価指標の読み方に影響。</t>
         </is>
       </c>
       <c r="E89" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc18 3-1</t>
+          <t>doc07§8-4</t>
         </is>
       </c>
       <c r="G89" s="23" t="inlineStr">
@@ -10429,27 +10429,27 @@
       </c>
       <c r="B90" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C90" s="25" t="inlineStr">
         <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
         </is>
       </c>
       <c r="D90" s="25" t="inlineStr">
         <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
         </is>
       </c>
       <c r="E90" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F90" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
+          <t>doc08§4,§8-2</t>
         </is>
       </c>
       <c r="G90" s="23" t="inlineStr">
@@ -10467,27 +10467,27 @@
       </c>
       <c r="B91" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C91" s="25" t="inlineStr">
         <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
         </is>
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t>doc17 B-3,doc18 4-3</t>
+          <t>doc02§20-1</t>
         </is>
       </c>
       <c r="G91" s="23" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="C92" s="25" t="inlineStr">
         <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
         </is>
       </c>
       <c r="D92" s="25" t="inlineStr">
         <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
         </is>
       </c>
       <c r="E92" s="23" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="F92" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 2-9</t>
+          <t>doc15,doc18</t>
         </is>
       </c>
       <c r="G92" s="23" t="inlineStr">
@@ -10548,22 +10548,22 @@
       </c>
       <c r="C93" s="25" t="inlineStr">
         <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
         </is>
       </c>
       <c r="D93" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
         </is>
       </c>
       <c r="E93" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 5-7</t>
+          <t>doc14§5,doc18 3-1</t>
         </is>
       </c>
       <c r="G93" s="23" t="inlineStr">
@@ -10581,27 +10581,27 @@
       </c>
       <c r="B94" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C94" s="25" t="inlineStr">
         <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
         </is>
       </c>
       <c r="D94" s="25" t="inlineStr">
         <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
         </is>
       </c>
       <c r="E94" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F94" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-4</t>
+          <t>doc14§5,doc15,doc18 4-5</t>
         </is>
       </c>
       <c r="G94" s="23" t="inlineStr">
@@ -10619,27 +10619,27 @@
       </c>
       <c r="B95" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C95" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
         </is>
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
         </is>
       </c>
       <c r="E95" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-73,Ⅱ-75</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t>doc01-5,doc18 1-2</t>
+          <t>doc17 B-3,doc18 4-3</t>
         </is>
       </c>
       <c r="G95" s="23" t="inlineStr">
@@ -10657,27 +10657,27 @@
       </c>
       <c r="B96" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C96" s="25" t="inlineStr">
         <is>
-          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
         </is>
       </c>
       <c r="D96" s="25" t="inlineStr">
         <is>
-          <t>施策の書きぶりに影響。</t>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
         </is>
       </c>
       <c r="E96" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-72</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F96" s="23" t="inlineStr">
         <is>
-          <t>doc01-12</t>
+          <t>doc17 A-1,doc18 2-9</t>
         </is>
       </c>
       <c r="G96" s="23" t="inlineStr">
@@ -10695,27 +10695,27 @@
       </c>
       <c r="B97" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C97" s="25" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
         </is>
       </c>
       <c r="D97" s="25" t="inlineStr">
         <is>
-          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
         </is>
       </c>
       <c r="E97" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-64,Ⅱ-75</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-13</t>
+          <t>doc17 A-1,doc18 5-7</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr">
@@ -10733,27 +10733,27 @@
       </c>
       <c r="B98" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C98" s="25" t="inlineStr">
         <is>
-          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
         </is>
       </c>
       <c r="D98" s="25" t="inlineStr">
         <is>
-          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
         </is>
       </c>
       <c r="E98" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-31</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F98" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-6</t>
+          <t>doc08§8-4</t>
         </is>
       </c>
       <c r="G98" s="23" t="inlineStr">
@@ -10771,27 +10771,27 @@
       </c>
       <c r="B99" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C99" s="25" t="inlineStr">
         <is>
-          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
         </is>
       </c>
       <c r="D99" s="25" t="inlineStr">
         <is>
-          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
         </is>
       </c>
       <c r="E99" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-40,Ⅰ-42</t>
+          <t>Ⅱ-73,Ⅱ-75</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-7</t>
+          <t>doc01-5,doc18 1-2</t>
         </is>
       </c>
       <c r="G99" s="23" t="inlineStr">
@@ -10809,346 +10809,346 @@
       </c>
       <c r="B100" s="24" t="inlineStr">
         <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C100" s="25" t="inlineStr">
+        <is>
+          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+        </is>
+      </c>
+      <c r="D100" s="25" t="inlineStr">
+        <is>
+          <t>施策の書きぶりに影響。</t>
+        </is>
+      </c>
+      <c r="E100" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-71,Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F100" s="23" t="inlineStr">
+        <is>
+          <t>doc01-12</t>
+        </is>
+      </c>
+      <c r="G100" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H100" s="25" t="inlineStr"/>
+    </row>
+    <row r="101" ht="34" customHeight="1">
+      <c r="A101" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B101" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C101" s="25" t="inlineStr">
+        <is>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+        </is>
+      </c>
+      <c r="D101" s="25" t="inlineStr">
+        <is>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+        </is>
+      </c>
+      <c r="E101" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F101" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-13</t>
+        </is>
+      </c>
+      <c r="G101" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H101" s="25" t="inlineStr"/>
+    </row>
+    <row r="102" ht="34" customHeight="1">
+      <c r="A102" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B102" s="24" t="inlineStr">
+        <is>
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C100" s="25" t="inlineStr">
+      <c r="C102" s="25" t="inlineStr">
+        <is>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+        </is>
+      </c>
+      <c r="D102" s="25" t="inlineStr">
+        <is>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+        </is>
+      </c>
+      <c r="E102" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-31</t>
+        </is>
+      </c>
+      <c r="F102" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-6</t>
+        </is>
+      </c>
+      <c r="G102" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H102" s="25" t="inlineStr"/>
+    </row>
+    <row r="103" ht="34" customHeight="1">
+      <c r="A103" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B103" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C103" s="25" t="inlineStr">
+        <is>
+          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+        </is>
+      </c>
+      <c r="D103" s="25" t="inlineStr">
+        <is>
+          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+        </is>
+      </c>
+      <c r="E103" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-40,Ⅰ-42</t>
+        </is>
+      </c>
+      <c r="F103" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-7</t>
+        </is>
+      </c>
+      <c r="G103" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H103" s="25" t="inlineStr"/>
+    </row>
+    <row r="104" ht="34" customHeight="1">
+      <c r="A104" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B104" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C104" s="25" t="inlineStr">
         <is>
           <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
         </is>
       </c>
-      <c r="D100" s="25" t="inlineStr">
+      <c r="D104" s="25" t="inlineStr">
         <is>
           <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
         </is>
       </c>
-      <c r="E100" s="23" t="inlineStr">
+      <c r="E104" s="23" t="inlineStr">
         <is>
           <t>Ⅰ-09</t>
         </is>
       </c>
-      <c r="F100" s="23" t="inlineStr">
+      <c r="F104" s="23" t="inlineStr">
         <is>
           <t>doc23§1-3</t>
         </is>
       </c>
-      <c r="G100" s="23" t="inlineStr">
+      <c r="G104" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H100" s="25" t="inlineStr"/>
-    </row>
-    <row r="101" ht="34" customHeight="1">
-      <c r="A101" s="38" t="inlineStr">
+      <c r="H104" s="25" t="inlineStr"/>
+    </row>
+    <row r="105" ht="34" customHeight="1">
+      <c r="A105" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B105" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C105" s="25" t="inlineStr">
+        <is>
+          <t>送付状の個人情報に関する説明の補強</t>
+        </is>
+      </c>
+      <c r="D105" s="25" t="inlineStr">
+        <is>
+          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+        </is>
+      </c>
+      <c r="E105" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-14</t>
+        </is>
+      </c>
+      <c r="F105" s="23" t="inlineStr">
+        <is>
+          <t>doc27§5-1</t>
+        </is>
+      </c>
+      <c r="G105" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H105" s="25" t="inlineStr"/>
+    </row>
+    <row r="106" ht="34" customHeight="1">
+      <c r="A106" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B106" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C106" s="25" t="inlineStr">
+        <is>
+          <t>ニーズ調査の選択肢の表記変更5件の可否（障がい表記・ぜひ・役場・移動販売・フルタイム）</t>
+        </is>
+      </c>
+      <c r="D106" s="25" t="inlineStr">
+        <is>
+          <t>村の表記ルール等による変更。手引きQ&amp;Aの「通称への置き換え」に近く多くは許容されると考えるが、「買い物（移動販売等※宅配は含まない）」のみ回答の範囲を広げる方向の変更で第9期・他保険者との比較に影響し得る。</t>
+        </is>
+      </c>
+      <c r="E106" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-09</t>
+        </is>
+      </c>
+      <c r="F106" s="23" t="inlineStr">
+        <is>
+          <t>doc27§4</t>
+        </is>
+      </c>
+      <c r="G106" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H106" s="25" t="inlineStr"/>
+    </row>
+    <row r="107" ht="34" customHeight="1">
+      <c r="A107" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B101" s="24" t="inlineStr">
+      <c r="B107" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C101" s="25" t="inlineStr">
+      <c r="C107" s="25" t="inlineStr">
         <is>
           <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
         </is>
       </c>
-      <c r="D101" s="25" t="inlineStr">
+      <c r="D107" s="25" t="inlineStr">
         <is>
           <t>第9期はA4・本文104頁・全6章＋資料編。</t>
         </is>
       </c>
-      <c r="E101" s="23" t="inlineStr">
+      <c r="E107" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-89</t>
         </is>
       </c>
-      <c r="F101" s="23" t="inlineStr">
+      <c r="F107" s="23" t="inlineStr">
         <is>
           <t>doc01-10</t>
         </is>
       </c>
-      <c r="G101" s="23" t="inlineStr">
+      <c r="G107" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H101" s="25" t="inlineStr"/>
-    </row>
-    <row r="102" ht="34" customHeight="1">
-      <c r="A102" s="38" t="inlineStr">
+      <c r="H107" s="25" t="inlineStr"/>
+    </row>
+    <row r="108" ht="34" customHeight="1">
+      <c r="A108" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B102" s="24" t="inlineStr">
+      <c r="B108" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C102" s="25" t="inlineStr">
+      <c r="C108" s="25" t="inlineStr">
         <is>
           <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
         </is>
       </c>
-      <c r="D102" s="25" t="inlineStr">
+      <c r="D108" s="25" t="inlineStr">
         <is>
           <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
         </is>
       </c>
-      <c r="E102" s="23" t="inlineStr">
+      <c r="E108" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-92</t>
         </is>
       </c>
-      <c r="F102" s="23" t="inlineStr">
+      <c r="F108" s="23" t="inlineStr">
         <is>
           <t>doc01-10,doc08</t>
         </is>
       </c>
-      <c r="G102" s="23" t="inlineStr">
+      <c r="G108" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H102" s="25" t="inlineStr"/>
-    </row>
-    <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="39" t="inlineStr">
+      <c r="H108" s="25" t="inlineStr"/>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="39" t="inlineStr">
         <is>
           <t>■ 解決済み（記録）</t>
         </is>
       </c>
-    </row>
-    <row r="105" ht="34" customHeight="1">
-      <c r="A105" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B105" s="41" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C105" s="42" t="inlineStr">
-        <is>
-          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
-        </is>
-      </c>
-      <c r="D105" s="42" t="inlineStr">
-        <is>
-          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
-        </is>
-      </c>
-      <c r="E105" s="40" t="inlineStr">
-        <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
-        </is>
-      </c>
-      <c r="F105" s="40" t="inlineStr">
-        <is>
-          <t>doc22 §1</t>
-        </is>
-      </c>
-      <c r="G105" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H105" s="42" t="inlineStr"/>
-    </row>
-    <row r="106" ht="34" customHeight="1">
-      <c r="A106" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B106" s="41" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C106" s="42" t="inlineStr">
-        <is>
-          <t>在宅介護実態調査 約150人の抽出基準</t>
-        </is>
-      </c>
-      <c r="D106" s="42" t="inlineStr">
-        <is>
-          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
-        </is>
-      </c>
-      <c r="E106" s="40" t="inlineStr">
-        <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
-        </is>
-      </c>
-      <c r="F106" s="40" t="inlineStr">
-        <is>
-          <t>doc22 §1</t>
-        </is>
-      </c>
-      <c r="G106" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H106" s="42" t="inlineStr"/>
-    </row>
-    <row r="107" ht="34" customHeight="1">
-      <c r="A107" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B107" s="41" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C107" s="42" t="inlineStr">
-        <is>
-          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
-        </is>
-      </c>
-      <c r="D107" s="42" t="inlineStr">
-        <is>
-          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
-        </is>
-      </c>
-      <c r="E107" s="40" t="inlineStr">
-        <is>
-          <t>Ⅰ-25,Ⅰ-26</t>
-        </is>
-      </c>
-      <c r="F107" s="40" t="inlineStr">
-        <is>
-          <t>doc22 §1</t>
-        </is>
-      </c>
-      <c r="G107" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H107" s="42" t="inlineStr"/>
-    </row>
-    <row r="108" ht="34" customHeight="1">
-      <c r="A108" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B108" s="41" t="inlineStr">
-        <is>
-          <t>計画構成</t>
-        </is>
-      </c>
-      <c r="C108" s="42" t="inlineStr">
-        <is>
-          <t>整合を図る関連計画の範囲</t>
-        </is>
-      </c>
-      <c r="D108" s="42" t="inlineStr">
-        <is>
-          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
-        </is>
-      </c>
-      <c r="E108" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-72</t>
-        </is>
-      </c>
-      <c r="F108" s="40" t="inlineStr">
-        <is>
-          <t>doc22 §1</t>
-        </is>
-      </c>
-      <c r="G108" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H108" s="42" t="inlineStr"/>
-    </row>
-    <row r="109" ht="34" customHeight="1">
-      <c r="A109" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B109" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C109" s="42" t="inlineStr">
-        <is>
-          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
-        </is>
-      </c>
-      <c r="D109" s="42" t="inlineStr">
-        <is>
-          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
-        </is>
-      </c>
-      <c r="E109" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F109" s="40" t="inlineStr">
-        <is>
-          <t>doc20§3,§4</t>
-        </is>
-      </c>
-      <c r="G109" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H109" s="42" t="inlineStr"/>
-    </row>
-    <row r="110" ht="34" customHeight="1">
-      <c r="A110" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B110" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C110" s="42" t="inlineStr">
-        <is>
-          <t>交付要綱の配点表（満点）</t>
-        </is>
-      </c>
-      <c r="D110" s="42" t="inlineStr">
-        <is>
-          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
-        </is>
-      </c>
-      <c r="E110" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F110" s="40" t="inlineStr">
-        <is>
-          <t>doc20§2</t>
-        </is>
-      </c>
-      <c r="G110" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H110" s="42" t="inlineStr"/>
     </row>
     <row r="111" ht="34" customHeight="1">
       <c r="A111" s="40" t="inlineStr">
@@ -11158,32 +11158,32 @@
       </c>
       <c r="B111" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C111" s="42" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の交付金評価結果</t>
+          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
         </is>
       </c>
       <c r="D111" s="42" t="inlineStr">
         <is>
-          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
         </is>
       </c>
       <c r="E111" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F111" s="40" t="inlineStr">
         <is>
-          <t>doc20§3-1</t>
+          <t>doc27§1-1</t>
         </is>
       </c>
       <c r="G111" s="40" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（一部再掲）</t>
         </is>
       </c>
       <c r="H111" s="42" t="inlineStr"/>
@@ -11196,27 +11196,27 @@
       </c>
       <c r="B112" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C112" s="42" t="inlineStr">
         <is>
-          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
         </is>
       </c>
       <c r="D112" s="42" t="inlineStr">
         <is>
-          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+          <t>第2稿（0904版）で両方とも修正済。</t>
         </is>
       </c>
       <c r="E112" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-58</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F112" s="40" t="inlineStr">
         <is>
-          <t>doc09</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G112" s="40" t="inlineStr">
@@ -11234,32 +11234,32 @@
       </c>
       <c r="B113" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C113" s="42" t="inlineStr">
         <is>
-          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
         </is>
       </c>
       <c r="D113" s="42" t="inlineStr">
         <is>
-          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
         </is>
       </c>
       <c r="E113" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F113" s="40" t="inlineStr">
         <is>
-          <t>doc02§20-2</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G113" s="40" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（番号は再掲）</t>
         </is>
       </c>
       <c r="H113" s="42" t="inlineStr"/>
@@ -11272,48 +11272,390 @@
       </c>
       <c r="B114" s="41" t="inlineStr">
         <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C114" s="42" t="inlineStr">
+        <is>
+          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
+        </is>
+      </c>
+      <c r="D114" s="42" t="inlineStr">
+        <is>
+          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
+        </is>
+      </c>
+      <c r="E114" s="40" t="inlineStr">
+        <is>
+          <t>Ⅰ-08,Ⅰ-24</t>
+        </is>
+      </c>
+      <c r="F114" s="40" t="inlineStr">
+        <is>
+          <t>doc22 §1</t>
+        </is>
+      </c>
+      <c r="G114" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H114" s="42" t="inlineStr"/>
+    </row>
+    <row r="115" ht="34" customHeight="1">
+      <c r="A115" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B115" s="41" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C115" s="42" t="inlineStr">
+        <is>
+          <t>在宅介護実態調査 約150人の抽出基準</t>
+        </is>
+      </c>
+      <c r="D115" s="42" t="inlineStr">
+        <is>
+          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
+        </is>
+      </c>
+      <c r="E115" s="40" t="inlineStr">
+        <is>
+          <t>Ⅰ-08,Ⅰ-24</t>
+        </is>
+      </c>
+      <c r="F115" s="40" t="inlineStr">
+        <is>
+          <t>doc22 §1</t>
+        </is>
+      </c>
+      <c r="G115" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H115" s="42" t="inlineStr"/>
+    </row>
+    <row r="116" ht="34" customHeight="1">
+      <c r="A116" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B116" s="41" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C116" s="42" t="inlineStr">
+        <is>
+          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
+        </is>
+      </c>
+      <c r="D116" s="42" t="inlineStr">
+        <is>
+          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
+        </is>
+      </c>
+      <c r="E116" s="40" t="inlineStr">
+        <is>
+          <t>Ⅰ-25,Ⅰ-26</t>
+        </is>
+      </c>
+      <c r="F116" s="40" t="inlineStr">
+        <is>
+          <t>doc22 §1</t>
+        </is>
+      </c>
+      <c r="G116" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H116" s="42" t="inlineStr"/>
+    </row>
+    <row r="117" ht="34" customHeight="1">
+      <c r="A117" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B117" s="41" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C117" s="42" t="inlineStr">
+        <is>
+          <t>整合を図る関連計画の範囲</t>
+        </is>
+      </c>
+      <c r="D117" s="42" t="inlineStr">
+        <is>
+          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+        </is>
+      </c>
+      <c r="E117" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F117" s="40" t="inlineStr">
+        <is>
+          <t>doc22 §1</t>
+        </is>
+      </c>
+      <c r="G117" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H117" s="42" t="inlineStr"/>
+    </row>
+    <row r="118" ht="34" customHeight="1">
+      <c r="A118" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B118" s="41" t="inlineStr">
+        <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="C114" s="42" t="inlineStr">
+      <c r="C118" s="42" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+        </is>
+      </c>
+      <c r="D118" s="42" t="inlineStr">
+        <is>
+          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+        </is>
+      </c>
+      <c r="E118" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F118" s="40" t="inlineStr">
+        <is>
+          <t>doc20§3,§4</t>
+        </is>
+      </c>
+      <c r="G118" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H118" s="42" t="inlineStr"/>
+    </row>
+    <row r="119" ht="34" customHeight="1">
+      <c r="A119" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B119" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C119" s="42" t="inlineStr">
+        <is>
+          <t>交付要綱の配点表（満点）</t>
+        </is>
+      </c>
+      <c r="D119" s="42" t="inlineStr">
+        <is>
+          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+        </is>
+      </c>
+      <c r="E119" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F119" s="40" t="inlineStr">
+        <is>
+          <t>doc20§2</t>
+        </is>
+      </c>
+      <c r="G119" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H119" s="42" t="inlineStr"/>
+    </row>
+    <row r="120" ht="34" customHeight="1">
+      <c r="A120" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B120" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C120" s="42" t="inlineStr">
+        <is>
+          <t>令和6年度・令和7年度の交付金評価結果</t>
+        </is>
+      </c>
+      <c r="D120" s="42" t="inlineStr">
+        <is>
+          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+        </is>
+      </c>
+      <c r="E120" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F120" s="40" t="inlineStr">
+        <is>
+          <t>doc20§3-1</t>
+        </is>
+      </c>
+      <c r="G120" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H120" s="42" t="inlineStr"/>
+    </row>
+    <row r="121" ht="34" customHeight="1">
+      <c r="A121" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B121" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C121" s="42" t="inlineStr">
+        <is>
+          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+        </is>
+      </c>
+      <c r="D121" s="42" t="inlineStr">
+        <is>
+          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+        </is>
+      </c>
+      <c r="E121" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-56,Ⅱ-58</t>
+        </is>
+      </c>
+      <c r="F121" s="40" t="inlineStr">
+        <is>
+          <t>doc09</t>
+        </is>
+      </c>
+      <c r="G121" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H121" s="42" t="inlineStr"/>
+    </row>
+    <row r="122" ht="34" customHeight="1">
+      <c r="A122" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B122" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C122" s="42" t="inlineStr">
+        <is>
+          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+        </is>
+      </c>
+      <c r="D122" s="42" t="inlineStr">
+        <is>
+          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+        </is>
+      </c>
+      <c r="E122" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-59</t>
+        </is>
+      </c>
+      <c r="F122" s="40" t="inlineStr">
+        <is>
+          <t>doc02§20-2</t>
+        </is>
+      </c>
+      <c r="G122" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H122" s="42" t="inlineStr"/>
+    </row>
+    <row r="123" ht="34" customHeight="1">
+      <c r="A123" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B123" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C123" s="42" t="inlineStr">
         <is>
           <t>国の指針・様式の更新有無</t>
         </is>
       </c>
-      <c r="D114" s="42" t="inlineStr">
+      <c r="D123" s="42" t="inlineStr">
         <is>
           <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
-      <c r="E114" s="40" t="inlineStr">
+      <c r="E123" s="40" t="inlineStr">
         <is>
           <t>Ⅰ-11</t>
         </is>
       </c>
-      <c r="F114" s="40" t="inlineStr">
+      <c r="F123" s="40" t="inlineStr">
         <is>
           <t>doc04,doc05</t>
         </is>
       </c>
-      <c r="G114" s="40" t="inlineStr">
+      <c r="G123" s="40" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H114" s="42" t="inlineStr"/>
+      <c r="H123" s="42" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H102"/>
+  <autoFilter ref="A4:H108"/>
   <mergeCells count="3">
+    <mergeCell ref="A110:H110"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A104:H104"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11327,7 +11669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12061,30 +12403,30 @@
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>成果物</t>
+          <t>調査票</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>第2回策定委員会 資料2・5・6・7（output/08_第2回策定委員会資料.docx）</t>
+          <t>調査票 第2稿（0904版）</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>26表・A4約30頁。資料2と7は本体完成、資料5と6は骨格</t>
+          <t>指摘13件のうち11件が反映。必須修正3件を新たに検出</t>
         </is>
       </c>
       <c r="D27" s="43" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>docs/…/26_第2回策定委員会_資料構成.md §11</t>
+          <t>docs/…/27_調査票第2稿レビュー.md</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>作成済</t>
+          <t>受領済</t>
         </is>
       </c>
     </row>
@@ -12096,12 +12438,12 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>集計仕様書（output/07_集計仕様書.xlsx）</t>
+          <t>第2回策定委員会 資料2・5・6・7（output/08_第2回策定委員会資料.docx）</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>6シート。ニーズ80設問・在宅26設問・派生変数20・クロス表20</t>
+          <t>26表・A4約30頁。資料2と7は本体完成、資料5と6は骨格</t>
         </is>
       </c>
       <c r="D28" s="43" t="n">
@@ -12109,7 +12451,7 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>docs/…/25_集計仕様書.md</t>
+          <t>docs/…/26_第2回策定委員会_資料構成.md §11</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -12126,12 +12468,12 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>第2回策定委員会 資料構成（doc26）</t>
+          <t>集計仕様書（output/07_集計仕様書.xlsx）</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>資料1〜8・約53頁＋素案別冊。合意事項5点</t>
+          <t>6シート。ニーズ80設問・在宅26設問・派生変数20・クロス表20</t>
         </is>
       </c>
       <c r="D29" s="43" t="n">
@@ -12139,7 +12481,7 @@
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>docs/…/26_第2回策定委員会_資料構成.md</t>
+          <t>docs/…/25_集計仕様書.md</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -12151,47 +12493,47 @@
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>調査票</t>
+          <t>成果物</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>調査票 第1稿（ニーズ調査・在宅介護実態調査）</t>
+          <t>第2回策定委員会 資料構成（doc26）</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>0828版。令和7年8月版・手法Ⅲ標準様式と全面突合</t>
+          <t>資料1〜8・約53頁＋素案別冊。合意事項5点</t>
         </is>
       </c>
       <c r="D30" s="43" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>docs/…/23_調査票第1稿レビュー_ICF分析設計.md</t>
+          <t>docs/…/26_第2回策定委員会_資料構成.md</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>受領済</t>
+          <t>作成済</t>
         </is>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>国資料</t>
+          <t>調査票</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>令和8年度 交付金評価指標（市町村分）配点表</t>
+          <t>調査票 第1稿（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>全17頁。推進400点・支援400点、目標Ⅰ〜Ⅳ各100点</t>
+          <t>0828版。令和7年8月版・手法Ⅲ標準様式と全面突合</t>
         </is>
       </c>
       <c r="D31" s="43" t="n">
@@ -12199,7 +12541,7 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>docs/…/20_交付金評価結果分析.md</t>
+          <t>docs/…/23_調査票第1稿レビュー_ICF分析設計.md</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -12216,12 +12558,12 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>令和6年度 該当状況調査票集計表（全国一覧表）</t>
+          <t>令和8年度 交付金評価指標（市町村分）配点表</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>全国1,741市町村。村は第398行。合計295点</t>
+          <t>全17頁。推進400点・支援400点、目標Ⅰ〜Ⅳ各100点</t>
         </is>
       </c>
       <c r="D32" s="43" t="n">
@@ -12246,12 +12588,12 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>令和7年度 該当状況調査票集計表（全国集計・市町村）</t>
+          <t>令和6年度 該当状況調査票集計表（全国一覧表）</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>合計339点。全国平均435.0点</t>
+          <t>全国1,741市町村。村は第398行。合計295点</t>
         </is>
       </c>
       <c r="D33" s="43" t="n">
@@ -12276,12 +12618,12 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>令和8年度 該当状況調査票集計表（全国集計・市町村）</t>
+          <t>令和7年度 該当状況調査票集計表（全国集計・市町村）</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>合計447点。全国平均455.1点／全国1,005位／県内34位</t>
+          <t>合計339点。全国平均435.0点</t>
         </is>
       </c>
       <c r="D34" s="43" t="n">
@@ -12301,17 +12643,17 @@
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>関連計画</t>
+          <t>国資料</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>第四次北塩原村生涯学習推進計画</t>
+          <t>令和8年度 該当状況調査票集計表（全国集計・市町村）</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>全112頁。2018〜2027年度。7z分割書庫4分割で受領</t>
+          <t>合計447点。全国平均455.1点／全国1,005位／県内34位</t>
         </is>
       </c>
       <c r="D35" s="43" t="n">
@@ -12319,49 +12661,79 @@
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
+          <t>docs/…/20_交付金評価結果分析.md</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>関連計画</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>第四次北塩原村生涯学習推進計画</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>全112頁。2018〜2027年度。7z分割書庫4分割で受領</t>
+        </is>
+      </c>
+      <c r="D36" s="43" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
           <t>docs/…/21_関連計画_第四次生涯学習推進計画.md</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>受領済</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="35" t="inlineStr">
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="35" t="inlineStr">
         <is>
           <t>村データ</t>
         </is>
       </c>
-      <c r="B36" s="34" t="inlineStr">
+      <c r="B37" s="34" t="inlineStr">
         <is>
           <t>★要介護認定データ（調査票との関連付け用）</t>
         </is>
       </c>
-      <c r="C36" s="34" t="inlineStr">
+      <c r="C37" s="34" t="inlineStr">
         <is>
           <t>仕様書4Ⅰ(5)。調査回収後に必要</t>
         </is>
       </c>
-      <c r="D36" s="35" t="inlineStr">
+      <c r="D37" s="35" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E36" s="34" t="inlineStr">
+      <c r="E37" s="34" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F36" s="35" t="inlineStr">
+      <c r="F37" s="35" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F36"/>
+  <autoFilter ref="A4:F37"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$108</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4127,11 +4127,11 @@
       <c r="J57" s="14" t="n"/>
       <c r="K57" s="14" t="n"/>
       <c r="L57" s="14" t="n">
-        <v>46259</v>
+        <v>46272</v>
       </c>
       <c r="M57" s="14" t="n"/>
       <c r="N57" s="15" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="O57" s="16" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="P57" s="13" t="inlineStr">
         <is>
-          <t>見える化・決算は受領。村の事業実績（通いの場実数・成年後見等）が未受領。</t>
+          <t>見える化・決算は受領。★9/7：成年後見の実績（利用促進施策の取組状況調査 令和7・8年度、会津権利擁護・成年後見センターの相談件数 令和6・7年度）と合計所得金額分布調査を受領。村単独事業（除雪・緊急通報・生活支援ハウス等）の実績数値は引き続き未受領。</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4450,7 @@
         <v>46265</v>
       </c>
       <c r="M62" s="8" t="n">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="N62" s="9" t="n">
         <v>1</v>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="P62" s="7" t="inlineStr">
         <is>
-          <t>doc13として2050年まで整理完了。高齢者数は2020年ピーク、75歳以上は2030年ピーク。</t>
+          <t>★doc13で整理。9/7に厚労省配布の第10期将来推計用人口推計（住基ベース・令和22年まで）を受領し確定。福島県では社人研の市町村別推計が公表されておらず、国が住基ベース推計を配布していることが判明（doc28§1-1）。</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="M63" s="14" t="n"/>
       <c r="N63" s="15" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="O63" s="16" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="M64" s="14" t="n"/>
       <c r="N64" s="15" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="O64" s="16" t="inlineStr">
         <is>
@@ -4845,11 +4845,11 @@
       <c r="J68" s="14" t="n"/>
       <c r="K68" s="14" t="n"/>
       <c r="L68" s="14" t="n">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="M68" s="14" t="n"/>
       <c r="N68" s="15" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="O68" s="16" t="inlineStr">
         <is>
@@ -5106,77 +5106,89 @@
       </c>
       <c r="J72" s="14" t="n"/>
       <c r="K72" s="14" t="n"/>
-      <c r="L72" s="14" t="n"/>
+      <c r="L72" s="14" t="n">
+        <v>46272</v>
+      </c>
       <c r="M72" s="14" t="n"/>
       <c r="N72" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" s="11" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P72" s="13" t="inlineStr"/>
+        <v>0.7</v>
+      </c>
+      <c r="O72" s="16" t="inlineStr">
+        <is>
+          <t>着手</t>
+        </is>
+      </c>
+      <c r="P72" s="13" t="inlineStr">
+        <is>
+          <t>★成年後見制度利用促進施策に係る取組状況調査（令和7・8年度）と会津権利擁護・成年後見センターの相談件数（令和6・7年度）を受領し実態が判明（doc28§3）。利用者4人（後見1・保佐2・補助1・任意後見0）、市町村長申立て0件、市民後見人の養成0人（広域中核機関で1人）・登録0人・受任0件、法人後見は圏域内0法人、任意後見の周知は未実施。一方で中核機関・協議会・申立費用助成・報酬助成はいずれも整備済で地域連携ネットワークは26項目中21項目が整備済。市町村計画は第9期と一体で策定済。</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="23" t="inlineStr">
+      <c r="A73" s="11" t="inlineStr">
         <is>
           <t>Ⅱ-69</t>
         </is>
       </c>
-      <c r="B73" s="24" t="inlineStr">
+      <c r="B73" s="12" t="inlineStr">
         <is>
           <t>Ⅱ 計画策定</t>
         </is>
       </c>
-      <c r="C73" s="24" t="inlineStr">
+      <c r="C73" s="12" t="inlineStr">
         <is>
           <t>Ⅱ-5 成年後見</t>
         </is>
       </c>
-      <c r="D73" s="25" t="inlineStr">
+      <c r="D73" s="13" t="inlineStr">
         <is>
           <t>利用促進の方向性・計画案の提示</t>
         </is>
       </c>
-      <c r="E73" s="23" t="inlineStr">
+      <c r="E73" s="11" t="inlineStr">
         <is>
           <t>仕様書4Ⅱ(5)</t>
         </is>
       </c>
-      <c r="F73" s="23" t="inlineStr">
+      <c r="F73" s="11" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G73" s="25" t="inlineStr">
+      <c r="G73" s="13" t="inlineStr">
         <is>
           <t>計画案</t>
         </is>
       </c>
-      <c r="H73" s="25" t="inlineStr">
+      <c r="H73" s="13" t="inlineStr">
         <is>
           <t>広域調整・関係機関協議は村が実施</t>
         </is>
       </c>
-      <c r="I73" s="23" t="inlineStr">
+      <c r="I73" s="11" t="inlineStr">
         <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="J73" s="26" t="n"/>
-      <c r="K73" s="26" t="n"/>
-      <c r="L73" s="26" t="n"/>
-      <c r="M73" s="26" t="n"/>
-      <c r="N73" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P73" s="25" t="inlineStr"/>
+      <c r="J73" s="14" t="n"/>
+      <c r="K73" s="14" t="n"/>
+      <c r="L73" s="14" t="n">
+        <v>46272</v>
+      </c>
+      <c r="M73" s="14" t="n"/>
+      <c r="N73" s="15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O73" s="16" t="inlineStr">
+        <is>
+          <t>着手</t>
+        </is>
+      </c>
+      <c r="P73" s="13" t="inlineStr">
+        <is>
+          <t>★実績判明により方向性を確定。「体制整備」から「利用促進と担い手確保」へ施策4-7の書きぶりを転換することを提案（doc28§3-4）。ニーズ調査 問11（認知度・家族との話し合い・利用意向）と組み合わせて「制度は整っているのに使われていない」原因を住民側の認知度から説明する。</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
@@ -7122,7 +7134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H123"/>
+  <dimension ref="A1:H132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7389,27 +7401,27 @@
       </c>
       <c r="B10" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C10" s="34" t="inlineStr">
         <is>
-          <t>在宅介護実態調査の手法（手法Ⅲか、手法Ⅳ〈新版 在宅生活改善調査〉を加えるか）</t>
+          <t>★第9期計画の第1号被保険者数の推計に用いたデータ（国配布の住基ベース推計か別の推計か）</t>
         </is>
       </c>
       <c r="D10" s="34" t="inlineStr">
         <is>
-          <t>調査票の設計・印刷頁数・集計方法がすべて決まる。第10期の新設手法。</t>
+          <t>★国の事務連絡により、福島県では社人研の市町村別推計が公表されておらず第9期でも住基ベース推計が配布されていたことが判明。当方が示してきた「社人研推計をそのまま用いたため6.6%ずれた」という説明の前提が崩れた。第10期の説明の組み立てに影響する。</t>
         </is>
       </c>
       <c r="E10" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-07,Ⅰ-10</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F10" s="35" t="inlineStr">
         <is>
-          <t>doc03/doc05</t>
+          <t>doc28§1-1 K-105</t>
         </is>
       </c>
       <c r="G10" s="35" t="inlineStr">
@@ -7427,32 +7439,32 @@
       </c>
       <c r="B11" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C11" s="34" t="inlineStr">
         <is>
-          <t>ニーズ調査 約850人の抽出基準（要支援認定者を含むか／第9期との対比）</t>
+          <t>★第10期の第1号被保険者数をA案（配布データ）とB案（令和8年実績にリベース）のどちらで置くか</t>
         </is>
       </c>
       <c r="D11" s="34" t="inlineStr">
         <is>
-          <t>議事録で在宅150件は「要支援1・2および要介護1〜5の在宅生活者等」と決着。ニーズ約850件の抽出基準（要支援を含むか）は未決着のため残置。</t>
+          <t>★配布データの推計値（令和8年954人）が実績（1,012人）を58人・5.7%下回っており、そのまま用いると第9期と同じ過少推計になる。第10期を通じて約57人・6%の差が生じ、保険料の基準額に直接影響する。県通知は「参考として適切に設定願います」としており配布データの使用を義務づけていない。</t>
         </is>
       </c>
       <c r="E11" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅱ-59,Ⅱ-64</t>
         </is>
       </c>
       <c r="F11" s="35" t="inlineStr">
         <is>
-          <t>doc01-2,3／doc22</t>
+          <t>doc28§1-4 K-106</t>
         </is>
       </c>
       <c r="G11" s="35" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H11" s="34" t="inlineStr"/>
@@ -7470,22 +7482,22 @@
       </c>
       <c r="C12" s="34" t="inlineStr">
         <is>
-          <t>オプション項目の採否（「問6 就労について」ほか）</t>
+          <t>在宅介護実態調査の手法（手法Ⅲか、手法Ⅳ〈新版 在宅生活改善調査〉を加えるか）</t>
         </is>
       </c>
       <c r="D12" s="34" t="inlineStr">
         <is>
-          <t>令和7年8月版で就労はオプションと確定。採否で頁数が変わる。</t>
+          <t>調査票の設計・印刷頁数・集計方法がすべて決まる。第10期の新設手法。</t>
         </is>
       </c>
       <c r="E12" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-12</t>
+          <t>Ⅰ-07,Ⅰ-10</t>
         </is>
       </c>
       <c r="F12" s="35" t="inlineStr">
         <is>
-          <t>doc05</t>
+          <t>doc03/doc05</t>
         </is>
       </c>
       <c r="G12" s="35" t="inlineStr">
@@ -7508,27 +7520,27 @@
       </c>
       <c r="C13" s="34" t="inlineStr">
         <is>
-          <t>村独自設問の採否（除雪・在宅医療・成年後見・歯科受診・服薬ほか）</t>
+          <t>ニーズ調査 約850人の抽出基準（要支援認定者を含むか／第9期との対比）</t>
         </is>
       </c>
       <c r="D13" s="34" t="inlineStr">
         <is>
-          <t>第9期との時系列比較を優先するか、新規論点を入れるかの判断。</t>
+          <t>議事録で在宅150件は「要支援1・2および要介護1〜5の在宅生活者等」と決着。ニーズ約850件の抽出基準（要支援を含むか）は未決着のため残置。</t>
         </is>
       </c>
       <c r="E13" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-13</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F13" s="35" t="inlineStr">
         <is>
-          <t>doc03</t>
+          <t>doc01-2,3／doc22</t>
         </is>
       </c>
       <c r="G13" s="35" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H13" s="34" t="inlineStr"/>
@@ -7546,22 +7558,22 @@
       </c>
       <c r="C14" s="34" t="inlineStr">
         <is>
-          <t>ウェブ回答フォームの仕様（回答期限・村HP掲載の有無・二次元コード印字位置）</t>
+          <t>オプション項目の採否（「問6 就労について」ほか）</t>
         </is>
       </c>
       <c r="D14" s="34" t="inlineStr">
         <is>
-          <t>入稿データ作成の前提。</t>
+          <t>令和7年8月版で就労はオプションと確定。採否で頁数が変わる。</t>
         </is>
       </c>
       <c r="E14" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-16,Ⅰ-17</t>
+          <t>Ⅰ-12</t>
         </is>
       </c>
       <c r="F14" s="35" t="inlineStr">
         <is>
-          <t>doc01-8</t>
+          <t>doc05</t>
         </is>
       </c>
       <c r="G14" s="35" t="inlineStr">
@@ -7584,27 +7596,27 @@
       </c>
       <c r="C15" s="34" t="inlineStr">
         <is>
-          <t>★発送日の確定（9/17前倒し／9/18のまま／9/24後ろ倒し）と回収期限</t>
+          <t>村独自設問の採否（除雪・在宅医療・成年後見・歯科受診・服薬ほか）</t>
         </is>
       </c>
       <c r="D15" s="34" t="inlineStr">
         <is>
-          <t>★議事録は「9月18日頃」とするのみで、5連休の論点に触れていない。9/17（木）への前倒し可否と回収期限を9/3の第1稿提出時に併せて提起する。</t>
+          <t>第9期との時系列比較を優先するか、新規論点を入れるかの判断。</t>
         </is>
       </c>
       <c r="E15" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-29,Ⅰ-32</t>
+          <t>Ⅰ-13</t>
         </is>
       </c>
       <c r="F15" s="35" t="inlineStr">
         <is>
-          <t>doc19 指-1／doc22 A-4</t>
+          <t>doc03</t>
         </is>
       </c>
       <c r="G15" s="35" t="inlineStr">
         <is>
-          <t>再提起</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H15" s="34" t="inlineStr"/>
@@ -7622,22 +7634,22 @@
       </c>
       <c r="C16" s="34" t="inlineStr">
         <is>
-          <t>★ウェブ回答フォームにGoogleフォームを用いることの可否</t>
+          <t>ウェブ回答フォームの仕様（回答期限・村HP掲載の有無・二次元コード印字位置）</t>
         </is>
       </c>
       <c r="D16" s="34" t="inlineStr">
         <is>
-          <t>★通信の暗号化とデータの保存先は別の論点。回答データが村外サーバに保存される。個人情報保護条例上の取扱いと、重複排除の実装・エクスポート後の元データ削除・公開期間管理の確認が必要。</t>
+          <t>入稿データ作成の前提。</t>
         </is>
       </c>
       <c r="E16" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-16,Ⅰ-18</t>
+          <t>Ⅰ-16,Ⅰ-17</t>
         </is>
       </c>
       <c r="F16" s="35" t="inlineStr">
         <is>
-          <t>doc19 追-3</t>
+          <t>doc01-8</t>
         </is>
       </c>
       <c r="G16" s="35" t="inlineStr">
@@ -7660,27 +7672,27 @@
       </c>
       <c r="C17" s="34" t="inlineStr">
         <is>
-          <t>調査票の印刷頁数の調整方針（仕様書はニーズ約12頁／在宅約8頁）</t>
+          <t>★発送日の確定（9/17前倒し／9/18のまま／9/24後ろ倒し）と回収期限</t>
         </is>
       </c>
       <c r="D17" s="34" t="inlineStr">
         <is>
-          <t>現在の調査票案は設問数が多く、レイアウト調整か設問の絞り込みが必要になる可能性。オプション項目の採否と一体。</t>
+          <t>★議事録は「9月18日頃」とするのみで、5連休の論点に触れていない。9/17（木）への前倒し可否と回収期限を9/3の第1稿提出時に併せて提起する。</t>
         </is>
       </c>
       <c r="E17" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-20,Ⅰ-21</t>
+          <t>Ⅰ-29,Ⅰ-32</t>
         </is>
       </c>
       <c r="F17" s="35" t="inlineStr">
         <is>
-          <t>doc19 S-5</t>
+          <t>doc19 指-1／doc22 A-4</t>
         </is>
       </c>
       <c r="G17" s="35" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>再提起</t>
         </is>
       </c>
       <c r="H17" s="34" t="inlineStr"/>
@@ -7698,27 +7710,27 @@
       </c>
       <c r="C18" s="34" t="inlineStr">
         <is>
-          <t>依頼状の差出人名義（村名義／村長名）</t>
+          <t>★ウェブ回答フォームにGoogleフォームを用いることの可否</t>
         </is>
       </c>
       <c r="D18" s="34" t="inlineStr">
         <is>
-          <t>★第1稿は「北塩原村長　遠藤　和夫」と村長名で作成済み。名義の可否と、あわせて現職の村長名が正しいかの確認が必要（当方が保有する平成30年の資料では別の方が村長）。</t>
+          <t>★通信の暗号化とデータの保存先は別の論点。回答データが村外サーバに保存される。個人情報保護条例上の取扱いと、重複排除の実装・エクスポート後の元データ削除・公開期間管理の確認が必要。</t>
         </is>
       </c>
       <c r="E18" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅰ-16,Ⅰ-18</t>
         </is>
       </c>
       <c r="F18" s="35" t="inlineStr">
         <is>
-          <t>doc19 追-4／doc23§5</t>
+          <t>doc19 追-3</t>
         </is>
       </c>
       <c r="G18" s="35" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H18" s="34" t="inlineStr"/>
@@ -7736,22 +7748,22 @@
       </c>
       <c r="C19" s="34" t="inlineStr">
         <is>
-          <t>調査票の印刷部数（予備を何部見込むか）</t>
+          <t>調査票の印刷頁数の調整方針（仕様書はニーズ約12頁／在宅約8頁）</t>
         </is>
       </c>
       <c r="D19" s="34" t="inlineStr">
         <is>
-          <t>約1,000部＋予備。発送後の追加印刷は工程上困難。</t>
+          <t>現在の調査票案は設問数が多く、レイアウト調整か設問の絞り込みが必要になる可能性。オプション項目の採否と一体。</t>
         </is>
       </c>
       <c r="E19" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-21,Ⅰ-22</t>
+          <t>Ⅰ-20,Ⅰ-21</t>
         </is>
       </c>
       <c r="F19" s="35" t="inlineStr">
         <is>
-          <t>doc19 追-5</t>
+          <t>doc19 S-5</t>
         </is>
       </c>
       <c r="G19" s="35" t="inlineStr">
@@ -7774,27 +7786,27 @@
       </c>
       <c r="C20" s="34" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 問8・問9の基準月</t>
+          <t>依頼状の差出人名義（村名義／村長名）</t>
         </is>
       </c>
       <c r="D20" s="34" t="inlineStr">
         <is>
-          <t>発送月の前月が通常。発送日の確定とセット。</t>
+          <t>★第1稿は「北塩原村長　遠藤　和夫」と村長名で作成済み。名義の可否と、あわせて現職の村長名が正しいかの確認が必要（当方が保有する平成30年の資料では別の方が村長）。</t>
         </is>
       </c>
       <c r="E20" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-14</t>
         </is>
       </c>
       <c r="F20" s="35" t="inlineStr">
         <is>
-          <t>doc19 追-2</t>
+          <t>doc19 追-4／doc23§5</t>
         </is>
       </c>
       <c r="G20" s="35" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H20" s="34" t="inlineStr"/>
@@ -7812,22 +7824,22 @@
       </c>
       <c r="C21" s="34" t="inlineStr">
         <is>
-          <t>★ニーズ調査 問7(7)「この1か月間に会った友人・知人の人数」の採用可否</t>
+          <t>調査票の印刷部数（予備を何部見込むか）</t>
         </is>
       </c>
       <c r="D21" s="34" t="inlineStr">
         <is>
-          <t>★第1稿では不採用のうえ以降の番号を繰り上げているため、見える化への入力時に設問の対応が崩れる。採用すれば番号ずれが解消し、かつICF分析の「参加」の量的指標としてそのまま使える。</t>
+          <t>約1,000部＋予備。発送後の追加印刷は工程上困難。</t>
         </is>
       </c>
       <c r="E21" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅰ-21,Ⅰ-22</t>
         </is>
       </c>
       <c r="F21" s="35" t="inlineStr">
         <is>
-          <t>doc23§1-2</t>
+          <t>doc19 追-5</t>
         </is>
       </c>
       <c r="G21" s="35" t="inlineStr">
@@ -7850,22 +7862,22 @@
       </c>
       <c r="C22" s="34" t="inlineStr">
         <is>
-          <t>★ニーズ調査 村独自設問14問の採否と頁数（問3(10)の削除・問7(9)の簡素化）</t>
+          <t>在宅介護実態調査 問8・問9の基準月</t>
         </is>
       </c>
       <c r="D22" s="34" t="inlineStr">
         <is>
-          <t>★標準約66問＋村独自14問＝約79問。仕様書の目安A4約12頁を超える見込み。削除を提案するのは問3(10)「1日に何回食事をとりますか」の1問のみ（低栄養は問3(1)(7)(8)で把握可能）。他13問は施策・交付金の指標と結びついており残すべき。</t>
+          <t>発送月の前月が通常。発送日の確定とセット。</t>
         </is>
       </c>
       <c r="E22" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-12,Ⅰ-13</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F22" s="35" t="inlineStr">
         <is>
-          <t>doc23§4</t>
+          <t>doc19 追-2</t>
         </is>
       </c>
       <c r="G22" s="35" t="inlineStr">
@@ -7888,22 +7900,22 @@
       </c>
       <c r="C23" s="34" t="inlineStr">
         <is>
-          <t>★現職の村長名・所管課・役場の住所の確認</t>
+          <t>★ニーズ調査 問7(7)「この1か月間に会った友人・知人の人数」の採用可否</t>
         </is>
       </c>
       <c r="D23" s="34" t="inlineStr">
         <is>
-          <t>★第1稿の依頼状に「北塩原村長 遠藤 和夫」「保健福祉課 福祉係」「大字北山字姥ヶ作3151番地」と記載。当方では現職の村長名を確認できない。所管課は住民課との別が未確認のまま（doc01 確認事項1）。</t>
+          <t>★第1稿では不採用のうえ以降の番号を繰り上げているため、見える化への入力時に設問の対応が崩れる。採用すれば番号ずれが解消し、かつICF分析の「参加」の量的指標としてそのまま使える。</t>
         </is>
       </c>
       <c r="E23" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F23" s="35" t="inlineStr">
         <is>
-          <t>doc23§5</t>
+          <t>doc23§1-2</t>
         </is>
       </c>
       <c r="G23" s="35" t="inlineStr">
@@ -7926,22 +7938,22 @@
       </c>
       <c r="C24" s="34" t="inlineStr">
         <is>
-          <t>★【必須】在宅A票 訪問診療の設問を問13に直す（問12が重複し問13が欠番）</t>
+          <t>★ニーズ調査 村独自設問14問の採否と頁数（問3(10)の削除・問7(9)の簡素化）</t>
         </is>
       </c>
       <c r="D24" s="34" t="inlineStr">
         <is>
-          <t>★第2稿で訪問診療が復活したが番号が問12となり、今後必要と感じる支援（問12）と重複している。回答者が混乱し集計時に設問を特定できない。9/9の校了までに必ず修正。</t>
+          <t>★標準約66問＋村独自14問＝約79問。仕様書の目安A4約12頁を超える見込み。削除を提案するのは問3(10)「1日に何回食事をとりますか」の1問のみ（低栄養は問3(1)(7)(8)で把握可能）。他13問は施策・交付金の指標と結びついており残すべき。</t>
         </is>
       </c>
       <c r="E24" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-12,Ⅰ-13</t>
         </is>
       </c>
       <c r="F24" s="35" t="inlineStr">
         <is>
-          <t>doc27§3-1</t>
+          <t>doc23§4</t>
         </is>
       </c>
       <c r="G24" s="35" t="inlineStr">
@@ -7964,22 +7976,22 @@
       </c>
       <c r="C25" s="34" t="inlineStr">
         <is>
-          <t>★【必須】在宅A票 問9の基準月を「令和8年8月」に修正</t>
+          <t>★現職の村長名・所管課・役場の住所の確認</t>
         </is>
       </c>
       <c r="D25" s="34" t="inlineStr">
         <is>
-          <t>★問8は修正されたが問9が「令和●年●月」のまま。</t>
+          <t>★第1稿の依頼状に「北塩原村長 遠藤 和夫」「保健福祉課 福祉係」「大字北山字姥ヶ作3151番地」と記載。当方では現職の村長名を確認できない。所管課は住民課との別が未確認のまま（doc01 確認事項1）。</t>
         </is>
       </c>
       <c r="E25" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-14</t>
         </is>
       </c>
       <c r="F25" s="35" t="inlineStr">
         <is>
-          <t>doc27§3-2</t>
+          <t>doc23§5</t>
         </is>
       </c>
       <c r="G25" s="35" t="inlineStr">
@@ -8002,98 +8014,98 @@
       </c>
       <c r="C26" s="34" t="inlineStr">
         <is>
+          <t>★【必須】在宅A票 訪問診療の設問を問13に直す（問12が重複し問13が欠番）</t>
+        </is>
+      </c>
+      <c r="D26" s="34" t="inlineStr">
+        <is>
+          <t>★第2稿で訪問診療が復活したが番号が問12となり、今後必要と感じる支援（問12）と重複している。回答者が混乱し集計時に設問を特定できない。9/9の校了までに必ず修正。</t>
+        </is>
+      </c>
+      <c r="E26" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F26" s="35" t="inlineStr">
+        <is>
+          <t>doc27§3-1</t>
+        </is>
+      </c>
+      <c r="G26" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H26" s="34" t="inlineStr"/>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B27" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C27" s="34" t="inlineStr">
+        <is>
+          <t>★【必須】在宅A票 問9の基準月を「令和8年8月」に修正</t>
+        </is>
+      </c>
+      <c r="D27" s="34" t="inlineStr">
+        <is>
+          <t>★問8は修正されたが問9が「令和●年●月」のまま。</t>
+        </is>
+      </c>
+      <c r="E27" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F27" s="35" t="inlineStr">
+        <is>
+          <t>doc27§3-2</t>
+        </is>
+      </c>
+      <c r="G27" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H27" s="34" t="inlineStr"/>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B28" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C28" s="34" t="inlineStr">
+        <is>
           <t>★【必須】ニーズ 問1(2)① 選択肢14・15を「14．その他／15．不明」に修正</t>
         </is>
       </c>
-      <c r="D26" s="34" t="inlineStr">
+      <c r="D28" s="34" t="inlineStr">
         <is>
           <t>★選択肢の順序の修正7か所のうち、この1か所のみ修正漏れ。標準は13．高齢による衰弱／14．その他（　）／15．不明。</t>
         </is>
       </c>
-      <c r="E26" s="35" t="inlineStr">
+      <c r="E28" s="35" t="inlineStr">
         <is>
           <t>Ⅰ-09</t>
         </is>
       </c>
-      <c r="F26" s="35" t="inlineStr">
+      <c r="F28" s="35" t="inlineStr">
         <is>
           <t>doc27§2-1</t>
-        </is>
-      </c>
-      <c r="G26" s="35" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H26" s="34" t="inlineStr"/>
-    </row>
-    <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="36" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B27" s="33" t="inlineStr">
-        <is>
-          <t>スケジュール</t>
-        </is>
-      </c>
-      <c r="C27" s="34" t="inlineStr">
-        <is>
-          <t>★第2回策定委員会の開催日（11月のいつか）</t>
-        </is>
-      </c>
-      <c r="D27" s="34" t="inlineStr">
-        <is>
-          <t>★資料の事前送付の期限が決まる。素案約90頁を当日配付では読めないため事前送付が前提。</t>
-        </is>
-      </c>
-      <c r="E27" s="35" t="inlineStr">
-        <is>
-          <t>Ⅱ-105</t>
-        </is>
-      </c>
-      <c r="F27" s="35" t="inlineStr">
-        <is>
-          <t>doc26§10 K-95</t>
-        </is>
-      </c>
-      <c r="G27" s="35" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H27" s="34" t="inlineStr"/>
-    </row>
-    <row r="28" ht="34" customHeight="1">
-      <c r="A28" s="36" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B28" s="33" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C28" s="34" t="inlineStr">
-        <is>
-          <t>★給付費適正化「主要3事業の全て実施」が令和7年度6点→令和8年度0点に低下した理由</t>
-        </is>
-      </c>
-      <c r="D28" s="34" t="inlineStr">
-        <is>
-          <t>★全国該当率96.9%の指標。縦覧点検は4帳票満点のため、①要介護認定の適正化 か ②ケアプラン等の点検 のいずれかが実施されなくなった可能性。取組の後退か調査票の記載漏れかで対応が変わる。</t>
-        </is>
-      </c>
-      <c r="E28" s="35" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F28" s="35" t="inlineStr">
-        <is>
-          <t>doc20§8-2 K-61</t>
         </is>
       </c>
       <c r="G28" s="35" t="inlineStr">
@@ -8111,27 +8123,27 @@
       </c>
       <c r="B29" s="33" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>スケジュール</t>
         </is>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>★福祉用具購入費・住宅改修費へのリハビリ専門職の関与（配点8点）が令和7年度8点→令和8年度0点に低下した理由</t>
+          <t>★第2回策定委員会の開催日（11月のいつか）</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>★アと合わせ14点が1年で失われている。仕組みが失われたのか調査票の記載によるものかを確認。</t>
+          <t>★資料の事前送付の期限が決まる。素案約90頁を当日配付では読めないため事前送付が前提。</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-105</t>
         </is>
       </c>
       <c r="F29" s="35" t="inlineStr">
         <is>
-          <t>doc20§8-2 K-61b</t>
+          <t>doc26§10 K-95</t>
         </is>
       </c>
       <c r="G29" s="35" t="inlineStr">
@@ -8154,22 +8166,22 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>認知症サポーター養成数・認知症地域支援推進員の配置と活動内容・チームオレンジの整備予定</t>
+          <t>★給付費適正化「主要3事業の全て実施」が令和7年度6点→令和8年度0点に低下した理由</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>★支援交付金目標Ⅱ（認知症総合支援）は32/100点で全国平均51.1点を19点下回る唯一の目標。3か年で唯一低下局面があった。</t>
+          <t>★全国該当率96.9%の指標。縦覧点検は4帳票満点のため、①要介護認定の適正化 か ②ケアプラン等の点検 のいずれかが実施されなくなった可能性。取組の後退か調査票の記載漏れかで対応が変わる。</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F30" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-62</t>
+          <t>doc20§8-2 K-61</t>
         </is>
       </c>
       <c r="G30" s="35" t="inlineStr">
@@ -8192,22 +8204,22 @@
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入の取組（健診での聴力チェック等）の有無</t>
+          <t>★福祉用具購入費・住宅改修費へのリハビリ専門職の関与（配点8点）が令和7年度8点→令和8年度0点に低下した理由</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>令和8年度評価で配点10点が0点（全国該当率48.8〜68.9%）。保健事業との連携で取得可能。</t>
+          <t>★アと合わせ14点が1年で失われている。仕組みが失われたのか調査票の記載によるものかを確認。</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F31" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-63</t>
+          <t>doc20§8-2 K-61b</t>
         </is>
       </c>
       <c r="G31" s="35" t="inlineStr">
@@ -8230,22 +8242,22 @@
       </c>
       <c r="C32" s="34" t="inlineStr">
         <is>
-          <t>在宅医療・介護連携推進事業の実施体制（村単独か会津圏域か）と課題・対応策の検討の場</t>
+          <t>認知症サポーター養成数・認知症地域支援推進員の配置と活動内容・チームオレンジの整備予定</t>
         </is>
       </c>
       <c r="D32" s="34" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲの「課題・対応策の検討」ア・エが0点（配点計10点、全国該当率57〜72%）。</t>
+          <t>★支援交付金目標Ⅱ（認知症総合支援）は32/100点で全国平均51.1点を19点下回る唯一の目標。3か年で唯一低下局面があった。</t>
         </is>
       </c>
       <c r="E32" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F32" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-64</t>
+          <t>doc20§6-2 K-62</t>
         </is>
       </c>
       <c r="G32" s="35" t="inlineStr">
@@ -8268,22 +8280,22 @@
       </c>
       <c r="C33" s="34" t="inlineStr">
         <is>
-          <t>★施設サービスが伸びない要因「重度化による病院への転院」の裏づけデータ</t>
+          <t>難聴高齢者の早期発見・早期介入の取組（健診での聴力チェック等）の有無</t>
         </is>
       </c>
       <c r="D33" s="34" t="inlineStr">
         <is>
-          <t>★議事録で示された村の見解。当方は村内施設ゼロ・村外施設依存の文脈で解釈していたため、素案の記述を修正する必要がある。KDB・給付実績で確認したい。</t>
+          <t>令和8年度評価で配点10点が0点（全国該当率48.8〜68.9%）。保健事業との連携で取得可能。</t>
         </is>
       </c>
       <c r="E33" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F33" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-75</t>
+          <t>doc20§6-2 K-63</t>
         </is>
       </c>
       <c r="G33" s="35" t="inlineStr">
@@ -8306,22 +8318,22 @@
       </c>
       <c r="C34" s="34" t="inlineStr">
         <is>
-          <t>★要介護認定データの提供時期と項目（要介護度・認定日・サービス利用状況）</t>
+          <t>在宅医療・介護連携推進事業の実施体制（村単独か会津圏域か）と課題・対応策の検討の場</t>
         </is>
       </c>
       <c r="D34" s="34" t="inlineStr">
         <is>
-          <t>★仕様書4Ⅰ(5)。ICF分析の「認定状況×生活機能リスク」表と在宅調査のクロスに必須。目的外利用の手続きの確認を含む。議事録の「元気な軽度者が総合事業を利用している」の検証はこの紐付けでしかできない。</t>
+          <t>支援交付金目標Ⅲの「課題・対応策の検討」ア・エが0点（配点計10点、全国該当率57〜72%）。</t>
         </is>
       </c>
       <c r="E34" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-37</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F34" s="35" t="inlineStr">
         <is>
-          <t>doc24§12 K-87</t>
+          <t>doc20§6-2 K-64</t>
         </is>
       </c>
       <c r="G34" s="35" t="inlineStr">
@@ -8339,27 +8351,27 @@
       </c>
       <c r="B35" s="33" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C35" s="34" t="inlineStr">
         <is>
-          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
+          <t>★施設サービスが伸びない要因「重度化による病院への転院」の裏づけデータ</t>
         </is>
       </c>
       <c r="D35" s="34" t="inlineStr">
         <is>
-          <t>連絡体制表の確定。第9期概要版の発行は住民課。</t>
+          <t>★議事録で示された村の見解。当方は村内施設ゼロ・村外施設依存の文脈で解釈していたため、素案の記述を修正する必要がある。KDB・給付実績で確認したい。</t>
         </is>
       </c>
       <c r="E35" s="35" t="inlineStr">
         <is>
-          <t>０-04</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F35" s="35" t="inlineStr">
         <is>
-          <t>doc01-1</t>
+          <t>doc22 K-75</t>
         </is>
       </c>
       <c r="G35" s="35" t="inlineStr">
@@ -8377,27 +8389,27 @@
       </c>
       <c r="B36" s="33" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C36" s="34" t="inlineStr">
         <is>
-          <t>契約締結日・契約書の取り交わし状況</t>
+          <t>★要介護認定データの提供時期と項目（要介護度・認定日・サービス利用状況）</t>
         </is>
       </c>
       <c r="D36" s="34" t="inlineStr">
         <is>
-          <t>業務開始日の確定。</t>
+          <t>★仕様書4Ⅰ(5)。ICF分析の「認定状況×生活機能リスク」表と在宅調査のクロスに必須。目的外利用の手続きの確認を含む。議事録の「元気な軽度者が総合事業を利用している」の検証はこの紐付けでしかできない。</t>
         </is>
       </c>
       <c r="E36" s="35" t="inlineStr">
         <is>
-          <t>０-02</t>
+          <t>Ⅰ-37</t>
         </is>
       </c>
       <c r="F36" s="35" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>doc24§12 K-87</t>
         </is>
       </c>
       <c r="G36" s="35" t="inlineStr">
@@ -8415,27 +8427,27 @@
       </c>
       <c r="B37" s="33" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C37" s="34" t="inlineStr">
         <is>
-          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
+          <t>★会津権利擁護・成年後見センターへの相談が1年で件数−43%・時間−55%と減少した要因</t>
         </is>
       </c>
       <c r="D37" s="34" t="inlineStr">
         <is>
-          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
+          <t>★令和6年度134件・1,625分→令和7年度76件・729分。圏域13市町村の総計は増加しているなかで本村のみ大きく減少。施策評価に必要。</t>
         </is>
       </c>
       <c r="E37" s="35" t="inlineStr">
         <is>
-          <t>０-06</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F37" s="35" t="inlineStr">
         <is>
-          <t>doc19 追-12</t>
+          <t>doc28§3-3 K-108</t>
         </is>
       </c>
       <c r="G37" s="35" t="inlineStr">
@@ -8458,22 +8470,22 @@
       </c>
       <c r="C38" s="34" t="inlineStr">
         <is>
-          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
+          <t>契約締結日・契約書の取り交わし状況</t>
         </is>
       </c>
       <c r="D38" s="34" t="inlineStr">
         <is>
-          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
+          <t>業務開始日の確定。</t>
         </is>
       </c>
       <c r="E38" s="35" t="inlineStr">
         <is>
-          <t>Ⅴ-96</t>
+          <t>０-02</t>
         </is>
       </c>
       <c r="F38" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-78</t>
+          <t>―</t>
         </is>
       </c>
       <c r="G38" s="35" t="inlineStr">
@@ -8496,22 +8508,22 @@
       </c>
       <c r="C39" s="34" t="inlineStr">
         <is>
-          <t>自由記述の匿名化の方針（削除・置換の範囲）</t>
+          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
         </is>
       </c>
       <c r="D39" s="34" t="inlineStr">
         <is>
-          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。</t>
+          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
         </is>
       </c>
       <c r="E39" s="35" t="inlineStr">
         <is>
-          <t>Ⅴ-96</t>
+          <t>０-06</t>
         </is>
       </c>
       <c r="F39" s="35" t="inlineStr">
         <is>
-          <t>doc24§12 K-89</t>
+          <t>doc19 追-12</t>
         </is>
       </c>
       <c r="G39" s="35" t="inlineStr">
@@ -8534,22 +8546,22 @@
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>第2回策定委員会の資料の事前送付の可否と時期</t>
+          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>素案（完成度7割・約90頁）は別冊として事前送付する前提で資料を設計している。</t>
+          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-105</t>
+          <t>Ⅴ-96</t>
         </is>
       </c>
       <c r="F40" s="35" t="inlineStr">
         <is>
-          <t>doc26§10 K-97</t>
+          <t>doc22 K-78</t>
         </is>
       </c>
       <c r="G40" s="35" t="inlineStr">
@@ -8567,27 +8579,27 @@
       </c>
       <c r="B41" s="33" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C41" s="34" t="inlineStr">
         <is>
-          <t>ICF分析は標準設問のみで完結することの確認</t>
+          <t>自由記述の匿名化の方針（削除・置換の範囲）</t>
         </is>
       </c>
       <c r="D41" s="34" t="inlineStr">
         <is>
-          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
+          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。</t>
         </is>
       </c>
       <c r="E41" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-50</t>
+          <t>Ⅴ-96</t>
         </is>
       </c>
       <c r="F41" s="35" t="inlineStr">
         <is>
-          <t>doc23§3-4</t>
+          <t>doc24§12 K-89</t>
         </is>
       </c>
       <c r="G41" s="35" t="inlineStr">
@@ -8605,27 +8617,27 @@
       </c>
       <c r="B42" s="33" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C42" s="34" t="inlineStr">
         <is>
-          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
+          <t>第2回策定委員会の資料の事前送付の可否と時期</t>
         </is>
       </c>
       <c r="D42" s="34" t="inlineStr">
         <is>
-          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
+          <t>素案（完成度7割・約90頁）は別冊として事前送付する前提で資料を設計している。</t>
         </is>
       </c>
       <c r="E42" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅱ-105</t>
         </is>
       </c>
       <c r="F42" s="35" t="inlineStr">
         <is>
-          <t>doc24§12 K-86</t>
+          <t>doc26§10 K-97</t>
         </is>
       </c>
       <c r="G42" s="35" t="inlineStr">
@@ -8648,22 +8660,22 @@
       </c>
       <c r="C43" s="34" t="inlineStr">
         <is>
-          <t>★リスク判定10種の該当基準（見える化システムの算出方法との突合）</t>
+          <t>ICF分析は標準設問のみで完結することの確認</t>
         </is>
       </c>
       <c r="D43" s="34" t="inlineStr">
         <is>
-          <t>★手引きに該当基準の明記があるのはBMI 18.5以下のみ。他9種は基本チェックリストに準じた案を置いているが、独自基準では全国・県と比較できない。手引きは算出方法が将来更新され得るとも記載しており、第9期の基準の流用も不可。</t>
+          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
         </is>
       </c>
       <c r="E43" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-46</t>
+          <t>Ⅰ-50</t>
         </is>
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>doc25§4-2 K-91</t>
+          <t>doc23§3-4</t>
         </is>
       </c>
       <c r="G43" s="35" t="inlineStr">
@@ -8681,27 +8693,27 @@
       </c>
       <c r="B44" s="33" t="inlineStr">
         <is>
-          <t>委員会</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C44" s="34" t="inlineStr">
         <is>
-          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
+          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
         </is>
       </c>
       <c r="D44" s="34" t="inlineStr">
         <is>
-          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
+          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
         </is>
       </c>
       <c r="E44" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-80,Ⅱ-81</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F44" s="35" t="inlineStr">
         <is>
-          <t>doc01-6,doc19 追-15</t>
+          <t>doc24§12 K-86</t>
         </is>
       </c>
       <c r="G44" s="35" t="inlineStr">
@@ -8719,27 +8731,27 @@
       </c>
       <c r="B45" s="33" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C45" s="34" t="inlineStr">
         <is>
-          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
+          <t>★リスク判定10種の該当基準（見える化システムの算出方法との突合）</t>
         </is>
       </c>
       <c r="D45" s="34" t="inlineStr">
         <is>
-          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
+          <t>★手引きに該当基準の明記があるのはBMI 18.5以下のみ。他9種は基本チェックリストに準じた案を置いているが、独自基準では全国・県と比較できない。手引きは算出方法が将来更新され得るとも記載しており、第9期の基準の流用も不可。</t>
         </is>
       </c>
       <c r="E45" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-76,Ⅱ-77</t>
+          <t>Ⅰ-46</t>
         </is>
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>doc01-7,doc19 指-3</t>
+          <t>doc25§4-2 K-91</t>
         </is>
       </c>
       <c r="G45" s="35" t="inlineStr">
@@ -8757,27 +8769,27 @@
       </c>
       <c r="B46" s="33" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>委員会</t>
         </is>
       </c>
       <c r="C46" s="34" t="inlineStr">
         <is>
-          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
+          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
         </is>
       </c>
       <c r="D46" s="34" t="inlineStr">
         <is>
-          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
+          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
         </is>
       </c>
       <c r="E46" s="35" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅱ-80,Ⅱ-81</t>
         </is>
       </c>
       <c r="F46" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-79</t>
+          <t>doc01-6,doc19 追-15</t>
         </is>
       </c>
       <c r="G46" s="35" t="inlineStr">
@@ -8795,27 +8807,27 @@
       </c>
       <c r="B47" s="33" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C47" s="34" t="inlineStr">
         <is>
-          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
+          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
         </is>
       </c>
       <c r="D47" s="34" t="inlineStr">
         <is>
-          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
+          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
         </is>
       </c>
       <c r="E47" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-76,Ⅱ-77</t>
         </is>
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-66</t>
+          <t>doc01-7,doc19 指-3</t>
         </is>
       </c>
       <c r="G47" s="35" t="inlineStr">
@@ -8833,27 +8845,27 @@
       </c>
       <c r="B48" s="33" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C48" s="34" t="inlineStr">
         <is>
-          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
+          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
         </is>
       </c>
       <c r="D48" s="34" t="inlineStr">
         <is>
-          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
+          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
         </is>
       </c>
       <c r="E48" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-62</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F48" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-81</t>
+          <t>doc22 K-79</t>
         </is>
       </c>
       <c r="G48" s="35" t="inlineStr">
@@ -8876,22 +8888,22 @@
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
+          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
+          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-70</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F49" s="35" t="inlineStr">
         <is>
-          <t>doc26§10 K-98</t>
+          <t>doc20§6-2 K-66</t>
         </is>
       </c>
       <c r="G49" s="35" t="inlineStr">
@@ -8914,22 +8926,22 @@
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
+          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。</t>
+          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-62</t>
         </is>
       </c>
       <c r="F50" s="35" t="inlineStr">
         <is>
-          <t>doc26§10 K-99</t>
+          <t>doc22 K-81</t>
         </is>
       </c>
       <c r="G50" s="35" t="inlineStr">
@@ -8947,27 +8959,27 @@
       </c>
       <c r="B51" s="33" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
+          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
+          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-70</t>
         </is>
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>doc21§5 K-69</t>
+          <t>doc26§10 K-98</t>
         </is>
       </c>
       <c r="G51" s="35" t="inlineStr">
@@ -8985,27 +8997,27 @@
       </c>
       <c r="B52" s="33" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C52" s="34" t="inlineStr">
         <is>
-          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
+          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
         </is>
       </c>
       <c r="D52" s="34" t="inlineStr">
         <is>
-          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
+          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。</t>
         </is>
       </c>
       <c r="E52" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F52" s="35" t="inlineStr">
         <is>
-          <t>doc21§5 K-70</t>
+          <t>doc26§10 K-99</t>
         </is>
       </c>
       <c r="G52" s="35" t="inlineStr">
@@ -9023,32 +9035,32 @@
       </c>
       <c r="B53" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C53" s="34" t="inlineStr">
         <is>
-          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
+          <t>補正係数を①3区分と②前期・後期高齢者別のどちらで用いるか</t>
         </is>
       </c>
       <c r="D53" s="34" t="inlineStr">
         <is>
-          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
+          <t>国は小規模保険者では①の係数が不安定になるため②の選択を勧めている。本村の85歳以上は200人で係数0.03（差6人）と1人の増減の影響が大きい。当方は②を提案。</t>
         </is>
       </c>
       <c r="E53" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-19,Ⅰ-25</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc28§1-2 K-107</t>
         </is>
       </c>
       <c r="G53" s="35" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H53" s="34" t="inlineStr"/>
@@ -9061,27 +9073,27 @@
       </c>
       <c r="B54" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C54" s="34" t="inlineStr">
         <is>
-          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
+          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
         </is>
       </c>
       <c r="D54" s="34" t="inlineStr">
         <is>
-          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
+          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
         </is>
       </c>
       <c r="E54" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-09,Ⅰ-10</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F54" s="35" t="inlineStr">
         <is>
-          <t>doc27§3-3</t>
+          <t>doc21§5 K-69</t>
         </is>
       </c>
       <c r="G54" s="35" t="inlineStr">
@@ -9099,27 +9111,27 @@
       </c>
       <c r="B55" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C55" s="34" t="inlineStr">
         <is>
-          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
+          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
         </is>
       </c>
       <c r="D55" s="34" t="inlineStr">
         <is>
-          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
+          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
         </is>
       </c>
       <c r="E55" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-09,Ⅰ-10</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>doc27§5-2</t>
+          <t>doc21§5 K-70</t>
         </is>
       </c>
       <c r="G55" s="35" t="inlineStr">
@@ -9137,27 +9149,27 @@
       </c>
       <c r="B56" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C56" s="34" t="inlineStr">
         <is>
-          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
         </is>
       </c>
       <c r="D56" s="34" t="inlineStr">
         <is>
-          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
         </is>
       </c>
       <c r="E56" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F56" s="35" t="inlineStr">
         <is>
-          <t>doc27§5-3</t>
+          <t>doc28§3-4 K-111</t>
         </is>
       </c>
       <c r="G56" s="35" t="inlineStr">
@@ -9180,182 +9192,182 @@
       </c>
       <c r="C57" s="34" t="inlineStr">
         <is>
+          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
+        </is>
+      </c>
+      <c r="D57" s="34" t="inlineStr">
+        <is>
+          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
+        </is>
+      </c>
+      <c r="E57" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-19,Ⅰ-25</t>
+        </is>
+      </c>
+      <c r="F57" s="35" t="inlineStr">
+        <is>
+          <t>doc22 §1</t>
+        </is>
+      </c>
+      <c r="G57" s="35" t="inlineStr">
+        <is>
+          <t>一部回答</t>
+        </is>
+      </c>
+      <c r="H57" s="34" t="inlineStr"/>
+    </row>
+    <row r="58" ht="34" customHeight="1">
+      <c r="A58" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B58" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C58" s="34" t="inlineStr">
+        <is>
+          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
+        </is>
+      </c>
+      <c r="D58" s="34" t="inlineStr">
+        <is>
+          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
+        </is>
+      </c>
+      <c r="E58" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-09,Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F58" s="35" t="inlineStr">
+        <is>
+          <t>doc27§3-3</t>
+        </is>
+      </c>
+      <c r="G58" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H58" s="34" t="inlineStr"/>
+    </row>
+    <row r="59" ht="34" customHeight="1">
+      <c r="A59" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B59" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C59" s="34" t="inlineStr">
+        <is>
+          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
+        </is>
+      </c>
+      <c r="D59" s="34" t="inlineStr">
+        <is>
+          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
+        </is>
+      </c>
+      <c r="E59" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-09,Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F59" s="35" t="inlineStr">
+        <is>
+          <t>doc27§5-2</t>
+        </is>
+      </c>
+      <c r="G59" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H59" s="34" t="inlineStr"/>
+    </row>
+    <row r="60" ht="34" customHeight="1">
+      <c r="A60" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B60" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C60" s="34" t="inlineStr">
+        <is>
+          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+        </is>
+      </c>
+      <c r="D60" s="34" t="inlineStr">
+        <is>
+          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+        </is>
+      </c>
+      <c r="E60" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F60" s="35" t="inlineStr">
+        <is>
+          <t>doc27§5-3</t>
+        </is>
+      </c>
+      <c r="G60" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H60" s="34" t="inlineStr"/>
+    </row>
+    <row r="61" ht="34" customHeight="1">
+      <c r="A61" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B61" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C61" s="34" t="inlineStr">
+        <is>
           <t>調査票のレイアウトの目視確認3点（幸福度の記入欄／宛名ラベル枠／頁数）</t>
         </is>
       </c>
-      <c r="D57" s="34" t="inlineStr">
+      <c r="D61" s="34" t="inlineStr">
         <is>
           <t>★当方の環境ではdocxからPDFへの変換ができずレイアウトを確認できない。ニーズ問8(2)の記入枠、表紙から削除された宛名ラベル枠と「第10期」表記、ルビ追加による頁数の増加を村側でご確認いただきたい。</t>
         </is>
       </c>
-      <c r="E57" s="35" t="inlineStr">
+      <c r="E61" s="35" t="inlineStr">
         <is>
           <t>Ⅰ-20</t>
         </is>
       </c>
-      <c r="F57" s="35" t="inlineStr">
+      <c r="F61" s="35" t="inlineStr">
         <is>
           <t>doc27§6</t>
         </is>
       </c>
-      <c r="G57" s="35" t="inlineStr">
+      <c r="G61" s="35" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H57" s="34" t="inlineStr"/>
-    </row>
-    <row r="58" ht="34" customHeight="1">
-      <c r="A58" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B58" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C58" s="25" t="inlineStr">
-        <is>
-          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
-        </is>
-      </c>
-      <c r="D58" s="25" t="inlineStr">
-        <is>
-          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
-        </is>
-      </c>
-      <c r="E58" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F58" s="23" t="inlineStr">
-        <is>
-          <t>doc02§22,doc08§8</t>
-        </is>
-      </c>
-      <c r="G58" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H58" s="25" t="inlineStr"/>
-    </row>
-    <row r="59" ht="34" customHeight="1">
-      <c r="A59" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B59" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C59" s="25" t="inlineStr">
-        <is>
-          <t>令和6年度決算および令和7年度の給付費見込</t>
-        </is>
-      </c>
-      <c r="D59" s="25" t="inlineStr">
-        <is>
-          <t>第9期の計画値と実績の乖離を確定させるために必要。</t>
-        </is>
-      </c>
-      <c r="E59" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
-        </is>
-      </c>
-      <c r="F59" s="23" t="inlineStr">
-        <is>
-          <t>doc08§8-1</t>
-        </is>
-      </c>
-      <c r="G59" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H59" s="25" t="inlineStr"/>
-    </row>
-    <row r="60" ht="34" customHeight="1">
-      <c r="A60" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B60" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C60" s="25" t="inlineStr">
-        <is>
-          <t>通いの場の実数（令和3〜7年度）</t>
-        </is>
-      </c>
-      <c r="D60" s="25" t="inlineStr">
-        <is>
-          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。</t>
-        </is>
-      </c>
-      <c r="E60" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F60" s="23" t="inlineStr">
-        <is>
-          <t>doc02§16,§22</t>
-        </is>
-      </c>
-      <c r="G60" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H60" s="25" t="inlineStr"/>
-    </row>
-    <row r="61" ht="34" customHeight="1">
-      <c r="A61" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B61" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C61" s="25" t="inlineStr">
-        <is>
-          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
-        </is>
-      </c>
-      <c r="D61" s="25" t="inlineStr">
-        <is>
-          <t>見える化に該当データがない。第9期は基本目標4-4に位置づけ。</t>
-        </is>
-      </c>
-      <c r="E61" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-68,Ⅱ-69</t>
-        </is>
-      </c>
-      <c r="F61" s="23" t="inlineStr">
-        <is>
-          <t>doc08§8-5</t>
-        </is>
-      </c>
-      <c r="G61" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H61" s="25" t="inlineStr"/>
+      <c r="H61" s="34" t="inlineStr"/>
     </row>
     <row r="62" ht="34" customHeight="1">
       <c r="A62" s="37" t="inlineStr">
@@ -9370,22 +9382,22 @@
       </c>
       <c r="C62" s="25" t="inlineStr">
         <is>
-          <t>高齢者福祉事業（村単独事業）の実績資料</t>
+          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
         </is>
       </c>
       <c r="D62" s="25" t="inlineStr">
         <is>
-          <t>現行計画の評価に必要。</t>
+          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
         </is>
       </c>
       <c r="E62" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F62" s="23" t="inlineStr">
         <is>
-          <t>doc01-11</t>
+          <t>doc02§22,doc08§8</t>
         </is>
       </c>
       <c r="G62" s="23" t="inlineStr">
@@ -9408,22 +9420,22 @@
       </c>
       <c r="C63" s="25" t="inlineStr">
         <is>
-          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
+          <t>令和6年度決算および令和7年度の給付費見込</t>
         </is>
       </c>
       <c r="D63" s="25" t="inlineStr">
         <is>
-          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
+          <t>第9期の計画値と実績の乖離を確定させるために必要。</t>
         </is>
       </c>
       <c r="E63" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-58,Ⅱ-59</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-9</t>
+          <t>doc08§8-1</t>
         </is>
       </c>
       <c r="G63" s="23" t="inlineStr">
@@ -9446,22 +9458,22 @@
       </c>
       <c r="C64" s="25" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告（月報・年報）の原データの提供可否</t>
+          <t>通いの場の実数（令和3〜7年度）</t>
         </is>
       </c>
       <c r="D64" s="25" t="inlineStr">
         <is>
-          <t>見える化に収録されていない項目（サービス種類別利用者数の月次推移等）が扱えるようになる。</t>
+          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。</t>
         </is>
       </c>
       <c r="E64" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F64" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-10</t>
+          <t>doc02§16,§22</t>
         </is>
       </c>
       <c r="G64" s="23" t="inlineStr">
@@ -9484,22 +9496,22 @@
       </c>
       <c r="C65" s="25" t="inlineStr">
         <is>
-          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
+          <t>高齢者福祉事業（村単独事業）の実績資料</t>
         </is>
       </c>
       <c r="D65" s="25" t="inlineStr">
         <is>
-          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
+          <t>現行計画の評価に必要。</t>
         </is>
       </c>
       <c r="E65" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc01-11</t>
         </is>
       </c>
       <c r="G65" s="23" t="inlineStr">
@@ -9522,22 +9534,22 @@
       </c>
       <c r="C66" s="25" t="inlineStr">
         <is>
-          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
+          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
         </is>
       </c>
       <c r="D66" s="25" t="inlineStr">
         <is>
-          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
+          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
         </is>
       </c>
       <c r="E66" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-58,Ⅱ-59</t>
         </is>
       </c>
       <c r="F66" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc19 追-9</t>
         </is>
       </c>
       <c r="G66" s="23" t="inlineStr">
@@ -9560,22 +9572,22 @@
       </c>
       <c r="C67" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
+          <t>介護保険事業状況報告（月報・年報）の原データの提供可否</t>
         </is>
       </c>
       <c r="D67" s="25" t="inlineStr">
         <is>
-          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
+          <t>見える化に収録されていない項目（サービス種類別利用者数の月次推移等）が扱えるようになる。</t>
         </is>
       </c>
       <c r="E67" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc19 追-10</t>
         </is>
       </c>
       <c r="G67" s="23" t="inlineStr">
@@ -9598,12 +9610,12 @@
       </c>
       <c r="C68" s="25" t="inlineStr">
         <is>
-          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
+          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
         </is>
       </c>
       <c r="D68" s="25" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
+          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
         </is>
       </c>
       <c r="E68" s="23" t="inlineStr">
@@ -9613,7 +9625,7 @@
       </c>
       <c r="F68" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-65</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G68" s="23" t="inlineStr">
@@ -9636,22 +9648,22 @@
       </c>
       <c r="C69" s="25" t="inlineStr">
         <is>
-          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
+          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
         </is>
       </c>
       <c r="D69" s="25" t="inlineStr">
         <is>
-          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
+          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
         </is>
       </c>
       <c r="E69" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F69" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-68</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G69" s="23" t="inlineStr">
@@ -9674,22 +9686,22 @@
       </c>
       <c r="C70" s="25" t="inlineStr">
         <is>
-          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
+          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
         </is>
       </c>
       <c r="D70" s="25" t="inlineStr">
         <is>
-          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
+          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
         </is>
       </c>
       <c r="E70" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F70" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-71</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G70" s="23" t="inlineStr">
@@ -9712,22 +9724,22 @@
       </c>
       <c r="C71" s="25" t="inlineStr">
         <is>
-          <t>シルバー人材センターの会員数・受注実績</t>
+          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
         </is>
       </c>
       <c r="D71" s="25" t="inlineStr">
         <is>
-          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
+          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
         </is>
       </c>
       <c r="E71" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-72</t>
+          <t>doc20§6-2 K-65</t>
         </is>
       </c>
       <c r="G71" s="23" t="inlineStr">
@@ -9750,22 +9762,22 @@
       </c>
       <c r="C72" s="25" t="inlineStr">
         <is>
-          <t>第9期調査の集計基準・集計表の提供</t>
+          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
         </is>
       </c>
       <c r="D72" s="25" t="inlineStr">
         <is>
-          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
+          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
         </is>
       </c>
       <c r="E72" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F72" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-92</t>
+          <t>doc21§5 K-68</t>
         </is>
       </c>
       <c r="G72" s="23" t="inlineStr">
@@ -9783,27 +9795,27 @@
       </c>
       <c r="B73" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C73" s="25" t="inlineStr">
         <is>
-          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
+          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
         </is>
       </c>
       <c r="D73" s="25" t="inlineStr">
         <is>
-          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
+          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
         </is>
       </c>
       <c r="E73" s="23" t="inlineStr">
         <is>
-          <t>Ⅴ-95</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F73" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-67</t>
+          <t>doc21§5 K-71</t>
         </is>
       </c>
       <c r="G73" s="23" t="inlineStr">
@@ -9821,27 +9833,27 @@
       </c>
       <c r="B74" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C74" s="25" t="inlineStr">
         <is>
-          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
+          <t>シルバー人材センターの会員数・受注実績</t>
         </is>
       </c>
       <c r="D74" s="25" t="inlineStr">
         <is>
-          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
+          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
         </is>
       </c>
       <c r="E74" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-35</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F74" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-93</t>
+          <t>doc21§5 K-72</t>
         </is>
       </c>
       <c r="G74" s="23" t="inlineStr">
@@ -9859,27 +9871,27 @@
       </c>
       <c r="B75" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C75" s="25" t="inlineStr">
         <is>
-          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
+          <t>第9期調査の集計基準・集計表の提供</t>
         </is>
       </c>
       <c r="D75" s="25" t="inlineStr">
         <is>
-          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
+          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
         </is>
       </c>
       <c r="E75" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-48</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F75" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-94</t>
+          <t>doc25§8 K-92</t>
         </is>
       </c>
       <c r="G75" s="23" t="inlineStr">
@@ -9897,27 +9909,27 @@
       </c>
       <c r="B76" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C76" s="25" t="inlineStr">
         <is>
-          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
+          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
         </is>
       </c>
       <c r="D76" s="25" t="inlineStr">
         <is>
-          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
+          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
         </is>
       </c>
       <c r="E76" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F76" s="23" t="inlineStr">
         <is>
-          <t>doc19 指-5</t>
+          <t>doc28§3-4 K-109</t>
         </is>
       </c>
       <c r="G76" s="23" t="inlineStr">
@@ -9935,27 +9947,27 @@
       </c>
       <c r="B77" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C77" s="25" t="inlineStr">
         <is>
-          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
+          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
         </is>
       </c>
       <c r="D77" s="25" t="inlineStr">
         <is>
-          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
+          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
         </is>
       </c>
       <c r="E77" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-108</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F77" s="23" t="inlineStr">
         <is>
-          <t>doc22 K-80</t>
+          <t>doc28§2 K-110</t>
         </is>
       </c>
       <c r="G77" s="23" t="inlineStr">
@@ -9973,27 +9985,27 @@
       </c>
       <c r="B78" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C78" s="25" t="inlineStr">
         <is>
-          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
+          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
         </is>
       </c>
       <c r="D78" s="25" t="inlineStr">
         <is>
-          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
+          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
         </is>
       </c>
       <c r="E78" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-90</t>
+          <t>Ⅴ-95</t>
         </is>
       </c>
       <c r="F78" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-88</t>
+          <t>doc20§6-2 K-67</t>
         </is>
       </c>
       <c r="G78" s="23" t="inlineStr">
@@ -10011,27 +10023,27 @@
       </c>
       <c r="B79" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C79" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
+          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
         </is>
       </c>
       <c r="D79" s="25" t="inlineStr">
         <is>
-          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
+          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
         </is>
       </c>
       <c r="E79" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅰ-35</t>
         </is>
       </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
-          <t>doc09§4,§10</t>
+          <t>doc25§8 K-93</t>
         </is>
       </c>
       <c r="G79" s="23" t="inlineStr">
@@ -10049,27 +10061,27 @@
       </c>
       <c r="B80" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C80" s="25" t="inlineStr">
         <is>
-          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
+          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
         </is>
       </c>
       <c r="D80" s="25" t="inlineStr">
         <is>
-          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
+          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
         </is>
       </c>
       <c r="E80" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅰ-48</t>
         </is>
       </c>
       <c r="F80" s="23" t="inlineStr">
         <is>
-          <t>doc09§8,§10</t>
+          <t>doc25§8 K-94</t>
         </is>
       </c>
       <c r="G80" s="23" t="inlineStr">
@@ -10087,27 +10099,27 @@
       </c>
       <c r="B81" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C81" s="25" t="inlineStr">
         <is>
-          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
+          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
         </is>
       </c>
       <c r="D81" s="25" t="inlineStr">
         <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
+          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
         </is>
       </c>
       <c r="E81" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t>doc02§17,doc07,doc18 4-1</t>
+          <t>doc19 指-5</t>
         </is>
       </c>
       <c r="G81" s="23" t="inlineStr">
@@ -10125,27 +10137,27 @@
       </c>
       <c r="B82" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C82" s="25" t="inlineStr">
         <is>
-          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
+          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
         </is>
       </c>
       <c r="D82" s="25" t="inlineStr">
         <is>
-          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
+          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
         </is>
       </c>
       <c r="E82" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-75</t>
+          <t>Ⅱ-108</t>
         </is>
       </c>
       <c r="F82" s="23" t="inlineStr">
         <is>
-          <t>doc17 C-1,doc02§20-2</t>
+          <t>doc22 K-80</t>
         </is>
       </c>
       <c r="G82" s="23" t="inlineStr">
@@ -10163,27 +10175,27 @@
       </c>
       <c r="B83" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C83" s="25" t="inlineStr">
         <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
         </is>
       </c>
       <c r="D83" s="25" t="inlineStr">
         <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
         </is>
       </c>
       <c r="E83" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
+          <t>Ⅳ-90</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t>doc13§6</t>
+          <t>doc24§12 K-88</t>
         </is>
       </c>
       <c r="G83" s="23" t="inlineStr">
@@ -10206,22 +10218,22 @@
       </c>
       <c r="C84" s="25" t="inlineStr">
         <is>
-          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
         </is>
       </c>
       <c r="D84" s="25" t="inlineStr">
         <is>
-          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
+          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
         </is>
       </c>
       <c r="E84" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F84" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-14</t>
+          <t>doc09§4,§10</t>
         </is>
       </c>
       <c r="G84" s="23" t="inlineStr">
@@ -10244,22 +10256,22 @@
       </c>
       <c r="C85" s="25" t="inlineStr">
         <is>
-          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
         </is>
       </c>
       <c r="D85" s="25" t="inlineStr">
         <is>
-          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
         </is>
       </c>
       <c r="E85" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t>doc19 §3</t>
+          <t>doc09§8,§10</t>
         </is>
       </c>
       <c r="G85" s="23" t="inlineStr">
@@ -10282,22 +10294,22 @@
       </c>
       <c r="C86" s="25" t="inlineStr">
         <is>
-          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
+          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
         </is>
       </c>
       <c r="D86" s="25" t="inlineStr">
         <is>
-          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
         </is>
       </c>
       <c r="E86" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F86" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-73</t>
+          <t>doc02§17,doc07,doc18 4-1</t>
         </is>
       </c>
       <c r="G86" s="23" t="inlineStr">
@@ -10320,22 +10332,22 @@
       </c>
       <c r="C87" s="25" t="inlineStr">
         <is>
-          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
         </is>
       </c>
       <c r="D87" s="25" t="inlineStr">
         <is>
-          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
         </is>
       </c>
       <c r="E87" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-105</t>
+          <t>Ⅱ-56,Ⅱ-75</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-90</t>
+          <t>doc17 C-1,doc02§20-2</t>
         </is>
       </c>
       <c r="G87" s="23" t="inlineStr">
@@ -10353,27 +10365,27 @@
       </c>
       <c r="B88" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C88" s="25" t="inlineStr">
         <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
         </is>
       </c>
       <c r="D88" s="25" t="inlineStr">
         <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
         </is>
       </c>
       <c r="E88" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-60,Ⅱ-65</t>
         </is>
       </c>
       <c r="F88" s="23" t="inlineStr">
         <is>
-          <t>doc07§4</t>
+          <t>doc13§6</t>
         </is>
       </c>
       <c r="G88" s="23" t="inlineStr">
@@ -10391,27 +10403,27 @@
       </c>
       <c r="B89" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C89" s="25" t="inlineStr">
         <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
         </is>
       </c>
       <c r="D89" s="25" t="inlineStr">
         <is>
-          <t>評価指標の読み方に影響。</t>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
         </is>
       </c>
       <c r="E89" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t>doc07§8-4</t>
+          <t>doc19 追-14</t>
         </is>
       </c>
       <c r="G89" s="23" t="inlineStr">
@@ -10429,27 +10441,27 @@
       </c>
       <c r="B90" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C90" s="25" t="inlineStr">
         <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
         </is>
       </c>
       <c r="D90" s="25" t="inlineStr">
         <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
         </is>
       </c>
       <c r="E90" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F90" s="23" t="inlineStr">
         <is>
-          <t>doc08§4,§8-2</t>
+          <t>doc19 §3</t>
         </is>
       </c>
       <c r="G90" s="23" t="inlineStr">
@@ -10467,27 +10479,27 @@
       </c>
       <c r="B91" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C91" s="25" t="inlineStr">
         <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
         </is>
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t>doc02§20-1</t>
+          <t>doc21§5 K-73</t>
         </is>
       </c>
       <c r="G91" s="23" t="inlineStr">
@@ -10505,27 +10517,27 @@
       </c>
       <c r="B92" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C92" s="25" t="inlineStr">
         <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
         </is>
       </c>
       <c r="D92" s="25" t="inlineStr">
         <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
         </is>
       </c>
       <c r="E92" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-105</t>
         </is>
       </c>
       <c r="F92" s="23" t="inlineStr">
         <is>
-          <t>doc15,doc18</t>
+          <t>doc24§12 K-90</t>
         </is>
       </c>
       <c r="G92" s="23" t="inlineStr">
@@ -10543,27 +10555,27 @@
       </c>
       <c r="B93" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C93" s="25" t="inlineStr">
         <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
         </is>
       </c>
       <c r="D93" s="25" t="inlineStr">
         <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
         </is>
       </c>
       <c r="E93" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc18 3-1</t>
+          <t>doc07§4</t>
         </is>
       </c>
       <c r="G93" s="23" t="inlineStr">
@@ -10581,27 +10593,27 @@
       </c>
       <c r="B94" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C94" s="25" t="inlineStr">
         <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
         </is>
       </c>
       <c r="D94" s="25" t="inlineStr">
         <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+          <t>評価指標の読み方に影響。</t>
         </is>
       </c>
       <c r="E94" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F94" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
+          <t>doc07§8-4</t>
         </is>
       </c>
       <c r="G94" s="23" t="inlineStr">
@@ -10619,27 +10631,27 @@
       </c>
       <c r="B95" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C95" s="25" t="inlineStr">
         <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
         </is>
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
         </is>
       </c>
       <c r="E95" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t>doc17 B-3,doc18 4-3</t>
+          <t>doc08§4,§8-2</t>
         </is>
       </c>
       <c r="G95" s="23" t="inlineStr">
@@ -10657,27 +10669,27 @@
       </c>
       <c r="B96" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C96" s="25" t="inlineStr">
         <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
         </is>
       </c>
       <c r="D96" s="25" t="inlineStr">
         <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
         </is>
       </c>
       <c r="E96" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F96" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 2-9</t>
+          <t>doc02§20-1</t>
         </is>
       </c>
       <c r="G96" s="23" t="inlineStr">
@@ -10700,22 +10712,22 @@
       </c>
       <c r="C97" s="25" t="inlineStr">
         <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
         </is>
       </c>
       <c r="D97" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
         </is>
       </c>
       <c r="E97" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 5-7</t>
+          <t>doc15,doc18</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr">
@@ -10733,27 +10745,27 @@
       </c>
       <c r="B98" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C98" s="25" t="inlineStr">
         <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
         </is>
       </c>
       <c r="D98" s="25" t="inlineStr">
         <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
         </is>
       </c>
       <c r="E98" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F98" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-4</t>
+          <t>doc14§5,doc18 3-1</t>
         </is>
       </c>
       <c r="G98" s="23" t="inlineStr">
@@ -10771,27 +10783,27 @@
       </c>
       <c r="B99" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C99" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
         </is>
       </c>
       <c r="D99" s="25" t="inlineStr">
         <is>
-          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
         </is>
       </c>
       <c r="E99" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-73,Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
         <is>
-          <t>doc01-5,doc18 1-2</t>
+          <t>doc14§5,doc15,doc18 4-5</t>
         </is>
       </c>
       <c r="G99" s="23" t="inlineStr">
@@ -10809,27 +10821,27 @@
       </c>
       <c r="B100" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C100" s="25" t="inlineStr">
         <is>
-          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
         </is>
       </c>
       <c r="D100" s="25" t="inlineStr">
         <is>
-          <t>施策の書きぶりに影響。</t>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
         </is>
       </c>
       <c r="E100" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-72</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F100" s="23" t="inlineStr">
         <is>
-          <t>doc01-12</t>
+          <t>doc17 B-3,doc18 4-3</t>
         </is>
       </c>
       <c r="G100" s="23" t="inlineStr">
@@ -10847,27 +10859,27 @@
       </c>
       <c r="B101" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C101" s="25" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
         </is>
       </c>
       <c r="D101" s="25" t="inlineStr">
         <is>
-          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
         </is>
       </c>
       <c r="E101" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F101" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-13</t>
+          <t>doc17 A-1,doc18 2-9</t>
         </is>
       </c>
       <c r="G101" s="23" t="inlineStr">
@@ -10885,27 +10897,27 @@
       </c>
       <c r="B102" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C102" s="25" t="inlineStr">
         <is>
-          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
         </is>
       </c>
       <c r="D102" s="25" t="inlineStr">
         <is>
-          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
         </is>
       </c>
       <c r="E102" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-31</t>
+          <t>Ⅱ-64,Ⅱ-75</t>
         </is>
       </c>
       <c r="F102" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-6</t>
+          <t>doc17 A-1,doc18 5-7</t>
         </is>
       </c>
       <c r="G102" s="23" t="inlineStr">
@@ -10923,27 +10935,27 @@
       </c>
       <c r="B103" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C103" s="25" t="inlineStr">
         <is>
-          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
         </is>
       </c>
       <c r="D103" s="25" t="inlineStr">
         <is>
-          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
         </is>
       </c>
       <c r="E103" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-40,Ⅰ-42</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-7</t>
+          <t>doc08§8-4</t>
         </is>
       </c>
       <c r="G103" s="23" t="inlineStr">
@@ -10961,27 +10973,27 @@
       </c>
       <c r="B104" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C104" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
         </is>
       </c>
       <c r="D104" s="25" t="inlineStr">
         <is>
-          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
         </is>
       </c>
       <c r="E104" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅱ-73,Ⅱ-75</t>
         </is>
       </c>
       <c r="F104" s="23" t="inlineStr">
         <is>
-          <t>doc23§1-3</t>
+          <t>doc01-5,doc18 1-2</t>
         </is>
       </c>
       <c r="G104" s="23" t="inlineStr">
@@ -10999,27 +11011,27 @@
       </c>
       <c r="B105" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C105" s="25" t="inlineStr">
         <is>
-          <t>送付状の個人情報に関する説明の補強</t>
+          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
         </is>
       </c>
       <c r="D105" s="25" t="inlineStr">
         <is>
-          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+          <t>施策の書きぶりに影響。</t>
         </is>
       </c>
       <c r="E105" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅱ-71,Ⅱ-72</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t>doc27§5-1</t>
+          <t>doc01-12</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
@@ -11037,308 +11049,308 @@
       </c>
       <c r="B106" s="24" t="inlineStr">
         <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C106" s="25" t="inlineStr">
+        <is>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+        </is>
+      </c>
+      <c r="D106" s="25" t="inlineStr">
+        <is>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+        </is>
+      </c>
+      <c r="E106" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F106" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-13</t>
+        </is>
+      </c>
+      <c r="G106" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H106" s="25" t="inlineStr"/>
+    </row>
+    <row r="107" ht="34" customHeight="1">
+      <c r="A107" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B107" s="24" t="inlineStr">
+        <is>
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C106" s="25" t="inlineStr">
+      <c r="C107" s="25" t="inlineStr">
+        <is>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+        </is>
+      </c>
+      <c r="D107" s="25" t="inlineStr">
+        <is>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+        </is>
+      </c>
+      <c r="E107" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-31</t>
+        </is>
+      </c>
+      <c r="F107" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-6</t>
+        </is>
+      </c>
+      <c r="G107" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H107" s="25" t="inlineStr"/>
+    </row>
+    <row r="108" ht="34" customHeight="1">
+      <c r="A108" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B108" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C108" s="25" t="inlineStr">
+        <is>
+          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+        </is>
+      </c>
+      <c r="D108" s="25" t="inlineStr">
+        <is>
+          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+        </is>
+      </c>
+      <c r="E108" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-40,Ⅰ-42</t>
+        </is>
+      </c>
+      <c r="F108" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-7</t>
+        </is>
+      </c>
+      <c r="G108" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H108" s="25" t="inlineStr"/>
+    </row>
+    <row r="109" ht="34" customHeight="1">
+      <c r="A109" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B109" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C109" s="25" t="inlineStr">
+        <is>
+          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+        </is>
+      </c>
+      <c r="D109" s="25" t="inlineStr">
+        <is>
+          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+        </is>
+      </c>
+      <c r="E109" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-09</t>
+        </is>
+      </c>
+      <c r="F109" s="23" t="inlineStr">
+        <is>
+          <t>doc23§1-3</t>
+        </is>
+      </c>
+      <c r="G109" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H109" s="25" t="inlineStr"/>
+    </row>
+    <row r="110" ht="34" customHeight="1">
+      <c r="A110" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B110" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C110" s="25" t="inlineStr">
+        <is>
+          <t>送付状の個人情報に関する説明の補強</t>
+        </is>
+      </c>
+      <c r="D110" s="25" t="inlineStr">
+        <is>
+          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+        </is>
+      </c>
+      <c r="E110" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-14</t>
+        </is>
+      </c>
+      <c r="F110" s="23" t="inlineStr">
+        <is>
+          <t>doc27§5-1</t>
+        </is>
+      </c>
+      <c r="G110" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H110" s="25" t="inlineStr"/>
+    </row>
+    <row r="111" ht="34" customHeight="1">
+      <c r="A111" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B111" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C111" s="25" t="inlineStr">
         <is>
           <t>ニーズ調査の選択肢の表記変更5件の可否（障がい表記・ぜひ・役場・移動販売・フルタイム）</t>
         </is>
       </c>
-      <c r="D106" s="25" t="inlineStr">
+      <c r="D111" s="25" t="inlineStr">
         <is>
           <t>村の表記ルール等による変更。手引きQ&amp;Aの「通称への置き換え」に近く多くは許容されると考えるが、「買い物（移動販売等※宅配は含まない）」のみ回答の範囲を広げる方向の変更で第9期・他保険者との比較に影響し得る。</t>
         </is>
       </c>
-      <c r="E106" s="23" t="inlineStr">
+      <c r="E111" s="23" t="inlineStr">
         <is>
           <t>Ⅰ-09</t>
         </is>
       </c>
-      <c r="F106" s="23" t="inlineStr">
+      <c r="F111" s="23" t="inlineStr">
         <is>
           <t>doc27§4</t>
         </is>
       </c>
-      <c r="G106" s="23" t="inlineStr">
+      <c r="G111" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H106" s="25" t="inlineStr"/>
-    </row>
-    <row r="107" ht="34" customHeight="1">
-      <c r="A107" s="38" t="inlineStr">
+      <c r="H111" s="25" t="inlineStr"/>
+    </row>
+    <row r="112" ht="34" customHeight="1">
+      <c r="A112" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B107" s="24" t="inlineStr">
+      <c r="B112" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C107" s="25" t="inlineStr">
+      <c r="C112" s="25" t="inlineStr">
         <is>
           <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
         </is>
       </c>
-      <c r="D107" s="25" t="inlineStr">
+      <c r="D112" s="25" t="inlineStr">
         <is>
           <t>第9期はA4・本文104頁・全6章＋資料編。</t>
         </is>
       </c>
-      <c r="E107" s="23" t="inlineStr">
+      <c r="E112" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-89</t>
         </is>
       </c>
-      <c r="F107" s="23" t="inlineStr">
+      <c r="F112" s="23" t="inlineStr">
         <is>
           <t>doc01-10</t>
         </is>
       </c>
-      <c r="G107" s="23" t="inlineStr">
+      <c r="G112" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H107" s="25" t="inlineStr"/>
-    </row>
-    <row r="108" ht="34" customHeight="1">
-      <c r="A108" s="38" t="inlineStr">
+      <c r="H112" s="25" t="inlineStr"/>
+    </row>
+    <row r="113" ht="34" customHeight="1">
+      <c r="A113" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B108" s="24" t="inlineStr">
+      <c r="B113" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C108" s="25" t="inlineStr">
+      <c r="C113" s="25" t="inlineStr">
         <is>
           <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
         </is>
       </c>
-      <c r="D108" s="25" t="inlineStr">
+      <c r="D113" s="25" t="inlineStr">
         <is>
           <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
         </is>
       </c>
-      <c r="E108" s="23" t="inlineStr">
+      <c r="E113" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-92</t>
         </is>
       </c>
-      <c r="F108" s="23" t="inlineStr">
+      <c r="F113" s="23" t="inlineStr">
         <is>
           <t>doc01-10,doc08</t>
         </is>
       </c>
-      <c r="G108" s="23" t="inlineStr">
+      <c r="G113" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H108" s="25" t="inlineStr"/>
-    </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="39" t="inlineStr">
+      <c r="H113" s="25" t="inlineStr"/>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="39" t="inlineStr">
         <is>
           <t>■ 解決済み（記録）</t>
         </is>
       </c>
-    </row>
-    <row r="111" ht="34" customHeight="1">
-      <c r="A111" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B111" s="41" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C111" s="42" t="inlineStr">
-        <is>
-          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
-        </is>
-      </c>
-      <c r="D111" s="42" t="inlineStr">
-        <is>
-          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
-        </is>
-      </c>
-      <c r="E111" s="40" t="inlineStr">
-        <is>
-          <t>Ⅰ-09</t>
-        </is>
-      </c>
-      <c r="F111" s="40" t="inlineStr">
-        <is>
-          <t>doc27§1-1</t>
-        </is>
-      </c>
-      <c r="G111" s="40" t="inlineStr">
-        <is>
-          <t>解決済（一部再掲）</t>
-        </is>
-      </c>
-      <c r="H111" s="42" t="inlineStr"/>
-    </row>
-    <row r="112" ht="34" customHeight="1">
-      <c r="A112" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B112" s="41" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C112" s="42" t="inlineStr">
-        <is>
-          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
-        </is>
-      </c>
-      <c r="D112" s="42" t="inlineStr">
-        <is>
-          <t>第2稿（0904版）で両方とも修正済。</t>
-        </is>
-      </c>
-      <c r="E112" s="40" t="inlineStr">
-        <is>
-          <t>Ⅰ-10</t>
-        </is>
-      </c>
-      <c r="F112" s="40" t="inlineStr">
-        <is>
-          <t>doc27§1-2</t>
-        </is>
-      </c>
-      <c r="G112" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H112" s="42" t="inlineStr"/>
-    </row>
-    <row r="113" ht="34" customHeight="1">
-      <c r="A113" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B113" s="41" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C113" s="42" t="inlineStr">
-        <is>
-          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
-        </is>
-      </c>
-      <c r="D113" s="42" t="inlineStr">
-        <is>
-          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
-        </is>
-      </c>
-      <c r="E113" s="40" t="inlineStr">
-        <is>
-          <t>Ⅰ-10</t>
-        </is>
-      </c>
-      <c r="F113" s="40" t="inlineStr">
-        <is>
-          <t>doc27§1-2</t>
-        </is>
-      </c>
-      <c r="G113" s="40" t="inlineStr">
-        <is>
-          <t>解決済（番号は再掲）</t>
-        </is>
-      </c>
-      <c r="H113" s="42" t="inlineStr"/>
-    </row>
-    <row r="114" ht="34" customHeight="1">
-      <c r="A114" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B114" s="41" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C114" s="42" t="inlineStr">
-        <is>
-          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
-        </is>
-      </c>
-      <c r="D114" s="42" t="inlineStr">
-        <is>
-          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
-        </is>
-      </c>
-      <c r="E114" s="40" t="inlineStr">
-        <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
-        </is>
-      </c>
-      <c r="F114" s="40" t="inlineStr">
-        <is>
-          <t>doc22 §1</t>
-        </is>
-      </c>
-      <c r="G114" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H114" s="42" t="inlineStr"/>
-    </row>
-    <row r="115" ht="34" customHeight="1">
-      <c r="A115" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B115" s="41" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C115" s="42" t="inlineStr">
-        <is>
-          <t>在宅介護実態調査 約150人の抽出基準</t>
-        </is>
-      </c>
-      <c r="D115" s="42" t="inlineStr">
-        <is>
-          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
-        </is>
-      </c>
-      <c r="E115" s="40" t="inlineStr">
-        <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
-        </is>
-      </c>
-      <c r="F115" s="40" t="inlineStr">
-        <is>
-          <t>doc22 §1</t>
-        </is>
-      </c>
-      <c r="G115" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H115" s="42" t="inlineStr"/>
     </row>
     <row r="116" ht="34" customHeight="1">
       <c r="A116" s="40" t="inlineStr">
@@ -11348,27 +11360,27 @@
       </c>
       <c r="B116" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C116" s="42" t="inlineStr">
         <is>
-          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
+          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
         </is>
       </c>
       <c r="D116" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
+          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
         </is>
       </c>
       <c r="E116" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-25,Ⅰ-26</t>
+          <t>Ⅱ-68,Ⅱ-69</t>
         </is>
       </c>
       <c r="F116" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc28§3</t>
         </is>
       </c>
       <c r="G116" s="40" t="inlineStr">
@@ -11386,27 +11398,27 @@
       </c>
       <c r="B117" s="41" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C117" s="42" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の範囲</t>
+          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
         </is>
       </c>
       <c r="D117" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
         </is>
       </c>
       <c r="E117" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>０-04</t>
         </is>
       </c>
       <c r="F117" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc28§4</t>
         </is>
       </c>
       <c r="G117" s="40" t="inlineStr">
@@ -11429,22 +11441,22 @@
       </c>
       <c r="C118" s="42" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+          <t>所得段階別の第1号被保険者数</t>
         </is>
       </c>
       <c r="D118" s="42" t="inlineStr">
         <is>
-          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
         </is>
       </c>
       <c r="E118" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F118" s="40" t="inlineStr">
         <is>
-          <t>doc20§3,§4</t>
+          <t>doc28§2</t>
         </is>
       </c>
       <c r="G118" s="40" t="inlineStr">
@@ -11467,22 +11479,22 @@
       </c>
       <c r="C119" s="42" t="inlineStr">
         <is>
-          <t>交付要綱の配点表（満点）</t>
+          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
         </is>
       </c>
       <c r="D119" s="42" t="inlineStr">
         <is>
-          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
         </is>
       </c>
       <c r="E119" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F119" s="40" t="inlineStr">
         <is>
-          <t>doc20§2</t>
+          <t>doc28§1</t>
         </is>
       </c>
       <c r="G119" s="40" t="inlineStr">
@@ -11500,32 +11512,32 @@
       </c>
       <c r="B120" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C120" s="42" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の交付金評価結果</t>
+          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
         </is>
       </c>
       <c r="D120" s="42" t="inlineStr">
         <is>
-          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
         </is>
       </c>
       <c r="E120" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F120" s="40" t="inlineStr">
         <is>
-          <t>doc20§3-1</t>
+          <t>doc27§1-1</t>
         </is>
       </c>
       <c r="G120" s="40" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（一部再掲）</t>
         </is>
       </c>
       <c r="H120" s="42" t="inlineStr"/>
@@ -11538,27 +11550,27 @@
       </c>
       <c r="B121" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C121" s="42" t="inlineStr">
         <is>
-          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
         </is>
       </c>
       <c r="D121" s="42" t="inlineStr">
         <is>
-          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+          <t>第2稿（0904版）で両方とも修正済。</t>
         </is>
       </c>
       <c r="E121" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-58</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F121" s="40" t="inlineStr">
         <is>
-          <t>doc09</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G121" s="40" t="inlineStr">
@@ -11576,32 +11588,32 @@
       </c>
       <c r="B122" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C122" s="42" t="inlineStr">
         <is>
-          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
         </is>
       </c>
       <c r="D122" s="42" t="inlineStr">
         <is>
-          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
         </is>
       </c>
       <c r="E122" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F122" s="40" t="inlineStr">
         <is>
-          <t>doc02§20-2</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G122" s="40" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（番号は再掲）</t>
         </is>
       </c>
       <c r="H122" s="42" t="inlineStr"/>
@@ -11614,48 +11626,390 @@
       </c>
       <c r="B123" s="41" t="inlineStr">
         <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C123" s="42" t="inlineStr">
+        <is>
+          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
+        </is>
+      </c>
+      <c r="D123" s="42" t="inlineStr">
+        <is>
+          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
+        </is>
+      </c>
+      <c r="E123" s="40" t="inlineStr">
+        <is>
+          <t>Ⅰ-08,Ⅰ-24</t>
+        </is>
+      </c>
+      <c r="F123" s="40" t="inlineStr">
+        <is>
+          <t>doc22 §1</t>
+        </is>
+      </c>
+      <c r="G123" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H123" s="42" t="inlineStr"/>
+    </row>
+    <row r="124" ht="34" customHeight="1">
+      <c r="A124" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B124" s="41" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C124" s="42" t="inlineStr">
+        <is>
+          <t>在宅介護実態調査 約150人の抽出基準</t>
+        </is>
+      </c>
+      <c r="D124" s="42" t="inlineStr">
+        <is>
+          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
+        </is>
+      </c>
+      <c r="E124" s="40" t="inlineStr">
+        <is>
+          <t>Ⅰ-08,Ⅰ-24</t>
+        </is>
+      </c>
+      <c r="F124" s="40" t="inlineStr">
+        <is>
+          <t>doc22 §1</t>
+        </is>
+      </c>
+      <c r="G124" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H124" s="42" t="inlineStr"/>
+    </row>
+    <row r="125" ht="34" customHeight="1">
+      <c r="A125" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B125" s="41" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C125" s="42" t="inlineStr">
+        <is>
+          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
+        </is>
+      </c>
+      <c r="D125" s="42" t="inlineStr">
+        <is>
+          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
+        </is>
+      </c>
+      <c r="E125" s="40" t="inlineStr">
+        <is>
+          <t>Ⅰ-25,Ⅰ-26</t>
+        </is>
+      </c>
+      <c r="F125" s="40" t="inlineStr">
+        <is>
+          <t>doc22 §1</t>
+        </is>
+      </c>
+      <c r="G125" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H125" s="42" t="inlineStr"/>
+    </row>
+    <row r="126" ht="34" customHeight="1">
+      <c r="A126" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B126" s="41" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C126" s="42" t="inlineStr">
+        <is>
+          <t>整合を図る関連計画の範囲</t>
+        </is>
+      </c>
+      <c r="D126" s="42" t="inlineStr">
+        <is>
+          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+        </is>
+      </c>
+      <c r="E126" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F126" s="40" t="inlineStr">
+        <is>
+          <t>doc22 §1</t>
+        </is>
+      </c>
+      <c r="G126" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H126" s="42" t="inlineStr"/>
+    </row>
+    <row r="127" ht="34" customHeight="1">
+      <c r="A127" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B127" s="41" t="inlineStr">
+        <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="C123" s="42" t="inlineStr">
+      <c r="C127" s="42" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+        </is>
+      </c>
+      <c r="D127" s="42" t="inlineStr">
+        <is>
+          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+        </is>
+      </c>
+      <c r="E127" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F127" s="40" t="inlineStr">
+        <is>
+          <t>doc20§3,§4</t>
+        </is>
+      </c>
+      <c r="G127" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H127" s="42" t="inlineStr"/>
+    </row>
+    <row r="128" ht="34" customHeight="1">
+      <c r="A128" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B128" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C128" s="42" t="inlineStr">
+        <is>
+          <t>交付要綱の配点表（満点）</t>
+        </is>
+      </c>
+      <c r="D128" s="42" t="inlineStr">
+        <is>
+          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+        </is>
+      </c>
+      <c r="E128" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F128" s="40" t="inlineStr">
+        <is>
+          <t>doc20§2</t>
+        </is>
+      </c>
+      <c r="G128" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H128" s="42" t="inlineStr"/>
+    </row>
+    <row r="129" ht="34" customHeight="1">
+      <c r="A129" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B129" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C129" s="42" t="inlineStr">
+        <is>
+          <t>令和6年度・令和7年度の交付金評価結果</t>
+        </is>
+      </c>
+      <c r="D129" s="42" t="inlineStr">
+        <is>
+          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+        </is>
+      </c>
+      <c r="E129" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F129" s="40" t="inlineStr">
+        <is>
+          <t>doc20§3-1</t>
+        </is>
+      </c>
+      <c r="G129" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H129" s="42" t="inlineStr"/>
+    </row>
+    <row r="130" ht="34" customHeight="1">
+      <c r="A130" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B130" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C130" s="42" t="inlineStr">
+        <is>
+          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+        </is>
+      </c>
+      <c r="D130" s="42" t="inlineStr">
+        <is>
+          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+        </is>
+      </c>
+      <c r="E130" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-56,Ⅱ-58</t>
+        </is>
+      </c>
+      <c r="F130" s="40" t="inlineStr">
+        <is>
+          <t>doc09</t>
+        </is>
+      </c>
+      <c r="G130" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H130" s="42" t="inlineStr"/>
+    </row>
+    <row r="131" ht="34" customHeight="1">
+      <c r="A131" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B131" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C131" s="42" t="inlineStr">
+        <is>
+          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+        </is>
+      </c>
+      <c r="D131" s="42" t="inlineStr">
+        <is>
+          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+        </is>
+      </c>
+      <c r="E131" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-59</t>
+        </is>
+      </c>
+      <c r="F131" s="40" t="inlineStr">
+        <is>
+          <t>doc02§20-2</t>
+        </is>
+      </c>
+      <c r="G131" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H131" s="42" t="inlineStr"/>
+    </row>
+    <row r="132" ht="34" customHeight="1">
+      <c r="A132" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B132" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C132" s="42" t="inlineStr">
         <is>
           <t>国の指針・様式の更新有無</t>
         </is>
       </c>
-      <c r="D123" s="42" t="inlineStr">
+      <c r="D132" s="42" t="inlineStr">
         <is>
           <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
-      <c r="E123" s="40" t="inlineStr">
+      <c r="E132" s="40" t="inlineStr">
         <is>
           <t>Ⅰ-11</t>
         </is>
       </c>
-      <c r="F123" s="40" t="inlineStr">
+      <c r="F132" s="40" t="inlineStr">
         <is>
           <t>doc04,doc05</t>
         </is>
       </c>
-      <c r="G123" s="40" t="inlineStr">
+      <c r="G132" s="40" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H123" s="42" t="inlineStr"/>
+      <c r="H132" s="42" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H108"/>
+  <autoFilter ref="A4:H113"/>
   <mergeCells count="3">
-    <mergeCell ref="A110:H110"/>
+    <mergeCell ref="A115:H115"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11669,7 +12023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12369,59 +12723,57 @@
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="35" t="inlineStr">
-        <is>
-          <t>村データ</t>
-        </is>
-      </c>
-      <c r="B26" s="34" t="inlineStr">
-        <is>
-          <t>★成年後見制度の利用実態・市民後見人養成実績</t>
-        </is>
-      </c>
-      <c r="C26" s="34" t="inlineStr">
-        <is>
-          <t>見える化に該当データなし</t>
-        </is>
-      </c>
-      <c r="D26" s="35" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E26" s="34" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="F26" s="35" t="inlineStr">
-        <is>
-          <t>未受領</t>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>国資料</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>第10期将来推計用人口推計（北塩原村のみ）＋推計の考え方（別紙1・2）</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>住基ベース推計と補正係数。令和22年まで。厚労省R8.8.24事務連絡／県R8.8.25通知</t>
+        </is>
+      </c>
+      <c r="D26" s="43" t="n">
+        <v>46272</v>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>docs/…/28_受領資料分析…md §1</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>受領済</t>
         </is>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>調査票</t>
+          <t>村データ</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>調査票 第2稿（0904版）</t>
+          <t>令和8年度 合計所得金額分布調査 調査票（入力済）</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>指摘13件のうち11件が反映。必須修正3件を新たに検出</t>
+          <t>所得段階別の第1号被保険者数13段階・合計1,015人。10万円刻みの分布を含む</t>
         </is>
       </c>
       <c r="D27" s="43" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>docs/…/27_調査票第2稿レビュー.md</t>
+          <t>docs/…/28_受領資料分析…md §2</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -12433,197 +12785,197 @@
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>成果物</t>
+          <t>村データ</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>第2回策定委員会 資料2・5・6・7（output/08_第2回策定委員会資料.docx）</t>
+          <t>成年後見制度利用促進施策に係る取組状況調査（令和7・8年度 市町村票）</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>26表・A4約30頁。資料2と7は本体完成、資料5と6は骨格</t>
+          <t>利用者4人、中核機関整備済、市民後見人0人ほか</t>
         </is>
       </c>
       <c r="D28" s="43" t="n">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>docs/…/26_第2回策定委員会_資料構成.md §11</t>
+          <t>docs/…/28_受領資料分析…md §3</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>作成済</t>
+          <t>受領済</t>
         </is>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>成果物</t>
+          <t>村データ</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>集計仕様書（output/07_集計仕様書.xlsx）</t>
+          <t>会津権利擁護・成年後見センター 相談件数（令和6・7年度）</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>6シート。ニーズ80設問・在宅26設問・派生変数20・クロス表20</t>
+          <t>本村 令和6年度134件／令和7年度76件。圏域13市町村の比較表</t>
         </is>
       </c>
       <c r="D29" s="43" t="n">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>docs/…/25_集計仕様書.md</t>
+          <t>docs/…/28_受領資料分析…md §3-3</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>作成済</t>
+          <t>受領済</t>
         </is>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>成果物</t>
+          <t>調査票</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>第2回策定委員会 資料構成（doc26）</t>
+          <t>調査票 第2稿（0904版）</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>資料1〜8・約53頁＋素案別冊。合意事項5点</t>
+          <t>指摘13件のうち11件が反映。必須修正3件を新たに検出</t>
         </is>
       </c>
       <c r="D30" s="43" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>docs/…/26_第2回策定委員会_資料構成.md</t>
+          <t>docs/…/27_調査票第2稿レビュー.md</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>作成済</t>
+          <t>受領済</t>
         </is>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>調査票</t>
+          <t>成果物</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>調査票 第1稿（ニーズ調査・在宅介護実態調査）</t>
+          <t>第2回策定委員会 資料2・5・6・7（output/08_第2回策定委員会資料.docx）</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>0828版。令和7年8月版・手法Ⅲ標準様式と全面突合</t>
+          <t>26表・A4約30頁。資料2と7は本体完成、資料5と6は骨格</t>
         </is>
       </c>
       <c r="D31" s="43" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>docs/…/23_調査票第1稿レビュー_ICF分析設計.md</t>
+          <t>docs/…/26_第2回策定委員会_資料構成.md §11</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>受領済</t>
+          <t>作成済</t>
         </is>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>国資料</t>
+          <t>成果物</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>令和8年度 交付金評価指標（市町村分）配点表</t>
+          <t>集計仕様書（output/07_集計仕様書.xlsx）</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>全17頁。推進400点・支援400点、目標Ⅰ〜Ⅳ各100点</t>
+          <t>6シート。ニーズ80設問・在宅26設問・派生変数20・クロス表20</t>
         </is>
       </c>
       <c r="D32" s="43" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>docs/…/20_交付金評価結果分析.md</t>
+          <t>docs/…/25_集計仕様書.md</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>受領済</t>
+          <t>作成済</t>
         </is>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>国資料</t>
+          <t>成果物</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>令和6年度 該当状況調査票集計表（全国一覧表）</t>
+          <t>第2回策定委員会 資料構成（doc26）</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>全国1,741市町村。村は第398行。合計295点</t>
+          <t>資料1〜8・約53頁＋素案別冊。合意事項5点</t>
         </is>
       </c>
       <c r="D33" s="43" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>docs/…/20_交付金評価結果分析.md</t>
+          <t>docs/…/26_第2回策定委員会_資料構成.md</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>受領済</t>
+          <t>作成済</t>
         </is>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>国資料</t>
+          <t>調査票</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>令和7年度 該当状況調査票集計表（全国集計・市町村）</t>
+          <t>調査票 第1稿（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>合計339点。全国平均435.0点</t>
+          <t>0828版。令和7年8月版・手法Ⅲ標準様式と全面突合</t>
         </is>
       </c>
       <c r="D34" s="43" t="n">
@@ -12631,7 +12983,7 @@
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>docs/…/20_交付金評価結果分析.md</t>
+          <t>docs/…/23_調査票第1稿レビュー_ICF分析設計.md</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -12648,12 +13000,12 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>令和8年度 該当状況調査票集計表（全国集計・市町村）</t>
+          <t>令和8年度 交付金評価指標（市町村分）配点表</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>合計447点。全国平均455.1点／全国1,005位／県内34位</t>
+          <t>全17頁。推進400点・支援400点、目標Ⅰ〜Ⅳ各100点</t>
         </is>
       </c>
       <c r="D35" s="43" t="n">
@@ -12673,17 +13025,17 @@
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>関連計画</t>
+          <t>国資料</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>第四次北塩原村生涯学習推進計画</t>
+          <t>令和6年度 該当状況調査票集計表（全国一覧表）</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>全112頁。2018〜2027年度。7z分割書庫4分割で受領</t>
+          <t>全国1,741市町村。村は第398行。合計295点</t>
         </is>
       </c>
       <c r="D36" s="43" t="n">
@@ -12691,49 +13043,139 @@
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
+          <t>docs/…/20_交付金評価結果分析.md</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>国資料</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>令和7年度 該当状況調査票集計表（全国集計・市町村）</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>合計339点。全国平均435.0点</t>
+        </is>
+      </c>
+      <c r="D37" s="43" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>docs/…/20_交付金評価結果分析.md</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>国資料</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>令和8年度 該当状況調査票集計表（全国集計・市町村）</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>合計447点。全国平均455.1点／全国1,005位／県内34位</t>
+        </is>
+      </c>
+      <c r="D38" s="43" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>docs/…/20_交付金評価結果分析.md</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>関連計画</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>第四次北塩原村生涯学習推進計画</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>全112頁。2018〜2027年度。7z分割書庫4分割で受領</t>
+        </is>
+      </c>
+      <c r="D39" s="43" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
           <t>docs/…/21_関連計画_第四次生涯学習推進計画.md</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>受領済</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="35" t="inlineStr">
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="35" t="inlineStr">
         <is>
           <t>村データ</t>
         </is>
       </c>
-      <c r="B37" s="34" t="inlineStr">
+      <c r="B40" s="34" t="inlineStr">
         <is>
           <t>★要介護認定データ（調査票との関連付け用）</t>
         </is>
       </c>
-      <c r="C37" s="34" t="inlineStr">
+      <c r="C40" s="34" t="inlineStr">
         <is>
           <t>仕様書4Ⅰ(5)。調査回収後に必要</t>
         </is>
       </c>
-      <c r="D37" s="35" t="inlineStr">
+      <c r="D40" s="35" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E37" s="34" t="inlineStr">
+      <c r="E40" s="34" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F37" s="35" t="inlineStr">
+      <c r="F40" s="35" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F37"/>
+  <autoFilter ref="A4:F40"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$104</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$113</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="M64" s="14" t="n"/>
       <c r="N64" s="15" t="n">
-        <v>0.55</v>
+        <v>0.8</v>
       </c>
       <c r="O64" s="16" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="P64" s="13" t="inlineStr">
         <is>
-          <t>doc13で年齢階級別認定率（前期6.49%／後期34.87%）による参考試算を実施（214→230人）。要介護度別推計は国ワークシート待ち。</t>
+          <t>★9/7：doc29／scripts/estimate_certified.py として要介護度別の推計を確立。見える化のB4-a（全体）とB4-d（75歳以上）から前期・後期別の要介護度別認定率を分解（前期5.86%／後期34.70%）。B案×令和8年の認定率で基準年が実績と完全一致（211人・要支援1=51・要支援2=29・要介護1=50）。令和9年214人／令和10年217人／令和11年220人。認定率の基準2種×被保険者数2案の4通りを出力し、令和11年度で最大12人・5.8%の幅。</t>
         </is>
       </c>
     </row>
@@ -4647,11 +4647,11 @@
       <c r="J65" s="14" t="n"/>
       <c r="K65" s="14" t="n"/>
       <c r="L65" s="14" t="n">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="M65" s="14" t="n"/>
       <c r="N65" s="15" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="O65" s="16" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12725,17 +12725,17 @@
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>国資料</t>
+          <t>成果物</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>第10期将来推計用人口推計（北塩原村のみ）＋推計の考え方（別紙1・2）</t>
+          <t>第10期 要介護度別認定者数の推計（doc29／data/…推計.csv）</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>住基ベース推計と補正係数。令和22年まで。厚労省R8.8.24事務連絡／県R8.8.25通知</t>
+          <t>前期・後期別の認定率に分解。基準年が実績と完全一致</t>
         </is>
       </c>
       <c r="D26" s="43" t="n">
@@ -12743,29 +12743,29 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>docs/…/28_受領資料分析…md §1</t>
+          <t>docs/…/29_要介護認定者数の推計.md</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>受領済</t>
+          <t>作成済</t>
         </is>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>村データ</t>
+          <t>国資料</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>令和8年度 合計所得金額分布調査 調査票（入力済）</t>
+          <t>第10期将来推計用人口推計（北塩原村のみ）＋推計の考え方（別紙1・2）</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>所得段階別の第1号被保険者数13段階・合計1,015人。10万円刻みの分布を含む</t>
+          <t>住基ベース推計と補正係数。令和22年まで。厚労省R8.8.24事務連絡／県R8.8.25通知</t>
         </is>
       </c>
       <c r="D27" s="43" t="n">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>docs/…/28_受領資料分析…md §2</t>
+          <t>docs/…/28_受領資料分析…md §1</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -12790,12 +12790,12 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>成年後見制度利用促進施策に係る取組状況調査（令和7・8年度 市町村票）</t>
+          <t>令和8年度 合計所得金額分布調査 調査票（入力済）</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>利用者4人、中核機関整備済、市民後見人0人ほか</t>
+          <t>所得段階別の第1号被保険者数13段階・合計1,015人。10万円刻みの分布を含む</t>
         </is>
       </c>
       <c r="D28" s="43" t="n">
@@ -12803,7 +12803,7 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>docs/…/28_受領資料分析…md §3</t>
+          <t>docs/…/28_受領資料分析…md §2</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -12820,12 +12820,12 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>会津権利擁護・成年後見センター 相談件数（令和6・7年度）</t>
+          <t>成年後見制度利用促進施策に係る取組状況調査（令和7・8年度 市町村票）</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>本村 令和6年度134件／令和7年度76件。圏域13市町村の比較表</t>
+          <t>利用者4人、中核機関整備済、市民後見人0人ほか</t>
         </is>
       </c>
       <c r="D29" s="43" t="n">
@@ -12833,7 +12833,7 @@
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>docs/…/28_受領資料分析…md §3-3</t>
+          <t>docs/…/28_受領資料分析…md §3</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -12845,25 +12845,25 @@
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>調査票</t>
+          <t>村データ</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>調査票 第2稿（0904版）</t>
+          <t>会津権利擁護・成年後見センター 相談件数（令和6・7年度）</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>指摘13件のうち11件が反映。必須修正3件を新たに検出</t>
+          <t>本村 令和6年度134件／令和7年度76件。圏域13市町村の比較表</t>
         </is>
       </c>
       <c r="D30" s="43" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>docs/…/27_調査票第2稿レビュー.md</t>
+          <t>docs/…/28_受領資料分析…md §3-3</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -12875,30 +12875,30 @@
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>成果物</t>
+          <t>調査票</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>第2回策定委員会 資料2・5・6・7（output/08_第2回策定委員会資料.docx）</t>
+          <t>調査票 第2稿（0904版）</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>26表・A4約30頁。資料2と7は本体完成、資料5と6は骨格</t>
+          <t>指摘13件のうち11件が反映。必須修正3件を新たに検出</t>
         </is>
       </c>
       <c r="D31" s="43" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>docs/…/26_第2回策定委員会_資料構成.md §11</t>
+          <t>docs/…/27_調査票第2稿レビュー.md</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>作成済</t>
+          <t>受領済</t>
         </is>
       </c>
     </row>
@@ -12910,12 +12910,12 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>集計仕様書（output/07_集計仕様書.xlsx）</t>
+          <t>第2回策定委員会 資料2・5・6・7（output/08_第2回策定委員会資料.docx）</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>6シート。ニーズ80設問・在宅26設問・派生変数20・クロス表20</t>
+          <t>26表・A4約30頁。資料2と7は本体完成、資料5と6は骨格</t>
         </is>
       </c>
       <c r="D32" s="43" t="n">
@@ -12923,7 +12923,7 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>docs/…/25_集計仕様書.md</t>
+          <t>docs/…/26_第2回策定委員会_資料構成.md §11</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -12940,12 +12940,12 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>第2回策定委員会 資料構成（doc26）</t>
+          <t>集計仕様書（output/07_集計仕様書.xlsx）</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>資料1〜8・約53頁＋素案別冊。合意事項5点</t>
+          <t>6シート。ニーズ80設問・在宅26設問・派生変数20・クロス表20</t>
         </is>
       </c>
       <c r="D33" s="43" t="n">
@@ -12953,7 +12953,7 @@
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>docs/…/26_第2回策定委員会_資料構成.md</t>
+          <t>docs/…/25_集計仕様書.md</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -12965,47 +12965,47 @@
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>調査票</t>
+          <t>成果物</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>調査票 第1稿（ニーズ調査・在宅介護実態調査）</t>
+          <t>第2回策定委員会 資料構成（doc26）</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>0828版。令和7年8月版・手法Ⅲ標準様式と全面突合</t>
+          <t>資料1〜8・約53頁＋素案別冊。合意事項5点</t>
         </is>
       </c>
       <c r="D34" s="43" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>docs/…/23_調査票第1稿レビュー_ICF分析設計.md</t>
+          <t>docs/…/26_第2回策定委員会_資料構成.md</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>受領済</t>
+          <t>作成済</t>
         </is>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>国資料</t>
+          <t>調査票</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>令和8年度 交付金評価指標（市町村分）配点表</t>
+          <t>調査票 第1稿（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>全17頁。推進400点・支援400点、目標Ⅰ〜Ⅳ各100点</t>
+          <t>0828版。令和7年8月版・手法Ⅲ標準様式と全面突合</t>
         </is>
       </c>
       <c r="D35" s="43" t="n">
@@ -13013,7 +13013,7 @@
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>docs/…/20_交付金評価結果分析.md</t>
+          <t>docs/…/23_調査票第1稿レビュー_ICF分析設計.md</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -13030,12 +13030,12 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>令和6年度 該当状況調査票集計表（全国一覧表）</t>
+          <t>令和8年度 交付金評価指標（市町村分）配点表</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>全国1,741市町村。村は第398行。合計295点</t>
+          <t>全17頁。推進400点・支援400点、目標Ⅰ〜Ⅳ各100点</t>
         </is>
       </c>
       <c r="D36" s="43" t="n">
@@ -13060,12 +13060,12 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>令和7年度 該当状況調査票集計表（全国集計・市町村）</t>
+          <t>令和6年度 該当状況調査票集計表（全国一覧表）</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>合計339点。全国平均435.0点</t>
+          <t>全国1,741市町村。村は第398行。合計295点</t>
         </is>
       </c>
       <c r="D37" s="43" t="n">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>令和8年度 該当状況調査票集計表（全国集計・市町村）</t>
+          <t>令和7年度 該当状況調査票集計表（全国集計・市町村）</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>合計447点。全国平均455.1点／全国1,005位／県内34位</t>
+          <t>合計339点。全国平均435.0点</t>
         </is>
       </c>
       <c r="D38" s="43" t="n">
@@ -13115,17 +13115,17 @@
     <row r="39" ht="28" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>関連計画</t>
+          <t>国資料</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>第四次北塩原村生涯学習推進計画</t>
+          <t>令和8年度 該当状況調査票集計表（全国集計・市町村）</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>全112頁。2018〜2027年度。7z分割書庫4分割で受領</t>
+          <t>合計447点。全国平均455.1点／全国1,005位／県内34位</t>
         </is>
       </c>
       <c r="D39" s="43" t="n">
@@ -13133,49 +13133,79 @@
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
+          <t>docs/…/20_交付金評価結果分析.md</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>関連計画</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>第四次北塩原村生涯学習推進計画</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>全112頁。2018〜2027年度。7z分割書庫4分割で受領</t>
+        </is>
+      </c>
+      <c r="D40" s="43" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
           <t>docs/…/21_関連計画_第四次生涯学習推進計画.md</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>受領済</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="35" t="inlineStr">
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="35" t="inlineStr">
         <is>
           <t>村データ</t>
         </is>
       </c>
-      <c r="B40" s="34" t="inlineStr">
+      <c r="B41" s="34" t="inlineStr">
         <is>
           <t>★要介護認定データ（調査票との関連付け用）</t>
         </is>
       </c>
-      <c r="C40" s="34" t="inlineStr">
+      <c r="C41" s="34" t="inlineStr">
         <is>
           <t>仕様書4Ⅰ(5)。調査回収後に必要</t>
         </is>
       </c>
-      <c r="D40" s="35" t="inlineStr">
+      <c r="D41" s="35" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E40" s="34" t="inlineStr">
+      <c r="E41" s="34" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F40" s="35" t="inlineStr">
+      <c r="F41" s="35" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F40"/>
+  <autoFilter ref="A4:F41"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$118</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="M65" s="14" t="n"/>
       <c r="N65" s="15" t="n">
-        <v>0.45</v>
+        <v>0.75</v>
       </c>
       <c r="O65" s="16" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
       </c>
       <c r="P65" s="13" t="inlineStr">
         <is>
-          <t>doc18 第5章5-4に見込量の様式を作成。27サービスの利用状況（実績あり18／過去のみ5／実績なし4）を確定し、受給者1人あたり利用日数・回数の実績を整理。受給者数の実績と見込量の数値は国ワークシートと村の月報・年報待ち。</t>
+          <t>★9/8：doc30として推計の枠組みを確定。「見える化」システムのデータ定義（受給者数＝年度延べ、D45系の分母＝要介護度別認定者数）を検算のうえ確定し、estimate_services.py により区分別・サービス種類別の見込量を算定。全28サービスのうち令和7年度に実績のある16サービスについて受給者数・利用量・給付費の暫定値を doc18 第5章5-4に投入。施設・居住系の種類別人数は見える化に系列がなく給付費比の按分値のため、村の月報（第2表・第3表）で置き換えが必要。介護給付と予防給付の分離も同じく月報待ち。</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="M66" s="14" t="n"/>
       <c r="N66" s="15" t="n">
-        <v>0.2</v>
+        <v>0.55</v>
       </c>
       <c r="O66" s="16" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="P66" s="13" t="inlineStr">
         <is>
-          <t>doc18 第5章5-6に標準給付費の様式を作成。第9期の計画値と実績の対比を参考として掲載。数値は国ワークシート待ち。</t>
+          <t>★9/8：サービス諸費（介護サービス等諸費＋介護予防サービス等諸費）の推計値を算定し doc18 第5章5-6に投入（令和9年度263,470千円／10年度263,505千円／11年度262,488千円）。見える化D48系に令和5年度までの決算が入っていることが判明し、令和3〜5年度の実績（244,097／247,333／258,848千円）と対比。決算の未入手は令和6・7年度の2か年に縮小。補足給付・高額介護サービス費・審査支払手数料は令和5年度決算まで把握済。</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="M68" s="14" t="n"/>
       <c r="N68" s="15" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="O68" s="16" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="P68" s="13" t="inlineStr">
         <is>
-          <t>★議事録で方針決着：第9期で県内平均を上回ったため急激な負担増を抑えたい意向。基金取崩も視野。令和9年度の介護報酬改定を見据え現行単価で一旦試算し単価確定後に補正。doc18 第5章5-7に様式と所得段階13段階の枠を作成済。</t>
+          <t>★議事録で方針決着：第9期で県内平均を上回ったため急激な負担増を抑えたい意向。基金取崩も視野。令和9年度の介護報酬改定を見据え現行単価で一旦試算し単価確定後に補正。doc18 第5章5-7に様式と所得段階13段階の枠を作成済。★9/8：サービス諸費の推計（doc30）が出たため、残る停止要因は基金残高と令和6・7年度決算の2件に絞られた。</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="P79" s="13" t="inlineStr">
         <is>
-          <t>doc18／output/06_計画素案.docx として全6章・65節・73表・図18点を作成。第2章の図はモノクロ印刷を前提に明度差＋線種＋マーカー＋ハッチングで識別。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。サービス区分別分析（訪問系−50.8%）を追加。第5章に見込量27サービスの様式・保険料算定様式・所得段階13段階・2040年見通しの枠を作成。数値は国ワークシート待ち。</t>
+          <t>doc18／output/06_計画素案.docx として全6章・65節・73表・図20点を作成。第2章の図はモノクロ印刷を前提に明度差＋線種＋マーカー＋ハッチングで識別。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。サービス区分別分析（訪問系−50.8%）を追加。★9/8：第5章5-4・5-5・5-6にサービス見込量と給付費の暫定推計値を投入（doc30）。残る空欄は保険料（5-7）と地域支援事業費の事業別内訳。</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H132"/>
+  <dimension ref="A1:H137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="D63" s="25" t="inlineStr">
         <is>
-          <t>第9期の計画値と実績の乖離を確定させるために必要。</t>
+          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
         </is>
       </c>
       <c r="E63" s="23" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-1</t>
+          <t>doc08§8-1,doc30§2-4</t>
         </is>
       </c>
       <c r="G63" s="23" t="inlineStr">
@@ -9572,22 +9572,22 @@
       </c>
       <c r="C67" s="25" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告（月報・年報）の原データの提供可否</t>
+          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
         </is>
       </c>
       <c r="D67" s="25" t="inlineStr">
         <is>
-          <t>見える化に収録されていない項目（サービス種類別利用者数の月次推移等）が扱えるようになる。</t>
+          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
         </is>
       </c>
       <c r="E67" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-10</t>
+          <t>doc30§5-3</t>
         </is>
       </c>
       <c r="G67" s="23" t="inlineStr">
@@ -9610,22 +9610,22 @@
       </c>
       <c r="C68" s="25" t="inlineStr">
         <is>
-          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
+          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
         </is>
       </c>
       <c r="D68" s="25" t="inlineStr">
         <is>
-          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
+          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
         </is>
       </c>
       <c r="E68" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F68" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G68" s="23" t="inlineStr">
@@ -9648,22 +9648,22 @@
       </c>
       <c r="C69" s="25" t="inlineStr">
         <is>
-          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
+          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
         </is>
       </c>
       <c r="D69" s="25" t="inlineStr">
         <is>
-          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
+          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
         </is>
       </c>
       <c r="E69" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F69" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G69" s="23" t="inlineStr">
@@ -9686,22 +9686,22 @@
       </c>
       <c r="C70" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
+          <t>居宅介護支援・介護予防支援の受給者数（令和5〜7年度）</t>
         </is>
       </c>
       <c r="D70" s="25" t="inlineStr">
         <is>
-          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
+          <t>見える化は両者を合算した給付費のみ。人数は在宅サービス受給者数（112.6人／月）に近い水準とみられるが実数が要る。</t>
         </is>
       </c>
       <c r="E70" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F70" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G70" s="23" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="C71" s="25" t="inlineStr">
         <is>
-          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
+          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
         </is>
       </c>
       <c r="D71" s="25" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
+          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
         </is>
       </c>
       <c r="E71" s="23" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-65</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G71" s="23" t="inlineStr">
@@ -9762,22 +9762,22 @@
       </c>
       <c r="C72" s="25" t="inlineStr">
         <is>
-          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
+          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
         </is>
       </c>
       <c r="D72" s="25" t="inlineStr">
         <is>
-          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
+          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
         </is>
       </c>
       <c r="E72" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F72" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-68</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G72" s="23" t="inlineStr">
@@ -9800,22 +9800,22 @@
       </c>
       <c r="C73" s="25" t="inlineStr">
         <is>
-          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
+          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
         </is>
       </c>
       <c r="D73" s="25" t="inlineStr">
         <is>
-          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
+          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
         </is>
       </c>
       <c r="E73" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F73" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-71</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G73" s="23" t="inlineStr">
@@ -9838,22 +9838,22 @@
       </c>
       <c r="C74" s="25" t="inlineStr">
         <is>
-          <t>シルバー人材センターの会員数・受注実績</t>
+          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
         </is>
       </c>
       <c r="D74" s="25" t="inlineStr">
         <is>
-          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
+          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
         </is>
       </c>
       <c r="E74" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F74" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-72</t>
+          <t>doc20§6-2 K-65</t>
         </is>
       </c>
       <c r="G74" s="23" t="inlineStr">
@@ -9876,22 +9876,22 @@
       </c>
       <c r="C75" s="25" t="inlineStr">
         <is>
-          <t>第9期調査の集計基準・集計表の提供</t>
+          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
         </is>
       </c>
       <c r="D75" s="25" t="inlineStr">
         <is>
-          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
+          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
         </is>
       </c>
       <c r="E75" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F75" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-92</t>
+          <t>doc21§5 K-68</t>
         </is>
       </c>
       <c r="G75" s="23" t="inlineStr">
@@ -9914,22 +9914,22 @@
       </c>
       <c r="C76" s="25" t="inlineStr">
         <is>
-          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
+          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
         </is>
       </c>
       <c r="D76" s="25" t="inlineStr">
         <is>
-          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
+          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
         </is>
       </c>
       <c r="E76" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F76" s="23" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-109</t>
+          <t>doc21§5 K-71</t>
         </is>
       </c>
       <c r="G76" s="23" t="inlineStr">
@@ -9952,22 +9952,22 @@
       </c>
       <c r="C77" s="25" t="inlineStr">
         <is>
-          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
+          <t>シルバー人材センターの会員数・受注実績</t>
         </is>
       </c>
       <c r="D77" s="25" t="inlineStr">
         <is>
-          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
+          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
         </is>
       </c>
       <c r="E77" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F77" s="23" t="inlineStr">
         <is>
-          <t>doc28§2 K-110</t>
+          <t>doc21§5 K-72</t>
         </is>
       </c>
       <c r="G77" s="23" t="inlineStr">
@@ -9985,27 +9985,27 @@
       </c>
       <c r="B78" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C78" s="25" t="inlineStr">
         <is>
-          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
+          <t>第9期調査の集計基準・集計表の提供</t>
         </is>
       </c>
       <c r="D78" s="25" t="inlineStr">
         <is>
-          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
+          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
         </is>
       </c>
       <c r="E78" s="23" t="inlineStr">
         <is>
-          <t>Ⅴ-95</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F78" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-67</t>
+          <t>doc25§8 K-92</t>
         </is>
       </c>
       <c r="G78" s="23" t="inlineStr">
@@ -10023,27 +10023,27 @@
       </c>
       <c r="B79" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C79" s="25" t="inlineStr">
         <is>
-          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
+          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
         </is>
       </c>
       <c r="D79" s="25" t="inlineStr">
         <is>
-          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
+          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
         </is>
       </c>
       <c r="E79" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-35</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-93</t>
+          <t>doc28§3-4 K-109</t>
         </is>
       </c>
       <c r="G79" s="23" t="inlineStr">
@@ -10061,27 +10061,27 @@
       </c>
       <c r="B80" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C80" s="25" t="inlineStr">
         <is>
-          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
+          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
         </is>
       </c>
       <c r="D80" s="25" t="inlineStr">
         <is>
-          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
+          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
         </is>
       </c>
       <c r="E80" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-48</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F80" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-94</t>
+          <t>doc28§2 K-110</t>
         </is>
       </c>
       <c r="G80" s="23" t="inlineStr">
@@ -10099,27 +10099,27 @@
       </c>
       <c r="B81" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C81" s="25" t="inlineStr">
         <is>
-          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
+          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
         </is>
       </c>
       <c r="D81" s="25" t="inlineStr">
         <is>
-          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
+          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
         </is>
       </c>
       <c r="E81" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅴ-95</t>
         </is>
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t>doc19 指-5</t>
+          <t>doc20§6-2 K-67</t>
         </is>
       </c>
       <c r="G81" s="23" t="inlineStr">
@@ -10137,27 +10137,27 @@
       </c>
       <c r="B82" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C82" s="25" t="inlineStr">
         <is>
-          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
+          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
         </is>
       </c>
       <c r="D82" s="25" t="inlineStr">
         <is>
-          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
+          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
         </is>
       </c>
       <c r="E82" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-108</t>
+          <t>Ⅰ-35</t>
         </is>
       </c>
       <c r="F82" s="23" t="inlineStr">
         <is>
-          <t>doc22 K-80</t>
+          <t>doc25§8 K-93</t>
         </is>
       </c>
       <c r="G82" s="23" t="inlineStr">
@@ -10175,27 +10175,27 @@
       </c>
       <c r="B83" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C83" s="25" t="inlineStr">
         <is>
-          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
+          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
         </is>
       </c>
       <c r="D83" s="25" t="inlineStr">
         <is>
-          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
+          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
         </is>
       </c>
       <c r="E83" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-90</t>
+          <t>Ⅰ-48</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-88</t>
+          <t>doc25§8 K-94</t>
         </is>
       </c>
       <c r="G83" s="23" t="inlineStr">
@@ -10213,27 +10213,27 @@
       </c>
       <c r="B84" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C84" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
+          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
         </is>
       </c>
       <c r="D84" s="25" t="inlineStr">
         <is>
-          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
+          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
         </is>
       </c>
       <c r="E84" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F84" s="23" t="inlineStr">
         <is>
-          <t>doc09§4,§10</t>
+          <t>doc19 指-5</t>
         </is>
       </c>
       <c r="G84" s="23" t="inlineStr">
@@ -10251,27 +10251,27 @@
       </c>
       <c r="B85" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C85" s="25" t="inlineStr">
         <is>
-          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
+          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
         </is>
       </c>
       <c r="D85" s="25" t="inlineStr">
         <is>
-          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
+          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
         </is>
       </c>
       <c r="E85" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-108</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t>doc09§8,§10</t>
+          <t>doc22 K-80</t>
         </is>
       </c>
       <c r="G85" s="23" t="inlineStr">
@@ -10289,27 +10289,27 @@
       </c>
       <c r="B86" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C86" s="25" t="inlineStr">
         <is>
-          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
+          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
         </is>
       </c>
       <c r="D86" s="25" t="inlineStr">
         <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
+          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
         </is>
       </c>
       <c r="E86" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅳ-90</t>
         </is>
       </c>
       <c r="F86" s="23" t="inlineStr">
         <is>
-          <t>doc02§17,doc07,doc18 4-1</t>
+          <t>doc24§12 K-88</t>
         </is>
       </c>
       <c r="G86" s="23" t="inlineStr">
@@ -10332,22 +10332,22 @@
       </c>
       <c r="C87" s="25" t="inlineStr">
         <is>
-          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
+          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
         </is>
       </c>
       <c r="D87" s="25" t="inlineStr">
         <is>
-          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
+          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
         </is>
       </c>
       <c r="E87" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-75</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr">
         <is>
-          <t>doc17 C-1,doc02§20-2</t>
+          <t>doc09§4,§10</t>
         </is>
       </c>
       <c r="G87" s="23" t="inlineStr">
@@ -10370,22 +10370,22 @@
       </c>
       <c r="C88" s="25" t="inlineStr">
         <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
         </is>
       </c>
       <c r="D88" s="25" t="inlineStr">
         <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
         </is>
       </c>
       <c r="E88" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F88" s="23" t="inlineStr">
         <is>
-          <t>doc13§6</t>
+          <t>doc09§8,§10</t>
         </is>
       </c>
       <c r="G88" s="23" t="inlineStr">
@@ -10408,22 +10408,22 @@
       </c>
       <c r="C89" s="25" t="inlineStr">
         <is>
-          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
         </is>
       </c>
       <c r="D89" s="25" t="inlineStr">
         <is>
-          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
         </is>
       </c>
       <c r="E89" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-14</t>
+          <t>doc02§17,doc07,doc18 4-1</t>
         </is>
       </c>
       <c r="G89" s="23" t="inlineStr">
@@ -10446,22 +10446,22 @@
       </c>
       <c r="C90" s="25" t="inlineStr">
         <is>
-          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
         </is>
       </c>
       <c r="D90" s="25" t="inlineStr">
         <is>
-          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
         </is>
       </c>
       <c r="E90" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-56,Ⅱ-75</t>
         </is>
       </c>
       <c r="F90" s="23" t="inlineStr">
         <is>
-          <t>doc19 §3</t>
+          <t>doc17 C-1,doc02§20-2</t>
         </is>
       </c>
       <c r="G90" s="23" t="inlineStr">
@@ -10484,22 +10484,22 @@
       </c>
       <c r="C91" s="25" t="inlineStr">
         <is>
-          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
         </is>
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-60,Ⅱ-65</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-73</t>
+          <t>doc13§6</t>
         </is>
       </c>
       <c r="G91" s="23" t="inlineStr">
@@ -10522,22 +10522,22 @@
       </c>
       <c r="C92" s="25" t="inlineStr">
         <is>
-          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
+          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
         </is>
       </c>
       <c r="D92" s="25" t="inlineStr">
         <is>
-          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
+          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
         </is>
       </c>
       <c r="E92" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-105</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F92" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-90</t>
+          <t>doc30§4-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G92" s="23" t="inlineStr">
@@ -10555,27 +10555,27 @@
       </c>
       <c r="B93" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C93" s="25" t="inlineStr">
         <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
         </is>
       </c>
       <c r="D93" s="25" t="inlineStr">
         <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
         </is>
       </c>
       <c r="E93" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t>doc07§4</t>
+          <t>doc30§5-4</t>
         </is>
       </c>
       <c r="G93" s="23" t="inlineStr">
@@ -10593,27 +10593,27 @@
       </c>
       <c r="B94" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C94" s="25" t="inlineStr">
         <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
         </is>
       </c>
       <c r="D94" s="25" t="inlineStr">
         <is>
-          <t>評価指標の読み方に影響。</t>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
         </is>
       </c>
       <c r="E94" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F94" s="23" t="inlineStr">
         <is>
-          <t>doc07§8-4</t>
+          <t>doc19 追-14</t>
         </is>
       </c>
       <c r="G94" s="23" t="inlineStr">
@@ -10631,27 +10631,27 @@
       </c>
       <c r="B95" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C95" s="25" t="inlineStr">
         <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
         </is>
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
         </is>
       </c>
       <c r="E95" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t>doc08§4,§8-2</t>
+          <t>doc19 §3</t>
         </is>
       </c>
       <c r="G95" s="23" t="inlineStr">
@@ -10669,27 +10669,27 @@
       </c>
       <c r="B96" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C96" s="25" t="inlineStr">
         <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
         </is>
       </c>
       <c r="D96" s="25" t="inlineStr">
         <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
         </is>
       </c>
       <c r="E96" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F96" s="23" t="inlineStr">
         <is>
-          <t>doc02§20-1</t>
+          <t>doc21§5 K-73</t>
         </is>
       </c>
       <c r="G96" s="23" t="inlineStr">
@@ -10707,27 +10707,27 @@
       </c>
       <c r="B97" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C97" s="25" t="inlineStr">
         <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
         </is>
       </c>
       <c r="D97" s="25" t="inlineStr">
         <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
         </is>
       </c>
       <c r="E97" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-105</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t>doc15,doc18</t>
+          <t>doc24§12 K-90</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr">
@@ -10745,27 +10745,27 @@
       </c>
       <c r="B98" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C98" s="25" t="inlineStr">
         <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
         </is>
       </c>
       <c r="D98" s="25" t="inlineStr">
         <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
         </is>
       </c>
       <c r="E98" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F98" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc18 3-1</t>
+          <t>doc07§4</t>
         </is>
       </c>
       <c r="G98" s="23" t="inlineStr">
@@ -10783,27 +10783,27 @@
       </c>
       <c r="B99" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C99" s="25" t="inlineStr">
         <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
         </is>
       </c>
       <c r="D99" s="25" t="inlineStr">
         <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+          <t>評価指標の読み方に影響。</t>
         </is>
       </c>
       <c r="E99" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
+          <t>doc07§8-4</t>
         </is>
       </c>
       <c r="G99" s="23" t="inlineStr">
@@ -10821,27 +10821,27 @@
       </c>
       <c r="B100" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C100" s="25" t="inlineStr">
         <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
         </is>
       </c>
       <c r="D100" s="25" t="inlineStr">
         <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
         </is>
       </c>
       <c r="E100" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F100" s="23" t="inlineStr">
         <is>
-          <t>doc17 B-3,doc18 4-3</t>
+          <t>doc08§4,§8-2</t>
         </is>
       </c>
       <c r="G100" s="23" t="inlineStr">
@@ -10859,27 +10859,27 @@
       </c>
       <c r="B101" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C101" s="25" t="inlineStr">
         <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
         </is>
       </c>
       <c r="D101" s="25" t="inlineStr">
         <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
         </is>
       </c>
       <c r="E101" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F101" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 2-9</t>
+          <t>doc02§20-1</t>
         </is>
       </c>
       <c r="G101" s="23" t="inlineStr">
@@ -10902,22 +10902,22 @@
       </c>
       <c r="C102" s="25" t="inlineStr">
         <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
         </is>
       </c>
       <c r="D102" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
         </is>
       </c>
       <c r="E102" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F102" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 5-7</t>
+          <t>doc15,doc18</t>
         </is>
       </c>
       <c r="G102" s="23" t="inlineStr">
@@ -10935,27 +10935,27 @@
       </c>
       <c r="B103" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C103" s="25" t="inlineStr">
         <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
         </is>
       </c>
       <c r="D103" s="25" t="inlineStr">
         <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
         </is>
       </c>
       <c r="E103" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-4</t>
+          <t>doc14§5,doc18 3-1</t>
         </is>
       </c>
       <c r="G103" s="23" t="inlineStr">
@@ -10973,27 +10973,27 @@
       </c>
       <c r="B104" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C104" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
         </is>
       </c>
       <c r="D104" s="25" t="inlineStr">
         <is>
-          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
         </is>
       </c>
       <c r="E104" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-73,Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F104" s="23" t="inlineStr">
         <is>
-          <t>doc01-5,doc18 1-2</t>
+          <t>doc14§5,doc15,doc18 4-5</t>
         </is>
       </c>
       <c r="G104" s="23" t="inlineStr">
@@ -11011,27 +11011,27 @@
       </c>
       <c r="B105" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C105" s="25" t="inlineStr">
         <is>
-          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
         </is>
       </c>
       <c r="D105" s="25" t="inlineStr">
         <is>
-          <t>施策の書きぶりに影響。</t>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
         </is>
       </c>
       <c r="E105" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-72</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t>doc01-12</t>
+          <t>doc17 B-3,doc18 4-3</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
@@ -11049,27 +11049,27 @@
       </c>
       <c r="B106" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C106" s="25" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
         </is>
       </c>
       <c r="D106" s="25" t="inlineStr">
         <is>
-          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
         </is>
       </c>
       <c r="E106" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F106" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-13</t>
+          <t>doc17 A-1,doc18 2-9</t>
         </is>
       </c>
       <c r="G106" s="23" t="inlineStr">
@@ -11087,27 +11087,27 @@
       </c>
       <c r="B107" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C107" s="25" t="inlineStr">
         <is>
-          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
         </is>
       </c>
       <c r="D107" s="25" t="inlineStr">
         <is>
-          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
         </is>
       </c>
       <c r="E107" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-31</t>
+          <t>Ⅱ-64,Ⅱ-75</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-6</t>
+          <t>doc17 A-1,doc18 5-7</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
@@ -11125,27 +11125,27 @@
       </c>
       <c r="B108" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C108" s="25" t="inlineStr">
         <is>
-          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
         </is>
       </c>
       <c r="D108" s="25" t="inlineStr">
         <is>
-          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
         </is>
       </c>
       <c r="E108" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-40,Ⅰ-42</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F108" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-7</t>
+          <t>doc08§8-4</t>
         </is>
       </c>
       <c r="G108" s="23" t="inlineStr">
@@ -11163,27 +11163,27 @@
       </c>
       <c r="B109" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C109" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
         </is>
       </c>
       <c r="D109" s="25" t="inlineStr">
         <is>
-          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
         </is>
       </c>
       <c r="E109" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅱ-73,Ⅱ-75</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t>doc23§1-3</t>
+          <t>doc01-5,doc18 1-2</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr">
@@ -11201,27 +11201,27 @@
       </c>
       <c r="B110" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C110" s="25" t="inlineStr">
         <is>
-          <t>送付状の個人情報に関する説明の補強</t>
+          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
         </is>
       </c>
       <c r="D110" s="25" t="inlineStr">
         <is>
-          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+          <t>施策の書きぶりに影響。</t>
         </is>
       </c>
       <c r="E110" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅱ-71,Ⅱ-72</t>
         </is>
       </c>
       <c r="F110" s="23" t="inlineStr">
         <is>
-          <t>doc27§5-1</t>
+          <t>doc01-12</t>
         </is>
       </c>
       <c r="G110" s="23" t="inlineStr">
@@ -11239,308 +11239,308 @@
       </c>
       <c r="B111" s="24" t="inlineStr">
         <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C111" s="25" t="inlineStr">
+        <is>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+        </is>
+      </c>
+      <c r="D111" s="25" t="inlineStr">
+        <is>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+        </is>
+      </c>
+      <c r="E111" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F111" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-13</t>
+        </is>
+      </c>
+      <c r="G111" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H111" s="25" t="inlineStr"/>
+    </row>
+    <row r="112" ht="34" customHeight="1">
+      <c r="A112" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B112" s="24" t="inlineStr">
+        <is>
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C111" s="25" t="inlineStr">
+      <c r="C112" s="25" t="inlineStr">
+        <is>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+        </is>
+      </c>
+      <c r="D112" s="25" t="inlineStr">
+        <is>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+        </is>
+      </c>
+      <c r="E112" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-31</t>
+        </is>
+      </c>
+      <c r="F112" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-6</t>
+        </is>
+      </c>
+      <c r="G112" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H112" s="25" t="inlineStr"/>
+    </row>
+    <row r="113" ht="34" customHeight="1">
+      <c r="A113" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B113" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C113" s="25" t="inlineStr">
+        <is>
+          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+        </is>
+      </c>
+      <c r="D113" s="25" t="inlineStr">
+        <is>
+          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+        </is>
+      </c>
+      <c r="E113" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-40,Ⅰ-42</t>
+        </is>
+      </c>
+      <c r="F113" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-7</t>
+        </is>
+      </c>
+      <c r="G113" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H113" s="25" t="inlineStr"/>
+    </row>
+    <row r="114" ht="34" customHeight="1">
+      <c r="A114" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B114" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C114" s="25" t="inlineStr">
+        <is>
+          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+        </is>
+      </c>
+      <c r="D114" s="25" t="inlineStr">
+        <is>
+          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+        </is>
+      </c>
+      <c r="E114" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-09</t>
+        </is>
+      </c>
+      <c r="F114" s="23" t="inlineStr">
+        <is>
+          <t>doc23§1-3</t>
+        </is>
+      </c>
+      <c r="G114" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H114" s="25" t="inlineStr"/>
+    </row>
+    <row r="115" ht="34" customHeight="1">
+      <c r="A115" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B115" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C115" s="25" t="inlineStr">
+        <is>
+          <t>送付状の個人情報に関する説明の補強</t>
+        </is>
+      </c>
+      <c r="D115" s="25" t="inlineStr">
+        <is>
+          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+        </is>
+      </c>
+      <c r="E115" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-14</t>
+        </is>
+      </c>
+      <c r="F115" s="23" t="inlineStr">
+        <is>
+          <t>doc27§5-1</t>
+        </is>
+      </c>
+      <c r="G115" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H115" s="25" t="inlineStr"/>
+    </row>
+    <row r="116" ht="34" customHeight="1">
+      <c r="A116" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B116" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C116" s="25" t="inlineStr">
         <is>
           <t>ニーズ調査の選択肢の表記変更5件の可否（障がい表記・ぜひ・役場・移動販売・フルタイム）</t>
         </is>
       </c>
-      <c r="D111" s="25" t="inlineStr">
+      <c r="D116" s="25" t="inlineStr">
         <is>
           <t>村の表記ルール等による変更。手引きQ&amp;Aの「通称への置き換え」に近く多くは許容されると考えるが、「買い物（移動販売等※宅配は含まない）」のみ回答の範囲を広げる方向の変更で第9期・他保険者との比較に影響し得る。</t>
         </is>
       </c>
-      <c r="E111" s="23" t="inlineStr">
+      <c r="E116" s="23" t="inlineStr">
         <is>
           <t>Ⅰ-09</t>
         </is>
       </c>
-      <c r="F111" s="23" t="inlineStr">
+      <c r="F116" s="23" t="inlineStr">
         <is>
           <t>doc27§4</t>
         </is>
       </c>
-      <c r="G111" s="23" t="inlineStr">
+      <c r="G116" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H111" s="25" t="inlineStr"/>
-    </row>
-    <row r="112" ht="34" customHeight="1">
-      <c r="A112" s="38" t="inlineStr">
+      <c r="H116" s="25" t="inlineStr"/>
+    </row>
+    <row r="117" ht="34" customHeight="1">
+      <c r="A117" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B112" s="24" t="inlineStr">
+      <c r="B117" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C112" s="25" t="inlineStr">
+      <c r="C117" s="25" t="inlineStr">
         <is>
           <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
         </is>
       </c>
-      <c r="D112" s="25" t="inlineStr">
+      <c r="D117" s="25" t="inlineStr">
         <is>
           <t>第9期はA4・本文104頁・全6章＋資料編。</t>
         </is>
       </c>
-      <c r="E112" s="23" t="inlineStr">
+      <c r="E117" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-89</t>
         </is>
       </c>
-      <c r="F112" s="23" t="inlineStr">
+      <c r="F117" s="23" t="inlineStr">
         <is>
           <t>doc01-10</t>
         </is>
       </c>
-      <c r="G112" s="23" t="inlineStr">
+      <c r="G117" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H112" s="25" t="inlineStr"/>
-    </row>
-    <row r="113" ht="34" customHeight="1">
-      <c r="A113" s="38" t="inlineStr">
+      <c r="H117" s="25" t="inlineStr"/>
+    </row>
+    <row r="118" ht="34" customHeight="1">
+      <c r="A118" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B113" s="24" t="inlineStr">
+      <c r="B118" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C113" s="25" t="inlineStr">
+      <c r="C118" s="25" t="inlineStr">
         <is>
           <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
         </is>
       </c>
-      <c r="D113" s="25" t="inlineStr">
+      <c r="D118" s="25" t="inlineStr">
         <is>
           <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
         </is>
       </c>
-      <c r="E113" s="23" t="inlineStr">
+      <c r="E118" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-92</t>
         </is>
       </c>
-      <c r="F113" s="23" t="inlineStr">
+      <c r="F118" s="23" t="inlineStr">
         <is>
           <t>doc01-10,doc08</t>
         </is>
       </c>
-      <c r="G113" s="23" t="inlineStr">
+      <c r="G118" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H113" s="25" t="inlineStr"/>
-    </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="39" t="inlineStr">
+      <c r="H118" s="25" t="inlineStr"/>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="39" t="inlineStr">
         <is>
           <t>■ 解決済み（記録）</t>
         </is>
       </c>
-    </row>
-    <row r="116" ht="34" customHeight="1">
-      <c r="A116" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B116" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C116" s="42" t="inlineStr">
-        <is>
-          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
-        </is>
-      </c>
-      <c r="D116" s="42" t="inlineStr">
-        <is>
-          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
-        </is>
-      </c>
-      <c r="E116" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-68,Ⅱ-69</t>
-        </is>
-      </c>
-      <c r="F116" s="40" t="inlineStr">
-        <is>
-          <t>doc28§3</t>
-        </is>
-      </c>
-      <c r="G116" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H116" s="42" t="inlineStr"/>
-    </row>
-    <row r="117" ht="34" customHeight="1">
-      <c r="A117" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B117" s="41" t="inlineStr">
-        <is>
-          <t>体制</t>
-        </is>
-      </c>
-      <c r="C117" s="42" t="inlineStr">
-        <is>
-          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
-        </is>
-      </c>
-      <c r="D117" s="42" t="inlineStr">
-        <is>
-          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
-        </is>
-      </c>
-      <c r="E117" s="40" t="inlineStr">
-        <is>
-          <t>０-04</t>
-        </is>
-      </c>
-      <c r="F117" s="40" t="inlineStr">
-        <is>
-          <t>doc28§4</t>
-        </is>
-      </c>
-      <c r="G117" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H117" s="42" t="inlineStr"/>
-    </row>
-    <row r="118" ht="34" customHeight="1">
-      <c r="A118" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B118" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C118" s="42" t="inlineStr">
-        <is>
-          <t>所得段階別の第1号被保険者数</t>
-        </is>
-      </c>
-      <c r="D118" s="42" t="inlineStr">
-        <is>
-          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
-        </is>
-      </c>
-      <c r="E118" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F118" s="40" t="inlineStr">
-        <is>
-          <t>doc28§2</t>
-        </is>
-      </c>
-      <c r="G118" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H118" s="42" t="inlineStr"/>
-    </row>
-    <row r="119" ht="34" customHeight="1">
-      <c r="A119" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B119" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C119" s="42" t="inlineStr">
-        <is>
-          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
-        </is>
-      </c>
-      <c r="D119" s="42" t="inlineStr">
-        <is>
-          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
-        </is>
-      </c>
-      <c r="E119" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-59</t>
-        </is>
-      </c>
-      <c r="F119" s="40" t="inlineStr">
-        <is>
-          <t>doc28§1</t>
-        </is>
-      </c>
-      <c r="G119" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H119" s="42" t="inlineStr"/>
-    </row>
-    <row r="120" ht="34" customHeight="1">
-      <c r="A120" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B120" s="41" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C120" s="42" t="inlineStr">
-        <is>
-          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
-        </is>
-      </c>
-      <c r="D120" s="42" t="inlineStr">
-        <is>
-          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
-        </is>
-      </c>
-      <c r="E120" s="40" t="inlineStr">
-        <is>
-          <t>Ⅰ-09</t>
-        </is>
-      </c>
-      <c r="F120" s="40" t="inlineStr">
-        <is>
-          <t>doc27§1-1</t>
-        </is>
-      </c>
-      <c r="G120" s="40" t="inlineStr">
-        <is>
-          <t>解決済（一部再掲）</t>
-        </is>
-      </c>
-      <c r="H120" s="42" t="inlineStr"/>
     </row>
     <row r="121" ht="34" customHeight="1">
       <c r="A121" s="40" t="inlineStr">
@@ -11550,27 +11550,27 @@
       </c>
       <c r="B121" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C121" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
+          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
         </is>
       </c>
       <c r="D121" s="42" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で両方とも修正済。</t>
+          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
         </is>
       </c>
       <c r="E121" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅱ-68,Ⅱ-69</t>
         </is>
       </c>
       <c r="F121" s="40" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc28§3</t>
         </is>
       </c>
       <c r="G121" s="40" t="inlineStr">
@@ -11588,32 +11588,32 @@
       </c>
       <c r="B122" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C122" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
+          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
         </is>
       </c>
       <c r="D122" s="42" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
+          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
         </is>
       </c>
       <c r="E122" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>０-04</t>
         </is>
       </c>
       <c r="F122" s="40" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc28§4</t>
         </is>
       </c>
       <c r="G122" s="40" t="inlineStr">
         <is>
-          <t>解決済（番号は再掲）</t>
+          <t>解決済</t>
         </is>
       </c>
       <c r="H122" s="42" t="inlineStr"/>
@@ -11626,27 +11626,27 @@
       </c>
       <c r="B123" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C123" s="42" t="inlineStr">
         <is>
-          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
+          <t>所得段階別の第1号被保険者数</t>
         </is>
       </c>
       <c r="D123" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
+          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
         </is>
       </c>
       <c r="E123" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F123" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc28§2</t>
         </is>
       </c>
       <c r="G123" s="40" t="inlineStr">
@@ -11664,27 +11664,27 @@
       </c>
       <c r="B124" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C124" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 約150人の抽出基準</t>
+          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
         </is>
       </c>
       <c r="D124" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
+          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
         </is>
       </c>
       <c r="E124" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F124" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc28§1</t>
         </is>
       </c>
       <c r="G124" s="40" t="inlineStr">
@@ -11707,27 +11707,27 @@
       </c>
       <c r="C125" s="42" t="inlineStr">
         <is>
-          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
+          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
         </is>
       </c>
       <c r="D125" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
+          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
         </is>
       </c>
       <c r="E125" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-25,Ⅰ-26</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F125" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-1</t>
         </is>
       </c>
       <c r="G125" s="40" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（一部再掲）</t>
         </is>
       </c>
       <c r="H125" s="42" t="inlineStr"/>
@@ -11740,27 +11740,27 @@
       </c>
       <c r="B126" s="41" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C126" s="42" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の範囲</t>
+          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
         </is>
       </c>
       <c r="D126" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+          <t>第2稿（0904版）で両方とも修正済。</t>
         </is>
       </c>
       <c r="E126" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F126" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G126" s="40" t="inlineStr">
@@ -11778,32 +11778,32 @@
       </c>
       <c r="B127" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C127" s="42" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
         </is>
       </c>
       <c r="D127" s="42" t="inlineStr">
         <is>
-          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
         </is>
       </c>
       <c r="E127" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F127" s="40" t="inlineStr">
         <is>
-          <t>doc20§3,§4</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G127" s="40" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（番号は再掲）</t>
         </is>
       </c>
       <c r="H127" s="42" t="inlineStr"/>
@@ -11816,27 +11816,27 @@
       </c>
       <c r="B128" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C128" s="42" t="inlineStr">
         <is>
-          <t>交付要綱の配点表（満点）</t>
+          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="D128" s="42" t="inlineStr">
         <is>
-          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
         </is>
       </c>
       <c r="E128" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F128" s="40" t="inlineStr">
         <is>
-          <t>doc20§2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G128" s="40" t="inlineStr">
@@ -11854,27 +11854,27 @@
       </c>
       <c r="B129" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C129" s="42" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の交付金評価結果</t>
+          <t>在宅介護実態調査 約150人の抽出基準</t>
         </is>
       </c>
       <c r="D129" s="42" t="inlineStr">
         <is>
-          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
         </is>
       </c>
       <c r="E129" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F129" s="40" t="inlineStr">
         <is>
-          <t>doc20§3-1</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G129" s="40" t="inlineStr">
@@ -11892,27 +11892,27 @@
       </c>
       <c r="B130" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C130" s="42" t="inlineStr">
         <is>
-          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
         </is>
       </c>
       <c r="D130" s="42" t="inlineStr">
         <is>
-          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
         </is>
       </c>
       <c r="E130" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-58</t>
+          <t>Ⅰ-25,Ⅰ-26</t>
         </is>
       </c>
       <c r="F130" s="40" t="inlineStr">
         <is>
-          <t>doc09</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G130" s="40" t="inlineStr">
@@ -11930,27 +11930,27 @@
       </c>
       <c r="B131" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C131" s="42" t="inlineStr">
         <is>
-          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+          <t>整合を図る関連計画の範囲</t>
         </is>
       </c>
       <c r="D131" s="42" t="inlineStr">
         <is>
-          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
         </is>
       </c>
       <c r="E131" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F131" s="40" t="inlineStr">
         <is>
-          <t>doc02§20-2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G131" s="40" t="inlineStr">
@@ -11973,43 +11973,233 @@
       </c>
       <c r="C132" s="42" t="inlineStr">
         <is>
+          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+        </is>
+      </c>
+      <c r="D132" s="42" t="inlineStr">
+        <is>
+          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+        </is>
+      </c>
+      <c r="E132" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F132" s="40" t="inlineStr">
+        <is>
+          <t>doc20§3,§4</t>
+        </is>
+      </c>
+      <c r="G132" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H132" s="42" t="inlineStr"/>
+    </row>
+    <row r="133" ht="34" customHeight="1">
+      <c r="A133" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B133" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C133" s="42" t="inlineStr">
+        <is>
+          <t>交付要綱の配点表（満点）</t>
+        </is>
+      </c>
+      <c r="D133" s="42" t="inlineStr">
+        <is>
+          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+        </is>
+      </c>
+      <c r="E133" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F133" s="40" t="inlineStr">
+        <is>
+          <t>doc20§2</t>
+        </is>
+      </c>
+      <c r="G133" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H133" s="42" t="inlineStr"/>
+    </row>
+    <row r="134" ht="34" customHeight="1">
+      <c r="A134" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B134" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C134" s="42" t="inlineStr">
+        <is>
+          <t>令和6年度・令和7年度の交付金評価結果</t>
+        </is>
+      </c>
+      <c r="D134" s="42" t="inlineStr">
+        <is>
+          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+        </is>
+      </c>
+      <c r="E134" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F134" s="40" t="inlineStr">
+        <is>
+          <t>doc20§3-1</t>
+        </is>
+      </c>
+      <c r="G134" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H134" s="42" t="inlineStr"/>
+    </row>
+    <row r="135" ht="34" customHeight="1">
+      <c r="A135" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B135" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C135" s="42" t="inlineStr">
+        <is>
+          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+        </is>
+      </c>
+      <c r="D135" s="42" t="inlineStr">
+        <is>
+          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+        </is>
+      </c>
+      <c r="E135" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-56,Ⅱ-58</t>
+        </is>
+      </c>
+      <c r="F135" s="40" t="inlineStr">
+        <is>
+          <t>doc09</t>
+        </is>
+      </c>
+      <c r="G135" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H135" s="42" t="inlineStr"/>
+    </row>
+    <row r="136" ht="34" customHeight="1">
+      <c r="A136" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B136" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C136" s="42" t="inlineStr">
+        <is>
+          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+        </is>
+      </c>
+      <c r="D136" s="42" t="inlineStr">
+        <is>
+          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+        </is>
+      </c>
+      <c r="E136" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-59</t>
+        </is>
+      </c>
+      <c r="F136" s="40" t="inlineStr">
+        <is>
+          <t>doc02§20-2</t>
+        </is>
+      </c>
+      <c r="G136" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H136" s="42" t="inlineStr"/>
+    </row>
+    <row r="137" ht="34" customHeight="1">
+      <c r="A137" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B137" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C137" s="42" t="inlineStr">
+        <is>
           <t>国の指針・様式の更新有無</t>
         </is>
       </c>
-      <c r="D132" s="42" t="inlineStr">
+      <c r="D137" s="42" t="inlineStr">
         <is>
           <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
-      <c r="E132" s="40" t="inlineStr">
+      <c r="E137" s="40" t="inlineStr">
         <is>
           <t>Ⅰ-11</t>
         </is>
       </c>
-      <c r="F132" s="40" t="inlineStr">
+      <c r="F137" s="40" t="inlineStr">
         <is>
           <t>doc04,doc05</t>
         </is>
       </c>
-      <c r="G132" s="40" t="inlineStr">
+      <c r="G137" s="40" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H132" s="42" t="inlineStr"/>
+      <c r="H137" s="42" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H113"/>
+  <autoFilter ref="A4:H118"/>
   <mergeCells count="3">
-    <mergeCell ref="A115:H115"/>
+    <mergeCell ref="A120:H120"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A118" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G118" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -5570,7 +5570,7 @@
       </c>
       <c r="P79" s="13" t="inlineStr">
         <is>
-          <t>doc18／output/06_計画素案.docx として全6章・65節・73表・図20点を作成。第2章の図はモノクロ印刷を前提に明度差＋線種＋マーカー＋ハッチングで識別。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。サービス区分別分析（訪問系−50.8%）を追加。★9/8：第5章5-4・5-5・5-6にサービス見込量と給付費の暫定推計値を投入（doc30）。残る空欄は保険料（5-7）と地域支援事業費の事業別内訳。</t>
+          <t>doc18／output/06_計画素案.docx として全6章・65節・73表・図20点を作成。第2章の図はモノクロ印刷を前提に明度差＋線種＋マーカー＋ハッチングで識別。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。サービス区分別分析（訪問系−50.8%）を追加。★9/8：第5章5-4・5-5・5-6にサービス見込量と給付費の暫定推計値を投入（doc30）。あわせて資料編（策定経過・委員名簿・アンケート調査の概要・パブリックコメント・用語の解説69語）を新設。残る空欄は保険料（5-7）と地域支援事業費の事業別内訳、および確定後に記入する日付・名簿。</t>
         </is>
       </c>
     </row>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -3253,7 +3253,7 @@
       </c>
       <c r="M43" s="14" t="n"/>
       <c r="N43" s="15" t="n">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="O43" s="16" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="P43" s="13" t="inlineStr">
         <is>
-          <t>★doc24でアンケート調査報告書の骨子を確定（全7章＋資料編・約118頁）。第Ⅰ部 単純集計編の掲載方式（全体／地区別／年齢階級別／前回比較／コメントの5点セット）と対象設問を確定。集計仕様書の作成は調査票の校了（9/9）後すぐに着手する。</t>
+          <t>★doc24でアンケート調査報告書の骨子を確定（全7章＋資料編・約118頁）。第Ⅰ部 単純集計編の掲載方式（全体／地区別／年齢階級別／前回比較／コメントの5点セット）と対象設問を確定。集計仕様書の作成は調査票の校了（9/9）後すぐに着手する。★9/8：集計プログラムを作成し、ダミーデータ430件で単純集計まで通した（doc31／output/10）。回答データが届いたらCSVのパスを指定するだけで集計が出る。</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="M44" s="14" t="n"/>
       <c r="N44" s="15" t="n">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="O44" s="16" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P44" s="13" t="inlineStr">
         <is>
-          <t>★doc24で全設問を地区別（北山・大塩・桧原・裏磐梯）・年齢階級別（65〜74／75〜84／85歳以上）で集計する方針を確定。移動手段・外出を控える理由・除雪は地区差が大きいと想定され施策の地区別展開の根拠になる。</t>
+          <t>★doc24で全設問を地区別（北山・大塩・桧原・裏磐梯）・年齢階級別（65〜74／75〜84／85歳以上）で集計する方針を確定。移動手段・外出を控える理由・除雪は地区差が大きいと想定され施策の地区別展開の根拠になる。★9/8：地区・年齢階級・性別・認定状況・生活機能4層の5軸で軸別集計を実装（doc31）。</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="M46" s="14" t="n"/>
       <c r="N46" s="15" t="n">
-        <v>0.45</v>
+        <v>0.65</v>
       </c>
       <c r="O46" s="16" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="P46" s="13" t="inlineStr">
         <is>
-          <t>★doc25／output/07_集計仕様書.xlsx でクロス表20件を定義（うち★10件が分析編の中核）。X-01疾病数×リスク該当領域数、X-02認定状況×リスク、X-03生活機能4層×参加意向、X-04支え合いの受領×提供、X-15施設入所検討×村内施設、X-16要介護度×就労継続。X-02とX-03は村からの認定データ（K-87）が前提。</t>
+          <t>★doc25／output/07_集計仕様書.xlsx でクロス表20件を定義（うち★10件が分析編の中核）。X-01疾病数×リスク該当領域数、X-02認定状況×リスク、X-03生活機能4層×参加意向、X-04支え合いの受領×提供、X-15施設入所検討×村内施設、X-16要介護度×就労継続。X-02とX-03は村からの認定データ（K-87）が前提。★9/8：20表のうち軸の定義が確定している9表を実装（X-01・X-02・X-04・X-05・X-06・X-12・X-15・X-16・X-17）。残りは自由記述の分類と複数回答どうしのクロスで、掲載の形を決めてから実装する。</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="M47" s="14" t="n"/>
       <c r="N47" s="15" t="n">
-        <v>0.45</v>
+        <v>0.7</v>
       </c>
       <c r="O47" s="16" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="P47" s="13" t="inlineStr">
         <is>
-          <t>★doc24§4-3で判定に用いる設問を確定（運動器・転倒・閉じこもり・低栄養・口腔・認知・IADL・うつ）。判定基準は見える化システムの算出方法に合わせる（独自基準を作ると全国・県との比較ができなくなるため）。</t>
+          <t>★doc24§4-3で判定に用いる設問を確定（運動器・転倒・閉じこもり・低栄養・口腔・認知・IADL・うつ）。判定基準は見える化システムの算出方法に合わせる（独自基準を作ると全国・県との比較ができなくなるため）。★9/8：R01〜R10・R99・D01・P01・S01/S02/S99・L01・B01・U01の20変数を実装（scripts/shukei_derive.py）。判定基準は1か所にまとめてあり、村から算出方法の提供を受けたらそこだけ直せば全集計が連動する。手引きに明記があるのは低栄養のBMI 18.5以下のみで、他9件は暫定。</t>
         </is>
       </c>
     </row>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="M49" s="14" t="n"/>
       <c r="N49" s="15" t="n">
-        <v>0.4</v>
+        <v>0.65</v>
       </c>
       <c r="O49" s="16" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="P49" s="13" t="inlineStr">
         <is>
-          <t>★doc24§5-2で仕様書4Ⅰ(6)が求めるクロスの設計を確定。軸1＝要介護度3区分、軸2＝主な介護者の勤務形態3区分。中核は「要介護度×就労継続の見通し」。村独自の問6-1（村内に施設があれば）と問6のクロスで施設の潜在需要を測る設計も確定。</t>
+          <t>★doc24§5-2で仕様書4Ⅰ(6)が求めるクロスの設計を確定。軸1＝要介護度3区分、軸2＝主な介護者の勤務形態3区分。中核は「要介護度×就労継続の見通し」。村独自の問6-1（村内に施設があれば）と問6のクロスで施設の潜在需要を測る設計も確定。★9/8：X-15（施設入所の検討状況×村内施設があれば）とX-16（要介護度×就労継続の見通し）を実装し、ダミーデータで出力を確認（doc31）。</t>
         </is>
       </c>
     </row>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -5303,7 +5303,7 @@
       </c>
       <c r="M75" s="14" t="n"/>
       <c r="N75" s="15" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="O75" s="16" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="P75" s="13" t="inlineStr">
         <is>
-          <t>doc14・doc18で施策体系（基本目標5本・施策28本）を確定。施策3-5「介護給付の適正化」を交付金配点表に基づき全面改訂（主要3事業への再編・縦覧点検4帳票満点の事実を反映）。基本目標5の独立可否は村と要協議。★9/4：資料4として委員会に諮る形に整理（基本目標5本・施策28本、区分別内訳は継続10／継続強化1／強化6／改称1／新規10）。新設10施策の根拠を1件ずつ明示。</t>
+          <t>doc14・doc18で施策体系（基本目標5本・施策28本）を確定。施策3-5「介護給付の適正化」を交付金配点表に基づき全面改訂（主要3事業への再編・縦覧点検4帳票満点の事実を反映）。基本目標5の独立可否は村と要協議。★9/4：資料4として委員会に諮る形に整理（基本目標5本・施策28本、区分別内訳は継続10／継続強化1／強化6／改称1／新規10）。新設10施策の根拠を1件ずつ明示。★9/8：給付適正化を施策3-5（取組内容）と第5章5-8（計画としての目標）の二本立てに整理。第9期は第5章にのみ置かれ施策体系の中に見えなかった課題（doc17 B-5）を解消。</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="P79" s="13" t="inlineStr">
         <is>
-          <t>doc18／output/06_計画素案.docx として全6章・65節・73表・図20点を作成。第2章の図はモノクロ印刷を前提に明度差＋線種＋マーカー＋ハッチングで識別。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。サービス区分別分析（訪問系−50.8%）を追加。★9/8：第5章5-4・5-5・5-6にサービス見込量と給付費の暫定推計値を投入（doc30）。あわせて資料編（策定経過・委員名簿・アンケート調査の概要・パブリックコメント・用語の解説69語）を新設。残る空欄は保険料（5-7）と地域支援事業費の事業別内訳、および確定後に記入する日付・名簿。</t>
+          <t>doc18／output/06_計画素案.docx として全6章・65節・73表・図20点を作成。第2章の図はモノクロ印刷を前提に明度差＋線種＋マーカー＋ハッチングで識別。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。サービス区分別分析（訪問系−50.8%）を追加。★9/8：第5章5-4・5-5・5-6にサービス見込量と給付費の暫定推計値を投入（doc30）。あわせて資料編（策定経過・委員名簿・アンケート調査の概要・パブリックコメント・用語の解説69語）を新設。★9/8：第5章の章題を仕様書・第9期の構成に合わせ「介護保険料の設定」に変更し、5-8介護給付適正化計画・5-9保険者機能強化推進交付金等の活用の2節を新設（第9期の並びに沿わせた）。全6章＋資料編・約110頁。残る空欄は保険料（5-7）、地域支援事業費の事業別内訳、交付金の交付見込額、および確定後に記入する日付・名簿。</t>
         </is>
       </c>
     </row>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$126</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="P79" s="13" t="inlineStr">
         <is>
-          <t>doc18／output/06_計画素案.docx として全6章・65節・73表・図20点を作成。第2章の図はモノクロ印刷を前提に明度差＋線種＋マーカー＋ハッチングで識別。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。サービス区分別分析（訪問系−50.8%）を追加。★9/8：第5章5-4・5-5・5-6にサービス見込量と給付費の暫定推計値を投入（doc30）。あわせて資料編（策定経過・委員名簿・アンケート調査の概要・パブリックコメント・用語の解説69語）を新設。★9/8：第5章の章題を仕様書・第9期の構成に合わせ「介護保険料の設定」に変更し、5-8介護給付適正化計画・5-9保険者機能強化推進交付金等の活用の2節を新設（第9期の並びに沿わせた）。全6章＋資料編・約110頁。残る空欄は保険料（5-7）、地域支援事業費の事業別内訳、交付金の交付見込額、および確定後に記入する日付・名簿。</t>
+          <t>doc18／output/06_計画素案.docx として全6章・65節・73表・図20点を作成。第2章の図はモノクロ印刷を前提に明度差＋線種＋マーカー＋ハッチングで識別。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。サービス区分別分析（訪問系−50.8%）を追加。★9/8：第5章5-4・5-5・5-6にサービス見込量と給付費の暫定推計値を投入（doc30）。あわせて資料編（策定経過・委員名簿・アンケート調査の概要・パブリックコメント・用語の解説69語）を新設。★9/8：第5章の章題を仕様書・第9期の構成に合わせ「介護保険料の設定」に変更し、5-8介護給付適正化計画・5-9保険者機能強化推進交付金等の活用の2節を新設（第9期の並びに沿わせた）。★9/10：法定記載事項をチェックし（doc32）、欠落5件を反映——地域密着型サービスの必要利用定員総数（介保法117条2項1号・義務）、老人福祉事業の量の目標（老福法20条の8第2項・義務、第4章4-6を新設）、地域支援事業の量の見込み（同117条2項2号・義務）、医療計画との整合（同117条5項）、高齢者虐待の防止・BCP・避難確保計画（基本指針）。あわせて給付適正化の根拠を「117条3項5号6号（努力義務）」から「117条2項3号4号（義務）」に訂正。全6章＋資料編・約115頁。残る空欄は保険料（5-7）、地域支援事業費の事業別内訳、交付金の交付見込額、および確定後に記入する日付・名簿。</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H137"/>
+  <dimension ref="A1:H145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9724,22 +9724,22 @@
       </c>
       <c r="C71" s="25" t="inlineStr">
         <is>
-          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
+          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
         </is>
       </c>
       <c r="D71" s="25" t="inlineStr">
         <is>
-          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
+          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
         </is>
       </c>
       <c r="E71" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§5-1</t>
         </is>
       </c>
       <c r="G71" s="23" t="inlineStr">
@@ -9762,22 +9762,22 @@
       </c>
       <c r="C72" s="25" t="inlineStr">
         <is>
-          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
+          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
         </is>
       </c>
       <c r="D72" s="25" t="inlineStr">
         <is>
-          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
+          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
         </is>
       </c>
       <c r="E72" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F72" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G72" s="23" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="C73" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
+          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
         </is>
       </c>
       <c r="D73" s="25" t="inlineStr">
         <is>
-          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
+          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
         </is>
       </c>
       <c r="E73" s="23" t="inlineStr">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="F73" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§5-2</t>
         </is>
       </c>
       <c r="G73" s="23" t="inlineStr">
@@ -9838,22 +9838,22 @@
       </c>
       <c r="C74" s="25" t="inlineStr">
         <is>
-          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
+          <t>第9期計画の本文（第5章81〜92ページ）</t>
         </is>
       </c>
       <c r="D74" s="25" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
+          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
         </is>
       </c>
       <c r="E74" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F74" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-65</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G74" s="23" t="inlineStr">
@@ -9876,22 +9876,22 @@
       </c>
       <c r="C75" s="25" t="inlineStr">
         <is>
-          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
+          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
         </is>
       </c>
       <c r="D75" s="25" t="inlineStr">
         <is>
-          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
+          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
         </is>
       </c>
       <c r="E75" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F75" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-68</t>
+          <t>doc32§3-3</t>
         </is>
       </c>
       <c r="G75" s="23" t="inlineStr">
@@ -9914,22 +9914,22 @@
       </c>
       <c r="C76" s="25" t="inlineStr">
         <is>
-          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
+          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
         </is>
       </c>
       <c r="D76" s="25" t="inlineStr">
         <is>
-          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
+          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
         </is>
       </c>
       <c r="E76" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F76" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-71</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G76" s="23" t="inlineStr">
@@ -9952,22 +9952,22 @@
       </c>
       <c r="C77" s="25" t="inlineStr">
         <is>
-          <t>シルバー人材センターの会員数・受注実績</t>
+          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
         </is>
       </c>
       <c r="D77" s="25" t="inlineStr">
         <is>
-          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
+          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
         </is>
       </c>
       <c r="E77" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F77" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-72</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G77" s="23" t="inlineStr">
@@ -9990,22 +9990,22 @@
       </c>
       <c r="C78" s="25" t="inlineStr">
         <is>
-          <t>第9期調査の集計基準・集計表の提供</t>
+          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
         </is>
       </c>
       <c r="D78" s="25" t="inlineStr">
         <is>
-          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
+          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
         </is>
       </c>
       <c r="E78" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F78" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-92</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G78" s="23" t="inlineStr">
@@ -10028,22 +10028,22 @@
       </c>
       <c r="C79" s="25" t="inlineStr">
         <is>
-          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
+          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
         </is>
       </c>
       <c r="D79" s="25" t="inlineStr">
         <is>
-          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
+          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
         </is>
       </c>
       <c r="E79" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-109</t>
+          <t>doc20§6-2 K-65</t>
         </is>
       </c>
       <c r="G79" s="23" t="inlineStr">
@@ -10066,22 +10066,22 @@
       </c>
       <c r="C80" s="25" t="inlineStr">
         <is>
-          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
+          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
         </is>
       </c>
       <c r="D80" s="25" t="inlineStr">
         <is>
-          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
+          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
         </is>
       </c>
       <c r="E80" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F80" s="23" t="inlineStr">
         <is>
-          <t>doc28§2 K-110</t>
+          <t>doc21§5 K-68</t>
         </is>
       </c>
       <c r="G80" s="23" t="inlineStr">
@@ -10099,27 +10099,27 @@
       </c>
       <c r="B81" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C81" s="25" t="inlineStr">
         <is>
-          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
+          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
         </is>
       </c>
       <c r="D81" s="25" t="inlineStr">
         <is>
-          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
+          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
         </is>
       </c>
       <c r="E81" s="23" t="inlineStr">
         <is>
-          <t>Ⅴ-95</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-67</t>
+          <t>doc21§5 K-71</t>
         </is>
       </c>
       <c r="G81" s="23" t="inlineStr">
@@ -10137,27 +10137,27 @@
       </c>
       <c r="B82" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C82" s="25" t="inlineStr">
         <is>
-          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
+          <t>シルバー人材センターの会員数・受注実績</t>
         </is>
       </c>
       <c r="D82" s="25" t="inlineStr">
         <is>
-          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
+          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
         </is>
       </c>
       <c r="E82" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-35</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F82" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-93</t>
+          <t>doc21§5 K-72</t>
         </is>
       </c>
       <c r="G82" s="23" t="inlineStr">
@@ -10175,27 +10175,27 @@
       </c>
       <c r="B83" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C83" s="25" t="inlineStr">
         <is>
-          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
+          <t>第9期調査の集計基準・集計表の提供</t>
         </is>
       </c>
       <c r="D83" s="25" t="inlineStr">
         <is>
-          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
+          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
         </is>
       </c>
       <c r="E83" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-48</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-94</t>
+          <t>doc25§8 K-92</t>
         </is>
       </c>
       <c r="G83" s="23" t="inlineStr">
@@ -10213,27 +10213,27 @@
       </c>
       <c r="B84" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C84" s="25" t="inlineStr">
         <is>
-          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
+          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
         </is>
       </c>
       <c r="D84" s="25" t="inlineStr">
         <is>
-          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
+          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
         </is>
       </c>
       <c r="E84" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F84" s="23" t="inlineStr">
         <is>
-          <t>doc19 指-5</t>
+          <t>doc28§3-4 K-109</t>
         </is>
       </c>
       <c r="G84" s="23" t="inlineStr">
@@ -10251,27 +10251,27 @@
       </c>
       <c r="B85" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C85" s="25" t="inlineStr">
         <is>
-          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
+          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
         </is>
       </c>
       <c r="D85" s="25" t="inlineStr">
         <is>
-          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
+          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
         </is>
       </c>
       <c r="E85" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-108</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t>doc22 K-80</t>
+          <t>doc28§2 K-110</t>
         </is>
       </c>
       <c r="G85" s="23" t="inlineStr">
@@ -10289,27 +10289,27 @@
       </c>
       <c r="B86" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C86" s="25" t="inlineStr">
         <is>
-          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
+          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
         </is>
       </c>
       <c r="D86" s="25" t="inlineStr">
         <is>
-          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
+          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
         </is>
       </c>
       <c r="E86" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-90</t>
+          <t>Ⅴ-95</t>
         </is>
       </c>
       <c r="F86" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-88</t>
+          <t>doc20§6-2 K-67</t>
         </is>
       </c>
       <c r="G86" s="23" t="inlineStr">
@@ -10327,27 +10327,27 @@
       </c>
       <c r="B87" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C87" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
+          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
         </is>
       </c>
       <c r="D87" s="25" t="inlineStr">
         <is>
-          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
+          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
         </is>
       </c>
       <c r="E87" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅰ-35</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr">
         <is>
-          <t>doc09§4,§10</t>
+          <t>doc25§8 K-93</t>
         </is>
       </c>
       <c r="G87" s="23" t="inlineStr">
@@ -10365,27 +10365,27 @@
       </c>
       <c r="B88" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C88" s="25" t="inlineStr">
         <is>
-          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
+          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
         </is>
       </c>
       <c r="D88" s="25" t="inlineStr">
         <is>
-          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
+          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
         </is>
       </c>
       <c r="E88" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅰ-48</t>
         </is>
       </c>
       <c r="F88" s="23" t="inlineStr">
         <is>
-          <t>doc09§8,§10</t>
+          <t>doc25§8 K-94</t>
         </is>
       </c>
       <c r="G88" s="23" t="inlineStr">
@@ -10403,27 +10403,27 @@
       </c>
       <c r="B89" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C89" s="25" t="inlineStr">
         <is>
-          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
+          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
         </is>
       </c>
       <c r="D89" s="25" t="inlineStr">
         <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
+          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
         </is>
       </c>
       <c r="E89" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t>doc02§17,doc07,doc18 4-1</t>
+          <t>doc19 指-5</t>
         </is>
       </c>
       <c r="G89" s="23" t="inlineStr">
@@ -10441,27 +10441,27 @@
       </c>
       <c r="B90" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C90" s="25" t="inlineStr">
         <is>
-          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
+          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
         </is>
       </c>
       <c r="D90" s="25" t="inlineStr">
         <is>
-          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
+          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
         </is>
       </c>
       <c r="E90" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-75</t>
+          <t>Ⅱ-108</t>
         </is>
       </c>
       <c r="F90" s="23" t="inlineStr">
         <is>
-          <t>doc17 C-1,doc02§20-2</t>
+          <t>doc22 K-80</t>
         </is>
       </c>
       <c r="G90" s="23" t="inlineStr">
@@ -10479,27 +10479,27 @@
       </c>
       <c r="B91" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C91" s="25" t="inlineStr">
         <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
         </is>
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
+          <t>Ⅳ-90</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t>doc13§6</t>
+          <t>doc24§12 K-88</t>
         </is>
       </c>
       <c r="G91" s="23" t="inlineStr">
@@ -10522,22 +10522,22 @@
       </c>
       <c r="C92" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
+          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
         </is>
       </c>
       <c r="D92" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
+          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
         </is>
       </c>
       <c r="E92" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F92" s="23" t="inlineStr">
         <is>
-          <t>doc30§4-2,doc18 5-4</t>
+          <t>doc09§4,§10</t>
         </is>
       </c>
       <c r="G92" s="23" t="inlineStr">
@@ -10560,22 +10560,22 @@
       </c>
       <c r="C93" s="25" t="inlineStr">
         <is>
-          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
+          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
         </is>
       </c>
       <c r="D93" s="25" t="inlineStr">
         <is>
-          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
+          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
         </is>
       </c>
       <c r="E93" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-4</t>
+          <t>doc09§8,§10</t>
         </is>
       </c>
       <c r="G93" s="23" t="inlineStr">
@@ -10598,22 +10598,22 @@
       </c>
       <c r="C94" s="25" t="inlineStr">
         <is>
-          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
         </is>
       </c>
       <c r="D94" s="25" t="inlineStr">
         <is>
-          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
         </is>
       </c>
       <c r="E94" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F94" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-14</t>
+          <t>doc02§17,doc07,doc18 4-1</t>
         </is>
       </c>
       <c r="G94" s="23" t="inlineStr">
@@ -10636,22 +10636,22 @@
       </c>
       <c r="C95" s="25" t="inlineStr">
         <is>
-          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
         </is>
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
         </is>
       </c>
       <c r="E95" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-56,Ⅱ-75</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t>doc19 §3</t>
+          <t>doc17 C-1,doc02§20-2</t>
         </is>
       </c>
       <c r="G95" s="23" t="inlineStr">
@@ -10674,22 +10674,22 @@
       </c>
       <c r="C96" s="25" t="inlineStr">
         <is>
-          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
         </is>
       </c>
       <c r="D96" s="25" t="inlineStr">
         <is>
-          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
         </is>
       </c>
       <c r="E96" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-60,Ⅱ-65</t>
         </is>
       </c>
       <c r="F96" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-73</t>
+          <t>doc13§6</t>
         </is>
       </c>
       <c r="G96" s="23" t="inlineStr">
@@ -10712,22 +10712,22 @@
       </c>
       <c r="C97" s="25" t="inlineStr">
         <is>
-          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
+          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
         </is>
       </c>
       <c r="D97" s="25" t="inlineStr">
         <is>
-          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
+          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
         </is>
       </c>
       <c r="E97" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-105</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-90</t>
+          <t>doc30§4-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr">
@@ -10745,27 +10745,27 @@
       </c>
       <c r="B98" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C98" s="25" t="inlineStr">
         <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
         </is>
       </c>
       <c r="D98" s="25" t="inlineStr">
         <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
         </is>
       </c>
       <c r="E98" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53,Ⅱ-57</t>
         </is>
       </c>
       <c r="F98" s="23" t="inlineStr">
         <is>
-          <t>doc07§4</t>
+          <t>doc32§7</t>
         </is>
       </c>
       <c r="G98" s="23" t="inlineStr">
@@ -10783,27 +10783,27 @@
       </c>
       <c r="B99" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C99" s="25" t="inlineStr">
         <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
         </is>
       </c>
       <c r="D99" s="25" t="inlineStr">
         <is>
-          <t>評価指標の読み方に影響。</t>
+          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
         </is>
       </c>
       <c r="E99" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
         <is>
-          <t>doc07§8-4</t>
+          <t>doc32§3-1</t>
         </is>
       </c>
       <c r="G99" s="23" t="inlineStr">
@@ -10821,27 +10821,27 @@
       </c>
       <c r="B100" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C100" s="25" t="inlineStr">
         <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
         </is>
       </c>
       <c r="D100" s="25" t="inlineStr">
         <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
         </is>
       </c>
       <c r="E100" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F100" s="23" t="inlineStr">
         <is>
-          <t>doc08§4,§8-2</t>
+          <t>doc30§5-4</t>
         </is>
       </c>
       <c r="G100" s="23" t="inlineStr">
@@ -10859,27 +10859,27 @@
       </c>
       <c r="B101" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C101" s="25" t="inlineStr">
         <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
         </is>
       </c>
       <c r="D101" s="25" t="inlineStr">
         <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
         </is>
       </c>
       <c r="E101" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F101" s="23" t="inlineStr">
         <is>
-          <t>doc02§20-1</t>
+          <t>doc19 追-14</t>
         </is>
       </c>
       <c r="G101" s="23" t="inlineStr">
@@ -10897,27 +10897,27 @@
       </c>
       <c r="B102" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C102" s="25" t="inlineStr">
         <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
         </is>
       </c>
       <c r="D102" s="25" t="inlineStr">
         <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
         </is>
       </c>
       <c r="E102" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F102" s="23" t="inlineStr">
         <is>
-          <t>doc15,doc18</t>
+          <t>doc19 §3</t>
         </is>
       </c>
       <c r="G102" s="23" t="inlineStr">
@@ -10935,27 +10935,27 @@
       </c>
       <c r="B103" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C103" s="25" t="inlineStr">
         <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
         </is>
       </c>
       <c r="D103" s="25" t="inlineStr">
         <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
         </is>
       </c>
       <c r="E103" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc18 3-1</t>
+          <t>doc21§5 K-73</t>
         </is>
       </c>
       <c r="G103" s="23" t="inlineStr">
@@ -10973,27 +10973,27 @@
       </c>
       <c r="B104" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C104" s="25" t="inlineStr">
         <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
         </is>
       </c>
       <c r="D104" s="25" t="inlineStr">
         <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
         </is>
       </c>
       <c r="E104" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-105</t>
         </is>
       </c>
       <c r="F104" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
+          <t>doc24§12 K-90</t>
         </is>
       </c>
       <c r="G104" s="23" t="inlineStr">
@@ -11011,27 +11011,27 @@
       </c>
       <c r="B105" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C105" s="25" t="inlineStr">
         <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
         </is>
       </c>
       <c r="D105" s="25" t="inlineStr">
         <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
         </is>
       </c>
       <c r="E105" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t>doc17 B-3,doc18 4-3</t>
+          <t>doc07§4</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
@@ -11049,27 +11049,27 @@
       </c>
       <c r="B106" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C106" s="25" t="inlineStr">
         <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
         </is>
       </c>
       <c r="D106" s="25" t="inlineStr">
         <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+          <t>評価指標の読み方に影響。</t>
         </is>
       </c>
       <c r="E106" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F106" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 2-9</t>
+          <t>doc07§8-4</t>
         </is>
       </c>
       <c r="G106" s="23" t="inlineStr">
@@ -11087,27 +11087,27 @@
       </c>
       <c r="B107" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C107" s="25" t="inlineStr">
         <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
         </is>
       </c>
       <c r="D107" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
         </is>
       </c>
       <c r="E107" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 5-7</t>
+          <t>doc08§4,§8-2</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
@@ -11125,27 +11125,27 @@
       </c>
       <c r="B108" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C108" s="25" t="inlineStr">
         <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
         </is>
       </c>
       <c r="D108" s="25" t="inlineStr">
         <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
         </is>
       </c>
       <c r="E108" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F108" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-4</t>
+          <t>doc02§20-1</t>
         </is>
       </c>
       <c r="G108" s="23" t="inlineStr">
@@ -11163,27 +11163,27 @@
       </c>
       <c r="B109" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C109" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
         </is>
       </c>
       <c r="D109" s="25" t="inlineStr">
         <is>
-          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
         </is>
       </c>
       <c r="E109" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-73,Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t>doc01-5,doc18 1-2</t>
+          <t>doc32§1,§2</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr">
@@ -11201,27 +11201,27 @@
       </c>
       <c r="B110" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C110" s="25" t="inlineStr">
         <is>
-          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
         </is>
       </c>
       <c r="D110" s="25" t="inlineStr">
         <is>
-          <t>施策の書きぶりに影響。</t>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
         </is>
       </c>
       <c r="E110" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-72</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F110" s="23" t="inlineStr">
         <is>
-          <t>doc01-12</t>
+          <t>doc15,doc18</t>
         </is>
       </c>
       <c r="G110" s="23" t="inlineStr">
@@ -11239,27 +11239,27 @@
       </c>
       <c r="B111" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C111" s="25" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
         </is>
       </c>
       <c r="D111" s="25" t="inlineStr">
         <is>
-          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
         </is>
       </c>
       <c r="E111" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-13</t>
+          <t>doc14§5,doc18 3-1</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
@@ -11277,27 +11277,27 @@
       </c>
       <c r="B112" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C112" s="25" t="inlineStr">
         <is>
-          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
         </is>
       </c>
       <c r="D112" s="25" t="inlineStr">
         <is>
-          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
         </is>
       </c>
       <c r="E112" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-31</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F112" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-6</t>
+          <t>doc14§5,doc15,doc18 4-5</t>
         </is>
       </c>
       <c r="G112" s="23" t="inlineStr">
@@ -11315,27 +11315,27 @@
       </c>
       <c r="B113" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C113" s="25" t="inlineStr">
         <is>
-          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
         </is>
       </c>
       <c r="D113" s="25" t="inlineStr">
         <is>
-          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
         </is>
       </c>
       <c r="E113" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-40,Ⅰ-42</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-7</t>
+          <t>doc17 B-3,doc18 4-3</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -11353,27 +11353,27 @@
       </c>
       <c r="B114" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C114" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
         </is>
       </c>
       <c r="D114" s="25" t="inlineStr">
         <is>
-          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
         </is>
       </c>
       <c r="E114" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F114" s="23" t="inlineStr">
         <is>
-          <t>doc23§1-3</t>
+          <t>doc17 A-1,doc18 2-9</t>
         </is>
       </c>
       <c r="G114" s="23" t="inlineStr">
@@ -11391,27 +11391,27 @@
       </c>
       <c r="B115" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C115" s="25" t="inlineStr">
         <is>
-          <t>送付状の個人情報に関する説明の補強</t>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
         </is>
       </c>
       <c r="D115" s="25" t="inlineStr">
         <is>
-          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
         </is>
       </c>
       <c r="E115" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅱ-64,Ⅱ-75</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t>doc27§5-1</t>
+          <t>doc17 A-1,doc18 5-7</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -11429,422 +11429,422 @@
       </c>
       <c r="B116" s="24" t="inlineStr">
         <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C116" s="25" t="inlineStr">
+        <is>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
+        </is>
+      </c>
+      <c r="D116" s="25" t="inlineStr">
+        <is>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+        </is>
+      </c>
+      <c r="E116" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F116" s="23" t="inlineStr">
+        <is>
+          <t>doc08§8-4</t>
+        </is>
+      </c>
+      <c r="G116" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H116" s="25" t="inlineStr"/>
+    </row>
+    <row r="117" ht="34" customHeight="1">
+      <c r="A117" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B117" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C117" s="25" t="inlineStr">
+        <is>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+        </is>
+      </c>
+      <c r="D117" s="25" t="inlineStr">
+        <is>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+        </is>
+      </c>
+      <c r="E117" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-73,Ⅱ-75</t>
+        </is>
+      </c>
+      <c r="F117" s="23" t="inlineStr">
+        <is>
+          <t>doc01-5,doc18 1-2</t>
+        </is>
+      </c>
+      <c r="G117" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H117" s="25" t="inlineStr"/>
+    </row>
+    <row r="118" ht="34" customHeight="1">
+      <c r="A118" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B118" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C118" s="25" t="inlineStr">
+        <is>
+          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+        </is>
+      </c>
+      <c r="D118" s="25" t="inlineStr">
+        <is>
+          <t>施策の書きぶりに影響。</t>
+        </is>
+      </c>
+      <c r="E118" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-71,Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F118" s="23" t="inlineStr">
+        <is>
+          <t>doc01-12</t>
+        </is>
+      </c>
+      <c r="G118" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H118" s="25" t="inlineStr"/>
+    </row>
+    <row r="119" ht="34" customHeight="1">
+      <c r="A119" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B119" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C119" s="25" t="inlineStr">
+        <is>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+        </is>
+      </c>
+      <c r="D119" s="25" t="inlineStr">
+        <is>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+        </is>
+      </c>
+      <c r="E119" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F119" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-13</t>
+        </is>
+      </c>
+      <c r="G119" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H119" s="25" t="inlineStr"/>
+    </row>
+    <row r="120" ht="34" customHeight="1">
+      <c r="A120" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B120" s="24" t="inlineStr">
+        <is>
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C116" s="25" t="inlineStr">
+      <c r="C120" s="25" t="inlineStr">
+        <is>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+        </is>
+      </c>
+      <c r="D120" s="25" t="inlineStr">
+        <is>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+        </is>
+      </c>
+      <c r="E120" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-31</t>
+        </is>
+      </c>
+      <c r="F120" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-6</t>
+        </is>
+      </c>
+      <c r="G120" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H120" s="25" t="inlineStr"/>
+    </row>
+    <row r="121" ht="34" customHeight="1">
+      <c r="A121" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B121" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C121" s="25" t="inlineStr">
+        <is>
+          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+        </is>
+      </c>
+      <c r="D121" s="25" t="inlineStr">
+        <is>
+          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+        </is>
+      </c>
+      <c r="E121" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-40,Ⅰ-42</t>
+        </is>
+      </c>
+      <c r="F121" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-7</t>
+        </is>
+      </c>
+      <c r="G121" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H121" s="25" t="inlineStr"/>
+    </row>
+    <row r="122" ht="34" customHeight="1">
+      <c r="A122" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B122" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C122" s="25" t="inlineStr">
+        <is>
+          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+        </is>
+      </c>
+      <c r="D122" s="25" t="inlineStr">
+        <is>
+          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+        </is>
+      </c>
+      <c r="E122" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-09</t>
+        </is>
+      </c>
+      <c r="F122" s="23" t="inlineStr">
+        <is>
+          <t>doc23§1-3</t>
+        </is>
+      </c>
+      <c r="G122" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H122" s="25" t="inlineStr"/>
+    </row>
+    <row r="123" ht="34" customHeight="1">
+      <c r="A123" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B123" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C123" s="25" t="inlineStr">
+        <is>
+          <t>送付状の個人情報に関する説明の補強</t>
+        </is>
+      </c>
+      <c r="D123" s="25" t="inlineStr">
+        <is>
+          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+        </is>
+      </c>
+      <c r="E123" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-14</t>
+        </is>
+      </c>
+      <c r="F123" s="23" t="inlineStr">
+        <is>
+          <t>doc27§5-1</t>
+        </is>
+      </c>
+      <c r="G123" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H123" s="25" t="inlineStr"/>
+    </row>
+    <row r="124" ht="34" customHeight="1">
+      <c r="A124" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B124" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C124" s="25" t="inlineStr">
         <is>
           <t>ニーズ調査の選択肢の表記変更5件の可否（障がい表記・ぜひ・役場・移動販売・フルタイム）</t>
         </is>
       </c>
-      <c r="D116" s="25" t="inlineStr">
+      <c r="D124" s="25" t="inlineStr">
         <is>
           <t>村の表記ルール等による変更。手引きQ&amp;Aの「通称への置き換え」に近く多くは許容されると考えるが、「買い物（移動販売等※宅配は含まない）」のみ回答の範囲を広げる方向の変更で第9期・他保険者との比較に影響し得る。</t>
         </is>
       </c>
-      <c r="E116" s="23" t="inlineStr">
+      <c r="E124" s="23" t="inlineStr">
         <is>
           <t>Ⅰ-09</t>
         </is>
       </c>
-      <c r="F116" s="23" t="inlineStr">
+      <c r="F124" s="23" t="inlineStr">
         <is>
           <t>doc27§4</t>
         </is>
       </c>
-      <c r="G116" s="23" t="inlineStr">
+      <c r="G124" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H116" s="25" t="inlineStr"/>
-    </row>
-    <row r="117" ht="34" customHeight="1">
-      <c r="A117" s="38" t="inlineStr">
+      <c r="H124" s="25" t="inlineStr"/>
+    </row>
+    <row r="125" ht="34" customHeight="1">
+      <c r="A125" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B117" s="24" t="inlineStr">
+      <c r="B125" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C117" s="25" t="inlineStr">
+      <c r="C125" s="25" t="inlineStr">
         <is>
           <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
         </is>
       </c>
-      <c r="D117" s="25" t="inlineStr">
+      <c r="D125" s="25" t="inlineStr">
         <is>
           <t>第9期はA4・本文104頁・全6章＋資料編。</t>
         </is>
       </c>
-      <c r="E117" s="23" t="inlineStr">
+      <c r="E125" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-89</t>
         </is>
       </c>
-      <c r="F117" s="23" t="inlineStr">
+      <c r="F125" s="23" t="inlineStr">
         <is>
           <t>doc01-10</t>
         </is>
       </c>
-      <c r="G117" s="23" t="inlineStr">
+      <c r="G125" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H117" s="25" t="inlineStr"/>
-    </row>
-    <row r="118" ht="34" customHeight="1">
-      <c r="A118" s="38" t="inlineStr">
+      <c r="H125" s="25" t="inlineStr"/>
+    </row>
+    <row r="126" ht="34" customHeight="1">
+      <c r="A126" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B118" s="24" t="inlineStr">
+      <c r="B126" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C118" s="25" t="inlineStr">
+      <c r="C126" s="25" t="inlineStr">
         <is>
           <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
         </is>
       </c>
-      <c r="D118" s="25" t="inlineStr">
+      <c r="D126" s="25" t="inlineStr">
         <is>
           <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
         </is>
       </c>
-      <c r="E118" s="23" t="inlineStr">
+      <c r="E126" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-92</t>
         </is>
       </c>
-      <c r="F118" s="23" t="inlineStr">
+      <c r="F126" s="23" t="inlineStr">
         <is>
           <t>doc01-10,doc08</t>
         </is>
       </c>
-      <c r="G118" s="23" t="inlineStr">
+      <c r="G126" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H118" s="25" t="inlineStr"/>
-    </row>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="39" t="inlineStr">
+      <c r="H126" s="25" t="inlineStr"/>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="39" t="inlineStr">
         <is>
           <t>■ 解決済み（記録）</t>
         </is>
       </c>
-    </row>
-    <row r="121" ht="34" customHeight="1">
-      <c r="A121" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B121" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C121" s="42" t="inlineStr">
-        <is>
-          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
-        </is>
-      </c>
-      <c r="D121" s="42" t="inlineStr">
-        <is>
-          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
-        </is>
-      </c>
-      <c r="E121" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-68,Ⅱ-69</t>
-        </is>
-      </c>
-      <c r="F121" s="40" t="inlineStr">
-        <is>
-          <t>doc28§3</t>
-        </is>
-      </c>
-      <c r="G121" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H121" s="42" t="inlineStr"/>
-    </row>
-    <row r="122" ht="34" customHeight="1">
-      <c r="A122" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B122" s="41" t="inlineStr">
-        <is>
-          <t>体制</t>
-        </is>
-      </c>
-      <c r="C122" s="42" t="inlineStr">
-        <is>
-          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
-        </is>
-      </c>
-      <c r="D122" s="42" t="inlineStr">
-        <is>
-          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
-        </is>
-      </c>
-      <c r="E122" s="40" t="inlineStr">
-        <is>
-          <t>０-04</t>
-        </is>
-      </c>
-      <c r="F122" s="40" t="inlineStr">
-        <is>
-          <t>doc28§4</t>
-        </is>
-      </c>
-      <c r="G122" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H122" s="42" t="inlineStr"/>
-    </row>
-    <row r="123" ht="34" customHeight="1">
-      <c r="A123" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B123" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C123" s="42" t="inlineStr">
-        <is>
-          <t>所得段階別の第1号被保険者数</t>
-        </is>
-      </c>
-      <c r="D123" s="42" t="inlineStr">
-        <is>
-          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
-        </is>
-      </c>
-      <c r="E123" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F123" s="40" t="inlineStr">
-        <is>
-          <t>doc28§2</t>
-        </is>
-      </c>
-      <c r="G123" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H123" s="42" t="inlineStr"/>
-    </row>
-    <row r="124" ht="34" customHeight="1">
-      <c r="A124" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B124" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C124" s="42" t="inlineStr">
-        <is>
-          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
-        </is>
-      </c>
-      <c r="D124" s="42" t="inlineStr">
-        <is>
-          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
-        </is>
-      </c>
-      <c r="E124" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-59</t>
-        </is>
-      </c>
-      <c r="F124" s="40" t="inlineStr">
-        <is>
-          <t>doc28§1</t>
-        </is>
-      </c>
-      <c r="G124" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H124" s="42" t="inlineStr"/>
-    </row>
-    <row r="125" ht="34" customHeight="1">
-      <c r="A125" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B125" s="41" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C125" s="42" t="inlineStr">
-        <is>
-          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
-        </is>
-      </c>
-      <c r="D125" s="42" t="inlineStr">
-        <is>
-          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
-        </is>
-      </c>
-      <c r="E125" s="40" t="inlineStr">
-        <is>
-          <t>Ⅰ-09</t>
-        </is>
-      </c>
-      <c r="F125" s="40" t="inlineStr">
-        <is>
-          <t>doc27§1-1</t>
-        </is>
-      </c>
-      <c r="G125" s="40" t="inlineStr">
-        <is>
-          <t>解決済（一部再掲）</t>
-        </is>
-      </c>
-      <c r="H125" s="42" t="inlineStr"/>
-    </row>
-    <row r="126" ht="34" customHeight="1">
-      <c r="A126" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B126" s="41" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C126" s="42" t="inlineStr">
-        <is>
-          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
-        </is>
-      </c>
-      <c r="D126" s="42" t="inlineStr">
-        <is>
-          <t>第2稿（0904版）で両方とも修正済。</t>
-        </is>
-      </c>
-      <c r="E126" s="40" t="inlineStr">
-        <is>
-          <t>Ⅰ-10</t>
-        </is>
-      </c>
-      <c r="F126" s="40" t="inlineStr">
-        <is>
-          <t>doc27§1-2</t>
-        </is>
-      </c>
-      <c r="G126" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H126" s="42" t="inlineStr"/>
-    </row>
-    <row r="127" ht="34" customHeight="1">
-      <c r="A127" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B127" s="41" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C127" s="42" t="inlineStr">
-        <is>
-          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
-        </is>
-      </c>
-      <c r="D127" s="42" t="inlineStr">
-        <is>
-          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
-        </is>
-      </c>
-      <c r="E127" s="40" t="inlineStr">
-        <is>
-          <t>Ⅰ-10</t>
-        </is>
-      </c>
-      <c r="F127" s="40" t="inlineStr">
-        <is>
-          <t>doc27§1-2</t>
-        </is>
-      </c>
-      <c r="G127" s="40" t="inlineStr">
-        <is>
-          <t>解決済（番号は再掲）</t>
-        </is>
-      </c>
-      <c r="H127" s="42" t="inlineStr"/>
-    </row>
-    <row r="128" ht="34" customHeight="1">
-      <c r="A128" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B128" s="41" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C128" s="42" t="inlineStr">
-        <is>
-          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
-        </is>
-      </c>
-      <c r="D128" s="42" t="inlineStr">
-        <is>
-          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
-        </is>
-      </c>
-      <c r="E128" s="40" t="inlineStr">
-        <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
-        </is>
-      </c>
-      <c r="F128" s="40" t="inlineStr">
-        <is>
-          <t>doc22 §1</t>
-        </is>
-      </c>
-      <c r="G128" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H128" s="42" t="inlineStr"/>
     </row>
     <row r="129" ht="34" customHeight="1">
       <c r="A129" s="40" t="inlineStr">
@@ -11854,27 +11854,27 @@
       </c>
       <c r="B129" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C129" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 約150人の抽出基準</t>
+          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
         </is>
       </c>
       <c r="D129" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
+          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
         </is>
       </c>
       <c r="E129" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅱ-68,Ⅱ-69</t>
         </is>
       </c>
       <c r="F129" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc28§3</t>
         </is>
       </c>
       <c r="G129" s="40" t="inlineStr">
@@ -11892,27 +11892,27 @@
       </c>
       <c r="B130" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C130" s="42" t="inlineStr">
         <is>
-          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
+          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
         </is>
       </c>
       <c r="D130" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
+          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
         </is>
       </c>
       <c r="E130" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-25,Ⅰ-26</t>
+          <t>０-04</t>
         </is>
       </c>
       <c r="F130" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc28§4</t>
         </is>
       </c>
       <c r="G130" s="40" t="inlineStr">
@@ -11930,27 +11930,27 @@
       </c>
       <c r="B131" s="41" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C131" s="42" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の範囲</t>
+          <t>所得段階別の第1号被保険者数</t>
         </is>
       </c>
       <c r="D131" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
         </is>
       </c>
       <c r="E131" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F131" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc28§2</t>
         </is>
       </c>
       <c r="G131" s="40" t="inlineStr">
@@ -11973,22 +11973,22 @@
       </c>
       <c r="C132" s="42" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
         </is>
       </c>
       <c r="D132" s="42" t="inlineStr">
         <is>
-          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
         </is>
       </c>
       <c r="E132" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F132" s="40" t="inlineStr">
         <is>
-          <t>doc20§3,§4</t>
+          <t>doc28§1</t>
         </is>
       </c>
       <c r="G132" s="40" t="inlineStr">
@@ -12006,32 +12006,32 @@
       </c>
       <c r="B133" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C133" s="42" t="inlineStr">
         <is>
-          <t>交付要綱の配点表（満点）</t>
+          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
         </is>
       </c>
       <c r="D133" s="42" t="inlineStr">
         <is>
-          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
         </is>
       </c>
       <c r="E133" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F133" s="40" t="inlineStr">
         <is>
-          <t>doc20§2</t>
+          <t>doc27§1-1</t>
         </is>
       </c>
       <c r="G133" s="40" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（一部再掲）</t>
         </is>
       </c>
       <c r="H133" s="42" t="inlineStr"/>
@@ -12044,27 +12044,27 @@
       </c>
       <c r="B134" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C134" s="42" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の交付金評価結果</t>
+          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
         </is>
       </c>
       <c r="D134" s="42" t="inlineStr">
         <is>
-          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+          <t>第2稿（0904版）で両方とも修正済。</t>
         </is>
       </c>
       <c r="E134" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F134" s="40" t="inlineStr">
         <is>
-          <t>doc20§3-1</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G134" s="40" t="inlineStr">
@@ -12082,32 +12082,32 @@
       </c>
       <c r="B135" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C135" s="42" t="inlineStr">
         <is>
-          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
         </is>
       </c>
       <c r="D135" s="42" t="inlineStr">
         <is>
-          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
         </is>
       </c>
       <c r="E135" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-58</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F135" s="40" t="inlineStr">
         <is>
-          <t>doc09</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G135" s="40" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（番号は再掲）</t>
         </is>
       </c>
       <c r="H135" s="42" t="inlineStr"/>
@@ -12120,27 +12120,27 @@
       </c>
       <c r="B136" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C136" s="42" t="inlineStr">
         <is>
-          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="D136" s="42" t="inlineStr">
         <is>
-          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
         </is>
       </c>
       <c r="E136" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F136" s="40" t="inlineStr">
         <is>
-          <t>doc02§20-2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G136" s="40" t="inlineStr">
@@ -12158,48 +12158,352 @@
       </c>
       <c r="B137" s="41" t="inlineStr">
         <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C137" s="42" t="inlineStr">
+        <is>
+          <t>在宅介護実態調査 約150人の抽出基準</t>
+        </is>
+      </c>
+      <c r="D137" s="42" t="inlineStr">
+        <is>
+          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
+        </is>
+      </c>
+      <c r="E137" s="40" t="inlineStr">
+        <is>
+          <t>Ⅰ-08,Ⅰ-24</t>
+        </is>
+      </c>
+      <c r="F137" s="40" t="inlineStr">
+        <is>
+          <t>doc22 §1</t>
+        </is>
+      </c>
+      <c r="G137" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H137" s="42" t="inlineStr"/>
+    </row>
+    <row r="138" ht="34" customHeight="1">
+      <c r="A138" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B138" s="41" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C138" s="42" t="inlineStr">
+        <is>
+          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
+        </is>
+      </c>
+      <c r="D138" s="42" t="inlineStr">
+        <is>
+          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
+        </is>
+      </c>
+      <c r="E138" s="40" t="inlineStr">
+        <is>
+          <t>Ⅰ-25,Ⅰ-26</t>
+        </is>
+      </c>
+      <c r="F138" s="40" t="inlineStr">
+        <is>
+          <t>doc22 §1</t>
+        </is>
+      </c>
+      <c r="G138" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H138" s="42" t="inlineStr"/>
+    </row>
+    <row r="139" ht="34" customHeight="1">
+      <c r="A139" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B139" s="41" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C139" s="42" t="inlineStr">
+        <is>
+          <t>整合を図る関連計画の範囲</t>
+        </is>
+      </c>
+      <c r="D139" s="42" t="inlineStr">
+        <is>
+          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+        </is>
+      </c>
+      <c r="E139" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F139" s="40" t="inlineStr">
+        <is>
+          <t>doc22 §1</t>
+        </is>
+      </c>
+      <c r="G139" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H139" s="42" t="inlineStr"/>
+    </row>
+    <row r="140" ht="34" customHeight="1">
+      <c r="A140" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B140" s="41" t="inlineStr">
+        <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="C137" s="42" t="inlineStr">
+      <c r="C140" s="42" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+        </is>
+      </c>
+      <c r="D140" s="42" t="inlineStr">
+        <is>
+          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+        </is>
+      </c>
+      <c r="E140" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F140" s="40" t="inlineStr">
+        <is>
+          <t>doc20§3,§4</t>
+        </is>
+      </c>
+      <c r="G140" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H140" s="42" t="inlineStr"/>
+    </row>
+    <row r="141" ht="34" customHeight="1">
+      <c r="A141" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B141" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C141" s="42" t="inlineStr">
+        <is>
+          <t>交付要綱の配点表（満点）</t>
+        </is>
+      </c>
+      <c r="D141" s="42" t="inlineStr">
+        <is>
+          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+        </is>
+      </c>
+      <c r="E141" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F141" s="40" t="inlineStr">
+        <is>
+          <t>doc20§2</t>
+        </is>
+      </c>
+      <c r="G141" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H141" s="42" t="inlineStr"/>
+    </row>
+    <row r="142" ht="34" customHeight="1">
+      <c r="A142" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B142" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C142" s="42" t="inlineStr">
+        <is>
+          <t>令和6年度・令和7年度の交付金評価結果</t>
+        </is>
+      </c>
+      <c r="D142" s="42" t="inlineStr">
+        <is>
+          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+        </is>
+      </c>
+      <c r="E142" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F142" s="40" t="inlineStr">
+        <is>
+          <t>doc20§3-1</t>
+        </is>
+      </c>
+      <c r="G142" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H142" s="42" t="inlineStr"/>
+    </row>
+    <row r="143" ht="34" customHeight="1">
+      <c r="A143" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B143" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C143" s="42" t="inlineStr">
+        <is>
+          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+        </is>
+      </c>
+      <c r="D143" s="42" t="inlineStr">
+        <is>
+          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+        </is>
+      </c>
+      <c r="E143" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-56,Ⅱ-58</t>
+        </is>
+      </c>
+      <c r="F143" s="40" t="inlineStr">
+        <is>
+          <t>doc09</t>
+        </is>
+      </c>
+      <c r="G143" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H143" s="42" t="inlineStr"/>
+    </row>
+    <row r="144" ht="34" customHeight="1">
+      <c r="A144" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B144" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C144" s="42" t="inlineStr">
+        <is>
+          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+        </is>
+      </c>
+      <c r="D144" s="42" t="inlineStr">
+        <is>
+          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+        </is>
+      </c>
+      <c r="E144" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-59</t>
+        </is>
+      </c>
+      <c r="F144" s="40" t="inlineStr">
+        <is>
+          <t>doc02§20-2</t>
+        </is>
+      </c>
+      <c r="G144" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H144" s="42" t="inlineStr"/>
+    </row>
+    <row r="145" ht="34" customHeight="1">
+      <c r="A145" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B145" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C145" s="42" t="inlineStr">
         <is>
           <t>国の指針・様式の更新有無</t>
         </is>
       </c>
-      <c r="D137" s="42" t="inlineStr">
+      <c r="D145" s="42" t="inlineStr">
         <is>
           <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
-      <c r="E137" s="40" t="inlineStr">
+      <c r="E145" s="40" t="inlineStr">
         <is>
           <t>Ⅰ-11</t>
         </is>
       </c>
-      <c r="F137" s="40" t="inlineStr">
+      <c r="F145" s="40" t="inlineStr">
         <is>
           <t>doc04,doc05</t>
         </is>
       </c>
-      <c r="G137" s="40" t="inlineStr">
+      <c r="G145" s="40" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H137" s="42" t="inlineStr"/>
+      <c r="H145" s="42" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H118"/>
+  <autoFilter ref="A4:H126"/>
   <mergeCells count="3">
-    <mergeCell ref="A120:H120"/>
+    <mergeCell ref="A128:H128"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A118" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A126" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G118" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G126" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$130</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="M54" s="14" t="n"/>
       <c r="N54" s="15" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="O54" s="16" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="P54" s="13" t="inlineStr">
         <is>
-          <t>交付金の令和8年度配点表を入手し評価指標の改定を確認（doc20）。★議事録により令和9年度の介護報酬改定への対応方針（現行単価で試算→単価確定後に補正）が決着。第10期の国の基本指針は告示待ち。</t>
+          <t>交付金の令和8年度配点表を入手し評価指標の改定を確認（doc20）。★議事録により令和9年度の介護報酬改定への対応方針（現行単価で試算→単価確定後に補正）が決着。第10期の国の基本指針は告示待ち。★9/12：社会福祉法等の一部を改正する法律（令和8年法律第51号）の7件を素案1-8に新設して反映。あわせて中山間・人口減少地域（特定地域）の指定基準を整理し、本村は75歳以上人口526人・密度5人/km²未満により基準②に該当する見込みと判定。村内に事業所がないサービスへの対応手段になるため、指定を受ける意向を依頼書45-1として確認する。</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="M65" s="14" t="n"/>
       <c r="N65" s="15" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="O65" s="16" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
       </c>
       <c r="P65" s="13" t="inlineStr">
         <is>
-          <t>★9/8：doc30として推計の枠組みを確定。「見える化」システムのデータ定義（受給者数＝年度延べ、D45系の分母＝要介護度別認定者数）を検算のうえ確定し、estimate_services.py により区分別・サービス種類別の見込量を算定。全28サービスのうち令和7年度に実績のある16サービスについて受給者数・利用量・給付費の暫定値を doc18 第5章5-4に投入。施設・居住系の種類別人数は見える化に系列がなく給付費比の按分値のため、村の月報（第2表・第3表）で置き換えが必要。介護給付と予防給付の分離も同じく月報待ち。</t>
+          <t>★9/8：doc30として推計の枠組みを確定。「見える化」システムのデータ定義（受給者数＝年度延べ、D45系の分母＝要介護度別認定者数）を検算のうえ確定し、estimate_services.py により区分別・サービス種類別の見込量を算定。全28サービスのうち令和7年度に実績のある16サービスについて受給者数・利用量・給付費の暫定値を doc18 第5章5-4に投入。施設・居住系の種類別人数は見える化に系列がなく給付費比の按分値のため、村の月報（第2表・第3表）で置き換えが必要。介護給付と予防給付の分離も同じく月報待ち。★9/12：他案件（川崎町・金ケ崎町・大雪）の到達水準と対照し（doc33）、基準年度を令和7年度と確定。見える化の系列別の月数を実測で確認し（D1はR7が11か月、D2/D3/D4は12か月相当）doc30の÷12が正しいことを裏付けて素案5-4に明記。令和9年4月新設4区分の枠と、国の推計ツールのワーニング判定式（閾値＝Q1−2Q〜Q3+2Q）による自己点検の手順を追加。国の推計ツールの出力は未受領で、依頼書18-2として最優先で追加した。</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="M66" s="14" t="n"/>
       <c r="N66" s="15" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="O66" s="16" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="P66" s="13" t="inlineStr">
         <is>
-          <t>★9/8：サービス諸費（介護サービス等諸費＋介護予防サービス等諸費）の推計値を算定し doc18 第5章5-6に投入（令和9年度263,470千円／10年度263,505千円／11年度262,488千円）。見える化D48系に令和5年度までの決算が入っていることが判明し、令和3〜5年度の実績（244,097／247,333／258,848千円）と対比。決算の未入手は令和6・7年度の2か年に縮小。補足給付・高額介護サービス費・審査支払手数料は令和5年度決算まで把握済。</t>
+          <t>★9/8：サービス諸費（介護サービス等諸費＋介護予防サービス等諸費）の推計値を算定し doc18 第5章5-6に投入（令和9年度263,470千円／10年度263,505千円／11年度262,488千円）。見える化D48系に令和5年度までの決算が入っていることが判明し、令和3〜5年度の実績（244,097／247,333／258,848千円）と対比。決算の未入手は令和6・7年度の2か年に縮小。補足給付・高額介護サービス費・審査支払手数料は令和5年度決算まで把握済。★9/12：標準給付費見込額（3年計854,014千円）を算定。令和6・7年度決算が未受領のため割増率とその他給付費は令和5年度決算で代用している。</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="M68" s="14" t="n"/>
       <c r="N68" s="15" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="O68" s="16" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="P68" s="13" t="inlineStr">
         <is>
-          <t>★議事録で方針決着：第9期で県内平均を上回ったため急激な負担増を抑えたい意向。基金取崩も視野。令和9年度の介護報酬改定を見据え現行単価で一旦試算し単価確定後に補正。doc18 第5章5-7に様式と所得段階13段階の枠を作成済。★9/8：サービス諸費の推計（doc30）が出たため、残る停止要因は基金残高と令和6・7年度決算の2件に絞られた。</t>
+          <t>★議事録で方針決着：第9期で県内平均を上回ったため急激な負担増を抑えたい意向。基金取崩も視野。令和9年度の介護報酬改定を見据え現行単価で一旦試算し単価確定後に補正。doc18 第5章5-7に様式と所得段階13段階の枠を作成済。★9/8：サービス諸費の推計（doc30）が出たため、残る停止要因は基金残高と令和6・7年度決算の2件に絞られた。★9/12：保険料算定の5式（金ケ崎町で第9期公表値と一致を確認した構造）と調整交付金見込交付割合の式（α+0.05）−α×F×Gを導入し、本村の第9期を0.32%で再現。限界率23.79%・F×G=1.034を復元。感応度9項目（給付費1%＝月額59円、第1号負担割合1pt＝294円、基金24,000千円＝▲702円）と12パターン（5,936〜7,341円・幅1,406円）を算定し素案5-7に投入（scripts/estimate_premium.py）。保険料の幅のうち702円は基金取崩の判断で決まるため、給付費推計の精緻化より基金方針の決定が先。</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H145"/>
+  <dimension ref="A1:H149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8166,22 +8166,22 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>★給付費適正化「主要3事業の全て実施」が令和7年度6点→令和8年度0点に低下した理由</t>
+          <t>国の介護保険事業計画作成支援ツール（将来推計総括表）の出力一式</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>★全国該当率96.9%の指標。縦覧点検は4帳票満点のため、①要介護認定の適正化 か ②ケアプラン等の点検 のいずれかが実施されなくなった可能性。取組の後退か調査票の記載漏れかで対応が変わる。</t>
+          <t>★★最優先。他案件（川崎町・金ケ崎町・大雪）はいずれも保険者が操作したツールの出力を受領し検証する立場にあるが、本村は見える化から独自算定しており国の様式との検算ができていない。他案件では令和8年度が実績でなく推計値、主要項目が未入力のまま保険料だけ数値が入る等の事例が実際に見つかっている。</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-55,Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F30" s="35" t="inlineStr">
         <is>
-          <t>doc20§8-2 K-61</t>
+          <t>doc33§5-1</t>
         </is>
       </c>
       <c r="G30" s="35" t="inlineStr">
@@ -8204,22 +8204,22 @@
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>★福祉用具購入費・住宅改修費へのリハビリ専門職の関与（配点8点）が令和7年度8点→令和8年度0点に低下した理由</t>
+          <t>第9期計画の本文（サービス別見込量の表を含む全体）</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>★アと合わせ14点が1年で失われている。仕組みが失われたのか調査票の記載によるものかを確認。</t>
+          <t>★★用途が2つある。①対計画比（サービス別の計画値と実績の対比）。他案件では総額が計画どおりでも内訳が11.5〜967.4％まで開くことが確認されており、本村は受給率を3か年平均で固定しているため偏りを持ち越す。②老人福祉事業の量の目標の記載位置の確認（doc32§4-1）。保有しているのは概要版のみでサービス別見込量がない。</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-53,Ⅱ-55</t>
         </is>
       </c>
       <c r="F31" s="35" t="inlineStr">
         <is>
-          <t>doc20§8-2 K-61b</t>
+          <t>doc33§5-2</t>
         </is>
       </c>
       <c r="G31" s="35" t="inlineStr">
@@ -8242,22 +8242,22 @@
       </c>
       <c r="C32" s="34" t="inlineStr">
         <is>
-          <t>認知症サポーター養成数・認知症地域支援推進員の配置と活動内容・チームオレンジの整備予定</t>
+          <t>★給付費適正化「主要3事業の全て実施」が令和7年度6点→令和8年度0点に低下した理由</t>
         </is>
       </c>
       <c r="D32" s="34" t="inlineStr">
         <is>
-          <t>★支援交付金目標Ⅱ（認知症総合支援）は32/100点で全国平均51.1点を19点下回る唯一の目標。3か年で唯一低下局面があった。</t>
+          <t>★全国該当率96.9%の指標。縦覧点検は4帳票満点のため、①要介護認定の適正化 か ②ケアプラン等の点検 のいずれかが実施されなくなった可能性。取組の後退か調査票の記載漏れかで対応が変わる。</t>
         </is>
       </c>
       <c r="E32" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F32" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-62</t>
+          <t>doc20§8-2 K-61</t>
         </is>
       </c>
       <c r="G32" s="35" t="inlineStr">
@@ -8280,22 +8280,22 @@
       </c>
       <c r="C33" s="34" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入の取組（健診での聴力チェック等）の有無</t>
+          <t>★福祉用具購入費・住宅改修費へのリハビリ専門職の関与（配点8点）が令和7年度8点→令和8年度0点に低下した理由</t>
         </is>
       </c>
       <c r="D33" s="34" t="inlineStr">
         <is>
-          <t>令和8年度評価で配点10点が0点（全国該当率48.8〜68.9%）。保健事業との連携で取得可能。</t>
+          <t>★アと合わせ14点が1年で失われている。仕組みが失われたのか調査票の記載によるものかを確認。</t>
         </is>
       </c>
       <c r="E33" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F33" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-63</t>
+          <t>doc20§8-2 K-61b</t>
         </is>
       </c>
       <c r="G33" s="35" t="inlineStr">
@@ -8318,22 +8318,22 @@
       </c>
       <c r="C34" s="34" t="inlineStr">
         <is>
-          <t>在宅医療・介護連携推進事業の実施体制（村単独か会津圏域か）と課題・対応策の検討の場</t>
+          <t>認知症サポーター養成数・認知症地域支援推進員の配置と活動内容・チームオレンジの整備予定</t>
         </is>
       </c>
       <c r="D34" s="34" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲの「課題・対応策の検討」ア・エが0点（配点計10点、全国該当率57〜72%）。</t>
+          <t>★支援交付金目標Ⅱ（認知症総合支援）は32/100点で全国平均51.1点を19点下回る唯一の目標。3か年で唯一低下局面があった。</t>
         </is>
       </c>
       <c r="E34" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F34" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-64</t>
+          <t>doc20§6-2 K-62</t>
         </is>
       </c>
       <c r="G34" s="35" t="inlineStr">
@@ -8356,22 +8356,22 @@
       </c>
       <c r="C35" s="34" t="inlineStr">
         <is>
-          <t>★施設サービスが伸びない要因「重度化による病院への転院」の裏づけデータ</t>
+          <t>難聴高齢者の早期発見・早期介入の取組（健診での聴力チェック等）の有無</t>
         </is>
       </c>
       <c r="D35" s="34" t="inlineStr">
         <is>
-          <t>★議事録で示された村の見解。当方は村内施設ゼロ・村外施設依存の文脈で解釈していたため、素案の記述を修正する必要がある。KDB・給付実績で確認したい。</t>
+          <t>令和8年度評価で配点10点が0点（全国該当率48.8〜68.9%）。保健事業との連携で取得可能。</t>
         </is>
       </c>
       <c r="E35" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F35" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-75</t>
+          <t>doc20§6-2 K-63</t>
         </is>
       </c>
       <c r="G35" s="35" t="inlineStr">
@@ -8394,22 +8394,22 @@
       </c>
       <c r="C36" s="34" t="inlineStr">
         <is>
-          <t>★要介護認定データの提供時期と項目（要介護度・認定日・サービス利用状況）</t>
+          <t>在宅医療・介護連携推進事業の実施体制（村単独か会津圏域か）と課題・対応策の検討の場</t>
         </is>
       </c>
       <c r="D36" s="34" t="inlineStr">
         <is>
-          <t>★仕様書4Ⅰ(5)。ICF分析の「認定状況×生活機能リスク」表と在宅調査のクロスに必須。目的外利用の手続きの確認を含む。議事録の「元気な軽度者が総合事業を利用している」の検証はこの紐付けでしかできない。</t>
+          <t>支援交付金目標Ⅲの「課題・対応策の検討」ア・エが0点（配点計10点、全国該当率57〜72%）。</t>
         </is>
       </c>
       <c r="E36" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-37</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F36" s="35" t="inlineStr">
         <is>
-          <t>doc24§12 K-87</t>
+          <t>doc20§6-2 K-64</t>
         </is>
       </c>
       <c r="G36" s="35" t="inlineStr">
@@ -8432,22 +8432,22 @@
       </c>
       <c r="C37" s="34" t="inlineStr">
         <is>
-          <t>★会津権利擁護・成年後見センターへの相談が1年で件数−43%・時間−55%と減少した要因</t>
+          <t>★施設サービスが伸びない要因「重度化による病院への転院」の裏づけデータ</t>
         </is>
       </c>
       <c r="D37" s="34" t="inlineStr">
         <is>
-          <t>★令和6年度134件・1,625分→令和7年度76件・729分。圏域13市町村の総計は増加しているなかで本村のみ大きく減少。施策評価に必要。</t>
+          <t>★議事録で示された村の見解。当方は村内施設ゼロ・村外施設依存の文脈で解釈していたため、素案の記述を修正する必要がある。KDB・給付実績で確認したい。</t>
         </is>
       </c>
       <c r="E37" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F37" s="35" t="inlineStr">
         <is>
-          <t>doc28§3-3 K-108</t>
+          <t>doc22 K-75</t>
         </is>
       </c>
       <c r="G37" s="35" t="inlineStr">
@@ -8465,27 +8465,27 @@
       </c>
       <c r="B38" s="33" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C38" s="34" t="inlineStr">
         <is>
-          <t>契約締結日・契約書の取り交わし状況</t>
+          <t>★要介護認定データの提供時期と項目（要介護度・認定日・サービス利用状況）</t>
         </is>
       </c>
       <c r="D38" s="34" t="inlineStr">
         <is>
-          <t>業務開始日の確定。</t>
+          <t>★仕様書4Ⅰ(5)。ICF分析の「認定状況×生活機能リスク」表と在宅調査のクロスに必須。目的外利用の手続きの確認を含む。議事録の「元気な軽度者が総合事業を利用している」の検証はこの紐付けでしかできない。</t>
         </is>
       </c>
       <c r="E38" s="35" t="inlineStr">
         <is>
-          <t>０-02</t>
+          <t>Ⅰ-37</t>
         </is>
       </c>
       <c r="F38" s="35" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>doc24§12 K-87</t>
         </is>
       </c>
       <c r="G38" s="35" t="inlineStr">
@@ -8503,27 +8503,27 @@
       </c>
       <c r="B39" s="33" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C39" s="34" t="inlineStr">
         <is>
-          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
+          <t>★会津権利擁護・成年後見センターへの相談が1年で件数−43%・時間−55%と減少した要因</t>
         </is>
       </c>
       <c r="D39" s="34" t="inlineStr">
         <is>
-          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
+          <t>★令和6年度134件・1,625分→令和7年度76件・729分。圏域13市町村の総計は増加しているなかで本村のみ大きく減少。施策評価に必要。</t>
         </is>
       </c>
       <c r="E39" s="35" t="inlineStr">
         <is>
-          <t>０-06</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F39" s="35" t="inlineStr">
         <is>
-          <t>doc19 追-12</t>
+          <t>doc28§3-3 K-108</t>
         </is>
       </c>
       <c r="G39" s="35" t="inlineStr">
@@ -8546,22 +8546,22 @@
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
+          <t>契約締結日・契約書の取り交わし状況</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
+          <t>業務開始日の確定。</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
         <is>
-          <t>Ⅴ-96</t>
+          <t>０-02</t>
         </is>
       </c>
       <c r="F40" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-78</t>
+          <t>―</t>
         </is>
       </c>
       <c r="G40" s="35" t="inlineStr">
@@ -8584,22 +8584,22 @@
       </c>
       <c r="C41" s="34" t="inlineStr">
         <is>
-          <t>自由記述の匿名化の方針（削除・置換の範囲）</t>
+          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
         </is>
       </c>
       <c r="D41" s="34" t="inlineStr">
         <is>
-          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。</t>
+          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
         </is>
       </c>
       <c r="E41" s="35" t="inlineStr">
         <is>
-          <t>Ⅴ-96</t>
+          <t>０-06</t>
         </is>
       </c>
       <c r="F41" s="35" t="inlineStr">
         <is>
-          <t>doc24§12 K-89</t>
+          <t>doc19 追-12</t>
         </is>
       </c>
       <c r="G41" s="35" t="inlineStr">
@@ -8622,22 +8622,22 @@
       </c>
       <c r="C42" s="34" t="inlineStr">
         <is>
-          <t>第2回策定委員会の資料の事前送付の可否と時期</t>
+          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
         </is>
       </c>
       <c r="D42" s="34" t="inlineStr">
         <is>
-          <t>素案（完成度7割・約90頁）は別冊として事前送付する前提で資料を設計している。</t>
+          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
         </is>
       </c>
       <c r="E42" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-105</t>
+          <t>Ⅴ-96</t>
         </is>
       </c>
       <c r="F42" s="35" t="inlineStr">
         <is>
-          <t>doc26§10 K-97</t>
+          <t>doc22 K-78</t>
         </is>
       </c>
       <c r="G42" s="35" t="inlineStr">
@@ -8655,27 +8655,27 @@
       </c>
       <c r="B43" s="33" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C43" s="34" t="inlineStr">
         <is>
-          <t>ICF分析は標準設問のみで完結することの確認</t>
+          <t>自由記述の匿名化の方針（削除・置換の範囲）</t>
         </is>
       </c>
       <c r="D43" s="34" t="inlineStr">
         <is>
-          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
+          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。</t>
         </is>
       </c>
       <c r="E43" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-50</t>
+          <t>Ⅴ-96</t>
         </is>
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>doc23§3-4</t>
+          <t>doc24§12 K-89</t>
         </is>
       </c>
       <c r="G43" s="35" t="inlineStr">
@@ -8693,27 +8693,27 @@
       </c>
       <c r="B44" s="33" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C44" s="34" t="inlineStr">
         <is>
-          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
+          <t>第2回策定委員会の資料の事前送付の可否と時期</t>
         </is>
       </c>
       <c r="D44" s="34" t="inlineStr">
         <is>
-          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
+          <t>素案（完成度7割・約90頁）は別冊として事前送付する前提で資料を設計している。</t>
         </is>
       </c>
       <c r="E44" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅱ-105</t>
         </is>
       </c>
       <c r="F44" s="35" t="inlineStr">
         <is>
-          <t>doc24§12 K-86</t>
+          <t>doc26§10 K-97</t>
         </is>
       </c>
       <c r="G44" s="35" t="inlineStr">
@@ -8736,22 +8736,22 @@
       </c>
       <c r="C45" s="34" t="inlineStr">
         <is>
-          <t>★リスク判定10種の該当基準（見える化システムの算出方法との突合）</t>
+          <t>ICF分析は標準設問のみで完結することの確認</t>
         </is>
       </c>
       <c r="D45" s="34" t="inlineStr">
         <is>
-          <t>★手引きに該当基準の明記があるのはBMI 18.5以下のみ。他9種は基本チェックリストに準じた案を置いているが、独自基準では全国・県と比較できない。手引きは算出方法が将来更新され得るとも記載しており、第9期の基準の流用も不可。</t>
+          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
         </is>
       </c>
       <c r="E45" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-46</t>
+          <t>Ⅰ-50</t>
         </is>
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>doc25§4-2 K-91</t>
+          <t>doc23§3-4</t>
         </is>
       </c>
       <c r="G45" s="35" t="inlineStr">
@@ -8769,27 +8769,27 @@
       </c>
       <c r="B46" s="33" t="inlineStr">
         <is>
-          <t>委員会</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C46" s="34" t="inlineStr">
         <is>
-          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
+          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
         </is>
       </c>
       <c r="D46" s="34" t="inlineStr">
         <is>
-          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
+          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
         </is>
       </c>
       <c r="E46" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-80,Ⅱ-81</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F46" s="35" t="inlineStr">
         <is>
-          <t>doc01-6,doc19 追-15</t>
+          <t>doc24§12 K-86</t>
         </is>
       </c>
       <c r="G46" s="35" t="inlineStr">
@@ -8807,27 +8807,27 @@
       </c>
       <c r="B47" s="33" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C47" s="34" t="inlineStr">
         <is>
-          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
+          <t>★リスク判定10種の該当基準（見える化システムの算出方法との突合）</t>
         </is>
       </c>
       <c r="D47" s="34" t="inlineStr">
         <is>
-          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
+          <t>★手引きに該当基準の明記があるのはBMI 18.5以下のみ。他9種は基本チェックリストに準じた案を置いているが、独自基準では全国・県と比較できない。手引きは算出方法が将来更新され得るとも記載しており、第9期の基準の流用も不可。</t>
         </is>
       </c>
       <c r="E47" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-76,Ⅱ-77</t>
+          <t>Ⅰ-46</t>
         </is>
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>doc01-7,doc19 指-3</t>
+          <t>doc25§4-2 K-91</t>
         </is>
       </c>
       <c r="G47" s="35" t="inlineStr">
@@ -8845,27 +8845,27 @@
       </c>
       <c r="B48" s="33" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>委員会</t>
         </is>
       </c>
       <c r="C48" s="34" t="inlineStr">
         <is>
-          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
+          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
         </is>
       </c>
       <c r="D48" s="34" t="inlineStr">
         <is>
-          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
+          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
         </is>
       </c>
       <c r="E48" s="35" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅱ-80,Ⅱ-81</t>
         </is>
       </c>
       <c r="F48" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-79</t>
+          <t>doc01-6,doc19 追-15</t>
         </is>
       </c>
       <c r="G48" s="35" t="inlineStr">
@@ -8883,27 +8883,27 @@
       </c>
       <c r="B49" s="33" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
+          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
+          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-76,Ⅱ-77</t>
         </is>
       </c>
       <c r="F49" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-66</t>
+          <t>doc01-7,doc19 指-3</t>
         </is>
       </c>
       <c r="G49" s="35" t="inlineStr">
@@ -8921,27 +8921,27 @@
       </c>
       <c r="B50" s="33" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
+          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
+          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-62</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F50" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-81</t>
+          <t>doc22 K-79</t>
         </is>
       </c>
       <c r="G50" s="35" t="inlineStr">
@@ -8964,22 +8964,22 @@
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
+          <t>中山間・人口減少地域（特定地域）の指定を受ける意向</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
+          <t>★令和8年法律第51号により令和9年4月1日創設。本村は75歳以上人口526人・密度5人/km²未満で指定基準②に該当する見込み（面積が105.2km²を超えれば該当し、本村はこれを大きく上回る）。特定地域サービスと特定地域居宅サービス等事業は、28サービスのうち12種類に実績がない本村への対応手段になる。指定は村の意向を踏まえ都道府県が定めるため計画への記載が起点。</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-70</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>doc26§10 K-98</t>
+          <t>doc33§3-5</t>
         </is>
       </c>
       <c r="G51" s="35" t="inlineStr">
@@ -9002,22 +9002,22 @@
       </c>
       <c r="C52" s="34" t="inlineStr">
         <is>
-          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
+          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
         </is>
       </c>
       <c r="D52" s="34" t="inlineStr">
         <is>
-          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。</t>
+          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
         </is>
       </c>
       <c r="E52" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F52" s="35" t="inlineStr">
         <is>
-          <t>doc26§10 K-99</t>
+          <t>doc20§6-2 K-66</t>
         </is>
       </c>
       <c r="G52" s="35" t="inlineStr">
@@ -9040,22 +9040,22 @@
       </c>
       <c r="C53" s="34" t="inlineStr">
         <is>
-          <t>補正係数を①3区分と②前期・後期高齢者別のどちらで用いるか</t>
+          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
         </is>
       </c>
       <c r="D53" s="34" t="inlineStr">
         <is>
-          <t>国は小規模保険者では①の係数が不安定になるため②の選択を勧めている。本村の85歳以上は200人で係数0.03（差6人）と1人の増減の影響が大きい。当方は②を提案。</t>
+          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
         </is>
       </c>
       <c r="E53" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-62</t>
         </is>
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>doc28§1-2 K-107</t>
+          <t>doc22 K-81</t>
         </is>
       </c>
       <c r="G53" s="35" t="inlineStr">
@@ -9073,27 +9073,27 @@
       </c>
       <c r="B54" s="33" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C54" s="34" t="inlineStr">
         <is>
-          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
+          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
         </is>
       </c>
       <c r="D54" s="34" t="inlineStr">
         <is>
-          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
+          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
         </is>
       </c>
       <c r="E54" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-70</t>
         </is>
       </c>
       <c r="F54" s="35" t="inlineStr">
         <is>
-          <t>doc21§5 K-69</t>
+          <t>doc26§10 K-98</t>
         </is>
       </c>
       <c r="G54" s="35" t="inlineStr">
@@ -9111,27 +9111,27 @@
       </c>
       <c r="B55" s="33" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C55" s="34" t="inlineStr">
         <is>
-          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
+          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
         </is>
       </c>
       <c r="D55" s="34" t="inlineStr">
         <is>
-          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
+          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。</t>
         </is>
       </c>
       <c r="E55" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>doc21§5 K-70</t>
+          <t>doc26§10 K-99</t>
         </is>
       </c>
       <c r="G55" s="35" t="inlineStr">
@@ -9149,27 +9149,27 @@
       </c>
       <c r="B56" s="33" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C56" s="34" t="inlineStr">
         <is>
-          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
+          <t>補正係数を①3区分と②前期・後期高齢者別のどちらで用いるか</t>
         </is>
       </c>
       <c r="D56" s="34" t="inlineStr">
         <is>
-          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
+          <t>国は小規模保険者では①の係数が不安定になるため②の選択を勧めている。本村の85歳以上は200人で係数0.03（差6人）と1人の増減の影響が大きい。当方は②を提案。</t>
         </is>
       </c>
       <c r="E56" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F56" s="35" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-111</t>
+          <t>doc28§1-2 K-107</t>
         </is>
       </c>
       <c r="G56" s="35" t="inlineStr">
@@ -9187,32 +9187,32 @@
       </c>
       <c r="B57" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C57" s="34" t="inlineStr">
         <is>
-          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
+          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
         </is>
       </c>
       <c r="D57" s="34" t="inlineStr">
         <is>
-          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
+          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
         </is>
       </c>
       <c r="E57" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-19,Ⅰ-25</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F57" s="35" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc21§5 K-69</t>
         </is>
       </c>
       <c r="G57" s="35" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H57" s="34" t="inlineStr"/>
@@ -9225,27 +9225,27 @@
       </c>
       <c r="B58" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C58" s="34" t="inlineStr">
         <is>
-          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
+          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
         </is>
       </c>
       <c r="D58" s="34" t="inlineStr">
         <is>
-          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
+          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
         </is>
       </c>
       <c r="E58" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-09,Ⅰ-10</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F58" s="35" t="inlineStr">
         <is>
-          <t>doc27§3-3</t>
+          <t>doc21§5 K-70</t>
         </is>
       </c>
       <c r="G58" s="35" t="inlineStr">
@@ -9263,27 +9263,27 @@
       </c>
       <c r="B59" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C59" s="34" t="inlineStr">
         <is>
-          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
+          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
         </is>
       </c>
       <c r="D59" s="34" t="inlineStr">
         <is>
-          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
+          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
         </is>
       </c>
       <c r="E59" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-09,Ⅰ-10</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>doc27§5-2</t>
+          <t>doc28§3-4 K-111</t>
         </is>
       </c>
       <c r="G59" s="35" t="inlineStr">
@@ -9306,27 +9306,27 @@
       </c>
       <c r="C60" s="34" t="inlineStr">
         <is>
-          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
         </is>
       </c>
       <c r="D60" s="34" t="inlineStr">
         <is>
-          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
         </is>
       </c>
       <c r="E60" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-19,Ⅰ-25</t>
         </is>
       </c>
       <c r="F60" s="35" t="inlineStr">
         <is>
-          <t>doc27§5-3</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G60" s="35" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H60" s="34" t="inlineStr"/>
@@ -9344,144 +9344,144 @@
       </c>
       <c r="C61" s="34" t="inlineStr">
         <is>
+          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
+        </is>
+      </c>
+      <c r="D61" s="34" t="inlineStr">
+        <is>
+          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
+        </is>
+      </c>
+      <c r="E61" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-09,Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F61" s="35" t="inlineStr">
+        <is>
+          <t>doc27§3-3</t>
+        </is>
+      </c>
+      <c r="G61" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H61" s="34" t="inlineStr"/>
+    </row>
+    <row r="62" ht="34" customHeight="1">
+      <c r="A62" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B62" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C62" s="34" t="inlineStr">
+        <is>
+          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
+        </is>
+      </c>
+      <c r="D62" s="34" t="inlineStr">
+        <is>
+          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
+        </is>
+      </c>
+      <c r="E62" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-09,Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F62" s="35" t="inlineStr">
+        <is>
+          <t>doc27§5-2</t>
+        </is>
+      </c>
+      <c r="G62" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H62" s="34" t="inlineStr"/>
+    </row>
+    <row r="63" ht="34" customHeight="1">
+      <c r="A63" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B63" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C63" s="34" t="inlineStr">
+        <is>
+          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+        </is>
+      </c>
+      <c r="D63" s="34" t="inlineStr">
+        <is>
+          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+        </is>
+      </c>
+      <c r="E63" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F63" s="35" t="inlineStr">
+        <is>
+          <t>doc27§5-3</t>
+        </is>
+      </c>
+      <c r="G63" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H63" s="34" t="inlineStr"/>
+    </row>
+    <row r="64" ht="34" customHeight="1">
+      <c r="A64" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B64" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C64" s="34" t="inlineStr">
+        <is>
           <t>調査票のレイアウトの目視確認3点（幸福度の記入欄／宛名ラベル枠／頁数）</t>
         </is>
       </c>
-      <c r="D61" s="34" t="inlineStr">
+      <c r="D64" s="34" t="inlineStr">
         <is>
           <t>★当方の環境ではdocxからPDFへの変換ができずレイアウトを確認できない。ニーズ問8(2)の記入枠、表紙から削除された宛名ラベル枠と「第10期」表記、ルビ追加による頁数の増加を村側でご確認いただきたい。</t>
         </is>
       </c>
-      <c r="E61" s="35" t="inlineStr">
+      <c r="E64" s="35" t="inlineStr">
         <is>
           <t>Ⅰ-20</t>
         </is>
       </c>
-      <c r="F61" s="35" t="inlineStr">
+      <c r="F64" s="35" t="inlineStr">
         <is>
           <t>doc27§6</t>
         </is>
       </c>
-      <c r="G61" s="35" t="inlineStr">
+      <c r="G64" s="35" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H61" s="34" t="inlineStr"/>
-    </row>
-    <row r="62" ht="34" customHeight="1">
-      <c r="A62" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B62" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C62" s="25" t="inlineStr">
-        <is>
-          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
-        </is>
-      </c>
-      <c r="D62" s="25" t="inlineStr">
-        <is>
-          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
-        </is>
-      </c>
-      <c r="E62" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F62" s="23" t="inlineStr">
-        <is>
-          <t>doc02§22,doc08§8</t>
-        </is>
-      </c>
-      <c r="G62" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H62" s="25" t="inlineStr"/>
-    </row>
-    <row r="63" ht="34" customHeight="1">
-      <c r="A63" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B63" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C63" s="25" t="inlineStr">
-        <is>
-          <t>令和6年度決算および令和7年度の給付費見込</t>
-        </is>
-      </c>
-      <c r="D63" s="25" t="inlineStr">
-        <is>
-          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
-        </is>
-      </c>
-      <c r="E63" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
-        </is>
-      </c>
-      <c r="F63" s="23" t="inlineStr">
-        <is>
-          <t>doc08§8-1,doc30§2-4</t>
-        </is>
-      </c>
-      <c r="G63" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H63" s="25" t="inlineStr"/>
-    </row>
-    <row r="64" ht="34" customHeight="1">
-      <c r="A64" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B64" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C64" s="25" t="inlineStr">
-        <is>
-          <t>通いの場の実数（令和3〜7年度）</t>
-        </is>
-      </c>
-      <c r="D64" s="25" t="inlineStr">
-        <is>
-          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。</t>
-        </is>
-      </c>
-      <c r="E64" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F64" s="23" t="inlineStr">
-        <is>
-          <t>doc02§16,§22</t>
-        </is>
-      </c>
-      <c r="G64" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H64" s="25" t="inlineStr"/>
+      <c r="H64" s="34" t="inlineStr"/>
     </row>
     <row r="65" ht="34" customHeight="1">
       <c r="A65" s="37" t="inlineStr">
@@ -9496,22 +9496,22 @@
       </c>
       <c r="C65" s="25" t="inlineStr">
         <is>
-          <t>高齢者福祉事業（村単独事業）の実績資料</t>
+          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
         </is>
       </c>
       <c r="D65" s="25" t="inlineStr">
         <is>
-          <t>現行計画の評価に必要。</t>
+          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
         </is>
       </c>
       <c r="E65" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
-          <t>doc01-11</t>
+          <t>doc02§22,doc08§8</t>
         </is>
       </c>
       <c r="G65" s="23" t="inlineStr">
@@ -9534,22 +9534,22 @@
       </c>
       <c r="C66" s="25" t="inlineStr">
         <is>
-          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
+          <t>令和6年度決算および令和7年度の給付費見込</t>
         </is>
       </c>
       <c r="D66" s="25" t="inlineStr">
         <is>
-          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
+          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
         </is>
       </c>
       <c r="E66" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-58,Ⅱ-59</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F66" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-9</t>
+          <t>doc08§8-1,doc30§2-4</t>
         </is>
       </c>
       <c r="G66" s="23" t="inlineStr">
@@ -9572,22 +9572,22 @@
       </c>
       <c r="C67" s="25" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
+          <t>通いの場の実数（令和3〜7年度）</t>
         </is>
       </c>
       <c r="D67" s="25" t="inlineStr">
         <is>
-          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
+          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。</t>
         </is>
       </c>
       <c r="E67" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-3</t>
+          <t>doc02§16,§22</t>
         </is>
       </c>
       <c r="G67" s="23" t="inlineStr">
@@ -9610,22 +9610,22 @@
       </c>
       <c r="C68" s="25" t="inlineStr">
         <is>
-          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
+          <t>高齢者福祉事業（村単独事業）の実績資料</t>
         </is>
       </c>
       <c r="D68" s="25" t="inlineStr">
         <is>
-          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
+          <t>現行計画の評価に必要。</t>
         </is>
       </c>
       <c r="E68" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F68" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc01-11</t>
         </is>
       </c>
       <c r="G68" s="23" t="inlineStr">
@@ -9648,22 +9648,22 @@
       </c>
       <c r="C69" s="25" t="inlineStr">
         <is>
-          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
+          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
         </is>
       </c>
       <c r="D69" s="25" t="inlineStr">
         <is>
-          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
+          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
         </is>
       </c>
       <c r="E69" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-58,Ⅱ-59</t>
         </is>
       </c>
       <c r="F69" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc19 追-9</t>
         </is>
       </c>
       <c r="G69" s="23" t="inlineStr">
@@ -9686,22 +9686,22 @@
       </c>
       <c r="C70" s="25" t="inlineStr">
         <is>
-          <t>居宅介護支援・介護予防支援の受給者数（令和5〜7年度）</t>
+          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
         </is>
       </c>
       <c r="D70" s="25" t="inlineStr">
         <is>
-          <t>見える化は両者を合算した給付費のみ。人数は在宅サービス受給者数（112.6人／月）に近い水準とみられるが実数が要る。</t>
+          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
         </is>
       </c>
       <c r="E70" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F70" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc30§5-3</t>
         </is>
       </c>
       <c r="G70" s="23" t="inlineStr">
@@ -9724,22 +9724,22 @@
       </c>
       <c r="C71" s="25" t="inlineStr">
         <is>
-          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
+          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
         </is>
       </c>
       <c r="D71" s="25" t="inlineStr">
         <is>
-          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
+          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
         </is>
       </c>
       <c r="E71" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-1</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G71" s="23" t="inlineStr">
@@ -9762,22 +9762,22 @@
       </c>
       <c r="C72" s="25" t="inlineStr">
         <is>
-          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
+          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
         </is>
       </c>
       <c r="D72" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
+          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
         </is>
       </c>
       <c r="E72" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F72" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G72" s="23" t="inlineStr">
@@ -9800,22 +9800,22 @@
       </c>
       <c r="C73" s="25" t="inlineStr">
         <is>
-          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
+          <t>居宅介護支援・介護予防支援の受給者数（令和5〜7年度）</t>
         </is>
       </c>
       <c r="D73" s="25" t="inlineStr">
         <is>
-          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
+          <t>見える化は両者を合算した給付費のみ。人数は在宅サービス受給者数（112.6人／月）に近い水準とみられるが実数が要る。</t>
         </is>
       </c>
       <c r="E73" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F73" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-2</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G73" s="23" t="inlineStr">
@@ -9838,22 +9838,22 @@
       </c>
       <c r="C74" s="25" t="inlineStr">
         <is>
-          <t>第9期計画の本文（第5章81〜92ページ）</t>
+          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
         </is>
       </c>
       <c r="D74" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
+          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
         </is>
       </c>
       <c r="E74" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F74" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc33§2</t>
         </is>
       </c>
       <c r="G74" s="23" t="inlineStr">
@@ -9876,22 +9876,22 @@
       </c>
       <c r="C75" s="25" t="inlineStr">
         <is>
-          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
+          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
         </is>
       </c>
       <c r="D75" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
+          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
         </is>
       </c>
       <c r="E75" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F75" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-3</t>
+          <t>doc32§5-1</t>
         </is>
       </c>
       <c r="G75" s="23" t="inlineStr">
@@ -9914,22 +9914,22 @@
       </c>
       <c r="C76" s="25" t="inlineStr">
         <is>
-          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
+          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
         </is>
       </c>
       <c r="D76" s="25" t="inlineStr">
         <is>
-          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
+          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
         </is>
       </c>
       <c r="E76" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F76" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G76" s="23" t="inlineStr">
@@ -9952,22 +9952,22 @@
       </c>
       <c r="C77" s="25" t="inlineStr">
         <is>
-          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
+          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
         </is>
       </c>
       <c r="D77" s="25" t="inlineStr">
         <is>
-          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
+          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
         </is>
       </c>
       <c r="E77" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F77" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§5-2</t>
         </is>
       </c>
       <c r="G77" s="23" t="inlineStr">
@@ -9990,22 +9990,22 @@
       </c>
       <c r="C78" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
+          <t>第9期計画の本文（第5章81〜92ページ）</t>
         </is>
       </c>
       <c r="D78" s="25" t="inlineStr">
         <is>
-          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
+          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
         </is>
       </c>
       <c r="E78" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F78" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G78" s="23" t="inlineStr">
@@ -10028,22 +10028,22 @@
       </c>
       <c r="C79" s="25" t="inlineStr">
         <is>
-          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
+          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
         </is>
       </c>
       <c r="D79" s="25" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
+          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
         </is>
       </c>
       <c r="E79" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-65</t>
+          <t>doc32§3-3</t>
         </is>
       </c>
       <c r="G79" s="23" t="inlineStr">
@@ -10066,22 +10066,22 @@
       </c>
       <c r="C80" s="25" t="inlineStr">
         <is>
-          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
+          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
         </is>
       </c>
       <c r="D80" s="25" t="inlineStr">
         <is>
-          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
+          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
         </is>
       </c>
       <c r="E80" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F80" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-68</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G80" s="23" t="inlineStr">
@@ -10104,22 +10104,22 @@
       </c>
       <c r="C81" s="25" t="inlineStr">
         <is>
-          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
+          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
         </is>
       </c>
       <c r="D81" s="25" t="inlineStr">
         <is>
-          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
+          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
         </is>
       </c>
       <c r="E81" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-71</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G81" s="23" t="inlineStr">
@@ -10142,22 +10142,22 @@
       </c>
       <c r="C82" s="25" t="inlineStr">
         <is>
-          <t>シルバー人材センターの会員数・受注実績</t>
+          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
         </is>
       </c>
       <c r="D82" s="25" t="inlineStr">
         <is>
-          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
+          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
         </is>
       </c>
       <c r="E82" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F82" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-72</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G82" s="23" t="inlineStr">
@@ -10180,22 +10180,22 @@
       </c>
       <c r="C83" s="25" t="inlineStr">
         <is>
-          <t>第9期調査の集計基準・集計表の提供</t>
+          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
         </is>
       </c>
       <c r="D83" s="25" t="inlineStr">
         <is>
-          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
+          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
         </is>
       </c>
       <c r="E83" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-92</t>
+          <t>doc20§6-2 K-65</t>
         </is>
       </c>
       <c r="G83" s="23" t="inlineStr">
@@ -10218,22 +10218,22 @@
       </c>
       <c r="C84" s="25" t="inlineStr">
         <is>
-          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
+          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
         </is>
       </c>
       <c r="D84" s="25" t="inlineStr">
         <is>
-          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
+          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
         </is>
       </c>
       <c r="E84" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F84" s="23" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-109</t>
+          <t>doc21§5 K-68</t>
         </is>
       </c>
       <c r="G84" s="23" t="inlineStr">
@@ -10256,22 +10256,22 @@
       </c>
       <c r="C85" s="25" t="inlineStr">
         <is>
-          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
+          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
         </is>
       </c>
       <c r="D85" s="25" t="inlineStr">
         <is>
-          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
+          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
         </is>
       </c>
       <c r="E85" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t>doc28§2 K-110</t>
+          <t>doc21§5 K-71</t>
         </is>
       </c>
       <c r="G85" s="23" t="inlineStr">
@@ -10289,27 +10289,27 @@
       </c>
       <c r="B86" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C86" s="25" t="inlineStr">
         <is>
-          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
+          <t>シルバー人材センターの会員数・受注実績</t>
         </is>
       </c>
       <c r="D86" s="25" t="inlineStr">
         <is>
-          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
+          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
         </is>
       </c>
       <c r="E86" s="23" t="inlineStr">
         <is>
-          <t>Ⅴ-95</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F86" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-67</t>
+          <t>doc21§5 K-72</t>
         </is>
       </c>
       <c r="G86" s="23" t="inlineStr">
@@ -10327,27 +10327,27 @@
       </c>
       <c r="B87" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C87" s="25" t="inlineStr">
         <is>
-          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
+          <t>第9期調査の集計基準・集計表の提供</t>
         </is>
       </c>
       <c r="D87" s="25" t="inlineStr">
         <is>
-          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
+          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
         </is>
       </c>
       <c r="E87" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-35</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-93</t>
+          <t>doc25§8 K-92</t>
         </is>
       </c>
       <c r="G87" s="23" t="inlineStr">
@@ -10365,27 +10365,27 @@
       </c>
       <c r="B88" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C88" s="25" t="inlineStr">
         <is>
-          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
+          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
         </is>
       </c>
       <c r="D88" s="25" t="inlineStr">
         <is>
-          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
+          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
         </is>
       </c>
       <c r="E88" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-48</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F88" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-94</t>
+          <t>doc28§3-4 K-109</t>
         </is>
       </c>
       <c r="G88" s="23" t="inlineStr">
@@ -10403,27 +10403,27 @@
       </c>
       <c r="B89" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C89" s="25" t="inlineStr">
         <is>
-          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
+          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
         </is>
       </c>
       <c r="D89" s="25" t="inlineStr">
         <is>
-          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
+          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
         </is>
       </c>
       <c r="E89" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t>doc19 指-5</t>
+          <t>doc28§2 K-110</t>
         </is>
       </c>
       <c r="G89" s="23" t="inlineStr">
@@ -10441,27 +10441,27 @@
       </c>
       <c r="B90" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C90" s="25" t="inlineStr">
         <is>
-          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
+          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
         </is>
       </c>
       <c r="D90" s="25" t="inlineStr">
         <is>
-          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
+          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
         </is>
       </c>
       <c r="E90" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-108</t>
+          <t>Ⅴ-95</t>
         </is>
       </c>
       <c r="F90" s="23" t="inlineStr">
         <is>
-          <t>doc22 K-80</t>
+          <t>doc20§6-2 K-67</t>
         </is>
       </c>
       <c r="G90" s="23" t="inlineStr">
@@ -10479,27 +10479,27 @@
       </c>
       <c r="B91" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C91" s="25" t="inlineStr">
         <is>
-          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
+          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
         </is>
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
+          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-90</t>
+          <t>Ⅰ-35</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-88</t>
+          <t>doc25§8 K-93</t>
         </is>
       </c>
       <c r="G91" s="23" t="inlineStr">
@@ -10517,27 +10517,27 @@
       </c>
       <c r="B92" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C92" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
+          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
         </is>
       </c>
       <c r="D92" s="25" t="inlineStr">
         <is>
-          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
+          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
         </is>
       </c>
       <c r="E92" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅰ-48</t>
         </is>
       </c>
       <c r="F92" s="23" t="inlineStr">
         <is>
-          <t>doc09§4,§10</t>
+          <t>doc25§8 K-94</t>
         </is>
       </c>
       <c r="G92" s="23" t="inlineStr">
@@ -10555,27 +10555,27 @@
       </c>
       <c r="B93" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C93" s="25" t="inlineStr">
         <is>
-          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
+          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
         </is>
       </c>
       <c r="D93" s="25" t="inlineStr">
         <is>
-          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
+          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
         </is>
       </c>
       <c r="E93" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t>doc09§8,§10</t>
+          <t>doc19 指-5</t>
         </is>
       </c>
       <c r="G93" s="23" t="inlineStr">
@@ -10593,27 +10593,27 @@
       </c>
       <c r="B94" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C94" s="25" t="inlineStr">
         <is>
-          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
+          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
         </is>
       </c>
       <c r="D94" s="25" t="inlineStr">
         <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
+          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
         </is>
       </c>
       <c r="E94" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-108</t>
         </is>
       </c>
       <c r="F94" s="23" t="inlineStr">
         <is>
-          <t>doc02§17,doc07,doc18 4-1</t>
+          <t>doc22 K-80</t>
         </is>
       </c>
       <c r="G94" s="23" t="inlineStr">
@@ -10631,27 +10631,27 @@
       </c>
       <c r="B95" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C95" s="25" t="inlineStr">
         <is>
-          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
+          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
         </is>
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
+          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
         </is>
       </c>
       <c r="E95" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-75</t>
+          <t>Ⅳ-90</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t>doc17 C-1,doc02§20-2</t>
+          <t>doc24§12 K-88</t>
         </is>
       </c>
       <c r="G95" s="23" t="inlineStr">
@@ -10674,22 +10674,22 @@
       </c>
       <c r="C96" s="25" t="inlineStr">
         <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
         </is>
       </c>
       <c r="D96" s="25" t="inlineStr">
         <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
         </is>
       </c>
       <c r="E96" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F96" s="23" t="inlineStr">
         <is>
-          <t>doc13§6</t>
+          <t>doc09§4,§10</t>
         </is>
       </c>
       <c r="G96" s="23" t="inlineStr">
@@ -10712,22 +10712,22 @@
       </c>
       <c r="C97" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
+          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
         </is>
       </c>
       <c r="D97" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
+          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
         </is>
       </c>
       <c r="E97" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t>doc30§4-2,doc18 5-4</t>
+          <t>doc09§8,§10</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr">
@@ -10750,22 +10750,22 @@
       </c>
       <c r="C98" s="25" t="inlineStr">
         <is>
-          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
+          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
         </is>
       </c>
       <c r="D98" s="25" t="inlineStr">
         <is>
-          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
         </is>
       </c>
       <c r="E98" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-57</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F98" s="23" t="inlineStr">
         <is>
-          <t>doc32§7</t>
+          <t>doc02§17,doc07,doc18 4-1</t>
         </is>
       </c>
       <c r="G98" s="23" t="inlineStr">
@@ -10788,22 +10788,22 @@
       </c>
       <c r="C99" s="25" t="inlineStr">
         <is>
-          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
         </is>
       </c>
       <c r="D99" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
         </is>
       </c>
       <c r="E99" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-56,Ⅱ-75</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-1</t>
+          <t>doc17 C-1,doc02§20-2</t>
         </is>
       </c>
       <c r="G99" s="23" t="inlineStr">
@@ -10826,22 +10826,22 @@
       </c>
       <c r="C100" s="25" t="inlineStr">
         <is>
-          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
         </is>
       </c>
       <c r="D100" s="25" t="inlineStr">
         <is>
-          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
         </is>
       </c>
       <c r="E100" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-60,Ⅱ-65</t>
         </is>
       </c>
       <c r="F100" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-4</t>
+          <t>doc13§6</t>
         </is>
       </c>
       <c r="G100" s="23" t="inlineStr">
@@ -10864,22 +10864,22 @@
       </c>
       <c r="C101" s="25" t="inlineStr">
         <is>
-          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
         </is>
       </c>
       <c r="D101" s="25" t="inlineStr">
         <is>
-          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
+          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
         </is>
       </c>
       <c r="E101" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F101" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-14</t>
+          <t>doc30§4-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G101" s="23" t="inlineStr">
@@ -10902,22 +10902,22 @@
       </c>
       <c r="C102" s="25" t="inlineStr">
         <is>
-          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
         </is>
       </c>
       <c r="D102" s="25" t="inlineStr">
         <is>
-          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
         </is>
       </c>
       <c r="E102" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-53,Ⅱ-57</t>
         </is>
       </c>
       <c r="F102" s="23" t="inlineStr">
         <is>
-          <t>doc19 §3</t>
+          <t>doc32§7</t>
         </is>
       </c>
       <c r="G102" s="23" t="inlineStr">
@@ -10940,22 +10940,22 @@
       </c>
       <c r="C103" s="25" t="inlineStr">
         <is>
-          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
+          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
         </is>
       </c>
       <c r="D103" s="25" t="inlineStr">
         <is>
-          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
+          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
         </is>
       </c>
       <c r="E103" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-73</t>
+          <t>doc32§3-1</t>
         </is>
       </c>
       <c r="G103" s="23" t="inlineStr">
@@ -10978,22 +10978,22 @@
       </c>
       <c r="C104" s="25" t="inlineStr">
         <is>
-          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
+          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
         </is>
       </c>
       <c r="D104" s="25" t="inlineStr">
         <is>
-          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
+          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
         </is>
       </c>
       <c r="E104" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-105</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F104" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-90</t>
+          <t>doc30§5-4</t>
         </is>
       </c>
       <c r="G104" s="23" t="inlineStr">
@@ -11011,27 +11011,27 @@
       </c>
       <c r="B105" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C105" s="25" t="inlineStr">
         <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
         </is>
       </c>
       <c r="D105" s="25" t="inlineStr">
         <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
         </is>
       </c>
       <c r="E105" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t>doc07§4</t>
+          <t>doc19 追-14</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
@@ -11049,27 +11049,27 @@
       </c>
       <c r="B106" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C106" s="25" t="inlineStr">
         <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
         </is>
       </c>
       <c r="D106" s="25" t="inlineStr">
         <is>
-          <t>評価指標の読み方に影響。</t>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
         </is>
       </c>
       <c r="E106" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F106" s="23" t="inlineStr">
         <is>
-          <t>doc07§8-4</t>
+          <t>doc19 §3</t>
         </is>
       </c>
       <c r="G106" s="23" t="inlineStr">
@@ -11087,27 +11087,27 @@
       </c>
       <c r="B107" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C107" s="25" t="inlineStr">
         <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
         </is>
       </c>
       <c r="D107" s="25" t="inlineStr">
         <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
         </is>
       </c>
       <c r="E107" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t>doc08§4,§8-2</t>
+          <t>doc21§5 K-73</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
@@ -11125,27 +11125,27 @@
       </c>
       <c r="B108" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C108" s="25" t="inlineStr">
         <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
         </is>
       </c>
       <c r="D108" s="25" t="inlineStr">
         <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
         </is>
       </c>
       <c r="E108" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-105</t>
         </is>
       </c>
       <c r="F108" s="23" t="inlineStr">
         <is>
-          <t>doc02§20-1</t>
+          <t>doc24§12 K-90</t>
         </is>
       </c>
       <c r="G108" s="23" t="inlineStr">
@@ -11168,22 +11168,22 @@
       </c>
       <c r="C109" s="25" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
         </is>
       </c>
       <c r="D109" s="25" t="inlineStr">
         <is>
-          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
         </is>
       </c>
       <c r="E109" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t>doc32§1,§2</t>
+          <t>doc07§4</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr">
@@ -11201,27 +11201,27 @@
       </c>
       <c r="B110" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C110" s="25" t="inlineStr">
         <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
         </is>
       </c>
       <c r="D110" s="25" t="inlineStr">
         <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+          <t>評価指標の読み方に影響。</t>
         </is>
       </c>
       <c r="E110" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F110" s="23" t="inlineStr">
         <is>
-          <t>doc15,doc18</t>
+          <t>doc07§8-4</t>
         </is>
       </c>
       <c r="G110" s="23" t="inlineStr">
@@ -11239,27 +11239,27 @@
       </c>
       <c r="B111" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C111" s="25" t="inlineStr">
         <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
         </is>
       </c>
       <c r="D111" s="25" t="inlineStr">
         <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
         </is>
       </c>
       <c r="E111" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc18 3-1</t>
+          <t>doc08§4,§8-2</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
@@ -11277,27 +11277,27 @@
       </c>
       <c r="B112" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C112" s="25" t="inlineStr">
         <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
         </is>
       </c>
       <c r="D112" s="25" t="inlineStr">
         <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
         </is>
       </c>
       <c r="E112" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F112" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
+          <t>doc02§20-1</t>
         </is>
       </c>
       <c r="G112" s="23" t="inlineStr">
@@ -11315,27 +11315,27 @@
       </c>
       <c r="B113" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C113" s="25" t="inlineStr">
         <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
         </is>
       </c>
       <c r="D113" s="25" t="inlineStr">
         <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
         </is>
       </c>
       <c r="E113" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t>doc17 B-3,doc18 4-3</t>
+          <t>doc32§1,§2</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -11358,12 +11358,12 @@
       </c>
       <c r="C114" s="25" t="inlineStr">
         <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
         </is>
       </c>
       <c r="D114" s="25" t="inlineStr">
         <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
         </is>
       </c>
       <c r="E114" s="23" t="inlineStr">
@@ -11373,7 +11373,7 @@
       </c>
       <c r="F114" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 2-9</t>
+          <t>doc15,doc18</t>
         </is>
       </c>
       <c r="G114" s="23" t="inlineStr">
@@ -11396,22 +11396,22 @@
       </c>
       <c r="C115" s="25" t="inlineStr">
         <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
         </is>
       </c>
       <c r="D115" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
         </is>
       </c>
       <c r="E115" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 5-7</t>
+          <t>doc14§5,doc18 3-1</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -11429,27 +11429,27 @@
       </c>
       <c r="B116" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C116" s="25" t="inlineStr">
         <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
         </is>
       </c>
       <c r="D116" s="25" t="inlineStr">
         <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
         </is>
       </c>
       <c r="E116" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F116" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-4</t>
+          <t>doc14§5,doc15,doc18 4-5</t>
         </is>
       </c>
       <c r="G116" s="23" t="inlineStr">
@@ -11467,27 +11467,27 @@
       </c>
       <c r="B117" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C117" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
         </is>
       </c>
       <c r="D117" s="25" t="inlineStr">
         <is>
-          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
         </is>
       </c>
       <c r="E117" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-73,Ⅱ-75</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t>doc01-5,doc18 1-2</t>
+          <t>doc17 B-3,doc18 4-3</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -11505,27 +11505,27 @@
       </c>
       <c r="B118" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C118" s="25" t="inlineStr">
         <is>
-          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
         </is>
       </c>
       <c r="D118" s="25" t="inlineStr">
         <is>
-          <t>施策の書きぶりに影響。</t>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
         </is>
       </c>
       <c r="E118" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-72</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F118" s="23" t="inlineStr">
         <is>
-          <t>doc01-12</t>
+          <t>doc17 A-1,doc18 2-9</t>
         </is>
       </c>
       <c r="G118" s="23" t="inlineStr">
@@ -11543,27 +11543,27 @@
       </c>
       <c r="B119" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C119" s="25" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
         </is>
       </c>
       <c r="D119" s="25" t="inlineStr">
         <is>
-          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
         </is>
       </c>
       <c r="E119" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-64,Ⅱ-75</t>
         </is>
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-13</t>
+          <t>doc17 A-1,doc18 5-7</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
@@ -11581,27 +11581,27 @@
       </c>
       <c r="B120" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C120" s="25" t="inlineStr">
         <is>
-          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
         </is>
       </c>
       <c r="D120" s="25" t="inlineStr">
         <is>
-          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
         </is>
       </c>
       <c r="E120" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-31</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F120" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-6</t>
+          <t>doc08§8-4</t>
         </is>
       </c>
       <c r="G120" s="23" t="inlineStr">
@@ -11619,27 +11619,27 @@
       </c>
       <c r="B121" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C121" s="25" t="inlineStr">
         <is>
-          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
         </is>
       </c>
       <c r="D121" s="25" t="inlineStr">
         <is>
-          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
         </is>
       </c>
       <c r="E121" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-40,Ⅰ-42</t>
+          <t>Ⅱ-73,Ⅱ-75</t>
         </is>
       </c>
       <c r="F121" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-7</t>
+          <t>doc01-5,doc18 1-2</t>
         </is>
       </c>
       <c r="G121" s="23" t="inlineStr">
@@ -11657,27 +11657,27 @@
       </c>
       <c r="B122" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C122" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
         </is>
       </c>
       <c r="D122" s="25" t="inlineStr">
         <is>
-          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+          <t>施策の書きぶりに影響。</t>
         </is>
       </c>
       <c r="E122" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅱ-71,Ⅱ-72</t>
         </is>
       </c>
       <c r="F122" s="23" t="inlineStr">
         <is>
-          <t>doc23§1-3</t>
+          <t>doc01-12</t>
         </is>
       </c>
       <c r="G122" s="23" t="inlineStr">
@@ -11695,27 +11695,27 @@
       </c>
       <c r="B123" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C123" s="25" t="inlineStr">
         <is>
-          <t>送付状の個人情報に関する説明の補強</t>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
         </is>
       </c>
       <c r="D123" s="25" t="inlineStr">
         <is>
-          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
         </is>
       </c>
       <c r="E123" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t>doc27§5-1</t>
+          <t>doc19 追-13</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -11738,265 +11738,265 @@
       </c>
       <c r="C124" s="25" t="inlineStr">
         <is>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+        </is>
+      </c>
+      <c r="D124" s="25" t="inlineStr">
+        <is>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+        </is>
+      </c>
+      <c r="E124" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-31</t>
+        </is>
+      </c>
+      <c r="F124" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-6</t>
+        </is>
+      </c>
+      <c r="G124" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H124" s="25" t="inlineStr"/>
+    </row>
+    <row r="125" ht="34" customHeight="1">
+      <c r="A125" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B125" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C125" s="25" t="inlineStr">
+        <is>
+          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+        </is>
+      </c>
+      <c r="D125" s="25" t="inlineStr">
+        <is>
+          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+        </is>
+      </c>
+      <c r="E125" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-40,Ⅰ-42</t>
+        </is>
+      </c>
+      <c r="F125" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-7</t>
+        </is>
+      </c>
+      <c r="G125" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H125" s="25" t="inlineStr"/>
+    </row>
+    <row r="126" ht="34" customHeight="1">
+      <c r="A126" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B126" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C126" s="25" t="inlineStr">
+        <is>
+          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+        </is>
+      </c>
+      <c r="D126" s="25" t="inlineStr">
+        <is>
+          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+        </is>
+      </c>
+      <c r="E126" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-09</t>
+        </is>
+      </c>
+      <c r="F126" s="23" t="inlineStr">
+        <is>
+          <t>doc23§1-3</t>
+        </is>
+      </c>
+      <c r="G126" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H126" s="25" t="inlineStr"/>
+    </row>
+    <row r="127" ht="34" customHeight="1">
+      <c r="A127" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B127" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C127" s="25" t="inlineStr">
+        <is>
+          <t>送付状の個人情報に関する説明の補強</t>
+        </is>
+      </c>
+      <c r="D127" s="25" t="inlineStr">
+        <is>
+          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+        </is>
+      </c>
+      <c r="E127" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-14</t>
+        </is>
+      </c>
+      <c r="F127" s="23" t="inlineStr">
+        <is>
+          <t>doc27§5-1</t>
+        </is>
+      </c>
+      <c r="G127" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H127" s="25" t="inlineStr"/>
+    </row>
+    <row r="128" ht="34" customHeight="1">
+      <c r="A128" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B128" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C128" s="25" t="inlineStr">
+        <is>
           <t>ニーズ調査の選択肢の表記変更5件の可否（障がい表記・ぜひ・役場・移動販売・フルタイム）</t>
         </is>
       </c>
-      <c r="D124" s="25" t="inlineStr">
+      <c r="D128" s="25" t="inlineStr">
         <is>
           <t>村の表記ルール等による変更。手引きQ&amp;Aの「通称への置き換え」に近く多くは許容されると考えるが、「買い物（移動販売等※宅配は含まない）」のみ回答の範囲を広げる方向の変更で第9期・他保険者との比較に影響し得る。</t>
         </is>
       </c>
-      <c r="E124" s="23" t="inlineStr">
+      <c r="E128" s="23" t="inlineStr">
         <is>
           <t>Ⅰ-09</t>
         </is>
       </c>
-      <c r="F124" s="23" t="inlineStr">
+      <c r="F128" s="23" t="inlineStr">
         <is>
           <t>doc27§4</t>
         </is>
       </c>
-      <c r="G124" s="23" t="inlineStr">
+      <c r="G128" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H124" s="25" t="inlineStr"/>
-    </row>
-    <row r="125" ht="34" customHeight="1">
-      <c r="A125" s="38" t="inlineStr">
+      <c r="H128" s="25" t="inlineStr"/>
+    </row>
+    <row r="129" ht="34" customHeight="1">
+      <c r="A129" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B125" s="24" t="inlineStr">
+      <c r="B129" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C125" s="25" t="inlineStr">
+      <c r="C129" s="25" t="inlineStr">
         <is>
           <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
         </is>
       </c>
-      <c r="D125" s="25" t="inlineStr">
+      <c r="D129" s="25" t="inlineStr">
         <is>
           <t>第9期はA4・本文104頁・全6章＋資料編。</t>
         </is>
       </c>
-      <c r="E125" s="23" t="inlineStr">
+      <c r="E129" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-89</t>
         </is>
       </c>
-      <c r="F125" s="23" t="inlineStr">
+      <c r="F129" s="23" t="inlineStr">
         <is>
           <t>doc01-10</t>
         </is>
       </c>
-      <c r="G125" s="23" t="inlineStr">
+      <c r="G129" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H125" s="25" t="inlineStr"/>
-    </row>
-    <row r="126" ht="34" customHeight="1">
-      <c r="A126" s="38" t="inlineStr">
+      <c r="H129" s="25" t="inlineStr"/>
+    </row>
+    <row r="130" ht="34" customHeight="1">
+      <c r="A130" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B126" s="24" t="inlineStr">
+      <c r="B130" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C126" s="25" t="inlineStr">
+      <c r="C130" s="25" t="inlineStr">
         <is>
           <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
         </is>
       </c>
-      <c r="D126" s="25" t="inlineStr">
+      <c r="D130" s="25" t="inlineStr">
         <is>
           <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
         </is>
       </c>
-      <c r="E126" s="23" t="inlineStr">
+      <c r="E130" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-92</t>
         </is>
       </c>
-      <c r="F126" s="23" t="inlineStr">
+      <c r="F130" s="23" t="inlineStr">
         <is>
           <t>doc01-10,doc08</t>
         </is>
       </c>
-      <c r="G126" s="23" t="inlineStr">
+      <c r="G130" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H126" s="25" t="inlineStr"/>
-    </row>
-    <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="39" t="inlineStr">
+      <c r="H130" s="25" t="inlineStr"/>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="39" t="inlineStr">
         <is>
           <t>■ 解決済み（記録）</t>
         </is>
       </c>
-    </row>
-    <row r="129" ht="34" customHeight="1">
-      <c r="A129" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B129" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C129" s="42" t="inlineStr">
-        <is>
-          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
-        </is>
-      </c>
-      <c r="D129" s="42" t="inlineStr">
-        <is>
-          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
-        </is>
-      </c>
-      <c r="E129" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-68,Ⅱ-69</t>
-        </is>
-      </c>
-      <c r="F129" s="40" t="inlineStr">
-        <is>
-          <t>doc28§3</t>
-        </is>
-      </c>
-      <c r="G129" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H129" s="42" t="inlineStr"/>
-    </row>
-    <row r="130" ht="34" customHeight="1">
-      <c r="A130" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B130" s="41" t="inlineStr">
-        <is>
-          <t>体制</t>
-        </is>
-      </c>
-      <c r="C130" s="42" t="inlineStr">
-        <is>
-          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
-        </is>
-      </c>
-      <c r="D130" s="42" t="inlineStr">
-        <is>
-          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
-        </is>
-      </c>
-      <c r="E130" s="40" t="inlineStr">
-        <is>
-          <t>０-04</t>
-        </is>
-      </c>
-      <c r="F130" s="40" t="inlineStr">
-        <is>
-          <t>doc28§4</t>
-        </is>
-      </c>
-      <c r="G130" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H130" s="42" t="inlineStr"/>
-    </row>
-    <row r="131" ht="34" customHeight="1">
-      <c r="A131" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B131" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C131" s="42" t="inlineStr">
-        <is>
-          <t>所得段階別の第1号被保険者数</t>
-        </is>
-      </c>
-      <c r="D131" s="42" t="inlineStr">
-        <is>
-          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
-        </is>
-      </c>
-      <c r="E131" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F131" s="40" t="inlineStr">
-        <is>
-          <t>doc28§2</t>
-        </is>
-      </c>
-      <c r="G131" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H131" s="42" t="inlineStr"/>
-    </row>
-    <row r="132" ht="34" customHeight="1">
-      <c r="A132" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B132" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C132" s="42" t="inlineStr">
-        <is>
-          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
-        </is>
-      </c>
-      <c r="D132" s="42" t="inlineStr">
-        <is>
-          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
-        </is>
-      </c>
-      <c r="E132" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-59</t>
-        </is>
-      </c>
-      <c r="F132" s="40" t="inlineStr">
-        <is>
-          <t>doc28§1</t>
-        </is>
-      </c>
-      <c r="G132" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H132" s="42" t="inlineStr"/>
     </row>
     <row r="133" ht="34" customHeight="1">
       <c r="A133" s="40" t="inlineStr">
@@ -12006,32 +12006,32 @@
       </c>
       <c r="B133" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C133" s="42" t="inlineStr">
         <is>
-          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
+          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
         </is>
       </c>
       <c r="D133" s="42" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
+          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
         </is>
       </c>
       <c r="E133" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅱ-68,Ⅱ-69</t>
         </is>
       </c>
       <c r="F133" s="40" t="inlineStr">
         <is>
-          <t>doc27§1-1</t>
+          <t>doc28§3</t>
         </is>
       </c>
       <c r="G133" s="40" t="inlineStr">
         <is>
-          <t>解決済（一部再掲）</t>
+          <t>解決済</t>
         </is>
       </c>
       <c r="H133" s="42" t="inlineStr"/>
@@ -12044,27 +12044,27 @@
       </c>
       <c r="B134" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C134" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
+          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
         </is>
       </c>
       <c r="D134" s="42" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で両方とも修正済。</t>
+          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
         </is>
       </c>
       <c r="E134" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>０-04</t>
         </is>
       </c>
       <c r="F134" s="40" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc28§4</t>
         </is>
       </c>
       <c r="G134" s="40" t="inlineStr">
@@ -12082,32 +12082,32 @@
       </c>
       <c r="B135" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C135" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
+          <t>所得段階別の第1号被保険者数</t>
         </is>
       </c>
       <c r="D135" s="42" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
+          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
         </is>
       </c>
       <c r="E135" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F135" s="40" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc28§2</t>
         </is>
       </c>
       <c r="G135" s="40" t="inlineStr">
         <is>
-          <t>解決済（番号は再掲）</t>
+          <t>解決済</t>
         </is>
       </c>
       <c r="H135" s="42" t="inlineStr"/>
@@ -12120,27 +12120,27 @@
       </c>
       <c r="B136" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C136" s="42" t="inlineStr">
         <is>
-          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
+          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
         </is>
       </c>
       <c r="D136" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
+          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
         </is>
       </c>
       <c r="E136" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F136" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc28§1</t>
         </is>
       </c>
       <c r="G136" s="40" t="inlineStr">
@@ -12163,27 +12163,27 @@
       </c>
       <c r="C137" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 約150人の抽出基準</t>
+          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
         </is>
       </c>
       <c r="D137" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
+          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
         </is>
       </c>
       <c r="E137" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F137" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-1</t>
         </is>
       </c>
       <c r="G137" s="40" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（一部再掲）</t>
         </is>
       </c>
       <c r="H137" s="42" t="inlineStr"/>
@@ -12201,22 +12201,22 @@
       </c>
       <c r="C138" s="42" t="inlineStr">
         <is>
-          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
+          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
         </is>
       </c>
       <c r="D138" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
+          <t>第2稿（0904版）で両方とも修正済。</t>
         </is>
       </c>
       <c r="E138" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-25,Ⅰ-26</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F138" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G138" s="40" t="inlineStr">
@@ -12234,32 +12234,32 @@
       </c>
       <c r="B139" s="41" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C139" s="42" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の範囲</t>
+          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
         </is>
       </c>
       <c r="D139" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
         </is>
       </c>
       <c r="E139" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F139" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G139" s="40" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（番号は再掲）</t>
         </is>
       </c>
       <c r="H139" s="42" t="inlineStr"/>
@@ -12272,27 +12272,27 @@
       </c>
       <c r="B140" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C140" s="42" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="D140" s="42" t="inlineStr">
         <is>
-          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
         </is>
       </c>
       <c r="E140" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F140" s="40" t="inlineStr">
         <is>
-          <t>doc20§3,§4</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G140" s="40" t="inlineStr">
@@ -12310,27 +12310,27 @@
       </c>
       <c r="B141" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C141" s="42" t="inlineStr">
         <is>
-          <t>交付要綱の配点表（満点）</t>
+          <t>在宅介護実態調査 約150人の抽出基準</t>
         </is>
       </c>
       <c r="D141" s="42" t="inlineStr">
         <is>
-          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
         </is>
       </c>
       <c r="E141" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F141" s="40" t="inlineStr">
         <is>
-          <t>doc20§2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G141" s="40" t="inlineStr">
@@ -12348,27 +12348,27 @@
       </c>
       <c r="B142" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C142" s="42" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の交付金評価結果</t>
+          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
         </is>
       </c>
       <c r="D142" s="42" t="inlineStr">
         <is>
-          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
         </is>
       </c>
       <c r="E142" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-25,Ⅰ-26</t>
         </is>
       </c>
       <c r="F142" s="40" t="inlineStr">
         <is>
-          <t>doc20§3-1</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G142" s="40" t="inlineStr">
@@ -12386,27 +12386,27 @@
       </c>
       <c r="B143" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C143" s="42" t="inlineStr">
         <is>
-          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+          <t>整合を図る関連計画の範囲</t>
         </is>
       </c>
       <c r="D143" s="42" t="inlineStr">
         <is>
-          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
         </is>
       </c>
       <c r="E143" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-58</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F143" s="40" t="inlineStr">
         <is>
-          <t>doc09</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G143" s="40" t="inlineStr">
@@ -12429,22 +12429,22 @@
       </c>
       <c r="C144" s="42" t="inlineStr">
         <is>
-          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
         </is>
       </c>
       <c r="D144" s="42" t="inlineStr">
         <is>
-          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
         </is>
       </c>
       <c r="E144" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F144" s="40" t="inlineStr">
         <is>
-          <t>doc02§20-2</t>
+          <t>doc20§3,§4</t>
         </is>
       </c>
       <c r="G144" s="40" t="inlineStr">
@@ -12467,43 +12467,195 @@
       </c>
       <c r="C145" s="42" t="inlineStr">
         <is>
+          <t>交付要綱の配点表（満点）</t>
+        </is>
+      </c>
+      <c r="D145" s="42" t="inlineStr">
+        <is>
+          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+        </is>
+      </c>
+      <c r="E145" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F145" s="40" t="inlineStr">
+        <is>
+          <t>doc20§2</t>
+        </is>
+      </c>
+      <c r="G145" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H145" s="42" t="inlineStr"/>
+    </row>
+    <row r="146" ht="34" customHeight="1">
+      <c r="A146" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B146" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C146" s="42" t="inlineStr">
+        <is>
+          <t>令和6年度・令和7年度の交付金評価結果</t>
+        </is>
+      </c>
+      <c r="D146" s="42" t="inlineStr">
+        <is>
+          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+        </is>
+      </c>
+      <c r="E146" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F146" s="40" t="inlineStr">
+        <is>
+          <t>doc20§3-1</t>
+        </is>
+      </c>
+      <c r="G146" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H146" s="42" t="inlineStr"/>
+    </row>
+    <row r="147" ht="34" customHeight="1">
+      <c r="A147" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B147" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C147" s="42" t="inlineStr">
+        <is>
+          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+        </is>
+      </c>
+      <c r="D147" s="42" t="inlineStr">
+        <is>
+          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+        </is>
+      </c>
+      <c r="E147" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-56,Ⅱ-58</t>
+        </is>
+      </c>
+      <c r="F147" s="40" t="inlineStr">
+        <is>
+          <t>doc09</t>
+        </is>
+      </c>
+      <c r="G147" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H147" s="42" t="inlineStr"/>
+    </row>
+    <row r="148" ht="34" customHeight="1">
+      <c r="A148" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B148" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C148" s="42" t="inlineStr">
+        <is>
+          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+        </is>
+      </c>
+      <c r="D148" s="42" t="inlineStr">
+        <is>
+          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+        </is>
+      </c>
+      <c r="E148" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-59</t>
+        </is>
+      </c>
+      <c r="F148" s="40" t="inlineStr">
+        <is>
+          <t>doc02§20-2</t>
+        </is>
+      </c>
+      <c r="G148" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H148" s="42" t="inlineStr"/>
+    </row>
+    <row r="149" ht="34" customHeight="1">
+      <c r="A149" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B149" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C149" s="42" t="inlineStr">
+        <is>
           <t>国の指針・様式の更新有無</t>
         </is>
       </c>
-      <c r="D145" s="42" t="inlineStr">
+      <c r="D149" s="42" t="inlineStr">
         <is>
           <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
-      <c r="E145" s="40" t="inlineStr">
+      <c r="E149" s="40" t="inlineStr">
         <is>
           <t>Ⅰ-11</t>
         </is>
       </c>
-      <c r="F145" s="40" t="inlineStr">
+      <c r="F149" s="40" t="inlineStr">
         <is>
           <t>doc04,doc05</t>
         </is>
       </c>
-      <c r="G145" s="40" t="inlineStr">
+      <c r="G149" s="40" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H145" s="42" t="inlineStr"/>
+      <c r="H149" s="42" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H126"/>
+  <autoFilter ref="A4:H130"/>
   <mergeCells count="3">
-    <mergeCell ref="A128:H128"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A132:H132"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A126" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A130" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G126" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G130" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>
